--- a/settlements/spark/2026-05/spark_settlement_may_2026.xlsx
+++ b/settlements/spark/2026-05/spark_settlement_may_2026.xlsx
@@ -485,7 +485,7 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>13241479.69929383</v>
+        <v>8471023.892760478</v>
       </c>
     </row>
     <row r="5">
@@ -501,7 +501,7 @@
     <row r="6">
       <c r="A6" t="inlineStr"/>
       <c r="B6" s="4" t="n">
-        <v>13241479.69929383</v>
+        <v>8471023.892760478</v>
       </c>
     </row>
     <row r="8">
@@ -609,7 +609,7 @@
         </is>
       </c>
       <c r="B21" s="3" t="n">
-        <v>13241479.69929383</v>
+        <v>8471023.892760478</v>
       </c>
     </row>
     <row r="22">
@@ -625,7 +625,7 @@
     <row r="23">
       <c r="A23" t="inlineStr"/>
       <c r="B23" s="4" t="n">
-        <v>2499419.897254848</v>
+        <v>-2271035.909278506</v>
       </c>
     </row>
     <row r="25">
@@ -660,7 +660,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-06-05T08:18:56+00:00</t>
+          <t>2026-06-05T13:13:14+00:00</t>
         </is>
       </c>
     </row>
@@ -687,7 +687,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S54"/>
+  <dimension ref="A1:S58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -857,13 +857,13 @@
         <v>1</v>
       </c>
       <c r="N2" s="6" t="n">
-        <v>4296836.522018082</v>
+        <v>3142112.038726919</v>
       </c>
       <c r="O2" s="6" t="n">
-        <v>4296836.522018082</v>
+        <v>3142112.038726919</v>
       </c>
       <c r="P2" s="6" t="n">
-        <v>-4296836.522018082</v>
+        <v>-3142112.038726919</v>
       </c>
       <c r="Q2" s="6" t="n">
         <v>0</v>
@@ -876,12 +876,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>S3</t>
+          <t>S57</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Spark USDT (SparkLend spToken)</t>
+          <t>Spark Savings V2 — spUSDT vault</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -891,44 +891,44 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>S2</t>
         </is>
       </c>
       <c r="E3" s="6" t="n">
-        <v>677669071.17383</v>
+        <v>1134703231.016836</v>
       </c>
       <c r="F3" s="6" t="n">
-        <v>495837665.420656</v>
+        <v>1270360913.25412</v>
       </c>
       <c r="G3" s="6" t="n">
-        <v>-181831405.753174</v>
+        <v>135657682.237284</v>
       </c>
       <c r="H3" s="6" t="n">
-        <v>1868112.168236</v>
+        <v>-2595205.75030597</v>
       </c>
       <c r="I3" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J3" s="6" t="n">
-        <v>1868112.168236</v>
+        <v>-2595205.75030597</v>
       </c>
       <c r="K3" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L3" s="6" t="n">
-        <v>671743280.2731394</v>
+        <v>1134703231.016836</v>
       </c>
       <c r="M3" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N3" s="6" t="n">
-        <v>1518600.300159217</v>
+        <v>1875837.778435055</v>
       </c>
       <c r="O3" s="6" t="n">
-        <v>1518600.300159217</v>
+        <v>1875837.778435055</v>
       </c>
       <c r="P3" s="6" t="n">
-        <v>349511.868076783</v>
+        <v>-4471043.528741025</v>
       </c>
       <c r="Q3" s="6" t="n">
         <v>0</v>
@@ -941,12 +941,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>S28</t>
+          <t>S3</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>PYUSD raw (ALM idle — $677M as of 2026-04)</t>
+          <t>Spark USDT (SparkLend spToken)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -956,44 +956,44 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E4" s="6" t="n">
-        <v>677151123.07819</v>
+        <v>677669071.17383</v>
       </c>
       <c r="F4" s="6" t="n">
-        <v>262428227.923162</v>
+        <v>495837665.420656</v>
       </c>
       <c r="G4" s="6" t="n">
-        <v>-414722895.155028</v>
+        <v>-181831405.753174</v>
       </c>
       <c r="H4" s="6" t="n">
-        <v>3091580</v>
+        <v>1868112.168236</v>
       </c>
       <c r="I4" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J4" s="6" t="n">
-        <v>3091580</v>
+        <v>1868112.168236</v>
       </c>
       <c r="K4" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L4" s="6" t="n">
-        <v>615465268.6039779</v>
+        <v>671743280.2731394</v>
       </c>
       <c r="M4" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N4" s="6" t="n">
-        <v>1391373.414646642</v>
+        <v>1110494.257971797</v>
       </c>
       <c r="O4" s="6" t="n">
-        <v>1391373.414646642</v>
+        <v>1110494.257971797</v>
       </c>
       <c r="P4" s="6" t="n">
-        <v>1700206.585353358</v>
+        <v>757617.9102642025</v>
       </c>
       <c r="Q4" s="6" t="n">
         <v>0</v>
@@ -1006,12 +1006,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>S27</t>
+          <t>S28</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>USDT raw (ALM idle — $442M as of 2026-04)</t>
+          <t>PYUSD raw (ALM idle — $677M as of 2026-04)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1025,40 +1025,40 @@
         </is>
       </c>
       <c r="E5" s="6" t="n">
-        <v>483436565.922284</v>
+        <v>677151123.07819</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>608678684.51526</v>
+        <v>262428227.923162</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>125242118.592976</v>
+        <v>-414722895.155028</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>-194444.4444439532</v>
+        <v>3091580</v>
       </c>
       <c r="I5" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>-194444.4444439532</v>
+        <v>3091580</v>
       </c>
       <c r="K5" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L5" s="6" t="n">
-        <v>539754938.8825277</v>
+        <v>615465268.6039779</v>
       </c>
       <c r="M5" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>1220216.169287376</v>
+        <v>1017458.107638799</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>1220216.169287376</v>
+        <v>1017458.107638799</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>-1414660.61373133</v>
+        <v>2074121.892361201</v>
       </c>
       <c r="Q5" s="6" t="n">
         <v>0</v>
@@ -1071,12 +1071,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>S4</t>
+          <t>S56</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Spark DAI (SparkLend spToken)</t>
+          <t>Spark Savings V2 — spUSDC vault</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1086,131 +1086,127 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>S2</t>
         </is>
       </c>
       <c r="E6" s="6" t="n">
-        <v>266184835.4745756</v>
+        <v>573332157.534611</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>266960907.7112744</v>
+        <v>303545287.192935</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>776072.2366988341</v>
+        <v>-269786870.341676</v>
       </c>
       <c r="H6" s="6" t="n">
-        <v>559452.9392412193</v>
+        <v>-2077933.247665395</v>
       </c>
       <c r="I6" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J6" s="6" t="n">
-        <v>559452.9392412193</v>
+        <v>-2077933.247665395</v>
       </c>
       <c r="K6" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L6" s="6" t="n">
-        <v>179549416.5672932</v>
+        <v>573332157.534611</v>
       </c>
       <c r="M6" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N6" s="6" t="n">
-        <v>405904.7643642005</v>
+        <v>947805.6387759986</v>
       </c>
       <c r="O6" s="6" t="n">
-        <v>405904.7643642005</v>
+        <v>947805.6387759986</v>
       </c>
       <c r="P6" s="6" t="n">
-        <v>153548.1748770188</v>
+        <v>-3025738.886441393</v>
       </c>
       <c r="Q6" s="6" t="n">
-        <v>86642406.62655522</v>
+        <v>0</v>
       </c>
       <c r="R6" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>(avg excl. lending_idle)</t>
-        </is>
-      </c>
+      <c r="S6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>S43</t>
+          <t>S27</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Savings USDS / sUSDS proxy (Arbitrum — POL)</t>
+          <t>USDT raw (ALM idle — $442M as of 2026-04)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>arbitrum</t>
+          <t>ethereum</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E7" s="6" t="n">
-        <v>143328568.5311704</v>
+        <v>483436565.922284</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>143764611.5800855</v>
+        <v>608678684.51526</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>436043.0489150246</v>
+        <v>125242118.592976</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>0</v>
+        <v>-194444.4444439532</v>
       </c>
       <c r="I7" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J7" s="6" t="n">
-        <v>0</v>
+        <v>-194444.4444439532</v>
       </c>
       <c r="K7" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L7" s="6" t="n">
-        <v>143328568.5311704</v>
+        <v>539754938.8825277</v>
       </c>
       <c r="M7" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N7" s="6" t="n">
-        <v>324020.8180487098</v>
+        <v>892297.3670793462</v>
       </c>
       <c r="O7" s="6" t="n">
-        <v>287556.0042069121</v>
+        <v>892297.3670793462</v>
       </c>
       <c r="P7" s="6" t="n">
-        <v>-324020.8180487098</v>
+        <v>-1086741.811523299</v>
       </c>
       <c r="Q7" s="6" t="n">
         <v>0</v>
       </c>
       <c r="R7" s="6" t="n">
-        <v>36464.81384179761</v>
+        <v>0</v>
       </c>
       <c r="S7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>S14</t>
+          <t>S4</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Maple syrupUSDC (ERC-4626)</t>
+          <t>Spark DAI (SparkLend spToken)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1220,127 +1216,131 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E8" s="6" t="n">
-        <v>105306162.1077363</v>
+        <v>266184835.4745756</v>
       </c>
       <c r="F8" s="6" t="n">
-        <v>105300451.2530954</v>
+        <v>266960907.7112744</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>-5710.854640941099</v>
+        <v>776072.2366988341</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>423530.6085832017</v>
+        <v>559452.9392412193</v>
       </c>
       <c r="I8" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J8" s="6" t="n">
-        <v>423530.6085832017</v>
+        <v>559452.9392412193</v>
       </c>
       <c r="K8" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L8" s="6" t="n">
-        <v>105079212.3991508</v>
+        <v>179549416.5672932</v>
       </c>
       <c r="M8" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N8" s="6" t="n">
-        <v>237551.0528738895</v>
+        <v>296822.6136018681</v>
       </c>
       <c r="O8" s="6" t="n">
-        <v>237551.0528738895</v>
+        <v>296822.6136018681</v>
       </c>
       <c r="P8" s="6" t="n">
-        <v>185979.5557093121</v>
+        <v>262630.3256393512</v>
       </c>
       <c r="Q8" s="6" t="n">
-        <v>0</v>
+        <v>86642406.62655522</v>
       </c>
       <c r="R8" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="S8" t="inlineStr"/>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>(avg excl. lending_idle)</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>S5</t>
+          <t>S43</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Spark PYUSD (SparkLend spToken)</t>
+          <t>Savings USDS / sUSDS proxy (Arbitrum — POL)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>ethereum</t>
+          <t>arbitrum</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E9" s="6" t="n">
-        <v>100001095.915921</v>
+        <v>143328568.5311704</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>100000628.579333</v>
+        <v>143764611.5800855</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>-467.336588</v>
+        <v>436043.0489150246</v>
       </c>
       <c r="H9" s="6" t="n">
-        <v>29003.9707</v>
+        <v>0</v>
       </c>
       <c r="I9" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J9" s="6" t="n">
-        <v>29003.9707</v>
+        <v>0</v>
       </c>
       <c r="K9" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L9" s="6" t="n">
-        <v>100000145.2285891</v>
+        <v>143328568.5311704</v>
       </c>
       <c r="M9" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N9" s="6" t="n">
-        <v>226068.8793170397</v>
+        <v>236944.0186918778</v>
       </c>
       <c r="O9" s="6" t="n">
-        <v>226068.8793170397</v>
+        <v>200479.2048500802</v>
       </c>
       <c r="P9" s="6" t="n">
-        <v>-197064.9086170397</v>
+        <v>-236944.0186918778</v>
       </c>
       <c r="Q9" s="6" t="n">
         <v>0</v>
       </c>
       <c r="R9" s="6" t="n">
-        <v>0</v>
+        <v>36464.81384179761</v>
       </c>
       <c r="S9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>S25</t>
+          <t>S14</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Spark.fi PYUSD Reserve Curve (PYUSD/USDS)</t>
+          <t>Maple syrupUSDC (ERC-4626)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1350,44 +1350,44 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E10" s="6" t="n">
-        <v>99998676.75316638</v>
+        <v>105306162.1077363</v>
       </c>
       <c r="F10" s="6" t="n">
-        <v>99999260.90933624</v>
+        <v>105300451.2530954</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>584.1561698611263</v>
+        <v>-5710.854640941099</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>6385.883871640342</v>
+        <v>423530.6085832017</v>
       </c>
       <c r="I10" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J10" s="6" t="n">
-        <v>6385.883871640342</v>
+        <v>423530.6085832017</v>
       </c>
       <c r="K10" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L10" s="6" t="n">
-        <v>99998489.60065988</v>
+        <v>105079212.3991508</v>
       </c>
       <c r="M10" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N10" s="6" t="n">
-        <v>226065.1364629701</v>
+        <v>173711.9900239393</v>
       </c>
       <c r="O10" s="6" t="n">
-        <v>226065.1364629701</v>
+        <v>173711.9900239393</v>
       </c>
       <c r="P10" s="6" t="n">
-        <v>-219679.2525913298</v>
+        <v>249818.6185592623</v>
       </c>
       <c r="Q10" s="6" t="n">
         <v>0</v>
@@ -1400,77 +1400,77 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>S47</t>
+          <t>S5</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Savings USDS / sUSDS proxy (Optimism — POL)</t>
+          <t>Spark PYUSD (SparkLend spToken)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>optimism</t>
+          <t>ethereum</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E11" s="6" t="n">
-        <v>102040993.0313656</v>
+        <v>100001095.915921</v>
       </c>
       <c r="F11" s="6" t="n">
-        <v>102351428.4607548</v>
+        <v>100000628.579333</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>310435.429389201</v>
+        <v>-467.336588</v>
       </c>
       <c r="H11" s="6" t="n">
-        <v>0</v>
+        <v>29003.9707</v>
       </c>
       <c r="I11" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J11" s="6" t="n">
-        <v>0</v>
+        <v>29003.9707</v>
       </c>
       <c r="K11" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L11" s="6" t="n">
-        <v>102040993.0313656</v>
+        <v>100000145.2285891</v>
       </c>
       <c r="M11" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N11" s="6" t="n">
-        <v>230682.5943729096</v>
+        <v>165315.5161113631</v>
       </c>
       <c r="O11" s="6" t="n">
-        <v>204721.9233548933</v>
+        <v>165315.5161113631</v>
       </c>
       <c r="P11" s="6" t="n">
-        <v>-230682.5943729096</v>
+        <v>-136311.5454113631</v>
       </c>
       <c r="Q11" s="6" t="n">
         <v>0</v>
       </c>
       <c r="R11" s="6" t="n">
-        <v>25960.67101801626</v>
+        <v>0</v>
       </c>
       <c r="S11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>S11</t>
+          <t>S25</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Spark Blue Chip USDT Vault (Morpho V2)</t>
+          <t>Spark.fi PYUSD Reserve Curve (PYUSD/USDS)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1480,44 +1480,44 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>F</t>
         </is>
       </c>
       <c r="E12" s="6" t="n">
-        <v>51710579.95350124</v>
+        <v>99998676.75316638</v>
       </c>
       <c r="F12" s="6" t="n">
-        <v>71943502.10038626</v>
+        <v>99999260.90933624</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>20232922.14688502</v>
+        <v>584.1561698611263</v>
       </c>
       <c r="H12" s="6" t="n">
-        <v>217269.3964465584</v>
+        <v>6385.883871640342</v>
       </c>
       <c r="I12" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J12" s="6" t="n">
-        <v>217269.3964465584</v>
+        <v>6385.883871640342</v>
       </c>
       <c r="K12" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L12" s="6" t="n">
-        <v>89619946.74579927</v>
+        <v>99998489.60065988</v>
       </c>
       <c r="M12" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N12" s="6" t="n">
-        <v>202602.5150159821</v>
+        <v>165312.7791054819</v>
       </c>
       <c r="O12" s="6" t="n">
-        <v>202602.5150159821</v>
+        <v>165312.7791054819</v>
       </c>
       <c r="P12" s="6" t="n">
-        <v>14666.8814305762</v>
+        <v>-158926.8952338415</v>
       </c>
       <c r="Q12" s="6" t="n">
         <v>0</v>
@@ -1530,17 +1530,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>S37</t>
+          <t>S11</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Savings USDS / sUSDS proxy (Base — POL)</t>
+          <t>Spark Blue Chip USDT Vault (Morpho V2)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>base</t>
+          <t>ethereum</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1549,139 +1549,143 @@
         </is>
       </c>
       <c r="E13" s="6" t="n">
-        <v>75772907.26348835</v>
+        <v>51710579.95350124</v>
       </c>
       <c r="F13" s="6" t="n">
-        <v>76003428.29531698</v>
+        <v>71943502.10038626</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>230521.0318286367</v>
+        <v>20232922.14688502</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>0</v>
+        <v>217269.3964465584</v>
       </c>
       <c r="I13" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J13" s="6" t="n">
-        <v>0</v>
+        <v>217269.3964465584</v>
       </c>
       <c r="K13" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L13" s="6" t="n">
-        <v>75772907.26348835</v>
+        <v>89619946.74579927</v>
       </c>
       <c r="M13" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N13" s="6" t="n">
-        <v>171298.7135018031</v>
+        <v>148155.4623374592</v>
       </c>
       <c r="O13" s="6" t="n">
-        <v>152021.0148131847</v>
+        <v>148155.4623374592</v>
       </c>
       <c r="P13" s="6" t="n">
-        <v>-171298.7135018031</v>
+        <v>69113.93410909919</v>
       </c>
       <c r="Q13" s="6" t="n">
         <v>0</v>
       </c>
       <c r="R13" s="6" t="n">
-        <v>19277.6986886184</v>
+        <v>0</v>
       </c>
       <c r="S13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>S1</t>
+          <t>S47</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Spark USDS (SparkLend spToken)</t>
+          <t>Savings USDS / sUSDS proxy (Optimism — POL)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>ethereum</t>
+          <t>optimism</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E14" s="6" t="n">
-        <v>147862782.1336161</v>
+        <v>102040993.0313656</v>
       </c>
       <c r="F14" s="6" t="n">
-        <v>550178045.362034</v>
+        <v>102351428.4607548</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>402315263.2284179</v>
+        <v>310435.429389201</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>294091.516876444</v>
+        <v>0</v>
       </c>
       <c r="I14" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J14" s="6" t="n">
-        <v>294091.516876444</v>
+        <v>0</v>
       </c>
       <c r="K14" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L14" s="6" t="n">
-        <v>57731388.11709616</v>
+        <v>102040993.0313656</v>
       </c>
       <c r="M14" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N14" s="6" t="n">
-        <v>130512.5125890093</v>
+        <v>168689.3492898001</v>
       </c>
       <c r="O14" s="6" t="n">
-        <v>130512.5125890093</v>
+        <v>142728.6782717838</v>
       </c>
       <c r="P14" s="6" t="n">
-        <v>163579.0042874348</v>
+        <v>-168689.3492898001</v>
       </c>
       <c r="Q14" s="6" t="n">
-        <v>103099818.9104406</v>
+        <v>0</v>
       </c>
       <c r="R14" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S14" t="inlineStr">
-        <is>
-          <t>(avg excl. lending_idle)</t>
-        </is>
-      </c>
+        <v>25960.67101801626</v>
+      </c>
+      <c r="S14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>SPREAD</t>
+          <t>S37</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>30bps sUSDS spread (Curve LP + PSM3) — Sky Revenue reduction</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr"/>
+          <t>Savings USDS / sUSDS proxy (Base — POL)</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>base</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
       <c r="E15" s="6" t="n">
-        <v>0</v>
+        <v>75772907.26348835</v>
       </c>
       <c r="F15" s="6" t="n">
-        <v>0</v>
+        <v>76003428.29531698</v>
       </c>
       <c r="G15" s="6" t="n">
-        <v>0</v>
+        <v>230521.0318286367</v>
       </c>
       <c r="H15" s="6" t="n">
         <v>0</v>
@@ -1696,64 +1700,52 @@
         <v>0</v>
       </c>
       <c r="L15" s="6" t="n">
-        <v>0</v>
+        <v>75772907.26348835</v>
       </c>
       <c r="M15" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N15" s="6" t="n">
-        <v>0</v>
+        <v>125264.1907958033</v>
       </c>
       <c r="O15" s="6" t="n">
-        <v>-102957.2966175266</v>
+        <v>105986.4921071849</v>
       </c>
       <c r="P15" s="6" t="n">
-        <v>0</v>
+        <v>-125264.1907958033</v>
       </c>
       <c r="Q15" s="6" t="n">
         <v>0</v>
       </c>
       <c r="R15" s="6" t="n">
-        <v>102957.2966175266</v>
-      </c>
-      <c r="S15" t="inlineStr">
-        <is>
-          <t>sky-revenue reduction (no CoF; computed outside venue loop)</t>
-        </is>
-      </c>
+        <v>19277.6986886184</v>
+      </c>
+      <c r="S15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>S24</t>
+          <t>SPREAD</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Spark.fi USDT Reserve Curve (sUSDS/USDT)</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>ethereum</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
+          <t>30bps sUSDS spread (Curve LP + PSM3) — Sky Revenue reduction</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr"/>
       <c r="E16" s="6" t="n">
-        <v>50002415.26289953</v>
+        <v>0</v>
       </c>
       <c r="F16" s="6" t="n">
-        <v>48750265.64989898</v>
+        <v>0</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>-1252149.613000547</v>
+        <v>0</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>74156.06084450937</v>
+        <v>0</v>
       </c>
       <c r="I16" s="6" t="n">
         <v>0</v>
@@ -1762,10 +1754,10 @@
         <v>0</v>
       </c>
       <c r="K16" s="6" t="n">
-        <v>74156.06084450937</v>
+        <v>0</v>
       </c>
       <c r="L16" s="6" t="n">
-        <v>49959631.20890453</v>
+        <v>0</v>
       </c>
       <c r="M16" s="7" t="n">
         <v>0</v>
@@ -1774,32 +1766,32 @@
         <v>0</v>
       </c>
       <c r="O16" s="6" t="n">
-        <v>74156.06084450937</v>
+        <v>-102957.2966175266</v>
       </c>
       <c r="P16" s="6" t="n">
         <v>0</v>
       </c>
       <c r="Q16" s="6" t="n">
-        <v>49959631.20890453</v>
+        <v>0</v>
       </c>
       <c r="R16" s="6" t="n">
-        <v>0</v>
+        <v>102957.2966175266</v>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>SDE (fixed)</t>
+          <t>sky-revenue reduction (no CoF; computed outside venue loop)</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>S15</t>
+          <t>S1</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Maple syrupUSDT (ERC-4626)</t>
+          <t>Spark USDS (SparkLend spToken)</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1809,62 +1801,66 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E17" s="6" t="n">
-        <v>76904851.98939763</v>
+        <v>147862782.1336161</v>
       </c>
       <c r="F17" s="6" t="n">
-        <v>0</v>
+        <v>550178045.362034</v>
       </c>
       <c r="G17" s="6" t="n">
-        <v>-76904851.98939763</v>
+        <v>402315263.2284179</v>
       </c>
       <c r="H17" s="6" t="n">
-        <v>119641.6179259726</v>
+        <v>294091.516876444</v>
       </c>
       <c r="I17" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J17" s="6" t="n">
-        <v>119641.6179259726</v>
+        <v>294091.516876444</v>
       </c>
       <c r="K17" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L17" s="6" t="n">
-        <v>29672997.14110577</v>
+        <v>57731388.11709616</v>
       </c>
       <c r="M17" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N17" s="6" t="n">
-        <v>67081.31467542819</v>
+        <v>95438.8036196037</v>
       </c>
       <c r="O17" s="6" t="n">
-        <v>67081.31467542819</v>
+        <v>95438.8036196037</v>
       </c>
       <c r="P17" s="6" t="n">
-        <v>52560.30325054442</v>
+        <v>198652.7132568404</v>
       </c>
       <c r="Q17" s="6" t="n">
-        <v>0</v>
+        <v>103099818.9104406</v>
       </c>
       <c r="R17" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="S17" t="inlineStr"/>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>(avg excl. lending_idle)</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>S18</t>
+          <t>S24</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Arkis Spark Prime USDC 1 (ERC-4626)</t>
+          <t>Spark.fi USDT Reserve Curve (sUSDS/USDT)</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1874,109 +1870,113 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>F</t>
         </is>
       </c>
       <c r="E18" s="6" t="n">
-        <v>0.28330096818</v>
+        <v>50002415.26289953</v>
       </c>
       <c r="F18" s="6" t="n">
-        <v>15021342.65332295</v>
+        <v>48750265.64989898</v>
       </c>
       <c r="G18" s="6" t="n">
-        <v>15021342.37002198</v>
+        <v>-1252149.613000547</v>
       </c>
       <c r="H18" s="6" t="n">
-        <v>21701.47150269761</v>
+        <v>74156.06084450937</v>
       </c>
       <c r="I18" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J18" s="6" t="n">
-        <v>21701.47150269761</v>
+        <v>0</v>
       </c>
       <c r="K18" s="6" t="n">
-        <v>0</v>
+        <v>74156.06084450937</v>
       </c>
       <c r="L18" s="6" t="n">
-        <v>9516094.162770383</v>
+        <v>49959631.20890453</v>
       </c>
       <c r="M18" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N18" s="6" t="n">
-        <v>21512.89618565363</v>
+        <v>0</v>
       </c>
       <c r="O18" s="6" t="n">
-        <v>21512.89618565363</v>
+        <v>74156.06084450937</v>
       </c>
       <c r="P18" s="6" t="n">
-        <v>188.575317043982</v>
+        <v>0</v>
       </c>
       <c r="Q18" s="6" t="n">
-        <v>0</v>
+        <v>49959631.20890453</v>
       </c>
       <c r="R18" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="S18" t="inlineStr"/>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>SDE (fixed)</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>S60</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Spark Savings V2 — spUSDC vault (Avalanche-C, CREATE2 same address)</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>avalanche_c</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
           <t>S2</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Spark USDC (SparkLend spToken)</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>ethereum</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
       <c r="E19" s="6" t="n">
-        <v>9229822.108306</v>
+        <v>37138817.432463</v>
       </c>
       <c r="F19" s="6" t="n">
-        <v>12183497.214187</v>
+        <v>25647247.422478</v>
       </c>
       <c r="G19" s="6" t="n">
-        <v>2953675.105881</v>
+        <v>-11491570.009985</v>
       </c>
       <c r="H19" s="6" t="n">
-        <v>32502.903353</v>
+        <v>-94676.37115954701</v>
       </c>
       <c r="I19" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J19" s="6" t="n">
-        <v>32502.903353</v>
+        <v>-94676.37115954701</v>
       </c>
       <c r="K19" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L19" s="6" t="n">
-        <v>9324053.469677871</v>
+        <v>37138817.432463</v>
       </c>
       <c r="M19" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N19" s="6" t="n">
-        <v>21078.75257344736</v>
+        <v>61396.1385513873</v>
       </c>
       <c r="O19" s="6" t="n">
-        <v>21078.75257344736</v>
+        <v>61396.1385513873</v>
       </c>
       <c r="P19" s="6" t="n">
-        <v>11424.15077955264</v>
+        <v>-156072.5097109343</v>
       </c>
       <c r="Q19" s="6" t="n">
         <v>0</v>
@@ -1989,59 +1989,59 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>S39</t>
+          <t>S15</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>USDC raw (Base — ALM idle)</t>
+          <t>Maple syrupUSDT (ERC-4626)</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>base</t>
+          <t>ethereum</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E20" s="6" t="n">
-        <v>5000000</v>
+        <v>76904851.98939763</v>
       </c>
       <c r="F20" s="6" t="n">
-        <v>4997576.708614</v>
+        <v>0</v>
       </c>
       <c r="G20" s="6" t="n">
-        <v>-2423.291386</v>
+        <v>-76904851.98939763</v>
       </c>
       <c r="H20" s="6" t="n">
-        <v>2.228968e-09</v>
+        <v>119641.6179259726</v>
       </c>
       <c r="I20" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J20" s="6" t="n">
-        <v>2.228968e-09</v>
+        <v>119641.6179259726</v>
       </c>
       <c r="K20" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L20" s="6" t="n">
-        <v>4999001.686505451</v>
+        <v>29672997.14110577</v>
       </c>
       <c r="M20" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N20" s="6" t="n">
-        <v>11301.17067719206</v>
+        <v>49053.99712910109</v>
       </c>
       <c r="O20" s="6" t="n">
-        <v>11301.17067719206</v>
+        <v>49053.99712910109</v>
       </c>
       <c r="P20" s="6" t="n">
-        <v>-11301.17067718983</v>
+        <v>70587.62079687153</v>
       </c>
       <c r="Q20" s="6" t="n">
         <v>0</v>
@@ -2054,59 +2054,59 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>S49</t>
+          <t>S18</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>USDC raw (Optimism — ALM idle)</t>
+          <t>Arkis Spark Prime USDC 1 (ERC-4626)</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>optimism</t>
+          <t>ethereum</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E21" s="6" t="n">
-        <v>5000000</v>
+        <v>0.28330096818</v>
       </c>
       <c r="F21" s="6" t="n">
-        <v>5019997.4</v>
+        <v>15021342.65332295</v>
       </c>
       <c r="G21" s="6" t="n">
-        <v>19997.4</v>
+        <v>15021342.37002198</v>
       </c>
       <c r="H21" s="6" t="n">
-        <v>1.8405064066e-10</v>
+        <v>21701.47150269761</v>
       </c>
       <c r="I21" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J21" s="6" t="n">
-        <v>1.8405064066e-10</v>
+        <v>21701.47150269761</v>
       </c>
       <c r="K21" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L21" s="6" t="n">
-        <v>4998671.605324483</v>
+        <v>9516094.162770383</v>
       </c>
       <c r="M21" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N21" s="6" t="n">
-        <v>11300.42446744912</v>
+        <v>15731.55733210839</v>
       </c>
       <c r="O21" s="6" t="n">
-        <v>11300.42446744912</v>
+        <v>15731.55733210839</v>
       </c>
       <c r="P21" s="6" t="n">
-        <v>-11300.42446744894</v>
+        <v>5969.914170589217</v>
       </c>
       <c r="Q21" s="6" t="n">
         <v>0</v>
@@ -2119,59 +2119,59 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>S53</t>
+          <t>S2</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>USDC raw (Unichain — ALM idle)</t>
+          <t>Spark USDC (SparkLend spToken)</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>unichain</t>
+          <t>ethereum</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E22" s="6" t="n">
-        <v>4996314.282982</v>
+        <v>9229822.108306</v>
       </c>
       <c r="F22" s="6" t="n">
-        <v>4992819.462732</v>
+        <v>12183497.214187</v>
       </c>
       <c r="G22" s="6" t="n">
-        <v>-3494.82025</v>
+        <v>2953675.105881</v>
       </c>
       <c r="H22" s="6" t="n">
-        <v>0</v>
+        <v>32502.903353</v>
       </c>
       <c r="I22" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J22" s="6" t="n">
-        <v>0</v>
+        <v>32502.903353</v>
       </c>
       <c r="K22" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L22" s="6" t="n">
-        <v>4997744.737919419</v>
+        <v>9324053.469677871</v>
       </c>
       <c r="M22" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N22" s="6" t="n">
-        <v>11298.32911173679</v>
+        <v>15414.08473023965</v>
       </c>
       <c r="O22" s="6" t="n">
-        <v>11298.32911173679</v>
+        <v>15414.08473023965</v>
       </c>
       <c r="P22" s="6" t="n">
-        <v>-11298.32911173679</v>
+        <v>17088.81862276035</v>
       </c>
       <c r="Q22" s="6" t="n">
         <v>0</v>
@@ -2184,17 +2184,17 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>S45</t>
+          <t>S39</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>USDC raw (Arbitrum — ALM idle)</t>
+          <t>USDC raw (Base — ALM idle)</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>arbitrum</t>
+          <t>base</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -2203,40 +2203,40 @@
         </is>
       </c>
       <c r="E23" s="6" t="n">
-        <v>5009602.263622</v>
+        <v>5000000</v>
       </c>
       <c r="F23" s="6" t="n">
-        <v>4975417.167355</v>
+        <v>4997576.708614</v>
       </c>
       <c r="G23" s="6" t="n">
-        <v>-34185.096267</v>
+        <v>-2423.291386</v>
       </c>
       <c r="H23" s="6" t="n">
-        <v>4.7e-10</v>
+        <v>2.228968e-09</v>
       </c>
       <c r="I23" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J23" s="6" t="n">
-        <v>4.7e-10</v>
+        <v>2.228968e-09</v>
       </c>
       <c r="K23" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L23" s="6" t="n">
-        <v>4954536.773106677</v>
+        <v>4999001.686505451</v>
       </c>
       <c r="M23" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N23" s="6" t="n">
-        <v>11200.64949176766</v>
+        <v>8264.113436606884</v>
       </c>
       <c r="O23" s="6" t="n">
-        <v>11200.64949176766</v>
+        <v>8264.113436606884</v>
       </c>
       <c r="P23" s="6" t="n">
-        <v>-11200.64949176719</v>
+        <v>-8264.113436604654</v>
       </c>
       <c r="Q23" s="6" t="n">
         <v>0</v>
@@ -2249,59 +2249,59 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>S10</t>
+          <t>S49</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Spark Blue Chip USDC Vault (Morpho)</t>
+          <t>USDC raw (Optimism — ALM idle)</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>ethereum</t>
+          <t>optimism</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E24" s="6" t="n">
-        <v>704090.8045421393</v>
+        <v>5000000</v>
       </c>
       <c r="F24" s="6" t="n">
-        <v>3501087.141508509</v>
+        <v>5019997.4</v>
       </c>
       <c r="G24" s="6" t="n">
-        <v>2796996.33696637</v>
+        <v>19997.4</v>
       </c>
       <c r="H24" s="6" t="n">
-        <v>609955.0966986277</v>
+        <v>1.8405064066e-10</v>
       </c>
       <c r="I24" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J24" s="6" t="n">
-        <v>609955.0966986277</v>
+        <v>1.8405064066e-10</v>
       </c>
       <c r="K24" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L24" s="6" t="n">
-        <v>1472511.375313347</v>
+        <v>4998671.605324483</v>
       </c>
       <c r="M24" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N24" s="6" t="n">
-        <v>3328.885129493906</v>
+        <v>8263.567761991457</v>
       </c>
       <c r="O24" s="6" t="n">
-        <v>3328.885129493906</v>
+        <v>8263.567761991457</v>
       </c>
       <c r="P24" s="6" t="n">
-        <v>606626.2115691338</v>
+        <v>-8263.567761991273</v>
       </c>
       <c r="Q24" s="6" t="n">
         <v>0</v>
@@ -2314,12 +2314,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>S51</t>
+          <t>S53</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Savings USDS / sUSDS proxy (Unichain — POL)</t>
+          <t>USDC raw (Unichain — ALM idle)</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -2329,17 +2329,17 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E25" s="6" t="n">
-        <v>982408.1850699954</v>
+        <v>4996314.282982</v>
       </c>
       <c r="F25" s="6" t="n">
-        <v>985396.9281006901</v>
+        <v>4992819.462732</v>
       </c>
       <c r="G25" s="6" t="n">
-        <v>2988.743030694792</v>
+        <v>-3494.82025</v>
       </c>
       <c r="H25" s="6" t="n">
         <v>0</v>
@@ -2354,84 +2354,84 @@
         <v>0</v>
       </c>
       <c r="L25" s="6" t="n">
-        <v>982408.1850699954</v>
+        <v>4997744.737919419</v>
       </c>
       <c r="M25" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N25" s="6" t="n">
-        <v>2220.91594890171</v>
+        <v>8262.035508582376</v>
       </c>
       <c r="O25" s="6" t="n">
-        <v>1970.977419881622</v>
+        <v>8262.035508582376</v>
       </c>
       <c r="P25" s="6" t="n">
-        <v>-2220.91594890171</v>
+        <v>-8262.035508582376</v>
       </c>
       <c r="Q25" s="6" t="n">
         <v>0</v>
       </c>
       <c r="R25" s="6" t="n">
-        <v>249.9385290200882</v>
+        <v>0</v>
       </c>
       <c r="S25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>S12</t>
+          <t>S45</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Spark DAI Vault (Morpho)</t>
+          <t>USDC raw (Arbitrum — ALM idle)</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>ethereum</t>
+          <t>arbitrum</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E26" s="6" t="n">
-        <v>458.5728307677575</v>
+        <v>5009602.263622</v>
       </c>
       <c r="F26" s="6" t="n">
-        <v>539.8728953809741</v>
+        <v>4975417.167355</v>
       </c>
       <c r="G26" s="6" t="n">
-        <v>81.30006461321658</v>
+        <v>-34185.096267</v>
       </c>
       <c r="H26" s="6" t="n">
-        <v>76.33046551920575</v>
+        <v>4.7e-10</v>
       </c>
       <c r="I26" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J26" s="6" t="n">
-        <v>76.33046551920575</v>
+        <v>4.7e-10</v>
       </c>
       <c r="K26" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L26" s="6" t="n">
-        <v>462.161691889013</v>
+        <v>4954536.773106677</v>
       </c>
       <c r="M26" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N26" s="6" t="n">
-        <v>1.044802240134609</v>
+        <v>8190.606142286837</v>
       </c>
       <c r="O26" s="6" t="n">
-        <v>1.044802240134609</v>
+        <v>8190.606142286837</v>
       </c>
       <c r="P26" s="6" t="n">
-        <v>75.28566327907113</v>
+        <v>-8190.606142286368</v>
       </c>
       <c r="Q26" s="6" t="n">
         <v>0</v>
@@ -2444,17 +2444,17 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>S34</t>
+          <t>S10</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Spark USDC Vault (Morpho, Base)</t>
+          <t>Spark Blue Chip USDC Vault (Morpho)</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>base</t>
+          <t>ethereum</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -2463,40 +2463,40 @@
         </is>
       </c>
       <c r="E27" s="6" t="n">
-        <v>224.7175624853434</v>
+        <v>704090.8045421393</v>
       </c>
       <c r="F27" s="6" t="n">
-        <v>424.9110349025811</v>
+        <v>3501087.141508509</v>
       </c>
       <c r="G27" s="6" t="n">
-        <v>200.1934724172377</v>
+        <v>2796996.33696637</v>
       </c>
       <c r="H27" s="6" t="n">
-        <v>1.161345275337778</v>
+        <v>609955.0966986277</v>
       </c>
       <c r="I27" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J27" s="6" t="n">
-        <v>1.161345275337778</v>
+        <v>609955.0966986277</v>
       </c>
       <c r="K27" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L27" s="6" t="n">
-        <v>368.0420981576889</v>
+        <v>1472511.375313347</v>
       </c>
       <c r="M27" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N27" s="6" t="n">
-        <v>0.8320274383782968</v>
+        <v>2434.286244618223</v>
       </c>
       <c r="O27" s="6" t="n">
-        <v>0.8320274383782968</v>
+        <v>2434.286244618223</v>
       </c>
       <c r="P27" s="6" t="n">
-        <v>0.3293178369594812</v>
+        <v>607520.8104540096</v>
       </c>
       <c r="Q27" s="6" t="n">
         <v>0</v>
@@ -2509,59 +2509,59 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>S36</t>
+          <t>S59</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Fluid Savings USDS (fsUSDS, Base)</t>
+          <t>Spark Savings V2 — spPYUSD vault</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>base</t>
+          <t>ethereum</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>S2</t>
         </is>
       </c>
       <c r="E28" s="6" t="n">
-        <v>283.8972488542868</v>
+        <v>1066559.875133</v>
       </c>
       <c r="F28" s="6" t="n">
-        <v>283.8972488542868</v>
+        <v>773533.783718</v>
       </c>
       <c r="G28" s="6" t="n">
-        <v>0</v>
+        <v>-293026.091415</v>
       </c>
       <c r="H28" s="6" t="n">
-        <v>0</v>
+        <v>-2640.43740244277</v>
       </c>
       <c r="I28" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J28" s="6" t="n">
-        <v>0</v>
+        <v>-2640.43740244277</v>
       </c>
       <c r="K28" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L28" s="6" t="n">
-        <v>283.8972488542868</v>
+        <v>1066559.875133</v>
       </c>
       <c r="M28" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N28" s="6" t="n">
-        <v>0.6418023968162277</v>
+        <v>1763.186401562094</v>
       </c>
       <c r="O28" s="6" t="n">
-        <v>0.6418023968162277</v>
+        <v>1763.186401562094</v>
       </c>
       <c r="P28" s="6" t="n">
-        <v>-0.6418023968162277</v>
+        <v>-4403.623804004864</v>
       </c>
       <c r="Q28" s="6" t="n">
         <v>0</v>
@@ -2574,77 +2574,77 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>S55</t>
+          <t>S51</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>USDC raw (Avalanche-C — ALM idle)</t>
+          <t>Savings USDS / sUSDS proxy (Unichain — POL)</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>avalanche_c</t>
+          <t>unichain</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E29" s="6" t="n">
-        <v>2500.221225</v>
+        <v>982408.1850699954</v>
       </c>
       <c r="F29" s="6" t="n">
-        <v>0</v>
+        <v>985396.9281006901</v>
       </c>
       <c r="G29" s="6" t="n">
-        <v>-2500.221225</v>
+        <v>2988.743030694792</v>
       </c>
       <c r="H29" s="6" t="n">
-        <v>-3.30458807350886e-10</v>
+        <v>0</v>
       </c>
       <c r="I29" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J29" s="6" t="n">
-        <v>-3.30458807350886e-10</v>
+        <v>0</v>
       </c>
       <c r="K29" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L29" s="6" t="n">
-        <v>115.3103732260555</v>
+        <v>982408.1850699954</v>
       </c>
       <c r="M29" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N29" s="6" t="n">
-        <v>0.2606804899058419</v>
+        <v>1624.070802853624</v>
       </c>
       <c r="O29" s="6" t="n">
-        <v>0.2606804899058419</v>
+        <v>1374.132273833536</v>
       </c>
       <c r="P29" s="6" t="n">
-        <v>-0.2606804902363007</v>
+        <v>-1624.070802853624</v>
       </c>
       <c r="Q29" s="6" t="n">
         <v>0</v>
       </c>
       <c r="R29" s="6" t="n">
-        <v>0</v>
+        <v>249.9385290200882</v>
       </c>
       <c r="S29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>S16</t>
+          <t>S12</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Ethena Staked USDe (sUSDe)</t>
+          <t>Spark DAI Vault (Morpho)</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2658,40 +2658,40 @@
         </is>
       </c>
       <c r="E30" s="6" t="n">
-        <v>99.50129408753318</v>
+        <v>458.5728307677575</v>
       </c>
       <c r="F30" s="6" t="n">
-        <v>99.81305763596731</v>
+        <v>539.8728953809741</v>
       </c>
       <c r="G30" s="6" t="n">
-        <v>0.3117635484341261</v>
+        <v>81.30006461321658</v>
       </c>
       <c r="H30" s="6" t="n">
-        <v>0.3117635484341261</v>
+        <v>76.33046551920575</v>
       </c>
       <c r="I30" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J30" s="6" t="n">
-        <v>0.3117635484341261</v>
+        <v>76.33046551920575</v>
       </c>
       <c r="K30" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L30" s="6" t="n">
-        <v>99.50129408753318</v>
+        <v>462.161691889013</v>
       </c>
       <c r="M30" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N30" s="6" t="n">
-        <v>0.2249411337708032</v>
+        <v>0.7640238766342328</v>
       </c>
       <c r="O30" s="6" t="n">
-        <v>0.2249411337708032</v>
+        <v>0.7640238766342328</v>
       </c>
       <c r="P30" s="6" t="n">
-        <v>0.08682241466332287</v>
+        <v>75.5664416425715</v>
       </c>
       <c r="Q30" s="6" t="n">
         <v>0</v>
@@ -2704,17 +2704,17 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>S13</t>
+          <t>S34</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Spark USDS Vault (Morpho)</t>
+          <t>Spark USDC Vault (Morpho, Base)</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>ethereum</t>
+          <t>base</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -2723,40 +2723,40 @@
         </is>
       </c>
       <c r="E31" s="6" t="n">
-        <v>21.90660666972937</v>
+        <v>224.7175624853434</v>
       </c>
       <c r="F31" s="6" t="n">
-        <v>21.90661272343654</v>
+        <v>424.9110349025811</v>
       </c>
       <c r="G31" s="6" t="n">
-        <v>6.053707169991468e-06</v>
+        <v>200.1934724172377</v>
       </c>
       <c r="H31" s="6" t="n">
-        <v>6.053707169991468e-06</v>
+        <v>1.161345275337778</v>
       </c>
       <c r="I31" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J31" s="6" t="n">
-        <v>6.053707169991468e-06</v>
+        <v>1.161345275337778</v>
       </c>
       <c r="K31" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L31" s="6" t="n">
-        <v>21.90660666972937</v>
+        <v>368.0420981576889</v>
       </c>
       <c r="M31" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N31" s="6" t="n">
-        <v>0.04952394827171772</v>
+        <v>0.6084298104624435</v>
       </c>
       <c r="O31" s="6" t="n">
-        <v>0.04952394827171772</v>
+        <v>0.6084298104624435</v>
       </c>
       <c r="P31" s="6" t="n">
-        <v>-0.04951789456454773</v>
+        <v>0.5529154648753346</v>
       </c>
       <c r="Q31" s="6" t="n">
         <v>0</v>
@@ -2769,59 +2769,59 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>S9</t>
+          <t>S36</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Aave Ethereum USDT (aToken)</t>
+          <t>Fluid Savings USDS (fsUSDS, Base)</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>ethereum</t>
+          <t>base</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E32" s="6" t="n">
-        <v>5.897868</v>
+        <v>283.8972488542868</v>
       </c>
       <c r="F32" s="6" t="n">
-        <v>5.913258</v>
+        <v>283.8972488542868</v>
       </c>
       <c r="G32" s="6" t="n">
-        <v>0.01539</v>
+        <v>0</v>
       </c>
       <c r="H32" s="6" t="n">
-        <v>0.01539</v>
+        <v>0</v>
       </c>
       <c r="I32" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J32" s="6" t="n">
-        <v>0.01539</v>
+        <v>0</v>
       </c>
       <c r="K32" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L32" s="6" t="n">
-        <v>5.897868</v>
+        <v>283.8972488542868</v>
       </c>
       <c r="M32" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N32" s="6" t="n">
-        <v>0.01333322472754415</v>
+        <v>0.4693255205745931</v>
       </c>
       <c r="O32" s="6" t="n">
-        <v>0.01333322472754415</v>
+        <v>0.4693255205745931</v>
       </c>
       <c r="P32" s="6" t="n">
-        <v>0.002056775272455852</v>
+        <v>-0.4693255205745931</v>
       </c>
       <c r="Q32" s="6" t="n">
         <v>0</v>
@@ -2834,59 +2834,59 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>S23</t>
+          <t>S55</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Anchorage tri-party loan escrow (USDC pass-through, ~$0 balance)</t>
+          <t>USDC raw (Avalanche-C — ALM idle)</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>ethereum</t>
+          <t>avalanche_c</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E33" s="6" t="n">
-        <v>1.545609</v>
+        <v>2500.221225</v>
       </c>
       <c r="F33" s="6" t="n">
-        <v>10.015998</v>
+        <v>0</v>
       </c>
       <c r="G33" s="6" t="n">
-        <v>8.470389000000001</v>
+        <v>-2500.221225</v>
       </c>
       <c r="H33" s="6" t="n">
-        <v>8.470389000000001</v>
+        <v>-3.30458807350886e-10</v>
       </c>
       <c r="I33" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J33" s="6" t="n">
-        <v>8.470389000000001</v>
+        <v>-3.30458807350886e-10</v>
       </c>
       <c r="K33" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L33" s="6" t="n">
-        <v>1.545609</v>
+        <v>115.3103732260555</v>
       </c>
       <c r="M33" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N33" s="6" t="n">
-        <v>0.003494135870439078</v>
+        <v>0.1906256617856336</v>
       </c>
       <c r="O33" s="6" t="n">
-        <v>0.003494135870439078</v>
+        <v>0.1906256617856336</v>
       </c>
       <c r="P33" s="6" t="n">
-        <v>8.466894864129561</v>
+        <v>-0.1906256621160924</v>
       </c>
       <c r="Q33" s="6" t="n">
         <v>0</v>
@@ -2899,59 +2899,59 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>S54</t>
+          <t>S16</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Aave Avalanche USDC (aAvaUSDC)</t>
+          <t>Ethena Staked USDe (sUSDe)</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>avalanche_c</t>
+          <t>ethereum</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E34" s="6" t="n">
-        <v>0.154431</v>
+        <v>99.50129408753318</v>
       </c>
       <c r="F34" s="6" t="n">
-        <v>0.155165</v>
+        <v>99.81305763596731</v>
       </c>
       <c r="G34" s="6" t="n">
-        <v>0.000734</v>
+        <v>0.3117635484341261</v>
       </c>
       <c r="H34" s="6" t="n">
-        <v>0.000734</v>
+        <v>0.3117635484341261</v>
       </c>
       <c r="I34" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J34" s="6" t="n">
-        <v>0.000734</v>
+        <v>0.3117635484341261</v>
       </c>
       <c r="K34" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L34" s="6" t="n">
-        <v>0.154431</v>
+        <v>99.50129408753318</v>
       </c>
       <c r="M34" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N34" s="6" t="n">
-        <v>0.0003491199239961576</v>
+        <v>0.164490838970566</v>
       </c>
       <c r="O34" s="6" t="n">
-        <v>0.0003491199239961576</v>
+        <v>0.164490838970566</v>
       </c>
       <c r="P34" s="6" t="n">
-        <v>0.0003848800760038423</v>
+        <v>0.1472727094635601</v>
       </c>
       <c r="Q34" s="6" t="n">
         <v>0</v>
@@ -2964,12 +2964,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>S8</t>
+          <t>S13</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Aave Ethereum USDC (aToken)</t>
+          <t>Spark USDS Vault (Morpho)</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2979,44 +2979,44 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E35" s="6" t="n">
-        <v>0.057783</v>
+        <v>21.90660666972937</v>
       </c>
       <c r="F35" s="6" t="n">
-        <v>0.057969</v>
+        <v>21.90661272343654</v>
       </c>
       <c r="G35" s="6" t="n">
-        <v>0.000186</v>
+        <v>6.053707169991468e-06</v>
       </c>
       <c r="H35" s="6" t="n">
-        <v>0.000186</v>
+        <v>6.053707169991468e-06</v>
       </c>
       <c r="I35" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J35" s="6" t="n">
-        <v>0.000186</v>
+        <v>6.053707169991468e-06</v>
       </c>
       <c r="K35" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L35" s="6" t="n">
-        <v>0.057783</v>
+        <v>21.90660666972937</v>
       </c>
       <c r="M35" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N35" s="6" t="n">
-        <v>0.0001306291908248343</v>
+        <v>0.03621496728406336</v>
       </c>
       <c r="O35" s="6" t="n">
-        <v>0.0001306291908248343</v>
+        <v>0.03621496728406336</v>
       </c>
       <c r="P35" s="6" t="n">
-        <v>5.537080917516575e-05</v>
+        <v>-0.03620891357689337</v>
       </c>
       <c r="Q35" s="6" t="n">
         <v>0</v>
@@ -3029,17 +3029,17 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>S41</t>
+          <t>S9</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Aave Arbitrum USDCn (aArbUSDCn)</t>
+          <t>Aave Ethereum USDT (aToken)</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>arbitrum</t>
+          <t>ethereum</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -3048,40 +3048,40 @@
         </is>
       </c>
       <c r="E36" s="6" t="n">
-        <v>0.006346</v>
+        <v>5.897868</v>
       </c>
       <c r="F36" s="6" t="n">
-        <v>0.006363</v>
+        <v>5.913258</v>
       </c>
       <c r="G36" s="6" t="n">
-        <v>1.7e-05</v>
+        <v>0.01539</v>
       </c>
       <c r="H36" s="6" t="n">
-        <v>1.7e-05</v>
+        <v>0.01539</v>
       </c>
       <c r="I36" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J36" s="6" t="n">
-        <v>1.7e-05</v>
+        <v>0.01539</v>
       </c>
       <c r="K36" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L36" s="6" t="n">
-        <v>0.006346</v>
+        <v>5.897868</v>
       </c>
       <c r="M36" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N36" s="6" t="n">
-        <v>1.434631024651538e-05</v>
+        <v>0.009750076763868005</v>
       </c>
       <c r="O36" s="6" t="n">
-        <v>1.434631024651538e-05</v>
+        <v>0.009750076763868005</v>
       </c>
       <c r="P36" s="6" t="n">
-        <v>2.653689753484621e-06</v>
+        <v>0.005639923236131995</v>
       </c>
       <c r="Q36" s="6" t="n">
         <v>0</v>
@@ -3094,12 +3094,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>S7</t>
+          <t>S23</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Aave Ethereum USDS (aToken)</t>
+          <t>Anchorage tri-party loan escrow (USDC pass-through, ~$0 balance)</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -3109,44 +3109,44 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E37" s="6" t="n">
-        <v>0.005744283090097436</v>
+        <v>1.545609</v>
       </c>
       <c r="F37" s="6" t="n">
-        <v>0.005746426914602806</v>
+        <v>10.015998</v>
       </c>
       <c r="G37" s="6" t="n">
-        <v>2.14382450537e-06</v>
+        <v>8.470389000000001</v>
       </c>
       <c r="H37" s="6" t="n">
-        <v>2.14382450537e-06</v>
+        <v>8.470389000000001</v>
       </c>
       <c r="I37" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J37" s="6" t="n">
-        <v>2.14382450537e-06</v>
+        <v>8.470389000000001</v>
       </c>
       <c r="K37" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L37" s="6" t="n">
-        <v>0.005744283090097436</v>
+        <v>1.545609</v>
       </c>
       <c r="M37" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N37" s="6" t="n">
-        <v>1.298601754717143e-05</v>
+        <v>0.002555127784637646</v>
       </c>
       <c r="O37" s="6" t="n">
-        <v>1.298601754717143e-05</v>
+        <v>0.002555127784637646</v>
       </c>
       <c r="P37" s="6" t="n">
-        <v>-1.084219304180143e-05</v>
+        <v>8.467833872215362</v>
       </c>
       <c r="Q37" s="6" t="n">
         <v>0</v>
@@ -3159,17 +3159,17 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>S35</t>
+          <t>S54</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Aave Base USDC (aBasUSDC)</t>
+          <t>Aave Avalanche USDC (aAvaUSDC)</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>base</t>
+          <t>avalanche_c</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -3178,40 +3178,40 @@
         </is>
       </c>
       <c r="E38" s="6" t="n">
-        <v>0.0017</v>
+        <v>0.154431</v>
       </c>
       <c r="F38" s="6" t="n">
-        <v>0.001705</v>
+        <v>0.155165</v>
       </c>
       <c r="G38" s="6" t="n">
-        <v>5e-06</v>
+        <v>0.000734</v>
       </c>
       <c r="H38" s="6" t="n">
-        <v>5e-06</v>
+        <v>0.000734</v>
       </c>
       <c r="I38" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J38" s="6" t="n">
-        <v>5e-06</v>
+        <v>0.000734</v>
       </c>
       <c r="K38" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L38" s="6" t="n">
-        <v>0.0017</v>
+        <v>0.154431</v>
       </c>
       <c r="M38" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N38" s="6" t="n">
-        <v>3.843165367014835e-06</v>
+        <v>0.0002552980339202064</v>
       </c>
       <c r="O38" s="6" t="n">
-        <v>3.843165367014835e-06</v>
+        <v>0.0002552980339202064</v>
       </c>
       <c r="P38" s="6" t="n">
-        <v>1.156834632985165e-06</v>
+        <v>0.0004787019660797936</v>
       </c>
       <c r="Q38" s="6" t="n">
         <v>0</v>
@@ -3224,12 +3224,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>S17</t>
+          <t>S8</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Fluid Savings USDS (fsUSDS)</t>
+          <t>Aave Ethereum USDC (aToken)</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -3239,44 +3239,44 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E39" s="6" t="n">
-        <v>0.001240144670509943</v>
+        <v>0.057783</v>
       </c>
       <c r="F39" s="6" t="n">
-        <v>0.001240144670509943</v>
+        <v>0.057969</v>
       </c>
       <c r="G39" s="6" t="n">
-        <v>0</v>
+        <v>0.000186</v>
       </c>
       <c r="H39" s="6" t="n">
-        <v>0</v>
+        <v>0.000186</v>
       </c>
       <c r="I39" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J39" s="6" t="n">
-        <v>0</v>
+        <v>0.000186</v>
       </c>
       <c r="K39" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L39" s="6" t="n">
-        <v>0.001240144670509943</v>
+        <v>0.057783</v>
       </c>
       <c r="M39" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N39" s="6" t="n">
-        <v>2.803577086936375e-06</v>
+        <v>9.552412594628854e-05</v>
       </c>
       <c r="O39" s="6" t="n">
-        <v>2.803577086936375e-06</v>
+        <v>9.552412594628854e-05</v>
       </c>
       <c r="P39" s="6" t="n">
-        <v>-2.803577086936375e-06</v>
+        <v>9.047587405371145e-05</v>
       </c>
       <c r="Q39" s="6" t="n">
         <v>0</v>
@@ -3289,17 +3289,17 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>S6</t>
+          <t>S41</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Aave Ethereum Lido USDS (aToken)</t>
+          <t>Aave Arbitrum USDCn (aArbUSDCn)</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>ethereum</t>
+          <t>arbitrum</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -3308,40 +3308,40 @@
         </is>
       </c>
       <c r="E40" s="6" t="n">
-        <v>0.0005209665645060241</v>
+        <v>0.006346</v>
       </c>
       <c r="F40" s="6" t="n">
-        <v>0.000521673271312833</v>
+        <v>0.006363</v>
       </c>
       <c r="G40" s="6" t="n">
-        <v>7.06706806809e-07</v>
+        <v>1.7e-05</v>
       </c>
       <c r="H40" s="6" t="n">
-        <v>7.06706806809e-07</v>
+        <v>1.7e-05</v>
       </c>
       <c r="I40" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J40" s="6" t="n">
-        <v>7.06706806809e-07</v>
+        <v>1.7e-05</v>
       </c>
       <c r="K40" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L40" s="6" t="n">
-        <v>0.0005209665645060241</v>
+        <v>0.006346</v>
       </c>
       <c r="M40" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N40" s="6" t="n">
-        <v>1.177741563577795e-06</v>
+        <v>1.049090741663027e-05</v>
       </c>
       <c r="O40" s="6" t="n">
-        <v>1.177741563577795e-06</v>
+        <v>1.049090741663027e-05</v>
       </c>
       <c r="P40" s="6" t="n">
-        <v>-4.710347567687951e-07</v>
+        <v>6.509092583369726e-06</v>
       </c>
       <c r="Q40" s="6" t="n">
         <v>0</v>
@@ -3354,12 +3354,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>S30</t>
+          <t>S7</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>USDe raw (ALM idle)</t>
+          <t>Aave Ethereum USDS (aToken)</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -3369,44 +3369,44 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E41" s="6" t="n">
-        <v>7.4896275897803e-05</v>
+        <v>0.005744283090097436</v>
       </c>
       <c r="F41" s="6" t="n">
-        <v>7.4896275897803e-05</v>
+        <v>0.005746426914602806</v>
       </c>
       <c r="G41" s="6" t="n">
-        <v>0</v>
+        <v>2.14382450537e-06</v>
       </c>
       <c r="H41" s="6" t="n">
-        <v>0</v>
+        <v>2.14382450537e-06</v>
       </c>
       <c r="I41" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J41" s="6" t="n">
-        <v>0</v>
+        <v>2.14382450537e-06</v>
       </c>
       <c r="K41" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L41" s="6" t="n">
-        <v>7.4896275897803e-05</v>
+        <v>0.005744283090097436</v>
       </c>
       <c r="M41" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N41" s="6" t="n">
-        <v>1.693169256757791e-07</v>
+        <v>9.496177446127806e-06</v>
       </c>
       <c r="O41" s="6" t="n">
-        <v>1.693169256757791e-07</v>
+        <v>9.496177446127806e-06</v>
       </c>
       <c r="P41" s="6" t="n">
-        <v>-1.693169256757791e-07</v>
+        <v>-7.352352940757807e-06</v>
       </c>
       <c r="Q41" s="6" t="n">
         <v>0</v>
@@ -3419,59 +3419,59 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>S19</t>
+          <t>S35</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>BlackRock USD Institutional Digital Liquidity Fund (BUIDL-I)</t>
+          <t>Aave Base USDC (aBasUSDC)</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>ethereum</t>
+          <t>base</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E42" s="6" t="n">
-        <v>0</v>
+        <v>0.0017</v>
       </c>
       <c r="F42" s="6" t="n">
-        <v>0</v>
+        <v>0.001705</v>
       </c>
       <c r="G42" s="6" t="n">
-        <v>0</v>
+        <v>5e-06</v>
       </c>
       <c r="H42" s="6" t="n">
-        <v>0</v>
+        <v>5e-06</v>
       </c>
       <c r="I42" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J42" s="6" t="n">
-        <v>0</v>
+        <v>5e-06</v>
       </c>
       <c r="K42" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L42" s="6" t="n">
-        <v>0</v>
+        <v>0.0017</v>
       </c>
       <c r="M42" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N42" s="6" t="n">
-        <v>0</v>
+        <v>2.810359692447442e-06</v>
       </c>
       <c r="O42" s="6" t="n">
-        <v>0</v>
+        <v>2.810359692447442e-06</v>
       </c>
       <c r="P42" s="6" t="n">
-        <v>0</v>
+        <v>2.189640307552558e-06</v>
       </c>
       <c r="Q42" s="6" t="n">
         <v>0</v>
@@ -3484,12 +3484,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>S20</t>
+          <t>S17</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Janus Henderson Anemoy Treasury Fund (JTRSY)</t>
+          <t>Fluid Savings USDS (fsUSDS)</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3499,14 +3499,14 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E43" s="6" t="n">
-        <v>0</v>
+        <v>0.001240144670509943</v>
       </c>
       <c r="F43" s="6" t="n">
-        <v>0</v>
+        <v>0.001240144670509943</v>
       </c>
       <c r="G43" s="6" t="n">
         <v>0</v>
@@ -3524,19 +3524,19 @@
         <v>0</v>
       </c>
       <c r="L43" s="6" t="n">
-        <v>0</v>
+        <v>0.001240144670509943</v>
       </c>
       <c r="M43" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N43" s="6" t="n">
-        <v>0</v>
+        <v>2.050148585179211e-06</v>
       </c>
       <c r="O43" s="6" t="n">
-        <v>0</v>
+        <v>2.050148585179211e-06</v>
       </c>
       <c r="P43" s="6" t="n">
-        <v>0</v>
+        <v>-2.050148585179211e-06</v>
       </c>
       <c r="Q43" s="6" t="n">
         <v>0</v>
@@ -3549,12 +3549,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>S21</t>
+          <t>S6</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Superstate Short Duration US Government Securities Fund (USTB)</t>
+          <t>Aave Ethereum Lido USDS (aToken)</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3564,44 +3564,44 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E44" s="6" t="n">
-        <v>0</v>
+        <v>0.0005209665645060241</v>
       </c>
       <c r="F44" s="6" t="n">
-        <v>0</v>
+        <v>0.000521673271312833</v>
       </c>
       <c r="G44" s="6" t="n">
-        <v>0</v>
+        <v>7.06706806809e-07</v>
       </c>
       <c r="H44" s="6" t="n">
-        <v>0</v>
+        <v>7.06706806809e-07</v>
       </c>
       <c r="I44" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J44" s="6" t="n">
-        <v>0</v>
+        <v>7.06706806809e-07</v>
       </c>
       <c r="K44" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L44" s="6" t="n">
-        <v>0</v>
+        <v>0.0005209665645060241</v>
       </c>
       <c r="M44" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N44" s="6" t="n">
-        <v>0</v>
+        <v>8.612373141179706e-07</v>
       </c>
       <c r="O44" s="6" t="n">
-        <v>0</v>
+        <v>8.612373141179706e-07</v>
       </c>
       <c r="P44" s="6" t="n">
-        <v>0</v>
+        <v>-1.545305073089706e-07</v>
       </c>
       <c r="Q44" s="6" t="n">
         <v>0</v>
@@ -3609,21 +3609,17 @@
       <c r="R44" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="S44" t="inlineStr">
-        <is>
-          <t>SDE (fixed)</t>
-        </is>
-      </c>
+      <c r="S44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>S22</t>
+          <t>S30</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Superstate Crypto Carry Fund (USCC)</t>
+          <t>USDe raw (ALM idle)</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3633,14 +3629,14 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E45" s="6" t="n">
-        <v>0</v>
+        <v>7.4896275897803e-05</v>
       </c>
       <c r="F45" s="6" t="n">
-        <v>0</v>
+        <v>7.4896275897803e-05</v>
       </c>
       <c r="G45" s="6" t="n">
         <v>0</v>
@@ -3658,19 +3654,19 @@
         <v>0</v>
       </c>
       <c r="L45" s="6" t="n">
-        <v>0</v>
+        <v>7.4896275897803e-05</v>
       </c>
       <c r="M45" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N45" s="6" t="n">
-        <v>0</v>
+        <v>1.238149852338873e-07</v>
       </c>
       <c r="O45" s="6" t="n">
-        <v>0</v>
+        <v>1.238149852338873e-07</v>
       </c>
       <c r="P45" s="6" t="n">
-        <v>0</v>
+        <v>-1.238149852338873e-07</v>
       </c>
       <c r="Q45" s="6" t="n">
         <v>0</v>
@@ -3683,12 +3679,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>S26</t>
+          <t>S19</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>USDC raw (ALM idle)</t>
+          <t>BlackRock USD Institutional Digital Liquidity Fund (BUIDL-I)</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3698,7 +3694,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E46" s="6" t="n">
@@ -3711,13 +3707,13 @@
         <v>0</v>
       </c>
       <c r="H46" s="6" t="n">
-        <v>6162610.279999871</v>
+        <v>0</v>
       </c>
       <c r="I46" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J46" s="6" t="n">
-        <v>6162610.279999871</v>
+        <v>0</v>
       </c>
       <c r="K46" s="6" t="n">
         <v>0</v>
@@ -3735,7 +3731,7 @@
         <v>0</v>
       </c>
       <c r="P46" s="6" t="n">
-        <v>6162610.279999871</v>
+        <v>0</v>
       </c>
       <c r="Q46" s="6" t="n">
         <v>0</v>
@@ -3748,12 +3744,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>S29</t>
+          <t>S20</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>DAI raw (ALM idle)</t>
+          <t>Janus Henderson Anemoy Treasury Fund (JTRSY)</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3763,7 +3759,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E47" s="6" t="n">
@@ -3776,13 +3772,13 @@
         <v>0</v>
       </c>
       <c r="H47" s="6" t="n">
-        <v>8.19007e-07</v>
+        <v>0</v>
       </c>
       <c r="I47" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J47" s="6" t="n">
-        <v>8.19007e-07</v>
+        <v>0</v>
       </c>
       <c r="K47" s="6" t="n">
         <v>0</v>
@@ -3800,7 +3796,7 @@
         <v>0</v>
       </c>
       <c r="P47" s="6" t="n">
-        <v>8.19007e-07</v>
+        <v>0</v>
       </c>
       <c r="Q47" s="6" t="n">
         <v>0</v>
@@ -3813,12 +3809,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>S31</t>
+          <t>S21</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>USDS raw / POL (ALM idle — already netted out of utilized)</t>
+          <t>Superstate Short Duration US Government Securities Fund (USTB)</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3828,7 +3824,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E48" s="6" t="n">
@@ -3841,19 +3837,19 @@
         <v>0</v>
       </c>
       <c r="H48" s="6" t="n">
-        <v>-2.5155451e-06</v>
+        <v>0</v>
       </c>
       <c r="I48" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J48" s="6" t="n">
-        <v>-2.5155451e-06</v>
+        <v>0</v>
       </c>
       <c r="K48" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L48" s="6" t="n">
-        <v>17.83075712531922</v>
+        <v>0</v>
       </c>
       <c r="M48" s="7" t="n">
         <v>0</v>
@@ -3865,46 +3861,46 @@
         <v>0</v>
       </c>
       <c r="P48" s="6" t="n">
-        <v>-2.5155451e-06</v>
+        <v>0</v>
       </c>
       <c r="Q48" s="6" t="n">
-        <v>17.83075712531922</v>
+        <v>0</v>
       </c>
       <c r="R48" s="6" t="n">
         <v>0</v>
       </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>CoF excluded (already deducted from utilized)</t>
+          <t>SDE (fixed)</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>S38</t>
+          <t>S22</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>USDS raw (Base — POL)</t>
+          <t>Superstate Crypto Carry Fund (USCC)</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>base</t>
+          <t>ethereum</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E49" s="6" t="n">
-        <v>65170000</v>
+        <v>0</v>
       </c>
       <c r="F49" s="6" t="n">
-        <v>65170000</v>
+        <v>0</v>
       </c>
       <c r="G49" s="6" t="n">
         <v>0</v>
@@ -3922,10 +3918,10 @@
         <v>0</v>
       </c>
       <c r="L49" s="6" t="n">
-        <v>65170000</v>
+        <v>0</v>
       </c>
       <c r="M49" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N49" s="6" t="n">
         <v>0</v>
@@ -3937,36 +3933,32 @@
         <v>0</v>
       </c>
       <c r="Q49" s="6" t="n">
-        <v>65170000</v>
+        <v>0</v>
       </c>
       <c r="R49" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="S49" t="inlineStr">
-        <is>
-          <t>CoF excluded (already deducted from utilized)</t>
-        </is>
-      </c>
+      <c r="S49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>S42</t>
+          <t>S26</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Fluid Savings USDS (fsUSDS, Arbitrum)</t>
+          <t>USDC raw (ALM idle)</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>arbitrum</t>
+          <t>ethereum</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E50" s="6" t="n">
@@ -3979,13 +3971,13 @@
         <v>0</v>
       </c>
       <c r="H50" s="6" t="n">
-        <v>0</v>
+        <v>6162610.279999871</v>
       </c>
       <c r="I50" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J50" s="6" t="n">
-        <v>0</v>
+        <v>6162610.279999871</v>
       </c>
       <c r="K50" s="6" t="n">
         <v>0</v>
@@ -4003,7 +3995,7 @@
         <v>0</v>
       </c>
       <c r="P50" s="6" t="n">
-        <v>0</v>
+        <v>6162610.279999871</v>
       </c>
       <c r="Q50" s="6" t="n">
         <v>0</v>
@@ -4016,17 +4008,17 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>S44</t>
+          <t>S29</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>USDS raw (Arbitrum — POL)</t>
+          <t>DAI raw (ALM idle)</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>arbitrum</t>
+          <t>ethereum</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -4035,31 +4027,31 @@
         </is>
       </c>
       <c r="E51" s="6" t="n">
-        <v>90000000</v>
+        <v>0</v>
       </c>
       <c r="F51" s="6" t="n">
-        <v>90000000</v>
+        <v>0</v>
       </c>
       <c r="G51" s="6" t="n">
         <v>0</v>
       </c>
       <c r="H51" s="6" t="n">
-        <v>0</v>
+        <v>8.19007e-07</v>
       </c>
       <c r="I51" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J51" s="6" t="n">
-        <v>0</v>
+        <v>8.19007e-07</v>
       </c>
       <c r="K51" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L51" s="6" t="n">
-        <v>90000000</v>
+        <v>0</v>
       </c>
       <c r="M51" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N51" s="6" t="n">
         <v>0</v>
@@ -4068,34 +4060,30 @@
         <v>0</v>
       </c>
       <c r="P51" s="6" t="n">
-        <v>0</v>
+        <v>8.19007e-07</v>
       </c>
       <c r="Q51" s="6" t="n">
-        <v>90000000</v>
+        <v>0</v>
       </c>
       <c r="R51" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="S51" t="inlineStr">
-        <is>
-          <t>CoF excluded (already deducted from utilized)</t>
-        </is>
-      </c>
+      <c r="S51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>S48</t>
+          <t>S31</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>USDS raw (Optimism — POL)</t>
+          <t>USDS raw / POL (ALM idle — already netted out of utilized)</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>optimism</t>
+          <t>ethereum</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -4104,28 +4092,28 @@
         </is>
       </c>
       <c r="E52" s="6" t="n">
-        <v>89900000</v>
+        <v>0</v>
       </c>
       <c r="F52" s="6" t="n">
-        <v>89900000</v>
+        <v>0</v>
       </c>
       <c r="G52" s="6" t="n">
         <v>0</v>
       </c>
       <c r="H52" s="6" t="n">
-        <v>0</v>
+        <v>-2.5155451e-06</v>
       </c>
       <c r="I52" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J52" s="6" t="n">
-        <v>0</v>
+        <v>-2.5155451e-06</v>
       </c>
       <c r="K52" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L52" s="6" t="n">
-        <v>89900000</v>
+        <v>17.83075712531922</v>
       </c>
       <c r="M52" s="7" t="n">
         <v>0</v>
@@ -4137,10 +4125,10 @@
         <v>0</v>
       </c>
       <c r="P52" s="6" t="n">
-        <v>0</v>
+        <v>-2.5155451e-06</v>
       </c>
       <c r="Q52" s="6" t="n">
-        <v>89900000</v>
+        <v>17.83075712531922</v>
       </c>
       <c r="R52" s="6" t="n">
         <v>0</v>
@@ -4154,17 +4142,17 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>S52</t>
+          <t>S38</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>USDS raw (Unichain — POL)</t>
+          <t>USDS raw (Base — POL)</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>unichain</t>
+          <t>base</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -4173,10 +4161,10 @@
         </is>
       </c>
       <c r="E53" s="6" t="n">
-        <v>89900000</v>
+        <v>65170000</v>
       </c>
       <c r="F53" s="6" t="n">
-        <v>89900000</v>
+        <v>65170000</v>
       </c>
       <c r="G53" s="6" t="n">
         <v>0</v>
@@ -4194,7 +4182,7 @@
         <v>0</v>
       </c>
       <c r="L53" s="6" t="n">
-        <v>89900000</v>
+        <v>65170000</v>
       </c>
       <c r="M53" s="7" t="n">
         <v>0</v>
@@ -4209,7 +4197,7 @@
         <v>0</v>
       </c>
       <c r="Q53" s="6" t="n">
-        <v>89900000</v>
+        <v>65170000</v>
       </c>
       <c r="R53" s="6" t="n">
         <v>0</v>
@@ -4223,59 +4211,331 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
+          <t>S42</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Fluid Savings USDS (fsUSDS, Arbitrum)</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>arbitrum</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="E54" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F54" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G54" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H54" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I54" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J54" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K54" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L54" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M54" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="N54" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O54" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P54" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q54" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R54" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>S44</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>USDS raw (Arbitrum — POL)</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>arbitrum</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E55" s="6" t="n">
+        <v>90000000</v>
+      </c>
+      <c r="F55" s="6" t="n">
+        <v>90000000</v>
+      </c>
+      <c r="G55" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H55" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I55" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J55" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K55" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L55" s="6" t="n">
+        <v>90000000</v>
+      </c>
+      <c r="M55" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N55" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O55" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P55" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q55" s="6" t="n">
+        <v>90000000</v>
+      </c>
+      <c r="R55" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>CoF excluded (already deducted from utilized)</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>S48</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>USDS raw (Optimism — POL)</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>optimism</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E56" s="6" t="n">
+        <v>89900000</v>
+      </c>
+      <c r="F56" s="6" t="n">
+        <v>89900000</v>
+      </c>
+      <c r="G56" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H56" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I56" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J56" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K56" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L56" s="6" t="n">
+        <v>89900000</v>
+      </c>
+      <c r="M56" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N56" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O56" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P56" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q56" s="6" t="n">
+        <v>89900000</v>
+      </c>
+      <c r="R56" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>CoF excluded (already deducted from utilized)</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>S52</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>USDS raw (Unichain — POL)</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>unichain</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E57" s="6" t="n">
+        <v>89900000</v>
+      </c>
+      <c r="F57" s="6" t="n">
+        <v>89900000</v>
+      </c>
+      <c r="G57" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H57" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I57" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J57" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K57" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L57" s="6" t="n">
+        <v>89900000</v>
+      </c>
+      <c r="M57" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N57" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O57" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P57" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q57" s="6" t="n">
+        <v>89900000</v>
+      </c>
+      <c r="R57" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>CoF excluded (already deducted from utilized)</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
           <t>PSM_CURVE_DEDUCT</t>
         </is>
       </c>
-      <c r="B54" t="inlineStr">
+      <c r="B58" t="inlineStr">
         <is>
           <t>PSM3 USDS + PSM3 USDC (SDE) + Curve idle USDS — BR deduction (unattributed)</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr"/>
-      <c r="D54" t="inlineStr"/>
-      <c r="E54" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F54" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G54" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H54" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I54" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J54" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K54" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L54" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M54" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N54" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O54" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P54" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q54" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R54" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S54" t="inlineStr">
+      <c r="C58" t="inlineStr"/>
+      <c r="D58" t="inlineStr"/>
+      <c r="E58" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F58" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G58" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H58" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I58" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J58" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K58" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L58" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M58" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N58" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O58" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P58" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q58" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R58" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S58" t="inlineStr">
         <is>
           <t>BR deduction from PSM3 USDS leg + PSM3 USDC leg (SDE, ≈$0 yield) + Curve idle USDS — not tracked per-venue; residual = sky_rev_br_reduction − Σ(known venue deduction_avg × effective_br_rate × n_days)</t>
         </is>

--- a/settlements/spark/2026-05/spark_settlement_may_2026.xlsx
+++ b/settlements/spark/2026-05/spark_settlement_may_2026.xlsx
@@ -11,6 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Venues" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sky Revenue" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sky Direct" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Debt" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -74,7 +75,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -87,6 +88,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -523,7 +525,7 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>10557149.38334401</v>
+        <v>3284300.977760902</v>
       </c>
     </row>
     <row r="10">
@@ -539,7 +541,7 @@
     <row r="11">
       <c r="A11" t="inlineStr"/>
       <c r="B11" s="4" t="n">
-        <v>10631305.44418851</v>
+        <v>3358457.038605412</v>
       </c>
     </row>
     <row r="13">
@@ -561,7 +563,7 @@
         </is>
       </c>
       <c r="B14" s="3" t="n">
-        <v>10557149.38334401</v>
+        <v>3284300.977760902</v>
       </c>
     </row>
     <row r="15">
@@ -571,7 +573,7 @@
         </is>
       </c>
       <c r="B15" s="3" t="n">
-        <v>-2819972.476227154</v>
+        <v>-10092820.88181026</v>
       </c>
     </row>
     <row r="16">
@@ -619,13 +621,13 @@
         </is>
       </c>
       <c r="B22" s="3" t="n">
-        <v>-10557149.38334401</v>
+        <v>-3284300.977760902</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr"/>
       <c r="B23" s="4" t="n">
-        <v>-2271035.909278506</v>
+        <v>5001812.496304598</v>
       </c>
     </row>
     <row r="25">
@@ -660,7 +662,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-06-05T13:13:14+00:00</t>
+          <t>2026-06-08T12:39:12+00:00</t>
         </is>
       </c>
     </row>
@@ -816,7 +818,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>sUSDS raw / POL (ALM — Cat B 4626, demand-side spread)</t>
+          <t>sUSDS raw / POL (ALM — Cat B 4626, demand-side spread + agent rate)</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -857,13 +859,13 @@
         <v>1</v>
       </c>
       <c r="N2" s="6" t="n">
-        <v>3142112.038726919</v>
+        <v>1014763.564397916</v>
       </c>
       <c r="O2" s="6" t="n">
-        <v>3142112.038726919</v>
+        <v>1014763.564397916</v>
       </c>
       <c r="P2" s="6" t="n">
-        <v>-3142112.038726919</v>
+        <v>-1014763.564397916</v>
       </c>
       <c r="Q2" s="6" t="n">
         <v>0</v>
@@ -922,13 +924,13 @@
         <v>1</v>
       </c>
       <c r="N3" s="6" t="n">
-        <v>1875837.778435055</v>
+        <v>605812.8439774774</v>
       </c>
       <c r="O3" s="6" t="n">
-        <v>1875837.778435055</v>
+        <v>605812.8439774774</v>
       </c>
       <c r="P3" s="6" t="n">
-        <v>-4471043.528741025</v>
+        <v>-3201018.594283448</v>
       </c>
       <c r="Q3" s="6" t="n">
         <v>0</v>
@@ -987,13 +989,13 @@
         <v>1</v>
       </c>
       <c r="N4" s="6" t="n">
-        <v>1110494.257971797</v>
+        <v>358640.6523936233</v>
       </c>
       <c r="O4" s="6" t="n">
-        <v>1110494.257971797</v>
+        <v>358640.6523936233</v>
       </c>
       <c r="P4" s="6" t="n">
-        <v>757617.9102642025</v>
+        <v>1509471.515842377</v>
       </c>
       <c r="Q4" s="6" t="n">
         <v>0</v>
@@ -1052,13 +1054,13 @@
         <v>1</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>1017458.107638799</v>
+        <v>328594.0804171427</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>1017458.107638799</v>
+        <v>328594.0804171427</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>2074121.892361201</v>
+        <v>2762985.919582857</v>
       </c>
       <c r="Q5" s="6" t="n">
         <v>0</v>
@@ -1117,13 +1119,13 @@
         <v>1</v>
       </c>
       <c r="N6" s="6" t="n">
-        <v>947805.6387759986</v>
+        <v>306099.4059112116</v>
       </c>
       <c r="O6" s="6" t="n">
-        <v>947805.6387759986</v>
+        <v>306099.4059112116</v>
       </c>
       <c r="P6" s="6" t="n">
-        <v>-3025738.886441393</v>
+        <v>-2384032.653576606</v>
       </c>
       <c r="Q6" s="6" t="n">
         <v>0</v>
@@ -1182,13 +1184,13 @@
         <v>1</v>
       </c>
       <c r="N7" s="6" t="n">
-        <v>892297.3670793462</v>
+        <v>288172.6830744011</v>
       </c>
       <c r="O7" s="6" t="n">
-        <v>892297.3670793462</v>
+        <v>288172.6830744011</v>
       </c>
       <c r="P7" s="6" t="n">
-        <v>-1086741.811523299</v>
+        <v>-482617.1275183543</v>
       </c>
       <c r="Q7" s="6" t="n">
         <v>0</v>
@@ -1201,146 +1203,142 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>S4</t>
+          <t>SPREAD</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Spark DAI (SparkLend spToken)</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>ethereum</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
+          <t>30bps sUSDS spread (Curve LP + PSM3) — Sky Revenue reduction</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr"/>
       <c r="E8" s="6" t="n">
-        <v>266184835.4745756</v>
+        <v>0</v>
       </c>
       <c r="F8" s="6" t="n">
-        <v>266960907.7112744</v>
+        <v>0</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>776072.2366988341</v>
+        <v>0</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>559452.9392412193</v>
+        <v>0</v>
       </c>
       <c r="I8" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J8" s="6" t="n">
-        <v>559452.9392412193</v>
+        <v>0</v>
       </c>
       <c r="K8" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L8" s="6" t="n">
-        <v>179549416.5672932</v>
+        <v>0</v>
       </c>
       <c r="M8" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N8" s="6" t="n">
-        <v>296822.6136018681</v>
+        <v>0</v>
       </c>
       <c r="O8" s="6" t="n">
-        <v>296822.6136018681</v>
+        <v>-102957.2966175266</v>
       </c>
       <c r="P8" s="6" t="n">
-        <v>262630.3256393512</v>
+        <v>0</v>
       </c>
       <c r="Q8" s="6" t="n">
-        <v>86642406.62655522</v>
+        <v>0</v>
       </c>
       <c r="R8" s="6" t="n">
-        <v>0</v>
+        <v>102957.2966175266</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>(avg excl. lending_idle)</t>
+          <t>sky-revenue reduction (no CoF; computed outside venue loop)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>S43</t>
+          <t>S4</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Savings USDS / sUSDS proxy (Arbitrum — POL)</t>
+          <t>Spark DAI (SparkLend spToken)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>arbitrum</t>
+          <t>ethereum</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E9" s="6" t="n">
-        <v>143328568.5311704</v>
+        <v>266184835.4745756</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>143764611.5800855</v>
+        <v>266960907.7112744</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>436043.0489150246</v>
+        <v>776072.2366988341</v>
       </c>
       <c r="H9" s="6" t="n">
-        <v>0</v>
+        <v>559452.9392412193</v>
       </c>
       <c r="I9" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J9" s="6" t="n">
-        <v>0</v>
+        <v>559452.9392412193</v>
       </c>
       <c r="K9" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L9" s="6" t="n">
-        <v>143328568.5311704</v>
+        <v>179549416.5672932</v>
       </c>
       <c r="M9" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N9" s="6" t="n">
-        <v>236944.0186918778</v>
+        <v>95860.60893442083</v>
       </c>
       <c r="O9" s="6" t="n">
-        <v>200479.2048500802</v>
+        <v>95860.60893442083</v>
       </c>
       <c r="P9" s="6" t="n">
-        <v>-236944.0186918778</v>
+        <v>463592.3303067985</v>
       </c>
       <c r="Q9" s="6" t="n">
-        <v>0</v>
+        <v>86642406.62655522</v>
       </c>
       <c r="R9" s="6" t="n">
-        <v>36464.81384179761</v>
-      </c>
-      <c r="S9" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>(avg excl. lending_idle)</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>S14</t>
+          <t>S24</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Maple syrupUSDC (ERC-4626)</t>
+          <t>Spark.fi USDT Reserve Curve (sUSDS/USDT)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1350,62 +1348,66 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>F</t>
         </is>
       </c>
       <c r="E10" s="6" t="n">
-        <v>105306162.1077363</v>
+        <v>50002415.26289953</v>
       </c>
       <c r="F10" s="6" t="n">
-        <v>105300451.2530954</v>
+        <v>48750265.64989898</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>-5710.854640941099</v>
+        <v>-1252149.613000547</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>423530.6085832017</v>
+        <v>74156.06084450937</v>
       </c>
       <c r="I10" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J10" s="6" t="n">
-        <v>423530.6085832017</v>
+        <v>0</v>
       </c>
       <c r="K10" s="6" t="n">
-        <v>0</v>
+        <v>74156.06084450937</v>
       </c>
       <c r="L10" s="6" t="n">
-        <v>105079212.3991508</v>
+        <v>49959631.20890453</v>
       </c>
       <c r="M10" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N10" s="6" t="n">
-        <v>173711.9900239393</v>
+        <v>0</v>
       </c>
       <c r="O10" s="6" t="n">
-        <v>173711.9900239393</v>
+        <v>74156.06084450937</v>
       </c>
       <c r="P10" s="6" t="n">
-        <v>249818.6185592623</v>
+        <v>0</v>
       </c>
       <c r="Q10" s="6" t="n">
-        <v>0</v>
+        <v>49959631.20890453</v>
       </c>
       <c r="R10" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="S10" t="inlineStr"/>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>SDE (fixed)</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>S5</t>
+          <t>S14</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Spark PYUSD (SparkLend spToken)</t>
+          <t>Maple syrupUSDC (ERC-4626)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1415,44 +1417,44 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E11" s="6" t="n">
-        <v>100001095.915921</v>
+        <v>105306162.1077363</v>
       </c>
       <c r="F11" s="6" t="n">
-        <v>100000628.579333</v>
+        <v>105300451.2530954</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>-467.336588</v>
+        <v>-5710.854640941099</v>
       </c>
       <c r="H11" s="6" t="n">
-        <v>29003.9707</v>
+        <v>423530.6085832017</v>
       </c>
       <c r="I11" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J11" s="6" t="n">
-        <v>29003.9707</v>
+        <v>423530.6085832017</v>
       </c>
       <c r="K11" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L11" s="6" t="n">
-        <v>100000145.2285891</v>
+        <v>105079212.3991508</v>
       </c>
       <c r="M11" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N11" s="6" t="n">
-        <v>165315.5161113631</v>
+        <v>56101.30892938157</v>
       </c>
       <c r="O11" s="6" t="n">
-        <v>165315.5161113631</v>
+        <v>56101.30892938157</v>
       </c>
       <c r="P11" s="6" t="n">
-        <v>-136311.5454113631</v>
+        <v>367429.2996538201</v>
       </c>
       <c r="Q11" s="6" t="n">
         <v>0</v>
@@ -1465,12 +1467,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>S25</t>
+          <t>S5</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Spark.fi PYUSD Reserve Curve (PYUSD/USDS)</t>
+          <t>Spark PYUSD (SparkLend spToken)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1480,44 +1482,44 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E12" s="6" t="n">
-        <v>99998676.75316638</v>
+        <v>100001095.915921</v>
       </c>
       <c r="F12" s="6" t="n">
-        <v>99999260.90933624</v>
+        <v>100000628.579333</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>584.1561698611263</v>
+        <v>-467.336588</v>
       </c>
       <c r="H12" s="6" t="n">
-        <v>6385.883871640342</v>
+        <v>29003.9707</v>
       </c>
       <c r="I12" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J12" s="6" t="n">
-        <v>6385.883871640342</v>
+        <v>29003.9707</v>
       </c>
       <c r="K12" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L12" s="6" t="n">
-        <v>99998489.60065988</v>
+        <v>100000145.2285891</v>
       </c>
       <c r="M12" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N12" s="6" t="n">
-        <v>165312.7791054819</v>
+        <v>53389.61829235638</v>
       </c>
       <c r="O12" s="6" t="n">
-        <v>165312.7791054819</v>
+        <v>53389.61829235638</v>
       </c>
       <c r="P12" s="6" t="n">
-        <v>-158926.8952338415</v>
+        <v>-24385.64759235637</v>
       </c>
       <c r="Q12" s="6" t="n">
         <v>0</v>
@@ -1530,12 +1532,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>S11</t>
+          <t>S25</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Spark Blue Chip USDT Vault (Morpho V2)</t>
+          <t>Spark.fi PYUSD Reserve Curve (PYUSD/USDS)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1545,44 +1547,44 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>F</t>
         </is>
       </c>
       <c r="E13" s="6" t="n">
-        <v>51710579.95350124</v>
+        <v>99998676.75316638</v>
       </c>
       <c r="F13" s="6" t="n">
-        <v>71943502.10038626</v>
+        <v>99999260.90933624</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>20232922.14688502</v>
+        <v>584.1561698611263</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>217269.3964465584</v>
+        <v>6385.883871640342</v>
       </c>
       <c r="I13" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J13" s="6" t="n">
-        <v>217269.3964465584</v>
+        <v>6385.883871640342</v>
       </c>
       <c r="K13" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L13" s="6" t="n">
-        <v>89619946.74579927</v>
+        <v>99998489.60065988</v>
       </c>
       <c r="M13" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N13" s="6" t="n">
-        <v>148155.4623374592</v>
+        <v>53388.73436020832</v>
       </c>
       <c r="O13" s="6" t="n">
-        <v>148155.4623374592</v>
+        <v>53388.73436020832</v>
       </c>
       <c r="P13" s="6" t="n">
-        <v>69113.93410909919</v>
+        <v>-47002.85048856798</v>
       </c>
       <c r="Q13" s="6" t="n">
         <v>0</v>
@@ -1595,17 +1597,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>S47</t>
+          <t>S11</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Savings USDS / sUSDS proxy (Optimism — POL)</t>
+          <t>Spark Blue Chip USDT Vault (Morpho V2)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>optimism</t>
+          <t>ethereum</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1614,63 +1616,63 @@
         </is>
       </c>
       <c r="E14" s="6" t="n">
-        <v>102040993.0313656</v>
+        <v>51710579.95350124</v>
       </c>
       <c r="F14" s="6" t="n">
-        <v>102351428.4607548</v>
+        <v>71943502.10038626</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>310435.429389201</v>
+        <v>20232922.14688502</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>0</v>
+        <v>217269.3964465584</v>
       </c>
       <c r="I14" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J14" s="6" t="n">
-        <v>0</v>
+        <v>217269.3964465584</v>
       </c>
       <c r="K14" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L14" s="6" t="n">
-        <v>102040993.0313656</v>
+        <v>89619946.74579927</v>
       </c>
       <c r="M14" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N14" s="6" t="n">
-        <v>168689.3492898001</v>
+        <v>47847.67799288761</v>
       </c>
       <c r="O14" s="6" t="n">
-        <v>142728.6782717838</v>
+        <v>47847.67799288761</v>
       </c>
       <c r="P14" s="6" t="n">
-        <v>-168689.3492898001</v>
+        <v>169421.7184536707</v>
       </c>
       <c r="Q14" s="6" t="n">
         <v>0</v>
       </c>
       <c r="R14" s="6" t="n">
-        <v>25960.67101801626</v>
+        <v>0</v>
       </c>
       <c r="S14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>S37</t>
+          <t>S43</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Savings USDS / sUSDS proxy (Base — POL)</t>
+          <t>Savings USDS / sUSDS proxy (Arbitrum — POL)</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>base</t>
+          <t>arbitrum</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1679,13 +1681,13 @@
         </is>
       </c>
       <c r="E15" s="6" t="n">
-        <v>75772907.26348835</v>
+        <v>143328568.5311704</v>
       </c>
       <c r="F15" s="6" t="n">
-        <v>76003428.29531698</v>
+        <v>143764611.5800855</v>
       </c>
       <c r="G15" s="6" t="n">
-        <v>230521.0318286367</v>
+        <v>436043.0489150246</v>
       </c>
       <c r="H15" s="6" t="n">
         <v>0</v>
@@ -1700,190 +1702,194 @@
         <v>0</v>
       </c>
       <c r="L15" s="6" t="n">
-        <v>75772907.26348835</v>
+        <v>143328568.5311704</v>
       </c>
       <c r="M15" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N15" s="6" t="n">
-        <v>125264.1907958033</v>
+        <v>76522.46451019474</v>
       </c>
       <c r="O15" s="6" t="n">
-        <v>105986.4921071849</v>
+        <v>40057.65066839712</v>
       </c>
       <c r="P15" s="6" t="n">
-        <v>-125264.1907958033</v>
+        <v>-76522.46451019474</v>
       </c>
       <c r="Q15" s="6" t="n">
         <v>0</v>
       </c>
       <c r="R15" s="6" t="n">
-        <v>19277.6986886184</v>
+        <v>36464.81384179761</v>
       </c>
       <c r="S15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>SPREAD</t>
+          <t>S1</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>30bps sUSDS spread (Curve LP + PSM3) — Sky Revenue reduction</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr"/>
+          <t>Spark USDS (SparkLend spToken)</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>ethereum</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
       <c r="E16" s="6" t="n">
-        <v>0</v>
+        <v>147862782.1336161</v>
       </c>
       <c r="F16" s="6" t="n">
-        <v>0</v>
+        <v>550178045.362034</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>0</v>
+        <v>402315263.2284179</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>0</v>
+        <v>294091.516876444</v>
       </c>
       <c r="I16" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J16" s="6" t="n">
-        <v>0</v>
+        <v>294091.516876444</v>
       </c>
       <c r="K16" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L16" s="6" t="n">
-        <v>0</v>
+        <v>57731388.11709616</v>
       </c>
       <c r="M16" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N16" s="6" t="n">
-        <v>0</v>
+        <v>30822.52298748116</v>
       </c>
       <c r="O16" s="6" t="n">
-        <v>-102957.2966175266</v>
+        <v>30822.52298748116</v>
       </c>
       <c r="P16" s="6" t="n">
-        <v>0</v>
+        <v>263268.9938889629</v>
       </c>
       <c r="Q16" s="6" t="n">
-        <v>0</v>
+        <v>103099818.9104406</v>
       </c>
       <c r="R16" s="6" t="n">
-        <v>102957.2966175266</v>
+        <v>0</v>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>sky-revenue reduction (no CoF; computed outside venue loop)</t>
+          <t>(avg excl. lending_idle)</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>S1</t>
+          <t>S47</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Spark USDS (SparkLend spToken)</t>
+          <t>Savings USDS / sUSDS proxy (Optimism — POL)</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>ethereum</t>
+          <t>optimism</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E17" s="6" t="n">
-        <v>147862782.1336161</v>
+        <v>102040993.0313656</v>
       </c>
       <c r="F17" s="6" t="n">
-        <v>550178045.362034</v>
+        <v>102351428.4607548</v>
       </c>
       <c r="G17" s="6" t="n">
-        <v>402315263.2284179</v>
+        <v>310435.429389201</v>
       </c>
       <c r="H17" s="6" t="n">
-        <v>294091.516876444</v>
+        <v>0</v>
       </c>
       <c r="I17" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J17" s="6" t="n">
-        <v>294091.516876444</v>
+        <v>0</v>
       </c>
       <c r="K17" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L17" s="6" t="n">
-        <v>57731388.11709616</v>
+        <v>102040993.0313656</v>
       </c>
       <c r="M17" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N17" s="6" t="n">
-        <v>95438.8036196037</v>
+        <v>54479.21756177701</v>
       </c>
       <c r="O17" s="6" t="n">
-        <v>95438.8036196037</v>
+        <v>28518.54654376076</v>
       </c>
       <c r="P17" s="6" t="n">
-        <v>198652.7132568404</v>
+        <v>-54479.21756177701</v>
       </c>
       <c r="Q17" s="6" t="n">
-        <v>103099818.9104406</v>
+        <v>0</v>
       </c>
       <c r="R17" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S17" t="inlineStr">
-        <is>
-          <t>(avg excl. lending_idle)</t>
-        </is>
-      </c>
+        <v>25960.67101801626</v>
+      </c>
+      <c r="S17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>S24</t>
+          <t>S37</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Spark.fi USDT Reserve Curve (sUSDS/USDT)</t>
+          <t>Savings USDS / sUSDS proxy (Base — POL)</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>ethereum</t>
+          <t>base</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E18" s="6" t="n">
-        <v>50002415.26289953</v>
+        <v>75772907.26348835</v>
       </c>
       <c r="F18" s="6" t="n">
-        <v>48750265.64989898</v>
+        <v>76003428.29531698</v>
       </c>
       <c r="G18" s="6" t="n">
-        <v>-1252149.613000547</v>
+        <v>230521.0318286367</v>
       </c>
       <c r="H18" s="6" t="n">
-        <v>74156.06084450937</v>
+        <v>0</v>
       </c>
       <c r="I18" s="6" t="n">
         <v>0</v>
@@ -1892,34 +1898,30 @@
         <v>0</v>
       </c>
       <c r="K18" s="6" t="n">
-        <v>74156.06084450937</v>
+        <v>0</v>
       </c>
       <c r="L18" s="6" t="n">
-        <v>49959631.20890453</v>
+        <v>75772907.26348835</v>
       </c>
       <c r="M18" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N18" s="6" t="n">
-        <v>0</v>
+        <v>40454.80720505187</v>
       </c>
       <c r="O18" s="6" t="n">
-        <v>74156.06084450937</v>
+        <v>21177.10851643347</v>
       </c>
       <c r="P18" s="6" t="n">
-        <v>0</v>
+        <v>-40454.80720505187</v>
       </c>
       <c r="Q18" s="6" t="n">
-        <v>49959631.20890453</v>
+        <v>0</v>
       </c>
       <c r="R18" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S18" t="inlineStr">
-        <is>
-          <t>SDE (fixed)</t>
-        </is>
-      </c>
+        <v>19277.6986886184</v>
+      </c>
+      <c r="S18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1970,13 +1972,13 @@
         <v>1</v>
       </c>
       <c r="N19" s="6" t="n">
-        <v>61396.1385513873</v>
+        <v>19828.24406920799</v>
       </c>
       <c r="O19" s="6" t="n">
-        <v>61396.1385513873</v>
+        <v>19828.24406920799</v>
       </c>
       <c r="P19" s="6" t="n">
-        <v>-156072.5097109343</v>
+        <v>-114504.615228755</v>
       </c>
       <c r="Q19" s="6" t="n">
         <v>0</v>
@@ -2035,13 +2037,13 @@
         <v>1</v>
       </c>
       <c r="N20" s="6" t="n">
-        <v>49053.99712910109</v>
+        <v>15842.27690202296</v>
       </c>
       <c r="O20" s="6" t="n">
-        <v>49053.99712910109</v>
+        <v>15842.27690202296</v>
       </c>
       <c r="P20" s="6" t="n">
-        <v>70587.62079687153</v>
+        <v>103799.3410239497</v>
       </c>
       <c r="Q20" s="6" t="n">
         <v>0</v>
@@ -2100,13 +2102,13 @@
         <v>1</v>
       </c>
       <c r="N21" s="6" t="n">
-        <v>15731.55733210839</v>
+        <v>5080.598971362107</v>
       </c>
       <c r="O21" s="6" t="n">
-        <v>15731.55733210839</v>
+        <v>5080.598971362107</v>
       </c>
       <c r="P21" s="6" t="n">
-        <v>5969.914170589217</v>
+        <v>16620.8725313355</v>
       </c>
       <c r="Q21" s="6" t="n">
         <v>0</v>
@@ -2165,13 +2167,13 @@
         <v>1</v>
       </c>
       <c r="N22" s="6" t="n">
-        <v>15414.08473023965</v>
+        <v>4978.069327256376</v>
       </c>
       <c r="O22" s="6" t="n">
-        <v>15414.08473023965</v>
+        <v>4978.069327256376</v>
       </c>
       <c r="P22" s="6" t="n">
-        <v>17088.81862276035</v>
+        <v>27524.83402574362</v>
       </c>
       <c r="Q22" s="6" t="n">
         <v>0</v>
@@ -2230,13 +2232,13 @@
         <v>1</v>
       </c>
       <c r="N23" s="6" t="n">
-        <v>8264.113436606884</v>
+        <v>2668.944042783939</v>
       </c>
       <c r="O23" s="6" t="n">
-        <v>8264.113436606884</v>
+        <v>2668.944042783939</v>
       </c>
       <c r="P23" s="6" t="n">
-        <v>-8264.113436604654</v>
+        <v>-2668.944042781711</v>
       </c>
       <c r="Q23" s="6" t="n">
         <v>0</v>
@@ -2295,13 +2297,13 @@
         <v>1</v>
       </c>
       <c r="N24" s="6" t="n">
-        <v>8263.567761991457</v>
+        <v>2668.767813957301</v>
       </c>
       <c r="O24" s="6" t="n">
-        <v>8263.567761991457</v>
+        <v>2668.767813957301</v>
       </c>
       <c r="P24" s="6" t="n">
-        <v>-8263.567761991273</v>
+        <v>-2668.767813957117</v>
       </c>
       <c r="Q24" s="6" t="n">
         <v>0</v>
@@ -2360,13 +2362,13 @@
         <v>1</v>
       </c>
       <c r="N25" s="6" t="n">
-        <v>8262.035508582376</v>
+        <v>2668.272963706325</v>
       </c>
       <c r="O25" s="6" t="n">
-        <v>8262.035508582376</v>
+        <v>2668.272963706325</v>
       </c>
       <c r="P25" s="6" t="n">
-        <v>-8262.035508582376</v>
+        <v>-2668.272963706325</v>
       </c>
       <c r="Q25" s="6" t="n">
         <v>0</v>
@@ -2425,13 +2427,13 @@
         <v>1</v>
       </c>
       <c r="N26" s="6" t="n">
-        <v>8190.606142286837</v>
+        <v>2645.204429723013</v>
       </c>
       <c r="O26" s="6" t="n">
-        <v>8190.606142286837</v>
+        <v>2645.204429723013</v>
       </c>
       <c r="P26" s="6" t="n">
-        <v>-8190.606142286368</v>
+        <v>-2645.204429722543</v>
       </c>
       <c r="Q26" s="6" t="n">
         <v>0</v>
@@ -2490,13 +2492,13 @@
         <v>1</v>
       </c>
       <c r="N27" s="6" t="n">
-        <v>2434.286244618223</v>
+        <v>786.1670608519926</v>
       </c>
       <c r="O27" s="6" t="n">
-        <v>2434.286244618223</v>
+        <v>786.1670608519926</v>
       </c>
       <c r="P27" s="6" t="n">
-        <v>607520.8104540096</v>
+        <v>609168.9296377758</v>
       </c>
       <c r="Q27" s="6" t="n">
         <v>0</v>
@@ -2555,13 +2557,13 @@
         <v>1</v>
       </c>
       <c r="N28" s="6" t="n">
-        <v>1763.186401562094</v>
+        <v>569.4314192157252</v>
       </c>
       <c r="O28" s="6" t="n">
-        <v>1763.186401562094</v>
+        <v>569.4314192157252</v>
       </c>
       <c r="P28" s="6" t="n">
-        <v>-4403.623804004864</v>
+        <v>-3209.868821658495</v>
       </c>
       <c r="Q28" s="6" t="n">
         <v>0</v>
@@ -2620,13 +2622,13 @@
         <v>1</v>
       </c>
       <c r="N29" s="6" t="n">
-        <v>1624.070802853624</v>
+        <v>524.5032183531125</v>
       </c>
       <c r="O29" s="6" t="n">
-        <v>1374.132273833536</v>
+        <v>274.5646893330244</v>
       </c>
       <c r="P29" s="6" t="n">
-        <v>-1624.070802853624</v>
+        <v>-524.5032183531125</v>
       </c>
       <c r="Q29" s="6" t="n">
         <v>0</v>
@@ -2685,13 +2687,13 @@
         <v>1</v>
       </c>
       <c r="N30" s="6" t="n">
-        <v>0.7640238766342328</v>
+        <v>0.2467460048472986</v>
       </c>
       <c r="O30" s="6" t="n">
-        <v>0.7640238766342328</v>
+        <v>0.2467460048472986</v>
       </c>
       <c r="P30" s="6" t="n">
-        <v>75.5664416425715</v>
+        <v>76.08371951435845</v>
       </c>
       <c r="Q30" s="6" t="n">
         <v>0</v>
@@ -2750,13 +2752,13 @@
         <v>1</v>
       </c>
       <c r="N31" s="6" t="n">
-        <v>0.6084298104624435</v>
+        <v>0.1964959859932215</v>
       </c>
       <c r="O31" s="6" t="n">
-        <v>0.6084298104624435</v>
+        <v>0.1964959859932215</v>
       </c>
       <c r="P31" s="6" t="n">
-        <v>0.5529154648753346</v>
+        <v>0.9648492893445566</v>
       </c>
       <c r="Q31" s="6" t="n">
         <v>0</v>
@@ -2815,13 +2817,13 @@
         <v>1</v>
       </c>
       <c r="N32" s="6" t="n">
-        <v>0.4693255205745931</v>
+        <v>0.1515714373807448</v>
       </c>
       <c r="O32" s="6" t="n">
-        <v>0.4693255205745931</v>
+        <v>0.1515714373807448</v>
       </c>
       <c r="P32" s="6" t="n">
-        <v>-0.4693255205745931</v>
+        <v>-0.1515714373807448</v>
       </c>
       <c r="Q32" s="6" t="n">
         <v>0</v>
@@ -2880,13 +2882,13 @@
         <v>1</v>
       </c>
       <c r="N33" s="6" t="n">
-        <v>0.1906256617856336</v>
+        <v>0.06156367870882053</v>
       </c>
       <c r="O33" s="6" t="n">
-        <v>0.1906256617856336</v>
+        <v>0.06156367870882053</v>
       </c>
       <c r="P33" s="6" t="n">
-        <v>-0.1906256621160924</v>
+        <v>-0.06156367903927934</v>
       </c>
       <c r="Q33" s="6" t="n">
         <v>0</v>
@@ -2945,13 +2947,13 @@
         <v>1</v>
       </c>
       <c r="N34" s="6" t="n">
-        <v>0.164490838970566</v>
+        <v>0.05312328395909313</v>
       </c>
       <c r="O34" s="6" t="n">
-        <v>0.164490838970566</v>
+        <v>0.05312328395909313</v>
       </c>
       <c r="P34" s="6" t="n">
-        <v>0.1472727094635601</v>
+        <v>0.258640264475033</v>
       </c>
       <c r="Q34" s="6" t="n">
         <v>0</v>
@@ -3010,13 +3012,13 @@
         <v>1</v>
       </c>
       <c r="N35" s="6" t="n">
-        <v>0.03621496728406336</v>
+        <v>0.01169583669607777</v>
       </c>
       <c r="O35" s="6" t="n">
-        <v>0.03621496728406336</v>
+        <v>0.01169583669607777</v>
       </c>
       <c r="P35" s="6" t="n">
-        <v>-0.03620891357689337</v>
+        <v>-0.01168978298890778</v>
       </c>
       <c r="Q35" s="6" t="n">
         <v>0</v>
@@ -3075,13 +3077,13 @@
         <v>1</v>
       </c>
       <c r="N36" s="6" t="n">
-        <v>0.009750076763868005</v>
+        <v>0.003148844639564389</v>
       </c>
       <c r="O36" s="6" t="n">
-        <v>0.009750076763868005</v>
+        <v>0.003148844639564389</v>
       </c>
       <c r="P36" s="6" t="n">
-        <v>0.005639923236131995</v>
+        <v>0.01224115536043561</v>
       </c>
       <c r="Q36" s="6" t="n">
         <v>0</v>
@@ -3140,13 +3142,13 @@
         <v>1</v>
       </c>
       <c r="N37" s="6" t="n">
-        <v>0.002555127784637646</v>
+        <v>0.0008251935469753605</v>
       </c>
       <c r="O37" s="6" t="n">
-        <v>0.002555127784637646</v>
+        <v>0.0008251935469753605</v>
       </c>
       <c r="P37" s="6" t="n">
-        <v>8.467833872215362</v>
+        <v>8.469563806453024</v>
       </c>
       <c r="Q37" s="6" t="n">
         <v>0</v>
@@ -3205,13 +3207,13 @@
         <v>1</v>
       </c>
       <c r="N38" s="6" t="n">
-        <v>0.0002552980339202064</v>
+        <v>8.245000168409469e-05</v>
       </c>
       <c r="O38" s="6" t="n">
-        <v>0.0002552980339202064</v>
+        <v>8.245000168409469e-05</v>
       </c>
       <c r="P38" s="6" t="n">
-        <v>0.0004787019660797936</v>
+        <v>0.0006515499983159053</v>
       </c>
       <c r="Q38" s="6" t="n">
         <v>0</v>
@@ -3270,13 +3272,13 @@
         <v>1</v>
       </c>
       <c r="N39" s="6" t="n">
-        <v>9.552412594628854e-05</v>
+        <v>3.085007833473877e-05</v>
       </c>
       <c r="O39" s="6" t="n">
-        <v>9.552412594628854e-05</v>
+        <v>3.085007833473877e-05</v>
       </c>
       <c r="P39" s="6" t="n">
-        <v>9.047587405371145e-05</v>
+        <v>0.0001551499216652612</v>
       </c>
       <c r="Q39" s="6" t="n">
         <v>0</v>
@@ -3335,13 +3337,13 @@
         <v>1</v>
       </c>
       <c r="N40" s="6" t="n">
-        <v>1.049090741663027e-05</v>
+        <v>3.388100256342735e-06</v>
       </c>
       <c r="O40" s="6" t="n">
-        <v>1.049090741663027e-05</v>
+        <v>3.388100256342735e-06</v>
       </c>
       <c r="P40" s="6" t="n">
-        <v>6.509092583369726e-06</v>
+        <v>1.361189974365727e-05</v>
       </c>
       <c r="Q40" s="6" t="n">
         <v>0</v>
@@ -3400,13 +3402,13 @@
         <v>1</v>
       </c>
       <c r="N41" s="6" t="n">
-        <v>9.496177446127806e-06</v>
+        <v>3.066846361497693e-06</v>
       </c>
       <c r="O41" s="6" t="n">
-        <v>9.496177446127806e-06</v>
+        <v>3.066846361497693e-06</v>
       </c>
       <c r="P41" s="6" t="n">
-        <v>-7.352352940757807e-06</v>
+        <v>-9.23021856127693e-07</v>
       </c>
       <c r="Q41" s="6" t="n">
         <v>0</v>
@@ -3465,13 +3467,13 @@
         <v>1</v>
       </c>
       <c r="N42" s="6" t="n">
-        <v>2.810359692447442e-06</v>
+        <v>9.07622192843153e-07</v>
       </c>
       <c r="O42" s="6" t="n">
-        <v>2.810359692447442e-06</v>
+        <v>9.07622192843153e-07</v>
       </c>
       <c r="P42" s="6" t="n">
-        <v>2.189640307552558e-06</v>
+        <v>4.092377807156847e-06</v>
       </c>
       <c r="Q42" s="6" t="n">
         <v>0</v>
@@ -3530,13 +3532,13 @@
         <v>1</v>
       </c>
       <c r="N43" s="6" t="n">
-        <v>2.050148585179211e-06</v>
+        <v>6.621075442888142e-07</v>
       </c>
       <c r="O43" s="6" t="n">
-        <v>2.050148585179211e-06</v>
+        <v>6.621075442888142e-07</v>
       </c>
       <c r="P43" s="6" t="n">
-        <v>-2.050148585179211e-06</v>
+        <v>-6.621075442888142e-07</v>
       </c>
       <c r="Q43" s="6" t="n">
         <v>0</v>
@@ -3595,13 +3597,13 @@
         <v>1</v>
       </c>
       <c r="N44" s="6" t="n">
-        <v>8.612373141179706e-07</v>
+        <v>2.781416562793655e-07</v>
       </c>
       <c r="O44" s="6" t="n">
-        <v>8.612373141179706e-07</v>
+        <v>2.781416562793655e-07</v>
       </c>
       <c r="P44" s="6" t="n">
-        <v>-1.545305073089706e-07</v>
+        <v>4.285651505296345e-07</v>
       </c>
       <c r="Q44" s="6" t="n">
         <v>0</v>
@@ -3660,13 +3662,13 @@
         <v>1</v>
       </c>
       <c r="N45" s="6" t="n">
-        <v>1.238149852338873e-07</v>
+        <v>3.998677774479397e-08</v>
       </c>
       <c r="O45" s="6" t="n">
-        <v>1.238149852338873e-07</v>
+        <v>3.998677774479397e-08</v>
       </c>
       <c r="P45" s="6" t="n">
-        <v>-1.238149852338873e-07</v>
+        <v>-3.998677774479397e-08</v>
       </c>
       <c r="Q45" s="6" t="n">
         <v>0</v>
@@ -4585,7 +4587,7 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>10557149.38334401</v>
+        <v>3284300.977760902</v>
       </c>
     </row>
     <row r="5">
@@ -4605,7 +4607,7 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>10631305.44418851</v>
+        <v>3358457.038605412</v>
       </c>
     </row>
     <row r="8">
@@ -4632,7 +4634,7 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>10557149.38334401</v>
+        <v>3284300.977760902</v>
       </c>
     </row>
     <row r="12">
@@ -4642,7 +4644,7 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>-2819972.476227154</v>
+        <v>-10092820.88181026</v>
       </c>
     </row>
     <row r="13" ht="60" customHeight="1">
@@ -4937,4 +4939,1669 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:O38"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="11" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="11" customWidth="1" min="13" max="13"/>
+    <col width="18" customWidth="1" min="14" max="14"/>
+    <col width="22" customWidth="1" min="15" max="15"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Daily ilk debt + Sky charge breakdown</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="45" customHeight="1">
+      <c r="A3" s="9" t="inlineStr">
+        <is>
+          <t>cum_debt = Σ on-chain Vat dart from frob (0x76088703) + grab (0x7bab3f40). utilized = cum_debt − Σ deductions. base_apy = (1+SSR)(1+0.003)−1 (multiplicative). sub_apy applies on the first cap_usd of utilized when the subsidy is active; excess pays base_apy.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>cum_debt</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>− ALM idle</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>− PSM USDS</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>− SDE NAV</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>− Curve idle</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>− Lending idle</t>
+        </is>
+      </c>
+      <c r="H5" s="2">
+        <f> utilized</f>
+        <v/>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>SSR APY</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>base APY</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>T (months)</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>ref_rate APY</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>sub APY</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>daily Sky charge</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>daily Sky charge (gross on cum_debt)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="n">
+        <v>3786873547.945224</v>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>334970000</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>109271584.0644501</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>81897516.64033359</v>
+      </c>
+      <c r="F6" s="6" t="n">
+        <v>68133383.80742754</v>
+      </c>
+      <c r="G6" s="6" t="n">
+        <v>127906874.3387326</v>
+      </c>
+      <c r="H6" s="6" t="n">
+        <v>3064694189.09428</v>
+      </c>
+      <c r="I6" s="7" t="n">
+        <v>0.0375</v>
+      </c>
+      <c r="J6" s="7" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="K6" t="n">
+        <v>4</v>
+      </c>
+      <c r="L6" s="7" t="n">
+        <v>0.0433</v>
+      </c>
+      <c r="M6" s="7" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="N6" s="3" t="n">
+        <v>334275.4575777341</v>
+      </c>
+      <c r="O6" s="3" t="n">
+        <v>413045.742878023</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="n">
+        <v>4113602587.50019</v>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>334970000</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>109236625.511487</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>74371158.35490692</v>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>66387928.31178243</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>131684974.1461452</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>3396951901.175869</v>
+      </c>
+      <c r="I7" s="7" t="n">
+        <v>0.0375</v>
+      </c>
+      <c r="J7" s="7" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="K7" t="n">
+        <v>4</v>
+      </c>
+      <c r="L7" s="7" t="n">
+        <v>0.0433</v>
+      </c>
+      <c r="M7" s="7" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="N7" s="3" t="n">
+        <v>370515.8104113157</v>
+      </c>
+      <c r="O7" s="3" t="n">
+        <v>448683.0666899128</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="n">
+        <v>4112495173.033005</v>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>334970000</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>109212118.7652359</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>78198703.5201842</v>
+      </c>
+      <c r="F8" s="6" t="n">
+        <v>69297142.12576202</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>129926697.4882286</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>3390890511.133594</v>
+      </c>
+      <c r="I8" s="7" t="n">
+        <v>0.0375</v>
+      </c>
+      <c r="J8" s="7" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="K8" t="n">
+        <v>4</v>
+      </c>
+      <c r="L8" s="7" t="n">
+        <v>0.0433</v>
+      </c>
+      <c r="M8" s="7" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="N8" s="3" t="n">
+        <v>369854.6762801686</v>
+      </c>
+      <c r="O8" s="3" t="n">
+        <v>448562.277647057</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="n">
+        <v>4014386628.19746</v>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>334970000</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>109413093.6674421</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>75725030.78440267</v>
+      </c>
+      <c r="F9" s="6" t="n">
+        <v>64115633.06430446</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>129945312.0277757</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>3300217558.653535</v>
+      </c>
+      <c r="I9" s="7" t="n">
+        <v>0.0375</v>
+      </c>
+      <c r="J9" s="7" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="K9" t="n">
+        <v>4</v>
+      </c>
+      <c r="L9" s="7" t="n">
+        <v>0.0433</v>
+      </c>
+      <c r="M9" s="7" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="N9" s="3" t="n">
+        <v>359964.7033138436</v>
+      </c>
+      <c r="O9" s="3" t="n">
+        <v>437861.2821500545</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="n">
+        <v>3967538459.305897</v>
+      </c>
+      <c r="C10" s="6" t="n">
+        <v>334970000</v>
+      </c>
+      <c r="D10" s="6" t="n">
+        <v>109666118.9886243</v>
+      </c>
+      <c r="E10" s="6" t="n">
+        <v>62633764.42527747</v>
+      </c>
+      <c r="F10" s="6" t="n">
+        <v>71985346.18365841</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>129991339.9884334</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>3258291889.719903</v>
+      </c>
+      <c r="I10" s="7" t="n">
+        <v>0.0375</v>
+      </c>
+      <c r="J10" s="7" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="K10" t="n">
+        <v>4</v>
+      </c>
+      <c r="L10" s="7" t="n">
+        <v>0.0433</v>
+      </c>
+      <c r="M10" s="7" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="N10" s="3" t="n">
+        <v>355391.7438920149</v>
+      </c>
+      <c r="O10" s="3" t="n">
+        <v>432751.4107806262</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="n">
+        <v>3773637803.723945</v>
+      </c>
+      <c r="C11" s="6" t="n">
+        <v>334970000</v>
+      </c>
+      <c r="D11" s="6" t="n">
+        <v>109667151.3287632</v>
+      </c>
+      <c r="E11" s="6" t="n">
+        <v>65914408.62152216</v>
+      </c>
+      <c r="F11" s="6" t="n">
+        <v>69182310.83017388</v>
+      </c>
+      <c r="G11" s="6" t="n">
+        <v>132866251.0455103</v>
+      </c>
+      <c r="H11" s="6" t="n">
+        <v>3061037681.897975</v>
+      </c>
+      <c r="I11" s="7" t="n">
+        <v>0.0375</v>
+      </c>
+      <c r="J11" s="7" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="K11" t="n">
+        <v>4</v>
+      </c>
+      <c r="L11" s="7" t="n">
+        <v>0.0433</v>
+      </c>
+      <c r="M11" s="7" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="N11" s="3" t="n">
+        <v>333876.6312868336</v>
+      </c>
+      <c r="O11" s="3" t="n">
+        <v>411602.080253643</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="n">
+        <v>3829641619.123199</v>
+      </c>
+      <c r="C12" s="6" t="n">
+        <v>334970000</v>
+      </c>
+      <c r="D12" s="6" t="n">
+        <v>109729057.8747254</v>
+      </c>
+      <c r="E12" s="6" t="n">
+        <v>68822191.85959996</v>
+      </c>
+      <c r="F12" s="6" t="n">
+        <v>59598590.74937253</v>
+      </c>
+      <c r="G12" s="6" t="n">
+        <v>133190285.3282568</v>
+      </c>
+      <c r="H12" s="6" t="n">
+        <v>3123331493.311244</v>
+      </c>
+      <c r="I12" s="7" t="n">
+        <v>0.0375</v>
+      </c>
+      <c r="J12" s="7" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="K12" t="n">
+        <v>4</v>
+      </c>
+      <c r="L12" s="7" t="n">
+        <v>0.0433</v>
+      </c>
+      <c r="M12" s="7" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="N12" s="3" t="n">
+        <v>340671.2055672075</v>
+      </c>
+      <c r="O12" s="3" t="n">
+        <v>417710.5856586202</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="n">
+        <v>3112489658.938523</v>
+      </c>
+      <c r="C13" s="6" t="n">
+        <v>334970000</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>109756088.3909883</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>46416747.2661341</v>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>62126087.28772155</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>136081135.6656561</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>2423139600.328023</v>
+      </c>
+      <c r="I13" s="7" t="n">
+        <v>0.0375</v>
+      </c>
+      <c r="J13" s="7" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="K13" t="n">
+        <v>4</v>
+      </c>
+      <c r="L13" s="7" t="n">
+        <v>0.0433</v>
+      </c>
+      <c r="M13" s="7" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="N13" s="3" t="n">
+        <v>264299.1596214559</v>
+      </c>
+      <c r="O13" s="3" t="n">
+        <v>339488.6539250828</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="n">
+        <v>3862142308.882361</v>
+      </c>
+      <c r="C14" s="6" t="n">
+        <v>334970000</v>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>109737227.1714184</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>59621771.27202594</v>
+      </c>
+      <c r="F14" s="6" t="n">
+        <v>63144552.54356655</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>136418480.8456975</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>3158250277.049653</v>
+      </c>
+      <c r="I14" s="7" t="n">
+        <v>0.0375</v>
+      </c>
+      <c r="J14" s="7" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="K14" t="n">
+        <v>4</v>
+      </c>
+      <c r="L14" s="7" t="n">
+        <v>0.0433</v>
+      </c>
+      <c r="M14" s="7" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="N14" s="3" t="n">
+        <v>344479.902844003</v>
+      </c>
+      <c r="O14" s="3" t="n">
+        <v>421255.5341169349</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="n">
+        <v>4007860775.201573</v>
+      </c>
+      <c r="C15" s="6" t="n">
+        <v>334970000</v>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>109820179.5695339</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>62881956.35592515</v>
+      </c>
+      <c r="F15" s="6" t="n">
+        <v>67929925.5704889</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>136520708.1372503</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>3295738005.568375</v>
+      </c>
+      <c r="I15" s="7" t="n">
+        <v>0.0375</v>
+      </c>
+      <c r="J15" s="7" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="K15" t="n">
+        <v>4</v>
+      </c>
+      <c r="L15" s="7" t="n">
+        <v>0.0433</v>
+      </c>
+      <c r="M15" s="7" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="N15" s="3" t="n">
+        <v>359476.1049203679</v>
+      </c>
+      <c r="O15" s="3" t="n">
+        <v>437149.4876408184</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="n">
+        <v>3944031608.133983</v>
+      </c>
+      <c r="C16" s="6" t="n">
+        <v>334970000</v>
+      </c>
+      <c r="D16" s="6" t="n">
+        <v>109824143.9731289</v>
+      </c>
+      <c r="E16" s="6" t="n">
+        <v>84921355.55294961</v>
+      </c>
+      <c r="F16" s="6" t="n">
+        <v>67458232.10747725</v>
+      </c>
+      <c r="G16" s="6" t="n">
+        <v>146800932.9007985</v>
+      </c>
+      <c r="H16" s="6" t="n">
+        <v>3200056943.599629</v>
+      </c>
+      <c r="I16" s="7" t="n">
+        <v>0.0375</v>
+      </c>
+      <c r="J16" s="7" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="K16" t="n">
+        <v>4</v>
+      </c>
+      <c r="L16" s="7" t="n">
+        <v>0.0433</v>
+      </c>
+      <c r="M16" s="7" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="N16" s="3" t="n">
+        <v>349039.8823161875</v>
+      </c>
+      <c r="O16" s="3" t="n">
+        <v>430187.4474789483</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="n">
+        <v>3869106066.859931</v>
+      </c>
+      <c r="C17" s="6" t="n">
+        <v>334970000</v>
+      </c>
+      <c r="D17" s="6" t="n">
+        <v>109837230.945328</v>
+      </c>
+      <c r="E17" s="6" t="n">
+        <v>78116321.12843026</v>
+      </c>
+      <c r="F17" s="6" t="n">
+        <v>58043367.04671003</v>
+      </c>
+      <c r="G17" s="6" t="n">
+        <v>146820705.7658038</v>
+      </c>
+      <c r="H17" s="6" t="n">
+        <v>3141318441.973659</v>
+      </c>
+      <c r="I17" s="7" t="n">
+        <v>0.0375</v>
+      </c>
+      <c r="J17" s="7" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="K17" t="n">
+        <v>4</v>
+      </c>
+      <c r="L17" s="7" t="n">
+        <v>0.0433</v>
+      </c>
+      <c r="M17" s="7" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="N17" s="3" t="n">
+        <v>342633.0964194667</v>
+      </c>
+      <c r="O17" s="3" t="n">
+        <v>422015.092245996</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="n">
+        <v>3869966485.495641</v>
+      </c>
+      <c r="C18" s="6" t="n">
+        <v>334970000</v>
+      </c>
+      <c r="D18" s="6" t="n">
+        <v>109812101.2069135</v>
+      </c>
+      <c r="E18" s="6" t="n">
+        <v>85902407.14010979</v>
+      </c>
+      <c r="F18" s="6" t="n">
+        <v>60741445.97380174</v>
+      </c>
+      <c r="G18" s="6" t="n">
+        <v>146084521.7500651</v>
+      </c>
+      <c r="H18" s="6" t="n">
+        <v>3132456009.424751</v>
+      </c>
+      <c r="I18" s="7" t="n">
+        <v>0.0375</v>
+      </c>
+      <c r="J18" s="7" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="K18" t="n">
+        <v>4</v>
+      </c>
+      <c r="L18" s="7" t="n">
+        <v>0.0433</v>
+      </c>
+      <c r="M18" s="7" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="N18" s="3" t="n">
+        <v>341666.4441165779</v>
+      </c>
+      <c r="O18" s="3" t="n">
+        <v>422108.9407070216</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="n">
+        <v>3906757002.936191</v>
+      </c>
+      <c r="C19" s="6" t="n">
+        <v>334970000</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>109817281.9042201</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>63272317.16911007</v>
+      </c>
+      <c r="F19" s="6" t="n">
+        <v>58432587.64789255</v>
+      </c>
+      <c r="G19" s="6" t="n">
+        <v>174559965.1979237</v>
+      </c>
+      <c r="H19" s="6" t="n">
+        <v>3165704851.017045</v>
+      </c>
+      <c r="I19" s="7" t="n">
+        <v>0.0375</v>
+      </c>
+      <c r="J19" s="7" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="K19" t="n">
+        <v>4</v>
+      </c>
+      <c r="L19" s="7" t="n">
+        <v>0.0433</v>
+      </c>
+      <c r="M19" s="7" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="N19" s="3" t="n">
+        <v>345292.9957564588</v>
+      </c>
+      <c r="O19" s="3" t="n">
+        <v>426121.7936356186</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="n">
+        <v>3941296256.964431</v>
+      </c>
+      <c r="C20" s="6" t="n">
+        <v>334970000</v>
+      </c>
+      <c r="D20" s="6" t="n">
+        <v>109861276.5733739</v>
+      </c>
+      <c r="E20" s="6" t="n">
+        <v>88511698.91894951</v>
+      </c>
+      <c r="F20" s="6" t="n">
+        <v>42181809.13057283</v>
+      </c>
+      <c r="G20" s="6" t="n">
+        <v>169618722.6830847</v>
+      </c>
+      <c r="H20" s="6" t="n">
+        <v>3196152749.65845</v>
+      </c>
+      <c r="I20" s="7" t="n">
+        <v>0.0375</v>
+      </c>
+      <c r="J20" s="7" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="K20" t="n">
+        <v>4</v>
+      </c>
+      <c r="L20" s="7" t="n">
+        <v>0.0433</v>
+      </c>
+      <c r="M20" s="7" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="N20" s="3" t="n">
+        <v>348614.0400834441</v>
+      </c>
+      <c r="O20" s="3" t="n">
+        <v>429889.0944598799</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="n">
+        <v>3949955056.90474</v>
+      </c>
+      <c r="C21" s="6" t="n">
+        <v>334970000</v>
+      </c>
+      <c r="D21" s="6" t="n">
+        <v>109944218.3095993</v>
+      </c>
+      <c r="E21" s="6" t="n">
+        <v>87033668.77329952</v>
+      </c>
+      <c r="F21" s="6" t="n">
+        <v>51954304.76465927</v>
+      </c>
+      <c r="G21" s="6" t="n">
+        <v>172338153.0245515</v>
+      </c>
+      <c r="H21" s="6" t="n">
+        <v>3193714712.03263</v>
+      </c>
+      <c r="I21" s="7" t="n">
+        <v>0.0375</v>
+      </c>
+      <c r="J21" s="7" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="K21" t="n">
+        <v>4</v>
+      </c>
+      <c r="L21" s="7" t="n">
+        <v>0.0433</v>
+      </c>
+      <c r="M21" s="7" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="N21" s="3" t="n">
+        <v>348348.1159511562</v>
+      </c>
+      <c r="O21" s="3" t="n">
+        <v>430833.5359387135</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="n">
+        <v>3930000358.477587</v>
+      </c>
+      <c r="C22" s="6" t="n">
+        <v>334970000</v>
+      </c>
+      <c r="D22" s="6" t="n">
+        <v>110151080.1866189</v>
+      </c>
+      <c r="E22" s="6" t="n">
+        <v>87868461.85445462</v>
+      </c>
+      <c r="F22" s="6" t="n">
+        <v>60263592.76517375</v>
+      </c>
+      <c r="G22" s="6" t="n">
+        <v>162877756.5589872</v>
+      </c>
+      <c r="H22" s="6" t="n">
+        <v>3173869467.112352</v>
+      </c>
+      <c r="I22" s="7" t="n">
+        <v>0.0375</v>
+      </c>
+      <c r="J22" s="7" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="K22" t="n">
+        <v>4</v>
+      </c>
+      <c r="L22" s="7" t="n">
+        <v>0.0433</v>
+      </c>
+      <c r="M22" s="7" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="N22" s="3" t="n">
+        <v>346183.5351097547</v>
+      </c>
+      <c r="O22" s="3" t="n">
+        <v>428657.0166725176</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="n">
+        <v>4128625750.909277</v>
+      </c>
+      <c r="C23" s="6" t="n">
+        <v>334970000</v>
+      </c>
+      <c r="D23" s="6" t="n">
+        <v>110145162.8914285</v>
+      </c>
+      <c r="E23" s="6" t="n">
+        <v>89081856.06629945</v>
+      </c>
+      <c r="F23" s="6" t="n">
+        <v>42740384.84050981</v>
+      </c>
+      <c r="G23" s="6" t="n">
+        <v>231737478.377994</v>
+      </c>
+      <c r="H23" s="6" t="n">
+        <v>3319950868.733045</v>
+      </c>
+      <c r="I23" s="7" t="n">
+        <v>0.0375</v>
+      </c>
+      <c r="J23" s="7" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="K23" t="n">
+        <v>4</v>
+      </c>
+      <c r="L23" s="7" t="n">
+        <v>0.0433</v>
+      </c>
+      <c r="M23" s="7" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="N23" s="3" t="n">
+        <v>362117.0750838638</v>
+      </c>
+      <c r="O23" s="3" t="n">
+        <v>450321.6885271936</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="B24" s="6" t="n">
+        <v>4099347532.103574</v>
+      </c>
+      <c r="C24" s="6" t="n">
+        <v>334970000</v>
+      </c>
+      <c r="D24" s="6" t="n">
+        <v>110135980.040481</v>
+      </c>
+      <c r="E24" s="6" t="n">
+        <v>90072399.6267707</v>
+      </c>
+      <c r="F24" s="6" t="n">
+        <v>56943828.95422778</v>
+      </c>
+      <c r="G24" s="6" t="n">
+        <v>229182741.6867744</v>
+      </c>
+      <c r="H24" s="6" t="n">
+        <v>3278042581.79532</v>
+      </c>
+      <c r="I24" s="7" t="n">
+        <v>0.0375</v>
+      </c>
+      <c r="J24" s="7" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="K24" t="n">
+        <v>4</v>
+      </c>
+      <c r="L24" s="7" t="n">
+        <v>0.0433</v>
+      </c>
+      <c r="M24" s="7" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="N24" s="3" t="n">
+        <v>357546.011568862</v>
+      </c>
+      <c r="O24" s="3" t="n">
+        <v>447128.2247149919</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="B25" s="6" t="n">
+        <v>3849261001.889072</v>
+      </c>
+      <c r="C25" s="6" t="n">
+        <v>334970000</v>
+      </c>
+      <c r="D25" s="6" t="n">
+        <v>110063401.5573106</v>
+      </c>
+      <c r="E25" s="6" t="n">
+        <v>90207535.65130401</v>
+      </c>
+      <c r="F25" s="6" t="n">
+        <v>51602034.69547939</v>
+      </c>
+      <c r="G25" s="6" t="n">
+        <v>230888253.3173563</v>
+      </c>
+      <c r="H25" s="6" t="n">
+        <v>3031529776.667622</v>
+      </c>
+      <c r="I25" s="7" t="n">
+        <v>0.0375</v>
+      </c>
+      <c r="J25" s="7" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="K25" t="n">
+        <v>4</v>
+      </c>
+      <c r="L25" s="7" t="n">
+        <v>0.0433</v>
+      </c>
+      <c r="M25" s="7" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="N25" s="3" t="n">
+        <v>330658.1148821178</v>
+      </c>
+      <c r="O25" s="3" t="n">
+        <v>419850.5310322215</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="B26" s="6" t="n">
+        <v>3796096805.831977</v>
+      </c>
+      <c r="C26" s="6" t="n">
+        <v>334970000</v>
+      </c>
+      <c r="D26" s="6" t="n">
+        <v>110201806.0378861</v>
+      </c>
+      <c r="E26" s="6" t="n">
+        <v>90137880.50639333</v>
+      </c>
+      <c r="F26" s="6" t="n">
+        <v>53876705.01782864</v>
+      </c>
+      <c r="G26" s="6" t="n">
+        <v>254742493.5135711</v>
+      </c>
+      <c r="H26" s="6" t="n">
+        <v>2952167920.756298</v>
+      </c>
+      <c r="I26" s="7" t="n">
+        <v>0.0375</v>
+      </c>
+      <c r="J26" s="7" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="K26" t="n">
+        <v>4</v>
+      </c>
+      <c r="L26" s="7" t="n">
+        <v>0.0433</v>
+      </c>
+      <c r="M26" s="7" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="N26" s="3" t="n">
+        <v>322001.8774038798</v>
+      </c>
+      <c r="O26" s="3" t="n">
+        <v>414051.7514910269</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B27" s="6" t="n">
+        <v>4276518811.263577</v>
+      </c>
+      <c r="C27" s="6" t="n">
+        <v>334970000</v>
+      </c>
+      <c r="D27" s="6" t="n">
+        <v>110246348.1665363</v>
+      </c>
+      <c r="E27" s="6" t="n">
+        <v>90683527.73142503</v>
+      </c>
+      <c r="F27" s="6" t="n">
+        <v>60950192.97977956</v>
+      </c>
+      <c r="G27" s="6" t="n">
+        <v>239797730.4064276</v>
+      </c>
+      <c r="H27" s="6" t="n">
+        <v>3439871011.979409</v>
+      </c>
+      <c r="I27" s="7" t="n">
+        <v>0.0375</v>
+      </c>
+      <c r="J27" s="7" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="K27" t="n">
+        <v>4</v>
+      </c>
+      <c r="L27" s="7" t="n">
+        <v>0.0433</v>
+      </c>
+      <c r="M27" s="7" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="N27" s="3" t="n">
+        <v>375197.1275403578</v>
+      </c>
+      <c r="O27" s="3" t="n">
+        <v>466452.8315947228</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="B28" s="6" t="n">
+        <v>4260541447.925423</v>
+      </c>
+      <c r="C28" s="6" t="n">
+        <v>334970000</v>
+      </c>
+      <c r="D28" s="6" t="n">
+        <v>110397429.3795781</v>
+      </c>
+      <c r="E28" s="6" t="n">
+        <v>90958523.65549019</v>
+      </c>
+      <c r="F28" s="6" t="n">
+        <v>64022634.63846193</v>
+      </c>
+      <c r="G28" s="6" t="n">
+        <v>240130221.5557107</v>
+      </c>
+      <c r="H28" s="6" t="n">
+        <v>3420062638.696182</v>
+      </c>
+      <c r="I28" s="7" t="n">
+        <v>0.0375</v>
+      </c>
+      <c r="J28" s="7" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="K28" t="n">
+        <v>4</v>
+      </c>
+      <c r="L28" s="7" t="n">
+        <v>0.0433</v>
+      </c>
+      <c r="M28" s="7" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="N28" s="3" t="n">
+        <v>373036.568399846</v>
+      </c>
+      <c r="O28" s="3" t="n">
+        <v>464710.1322873164</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="n">
+        <v>4278271428.210862</v>
+      </c>
+      <c r="C29" s="6" t="n">
+        <v>334970000</v>
+      </c>
+      <c r="D29" s="6" t="n">
+        <v>110459412.1575361</v>
+      </c>
+      <c r="E29" s="6" t="n">
+        <v>91000613.80843022</v>
+      </c>
+      <c r="F29" s="6" t="n">
+        <v>63901753.89657893</v>
+      </c>
+      <c r="G29" s="6" t="n">
+        <v>243572783.8200219</v>
+      </c>
+      <c r="H29" s="6" t="n">
+        <v>3434366864.528295</v>
+      </c>
+      <c r="I29" s="7" t="n">
+        <v>0.0375</v>
+      </c>
+      <c r="J29" s="7" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="K29" t="n">
+        <v>4</v>
+      </c>
+      <c r="L29" s="7" t="n">
+        <v>0.0433</v>
+      </c>
+      <c r="M29" s="7" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="N29" s="3" t="n">
+        <v>374596.7735427734</v>
+      </c>
+      <c r="O29" s="3" t="n">
+        <v>466643.9948220676</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="n">
+        <v>4275937035.604297</v>
+      </c>
+      <c r="C30" s="6" t="n">
+        <v>334970000</v>
+      </c>
+      <c r="D30" s="6" t="n">
+        <v>110548351.2880701</v>
+      </c>
+      <c r="E30" s="6" t="n">
+        <v>90132356.81756249</v>
+      </c>
+      <c r="F30" s="6" t="n">
+        <v>65846944.15199657</v>
+      </c>
+      <c r="G30" s="6" t="n">
+        <v>245605231.7022537</v>
+      </c>
+      <c r="H30" s="6" t="n">
+        <v>3428834151.644414</v>
+      </c>
+      <c r="I30" s="7" t="n">
+        <v>0.0375</v>
+      </c>
+      <c r="J30" s="7" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="K30" t="n">
+        <v>4</v>
+      </c>
+      <c r="L30" s="7" t="n">
+        <v>0.0433</v>
+      </c>
+      <c r="M30" s="7" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="N30" s="3" t="n">
+        <v>373993.3038271044</v>
+      </c>
+      <c r="O30" s="3" t="n">
+        <v>466389.3755652744</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="n">
+        <v>4019063778.948612</v>
+      </c>
+      <c r="C31" s="6" t="n">
+        <v>334970000</v>
+      </c>
+      <c r="D31" s="6" t="n">
+        <v>110567333.2809158</v>
+      </c>
+      <c r="E31" s="6" t="n">
+        <v>91214545.99128646</v>
+      </c>
+      <c r="F31" s="6" t="n">
+        <v>71416697.68580709</v>
+      </c>
+      <c r="G31" s="6" t="n">
+        <v>179571549.4489093</v>
+      </c>
+      <c r="H31" s="6" t="n">
+        <v>3231323652.541693</v>
+      </c>
+      <c r="I31" s="7" t="n">
+        <v>0.0375</v>
+      </c>
+      <c r="J31" s="7" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="K31" t="n">
+        <v>4</v>
+      </c>
+      <c r="L31" s="7" t="n">
+        <v>0.0433</v>
+      </c>
+      <c r="M31" s="7" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="N31" s="3" t="n">
+        <v>352450.2367573421</v>
+      </c>
+      <c r="O31" s="3" t="n">
+        <v>438371.433118156</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B32" s="6" t="n">
+        <v>3894612666.177943</v>
+      </c>
+      <c r="C32" s="6" t="n">
+        <v>334970000</v>
+      </c>
+      <c r="D32" s="6" t="n">
+        <v>110810390.8233007</v>
+      </c>
+      <c r="E32" s="6" t="n">
+        <v>91260440.13070874</v>
+      </c>
+      <c r="F32" s="6" t="n">
+        <v>74954030.44580247</v>
+      </c>
+      <c r="G32" s="6" t="n">
+        <v>206116586.0471416</v>
+      </c>
+      <c r="H32" s="6" t="n">
+        <v>3076501218.730989</v>
+      </c>
+      <c r="I32" s="7" t="n">
+        <v>0.0375</v>
+      </c>
+      <c r="J32" s="7" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="K32" t="n">
+        <v>4</v>
+      </c>
+      <c r="L32" s="7" t="n">
+        <v>0.0433</v>
+      </c>
+      <c r="M32" s="7" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="N32" s="3" t="n">
+        <v>335563.2859843952</v>
+      </c>
+      <c r="O32" s="3" t="n">
+        <v>424797.1741217737</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="B33" s="6" t="n">
+        <v>3904793970.371299</v>
+      </c>
+      <c r="C33" s="6" t="n">
+        <v>334970000</v>
+      </c>
+      <c r="D33" s="6" t="n">
+        <v>110784766.9258687</v>
+      </c>
+      <c r="E33" s="6" t="n">
+        <v>90992031.3551863</v>
+      </c>
+      <c r="F33" s="6" t="n">
+        <v>75076806.84493634</v>
+      </c>
+      <c r="G33" s="6" t="n">
+        <v>248420857.3449725</v>
+      </c>
+      <c r="H33" s="6" t="n">
+        <v>3044549507.900335</v>
+      </c>
+      <c r="I33" s="7" t="n">
+        <v>0.0375</v>
+      </c>
+      <c r="J33" s="7" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="K33" t="n">
+        <v>4</v>
+      </c>
+      <c r="L33" s="7" t="n">
+        <v>0.0433</v>
+      </c>
+      <c r="M33" s="7" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="N33" s="3" t="n">
+        <v>332078.2163169826</v>
+      </c>
+      <c r="O33" s="3" t="n">
+        <v>425907.6797409258</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="B34" s="6" t="n">
+        <v>3980438326.717189</v>
+      </c>
+      <c r="C34" s="6" t="n">
+        <v>334970000</v>
+      </c>
+      <c r="D34" s="6" t="n">
+        <v>110800643.1083902</v>
+      </c>
+      <c r="E34" s="6" t="n">
+        <v>89742687.66481608</v>
+      </c>
+      <c r="F34" s="6" t="n">
+        <v>75116667.49366367</v>
+      </c>
+      <c r="G34" s="6" t="n">
+        <v>303291142.7334828</v>
+      </c>
+      <c r="H34" s="6" t="n">
+        <v>3066517185.716836</v>
+      </c>
+      <c r="I34" s="7" t="n">
+        <v>0.0375</v>
+      </c>
+      <c r="J34" s="7" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="K34" t="n">
+        <v>4</v>
+      </c>
+      <c r="L34" s="7" t="n">
+        <v>0.0433</v>
+      </c>
+      <c r="M34" s="7" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="N34" s="3" t="n">
+        <v>334474.2973289681</v>
+      </c>
+      <c r="O34" s="3" t="n">
+        <v>434158.4383062261</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+      <c r="B35" s="6" t="n">
+        <v>3949996189.520216</v>
+      </c>
+      <c r="C35" s="6" t="n">
+        <v>334970000</v>
+      </c>
+      <c r="D35" s="6" t="n">
+        <v>110800910.0818387</v>
+      </c>
+      <c r="E35" s="6" t="n">
+        <v>89921451.17719229</v>
+      </c>
+      <c r="F35" s="6" t="n">
+        <v>72969997.84221481</v>
+      </c>
+      <c r="G35" s="6" t="n">
+        <v>295800536.4468129</v>
+      </c>
+      <c r="H35" s="6" t="n">
+        <v>3045533293.972157</v>
+      </c>
+      <c r="I35" s="7" t="n">
+        <v>0.0375</v>
+      </c>
+      <c r="J35" s="7" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="K35" t="n">
+        <v>4</v>
+      </c>
+      <c r="L35" s="7" t="n">
+        <v>0.0433</v>
+      </c>
+      <c r="M35" s="7" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="N35" s="3" t="n">
+        <v>332185.5208371161</v>
+      </c>
+      <c r="O35" s="3" t="n">
+        <v>430838.0223973978</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="B36" s="6" t="n">
+        <v>3938439863.321327</v>
+      </c>
+      <c r="C36" s="6" t="n">
+        <v>334970000</v>
+      </c>
+      <c r="D36" s="6" t="n">
+        <v>110840456.802935</v>
+      </c>
+      <c r="E36" s="6" t="n">
+        <v>90106496.23897925</v>
+      </c>
+      <c r="F36" s="6" t="n">
+        <v>73041937.31867403</v>
+      </c>
+      <c r="G36" s="6" t="n">
+        <v>289518568.352541</v>
+      </c>
+      <c r="H36" s="6" t="n">
+        <v>3039962404.608198</v>
+      </c>
+      <c r="I36" s="7" t="n">
+        <v>0.0375</v>
+      </c>
+      <c r="J36" s="7" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="K36" t="n">
+        <v>4</v>
+      </c>
+      <c r="L36" s="7" t="n">
+        <v>0.0433</v>
+      </c>
+      <c r="M36" s="7" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="N36" s="3" t="n">
+        <v>331577.8870973847</v>
+      </c>
+      <c r="O36" s="3" t="n">
+        <v>429577.5389723965</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="8" t="inlineStr">
+        <is>
+          <t>Σ daily charges</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr"/>
+      <c r="C38" t="inlineStr"/>
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="inlineStr"/>
+      <c r="F38" t="inlineStr"/>
+      <c r="G38" t="inlineStr"/>
+      <c r="H38" t="inlineStr"/>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr"/>
+      <c r="N38" s="10" t="n">
+        <v>10742059.80203898</v>
+      </c>
+      <c r="O38" s="10" t="n">
+        <v>13377121.85957116</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/settlements/spark/2026-05/spark_settlement_may_2026.xlsx
+++ b/settlements/spark/2026-05/spark_settlement_may_2026.xlsx
@@ -525,7 +525,7 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>3284300.977760902</v>
+        <v>10234615.9342856</v>
       </c>
     </row>
     <row r="10">
@@ -541,7 +541,7 @@
     <row r="11">
       <c r="A11" t="inlineStr"/>
       <c r="B11" s="4" t="n">
-        <v>3358457.038605412</v>
+        <v>10308771.99513011</v>
       </c>
     </row>
     <row r="13">
@@ -563,7 +563,7 @@
         </is>
       </c>
       <c r="B14" s="3" t="n">
-        <v>3284300.977760902</v>
+        <v>10234615.9342856</v>
       </c>
     </row>
     <row r="15">
@@ -573,7 +573,7 @@
         </is>
       </c>
       <c r="B15" s="3" t="n">
-        <v>-10092820.88181026</v>
+        <v>-3142505.92528556</v>
       </c>
     </row>
     <row r="16">
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="B22" s="3" t="n">
-        <v>-3284300.977760902</v>
+        <v>-10234615.9342856</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr"/>
       <c r="B23" s="4" t="n">
-        <v>5001812.496304598</v>
+        <v>-1948502.4602201</v>
       </c>
     </row>
     <row r="25">
@@ -662,7 +662,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-06-08T12:39:12+00:00</t>
+          <t>2026-06-08T14:52:11+00:00</t>
         </is>
       </c>
     </row>
@@ -859,13 +859,13 @@
         <v>1</v>
       </c>
       <c r="N2" s="6" t="n">
-        <v>1014763.564397916</v>
+        <v>4167822.764039975</v>
       </c>
       <c r="O2" s="6" t="n">
-        <v>1014763.564397916</v>
+        <v>4167822.764039975</v>
       </c>
       <c r="P2" s="6" t="n">
-        <v>-1014763.564397916</v>
+        <v>-4167822.764039975</v>
       </c>
       <c r="Q2" s="6" t="n">
         <v>0</v>
@@ -878,12 +878,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>S57</t>
+          <t>S3</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Spark Savings V2 — spUSDT vault</t>
+          <t>Spark USDT (SparkLend spToken)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -893,44 +893,44 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E3" s="6" t="n">
-        <v>1134703231.016836</v>
+        <v>677669071.17383</v>
       </c>
       <c r="F3" s="6" t="n">
-        <v>1270360913.25412</v>
+        <v>495837665.420656</v>
       </c>
       <c r="G3" s="6" t="n">
-        <v>135657682.237284</v>
+        <v>-181831405.753174</v>
       </c>
       <c r="H3" s="6" t="n">
-        <v>-2595205.75030597</v>
+        <v>1868112.168236</v>
       </c>
       <c r="I3" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J3" s="6" t="n">
-        <v>-2595205.75030597</v>
+        <v>1868112.168236</v>
       </c>
       <c r="K3" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L3" s="6" t="n">
-        <v>1134703231.016836</v>
+        <v>671743280.2731394</v>
       </c>
       <c r="M3" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N3" s="6" t="n">
-        <v>605812.8439774774</v>
+        <v>1473003.887406189</v>
       </c>
       <c r="O3" s="6" t="n">
-        <v>605812.8439774774</v>
+        <v>1473003.887406189</v>
       </c>
       <c r="P3" s="6" t="n">
-        <v>-3201018.594283448</v>
+        <v>395108.2808298113</v>
       </c>
       <c r="Q3" s="6" t="n">
         <v>0</v>
@@ -943,12 +943,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>S3</t>
+          <t>S28</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Spark USDT (SparkLend spToken)</t>
+          <t>PYUSD raw (ALM idle — $677M as of 2026-04)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -958,44 +958,44 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E4" s="6" t="n">
-        <v>677669071.17383</v>
+        <v>677151123.07819</v>
       </c>
       <c r="F4" s="6" t="n">
-        <v>495837665.420656</v>
+        <v>262428227.923162</v>
       </c>
       <c r="G4" s="6" t="n">
-        <v>-181831405.753174</v>
+        <v>-414722895.155028</v>
       </c>
       <c r="H4" s="6" t="n">
-        <v>1868112.168236</v>
+        <v>3091580</v>
       </c>
       <c r="I4" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J4" s="6" t="n">
-        <v>1868112.168236</v>
+        <v>3091580</v>
       </c>
       <c r="K4" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L4" s="6" t="n">
-        <v>671743280.2731394</v>
+        <v>615465268.6039779</v>
       </c>
       <c r="M4" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N4" s="6" t="n">
-        <v>358640.6523936233</v>
+        <v>1349597.02588841</v>
       </c>
       <c r="O4" s="6" t="n">
-        <v>358640.6523936233</v>
+        <v>1349597.02588841</v>
       </c>
       <c r="P4" s="6" t="n">
-        <v>1509471.515842377</v>
+        <v>1741982.97411159</v>
       </c>
       <c r="Q4" s="6" t="n">
         <v>0</v>
@@ -1008,12 +1008,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>S28</t>
+          <t>S27</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>PYUSD raw (ALM idle — $677M as of 2026-04)</t>
+          <t>USDT raw (ALM idle — $442M as of 2026-04)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1027,40 +1027,40 @@
         </is>
       </c>
       <c r="E5" s="6" t="n">
-        <v>677151123.07819</v>
+        <v>483436565.922284</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>262428227.923162</v>
+        <v>608678684.51526</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>-414722895.155028</v>
+        <v>125242118.592976</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>3091580</v>
+        <v>-194444.4444439532</v>
       </c>
       <c r="I5" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>3091580</v>
+        <v>-194444.4444439532</v>
       </c>
       <c r="K5" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L5" s="6" t="n">
-        <v>615465268.6039779</v>
+        <v>539754938.8825277</v>
       </c>
       <c r="M5" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>328594.0804171427</v>
+        <v>1183578.826270314</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>328594.0804171427</v>
+        <v>1183578.826270314</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>2762985.919582857</v>
+        <v>-1378023.270714268</v>
       </c>
       <c r="Q5" s="6" t="n">
         <v>0</v>
@@ -1073,12 +1073,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>S56</t>
+          <t>S4</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Spark Savings V2 — spUSDC vault</t>
+          <t>Spark DAI (SparkLend spToken)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1088,188 +1088,196 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E6" s="6" t="n">
-        <v>573332157.534611</v>
+        <v>266184835.4745756</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>303545287.192935</v>
+        <v>266960907.7112744</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>-269786870.341676</v>
+        <v>776072.2366988341</v>
       </c>
       <c r="H6" s="6" t="n">
-        <v>-2077933.247665395</v>
+        <v>559452.9392412193</v>
       </c>
       <c r="I6" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J6" s="6" t="n">
-        <v>-2077933.247665395</v>
+        <v>559452.9392412193</v>
       </c>
       <c r="K6" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L6" s="6" t="n">
-        <v>573332157.534611</v>
+        <v>179549416.5672932</v>
       </c>
       <c r="M6" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N6" s="6" t="n">
-        <v>306099.4059112116</v>
+        <v>393717.3565437027</v>
       </c>
       <c r="O6" s="6" t="n">
-        <v>306099.4059112116</v>
+        <v>393717.3565437027</v>
       </c>
       <c r="P6" s="6" t="n">
-        <v>-2384032.653576606</v>
+        <v>165735.5826975166</v>
       </c>
       <c r="Q6" s="6" t="n">
-        <v>0</v>
+        <v>86642406.62655522</v>
       </c>
       <c r="R6" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="S6" t="inlineStr"/>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>(avg excl. lending_idle)</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>S27</t>
+          <t>S43</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>USDT raw (ALM idle — $442M as of 2026-04)</t>
+          <t>Savings USDS / sUSDS proxy (Arbitrum — POL)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>ethereum</t>
+          <t>arbitrum</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E7" s="6" t="n">
-        <v>483436565.922284</v>
+        <v>143328568.5311704</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>608678684.51526</v>
+        <v>143764611.5800855</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>125242118.592976</v>
+        <v>436043.0489150246</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>-194444.4444439532</v>
+        <v>0</v>
       </c>
       <c r="I7" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J7" s="6" t="n">
-        <v>-194444.4444439532</v>
+        <v>0</v>
       </c>
       <c r="K7" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L7" s="6" t="n">
-        <v>539754938.8825277</v>
+        <v>143328568.5311704</v>
       </c>
       <c r="M7" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N7" s="6" t="n">
-        <v>288172.6830744011</v>
+        <v>314291.9993735298</v>
       </c>
       <c r="O7" s="6" t="n">
-        <v>288172.6830744011</v>
+        <v>277827.1855317322</v>
       </c>
       <c r="P7" s="6" t="n">
-        <v>-482617.1275183543</v>
+        <v>-314291.9993735298</v>
       </c>
       <c r="Q7" s="6" t="n">
         <v>0</v>
       </c>
       <c r="R7" s="6" t="n">
-        <v>0</v>
+        <v>36464.81384179761</v>
       </c>
       <c r="S7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SPREAD</t>
+          <t>S14</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>30bps sUSDS spread (Curve LP + PSM3) — Sky Revenue reduction</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
+          <t>Maple syrupUSDC (ERC-4626)</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>ethereum</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
       <c r="E8" s="6" t="n">
-        <v>0</v>
+        <v>105306162.1077363</v>
       </c>
       <c r="F8" s="6" t="n">
-        <v>0</v>
+        <v>105300451.2530954</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>0</v>
+        <v>-5710.854640941099</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>0</v>
+        <v>423530.6085832017</v>
       </c>
       <c r="I8" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J8" s="6" t="n">
-        <v>0</v>
+        <v>423530.6085832017</v>
       </c>
       <c r="K8" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L8" s="6" t="n">
-        <v>0</v>
+        <v>105079212.3991508</v>
       </c>
       <c r="M8" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N8" s="6" t="n">
-        <v>0</v>
+        <v>230418.5138801736</v>
       </c>
       <c r="O8" s="6" t="n">
-        <v>-102957.2966175266</v>
+        <v>230418.5138801736</v>
       </c>
       <c r="P8" s="6" t="n">
-        <v>0</v>
+        <v>193112.0947030281</v>
       </c>
       <c r="Q8" s="6" t="n">
         <v>0</v>
       </c>
       <c r="R8" s="6" t="n">
-        <v>102957.2966175266</v>
-      </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>sky-revenue reduction (no CoF; computed outside venue loop)</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="S8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>S4</t>
+          <t>S5</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Spark DAI (SparkLend spToken)</t>
+          <t>Spark PYUSD (SparkLend spToken)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1283,62 +1291,58 @@
         </is>
       </c>
       <c r="E9" s="6" t="n">
-        <v>266184835.4745756</v>
+        <v>100001095.915921</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>266960907.7112744</v>
+        <v>100000628.579333</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>776072.2366988341</v>
+        <v>-467.336588</v>
       </c>
       <c r="H9" s="6" t="n">
-        <v>559452.9392412193</v>
+        <v>29003.9707</v>
       </c>
       <c r="I9" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J9" s="6" t="n">
-        <v>559452.9392412193</v>
+        <v>29003.9707</v>
       </c>
       <c r="K9" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L9" s="6" t="n">
-        <v>179549416.5672932</v>
+        <v>100000145.2285891</v>
       </c>
       <c r="M9" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N9" s="6" t="n">
-        <v>95860.60893442083</v>
+        <v>219281.0959016976</v>
       </c>
       <c r="O9" s="6" t="n">
-        <v>95860.60893442083</v>
+        <v>219281.0959016976</v>
       </c>
       <c r="P9" s="6" t="n">
-        <v>463592.3303067985</v>
+        <v>-190277.1252016976</v>
       </c>
       <c r="Q9" s="6" t="n">
-        <v>86642406.62655522</v>
+        <v>0</v>
       </c>
       <c r="R9" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>(avg excl. lending_idle)</t>
-        </is>
-      </c>
+      <c r="S9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>S24</t>
+          <t>S25</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Spark.fi USDT Reserve Curve (sUSDS/USDT)</t>
+          <t>Spark.fi PYUSD Reserve Curve (PYUSD/USDS)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1352,67 +1356,63 @@
         </is>
       </c>
       <c r="E10" s="6" t="n">
-        <v>50002415.26289953</v>
+        <v>99998676.75316638</v>
       </c>
       <c r="F10" s="6" t="n">
-        <v>48750265.64989898</v>
+        <v>99999260.90933624</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>-1252149.613000547</v>
+        <v>584.1561698611263</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>74156.06084450937</v>
+        <v>6385.883871640342</v>
       </c>
       <c r="I10" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J10" s="6" t="n">
-        <v>0</v>
+        <v>6385.883871640342</v>
       </c>
       <c r="K10" s="6" t="n">
-        <v>74156.06084450937</v>
+        <v>0</v>
       </c>
       <c r="L10" s="6" t="n">
-        <v>49959631.20890453</v>
+        <v>99998489.60065988</v>
       </c>
       <c r="M10" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N10" s="6" t="n">
-        <v>0</v>
+        <v>219277.4654279028</v>
       </c>
       <c r="O10" s="6" t="n">
-        <v>74156.06084450937</v>
+        <v>219277.4654279028</v>
       </c>
       <c r="P10" s="6" t="n">
-        <v>0</v>
+        <v>-212891.5815562624</v>
       </c>
       <c r="Q10" s="6" t="n">
-        <v>49959631.20890453</v>
+        <v>0</v>
       </c>
       <c r="R10" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>SDE (fixed)</t>
-        </is>
-      </c>
+      <c r="S10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>S14</t>
+          <t>S47</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Maple syrupUSDC (ERC-4626)</t>
+          <t>Savings USDS / sUSDS proxy (Optimism — POL)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>ethereum</t>
+          <t>optimism</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1421,58 +1421,58 @@
         </is>
       </c>
       <c r="E11" s="6" t="n">
-        <v>105306162.1077363</v>
+        <v>102040993.0313656</v>
       </c>
       <c r="F11" s="6" t="n">
-        <v>105300451.2530954</v>
+        <v>102351428.4607548</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>-5710.854640941099</v>
+        <v>310435.429389201</v>
       </c>
       <c r="H11" s="6" t="n">
-        <v>423530.6085832017</v>
+        <v>0</v>
       </c>
       <c r="I11" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J11" s="6" t="n">
-        <v>423530.6085832017</v>
+        <v>0</v>
       </c>
       <c r="K11" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L11" s="6" t="n">
-        <v>105079212.3991508</v>
+        <v>102040993.0313656</v>
       </c>
       <c r="M11" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N11" s="6" t="n">
-        <v>56101.30892938157</v>
+        <v>223756.2828300607</v>
       </c>
       <c r="O11" s="6" t="n">
-        <v>56101.30892938157</v>
+        <v>197795.6118120444</v>
       </c>
       <c r="P11" s="6" t="n">
-        <v>367429.2996538201</v>
+        <v>-223756.2828300607</v>
       </c>
       <c r="Q11" s="6" t="n">
         <v>0</v>
       </c>
       <c r="R11" s="6" t="n">
-        <v>0</v>
+        <v>25960.67101801626</v>
       </c>
       <c r="S11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>S5</t>
+          <t>S11</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Spark PYUSD (SparkLend spToken)</t>
+          <t>Spark Blue Chip USDT Vault (Morpho V2)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1482,44 +1482,44 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E12" s="6" t="n">
-        <v>100001095.915921</v>
+        <v>51710579.95350124</v>
       </c>
       <c r="F12" s="6" t="n">
-        <v>100000628.579333</v>
+        <v>71943502.10038626</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>-467.336588</v>
+        <v>20232922.14688502</v>
       </c>
       <c r="H12" s="6" t="n">
-        <v>29003.9707</v>
+        <v>217269.3964465584</v>
       </c>
       <c r="I12" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J12" s="6" t="n">
-        <v>29003.9707</v>
+        <v>217269.3964465584</v>
       </c>
       <c r="K12" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L12" s="6" t="n">
-        <v>100000145.2285891</v>
+        <v>89619946.74579927</v>
       </c>
       <c r="M12" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N12" s="6" t="n">
-        <v>53389.61829235638</v>
+        <v>196519.3159684765</v>
       </c>
       <c r="O12" s="6" t="n">
-        <v>53389.61829235638</v>
+        <v>196519.3159684765</v>
       </c>
       <c r="P12" s="6" t="n">
-        <v>-24385.64759235637</v>
+        <v>20750.08047808185</v>
       </c>
       <c r="Q12" s="6" t="n">
         <v>0</v>
@@ -1532,77 +1532,77 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>S25</t>
+          <t>S37</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Spark.fi PYUSD Reserve Curve (PYUSD/USDS)</t>
+          <t>Savings USDS / sUSDS proxy (Base — POL)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>ethereum</t>
+          <t>base</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E13" s="6" t="n">
-        <v>99998676.75316638</v>
+        <v>75772907.26348835</v>
       </c>
       <c r="F13" s="6" t="n">
-        <v>99999260.90933624</v>
+        <v>76003428.29531698</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>584.1561698611263</v>
+        <v>230521.0318286367</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>6385.883871640342</v>
+        <v>0</v>
       </c>
       <c r="I13" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J13" s="6" t="n">
-        <v>6385.883871640342</v>
+        <v>0</v>
       </c>
       <c r="K13" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L13" s="6" t="n">
-        <v>99998489.60065988</v>
+        <v>75772907.26348835</v>
       </c>
       <c r="M13" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N13" s="6" t="n">
-        <v>53388.73436020832</v>
+        <v>166155.4201387819</v>
       </c>
       <c r="O13" s="6" t="n">
-        <v>53388.73436020832</v>
+        <v>146877.7214501635</v>
       </c>
       <c r="P13" s="6" t="n">
-        <v>-47002.85048856798</v>
+        <v>-166155.4201387819</v>
       </c>
       <c r="Q13" s="6" t="n">
         <v>0</v>
       </c>
       <c r="R13" s="6" t="n">
-        <v>0</v>
+        <v>19277.6986886184</v>
       </c>
       <c r="S13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>S11</t>
+          <t>S1</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Spark Blue Chip USDT Vault (Morpho V2)</t>
+          <t>Spark USDS (SparkLend spToken)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1612,82 +1612,78 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E14" s="6" t="n">
-        <v>51710579.95350124</v>
+        <v>147862782.1336161</v>
       </c>
       <c r="F14" s="6" t="n">
-        <v>71943502.10038626</v>
+        <v>550178045.362034</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>20232922.14688502</v>
+        <v>402315263.2284179</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>217269.3964465584</v>
+        <v>294091.516876444</v>
       </c>
       <c r="I14" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J14" s="6" t="n">
-        <v>217269.3964465584</v>
+        <v>294091.516876444</v>
       </c>
       <c r="K14" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L14" s="6" t="n">
-        <v>89619946.74579927</v>
+        <v>57731388.11709616</v>
       </c>
       <c r="M14" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N14" s="6" t="n">
-        <v>47847.67799288761</v>
+        <v>126593.836691988</v>
       </c>
       <c r="O14" s="6" t="n">
-        <v>47847.67799288761</v>
+        <v>126593.836691988</v>
       </c>
       <c r="P14" s="6" t="n">
-        <v>169421.7184536707</v>
+        <v>167497.6801844561</v>
       </c>
       <c r="Q14" s="6" t="n">
-        <v>0</v>
+        <v>103099818.9104406</v>
       </c>
       <c r="R14" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="S14" t="inlineStr"/>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>(avg excl. lending_idle)</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>S43</t>
+          <t>SPREAD</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Savings USDS / sUSDS proxy (Arbitrum — POL)</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>arbitrum</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
+          <t>30bps sUSDS spread (Curve LP + PSM3) — Sky Revenue reduction</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr"/>
       <c r="E15" s="6" t="n">
-        <v>143328568.5311704</v>
+        <v>0</v>
       </c>
       <c r="F15" s="6" t="n">
-        <v>143764611.5800855</v>
+        <v>0</v>
       </c>
       <c r="G15" s="6" t="n">
-        <v>436043.0489150246</v>
+        <v>0</v>
       </c>
       <c r="H15" s="6" t="n">
         <v>0</v>
@@ -1702,37 +1698,41 @@
         <v>0</v>
       </c>
       <c r="L15" s="6" t="n">
-        <v>143328568.5311704</v>
+        <v>0</v>
       </c>
       <c r="M15" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N15" s="6" t="n">
-        <v>76522.46451019474</v>
+        <v>0</v>
       </c>
       <c r="O15" s="6" t="n">
-        <v>40057.65066839712</v>
+        <v>-102957.2966175266</v>
       </c>
       <c r="P15" s="6" t="n">
-        <v>-76522.46451019474</v>
+        <v>0</v>
       </c>
       <c r="Q15" s="6" t="n">
         <v>0</v>
       </c>
       <c r="R15" s="6" t="n">
-        <v>36464.81384179761</v>
-      </c>
-      <c r="S15" t="inlineStr"/>
+        <v>102957.2966175266</v>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>sky-revenue reduction (no CoF; computed outside venue loop)</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>S1</t>
+          <t>S24</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Spark USDS (SparkLend spToken)</t>
+          <t>Spark.fi USDT Reserve Curve (sUSDS/USDT)</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1742,71 +1742,71 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>F</t>
         </is>
       </c>
       <c r="E16" s="6" t="n">
-        <v>147862782.1336161</v>
+        <v>50002415.26289953</v>
       </c>
       <c r="F16" s="6" t="n">
-        <v>550178045.362034</v>
+        <v>48750265.64989898</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>402315263.2284179</v>
+        <v>-1252149.613000547</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>294091.516876444</v>
+        <v>74156.06084450937</v>
       </c>
       <c r="I16" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J16" s="6" t="n">
-        <v>294091.516876444</v>
+        <v>0</v>
       </c>
       <c r="K16" s="6" t="n">
-        <v>0</v>
+        <v>74156.06084450937</v>
       </c>
       <c r="L16" s="6" t="n">
-        <v>57731388.11709616</v>
+        <v>49959631.20890453</v>
       </c>
       <c r="M16" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N16" s="6" t="n">
-        <v>30822.52298748116</v>
+        <v>0</v>
       </c>
       <c r="O16" s="6" t="n">
-        <v>30822.52298748116</v>
+        <v>74156.06084450937</v>
       </c>
       <c r="P16" s="6" t="n">
-        <v>263268.9938889629</v>
+        <v>0</v>
       </c>
       <c r="Q16" s="6" t="n">
-        <v>103099818.9104406</v>
+        <v>49959631.20890453</v>
       </c>
       <c r="R16" s="6" t="n">
         <v>0</v>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>(avg excl. lending_idle)</t>
+          <t>SDE (fixed)</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>S47</t>
+          <t>S15</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Savings USDS / sUSDS proxy (Optimism — POL)</t>
+          <t>Maple syrupUSDT (ERC-4626)</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>optimism</t>
+          <t>ethereum</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1815,63 +1815,63 @@
         </is>
       </c>
       <c r="E17" s="6" t="n">
-        <v>102040993.0313656</v>
+        <v>76904851.98939763</v>
       </c>
       <c r="F17" s="6" t="n">
-        <v>102351428.4607548</v>
+        <v>0</v>
       </c>
       <c r="G17" s="6" t="n">
-        <v>310435.429389201</v>
+        <v>-76904851.98939763</v>
       </c>
       <c r="H17" s="6" t="n">
-        <v>0</v>
+        <v>119641.6179259726</v>
       </c>
       <c r="I17" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J17" s="6" t="n">
-        <v>0</v>
+        <v>119641.6179259726</v>
       </c>
       <c r="K17" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L17" s="6" t="n">
-        <v>102040993.0313656</v>
+        <v>29672997.14110577</v>
       </c>
       <c r="M17" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N17" s="6" t="n">
-        <v>54479.21756177701</v>
+        <v>65067.17882175036</v>
       </c>
       <c r="O17" s="6" t="n">
-        <v>28518.54654376076</v>
+        <v>65067.17882175036</v>
       </c>
       <c r="P17" s="6" t="n">
-        <v>-54479.21756177701</v>
+        <v>54574.43910422226</v>
       </c>
       <c r="Q17" s="6" t="n">
         <v>0</v>
       </c>
       <c r="R17" s="6" t="n">
-        <v>25960.67101801626</v>
+        <v>0</v>
       </c>
       <c r="S17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>S37</t>
+          <t>S18</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Savings USDS / sUSDS proxy (Base — POL)</t>
+          <t>Arkis Spark Prime USDC 1 (ERC-4626)</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>base</t>
+          <t>ethereum</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1880,105 +1880,105 @@
         </is>
       </c>
       <c r="E18" s="6" t="n">
-        <v>75772907.26348835</v>
+        <v>0.28330096818</v>
       </c>
       <c r="F18" s="6" t="n">
-        <v>76003428.29531698</v>
+        <v>15021342.65332295</v>
       </c>
       <c r="G18" s="6" t="n">
-        <v>230521.0318286367</v>
+        <v>15021342.37002198</v>
       </c>
       <c r="H18" s="6" t="n">
-        <v>0</v>
+        <v>21701.47150269761</v>
       </c>
       <c r="I18" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J18" s="6" t="n">
-        <v>0</v>
+        <v>21701.47150269761</v>
       </c>
       <c r="K18" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L18" s="6" t="n">
-        <v>75772907.26348835</v>
+        <v>9516094.162770383</v>
       </c>
       <c r="M18" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N18" s="6" t="n">
-        <v>40454.80720505187</v>
+        <v>20866.96526236113</v>
       </c>
       <c r="O18" s="6" t="n">
-        <v>21177.10851643347</v>
+        <v>20866.96526236113</v>
       </c>
       <c r="P18" s="6" t="n">
-        <v>-40454.80720505187</v>
+        <v>834.506240336483</v>
       </c>
       <c r="Q18" s="6" t="n">
         <v>0</v>
       </c>
       <c r="R18" s="6" t="n">
-        <v>19277.6986886184</v>
+        <v>0</v>
       </c>
       <c r="S18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>S60</t>
+          <t>S2</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Spark Savings V2 — spUSDC vault (Avalanche-C, CREATE2 same address)</t>
+          <t>Spark USDC (SparkLend spToken)</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>avalanche_c</t>
+          <t>ethereum</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E19" s="6" t="n">
-        <v>37138817.432463</v>
+        <v>9229822.108306</v>
       </c>
       <c r="F19" s="6" t="n">
-        <v>25647247.422478</v>
+        <v>12183497.214187</v>
       </c>
       <c r="G19" s="6" t="n">
-        <v>-11491570.009985</v>
+        <v>2953675.105881</v>
       </c>
       <c r="H19" s="6" t="n">
-        <v>-94676.37115954701</v>
+        <v>32502.903353</v>
       </c>
       <c r="I19" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J19" s="6" t="n">
-        <v>-94676.37115954701</v>
+        <v>32502.903353</v>
       </c>
       <c r="K19" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L19" s="6" t="n">
-        <v>37138817.432463</v>
+        <v>9324053.469677871</v>
       </c>
       <c r="M19" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N19" s="6" t="n">
-        <v>19828.24406920799</v>
+        <v>20445.85693754033</v>
       </c>
       <c r="O19" s="6" t="n">
-        <v>19828.24406920799</v>
+        <v>20445.85693754033</v>
       </c>
       <c r="P19" s="6" t="n">
-        <v>-114504.615228755</v>
+        <v>12057.04641545967</v>
       </c>
       <c r="Q19" s="6" t="n">
         <v>0</v>
@@ -1991,59 +1991,59 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>S15</t>
+          <t>S39</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Maple syrupUSDT (ERC-4626)</t>
+          <t>USDC raw (Base — ALM idle)</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>ethereum</t>
+          <t>base</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E20" s="6" t="n">
-        <v>76904851.98939763</v>
+        <v>5000000</v>
       </c>
       <c r="F20" s="6" t="n">
-        <v>0</v>
+        <v>4997576.708614</v>
       </c>
       <c r="G20" s="6" t="n">
-        <v>-76904851.98939763</v>
+        <v>-2423.291386</v>
       </c>
       <c r="H20" s="6" t="n">
-        <v>119641.6179259726</v>
+        <v>2.228968e-09</v>
       </c>
       <c r="I20" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J20" s="6" t="n">
-        <v>119641.6179259726</v>
+        <v>2.228968e-09</v>
       </c>
       <c r="K20" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L20" s="6" t="n">
-        <v>29672997.14110577</v>
+        <v>4999001.686505451</v>
       </c>
       <c r="M20" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N20" s="6" t="n">
-        <v>15842.27690202296</v>
+        <v>10961.84976257375</v>
       </c>
       <c r="O20" s="6" t="n">
-        <v>15842.27690202296</v>
+        <v>10961.84976257375</v>
       </c>
       <c r="P20" s="6" t="n">
-        <v>103799.3410239497</v>
+        <v>-10961.84976257152</v>
       </c>
       <c r="Q20" s="6" t="n">
         <v>0</v>
@@ -2056,59 +2056,59 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>S18</t>
+          <t>S49</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Arkis Spark Prime USDC 1 (ERC-4626)</t>
+          <t>USDC raw (Optimism — ALM idle)</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>ethereum</t>
+          <t>optimism</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E21" s="6" t="n">
-        <v>0.28330096818</v>
+        <v>5000000</v>
       </c>
       <c r="F21" s="6" t="n">
-        <v>15021342.65332295</v>
+        <v>5019997.4</v>
       </c>
       <c r="G21" s="6" t="n">
-        <v>15021342.37002198</v>
+        <v>19997.4</v>
       </c>
       <c r="H21" s="6" t="n">
-        <v>21701.47150269761</v>
+        <v>1.8405064066e-10</v>
       </c>
       <c r="I21" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J21" s="6" t="n">
-        <v>21701.47150269761</v>
+        <v>1.8405064066e-10</v>
       </c>
       <c r="K21" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L21" s="6" t="n">
-        <v>9516094.162770383</v>
+        <v>4998671.605324483</v>
       </c>
       <c r="M21" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N21" s="6" t="n">
-        <v>5080.598971362107</v>
+        <v>10961.12595799393</v>
       </c>
       <c r="O21" s="6" t="n">
-        <v>5080.598971362107</v>
+        <v>10961.12595799393</v>
       </c>
       <c r="P21" s="6" t="n">
-        <v>16620.8725313355</v>
+        <v>-10961.12595799374</v>
       </c>
       <c r="Q21" s="6" t="n">
         <v>0</v>
@@ -2121,59 +2121,59 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>S53</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Spark USDC (SparkLend spToken)</t>
+          <t>USDC raw (Unichain — ALM idle)</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>ethereum</t>
+          <t>unichain</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E22" s="6" t="n">
-        <v>9229822.108306</v>
+        <v>4996314.282982</v>
       </c>
       <c r="F22" s="6" t="n">
-        <v>12183497.214187</v>
+        <v>4992819.462732</v>
       </c>
       <c r="G22" s="6" t="n">
-        <v>2953675.105881</v>
+        <v>-3494.82025</v>
       </c>
       <c r="H22" s="6" t="n">
-        <v>32502.903353</v>
+        <v>0</v>
       </c>
       <c r="I22" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J22" s="6" t="n">
-        <v>32502.903353</v>
+        <v>0</v>
       </c>
       <c r="K22" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L22" s="6" t="n">
-        <v>9324053.469677871</v>
+        <v>4997744.737919419</v>
       </c>
       <c r="M22" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N22" s="6" t="n">
-        <v>4978.069327256376</v>
+        <v>10959.09351594223</v>
       </c>
       <c r="O22" s="6" t="n">
-        <v>4978.069327256376</v>
+        <v>10959.09351594223</v>
       </c>
       <c r="P22" s="6" t="n">
-        <v>27524.83402574362</v>
+        <v>-10959.09351594223</v>
       </c>
       <c r="Q22" s="6" t="n">
         <v>0</v>
@@ -2186,17 +2186,17 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>S39</t>
+          <t>S45</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>USDC raw (Base — ALM idle)</t>
+          <t>USDC raw (Arbitrum — ALM idle)</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>base</t>
+          <t>arbitrum</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -2205,40 +2205,40 @@
         </is>
       </c>
       <c r="E23" s="6" t="n">
-        <v>5000000</v>
+        <v>5009602.263622</v>
       </c>
       <c r="F23" s="6" t="n">
-        <v>4997576.708614</v>
+        <v>4975417.167355</v>
       </c>
       <c r="G23" s="6" t="n">
-        <v>-2423.291386</v>
+        <v>-34185.096267</v>
       </c>
       <c r="H23" s="6" t="n">
-        <v>2.228968e-09</v>
+        <v>4.7e-10</v>
       </c>
       <c r="I23" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J23" s="6" t="n">
-        <v>2.228968e-09</v>
+        <v>4.7e-10</v>
       </c>
       <c r="K23" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L23" s="6" t="n">
-        <v>4999001.686505451</v>
+        <v>4954536.773106677</v>
       </c>
       <c r="M23" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N23" s="6" t="n">
-        <v>2668.944042783939</v>
+        <v>10864.34675478342</v>
       </c>
       <c r="O23" s="6" t="n">
-        <v>2668.944042783939</v>
+        <v>10864.34675478342</v>
       </c>
       <c r="P23" s="6" t="n">
-        <v>-2668.944042781711</v>
+        <v>-10864.34675478295</v>
       </c>
       <c r="Q23" s="6" t="n">
         <v>0</v>
@@ -2251,59 +2251,59 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>S49</t>
+          <t>S10</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>USDC raw (Optimism — ALM idle)</t>
+          <t>Spark Blue Chip USDC Vault (Morpho)</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>optimism</t>
+          <t>ethereum</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E24" s="6" t="n">
-        <v>5000000</v>
+        <v>704090.8045421393</v>
       </c>
       <c r="F24" s="6" t="n">
-        <v>5019997.4</v>
+        <v>3501087.141508509</v>
       </c>
       <c r="G24" s="6" t="n">
-        <v>19997.4</v>
+        <v>2796996.33696637</v>
       </c>
       <c r="H24" s="6" t="n">
-        <v>1.8405064066e-10</v>
+        <v>609955.0966986277</v>
       </c>
       <c r="I24" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J24" s="6" t="n">
-        <v>1.8405064066e-10</v>
+        <v>609955.0966986277</v>
       </c>
       <c r="K24" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L24" s="6" t="n">
-        <v>4998671.605324483</v>
+        <v>1472511.375313347</v>
       </c>
       <c r="M24" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N24" s="6" t="n">
-        <v>2668.767813957301</v>
+        <v>3228.934391728406</v>
       </c>
       <c r="O24" s="6" t="n">
-        <v>2668.767813957301</v>
+        <v>3228.934391728406</v>
       </c>
       <c r="P24" s="6" t="n">
-        <v>-2668.767813957117</v>
+        <v>606726.1623068993</v>
       </c>
       <c r="Q24" s="6" t="n">
         <v>0</v>
@@ -2316,12 +2316,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>S53</t>
+          <t>S51</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>USDC raw (Unichain — ALM idle)</t>
+          <t>Savings USDS / sUSDS proxy (Unichain — POL)</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -2331,17 +2331,17 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E25" s="6" t="n">
-        <v>4996314.282982</v>
+        <v>982408.1850699954</v>
       </c>
       <c r="F25" s="6" t="n">
-        <v>4992819.462732</v>
+        <v>985396.9281006901</v>
       </c>
       <c r="G25" s="6" t="n">
-        <v>-3494.82025</v>
+        <v>2988.743030694792</v>
       </c>
       <c r="H25" s="6" t="n">
         <v>0</v>
@@ -2356,84 +2356,84 @@
         <v>0</v>
       </c>
       <c r="L25" s="6" t="n">
-        <v>4997744.737919419</v>
+        <v>982408.1850699954</v>
       </c>
       <c r="M25" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N25" s="6" t="n">
-        <v>2668.272963706325</v>
+        <v>2154.232305888279</v>
       </c>
       <c r="O25" s="6" t="n">
-        <v>2668.272963706325</v>
+        <v>1904.293776868191</v>
       </c>
       <c r="P25" s="6" t="n">
-        <v>-2668.272963706325</v>
+        <v>-2154.232305888279</v>
       </c>
       <c r="Q25" s="6" t="n">
         <v>0</v>
       </c>
       <c r="R25" s="6" t="n">
-        <v>0</v>
+        <v>249.9385290200882</v>
       </c>
       <c r="S25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>S45</t>
+          <t>S12</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>USDC raw (Arbitrum — ALM idle)</t>
+          <t>Spark DAI Vault (Morpho)</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>arbitrum</t>
+          <t>ethereum</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E26" s="6" t="n">
-        <v>5009602.263622</v>
+        <v>458.5728307677575</v>
       </c>
       <c r="F26" s="6" t="n">
-        <v>4975417.167355</v>
+        <v>539.8728953809741</v>
       </c>
       <c r="G26" s="6" t="n">
-        <v>-34185.096267</v>
+        <v>81.30006461321658</v>
       </c>
       <c r="H26" s="6" t="n">
-        <v>4.7e-10</v>
+        <v>76.33046551920575</v>
       </c>
       <c r="I26" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J26" s="6" t="n">
-        <v>4.7e-10</v>
+        <v>76.33046551920575</v>
       </c>
       <c r="K26" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L26" s="6" t="n">
-        <v>4954536.773106677</v>
+        <v>462.161691889013</v>
       </c>
       <c r="M26" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N26" s="6" t="n">
-        <v>2645.204429723013</v>
+        <v>1.013431751019421</v>
       </c>
       <c r="O26" s="6" t="n">
-        <v>2645.204429723013</v>
+        <v>1.013431751019421</v>
       </c>
       <c r="P26" s="6" t="n">
-        <v>-2645.204429722543</v>
+        <v>75.31703376818632</v>
       </c>
       <c r="Q26" s="6" t="n">
         <v>0</v>
@@ -2446,17 +2446,17 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>S10</t>
+          <t>S34</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Spark Blue Chip USDC Vault (Morpho)</t>
+          <t>Spark USDC Vault (Morpho, Base)</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>ethereum</t>
+          <t>base</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -2465,40 +2465,40 @@
         </is>
       </c>
       <c r="E27" s="6" t="n">
-        <v>704090.8045421393</v>
+        <v>224.7175624853434</v>
       </c>
       <c r="F27" s="6" t="n">
-        <v>3501087.141508509</v>
+        <v>424.9110349025811</v>
       </c>
       <c r="G27" s="6" t="n">
-        <v>2796996.33696637</v>
+        <v>200.1934724172377</v>
       </c>
       <c r="H27" s="6" t="n">
-        <v>609955.0966986277</v>
+        <v>1.161345275337778</v>
       </c>
       <c r="I27" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J27" s="6" t="n">
-        <v>609955.0966986277</v>
+        <v>1.161345275337778</v>
       </c>
       <c r="K27" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L27" s="6" t="n">
-        <v>1472511.375313347</v>
+        <v>368.0420981576889</v>
       </c>
       <c r="M27" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N27" s="6" t="n">
-        <v>786.1670608519926</v>
+        <v>0.807045574158881</v>
       </c>
       <c r="O27" s="6" t="n">
-        <v>786.1670608519926</v>
+        <v>0.807045574158881</v>
       </c>
       <c r="P27" s="6" t="n">
-        <v>609168.9296377758</v>
+        <v>0.3542997011788971</v>
       </c>
       <c r="Q27" s="6" t="n">
         <v>0</v>
@@ -2511,59 +2511,59 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>S59</t>
+          <t>S36</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Spark Savings V2 — spPYUSD vault</t>
+          <t>Fluid Savings USDS (fsUSDS, Base)</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>ethereum</t>
+          <t>base</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E28" s="6" t="n">
-        <v>1066559.875133</v>
+        <v>283.8972488542868</v>
       </c>
       <c r="F28" s="6" t="n">
-        <v>773533.783718</v>
+        <v>283.8972488542868</v>
       </c>
       <c r="G28" s="6" t="n">
-        <v>-293026.091415</v>
+        <v>0</v>
       </c>
       <c r="H28" s="6" t="n">
-        <v>-2640.43740244277</v>
+        <v>0</v>
       </c>
       <c r="I28" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J28" s="6" t="n">
-        <v>-2640.43740244277</v>
+        <v>0</v>
       </c>
       <c r="K28" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L28" s="6" t="n">
-        <v>1066559.875133</v>
+        <v>283.8972488542868</v>
       </c>
       <c r="M28" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N28" s="6" t="n">
-        <v>569.4314192157252</v>
+        <v>0.6225320944278722</v>
       </c>
       <c r="O28" s="6" t="n">
-        <v>569.4314192157252</v>
+        <v>0.6225320944278722</v>
       </c>
       <c r="P28" s="6" t="n">
-        <v>-3209.868821658495</v>
+        <v>-0.6225320944278722</v>
       </c>
       <c r="Q28" s="6" t="n">
         <v>0</v>
@@ -2576,77 +2576,77 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>S51</t>
+          <t>S55</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Savings USDS / sUSDS proxy (Unichain — POL)</t>
+          <t>USDC raw (Avalanche-C — ALM idle)</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>unichain</t>
+          <t>avalanche_c</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E29" s="6" t="n">
-        <v>982408.1850699954</v>
+        <v>2500.221225</v>
       </c>
       <c r="F29" s="6" t="n">
-        <v>985396.9281006901</v>
+        <v>0</v>
       </c>
       <c r="G29" s="6" t="n">
-        <v>2988.743030694792</v>
+        <v>-2500.221225</v>
       </c>
       <c r="H29" s="6" t="n">
-        <v>0</v>
+        <v>-3.30458807350886e-10</v>
       </c>
       <c r="I29" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J29" s="6" t="n">
-        <v>0</v>
+        <v>-3.30458807350886e-10</v>
       </c>
       <c r="K29" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L29" s="6" t="n">
-        <v>982408.1850699954</v>
+        <v>115.3103732260555</v>
       </c>
       <c r="M29" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N29" s="6" t="n">
-        <v>524.5032183531125</v>
+        <v>0.2528534828828865</v>
       </c>
       <c r="O29" s="6" t="n">
-        <v>274.5646893330244</v>
+        <v>0.2528534828828865</v>
       </c>
       <c r="P29" s="6" t="n">
-        <v>-524.5032183531125</v>
+        <v>-0.2528534832133453</v>
       </c>
       <c r="Q29" s="6" t="n">
         <v>0</v>
       </c>
       <c r="R29" s="6" t="n">
-        <v>249.9385290200882</v>
+        <v>0</v>
       </c>
       <c r="S29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>S12</t>
+          <t>S16</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Spark DAI Vault (Morpho)</t>
+          <t>Ethena Staked USDe (sUSDe)</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2660,40 +2660,40 @@
         </is>
       </c>
       <c r="E30" s="6" t="n">
-        <v>458.5728307677575</v>
+        <v>99.50129408753318</v>
       </c>
       <c r="F30" s="6" t="n">
-        <v>539.8728953809741</v>
+        <v>99.81305763596731</v>
       </c>
       <c r="G30" s="6" t="n">
-        <v>81.30006461321658</v>
+        <v>0.3117635484341261</v>
       </c>
       <c r="H30" s="6" t="n">
-        <v>76.33046551920575</v>
+        <v>0.3117635484341261</v>
       </c>
       <c r="I30" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J30" s="6" t="n">
-        <v>76.33046551920575</v>
+        <v>0.3117635484341261</v>
       </c>
       <c r="K30" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L30" s="6" t="n">
-        <v>462.161691889013</v>
+        <v>99.50129408753318</v>
       </c>
       <c r="M30" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N30" s="6" t="n">
-        <v>0.2467460048472986</v>
+        <v>0.2181872112413053</v>
       </c>
       <c r="O30" s="6" t="n">
-        <v>0.2467460048472986</v>
+        <v>0.2181872112413053</v>
       </c>
       <c r="P30" s="6" t="n">
-        <v>76.08371951435845</v>
+        <v>0.09357633719282084</v>
       </c>
       <c r="Q30" s="6" t="n">
         <v>0</v>
@@ -2706,17 +2706,17 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>S34</t>
+          <t>S13</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Spark USDC Vault (Morpho, Base)</t>
+          <t>Spark USDS Vault (Morpho)</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>base</t>
+          <t>ethereum</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -2725,40 +2725,40 @@
         </is>
       </c>
       <c r="E31" s="6" t="n">
-        <v>224.7175624853434</v>
+        <v>21.90660666972937</v>
       </c>
       <c r="F31" s="6" t="n">
-        <v>424.9110349025811</v>
+        <v>21.90661272343654</v>
       </c>
       <c r="G31" s="6" t="n">
-        <v>200.1934724172377</v>
+        <v>6.053707169991468e-06</v>
       </c>
       <c r="H31" s="6" t="n">
-        <v>1.161345275337778</v>
+        <v>6.053707169991468e-06</v>
       </c>
       <c r="I31" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J31" s="6" t="n">
-        <v>1.161345275337778</v>
+        <v>6.053707169991468e-06</v>
       </c>
       <c r="K31" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L31" s="6" t="n">
-        <v>368.0420981576889</v>
+        <v>21.90660666972937</v>
       </c>
       <c r="M31" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N31" s="6" t="n">
-        <v>0.1964959859932215</v>
+        <v>0.04803697741683239</v>
       </c>
       <c r="O31" s="6" t="n">
-        <v>0.1964959859932215</v>
+        <v>0.04803697741683239</v>
       </c>
       <c r="P31" s="6" t="n">
-        <v>0.9648492893445566</v>
+        <v>-0.04803092370966239</v>
       </c>
       <c r="Q31" s="6" t="n">
         <v>0</v>
@@ -2771,59 +2771,59 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>S36</t>
+          <t>S9</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Fluid Savings USDS (fsUSDS, Base)</t>
+          <t>Aave Ethereum USDT (aToken)</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>base</t>
+          <t>ethereum</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E32" s="6" t="n">
-        <v>283.8972488542868</v>
+        <v>5.897868</v>
       </c>
       <c r="F32" s="6" t="n">
-        <v>283.8972488542868</v>
+        <v>5.913258</v>
       </c>
       <c r="G32" s="6" t="n">
-        <v>0</v>
+        <v>0.01539</v>
       </c>
       <c r="H32" s="6" t="n">
-        <v>0</v>
+        <v>0.01539</v>
       </c>
       <c r="I32" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J32" s="6" t="n">
-        <v>0</v>
+        <v>0.01539</v>
       </c>
       <c r="K32" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L32" s="6" t="n">
-        <v>283.8972488542868</v>
+        <v>5.897868</v>
       </c>
       <c r="M32" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N32" s="6" t="n">
-        <v>0.1515714373807448</v>
+        <v>0.01293289080298069</v>
       </c>
       <c r="O32" s="6" t="n">
-        <v>0.1515714373807448</v>
+        <v>0.01293289080298069</v>
       </c>
       <c r="P32" s="6" t="n">
-        <v>-0.1515714373807448</v>
+        <v>0.002457109197019311</v>
       </c>
       <c r="Q32" s="6" t="n">
         <v>0</v>
@@ -2836,59 +2836,59 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>S55</t>
+          <t>S23</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>USDC raw (Avalanche-C — ALM idle)</t>
+          <t>Anchorage tri-party loan escrow (USDC pass-through, ~$0 balance)</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>avalanche_c</t>
+          <t>ethereum</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E33" s="6" t="n">
-        <v>2500.221225</v>
+        <v>1.545609</v>
       </c>
       <c r="F33" s="6" t="n">
-        <v>0</v>
+        <v>10.015998</v>
       </c>
       <c r="G33" s="6" t="n">
-        <v>-2500.221225</v>
+        <v>8.470389000000001</v>
       </c>
       <c r="H33" s="6" t="n">
-        <v>-3.30458807350886e-10</v>
+        <v>8.470389000000001</v>
       </c>
       <c r="I33" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J33" s="6" t="n">
-        <v>-3.30458807350886e-10</v>
+        <v>8.470389000000001</v>
       </c>
       <c r="K33" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L33" s="6" t="n">
-        <v>115.3103732260555</v>
+        <v>1.545609</v>
       </c>
       <c r="M33" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N33" s="6" t="n">
-        <v>0.06156367870882053</v>
+        <v>0.003389223431433898</v>
       </c>
       <c r="O33" s="6" t="n">
-        <v>0.06156367870882053</v>
+        <v>0.003389223431433898</v>
       </c>
       <c r="P33" s="6" t="n">
-        <v>-0.06156367903927934</v>
+        <v>8.466999776568565</v>
       </c>
       <c r="Q33" s="6" t="n">
         <v>0</v>
@@ -2901,59 +2901,59 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>S16</t>
+          <t>S54</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Ethena Staked USDe (sUSDe)</t>
+          <t>Aave Avalanche USDC (aAvaUSDC)</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>ethereum</t>
+          <t>avalanche_c</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E34" s="6" t="n">
-        <v>99.50129408753318</v>
+        <v>0.154431</v>
       </c>
       <c r="F34" s="6" t="n">
-        <v>99.81305763596731</v>
+        <v>0.155165</v>
       </c>
       <c r="G34" s="6" t="n">
-        <v>0.3117635484341261</v>
+        <v>0.000734</v>
       </c>
       <c r="H34" s="6" t="n">
-        <v>0.3117635484341261</v>
+        <v>0.000734</v>
       </c>
       <c r="I34" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J34" s="6" t="n">
-        <v>0.3117635484341261</v>
+        <v>0.000734</v>
       </c>
       <c r="K34" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L34" s="6" t="n">
-        <v>99.50129408753318</v>
+        <v>0.154431</v>
       </c>
       <c r="M34" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N34" s="6" t="n">
-        <v>0.05312328395909313</v>
+        <v>0.0003386374974134909</v>
       </c>
       <c r="O34" s="6" t="n">
-        <v>0.05312328395909313</v>
+        <v>0.0003386374974134909</v>
       </c>
       <c r="P34" s="6" t="n">
-        <v>0.258640264475033</v>
+        <v>0.0003953625025865091</v>
       </c>
       <c r="Q34" s="6" t="n">
         <v>0</v>
@@ -2966,12 +2966,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>S13</t>
+          <t>S8</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Spark USDS Vault (Morpho)</t>
+          <t>Aave Ethereum USDC (aToken)</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2981,44 +2981,44 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E35" s="6" t="n">
-        <v>21.90660666972937</v>
+        <v>0.057783</v>
       </c>
       <c r="F35" s="6" t="n">
-        <v>21.90661272343654</v>
+        <v>0.057969</v>
       </c>
       <c r="G35" s="6" t="n">
-        <v>6.053707169991468e-06</v>
+        <v>0.000186</v>
       </c>
       <c r="H35" s="6" t="n">
-        <v>6.053707169991468e-06</v>
+        <v>0.000186</v>
       </c>
       <c r="I35" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J35" s="6" t="n">
-        <v>6.053707169991468e-06</v>
+        <v>0.000186</v>
       </c>
       <c r="K35" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L35" s="6" t="n">
-        <v>21.90660666972937</v>
+        <v>0.057783</v>
       </c>
       <c r="M35" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N35" s="6" t="n">
-        <v>0.01169583669607777</v>
+        <v>0.0001267070116300726</v>
       </c>
       <c r="O35" s="6" t="n">
-        <v>0.01169583669607777</v>
+        <v>0.0001267070116300726</v>
       </c>
       <c r="P35" s="6" t="n">
-        <v>-0.01168978298890778</v>
+        <v>5.929298836992738e-05</v>
       </c>
       <c r="Q35" s="6" t="n">
         <v>0</v>
@@ -3031,17 +3031,17 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>S9</t>
+          <t>S41</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Aave Ethereum USDT (aToken)</t>
+          <t>Aave Arbitrum USDCn (aArbUSDCn)</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>ethereum</t>
+          <t>arbitrum</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -3050,40 +3050,40 @@
         </is>
       </c>
       <c r="E36" s="6" t="n">
-        <v>5.897868</v>
+        <v>0.006346</v>
       </c>
       <c r="F36" s="6" t="n">
-        <v>5.913258</v>
+        <v>0.006363</v>
       </c>
       <c r="G36" s="6" t="n">
-        <v>0.01539</v>
+        <v>1.7e-05</v>
       </c>
       <c r="H36" s="6" t="n">
-        <v>0.01539</v>
+        <v>1.7e-05</v>
       </c>
       <c r="I36" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J36" s="6" t="n">
-        <v>0.01539</v>
+        <v>1.7e-05</v>
       </c>
       <c r="K36" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L36" s="6" t="n">
-        <v>5.897868</v>
+        <v>0.006346</v>
       </c>
       <c r="M36" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N36" s="6" t="n">
-        <v>0.003148844639564389</v>
+        <v>1.391555813655298e-05</v>
       </c>
       <c r="O36" s="6" t="n">
-        <v>0.003148844639564389</v>
+        <v>1.391555813655298e-05</v>
       </c>
       <c r="P36" s="6" t="n">
-        <v>0.01224115536043561</v>
+        <v>3.08444186344702e-06</v>
       </c>
       <c r="Q36" s="6" t="n">
         <v>0</v>
@@ -3096,12 +3096,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>S23</t>
+          <t>S7</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Anchorage tri-party loan escrow (USDC pass-through, ~$0 balance)</t>
+          <t>Aave Ethereum USDS (aToken)</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -3111,44 +3111,44 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E37" s="6" t="n">
-        <v>1.545609</v>
+        <v>0.005744283090097436</v>
       </c>
       <c r="F37" s="6" t="n">
-        <v>10.015998</v>
+        <v>0.005746426914602806</v>
       </c>
       <c r="G37" s="6" t="n">
-        <v>8.470389000000001</v>
+        <v>2.14382450537e-06</v>
       </c>
       <c r="H37" s="6" t="n">
-        <v>8.470389000000001</v>
+        <v>2.14382450537e-06</v>
       </c>
       <c r="I37" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J37" s="6" t="n">
-        <v>8.470389000000001</v>
+        <v>2.14382450537e-06</v>
       </c>
       <c r="K37" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L37" s="6" t="n">
-        <v>1.545609</v>
+        <v>0.005744283090097436</v>
       </c>
       <c r="M37" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N37" s="6" t="n">
-        <v>0.0008251935469753605</v>
+        <v>1.259610861851073e-05</v>
       </c>
       <c r="O37" s="6" t="n">
-        <v>0.0008251935469753605</v>
+        <v>1.259610861851073e-05</v>
       </c>
       <c r="P37" s="6" t="n">
-        <v>8.469563806453024</v>
+        <v>-1.045228411314073e-05</v>
       </c>
       <c r="Q37" s="6" t="n">
         <v>0</v>
@@ -3161,17 +3161,17 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>S54</t>
+          <t>S35</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Aave Avalanche USDC (aAvaUSDC)</t>
+          <t>Aave Base USDC (aBasUSDC)</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>avalanche_c</t>
+          <t>base</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -3180,40 +3180,40 @@
         </is>
       </c>
       <c r="E38" s="6" t="n">
-        <v>0.154431</v>
+        <v>0.0017</v>
       </c>
       <c r="F38" s="6" t="n">
-        <v>0.155165</v>
+        <v>0.001705</v>
       </c>
       <c r="G38" s="6" t="n">
-        <v>0.000734</v>
+        <v>5e-06</v>
       </c>
       <c r="H38" s="6" t="n">
-        <v>0.000734</v>
+        <v>5e-06</v>
       </c>
       <c r="I38" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J38" s="6" t="n">
-        <v>0.000734</v>
+        <v>5e-06</v>
       </c>
       <c r="K38" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L38" s="6" t="n">
-        <v>0.154431</v>
+        <v>0.0017</v>
       </c>
       <c r="M38" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N38" s="6" t="n">
-        <v>8.245000168409469e-05</v>
+        <v>3.727773216536412e-06</v>
       </c>
       <c r="O38" s="6" t="n">
-        <v>8.245000168409469e-05</v>
+        <v>3.727773216536412e-06</v>
       </c>
       <c r="P38" s="6" t="n">
-        <v>0.0006515499983159053</v>
+        <v>1.272226783463589e-06</v>
       </c>
       <c r="Q38" s="6" t="n">
         <v>0</v>
@@ -3226,12 +3226,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>S8</t>
+          <t>S17</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Aave Ethereum USDC (aToken)</t>
+          <t>Fluid Savings USDS (fsUSDS)</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -3241,44 +3241,44 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E39" s="6" t="n">
-        <v>0.057783</v>
+        <v>0.001240144670509943</v>
       </c>
       <c r="F39" s="6" t="n">
-        <v>0.057969</v>
+        <v>0.001240144670509943</v>
       </c>
       <c r="G39" s="6" t="n">
-        <v>0.000186</v>
+        <v>0</v>
       </c>
       <c r="H39" s="6" t="n">
-        <v>0.000186</v>
+        <v>0</v>
       </c>
       <c r="I39" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J39" s="6" t="n">
-        <v>0.000186</v>
+        <v>0</v>
       </c>
       <c r="K39" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L39" s="6" t="n">
-        <v>0.057783</v>
+        <v>0.001240144670509943</v>
       </c>
       <c r="M39" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N39" s="6" t="n">
-        <v>3.085007833473877e-05</v>
+        <v>2.719398874916082e-06</v>
       </c>
       <c r="O39" s="6" t="n">
-        <v>3.085007833473877e-05</v>
+        <v>2.719398874916082e-06</v>
       </c>
       <c r="P39" s="6" t="n">
-        <v>0.0001551499216652612</v>
+        <v>-2.719398874916082e-06</v>
       </c>
       <c r="Q39" s="6" t="n">
         <v>0</v>
@@ -3291,17 +3291,17 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>S41</t>
+          <t>S6</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Aave Arbitrum USDCn (aArbUSDCn)</t>
+          <t>Aave Ethereum Lido USDS (aToken)</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>arbitrum</t>
+          <t>ethereum</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -3310,40 +3310,40 @@
         </is>
       </c>
       <c r="E40" s="6" t="n">
-        <v>0.006346</v>
+        <v>0.0005209665645060241</v>
       </c>
       <c r="F40" s="6" t="n">
-        <v>0.006363</v>
+        <v>0.000521673271312833</v>
       </c>
       <c r="G40" s="6" t="n">
-        <v>1.7e-05</v>
+        <v>7.06706806809e-07</v>
       </c>
       <c r="H40" s="6" t="n">
-        <v>1.7e-05</v>
+        <v>7.06706806809e-07</v>
       </c>
       <c r="I40" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J40" s="6" t="n">
-        <v>1.7e-05</v>
+        <v>7.06706806809e-07</v>
       </c>
       <c r="K40" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L40" s="6" t="n">
-        <v>0.006346</v>
+        <v>0.0005209665645060241</v>
       </c>
       <c r="M40" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N40" s="6" t="n">
-        <v>3.388100256342735e-06</v>
+        <v>1.142379532868556e-06</v>
       </c>
       <c r="O40" s="6" t="n">
-        <v>3.388100256342735e-06</v>
+        <v>1.142379532868556e-06</v>
       </c>
       <c r="P40" s="6" t="n">
-        <v>1.361189974365727e-05</v>
+        <v>-4.356727260595558e-07</v>
       </c>
       <c r="Q40" s="6" t="n">
         <v>0</v>
@@ -3356,12 +3356,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>S7</t>
+          <t>S30</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Aave Ethereum USDS (aToken)</t>
+          <t>USDe raw (ALM idle)</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -3371,44 +3371,44 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E41" s="6" t="n">
-        <v>0.005744283090097436</v>
+        <v>7.4896275897803e-05</v>
       </c>
       <c r="F41" s="6" t="n">
-        <v>0.005746426914602806</v>
+        <v>7.4896275897803e-05</v>
       </c>
       <c r="G41" s="6" t="n">
-        <v>2.14382450537e-06</v>
+        <v>0</v>
       </c>
       <c r="H41" s="6" t="n">
-        <v>2.14382450537e-06</v>
+        <v>0</v>
       </c>
       <c r="I41" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J41" s="6" t="n">
-        <v>2.14382450537e-06</v>
+        <v>0</v>
       </c>
       <c r="K41" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L41" s="6" t="n">
-        <v>0.005744283090097436</v>
+        <v>7.4896275897803e-05</v>
       </c>
       <c r="M41" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N41" s="6" t="n">
-        <v>3.066846361497693e-06</v>
+        <v>1.642331360647951e-07</v>
       </c>
       <c r="O41" s="6" t="n">
-        <v>3.066846361497693e-06</v>
+        <v>1.642331360647951e-07</v>
       </c>
       <c r="P41" s="6" t="n">
-        <v>-9.23021856127693e-07</v>
+        <v>-1.642331360647951e-07</v>
       </c>
       <c r="Q41" s="6" t="n">
         <v>0</v>
@@ -3421,59 +3421,59 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>S35</t>
+          <t>S19</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Aave Base USDC (aBasUSDC)</t>
+          <t>BlackRock USD Institutional Digital Liquidity Fund (BUIDL-I)</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>base</t>
+          <t>ethereum</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E42" s="6" t="n">
-        <v>0.0017</v>
+        <v>0</v>
       </c>
       <c r="F42" s="6" t="n">
-        <v>0.001705</v>
+        <v>0</v>
       </c>
       <c r="G42" s="6" t="n">
-        <v>5e-06</v>
+        <v>0</v>
       </c>
       <c r="H42" s="6" t="n">
-        <v>5e-06</v>
+        <v>0</v>
       </c>
       <c r="I42" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J42" s="6" t="n">
-        <v>5e-06</v>
+        <v>0</v>
       </c>
       <c r="K42" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L42" s="6" t="n">
-        <v>0.0017</v>
+        <v>0</v>
       </c>
       <c r="M42" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N42" s="6" t="n">
-        <v>9.07622192843153e-07</v>
+        <v>0</v>
       </c>
       <c r="O42" s="6" t="n">
-        <v>9.07622192843153e-07</v>
+        <v>0</v>
       </c>
       <c r="P42" s="6" t="n">
-        <v>4.092377807156847e-06</v>
+        <v>0</v>
       </c>
       <c r="Q42" s="6" t="n">
         <v>0</v>
@@ -3486,12 +3486,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>S17</t>
+          <t>S20</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Fluid Savings USDS (fsUSDS)</t>
+          <t>Janus Henderson Anemoy Treasury Fund (JTRSY)</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3501,14 +3501,14 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E43" s="6" t="n">
-        <v>0.001240144670509943</v>
+        <v>0</v>
       </c>
       <c r="F43" s="6" t="n">
-        <v>0.001240144670509943</v>
+        <v>0</v>
       </c>
       <c r="G43" s="6" t="n">
         <v>0</v>
@@ -3526,19 +3526,19 @@
         <v>0</v>
       </c>
       <c r="L43" s="6" t="n">
-        <v>0.001240144670509943</v>
+        <v>0</v>
       </c>
       <c r="M43" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N43" s="6" t="n">
-        <v>6.621075442888142e-07</v>
+        <v>0</v>
       </c>
       <c r="O43" s="6" t="n">
-        <v>6.621075442888142e-07</v>
+        <v>0</v>
       </c>
       <c r="P43" s="6" t="n">
-        <v>-6.621075442888142e-07</v>
+        <v>0</v>
       </c>
       <c r="Q43" s="6" t="n">
         <v>0</v>
@@ -3551,12 +3551,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>S6</t>
+          <t>S21</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Aave Ethereum Lido USDS (aToken)</t>
+          <t>Superstate Short Duration US Government Securities Fund (USTB)</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3566,44 +3566,44 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E44" s="6" t="n">
-        <v>0.0005209665645060241</v>
+        <v>0</v>
       </c>
       <c r="F44" s="6" t="n">
-        <v>0.000521673271312833</v>
+        <v>0</v>
       </c>
       <c r="G44" s="6" t="n">
-        <v>7.06706806809e-07</v>
+        <v>0</v>
       </c>
       <c r="H44" s="6" t="n">
-        <v>7.06706806809e-07</v>
+        <v>0</v>
       </c>
       <c r="I44" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J44" s="6" t="n">
-        <v>7.06706806809e-07</v>
+        <v>0</v>
       </c>
       <c r="K44" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L44" s="6" t="n">
-        <v>0.0005209665645060241</v>
+        <v>0</v>
       </c>
       <c r="M44" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N44" s="6" t="n">
-        <v>2.781416562793655e-07</v>
+        <v>0</v>
       </c>
       <c r="O44" s="6" t="n">
-        <v>2.781416562793655e-07</v>
+        <v>0</v>
       </c>
       <c r="P44" s="6" t="n">
-        <v>4.285651505296345e-07</v>
+        <v>0</v>
       </c>
       <c r="Q44" s="6" t="n">
         <v>0</v>
@@ -3611,17 +3611,21 @@
       <c r="R44" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="S44" t="inlineStr"/>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>SDE (fixed)</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>S30</t>
+          <t>S22</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>USDe raw (ALM idle)</t>
+          <t>Superstate Crypto Carry Fund (USCC)</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3631,14 +3635,14 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E45" s="6" t="n">
-        <v>7.4896275897803e-05</v>
+        <v>0</v>
       </c>
       <c r="F45" s="6" t="n">
-        <v>7.4896275897803e-05</v>
+        <v>0</v>
       </c>
       <c r="G45" s="6" t="n">
         <v>0</v>
@@ -3656,19 +3660,19 @@
         <v>0</v>
       </c>
       <c r="L45" s="6" t="n">
-        <v>7.4896275897803e-05</v>
+        <v>0</v>
       </c>
       <c r="M45" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N45" s="6" t="n">
-        <v>3.998677774479397e-08</v>
+        <v>0</v>
       </c>
       <c r="O45" s="6" t="n">
-        <v>3.998677774479397e-08</v>
+        <v>0</v>
       </c>
       <c r="P45" s="6" t="n">
-        <v>-3.998677774479397e-08</v>
+        <v>0</v>
       </c>
       <c r="Q45" s="6" t="n">
         <v>0</v>
@@ -3681,12 +3685,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>S19</t>
+          <t>S26</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>BlackRock USD Institutional Digital Liquidity Fund (BUIDL-I)</t>
+          <t>USDC raw (ALM idle)</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3696,7 +3700,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E46" s="6" t="n">
@@ -3709,13 +3713,13 @@
         <v>0</v>
       </c>
       <c r="H46" s="6" t="n">
-        <v>0</v>
+        <v>6162610.279999871</v>
       </c>
       <c r="I46" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J46" s="6" t="n">
-        <v>0</v>
+        <v>6162610.279999871</v>
       </c>
       <c r="K46" s="6" t="n">
         <v>0</v>
@@ -3733,7 +3737,7 @@
         <v>0</v>
       </c>
       <c r="P46" s="6" t="n">
-        <v>0</v>
+        <v>6162610.279999871</v>
       </c>
       <c r="Q46" s="6" t="n">
         <v>0</v>
@@ -3746,12 +3750,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>S20</t>
+          <t>S29</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Janus Henderson Anemoy Treasury Fund (JTRSY)</t>
+          <t>DAI raw (ALM idle)</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3761,7 +3765,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E47" s="6" t="n">
@@ -3774,13 +3778,13 @@
         <v>0</v>
       </c>
       <c r="H47" s="6" t="n">
-        <v>0</v>
+        <v>8.19007e-07</v>
       </c>
       <c r="I47" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J47" s="6" t="n">
-        <v>0</v>
+        <v>8.19007e-07</v>
       </c>
       <c r="K47" s="6" t="n">
         <v>0</v>
@@ -3798,7 +3802,7 @@
         <v>0</v>
       </c>
       <c r="P47" s="6" t="n">
-        <v>0</v>
+        <v>8.19007e-07</v>
       </c>
       <c r="Q47" s="6" t="n">
         <v>0</v>
@@ -3811,12 +3815,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>S21</t>
+          <t>S31</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Superstate Short Duration US Government Securities Fund (USTB)</t>
+          <t>USDS raw / POL (ALM idle — already netted out of utilized)</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3826,7 +3830,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E48" s="6" t="n">
@@ -3839,19 +3843,19 @@
         <v>0</v>
       </c>
       <c r="H48" s="6" t="n">
-        <v>0</v>
+        <v>-2.5155451e-06</v>
       </c>
       <c r="I48" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J48" s="6" t="n">
-        <v>0</v>
+        <v>-2.5155451e-06</v>
       </c>
       <c r="K48" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L48" s="6" t="n">
-        <v>0</v>
+        <v>17.83075712531922</v>
       </c>
       <c r="M48" s="7" t="n">
         <v>0</v>
@@ -3863,7 +3867,7 @@
         <v>0</v>
       </c>
       <c r="P48" s="6" t="n">
-        <v>0</v>
+        <v>-2.5155451e-06</v>
       </c>
       <c r="Q48" s="6" t="n">
         <v>0</v>
@@ -3873,36 +3877,36 @@
       </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>SDE (fixed)</t>
+          <t>CoF excluded (Savings V2 depositor capital; not in cum_alm_usds)</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>S22</t>
+          <t>S38</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Superstate Crypto Carry Fund (USCC)</t>
+          <t>USDS raw (Base — POL)</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>ethereum</t>
+          <t>base</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E49" s="6" t="n">
-        <v>0</v>
+        <v>65170000</v>
       </c>
       <c r="F49" s="6" t="n">
-        <v>0</v>
+        <v>65170000</v>
       </c>
       <c r="G49" s="6" t="n">
         <v>0</v>
@@ -3920,10 +3924,10 @@
         <v>0</v>
       </c>
       <c r="L49" s="6" t="n">
-        <v>0</v>
+        <v>65170000</v>
       </c>
       <c r="M49" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N49" s="6" t="n">
         <v>0</v>
@@ -3935,32 +3939,36 @@
         <v>0</v>
       </c>
       <c r="Q49" s="6" t="n">
-        <v>0</v>
+        <v>65170000</v>
       </c>
       <c r="R49" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="S49" t="inlineStr"/>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>CoF excluded (already deducted from utilized)</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>S26</t>
+          <t>S42</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>USDC raw (ALM idle)</t>
+          <t>Fluid Savings USDS (fsUSDS, Arbitrum)</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>ethereum</t>
+          <t>arbitrum</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E50" s="6" t="n">
@@ -3973,13 +3981,13 @@
         <v>0</v>
       </c>
       <c r="H50" s="6" t="n">
-        <v>6162610.279999871</v>
+        <v>0</v>
       </c>
       <c r="I50" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J50" s="6" t="n">
-        <v>6162610.279999871</v>
+        <v>0</v>
       </c>
       <c r="K50" s="6" t="n">
         <v>0</v>
@@ -3997,7 +4005,7 @@
         <v>0</v>
       </c>
       <c r="P50" s="6" t="n">
-        <v>6162610.279999871</v>
+        <v>0</v>
       </c>
       <c r="Q50" s="6" t="n">
         <v>0</v>
@@ -4010,17 +4018,17 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>S29</t>
+          <t>S44</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>DAI raw (ALM idle)</t>
+          <t>USDS raw (Arbitrum — POL)</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>ethereum</t>
+          <t>arbitrum</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -4029,31 +4037,31 @@
         </is>
       </c>
       <c r="E51" s="6" t="n">
-        <v>0</v>
+        <v>90000000</v>
       </c>
       <c r="F51" s="6" t="n">
-        <v>0</v>
+        <v>90000000</v>
       </c>
       <c r="G51" s="6" t="n">
         <v>0</v>
       </c>
       <c r="H51" s="6" t="n">
-        <v>8.19007e-07</v>
+        <v>0</v>
       </c>
       <c r="I51" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J51" s="6" t="n">
-        <v>8.19007e-07</v>
+        <v>0</v>
       </c>
       <c r="K51" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L51" s="6" t="n">
-        <v>0</v>
+        <v>90000000</v>
       </c>
       <c r="M51" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N51" s="6" t="n">
         <v>0</v>
@@ -4062,30 +4070,34 @@
         <v>0</v>
       </c>
       <c r="P51" s="6" t="n">
-        <v>8.19007e-07</v>
+        <v>0</v>
       </c>
       <c r="Q51" s="6" t="n">
-        <v>0</v>
+        <v>90000000</v>
       </c>
       <c r="R51" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="S51" t="inlineStr"/>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>CoF excluded (already deducted from utilized)</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>S31</t>
+          <t>S48</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>USDS raw / POL (ALM idle — already netted out of utilized)</t>
+          <t>USDS raw (Optimism — POL)</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>ethereum</t>
+          <t>optimism</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -4094,28 +4106,28 @@
         </is>
       </c>
       <c r="E52" s="6" t="n">
-        <v>0</v>
+        <v>89900000</v>
       </c>
       <c r="F52" s="6" t="n">
-        <v>0</v>
+        <v>89900000</v>
       </c>
       <c r="G52" s="6" t="n">
         <v>0</v>
       </c>
       <c r="H52" s="6" t="n">
-        <v>-2.5155451e-06</v>
+        <v>0</v>
       </c>
       <c r="I52" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J52" s="6" t="n">
-        <v>-2.5155451e-06</v>
+        <v>0</v>
       </c>
       <c r="K52" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L52" s="6" t="n">
-        <v>17.83075712531922</v>
+        <v>89900000</v>
       </c>
       <c r="M52" s="7" t="n">
         <v>0</v>
@@ -4127,10 +4139,10 @@
         <v>0</v>
       </c>
       <c r="P52" s="6" t="n">
-        <v>-2.5155451e-06</v>
+        <v>0</v>
       </c>
       <c r="Q52" s="6" t="n">
-        <v>17.83075712531922</v>
+        <v>89900000</v>
       </c>
       <c r="R52" s="6" t="n">
         <v>0</v>
@@ -4144,17 +4156,17 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>S38</t>
+          <t>S52</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>USDS raw (Base — POL)</t>
+          <t>USDS raw (Unichain — POL)</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>base</t>
+          <t>unichain</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -4163,10 +4175,10 @@
         </is>
       </c>
       <c r="E53" s="6" t="n">
-        <v>65170000</v>
+        <v>89900000</v>
       </c>
       <c r="F53" s="6" t="n">
-        <v>65170000</v>
+        <v>89900000</v>
       </c>
       <c r="G53" s="6" t="n">
         <v>0</v>
@@ -4184,7 +4196,7 @@
         <v>0</v>
       </c>
       <c r="L53" s="6" t="n">
-        <v>65170000</v>
+        <v>89900000</v>
       </c>
       <c r="M53" s="7" t="n">
         <v>0</v>
@@ -4199,7 +4211,7 @@
         <v>0</v>
       </c>
       <c r="Q53" s="6" t="n">
-        <v>65170000</v>
+        <v>89900000</v>
       </c>
       <c r="R53" s="6" t="n">
         <v>0</v>
@@ -4213,50 +4225,50 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>S42</t>
+          <t>S56</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Fluid Savings USDS (fsUSDS, Arbitrum)</t>
+          <t>Spark Savings V2 — spUSDC vault</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>arbitrum</t>
+          <t>ethereum</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>S2</t>
         </is>
       </c>
       <c r="E54" s="6" t="n">
-        <v>0</v>
+        <v>573332157.534611</v>
       </c>
       <c r="F54" s="6" t="n">
-        <v>0</v>
+        <v>303545287.192935</v>
       </c>
       <c r="G54" s="6" t="n">
-        <v>0</v>
+        <v>-269786870.341676</v>
       </c>
       <c r="H54" s="6" t="n">
-        <v>0</v>
+        <v>-2077933.247665395</v>
       </c>
       <c r="I54" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J54" s="6" t="n">
-        <v>0</v>
+        <v>-2077933.247665395</v>
       </c>
       <c r="K54" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L54" s="6" t="n">
-        <v>0</v>
+        <v>573332157.534611</v>
       </c>
       <c r="M54" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N54" s="6" t="n">
         <v>0</v>
@@ -4265,7 +4277,7 @@
         <v>0</v>
       </c>
       <c r="P54" s="6" t="n">
-        <v>0</v>
+        <v>-2077933.247665395</v>
       </c>
       <c r="Q54" s="6" t="n">
         <v>0</v>
@@ -4273,52 +4285,56 @@
       <c r="R54" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="S54" t="inlineStr"/>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>CoF excluded (Savings V2 depositor capital; not in cum_alm_usds)</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>S44</t>
+          <t>S57</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>USDS raw (Arbitrum — POL)</t>
+          <t>Spark Savings V2 — spUSDT vault</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>arbitrum</t>
+          <t>ethereum</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>S2</t>
         </is>
       </c>
       <c r="E55" s="6" t="n">
-        <v>90000000</v>
+        <v>1134703231.016836</v>
       </c>
       <c r="F55" s="6" t="n">
-        <v>90000000</v>
+        <v>1270360913.25412</v>
       </c>
       <c r="G55" s="6" t="n">
-        <v>0</v>
+        <v>135657682.237284</v>
       </c>
       <c r="H55" s="6" t="n">
-        <v>0</v>
+        <v>-2595205.75030597</v>
       </c>
       <c r="I55" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J55" s="6" t="n">
-        <v>0</v>
+        <v>-2595205.75030597</v>
       </c>
       <c r="K55" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L55" s="6" t="n">
-        <v>90000000</v>
+        <v>1134703231.016836</v>
       </c>
       <c r="M55" s="7" t="n">
         <v>0</v>
@@ -4330,64 +4346,64 @@
         <v>0</v>
       </c>
       <c r="P55" s="6" t="n">
-        <v>0</v>
+        <v>-2595205.75030597</v>
       </c>
       <c r="Q55" s="6" t="n">
-        <v>90000000</v>
+        <v>0</v>
       </c>
       <c r="R55" s="6" t="n">
         <v>0</v>
       </c>
       <c r="S55" t="inlineStr">
         <is>
-          <t>CoF excluded (already deducted from utilized)</t>
+          <t>CoF excluded (Savings V2 depositor capital; not in cum_alm_usds)</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>S48</t>
+          <t>S59</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>USDS raw (Optimism — POL)</t>
+          <t>Spark Savings V2 — spPYUSD vault</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>optimism</t>
+          <t>ethereum</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>S2</t>
         </is>
       </c>
       <c r="E56" s="6" t="n">
-        <v>89900000</v>
+        <v>1066559.875133</v>
       </c>
       <c r="F56" s="6" t="n">
-        <v>89900000</v>
+        <v>773533.783718</v>
       </c>
       <c r="G56" s="6" t="n">
-        <v>0</v>
+        <v>-293026.091415</v>
       </c>
       <c r="H56" s="6" t="n">
-        <v>0</v>
+        <v>-2640.43740244277</v>
       </c>
       <c r="I56" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J56" s="6" t="n">
-        <v>0</v>
+        <v>-2640.43740244277</v>
       </c>
       <c r="K56" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L56" s="6" t="n">
-        <v>89900000</v>
+        <v>1066559.875133</v>
       </c>
       <c r="M56" s="7" t="n">
         <v>0</v>
@@ -4399,64 +4415,64 @@
         <v>0</v>
       </c>
       <c r="P56" s="6" t="n">
-        <v>0</v>
+        <v>-2640.43740244277</v>
       </c>
       <c r="Q56" s="6" t="n">
-        <v>89900000</v>
+        <v>0</v>
       </c>
       <c r="R56" s="6" t="n">
         <v>0</v>
       </c>
       <c r="S56" t="inlineStr">
         <is>
-          <t>CoF excluded (already deducted from utilized)</t>
+          <t>CoF excluded (Savings V2 depositor capital; not in cum_alm_usds)</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>S52</t>
+          <t>S60</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>USDS raw (Unichain — POL)</t>
+          <t>Spark Savings V2 — spUSDC vault (Avalanche-C, CREATE2 same address)</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>unichain</t>
+          <t>avalanche_c</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>S2</t>
         </is>
       </c>
       <c r="E57" s="6" t="n">
-        <v>89900000</v>
+        <v>37138817.432463</v>
       </c>
       <c r="F57" s="6" t="n">
-        <v>89900000</v>
+        <v>25647247.422478</v>
       </c>
       <c r="G57" s="6" t="n">
-        <v>0</v>
+        <v>-11491570.009985</v>
       </c>
       <c r="H57" s="6" t="n">
-        <v>0</v>
+        <v>-94676.37115954701</v>
       </c>
       <c r="I57" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J57" s="6" t="n">
-        <v>0</v>
+        <v>-94676.37115954701</v>
       </c>
       <c r="K57" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L57" s="6" t="n">
-        <v>89900000</v>
+        <v>37138817.432463</v>
       </c>
       <c r="M57" s="7" t="n">
         <v>0</v>
@@ -4468,17 +4484,17 @@
         <v>0</v>
       </c>
       <c r="P57" s="6" t="n">
-        <v>0</v>
+        <v>-94676.37115954701</v>
       </c>
       <c r="Q57" s="6" t="n">
-        <v>89900000</v>
+        <v>0</v>
       </c>
       <c r="R57" s="6" t="n">
         <v>0</v>
       </c>
       <c r="S57" t="inlineStr">
         <is>
-          <t>CoF excluded (already deducted from utilized)</t>
+          <t>CoF excluded (Savings V2 depositor capital; not in cum_alm_usds)</t>
         </is>
       </c>
     </row>
@@ -4587,7 +4603,7 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>3284300.977760902</v>
+        <v>10234615.9342856</v>
       </c>
     </row>
     <row r="5">
@@ -4607,7 +4623,7 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>3358457.038605412</v>
+        <v>10308771.99513011</v>
       </c>
     </row>
     <row r="8">
@@ -4634,7 +4650,7 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>3284300.977760902</v>
+        <v>10234615.9342856</v>
       </c>
     </row>
     <row r="12">
@@ -4644,7 +4660,7 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>-10092820.88181026</v>
+        <v>-3142505.92528556</v>
       </c>
     </row>
     <row r="13" ht="60" customHeight="1">

--- a/settlements/spark/2026-05/spark_settlement_may_2026.xlsx
+++ b/settlements/spark/2026-05/spark_settlement_may_2026.xlsx
@@ -11,6 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Venues" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sky Revenue" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sky Direct" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Debt" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -74,7 +75,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -87,6 +88,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -523,7 +525,7 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>10557149.38334401</v>
+        <v>10234615.9342856</v>
       </c>
     </row>
     <row r="10">
@@ -539,7 +541,7 @@
     <row r="11">
       <c r="A11" t="inlineStr"/>
       <c r="B11" s="4" t="n">
-        <v>10631305.44418851</v>
+        <v>10308771.99513011</v>
       </c>
     </row>
     <row r="13">
@@ -561,7 +563,7 @@
         </is>
       </c>
       <c r="B14" s="3" t="n">
-        <v>10557149.38334401</v>
+        <v>10234615.9342856</v>
       </c>
     </row>
     <row r="15">
@@ -571,7 +573,7 @@
         </is>
       </c>
       <c r="B15" s="3" t="n">
-        <v>-2819972.476227154</v>
+        <v>-3142505.92528556</v>
       </c>
     </row>
     <row r="16">
@@ -619,13 +621,13 @@
         </is>
       </c>
       <c r="B22" s="3" t="n">
-        <v>-10557149.38334401</v>
+        <v>-10234615.9342856</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr"/>
       <c r="B23" s="4" t="n">
-        <v>-2271035.909278506</v>
+        <v>-1948502.4602201</v>
       </c>
     </row>
     <row r="25">
@@ -660,7 +662,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-06-05T13:13:14+00:00</t>
+          <t>2026-06-08T14:52:11+00:00</t>
         </is>
       </c>
     </row>
@@ -816,7 +818,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>sUSDS raw / POL (ALM — Cat B 4626, demand-side spread)</t>
+          <t>sUSDS raw / POL (ALM — Cat B 4626, demand-side spread + agent rate)</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -857,13 +859,13 @@
         <v>1</v>
       </c>
       <c r="N2" s="6" t="n">
-        <v>3142112.038726919</v>
+        <v>4167822.764039975</v>
       </c>
       <c r="O2" s="6" t="n">
-        <v>3142112.038726919</v>
+        <v>4167822.764039975</v>
       </c>
       <c r="P2" s="6" t="n">
-        <v>-3142112.038726919</v>
+        <v>-4167822.764039975</v>
       </c>
       <c r="Q2" s="6" t="n">
         <v>0</v>
@@ -876,12 +878,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>S57</t>
+          <t>S3</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Spark Savings V2 — spUSDT vault</t>
+          <t>Spark USDT (SparkLend spToken)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -891,44 +893,44 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E3" s="6" t="n">
-        <v>1134703231.016836</v>
+        <v>677669071.17383</v>
       </c>
       <c r="F3" s="6" t="n">
-        <v>1270360913.25412</v>
+        <v>495837665.420656</v>
       </c>
       <c r="G3" s="6" t="n">
-        <v>135657682.237284</v>
+        <v>-181831405.753174</v>
       </c>
       <c r="H3" s="6" t="n">
-        <v>-2595205.75030597</v>
+        <v>1868112.168236</v>
       </c>
       <c r="I3" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J3" s="6" t="n">
-        <v>-2595205.75030597</v>
+        <v>1868112.168236</v>
       </c>
       <c r="K3" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L3" s="6" t="n">
-        <v>1134703231.016836</v>
+        <v>671743280.2731394</v>
       </c>
       <c r="M3" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N3" s="6" t="n">
-        <v>1875837.778435055</v>
+        <v>1473003.887406189</v>
       </c>
       <c r="O3" s="6" t="n">
-        <v>1875837.778435055</v>
+        <v>1473003.887406189</v>
       </c>
       <c r="P3" s="6" t="n">
-        <v>-4471043.528741025</v>
+        <v>395108.2808298113</v>
       </c>
       <c r="Q3" s="6" t="n">
         <v>0</v>
@@ -941,12 +943,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>S3</t>
+          <t>S28</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Spark USDT (SparkLend spToken)</t>
+          <t>PYUSD raw (ALM idle — $677M as of 2026-04)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -956,44 +958,44 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E4" s="6" t="n">
-        <v>677669071.17383</v>
+        <v>677151123.07819</v>
       </c>
       <c r="F4" s="6" t="n">
-        <v>495837665.420656</v>
+        <v>262428227.923162</v>
       </c>
       <c r="G4" s="6" t="n">
-        <v>-181831405.753174</v>
+        <v>-414722895.155028</v>
       </c>
       <c r="H4" s="6" t="n">
-        <v>1868112.168236</v>
+        <v>3091580</v>
       </c>
       <c r="I4" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J4" s="6" t="n">
-        <v>1868112.168236</v>
+        <v>3091580</v>
       </c>
       <c r="K4" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L4" s="6" t="n">
-        <v>671743280.2731394</v>
+        <v>615465268.6039779</v>
       </c>
       <c r="M4" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N4" s="6" t="n">
-        <v>1110494.257971797</v>
+        <v>1349597.02588841</v>
       </c>
       <c r="O4" s="6" t="n">
-        <v>1110494.257971797</v>
+        <v>1349597.02588841</v>
       </c>
       <c r="P4" s="6" t="n">
-        <v>757617.9102642025</v>
+        <v>1741982.97411159</v>
       </c>
       <c r="Q4" s="6" t="n">
         <v>0</v>
@@ -1006,12 +1008,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>S28</t>
+          <t>S27</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>PYUSD raw (ALM idle — $677M as of 2026-04)</t>
+          <t>USDT raw (ALM idle — $442M as of 2026-04)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1025,40 +1027,40 @@
         </is>
       </c>
       <c r="E5" s="6" t="n">
-        <v>677151123.07819</v>
+        <v>483436565.922284</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>262428227.923162</v>
+        <v>608678684.51526</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>-414722895.155028</v>
+        <v>125242118.592976</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>3091580</v>
+        <v>-194444.4444439532</v>
       </c>
       <c r="I5" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>3091580</v>
+        <v>-194444.4444439532</v>
       </c>
       <c r="K5" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L5" s="6" t="n">
-        <v>615465268.6039779</v>
+        <v>539754938.8825277</v>
       </c>
       <c r="M5" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>1017458.107638799</v>
+        <v>1183578.826270314</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>1017458.107638799</v>
+        <v>1183578.826270314</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>2074121.892361201</v>
+        <v>-1378023.270714268</v>
       </c>
       <c r="Q5" s="6" t="n">
         <v>0</v>
@@ -1071,12 +1073,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>S56</t>
+          <t>S4</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Spark Savings V2 — spUSDC vault</t>
+          <t>Spark DAI (SparkLend spToken)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1086,127 +1088,131 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E6" s="6" t="n">
-        <v>573332157.534611</v>
+        <v>266184835.4745756</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>303545287.192935</v>
+        <v>266960907.7112744</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>-269786870.341676</v>
+        <v>776072.2366988341</v>
       </c>
       <c r="H6" s="6" t="n">
-        <v>-2077933.247665395</v>
+        <v>559452.9392412193</v>
       </c>
       <c r="I6" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J6" s="6" t="n">
-        <v>-2077933.247665395</v>
+        <v>559452.9392412193</v>
       </c>
       <c r="K6" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L6" s="6" t="n">
-        <v>573332157.534611</v>
+        <v>179549416.5672932</v>
       </c>
       <c r="M6" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N6" s="6" t="n">
-        <v>947805.6387759986</v>
+        <v>393717.3565437027</v>
       </c>
       <c r="O6" s="6" t="n">
-        <v>947805.6387759986</v>
+        <v>393717.3565437027</v>
       </c>
       <c r="P6" s="6" t="n">
-        <v>-3025738.886441393</v>
+        <v>165735.5826975166</v>
       </c>
       <c r="Q6" s="6" t="n">
-        <v>0</v>
+        <v>86642406.62655522</v>
       </c>
       <c r="R6" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="S6" t="inlineStr"/>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>(avg excl. lending_idle)</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>S27</t>
+          <t>S43</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>USDT raw (ALM idle — $442M as of 2026-04)</t>
+          <t>Savings USDS / sUSDS proxy (Arbitrum — POL)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>ethereum</t>
+          <t>arbitrum</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E7" s="6" t="n">
-        <v>483436565.922284</v>
+        <v>143328568.5311704</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>608678684.51526</v>
+        <v>143764611.5800855</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>125242118.592976</v>
+        <v>436043.0489150246</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>-194444.4444439532</v>
+        <v>0</v>
       </c>
       <c r="I7" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J7" s="6" t="n">
-        <v>-194444.4444439532</v>
+        <v>0</v>
       </c>
       <c r="K7" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L7" s="6" t="n">
-        <v>539754938.8825277</v>
+        <v>143328568.5311704</v>
       </c>
       <c r="M7" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N7" s="6" t="n">
-        <v>892297.3670793462</v>
+        <v>314291.9993735298</v>
       </c>
       <c r="O7" s="6" t="n">
-        <v>892297.3670793462</v>
+        <v>277827.1855317322</v>
       </c>
       <c r="P7" s="6" t="n">
-        <v>-1086741.811523299</v>
+        <v>-314291.9993735298</v>
       </c>
       <c r="Q7" s="6" t="n">
         <v>0</v>
       </c>
       <c r="R7" s="6" t="n">
-        <v>0</v>
+        <v>36464.81384179761</v>
       </c>
       <c r="S7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>S4</t>
+          <t>S14</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Spark DAI (SparkLend spToken)</t>
+          <t>Maple syrupUSDC (ERC-4626)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1216,131 +1222,127 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E8" s="6" t="n">
-        <v>266184835.4745756</v>
+        <v>105306162.1077363</v>
       </c>
       <c r="F8" s="6" t="n">
-        <v>266960907.7112744</v>
+        <v>105300451.2530954</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>776072.2366988341</v>
+        <v>-5710.854640941099</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>559452.9392412193</v>
+        <v>423530.6085832017</v>
       </c>
       <c r="I8" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J8" s="6" t="n">
-        <v>559452.9392412193</v>
+        <v>423530.6085832017</v>
       </c>
       <c r="K8" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L8" s="6" t="n">
-        <v>179549416.5672932</v>
+        <v>105079212.3991508</v>
       </c>
       <c r="M8" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N8" s="6" t="n">
-        <v>296822.6136018681</v>
+        <v>230418.5138801736</v>
       </c>
       <c r="O8" s="6" t="n">
-        <v>296822.6136018681</v>
+        <v>230418.5138801736</v>
       </c>
       <c r="P8" s="6" t="n">
-        <v>262630.3256393512</v>
+        <v>193112.0947030281</v>
       </c>
       <c r="Q8" s="6" t="n">
-        <v>86642406.62655522</v>
+        <v>0</v>
       </c>
       <c r="R8" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>(avg excl. lending_idle)</t>
-        </is>
-      </c>
+      <c r="S8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>S43</t>
+          <t>S5</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Savings USDS / sUSDS proxy (Arbitrum — POL)</t>
+          <t>Spark PYUSD (SparkLend spToken)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>arbitrum</t>
+          <t>ethereum</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E9" s="6" t="n">
-        <v>143328568.5311704</v>
+        <v>100001095.915921</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>143764611.5800855</v>
+        <v>100000628.579333</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>436043.0489150246</v>
+        <v>-467.336588</v>
       </c>
       <c r="H9" s="6" t="n">
-        <v>0</v>
+        <v>29003.9707</v>
       </c>
       <c r="I9" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J9" s="6" t="n">
-        <v>0</v>
+        <v>29003.9707</v>
       </c>
       <c r="K9" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L9" s="6" t="n">
-        <v>143328568.5311704</v>
+        <v>100000145.2285891</v>
       </c>
       <c r="M9" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N9" s="6" t="n">
-        <v>236944.0186918778</v>
+        <v>219281.0959016976</v>
       </c>
       <c r="O9" s="6" t="n">
-        <v>200479.2048500802</v>
+        <v>219281.0959016976</v>
       </c>
       <c r="P9" s="6" t="n">
-        <v>-236944.0186918778</v>
+        <v>-190277.1252016976</v>
       </c>
       <c r="Q9" s="6" t="n">
         <v>0</v>
       </c>
       <c r="R9" s="6" t="n">
-        <v>36464.81384179761</v>
+        <v>0</v>
       </c>
       <c r="S9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>S14</t>
+          <t>S25</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Maple syrupUSDC (ERC-4626)</t>
+          <t>Spark.fi PYUSD Reserve Curve (PYUSD/USDS)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1350,44 +1352,44 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>F</t>
         </is>
       </c>
       <c r="E10" s="6" t="n">
-        <v>105306162.1077363</v>
+        <v>99998676.75316638</v>
       </c>
       <c r="F10" s="6" t="n">
-        <v>105300451.2530954</v>
+        <v>99999260.90933624</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>-5710.854640941099</v>
+        <v>584.1561698611263</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>423530.6085832017</v>
+        <v>6385.883871640342</v>
       </c>
       <c r="I10" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J10" s="6" t="n">
-        <v>423530.6085832017</v>
+        <v>6385.883871640342</v>
       </c>
       <c r="K10" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L10" s="6" t="n">
-        <v>105079212.3991508</v>
+        <v>99998489.60065988</v>
       </c>
       <c r="M10" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N10" s="6" t="n">
-        <v>173711.9900239393</v>
+        <v>219277.4654279028</v>
       </c>
       <c r="O10" s="6" t="n">
-        <v>173711.9900239393</v>
+        <v>219277.4654279028</v>
       </c>
       <c r="P10" s="6" t="n">
-        <v>249818.6185592623</v>
+        <v>-212891.5815562624</v>
       </c>
       <c r="Q10" s="6" t="n">
         <v>0</v>
@@ -1400,77 +1402,77 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>S5</t>
+          <t>S47</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Spark PYUSD (SparkLend spToken)</t>
+          <t>Savings USDS / sUSDS proxy (Optimism — POL)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>ethereum</t>
+          <t>optimism</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E11" s="6" t="n">
-        <v>100001095.915921</v>
+        <v>102040993.0313656</v>
       </c>
       <c r="F11" s="6" t="n">
-        <v>100000628.579333</v>
+        <v>102351428.4607548</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>-467.336588</v>
+        <v>310435.429389201</v>
       </c>
       <c r="H11" s="6" t="n">
-        <v>29003.9707</v>
+        <v>0</v>
       </c>
       <c r="I11" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J11" s="6" t="n">
-        <v>29003.9707</v>
+        <v>0</v>
       </c>
       <c r="K11" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L11" s="6" t="n">
-        <v>100000145.2285891</v>
+        <v>102040993.0313656</v>
       </c>
       <c r="M11" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N11" s="6" t="n">
-        <v>165315.5161113631</v>
+        <v>223756.2828300607</v>
       </c>
       <c r="O11" s="6" t="n">
-        <v>165315.5161113631</v>
+        <v>197795.6118120444</v>
       </c>
       <c r="P11" s="6" t="n">
-        <v>-136311.5454113631</v>
+        <v>-223756.2828300607</v>
       </c>
       <c r="Q11" s="6" t="n">
         <v>0</v>
       </c>
       <c r="R11" s="6" t="n">
-        <v>0</v>
+        <v>25960.67101801626</v>
       </c>
       <c r="S11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>S25</t>
+          <t>S11</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Spark.fi PYUSD Reserve Curve (PYUSD/USDS)</t>
+          <t>Spark Blue Chip USDT Vault (Morpho V2)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1480,44 +1482,44 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E12" s="6" t="n">
-        <v>99998676.75316638</v>
+        <v>51710579.95350124</v>
       </c>
       <c r="F12" s="6" t="n">
-        <v>99999260.90933624</v>
+        <v>71943502.10038626</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>584.1561698611263</v>
+        <v>20232922.14688502</v>
       </c>
       <c r="H12" s="6" t="n">
-        <v>6385.883871640342</v>
+        <v>217269.3964465584</v>
       </c>
       <c r="I12" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J12" s="6" t="n">
-        <v>6385.883871640342</v>
+        <v>217269.3964465584</v>
       </c>
       <c r="K12" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L12" s="6" t="n">
-        <v>99998489.60065988</v>
+        <v>89619946.74579927</v>
       </c>
       <c r="M12" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N12" s="6" t="n">
-        <v>165312.7791054819</v>
+        <v>196519.3159684765</v>
       </c>
       <c r="O12" s="6" t="n">
-        <v>165312.7791054819</v>
+        <v>196519.3159684765</v>
       </c>
       <c r="P12" s="6" t="n">
-        <v>-158926.8952338415</v>
+        <v>20750.08047808185</v>
       </c>
       <c r="Q12" s="6" t="n">
         <v>0</v>
@@ -1530,17 +1532,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>S11</t>
+          <t>S37</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Spark Blue Chip USDT Vault (Morpho V2)</t>
+          <t>Savings USDS / sUSDS proxy (Base — POL)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>ethereum</t>
+          <t>base</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1549,143 +1551,139 @@
         </is>
       </c>
       <c r="E13" s="6" t="n">
-        <v>51710579.95350124</v>
+        <v>75772907.26348835</v>
       </c>
       <c r="F13" s="6" t="n">
-        <v>71943502.10038626</v>
+        <v>76003428.29531698</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>20232922.14688502</v>
+        <v>230521.0318286367</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>217269.3964465584</v>
+        <v>0</v>
       </c>
       <c r="I13" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J13" s="6" t="n">
-        <v>217269.3964465584</v>
+        <v>0</v>
       </c>
       <c r="K13" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L13" s="6" t="n">
-        <v>89619946.74579927</v>
+        <v>75772907.26348835</v>
       </c>
       <c r="M13" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N13" s="6" t="n">
-        <v>148155.4623374592</v>
+        <v>166155.4201387819</v>
       </c>
       <c r="O13" s="6" t="n">
-        <v>148155.4623374592</v>
+        <v>146877.7214501635</v>
       </c>
       <c r="P13" s="6" t="n">
-        <v>69113.93410909919</v>
+        <v>-166155.4201387819</v>
       </c>
       <c r="Q13" s="6" t="n">
         <v>0</v>
       </c>
       <c r="R13" s="6" t="n">
-        <v>0</v>
+        <v>19277.6986886184</v>
       </c>
       <c r="S13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>S47</t>
+          <t>S1</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Savings USDS / sUSDS proxy (Optimism — POL)</t>
+          <t>Spark USDS (SparkLend spToken)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>optimism</t>
+          <t>ethereum</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E14" s="6" t="n">
-        <v>102040993.0313656</v>
+        <v>147862782.1336161</v>
       </c>
       <c r="F14" s="6" t="n">
-        <v>102351428.4607548</v>
+        <v>550178045.362034</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>310435.429389201</v>
+        <v>402315263.2284179</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>0</v>
+        <v>294091.516876444</v>
       </c>
       <c r="I14" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J14" s="6" t="n">
-        <v>0</v>
+        <v>294091.516876444</v>
       </c>
       <c r="K14" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L14" s="6" t="n">
-        <v>102040993.0313656</v>
+        <v>57731388.11709616</v>
       </c>
       <c r="M14" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N14" s="6" t="n">
-        <v>168689.3492898001</v>
+        <v>126593.836691988</v>
       </c>
       <c r="O14" s="6" t="n">
-        <v>142728.6782717838</v>
+        <v>126593.836691988</v>
       </c>
       <c r="P14" s="6" t="n">
-        <v>-168689.3492898001</v>
+        <v>167497.6801844561</v>
       </c>
       <c r="Q14" s="6" t="n">
-        <v>0</v>
+        <v>103099818.9104406</v>
       </c>
       <c r="R14" s="6" t="n">
-        <v>25960.67101801626</v>
-      </c>
-      <c r="S14" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>(avg excl. lending_idle)</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>S37</t>
+          <t>SPREAD</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Savings USDS / sUSDS proxy (Base — POL)</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>base</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
+          <t>30bps sUSDS spread (Curve LP + PSM3) — Sky Revenue reduction</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr"/>
       <c r="E15" s="6" t="n">
-        <v>75772907.26348835</v>
+        <v>0</v>
       </c>
       <c r="F15" s="6" t="n">
-        <v>76003428.29531698</v>
+        <v>0</v>
       </c>
       <c r="G15" s="6" t="n">
-        <v>230521.0318286367</v>
+        <v>0</v>
       </c>
       <c r="H15" s="6" t="n">
         <v>0</v>
@@ -1700,52 +1698,64 @@
         <v>0</v>
       </c>
       <c r="L15" s="6" t="n">
-        <v>75772907.26348835</v>
+        <v>0</v>
       </c>
       <c r="M15" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N15" s="6" t="n">
-        <v>125264.1907958033</v>
+        <v>0</v>
       </c>
       <c r="O15" s="6" t="n">
-        <v>105986.4921071849</v>
+        <v>-102957.2966175266</v>
       </c>
       <c r="P15" s="6" t="n">
-        <v>-125264.1907958033</v>
+        <v>0</v>
       </c>
       <c r="Q15" s="6" t="n">
         <v>0</v>
       </c>
       <c r="R15" s="6" t="n">
-        <v>19277.6986886184</v>
-      </c>
-      <c r="S15" t="inlineStr"/>
+        <v>102957.2966175266</v>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>sky-revenue reduction (no CoF; computed outside venue loop)</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>SPREAD</t>
+          <t>S24</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>30bps sUSDS spread (Curve LP + PSM3) — Sky Revenue reduction</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr"/>
+          <t>Spark.fi USDT Reserve Curve (sUSDS/USDT)</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>ethereum</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
       <c r="E16" s="6" t="n">
-        <v>0</v>
+        <v>50002415.26289953</v>
       </c>
       <c r="F16" s="6" t="n">
-        <v>0</v>
+        <v>48750265.64989898</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>0</v>
+        <v>-1252149.613000547</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>0</v>
+        <v>74156.06084450937</v>
       </c>
       <c r="I16" s="6" t="n">
         <v>0</v>
@@ -1754,10 +1764,10 @@
         <v>0</v>
       </c>
       <c r="K16" s="6" t="n">
-        <v>0</v>
+        <v>74156.06084450937</v>
       </c>
       <c r="L16" s="6" t="n">
-        <v>0</v>
+        <v>49959631.20890453</v>
       </c>
       <c r="M16" s="7" t="n">
         <v>0</v>
@@ -1766,32 +1776,32 @@
         <v>0</v>
       </c>
       <c r="O16" s="6" t="n">
-        <v>-102957.2966175266</v>
+        <v>74156.06084450937</v>
       </c>
       <c r="P16" s="6" t="n">
         <v>0</v>
       </c>
       <c r="Q16" s="6" t="n">
-        <v>0</v>
+        <v>49959631.20890453</v>
       </c>
       <c r="R16" s="6" t="n">
-        <v>102957.2966175266</v>
+        <v>0</v>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>sky-revenue reduction (no CoF; computed outside venue loop)</t>
+          <t>SDE (fixed)</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>S1</t>
+          <t>S15</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Spark USDS (SparkLend spToken)</t>
+          <t>Maple syrupUSDT (ERC-4626)</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1801,66 +1811,62 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E17" s="6" t="n">
-        <v>147862782.1336161</v>
+        <v>76904851.98939763</v>
       </c>
       <c r="F17" s="6" t="n">
-        <v>550178045.362034</v>
+        <v>0</v>
       </c>
       <c r="G17" s="6" t="n">
-        <v>402315263.2284179</v>
+        <v>-76904851.98939763</v>
       </c>
       <c r="H17" s="6" t="n">
-        <v>294091.516876444</v>
+        <v>119641.6179259726</v>
       </c>
       <c r="I17" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J17" s="6" t="n">
-        <v>294091.516876444</v>
+        <v>119641.6179259726</v>
       </c>
       <c r="K17" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L17" s="6" t="n">
-        <v>57731388.11709616</v>
+        <v>29672997.14110577</v>
       </c>
       <c r="M17" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N17" s="6" t="n">
-        <v>95438.8036196037</v>
+        <v>65067.17882175036</v>
       </c>
       <c r="O17" s="6" t="n">
-        <v>95438.8036196037</v>
+        <v>65067.17882175036</v>
       </c>
       <c r="P17" s="6" t="n">
-        <v>198652.7132568404</v>
+        <v>54574.43910422226</v>
       </c>
       <c r="Q17" s="6" t="n">
-        <v>103099818.9104406</v>
+        <v>0</v>
       </c>
       <c r="R17" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="S17" t="inlineStr">
-        <is>
-          <t>(avg excl. lending_idle)</t>
-        </is>
-      </c>
+      <c r="S17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>S24</t>
+          <t>S18</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Spark.fi USDT Reserve Curve (sUSDS/USDT)</t>
+          <t>Arkis Spark Prime USDC 1 (ERC-4626)</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1870,113 +1876,109 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E18" s="6" t="n">
-        <v>50002415.26289953</v>
+        <v>0.28330096818</v>
       </c>
       <c r="F18" s="6" t="n">
-        <v>48750265.64989898</v>
+        <v>15021342.65332295</v>
       </c>
       <c r="G18" s="6" t="n">
-        <v>-1252149.613000547</v>
+        <v>15021342.37002198</v>
       </c>
       <c r="H18" s="6" t="n">
-        <v>74156.06084450937</v>
+        <v>21701.47150269761</v>
       </c>
       <c r="I18" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J18" s="6" t="n">
-        <v>0</v>
+        <v>21701.47150269761</v>
       </c>
       <c r="K18" s="6" t="n">
-        <v>74156.06084450937</v>
+        <v>0</v>
       </c>
       <c r="L18" s="6" t="n">
-        <v>49959631.20890453</v>
+        <v>9516094.162770383</v>
       </c>
       <c r="M18" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N18" s="6" t="n">
-        <v>0</v>
+        <v>20866.96526236113</v>
       </c>
       <c r="O18" s="6" t="n">
-        <v>74156.06084450937</v>
+        <v>20866.96526236113</v>
       </c>
       <c r="P18" s="6" t="n">
-        <v>0</v>
+        <v>834.506240336483</v>
       </c>
       <c r="Q18" s="6" t="n">
-        <v>49959631.20890453</v>
+        <v>0</v>
       </c>
       <c r="R18" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="S18" t="inlineStr">
-        <is>
-          <t>SDE (fixed)</t>
-        </is>
-      </c>
+      <c r="S18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>S60</t>
+          <t>S2</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Spark Savings V2 — spUSDC vault (Avalanche-C, CREATE2 same address)</t>
+          <t>Spark USDC (SparkLend spToken)</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>avalanche_c</t>
+          <t>ethereum</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E19" s="6" t="n">
-        <v>37138817.432463</v>
+        <v>9229822.108306</v>
       </c>
       <c r="F19" s="6" t="n">
-        <v>25647247.422478</v>
+        <v>12183497.214187</v>
       </c>
       <c r="G19" s="6" t="n">
-        <v>-11491570.009985</v>
+        <v>2953675.105881</v>
       </c>
       <c r="H19" s="6" t="n">
-        <v>-94676.37115954701</v>
+        <v>32502.903353</v>
       </c>
       <c r="I19" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J19" s="6" t="n">
-        <v>-94676.37115954701</v>
+        <v>32502.903353</v>
       </c>
       <c r="K19" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L19" s="6" t="n">
-        <v>37138817.432463</v>
+        <v>9324053.469677871</v>
       </c>
       <c r="M19" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N19" s="6" t="n">
-        <v>61396.1385513873</v>
+        <v>20445.85693754033</v>
       </c>
       <c r="O19" s="6" t="n">
-        <v>61396.1385513873</v>
+        <v>20445.85693754033</v>
       </c>
       <c r="P19" s="6" t="n">
-        <v>-156072.5097109343</v>
+        <v>12057.04641545967</v>
       </c>
       <c r="Q19" s="6" t="n">
         <v>0</v>
@@ -1989,59 +1991,59 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>S15</t>
+          <t>S39</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Maple syrupUSDT (ERC-4626)</t>
+          <t>USDC raw (Base — ALM idle)</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>ethereum</t>
+          <t>base</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E20" s="6" t="n">
-        <v>76904851.98939763</v>
+        <v>5000000</v>
       </c>
       <c r="F20" s="6" t="n">
-        <v>0</v>
+        <v>4997576.708614</v>
       </c>
       <c r="G20" s="6" t="n">
-        <v>-76904851.98939763</v>
+        <v>-2423.291386</v>
       </c>
       <c r="H20" s="6" t="n">
-        <v>119641.6179259726</v>
+        <v>2.228968e-09</v>
       </c>
       <c r="I20" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J20" s="6" t="n">
-        <v>119641.6179259726</v>
+        <v>2.228968e-09</v>
       </c>
       <c r="K20" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L20" s="6" t="n">
-        <v>29672997.14110577</v>
+        <v>4999001.686505451</v>
       </c>
       <c r="M20" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N20" s="6" t="n">
-        <v>49053.99712910109</v>
+        <v>10961.84976257375</v>
       </c>
       <c r="O20" s="6" t="n">
-        <v>49053.99712910109</v>
+        <v>10961.84976257375</v>
       </c>
       <c r="P20" s="6" t="n">
-        <v>70587.62079687153</v>
+        <v>-10961.84976257152</v>
       </c>
       <c r="Q20" s="6" t="n">
         <v>0</v>
@@ -2054,59 +2056,59 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>S18</t>
+          <t>S49</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Arkis Spark Prime USDC 1 (ERC-4626)</t>
+          <t>USDC raw (Optimism — ALM idle)</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>ethereum</t>
+          <t>optimism</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E21" s="6" t="n">
-        <v>0.28330096818</v>
+        <v>5000000</v>
       </c>
       <c r="F21" s="6" t="n">
-        <v>15021342.65332295</v>
+        <v>5019997.4</v>
       </c>
       <c r="G21" s="6" t="n">
-        <v>15021342.37002198</v>
+        <v>19997.4</v>
       </c>
       <c r="H21" s="6" t="n">
-        <v>21701.47150269761</v>
+        <v>1.8405064066e-10</v>
       </c>
       <c r="I21" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J21" s="6" t="n">
-        <v>21701.47150269761</v>
+        <v>1.8405064066e-10</v>
       </c>
       <c r="K21" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L21" s="6" t="n">
-        <v>9516094.162770383</v>
+        <v>4998671.605324483</v>
       </c>
       <c r="M21" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N21" s="6" t="n">
-        <v>15731.55733210839</v>
+        <v>10961.12595799393</v>
       </c>
       <c r="O21" s="6" t="n">
-        <v>15731.55733210839</v>
+        <v>10961.12595799393</v>
       </c>
       <c r="P21" s="6" t="n">
-        <v>5969.914170589217</v>
+        <v>-10961.12595799374</v>
       </c>
       <c r="Q21" s="6" t="n">
         <v>0</v>
@@ -2119,59 +2121,59 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>S53</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Spark USDC (SparkLend spToken)</t>
+          <t>USDC raw (Unichain — ALM idle)</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>ethereum</t>
+          <t>unichain</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E22" s="6" t="n">
-        <v>9229822.108306</v>
+        <v>4996314.282982</v>
       </c>
       <c r="F22" s="6" t="n">
-        <v>12183497.214187</v>
+        <v>4992819.462732</v>
       </c>
       <c r="G22" s="6" t="n">
-        <v>2953675.105881</v>
+        <v>-3494.82025</v>
       </c>
       <c r="H22" s="6" t="n">
-        <v>32502.903353</v>
+        <v>0</v>
       </c>
       <c r="I22" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J22" s="6" t="n">
-        <v>32502.903353</v>
+        <v>0</v>
       </c>
       <c r="K22" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L22" s="6" t="n">
-        <v>9324053.469677871</v>
+        <v>4997744.737919419</v>
       </c>
       <c r="M22" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N22" s="6" t="n">
-        <v>15414.08473023965</v>
+        <v>10959.09351594223</v>
       </c>
       <c r="O22" s="6" t="n">
-        <v>15414.08473023965</v>
+        <v>10959.09351594223</v>
       </c>
       <c r="P22" s="6" t="n">
-        <v>17088.81862276035</v>
+        <v>-10959.09351594223</v>
       </c>
       <c r="Q22" s="6" t="n">
         <v>0</v>
@@ -2184,17 +2186,17 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>S39</t>
+          <t>S45</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>USDC raw (Base — ALM idle)</t>
+          <t>USDC raw (Arbitrum — ALM idle)</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>base</t>
+          <t>arbitrum</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -2203,40 +2205,40 @@
         </is>
       </c>
       <c r="E23" s="6" t="n">
-        <v>5000000</v>
+        <v>5009602.263622</v>
       </c>
       <c r="F23" s="6" t="n">
-        <v>4997576.708614</v>
+        <v>4975417.167355</v>
       </c>
       <c r="G23" s="6" t="n">
-        <v>-2423.291386</v>
+        <v>-34185.096267</v>
       </c>
       <c r="H23" s="6" t="n">
-        <v>2.228968e-09</v>
+        <v>4.7e-10</v>
       </c>
       <c r="I23" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J23" s="6" t="n">
-        <v>2.228968e-09</v>
+        <v>4.7e-10</v>
       </c>
       <c r="K23" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L23" s="6" t="n">
-        <v>4999001.686505451</v>
+        <v>4954536.773106677</v>
       </c>
       <c r="M23" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N23" s="6" t="n">
-        <v>8264.113436606884</v>
+        <v>10864.34675478342</v>
       </c>
       <c r="O23" s="6" t="n">
-        <v>8264.113436606884</v>
+        <v>10864.34675478342</v>
       </c>
       <c r="P23" s="6" t="n">
-        <v>-8264.113436604654</v>
+        <v>-10864.34675478295</v>
       </c>
       <c r="Q23" s="6" t="n">
         <v>0</v>
@@ -2249,59 +2251,59 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>S49</t>
+          <t>S10</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>USDC raw (Optimism — ALM idle)</t>
+          <t>Spark Blue Chip USDC Vault (Morpho)</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>optimism</t>
+          <t>ethereum</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E24" s="6" t="n">
-        <v>5000000</v>
+        <v>704090.8045421393</v>
       </c>
       <c r="F24" s="6" t="n">
-        <v>5019997.4</v>
+        <v>3501087.141508509</v>
       </c>
       <c r="G24" s="6" t="n">
-        <v>19997.4</v>
+        <v>2796996.33696637</v>
       </c>
       <c r="H24" s="6" t="n">
-        <v>1.8405064066e-10</v>
+        <v>609955.0966986277</v>
       </c>
       <c r="I24" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J24" s="6" t="n">
-        <v>1.8405064066e-10</v>
+        <v>609955.0966986277</v>
       </c>
       <c r="K24" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L24" s="6" t="n">
-        <v>4998671.605324483</v>
+        <v>1472511.375313347</v>
       </c>
       <c r="M24" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N24" s="6" t="n">
-        <v>8263.567761991457</v>
+        <v>3228.934391728406</v>
       </c>
       <c r="O24" s="6" t="n">
-        <v>8263.567761991457</v>
+        <v>3228.934391728406</v>
       </c>
       <c r="P24" s="6" t="n">
-        <v>-8263.567761991273</v>
+        <v>606726.1623068993</v>
       </c>
       <c r="Q24" s="6" t="n">
         <v>0</v>
@@ -2314,12 +2316,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>S53</t>
+          <t>S51</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>USDC raw (Unichain — ALM idle)</t>
+          <t>Savings USDS / sUSDS proxy (Unichain — POL)</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -2329,17 +2331,17 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E25" s="6" t="n">
-        <v>4996314.282982</v>
+        <v>982408.1850699954</v>
       </c>
       <c r="F25" s="6" t="n">
-        <v>4992819.462732</v>
+        <v>985396.9281006901</v>
       </c>
       <c r="G25" s="6" t="n">
-        <v>-3494.82025</v>
+        <v>2988.743030694792</v>
       </c>
       <c r="H25" s="6" t="n">
         <v>0</v>
@@ -2354,84 +2356,84 @@
         <v>0</v>
       </c>
       <c r="L25" s="6" t="n">
-        <v>4997744.737919419</v>
+        <v>982408.1850699954</v>
       </c>
       <c r="M25" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N25" s="6" t="n">
-        <v>8262.035508582376</v>
+        <v>2154.232305888279</v>
       </c>
       <c r="O25" s="6" t="n">
-        <v>8262.035508582376</v>
+        <v>1904.293776868191</v>
       </c>
       <c r="P25" s="6" t="n">
-        <v>-8262.035508582376</v>
+        <v>-2154.232305888279</v>
       </c>
       <c r="Q25" s="6" t="n">
         <v>0</v>
       </c>
       <c r="R25" s="6" t="n">
-        <v>0</v>
+        <v>249.9385290200882</v>
       </c>
       <c r="S25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>S45</t>
+          <t>S12</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>USDC raw (Arbitrum — ALM idle)</t>
+          <t>Spark DAI Vault (Morpho)</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>arbitrum</t>
+          <t>ethereum</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E26" s="6" t="n">
-        <v>5009602.263622</v>
+        <v>458.5728307677575</v>
       </c>
       <c r="F26" s="6" t="n">
-        <v>4975417.167355</v>
+        <v>539.8728953809741</v>
       </c>
       <c r="G26" s="6" t="n">
-        <v>-34185.096267</v>
+        <v>81.30006461321658</v>
       </c>
       <c r="H26" s="6" t="n">
-        <v>4.7e-10</v>
+        <v>76.33046551920575</v>
       </c>
       <c r="I26" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J26" s="6" t="n">
-        <v>4.7e-10</v>
+        <v>76.33046551920575</v>
       </c>
       <c r="K26" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L26" s="6" t="n">
-        <v>4954536.773106677</v>
+        <v>462.161691889013</v>
       </c>
       <c r="M26" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N26" s="6" t="n">
-        <v>8190.606142286837</v>
+        <v>1.013431751019421</v>
       </c>
       <c r="O26" s="6" t="n">
-        <v>8190.606142286837</v>
+        <v>1.013431751019421</v>
       </c>
       <c r="P26" s="6" t="n">
-        <v>-8190.606142286368</v>
+        <v>75.31703376818632</v>
       </c>
       <c r="Q26" s="6" t="n">
         <v>0</v>
@@ -2444,17 +2446,17 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>S10</t>
+          <t>S34</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Spark Blue Chip USDC Vault (Morpho)</t>
+          <t>Spark USDC Vault (Morpho, Base)</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>ethereum</t>
+          <t>base</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -2463,40 +2465,40 @@
         </is>
       </c>
       <c r="E27" s="6" t="n">
-        <v>704090.8045421393</v>
+        <v>224.7175624853434</v>
       </c>
       <c r="F27" s="6" t="n">
-        <v>3501087.141508509</v>
+        <v>424.9110349025811</v>
       </c>
       <c r="G27" s="6" t="n">
-        <v>2796996.33696637</v>
+        <v>200.1934724172377</v>
       </c>
       <c r="H27" s="6" t="n">
-        <v>609955.0966986277</v>
+        <v>1.161345275337778</v>
       </c>
       <c r="I27" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J27" s="6" t="n">
-        <v>609955.0966986277</v>
+        <v>1.161345275337778</v>
       </c>
       <c r="K27" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L27" s="6" t="n">
-        <v>1472511.375313347</v>
+        <v>368.0420981576889</v>
       </c>
       <c r="M27" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N27" s="6" t="n">
-        <v>2434.286244618223</v>
+        <v>0.807045574158881</v>
       </c>
       <c r="O27" s="6" t="n">
-        <v>2434.286244618223</v>
+        <v>0.807045574158881</v>
       </c>
       <c r="P27" s="6" t="n">
-        <v>607520.8104540096</v>
+        <v>0.3542997011788971</v>
       </c>
       <c r="Q27" s="6" t="n">
         <v>0</v>
@@ -2509,59 +2511,59 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>S59</t>
+          <t>S36</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Spark Savings V2 — spPYUSD vault</t>
+          <t>Fluid Savings USDS (fsUSDS, Base)</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>ethereum</t>
+          <t>base</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>S2</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E28" s="6" t="n">
-        <v>1066559.875133</v>
+        <v>283.8972488542868</v>
       </c>
       <c r="F28" s="6" t="n">
-        <v>773533.783718</v>
+        <v>283.8972488542868</v>
       </c>
       <c r="G28" s="6" t="n">
-        <v>-293026.091415</v>
+        <v>0</v>
       </c>
       <c r="H28" s="6" t="n">
-        <v>-2640.43740244277</v>
+        <v>0</v>
       </c>
       <c r="I28" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J28" s="6" t="n">
-        <v>-2640.43740244277</v>
+        <v>0</v>
       </c>
       <c r="K28" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L28" s="6" t="n">
-        <v>1066559.875133</v>
+        <v>283.8972488542868</v>
       </c>
       <c r="M28" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N28" s="6" t="n">
-        <v>1763.186401562094</v>
+        <v>0.6225320944278722</v>
       </c>
       <c r="O28" s="6" t="n">
-        <v>1763.186401562094</v>
+        <v>0.6225320944278722</v>
       </c>
       <c r="P28" s="6" t="n">
-        <v>-4403.623804004864</v>
+        <v>-0.6225320944278722</v>
       </c>
       <c r="Q28" s="6" t="n">
         <v>0</v>
@@ -2574,77 +2576,77 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>S51</t>
+          <t>S55</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Savings USDS / sUSDS proxy (Unichain — POL)</t>
+          <t>USDC raw (Avalanche-C — ALM idle)</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>unichain</t>
+          <t>avalanche_c</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E29" s="6" t="n">
-        <v>982408.1850699954</v>
+        <v>2500.221225</v>
       </c>
       <c r="F29" s="6" t="n">
-        <v>985396.9281006901</v>
+        <v>0</v>
       </c>
       <c r="G29" s="6" t="n">
-        <v>2988.743030694792</v>
+        <v>-2500.221225</v>
       </c>
       <c r="H29" s="6" t="n">
-        <v>0</v>
+        <v>-3.30458807350886e-10</v>
       </c>
       <c r="I29" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J29" s="6" t="n">
-        <v>0</v>
+        <v>-3.30458807350886e-10</v>
       </c>
       <c r="K29" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L29" s="6" t="n">
-        <v>982408.1850699954</v>
+        <v>115.3103732260555</v>
       </c>
       <c r="M29" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N29" s="6" t="n">
-        <v>1624.070802853624</v>
+        <v>0.2528534828828865</v>
       </c>
       <c r="O29" s="6" t="n">
-        <v>1374.132273833536</v>
+        <v>0.2528534828828865</v>
       </c>
       <c r="P29" s="6" t="n">
-        <v>-1624.070802853624</v>
+        <v>-0.2528534832133453</v>
       </c>
       <c r="Q29" s="6" t="n">
         <v>0</v>
       </c>
       <c r="R29" s="6" t="n">
-        <v>249.9385290200882</v>
+        <v>0</v>
       </c>
       <c r="S29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>S12</t>
+          <t>S16</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Spark DAI Vault (Morpho)</t>
+          <t>Ethena Staked USDe (sUSDe)</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2658,40 +2660,40 @@
         </is>
       </c>
       <c r="E30" s="6" t="n">
-        <v>458.5728307677575</v>
+        <v>99.50129408753318</v>
       </c>
       <c r="F30" s="6" t="n">
-        <v>539.8728953809741</v>
+        <v>99.81305763596731</v>
       </c>
       <c r="G30" s="6" t="n">
-        <v>81.30006461321658</v>
+        <v>0.3117635484341261</v>
       </c>
       <c r="H30" s="6" t="n">
-        <v>76.33046551920575</v>
+        <v>0.3117635484341261</v>
       </c>
       <c r="I30" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J30" s="6" t="n">
-        <v>76.33046551920575</v>
+        <v>0.3117635484341261</v>
       </c>
       <c r="K30" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L30" s="6" t="n">
-        <v>462.161691889013</v>
+        <v>99.50129408753318</v>
       </c>
       <c r="M30" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N30" s="6" t="n">
-        <v>0.7640238766342328</v>
+        <v>0.2181872112413053</v>
       </c>
       <c r="O30" s="6" t="n">
-        <v>0.7640238766342328</v>
+        <v>0.2181872112413053</v>
       </c>
       <c r="P30" s="6" t="n">
-        <v>75.5664416425715</v>
+        <v>0.09357633719282084</v>
       </c>
       <c r="Q30" s="6" t="n">
         <v>0</v>
@@ -2704,17 +2706,17 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>S34</t>
+          <t>S13</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Spark USDC Vault (Morpho, Base)</t>
+          <t>Spark USDS Vault (Morpho)</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>base</t>
+          <t>ethereum</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -2723,40 +2725,40 @@
         </is>
       </c>
       <c r="E31" s="6" t="n">
-        <v>224.7175624853434</v>
+        <v>21.90660666972937</v>
       </c>
       <c r="F31" s="6" t="n">
-        <v>424.9110349025811</v>
+        <v>21.90661272343654</v>
       </c>
       <c r="G31" s="6" t="n">
-        <v>200.1934724172377</v>
+        <v>6.053707169991468e-06</v>
       </c>
       <c r="H31" s="6" t="n">
-        <v>1.161345275337778</v>
+        <v>6.053707169991468e-06</v>
       </c>
       <c r="I31" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J31" s="6" t="n">
-        <v>1.161345275337778</v>
+        <v>6.053707169991468e-06</v>
       </c>
       <c r="K31" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L31" s="6" t="n">
-        <v>368.0420981576889</v>
+        <v>21.90660666972937</v>
       </c>
       <c r="M31" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N31" s="6" t="n">
-        <v>0.6084298104624435</v>
+        <v>0.04803697741683239</v>
       </c>
       <c r="O31" s="6" t="n">
-        <v>0.6084298104624435</v>
+        <v>0.04803697741683239</v>
       </c>
       <c r="P31" s="6" t="n">
-        <v>0.5529154648753346</v>
+        <v>-0.04803092370966239</v>
       </c>
       <c r="Q31" s="6" t="n">
         <v>0</v>
@@ -2769,59 +2771,59 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>S36</t>
+          <t>S9</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Fluid Savings USDS (fsUSDS, Base)</t>
+          <t>Aave Ethereum USDT (aToken)</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>base</t>
+          <t>ethereum</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E32" s="6" t="n">
-        <v>283.8972488542868</v>
+        <v>5.897868</v>
       </c>
       <c r="F32" s="6" t="n">
-        <v>283.8972488542868</v>
+        <v>5.913258</v>
       </c>
       <c r="G32" s="6" t="n">
-        <v>0</v>
+        <v>0.01539</v>
       </c>
       <c r="H32" s="6" t="n">
-        <v>0</v>
+        <v>0.01539</v>
       </c>
       <c r="I32" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J32" s="6" t="n">
-        <v>0</v>
+        <v>0.01539</v>
       </c>
       <c r="K32" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L32" s="6" t="n">
-        <v>283.8972488542868</v>
+        <v>5.897868</v>
       </c>
       <c r="M32" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N32" s="6" t="n">
-        <v>0.4693255205745931</v>
+        <v>0.01293289080298069</v>
       </c>
       <c r="O32" s="6" t="n">
-        <v>0.4693255205745931</v>
+        <v>0.01293289080298069</v>
       </c>
       <c r="P32" s="6" t="n">
-        <v>-0.4693255205745931</v>
+        <v>0.002457109197019311</v>
       </c>
       <c r="Q32" s="6" t="n">
         <v>0</v>
@@ -2834,59 +2836,59 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>S55</t>
+          <t>S23</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>USDC raw (Avalanche-C — ALM idle)</t>
+          <t>Anchorage tri-party loan escrow (USDC pass-through, ~$0 balance)</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>avalanche_c</t>
+          <t>ethereum</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E33" s="6" t="n">
-        <v>2500.221225</v>
+        <v>1.545609</v>
       </c>
       <c r="F33" s="6" t="n">
-        <v>0</v>
+        <v>10.015998</v>
       </c>
       <c r="G33" s="6" t="n">
-        <v>-2500.221225</v>
+        <v>8.470389000000001</v>
       </c>
       <c r="H33" s="6" t="n">
-        <v>-3.30458807350886e-10</v>
+        <v>8.470389000000001</v>
       </c>
       <c r="I33" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J33" s="6" t="n">
-        <v>-3.30458807350886e-10</v>
+        <v>8.470389000000001</v>
       </c>
       <c r="K33" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L33" s="6" t="n">
-        <v>115.3103732260555</v>
+        <v>1.545609</v>
       </c>
       <c r="M33" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N33" s="6" t="n">
-        <v>0.1906256617856336</v>
+        <v>0.003389223431433898</v>
       </c>
       <c r="O33" s="6" t="n">
-        <v>0.1906256617856336</v>
+        <v>0.003389223431433898</v>
       </c>
       <c r="P33" s="6" t="n">
-        <v>-0.1906256621160924</v>
+        <v>8.466999776568565</v>
       </c>
       <c r="Q33" s="6" t="n">
         <v>0</v>
@@ -2899,59 +2901,59 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>S16</t>
+          <t>S54</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Ethena Staked USDe (sUSDe)</t>
+          <t>Aave Avalanche USDC (aAvaUSDC)</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>ethereum</t>
+          <t>avalanche_c</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E34" s="6" t="n">
-        <v>99.50129408753318</v>
+        <v>0.154431</v>
       </c>
       <c r="F34" s="6" t="n">
-        <v>99.81305763596731</v>
+        <v>0.155165</v>
       </c>
       <c r="G34" s="6" t="n">
-        <v>0.3117635484341261</v>
+        <v>0.000734</v>
       </c>
       <c r="H34" s="6" t="n">
-        <v>0.3117635484341261</v>
+        <v>0.000734</v>
       </c>
       <c r="I34" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J34" s="6" t="n">
-        <v>0.3117635484341261</v>
+        <v>0.000734</v>
       </c>
       <c r="K34" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L34" s="6" t="n">
-        <v>99.50129408753318</v>
+        <v>0.154431</v>
       </c>
       <c r="M34" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N34" s="6" t="n">
-        <v>0.164490838970566</v>
+        <v>0.0003386374974134909</v>
       </c>
       <c r="O34" s="6" t="n">
-        <v>0.164490838970566</v>
+        <v>0.0003386374974134909</v>
       </c>
       <c r="P34" s="6" t="n">
-        <v>0.1472727094635601</v>
+        <v>0.0003953625025865091</v>
       </c>
       <c r="Q34" s="6" t="n">
         <v>0</v>
@@ -2964,12 +2966,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>S13</t>
+          <t>S8</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Spark USDS Vault (Morpho)</t>
+          <t>Aave Ethereum USDC (aToken)</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2979,44 +2981,44 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E35" s="6" t="n">
-        <v>21.90660666972937</v>
+        <v>0.057783</v>
       </c>
       <c r="F35" s="6" t="n">
-        <v>21.90661272343654</v>
+        <v>0.057969</v>
       </c>
       <c r="G35" s="6" t="n">
-        <v>6.053707169991468e-06</v>
+        <v>0.000186</v>
       </c>
       <c r="H35" s="6" t="n">
-        <v>6.053707169991468e-06</v>
+        <v>0.000186</v>
       </c>
       <c r="I35" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J35" s="6" t="n">
-        <v>6.053707169991468e-06</v>
+        <v>0.000186</v>
       </c>
       <c r="K35" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L35" s="6" t="n">
-        <v>21.90660666972937</v>
+        <v>0.057783</v>
       </c>
       <c r="M35" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N35" s="6" t="n">
-        <v>0.03621496728406336</v>
+        <v>0.0001267070116300726</v>
       </c>
       <c r="O35" s="6" t="n">
-        <v>0.03621496728406336</v>
+        <v>0.0001267070116300726</v>
       </c>
       <c r="P35" s="6" t="n">
-        <v>-0.03620891357689337</v>
+        <v>5.929298836992738e-05</v>
       </c>
       <c r="Q35" s="6" t="n">
         <v>0</v>
@@ -3029,17 +3031,17 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>S9</t>
+          <t>S41</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Aave Ethereum USDT (aToken)</t>
+          <t>Aave Arbitrum USDCn (aArbUSDCn)</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>ethereum</t>
+          <t>arbitrum</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -3048,40 +3050,40 @@
         </is>
       </c>
       <c r="E36" s="6" t="n">
-        <v>5.897868</v>
+        <v>0.006346</v>
       </c>
       <c r="F36" s="6" t="n">
-        <v>5.913258</v>
+        <v>0.006363</v>
       </c>
       <c r="G36" s="6" t="n">
-        <v>0.01539</v>
+        <v>1.7e-05</v>
       </c>
       <c r="H36" s="6" t="n">
-        <v>0.01539</v>
+        <v>1.7e-05</v>
       </c>
       <c r="I36" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J36" s="6" t="n">
-        <v>0.01539</v>
+        <v>1.7e-05</v>
       </c>
       <c r="K36" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L36" s="6" t="n">
-        <v>5.897868</v>
+        <v>0.006346</v>
       </c>
       <c r="M36" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N36" s="6" t="n">
-        <v>0.009750076763868005</v>
+        <v>1.391555813655298e-05</v>
       </c>
       <c r="O36" s="6" t="n">
-        <v>0.009750076763868005</v>
+        <v>1.391555813655298e-05</v>
       </c>
       <c r="P36" s="6" t="n">
-        <v>0.005639923236131995</v>
+        <v>3.08444186344702e-06</v>
       </c>
       <c r="Q36" s="6" t="n">
         <v>0</v>
@@ -3094,12 +3096,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>S23</t>
+          <t>S7</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Anchorage tri-party loan escrow (USDC pass-through, ~$0 balance)</t>
+          <t>Aave Ethereum USDS (aToken)</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -3109,44 +3111,44 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E37" s="6" t="n">
-        <v>1.545609</v>
+        <v>0.005744283090097436</v>
       </c>
       <c r="F37" s="6" t="n">
-        <v>10.015998</v>
+        <v>0.005746426914602806</v>
       </c>
       <c r="G37" s="6" t="n">
-        <v>8.470389000000001</v>
+        <v>2.14382450537e-06</v>
       </c>
       <c r="H37" s="6" t="n">
-        <v>8.470389000000001</v>
+        <v>2.14382450537e-06</v>
       </c>
       <c r="I37" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J37" s="6" t="n">
-        <v>8.470389000000001</v>
+        <v>2.14382450537e-06</v>
       </c>
       <c r="K37" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L37" s="6" t="n">
-        <v>1.545609</v>
+        <v>0.005744283090097436</v>
       </c>
       <c r="M37" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N37" s="6" t="n">
-        <v>0.002555127784637646</v>
+        <v>1.259610861851073e-05</v>
       </c>
       <c r="O37" s="6" t="n">
-        <v>0.002555127784637646</v>
+        <v>1.259610861851073e-05</v>
       </c>
       <c r="P37" s="6" t="n">
-        <v>8.467833872215362</v>
+        <v>-1.045228411314073e-05</v>
       </c>
       <c r="Q37" s="6" t="n">
         <v>0</v>
@@ -3159,17 +3161,17 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>S54</t>
+          <t>S35</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Aave Avalanche USDC (aAvaUSDC)</t>
+          <t>Aave Base USDC (aBasUSDC)</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>avalanche_c</t>
+          <t>base</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -3178,40 +3180,40 @@
         </is>
       </c>
       <c r="E38" s="6" t="n">
-        <v>0.154431</v>
+        <v>0.0017</v>
       </c>
       <c r="F38" s="6" t="n">
-        <v>0.155165</v>
+        <v>0.001705</v>
       </c>
       <c r="G38" s="6" t="n">
-        <v>0.000734</v>
+        <v>5e-06</v>
       </c>
       <c r="H38" s="6" t="n">
-        <v>0.000734</v>
+        <v>5e-06</v>
       </c>
       <c r="I38" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J38" s="6" t="n">
-        <v>0.000734</v>
+        <v>5e-06</v>
       </c>
       <c r="K38" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L38" s="6" t="n">
-        <v>0.154431</v>
+        <v>0.0017</v>
       </c>
       <c r="M38" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N38" s="6" t="n">
-        <v>0.0002552980339202064</v>
+        <v>3.727773216536412e-06</v>
       </c>
       <c r="O38" s="6" t="n">
-        <v>0.0002552980339202064</v>
+        <v>3.727773216536412e-06</v>
       </c>
       <c r="P38" s="6" t="n">
-        <v>0.0004787019660797936</v>
+        <v>1.272226783463589e-06</v>
       </c>
       <c r="Q38" s="6" t="n">
         <v>0</v>
@@ -3224,12 +3226,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>S8</t>
+          <t>S17</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Aave Ethereum USDC (aToken)</t>
+          <t>Fluid Savings USDS (fsUSDS)</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -3239,44 +3241,44 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E39" s="6" t="n">
-        <v>0.057783</v>
+        <v>0.001240144670509943</v>
       </c>
       <c r="F39" s="6" t="n">
-        <v>0.057969</v>
+        <v>0.001240144670509943</v>
       </c>
       <c r="G39" s="6" t="n">
-        <v>0.000186</v>
+        <v>0</v>
       </c>
       <c r="H39" s="6" t="n">
-        <v>0.000186</v>
+        <v>0</v>
       </c>
       <c r="I39" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J39" s="6" t="n">
-        <v>0.000186</v>
+        <v>0</v>
       </c>
       <c r="K39" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L39" s="6" t="n">
-        <v>0.057783</v>
+        <v>0.001240144670509943</v>
       </c>
       <c r="M39" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N39" s="6" t="n">
-        <v>9.552412594628854e-05</v>
+        <v>2.719398874916082e-06</v>
       </c>
       <c r="O39" s="6" t="n">
-        <v>9.552412594628854e-05</v>
+        <v>2.719398874916082e-06</v>
       </c>
       <c r="P39" s="6" t="n">
-        <v>9.047587405371145e-05</v>
+        <v>-2.719398874916082e-06</v>
       </c>
       <c r="Q39" s="6" t="n">
         <v>0</v>
@@ -3289,17 +3291,17 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>S41</t>
+          <t>S6</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Aave Arbitrum USDCn (aArbUSDCn)</t>
+          <t>Aave Ethereum Lido USDS (aToken)</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>arbitrum</t>
+          <t>ethereum</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -3308,40 +3310,40 @@
         </is>
       </c>
       <c r="E40" s="6" t="n">
-        <v>0.006346</v>
+        <v>0.0005209665645060241</v>
       </c>
       <c r="F40" s="6" t="n">
-        <v>0.006363</v>
+        <v>0.000521673271312833</v>
       </c>
       <c r="G40" s="6" t="n">
-        <v>1.7e-05</v>
+        <v>7.06706806809e-07</v>
       </c>
       <c r="H40" s="6" t="n">
-        <v>1.7e-05</v>
+        <v>7.06706806809e-07</v>
       </c>
       <c r="I40" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J40" s="6" t="n">
-        <v>1.7e-05</v>
+        <v>7.06706806809e-07</v>
       </c>
       <c r="K40" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L40" s="6" t="n">
-        <v>0.006346</v>
+        <v>0.0005209665645060241</v>
       </c>
       <c r="M40" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N40" s="6" t="n">
-        <v>1.049090741663027e-05</v>
+        <v>1.142379532868556e-06</v>
       </c>
       <c r="O40" s="6" t="n">
-        <v>1.049090741663027e-05</v>
+        <v>1.142379532868556e-06</v>
       </c>
       <c r="P40" s="6" t="n">
-        <v>6.509092583369726e-06</v>
+        <v>-4.356727260595558e-07</v>
       </c>
       <c r="Q40" s="6" t="n">
         <v>0</v>
@@ -3354,12 +3356,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>S7</t>
+          <t>S30</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Aave Ethereum USDS (aToken)</t>
+          <t>USDe raw (ALM idle)</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -3369,44 +3371,44 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E41" s="6" t="n">
-        <v>0.005744283090097436</v>
+        <v>7.4896275897803e-05</v>
       </c>
       <c r="F41" s="6" t="n">
-        <v>0.005746426914602806</v>
+        <v>7.4896275897803e-05</v>
       </c>
       <c r="G41" s="6" t="n">
-        <v>2.14382450537e-06</v>
+        <v>0</v>
       </c>
       <c r="H41" s="6" t="n">
-        <v>2.14382450537e-06</v>
+        <v>0</v>
       </c>
       <c r="I41" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J41" s="6" t="n">
-        <v>2.14382450537e-06</v>
+        <v>0</v>
       </c>
       <c r="K41" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L41" s="6" t="n">
-        <v>0.005744283090097436</v>
+        <v>7.4896275897803e-05</v>
       </c>
       <c r="M41" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N41" s="6" t="n">
-        <v>9.496177446127806e-06</v>
+        <v>1.642331360647951e-07</v>
       </c>
       <c r="O41" s="6" t="n">
-        <v>9.496177446127806e-06</v>
+        <v>1.642331360647951e-07</v>
       </c>
       <c r="P41" s="6" t="n">
-        <v>-7.352352940757807e-06</v>
+        <v>-1.642331360647951e-07</v>
       </c>
       <c r="Q41" s="6" t="n">
         <v>0</v>
@@ -3419,59 +3421,59 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>S35</t>
+          <t>S19</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Aave Base USDC (aBasUSDC)</t>
+          <t>BlackRock USD Institutional Digital Liquidity Fund (BUIDL-I)</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>base</t>
+          <t>ethereum</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E42" s="6" t="n">
-        <v>0.0017</v>
+        <v>0</v>
       </c>
       <c r="F42" s="6" t="n">
-        <v>0.001705</v>
+        <v>0</v>
       </c>
       <c r="G42" s="6" t="n">
-        <v>5e-06</v>
+        <v>0</v>
       </c>
       <c r="H42" s="6" t="n">
-        <v>5e-06</v>
+        <v>0</v>
       </c>
       <c r="I42" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J42" s="6" t="n">
-        <v>5e-06</v>
+        <v>0</v>
       </c>
       <c r="K42" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L42" s="6" t="n">
-        <v>0.0017</v>
+        <v>0</v>
       </c>
       <c r="M42" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N42" s="6" t="n">
-        <v>2.810359692447442e-06</v>
+        <v>0</v>
       </c>
       <c r="O42" s="6" t="n">
-        <v>2.810359692447442e-06</v>
+        <v>0</v>
       </c>
       <c r="P42" s="6" t="n">
-        <v>2.189640307552558e-06</v>
+        <v>0</v>
       </c>
       <c r="Q42" s="6" t="n">
         <v>0</v>
@@ -3484,12 +3486,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>S17</t>
+          <t>S20</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Fluid Savings USDS (fsUSDS)</t>
+          <t>Janus Henderson Anemoy Treasury Fund (JTRSY)</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3499,14 +3501,14 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E43" s="6" t="n">
-        <v>0.001240144670509943</v>
+        <v>0</v>
       </c>
       <c r="F43" s="6" t="n">
-        <v>0.001240144670509943</v>
+        <v>0</v>
       </c>
       <c r="G43" s="6" t="n">
         <v>0</v>
@@ -3524,19 +3526,19 @@
         <v>0</v>
       </c>
       <c r="L43" s="6" t="n">
-        <v>0.001240144670509943</v>
+        <v>0</v>
       </c>
       <c r="M43" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N43" s="6" t="n">
-        <v>2.050148585179211e-06</v>
+        <v>0</v>
       </c>
       <c r="O43" s="6" t="n">
-        <v>2.050148585179211e-06</v>
+        <v>0</v>
       </c>
       <c r="P43" s="6" t="n">
-        <v>-2.050148585179211e-06</v>
+        <v>0</v>
       </c>
       <c r="Q43" s="6" t="n">
         <v>0</v>
@@ -3549,12 +3551,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>S6</t>
+          <t>S21</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Aave Ethereum Lido USDS (aToken)</t>
+          <t>Superstate Short Duration US Government Securities Fund (USTB)</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3564,44 +3566,44 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E44" s="6" t="n">
-        <v>0.0005209665645060241</v>
+        <v>0</v>
       </c>
       <c r="F44" s="6" t="n">
-        <v>0.000521673271312833</v>
+        <v>0</v>
       </c>
       <c r="G44" s="6" t="n">
-        <v>7.06706806809e-07</v>
+        <v>0</v>
       </c>
       <c r="H44" s="6" t="n">
-        <v>7.06706806809e-07</v>
+        <v>0</v>
       </c>
       <c r="I44" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J44" s="6" t="n">
-        <v>7.06706806809e-07</v>
+        <v>0</v>
       </c>
       <c r="K44" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L44" s="6" t="n">
-        <v>0.0005209665645060241</v>
+        <v>0</v>
       </c>
       <c r="M44" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N44" s="6" t="n">
-        <v>8.612373141179706e-07</v>
+        <v>0</v>
       </c>
       <c r="O44" s="6" t="n">
-        <v>8.612373141179706e-07</v>
+        <v>0</v>
       </c>
       <c r="P44" s="6" t="n">
-        <v>-1.545305073089706e-07</v>
+        <v>0</v>
       </c>
       <c r="Q44" s="6" t="n">
         <v>0</v>
@@ -3609,17 +3611,21 @@
       <c r="R44" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="S44" t="inlineStr"/>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>SDE (fixed)</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>S30</t>
+          <t>S22</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>USDe raw (ALM idle)</t>
+          <t>Superstate Crypto Carry Fund (USCC)</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3629,14 +3635,14 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E45" s="6" t="n">
-        <v>7.4896275897803e-05</v>
+        <v>0</v>
       </c>
       <c r="F45" s="6" t="n">
-        <v>7.4896275897803e-05</v>
+        <v>0</v>
       </c>
       <c r="G45" s="6" t="n">
         <v>0</v>
@@ -3654,19 +3660,19 @@
         <v>0</v>
       </c>
       <c r="L45" s="6" t="n">
-        <v>7.4896275897803e-05</v>
+        <v>0</v>
       </c>
       <c r="M45" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N45" s="6" t="n">
-        <v>1.238149852338873e-07</v>
+        <v>0</v>
       </c>
       <c r="O45" s="6" t="n">
-        <v>1.238149852338873e-07</v>
+        <v>0</v>
       </c>
       <c r="P45" s="6" t="n">
-        <v>-1.238149852338873e-07</v>
+        <v>0</v>
       </c>
       <c r="Q45" s="6" t="n">
         <v>0</v>
@@ -3679,12 +3685,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>S19</t>
+          <t>S26</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>BlackRock USD Institutional Digital Liquidity Fund (BUIDL-I)</t>
+          <t>USDC raw (ALM idle)</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3694,7 +3700,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E46" s="6" t="n">
@@ -3707,13 +3713,13 @@
         <v>0</v>
       </c>
       <c r="H46" s="6" t="n">
-        <v>0</v>
+        <v>6162610.279999871</v>
       </c>
       <c r="I46" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J46" s="6" t="n">
-        <v>0</v>
+        <v>6162610.279999871</v>
       </c>
       <c r="K46" s="6" t="n">
         <v>0</v>
@@ -3731,7 +3737,7 @@
         <v>0</v>
       </c>
       <c r="P46" s="6" t="n">
-        <v>0</v>
+        <v>6162610.279999871</v>
       </c>
       <c r="Q46" s="6" t="n">
         <v>0</v>
@@ -3744,12 +3750,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>S20</t>
+          <t>S29</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Janus Henderson Anemoy Treasury Fund (JTRSY)</t>
+          <t>DAI raw (ALM idle)</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3759,7 +3765,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E47" s="6" t="n">
@@ -3772,13 +3778,13 @@
         <v>0</v>
       </c>
       <c r="H47" s="6" t="n">
-        <v>0</v>
+        <v>8.19007e-07</v>
       </c>
       <c r="I47" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J47" s="6" t="n">
-        <v>0</v>
+        <v>8.19007e-07</v>
       </c>
       <c r="K47" s="6" t="n">
         <v>0</v>
@@ -3796,7 +3802,7 @@
         <v>0</v>
       </c>
       <c r="P47" s="6" t="n">
-        <v>0</v>
+        <v>8.19007e-07</v>
       </c>
       <c r="Q47" s="6" t="n">
         <v>0</v>
@@ -3809,12 +3815,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>S21</t>
+          <t>S31</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Superstate Short Duration US Government Securities Fund (USTB)</t>
+          <t>USDS raw / POL (ALM idle — already netted out of utilized)</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3824,7 +3830,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E48" s="6" t="n">
@@ -3837,19 +3843,19 @@
         <v>0</v>
       </c>
       <c r="H48" s="6" t="n">
-        <v>0</v>
+        <v>-2.5155451e-06</v>
       </c>
       <c r="I48" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J48" s="6" t="n">
-        <v>0</v>
+        <v>-2.5155451e-06</v>
       </c>
       <c r="K48" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L48" s="6" t="n">
-        <v>0</v>
+        <v>17.83075712531922</v>
       </c>
       <c r="M48" s="7" t="n">
         <v>0</v>
@@ -3861,7 +3867,7 @@
         <v>0</v>
       </c>
       <c r="P48" s="6" t="n">
-        <v>0</v>
+        <v>-2.5155451e-06</v>
       </c>
       <c r="Q48" s="6" t="n">
         <v>0</v>
@@ -3871,36 +3877,36 @@
       </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>SDE (fixed)</t>
+          <t>CoF excluded (Savings V2 depositor capital; not in cum_alm_usds)</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>S22</t>
+          <t>S38</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Superstate Crypto Carry Fund (USCC)</t>
+          <t>USDS raw (Base — POL)</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>ethereum</t>
+          <t>base</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E49" s="6" t="n">
-        <v>0</v>
+        <v>65170000</v>
       </c>
       <c r="F49" s="6" t="n">
-        <v>0</v>
+        <v>65170000</v>
       </c>
       <c r="G49" s="6" t="n">
         <v>0</v>
@@ -3918,10 +3924,10 @@
         <v>0</v>
       </c>
       <c r="L49" s="6" t="n">
-        <v>0</v>
+        <v>65170000</v>
       </c>
       <c r="M49" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N49" s="6" t="n">
         <v>0</v>
@@ -3933,32 +3939,36 @@
         <v>0</v>
       </c>
       <c r="Q49" s="6" t="n">
-        <v>0</v>
+        <v>65170000</v>
       </c>
       <c r="R49" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="S49" t="inlineStr"/>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>CoF excluded (already deducted from utilized)</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>S26</t>
+          <t>S42</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>USDC raw (ALM idle)</t>
+          <t>Fluid Savings USDS (fsUSDS, Arbitrum)</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>ethereum</t>
+          <t>arbitrum</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E50" s="6" t="n">
@@ -3971,13 +3981,13 @@
         <v>0</v>
       </c>
       <c r="H50" s="6" t="n">
-        <v>6162610.279999871</v>
+        <v>0</v>
       </c>
       <c r="I50" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J50" s="6" t="n">
-        <v>6162610.279999871</v>
+        <v>0</v>
       </c>
       <c r="K50" s="6" t="n">
         <v>0</v>
@@ -3995,7 +4005,7 @@
         <v>0</v>
       </c>
       <c r="P50" s="6" t="n">
-        <v>6162610.279999871</v>
+        <v>0</v>
       </c>
       <c r="Q50" s="6" t="n">
         <v>0</v>
@@ -4008,17 +4018,17 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>S29</t>
+          <t>S44</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>DAI raw (ALM idle)</t>
+          <t>USDS raw (Arbitrum — POL)</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>ethereum</t>
+          <t>arbitrum</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -4027,31 +4037,31 @@
         </is>
       </c>
       <c r="E51" s="6" t="n">
-        <v>0</v>
+        <v>90000000</v>
       </c>
       <c r="F51" s="6" t="n">
-        <v>0</v>
+        <v>90000000</v>
       </c>
       <c r="G51" s="6" t="n">
         <v>0</v>
       </c>
       <c r="H51" s="6" t="n">
-        <v>8.19007e-07</v>
+        <v>0</v>
       </c>
       <c r="I51" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J51" s="6" t="n">
-        <v>8.19007e-07</v>
+        <v>0</v>
       </c>
       <c r="K51" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L51" s="6" t="n">
-        <v>0</v>
+        <v>90000000</v>
       </c>
       <c r="M51" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N51" s="6" t="n">
         <v>0</v>
@@ -4060,30 +4070,34 @@
         <v>0</v>
       </c>
       <c r="P51" s="6" t="n">
-        <v>8.19007e-07</v>
+        <v>0</v>
       </c>
       <c r="Q51" s="6" t="n">
-        <v>0</v>
+        <v>90000000</v>
       </c>
       <c r="R51" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="S51" t="inlineStr"/>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>CoF excluded (already deducted from utilized)</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>S31</t>
+          <t>S48</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>USDS raw / POL (ALM idle — already netted out of utilized)</t>
+          <t>USDS raw (Optimism — POL)</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>ethereum</t>
+          <t>optimism</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -4092,28 +4106,28 @@
         </is>
       </c>
       <c r="E52" s="6" t="n">
-        <v>0</v>
+        <v>89900000</v>
       </c>
       <c r="F52" s="6" t="n">
-        <v>0</v>
+        <v>89900000</v>
       </c>
       <c r="G52" s="6" t="n">
         <v>0</v>
       </c>
       <c r="H52" s="6" t="n">
-        <v>-2.5155451e-06</v>
+        <v>0</v>
       </c>
       <c r="I52" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J52" s="6" t="n">
-        <v>-2.5155451e-06</v>
+        <v>0</v>
       </c>
       <c r="K52" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L52" s="6" t="n">
-        <v>17.83075712531922</v>
+        <v>89900000</v>
       </c>
       <c r="M52" s="7" t="n">
         <v>0</v>
@@ -4125,10 +4139,10 @@
         <v>0</v>
       </c>
       <c r="P52" s="6" t="n">
-        <v>-2.5155451e-06</v>
+        <v>0</v>
       </c>
       <c r="Q52" s="6" t="n">
-        <v>17.83075712531922</v>
+        <v>89900000</v>
       </c>
       <c r="R52" s="6" t="n">
         <v>0</v>
@@ -4142,17 +4156,17 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>S38</t>
+          <t>S52</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>USDS raw (Base — POL)</t>
+          <t>USDS raw (Unichain — POL)</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>base</t>
+          <t>unichain</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -4161,10 +4175,10 @@
         </is>
       </c>
       <c r="E53" s="6" t="n">
-        <v>65170000</v>
+        <v>89900000</v>
       </c>
       <c r="F53" s="6" t="n">
-        <v>65170000</v>
+        <v>89900000</v>
       </c>
       <c r="G53" s="6" t="n">
         <v>0</v>
@@ -4182,7 +4196,7 @@
         <v>0</v>
       </c>
       <c r="L53" s="6" t="n">
-        <v>65170000</v>
+        <v>89900000</v>
       </c>
       <c r="M53" s="7" t="n">
         <v>0</v>
@@ -4197,7 +4211,7 @@
         <v>0</v>
       </c>
       <c r="Q53" s="6" t="n">
-        <v>65170000</v>
+        <v>89900000</v>
       </c>
       <c r="R53" s="6" t="n">
         <v>0</v>
@@ -4211,50 +4225,50 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>S42</t>
+          <t>S56</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Fluid Savings USDS (fsUSDS, Arbitrum)</t>
+          <t>Spark Savings V2 — spUSDC vault</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>arbitrum</t>
+          <t>ethereum</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>S2</t>
         </is>
       </c>
       <c r="E54" s="6" t="n">
-        <v>0</v>
+        <v>573332157.534611</v>
       </c>
       <c r="F54" s="6" t="n">
-        <v>0</v>
+        <v>303545287.192935</v>
       </c>
       <c r="G54" s="6" t="n">
-        <v>0</v>
+        <v>-269786870.341676</v>
       </c>
       <c r="H54" s="6" t="n">
-        <v>0</v>
+        <v>-2077933.247665395</v>
       </c>
       <c r="I54" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J54" s="6" t="n">
-        <v>0</v>
+        <v>-2077933.247665395</v>
       </c>
       <c r="K54" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L54" s="6" t="n">
-        <v>0</v>
+        <v>573332157.534611</v>
       </c>
       <c r="M54" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N54" s="6" t="n">
         <v>0</v>
@@ -4263,7 +4277,7 @@
         <v>0</v>
       </c>
       <c r="P54" s="6" t="n">
-        <v>0</v>
+        <v>-2077933.247665395</v>
       </c>
       <c r="Q54" s="6" t="n">
         <v>0</v>
@@ -4271,52 +4285,56 @@
       <c r="R54" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="S54" t="inlineStr"/>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>CoF excluded (Savings V2 depositor capital; not in cum_alm_usds)</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>S44</t>
+          <t>S57</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>USDS raw (Arbitrum — POL)</t>
+          <t>Spark Savings V2 — spUSDT vault</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>arbitrum</t>
+          <t>ethereum</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>S2</t>
         </is>
       </c>
       <c r="E55" s="6" t="n">
-        <v>90000000</v>
+        <v>1134703231.016836</v>
       </c>
       <c r="F55" s="6" t="n">
-        <v>90000000</v>
+        <v>1270360913.25412</v>
       </c>
       <c r="G55" s="6" t="n">
-        <v>0</v>
+        <v>135657682.237284</v>
       </c>
       <c r="H55" s="6" t="n">
-        <v>0</v>
+        <v>-2595205.75030597</v>
       </c>
       <c r="I55" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J55" s="6" t="n">
-        <v>0</v>
+        <v>-2595205.75030597</v>
       </c>
       <c r="K55" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L55" s="6" t="n">
-        <v>90000000</v>
+        <v>1134703231.016836</v>
       </c>
       <c r="M55" s="7" t="n">
         <v>0</v>
@@ -4328,64 +4346,64 @@
         <v>0</v>
       </c>
       <c r="P55" s="6" t="n">
-        <v>0</v>
+        <v>-2595205.75030597</v>
       </c>
       <c r="Q55" s="6" t="n">
-        <v>90000000</v>
+        <v>0</v>
       </c>
       <c r="R55" s="6" t="n">
         <v>0</v>
       </c>
       <c r="S55" t="inlineStr">
         <is>
-          <t>CoF excluded (already deducted from utilized)</t>
+          <t>CoF excluded (Savings V2 depositor capital; not in cum_alm_usds)</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>S48</t>
+          <t>S59</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>USDS raw (Optimism — POL)</t>
+          <t>Spark Savings V2 — spPYUSD vault</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>optimism</t>
+          <t>ethereum</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>S2</t>
         </is>
       </c>
       <c r="E56" s="6" t="n">
-        <v>89900000</v>
+        <v>1066559.875133</v>
       </c>
       <c r="F56" s="6" t="n">
-        <v>89900000</v>
+        <v>773533.783718</v>
       </c>
       <c r="G56" s="6" t="n">
-        <v>0</v>
+        <v>-293026.091415</v>
       </c>
       <c r="H56" s="6" t="n">
-        <v>0</v>
+        <v>-2640.43740244277</v>
       </c>
       <c r="I56" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J56" s="6" t="n">
-        <v>0</v>
+        <v>-2640.43740244277</v>
       </c>
       <c r="K56" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L56" s="6" t="n">
-        <v>89900000</v>
+        <v>1066559.875133</v>
       </c>
       <c r="M56" s="7" t="n">
         <v>0</v>
@@ -4397,64 +4415,64 @@
         <v>0</v>
       </c>
       <c r="P56" s="6" t="n">
-        <v>0</v>
+        <v>-2640.43740244277</v>
       </c>
       <c r="Q56" s="6" t="n">
-        <v>89900000</v>
+        <v>0</v>
       </c>
       <c r="R56" s="6" t="n">
         <v>0</v>
       </c>
       <c r="S56" t="inlineStr">
         <is>
-          <t>CoF excluded (already deducted from utilized)</t>
+          <t>CoF excluded (Savings V2 depositor capital; not in cum_alm_usds)</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>S52</t>
+          <t>S60</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>USDS raw (Unichain — POL)</t>
+          <t>Spark Savings V2 — spUSDC vault (Avalanche-C, CREATE2 same address)</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>unichain</t>
+          <t>avalanche_c</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>S2</t>
         </is>
       </c>
       <c r="E57" s="6" t="n">
-        <v>89900000</v>
+        <v>37138817.432463</v>
       </c>
       <c r="F57" s="6" t="n">
-        <v>89900000</v>
+        <v>25647247.422478</v>
       </c>
       <c r="G57" s="6" t="n">
-        <v>0</v>
+        <v>-11491570.009985</v>
       </c>
       <c r="H57" s="6" t="n">
-        <v>0</v>
+        <v>-94676.37115954701</v>
       </c>
       <c r="I57" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J57" s="6" t="n">
-        <v>0</v>
+        <v>-94676.37115954701</v>
       </c>
       <c r="K57" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L57" s="6" t="n">
-        <v>89900000</v>
+        <v>37138817.432463</v>
       </c>
       <c r="M57" s="7" t="n">
         <v>0</v>
@@ -4466,17 +4484,17 @@
         <v>0</v>
       </c>
       <c r="P57" s="6" t="n">
-        <v>0</v>
+        <v>-94676.37115954701</v>
       </c>
       <c r="Q57" s="6" t="n">
-        <v>89900000</v>
+        <v>0</v>
       </c>
       <c r="R57" s="6" t="n">
         <v>0</v>
       </c>
       <c r="S57" t="inlineStr">
         <is>
-          <t>CoF excluded (already deducted from utilized)</t>
+          <t>CoF excluded (Savings V2 depositor capital; not in cum_alm_usds)</t>
         </is>
       </c>
     </row>
@@ -4585,7 +4603,7 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>10557149.38334401</v>
+        <v>10234615.9342856</v>
       </c>
     </row>
     <row r="5">
@@ -4605,7 +4623,7 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>10631305.44418851</v>
+        <v>10308771.99513011</v>
       </c>
     </row>
     <row r="8">
@@ -4632,7 +4650,7 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>10557149.38334401</v>
+        <v>10234615.9342856</v>
       </c>
     </row>
     <row r="12">
@@ -4642,7 +4660,7 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>-2819972.476227154</v>
+        <v>-3142505.92528556</v>
       </c>
     </row>
     <row r="13" ht="60" customHeight="1">
@@ -4937,4 +4955,1669 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:O38"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="11" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="11" customWidth="1" min="13" max="13"/>
+    <col width="18" customWidth="1" min="14" max="14"/>
+    <col width="22" customWidth="1" min="15" max="15"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Daily ilk debt + Sky charge breakdown</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="45" customHeight="1">
+      <c r="A3" s="9" t="inlineStr">
+        <is>
+          <t>cum_debt = Σ on-chain Vat dart from frob (0x76088703) + grab (0x7bab3f40). utilized = cum_debt − Σ deductions. base_apy = (1+SSR)(1+0.003)−1 (multiplicative). sub_apy applies on the first cap_usd of utilized when the subsidy is active; excess pays base_apy.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>cum_debt</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>− ALM idle</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>− PSM USDS</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>− SDE NAV</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>− Curve idle</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>− Lending idle</t>
+        </is>
+      </c>
+      <c r="H5" s="2">
+        <f> utilized</f>
+        <v/>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>SSR APY</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>base APY</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>T (months)</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>ref_rate APY</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>sub APY</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>daily Sky charge</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>daily Sky charge (gross on cum_debt)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="n">
+        <v>3786873547.945224</v>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>334970000</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>109271584.0644501</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>81897516.64033359</v>
+      </c>
+      <c r="F6" s="6" t="n">
+        <v>68133383.80742754</v>
+      </c>
+      <c r="G6" s="6" t="n">
+        <v>127906874.3387326</v>
+      </c>
+      <c r="H6" s="6" t="n">
+        <v>3064694189.09428</v>
+      </c>
+      <c r="I6" s="7" t="n">
+        <v>0.0375</v>
+      </c>
+      <c r="J6" s="7" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="K6" t="n">
+        <v>4</v>
+      </c>
+      <c r="L6" s="7" t="n">
+        <v>0.0433</v>
+      </c>
+      <c r="M6" s="7" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="N6" s="3" t="n">
+        <v>334275.4575777341</v>
+      </c>
+      <c r="O6" s="3" t="n">
+        <v>413045.742878023</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="n">
+        <v>4113602587.50019</v>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>334970000</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>109236625.511487</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>74371158.35490692</v>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>66387928.31178243</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>131684974.1461452</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>3396951901.175869</v>
+      </c>
+      <c r="I7" s="7" t="n">
+        <v>0.0375</v>
+      </c>
+      <c r="J7" s="7" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="K7" t="n">
+        <v>4</v>
+      </c>
+      <c r="L7" s="7" t="n">
+        <v>0.0433</v>
+      </c>
+      <c r="M7" s="7" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="N7" s="3" t="n">
+        <v>370515.8104113157</v>
+      </c>
+      <c r="O7" s="3" t="n">
+        <v>448683.0666899128</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="n">
+        <v>4112495173.033005</v>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>334970000</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>109212118.7652359</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>78198703.5201842</v>
+      </c>
+      <c r="F8" s="6" t="n">
+        <v>69297142.12576202</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>129926697.4882286</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>3390890511.133594</v>
+      </c>
+      <c r="I8" s="7" t="n">
+        <v>0.0375</v>
+      </c>
+      <c r="J8" s="7" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="K8" t="n">
+        <v>4</v>
+      </c>
+      <c r="L8" s="7" t="n">
+        <v>0.0433</v>
+      </c>
+      <c r="M8" s="7" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="N8" s="3" t="n">
+        <v>369854.6762801686</v>
+      </c>
+      <c r="O8" s="3" t="n">
+        <v>448562.277647057</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="n">
+        <v>4014386628.19746</v>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>334970000</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>109413093.6674421</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>75725030.78440267</v>
+      </c>
+      <c r="F9" s="6" t="n">
+        <v>64115633.06430446</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>129945312.0277757</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>3300217558.653535</v>
+      </c>
+      <c r="I9" s="7" t="n">
+        <v>0.0375</v>
+      </c>
+      <c r="J9" s="7" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="K9" t="n">
+        <v>4</v>
+      </c>
+      <c r="L9" s="7" t="n">
+        <v>0.0433</v>
+      </c>
+      <c r="M9" s="7" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="N9" s="3" t="n">
+        <v>359964.7033138436</v>
+      </c>
+      <c r="O9" s="3" t="n">
+        <v>437861.2821500545</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="n">
+        <v>3967538459.305897</v>
+      </c>
+      <c r="C10" s="6" t="n">
+        <v>334970000</v>
+      </c>
+      <c r="D10" s="6" t="n">
+        <v>109666118.9886243</v>
+      </c>
+      <c r="E10" s="6" t="n">
+        <v>62633764.42527747</v>
+      </c>
+      <c r="F10" s="6" t="n">
+        <v>71985346.18365841</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>129991339.9884334</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>3258291889.719903</v>
+      </c>
+      <c r="I10" s="7" t="n">
+        <v>0.0375</v>
+      </c>
+      <c r="J10" s="7" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="K10" t="n">
+        <v>4</v>
+      </c>
+      <c r="L10" s="7" t="n">
+        <v>0.0433</v>
+      </c>
+      <c r="M10" s="7" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="N10" s="3" t="n">
+        <v>355391.7438920149</v>
+      </c>
+      <c r="O10" s="3" t="n">
+        <v>432751.4107806262</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="n">
+        <v>3773637803.723945</v>
+      </c>
+      <c r="C11" s="6" t="n">
+        <v>334970000</v>
+      </c>
+      <c r="D11" s="6" t="n">
+        <v>109667151.3287632</v>
+      </c>
+      <c r="E11" s="6" t="n">
+        <v>65914408.62152216</v>
+      </c>
+      <c r="F11" s="6" t="n">
+        <v>69182310.83017388</v>
+      </c>
+      <c r="G11" s="6" t="n">
+        <v>132866251.0455103</v>
+      </c>
+      <c r="H11" s="6" t="n">
+        <v>3061037681.897975</v>
+      </c>
+      <c r="I11" s="7" t="n">
+        <v>0.0375</v>
+      </c>
+      <c r="J11" s="7" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="K11" t="n">
+        <v>4</v>
+      </c>
+      <c r="L11" s="7" t="n">
+        <v>0.0433</v>
+      </c>
+      <c r="M11" s="7" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="N11" s="3" t="n">
+        <v>333876.6312868336</v>
+      </c>
+      <c r="O11" s="3" t="n">
+        <v>411602.080253643</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="n">
+        <v>3829641619.123199</v>
+      </c>
+      <c r="C12" s="6" t="n">
+        <v>334970000</v>
+      </c>
+      <c r="D12" s="6" t="n">
+        <v>109729057.8747254</v>
+      </c>
+      <c r="E12" s="6" t="n">
+        <v>68822191.85959996</v>
+      </c>
+      <c r="F12" s="6" t="n">
+        <v>59598590.74937253</v>
+      </c>
+      <c r="G12" s="6" t="n">
+        <v>133190285.3282568</v>
+      </c>
+      <c r="H12" s="6" t="n">
+        <v>3123331493.311244</v>
+      </c>
+      <c r="I12" s="7" t="n">
+        <v>0.0375</v>
+      </c>
+      <c r="J12" s="7" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="K12" t="n">
+        <v>4</v>
+      </c>
+      <c r="L12" s="7" t="n">
+        <v>0.0433</v>
+      </c>
+      <c r="M12" s="7" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="N12" s="3" t="n">
+        <v>340671.2055672075</v>
+      </c>
+      <c r="O12" s="3" t="n">
+        <v>417710.5856586202</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="n">
+        <v>3112489658.938523</v>
+      </c>
+      <c r="C13" s="6" t="n">
+        <v>334970000</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>109756088.3909883</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>46416747.2661341</v>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>62126087.28772155</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>136081135.6656561</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>2423139600.328023</v>
+      </c>
+      <c r="I13" s="7" t="n">
+        <v>0.0375</v>
+      </c>
+      <c r="J13" s="7" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="K13" t="n">
+        <v>4</v>
+      </c>
+      <c r="L13" s="7" t="n">
+        <v>0.0433</v>
+      </c>
+      <c r="M13" s="7" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="N13" s="3" t="n">
+        <v>264299.1596214559</v>
+      </c>
+      <c r="O13" s="3" t="n">
+        <v>339488.6539250828</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="n">
+        <v>3862142308.882361</v>
+      </c>
+      <c r="C14" s="6" t="n">
+        <v>334970000</v>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>109737227.1714184</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>59621771.27202594</v>
+      </c>
+      <c r="F14" s="6" t="n">
+        <v>63144552.54356655</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>136418480.8456975</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>3158250277.049653</v>
+      </c>
+      <c r="I14" s="7" t="n">
+        <v>0.0375</v>
+      </c>
+      <c r="J14" s="7" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="K14" t="n">
+        <v>4</v>
+      </c>
+      <c r="L14" s="7" t="n">
+        <v>0.0433</v>
+      </c>
+      <c r="M14" s="7" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="N14" s="3" t="n">
+        <v>344479.902844003</v>
+      </c>
+      <c r="O14" s="3" t="n">
+        <v>421255.5341169349</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="n">
+        <v>4007860775.201573</v>
+      </c>
+      <c r="C15" s="6" t="n">
+        <v>334970000</v>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>109820179.5695339</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>62881956.35592515</v>
+      </c>
+      <c r="F15" s="6" t="n">
+        <v>67929925.5704889</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>136520708.1372503</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>3295738005.568375</v>
+      </c>
+      <c r="I15" s="7" t="n">
+        <v>0.0375</v>
+      </c>
+      <c r="J15" s="7" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="K15" t="n">
+        <v>4</v>
+      </c>
+      <c r="L15" s="7" t="n">
+        <v>0.0433</v>
+      </c>
+      <c r="M15" s="7" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="N15" s="3" t="n">
+        <v>359476.1049203679</v>
+      </c>
+      <c r="O15" s="3" t="n">
+        <v>437149.4876408184</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="n">
+        <v>3944031608.133983</v>
+      </c>
+      <c r="C16" s="6" t="n">
+        <v>334970000</v>
+      </c>
+      <c r="D16" s="6" t="n">
+        <v>109824143.9731289</v>
+      </c>
+      <c r="E16" s="6" t="n">
+        <v>84921355.55294961</v>
+      </c>
+      <c r="F16" s="6" t="n">
+        <v>67458232.10747725</v>
+      </c>
+      <c r="G16" s="6" t="n">
+        <v>146800932.9007985</v>
+      </c>
+      <c r="H16" s="6" t="n">
+        <v>3200056943.599629</v>
+      </c>
+      <c r="I16" s="7" t="n">
+        <v>0.0375</v>
+      </c>
+      <c r="J16" s="7" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="K16" t="n">
+        <v>4</v>
+      </c>
+      <c r="L16" s="7" t="n">
+        <v>0.0433</v>
+      </c>
+      <c r="M16" s="7" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="N16" s="3" t="n">
+        <v>349039.8823161875</v>
+      </c>
+      <c r="O16" s="3" t="n">
+        <v>430187.4474789483</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="n">
+        <v>3869106066.859931</v>
+      </c>
+      <c r="C17" s="6" t="n">
+        <v>334970000</v>
+      </c>
+      <c r="D17" s="6" t="n">
+        <v>109837230.945328</v>
+      </c>
+      <c r="E17" s="6" t="n">
+        <v>78116321.12843026</v>
+      </c>
+      <c r="F17" s="6" t="n">
+        <v>58043367.04671003</v>
+      </c>
+      <c r="G17" s="6" t="n">
+        <v>146820705.7658038</v>
+      </c>
+      <c r="H17" s="6" t="n">
+        <v>3141318441.973659</v>
+      </c>
+      <c r="I17" s="7" t="n">
+        <v>0.0375</v>
+      </c>
+      <c r="J17" s="7" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="K17" t="n">
+        <v>4</v>
+      </c>
+      <c r="L17" s="7" t="n">
+        <v>0.0433</v>
+      </c>
+      <c r="M17" s="7" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="N17" s="3" t="n">
+        <v>342633.0964194667</v>
+      </c>
+      <c r="O17" s="3" t="n">
+        <v>422015.092245996</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="n">
+        <v>3869966485.495641</v>
+      </c>
+      <c r="C18" s="6" t="n">
+        <v>334970000</v>
+      </c>
+      <c r="D18" s="6" t="n">
+        <v>109812101.2069135</v>
+      </c>
+      <c r="E18" s="6" t="n">
+        <v>85902407.14010979</v>
+      </c>
+      <c r="F18" s="6" t="n">
+        <v>60741445.97380174</v>
+      </c>
+      <c r="G18" s="6" t="n">
+        <v>146084521.7500651</v>
+      </c>
+      <c r="H18" s="6" t="n">
+        <v>3132456009.424751</v>
+      </c>
+      <c r="I18" s="7" t="n">
+        <v>0.0375</v>
+      </c>
+      <c r="J18" s="7" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="K18" t="n">
+        <v>4</v>
+      </c>
+      <c r="L18" s="7" t="n">
+        <v>0.0433</v>
+      </c>
+      <c r="M18" s="7" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="N18" s="3" t="n">
+        <v>341666.4441165779</v>
+      </c>
+      <c r="O18" s="3" t="n">
+        <v>422108.9407070216</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="n">
+        <v>3906757002.936191</v>
+      </c>
+      <c r="C19" s="6" t="n">
+        <v>334970000</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>109817281.9042201</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>63272317.16911007</v>
+      </c>
+      <c r="F19" s="6" t="n">
+        <v>58432587.64789255</v>
+      </c>
+      <c r="G19" s="6" t="n">
+        <v>174559965.1979237</v>
+      </c>
+      <c r="H19" s="6" t="n">
+        <v>3165704851.017045</v>
+      </c>
+      <c r="I19" s="7" t="n">
+        <v>0.0375</v>
+      </c>
+      <c r="J19" s="7" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="K19" t="n">
+        <v>4</v>
+      </c>
+      <c r="L19" s="7" t="n">
+        <v>0.0433</v>
+      </c>
+      <c r="M19" s="7" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="N19" s="3" t="n">
+        <v>345292.9957564588</v>
+      </c>
+      <c r="O19" s="3" t="n">
+        <v>426121.7936356186</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="n">
+        <v>3941296256.964431</v>
+      </c>
+      <c r="C20" s="6" t="n">
+        <v>334970000</v>
+      </c>
+      <c r="D20" s="6" t="n">
+        <v>109861276.5733739</v>
+      </c>
+      <c r="E20" s="6" t="n">
+        <v>88511698.91894951</v>
+      </c>
+      <c r="F20" s="6" t="n">
+        <v>42181809.13057283</v>
+      </c>
+      <c r="G20" s="6" t="n">
+        <v>169618722.6830847</v>
+      </c>
+      <c r="H20" s="6" t="n">
+        <v>3196152749.65845</v>
+      </c>
+      <c r="I20" s="7" t="n">
+        <v>0.0375</v>
+      </c>
+      <c r="J20" s="7" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="K20" t="n">
+        <v>4</v>
+      </c>
+      <c r="L20" s="7" t="n">
+        <v>0.0433</v>
+      </c>
+      <c r="M20" s="7" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="N20" s="3" t="n">
+        <v>348614.0400834441</v>
+      </c>
+      <c r="O20" s="3" t="n">
+        <v>429889.0944598799</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="n">
+        <v>3949955056.90474</v>
+      </c>
+      <c r="C21" s="6" t="n">
+        <v>334970000</v>
+      </c>
+      <c r="D21" s="6" t="n">
+        <v>109944218.3095993</v>
+      </c>
+      <c r="E21" s="6" t="n">
+        <v>87033668.77329952</v>
+      </c>
+      <c r="F21" s="6" t="n">
+        <v>51954304.76465927</v>
+      </c>
+      <c r="G21" s="6" t="n">
+        <v>172338153.0245515</v>
+      </c>
+      <c r="H21" s="6" t="n">
+        <v>3193714712.03263</v>
+      </c>
+      <c r="I21" s="7" t="n">
+        <v>0.0375</v>
+      </c>
+      <c r="J21" s="7" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="K21" t="n">
+        <v>4</v>
+      </c>
+      <c r="L21" s="7" t="n">
+        <v>0.0433</v>
+      </c>
+      <c r="M21" s="7" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="N21" s="3" t="n">
+        <v>348348.1159511562</v>
+      </c>
+      <c r="O21" s="3" t="n">
+        <v>430833.5359387135</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="n">
+        <v>3930000358.477587</v>
+      </c>
+      <c r="C22" s="6" t="n">
+        <v>334970000</v>
+      </c>
+      <c r="D22" s="6" t="n">
+        <v>110151080.1866189</v>
+      </c>
+      <c r="E22" s="6" t="n">
+        <v>87868461.85445462</v>
+      </c>
+      <c r="F22" s="6" t="n">
+        <v>60263592.76517375</v>
+      </c>
+      <c r="G22" s="6" t="n">
+        <v>162877756.5589872</v>
+      </c>
+      <c r="H22" s="6" t="n">
+        <v>3173869467.112352</v>
+      </c>
+      <c r="I22" s="7" t="n">
+        <v>0.0375</v>
+      </c>
+      <c r="J22" s="7" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="K22" t="n">
+        <v>4</v>
+      </c>
+      <c r="L22" s="7" t="n">
+        <v>0.0433</v>
+      </c>
+      <c r="M22" s="7" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="N22" s="3" t="n">
+        <v>346183.5351097547</v>
+      </c>
+      <c r="O22" s="3" t="n">
+        <v>428657.0166725176</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="n">
+        <v>4128625750.909277</v>
+      </c>
+      <c r="C23" s="6" t="n">
+        <v>334970000</v>
+      </c>
+      <c r="D23" s="6" t="n">
+        <v>110145162.8914285</v>
+      </c>
+      <c r="E23" s="6" t="n">
+        <v>89081856.06629945</v>
+      </c>
+      <c r="F23" s="6" t="n">
+        <v>42740384.84050981</v>
+      </c>
+      <c r="G23" s="6" t="n">
+        <v>231737478.377994</v>
+      </c>
+      <c r="H23" s="6" t="n">
+        <v>3319950868.733045</v>
+      </c>
+      <c r="I23" s="7" t="n">
+        <v>0.0375</v>
+      </c>
+      <c r="J23" s="7" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="K23" t="n">
+        <v>4</v>
+      </c>
+      <c r="L23" s="7" t="n">
+        <v>0.0433</v>
+      </c>
+      <c r="M23" s="7" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="N23" s="3" t="n">
+        <v>362117.0750838638</v>
+      </c>
+      <c r="O23" s="3" t="n">
+        <v>450321.6885271936</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="B24" s="6" t="n">
+        <v>4099347532.103574</v>
+      </c>
+      <c r="C24" s="6" t="n">
+        <v>334970000</v>
+      </c>
+      <c r="D24" s="6" t="n">
+        <v>110135980.040481</v>
+      </c>
+      <c r="E24" s="6" t="n">
+        <v>90072399.6267707</v>
+      </c>
+      <c r="F24" s="6" t="n">
+        <v>56943828.95422778</v>
+      </c>
+      <c r="G24" s="6" t="n">
+        <v>229182741.6867744</v>
+      </c>
+      <c r="H24" s="6" t="n">
+        <v>3278042581.79532</v>
+      </c>
+      <c r="I24" s="7" t="n">
+        <v>0.0375</v>
+      </c>
+      <c r="J24" s="7" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="K24" t="n">
+        <v>4</v>
+      </c>
+      <c r="L24" s="7" t="n">
+        <v>0.0433</v>
+      </c>
+      <c r="M24" s="7" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="N24" s="3" t="n">
+        <v>357546.011568862</v>
+      </c>
+      <c r="O24" s="3" t="n">
+        <v>447128.2247149919</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="B25" s="6" t="n">
+        <v>3849261001.889072</v>
+      </c>
+      <c r="C25" s="6" t="n">
+        <v>334970000</v>
+      </c>
+      <c r="D25" s="6" t="n">
+        <v>110063401.5573106</v>
+      </c>
+      <c r="E25" s="6" t="n">
+        <v>90207535.65130401</v>
+      </c>
+      <c r="F25" s="6" t="n">
+        <v>51602034.69547939</v>
+      </c>
+      <c r="G25" s="6" t="n">
+        <v>230888253.3173563</v>
+      </c>
+      <c r="H25" s="6" t="n">
+        <v>3031529776.667622</v>
+      </c>
+      <c r="I25" s="7" t="n">
+        <v>0.0375</v>
+      </c>
+      <c r="J25" s="7" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="K25" t="n">
+        <v>4</v>
+      </c>
+      <c r="L25" s="7" t="n">
+        <v>0.0433</v>
+      </c>
+      <c r="M25" s="7" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="N25" s="3" t="n">
+        <v>330658.1148821178</v>
+      </c>
+      <c r="O25" s="3" t="n">
+        <v>419850.5310322215</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="B26" s="6" t="n">
+        <v>3796096805.831977</v>
+      </c>
+      <c r="C26" s="6" t="n">
+        <v>334970000</v>
+      </c>
+      <c r="D26" s="6" t="n">
+        <v>110201806.0378861</v>
+      </c>
+      <c r="E26" s="6" t="n">
+        <v>90137880.50639333</v>
+      </c>
+      <c r="F26" s="6" t="n">
+        <v>53876705.01782864</v>
+      </c>
+      <c r="G26" s="6" t="n">
+        <v>254742493.5135711</v>
+      </c>
+      <c r="H26" s="6" t="n">
+        <v>2952167920.756298</v>
+      </c>
+      <c r="I26" s="7" t="n">
+        <v>0.0375</v>
+      </c>
+      <c r="J26" s="7" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="K26" t="n">
+        <v>4</v>
+      </c>
+      <c r="L26" s="7" t="n">
+        <v>0.0433</v>
+      </c>
+      <c r="M26" s="7" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="N26" s="3" t="n">
+        <v>322001.8774038798</v>
+      </c>
+      <c r="O26" s="3" t="n">
+        <v>414051.7514910269</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B27" s="6" t="n">
+        <v>4276518811.263577</v>
+      </c>
+      <c r="C27" s="6" t="n">
+        <v>334970000</v>
+      </c>
+      <c r="D27" s="6" t="n">
+        <v>110246348.1665363</v>
+      </c>
+      <c r="E27" s="6" t="n">
+        <v>90683527.73142503</v>
+      </c>
+      <c r="F27" s="6" t="n">
+        <v>60950192.97977956</v>
+      </c>
+      <c r="G27" s="6" t="n">
+        <v>239797730.4064276</v>
+      </c>
+      <c r="H27" s="6" t="n">
+        <v>3439871011.979409</v>
+      </c>
+      <c r="I27" s="7" t="n">
+        <v>0.0375</v>
+      </c>
+      <c r="J27" s="7" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="K27" t="n">
+        <v>4</v>
+      </c>
+      <c r="L27" s="7" t="n">
+        <v>0.0433</v>
+      </c>
+      <c r="M27" s="7" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="N27" s="3" t="n">
+        <v>375197.1275403578</v>
+      </c>
+      <c r="O27" s="3" t="n">
+        <v>466452.8315947228</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="B28" s="6" t="n">
+        <v>4260541447.925423</v>
+      </c>
+      <c r="C28" s="6" t="n">
+        <v>334970000</v>
+      </c>
+      <c r="D28" s="6" t="n">
+        <v>110397429.3795781</v>
+      </c>
+      <c r="E28" s="6" t="n">
+        <v>90958523.65549019</v>
+      </c>
+      <c r="F28" s="6" t="n">
+        <v>64022634.63846193</v>
+      </c>
+      <c r="G28" s="6" t="n">
+        <v>240130221.5557107</v>
+      </c>
+      <c r="H28" s="6" t="n">
+        <v>3420062638.696182</v>
+      </c>
+      <c r="I28" s="7" t="n">
+        <v>0.0375</v>
+      </c>
+      <c r="J28" s="7" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="K28" t="n">
+        <v>4</v>
+      </c>
+      <c r="L28" s="7" t="n">
+        <v>0.0433</v>
+      </c>
+      <c r="M28" s="7" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="N28" s="3" t="n">
+        <v>373036.568399846</v>
+      </c>
+      <c r="O28" s="3" t="n">
+        <v>464710.1322873164</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="n">
+        <v>4278271428.210862</v>
+      </c>
+      <c r="C29" s="6" t="n">
+        <v>334970000</v>
+      </c>
+      <c r="D29" s="6" t="n">
+        <v>110459412.1575361</v>
+      </c>
+      <c r="E29" s="6" t="n">
+        <v>91000613.80843022</v>
+      </c>
+      <c r="F29" s="6" t="n">
+        <v>63901753.89657893</v>
+      </c>
+      <c r="G29" s="6" t="n">
+        <v>243572783.8200219</v>
+      </c>
+      <c r="H29" s="6" t="n">
+        <v>3434366864.528295</v>
+      </c>
+      <c r="I29" s="7" t="n">
+        <v>0.0375</v>
+      </c>
+      <c r="J29" s="7" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="K29" t="n">
+        <v>4</v>
+      </c>
+      <c r="L29" s="7" t="n">
+        <v>0.0433</v>
+      </c>
+      <c r="M29" s="7" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="N29" s="3" t="n">
+        <v>374596.7735427734</v>
+      </c>
+      <c r="O29" s="3" t="n">
+        <v>466643.9948220676</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="n">
+        <v>4275937035.604297</v>
+      </c>
+      <c r="C30" s="6" t="n">
+        <v>334970000</v>
+      </c>
+      <c r="D30" s="6" t="n">
+        <v>110548351.2880701</v>
+      </c>
+      <c r="E30" s="6" t="n">
+        <v>90132356.81756249</v>
+      </c>
+      <c r="F30" s="6" t="n">
+        <v>65846944.15199657</v>
+      </c>
+      <c r="G30" s="6" t="n">
+        <v>245605231.7022537</v>
+      </c>
+      <c r="H30" s="6" t="n">
+        <v>3428834151.644414</v>
+      </c>
+      <c r="I30" s="7" t="n">
+        <v>0.0375</v>
+      </c>
+      <c r="J30" s="7" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="K30" t="n">
+        <v>4</v>
+      </c>
+      <c r="L30" s="7" t="n">
+        <v>0.0433</v>
+      </c>
+      <c r="M30" s="7" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="N30" s="3" t="n">
+        <v>373993.3038271044</v>
+      </c>
+      <c r="O30" s="3" t="n">
+        <v>466389.3755652744</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="n">
+        <v>4019063778.948612</v>
+      </c>
+      <c r="C31" s="6" t="n">
+        <v>334970000</v>
+      </c>
+      <c r="D31" s="6" t="n">
+        <v>110567333.2809158</v>
+      </c>
+      <c r="E31" s="6" t="n">
+        <v>91214545.99128646</v>
+      </c>
+      <c r="F31" s="6" t="n">
+        <v>71416697.68580709</v>
+      </c>
+      <c r="G31" s="6" t="n">
+        <v>179571549.4489093</v>
+      </c>
+      <c r="H31" s="6" t="n">
+        <v>3231323652.541693</v>
+      </c>
+      <c r="I31" s="7" t="n">
+        <v>0.0375</v>
+      </c>
+      <c r="J31" s="7" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="K31" t="n">
+        <v>4</v>
+      </c>
+      <c r="L31" s="7" t="n">
+        <v>0.0433</v>
+      </c>
+      <c r="M31" s="7" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="N31" s="3" t="n">
+        <v>352450.2367573421</v>
+      </c>
+      <c r="O31" s="3" t="n">
+        <v>438371.433118156</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B32" s="6" t="n">
+        <v>3894612666.177943</v>
+      </c>
+      <c r="C32" s="6" t="n">
+        <v>334970000</v>
+      </c>
+      <c r="D32" s="6" t="n">
+        <v>110810390.8233007</v>
+      </c>
+      <c r="E32" s="6" t="n">
+        <v>91260440.13070874</v>
+      </c>
+      <c r="F32" s="6" t="n">
+        <v>74954030.44580247</v>
+      </c>
+      <c r="G32" s="6" t="n">
+        <v>206116586.0471416</v>
+      </c>
+      <c r="H32" s="6" t="n">
+        <v>3076501218.730989</v>
+      </c>
+      <c r="I32" s="7" t="n">
+        <v>0.0375</v>
+      </c>
+      <c r="J32" s="7" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="K32" t="n">
+        <v>4</v>
+      </c>
+      <c r="L32" s="7" t="n">
+        <v>0.0433</v>
+      </c>
+      <c r="M32" s="7" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="N32" s="3" t="n">
+        <v>335563.2859843952</v>
+      </c>
+      <c r="O32" s="3" t="n">
+        <v>424797.1741217737</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="B33" s="6" t="n">
+        <v>3904793970.371299</v>
+      </c>
+      <c r="C33" s="6" t="n">
+        <v>334970000</v>
+      </c>
+      <c r="D33" s="6" t="n">
+        <v>110784766.9258687</v>
+      </c>
+      <c r="E33" s="6" t="n">
+        <v>90992031.3551863</v>
+      </c>
+      <c r="F33" s="6" t="n">
+        <v>75076806.84493634</v>
+      </c>
+      <c r="G33" s="6" t="n">
+        <v>248420857.3449725</v>
+      </c>
+      <c r="H33" s="6" t="n">
+        <v>3044549507.900335</v>
+      </c>
+      <c r="I33" s="7" t="n">
+        <v>0.0375</v>
+      </c>
+      <c r="J33" s="7" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="K33" t="n">
+        <v>4</v>
+      </c>
+      <c r="L33" s="7" t="n">
+        <v>0.0433</v>
+      </c>
+      <c r="M33" s="7" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="N33" s="3" t="n">
+        <v>332078.2163169826</v>
+      </c>
+      <c r="O33" s="3" t="n">
+        <v>425907.6797409258</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="B34" s="6" t="n">
+        <v>3980438326.717189</v>
+      </c>
+      <c r="C34" s="6" t="n">
+        <v>334970000</v>
+      </c>
+      <c r="D34" s="6" t="n">
+        <v>110800643.1083902</v>
+      </c>
+      <c r="E34" s="6" t="n">
+        <v>89742687.66481608</v>
+      </c>
+      <c r="F34" s="6" t="n">
+        <v>75116667.49366367</v>
+      </c>
+      <c r="G34" s="6" t="n">
+        <v>303291142.7334828</v>
+      </c>
+      <c r="H34" s="6" t="n">
+        <v>3066517185.716836</v>
+      </c>
+      <c r="I34" s="7" t="n">
+        <v>0.0375</v>
+      </c>
+      <c r="J34" s="7" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="K34" t="n">
+        <v>4</v>
+      </c>
+      <c r="L34" s="7" t="n">
+        <v>0.0433</v>
+      </c>
+      <c r="M34" s="7" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="N34" s="3" t="n">
+        <v>334474.2973289681</v>
+      </c>
+      <c r="O34" s="3" t="n">
+        <v>434158.4383062261</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+      <c r="B35" s="6" t="n">
+        <v>3949996189.520216</v>
+      </c>
+      <c r="C35" s="6" t="n">
+        <v>334970000</v>
+      </c>
+      <c r="D35" s="6" t="n">
+        <v>110800910.0818387</v>
+      </c>
+      <c r="E35" s="6" t="n">
+        <v>89921451.17719229</v>
+      </c>
+      <c r="F35" s="6" t="n">
+        <v>72969997.84221481</v>
+      </c>
+      <c r="G35" s="6" t="n">
+        <v>295800536.4468129</v>
+      </c>
+      <c r="H35" s="6" t="n">
+        <v>3045533293.972157</v>
+      </c>
+      <c r="I35" s="7" t="n">
+        <v>0.0375</v>
+      </c>
+      <c r="J35" s="7" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="K35" t="n">
+        <v>4</v>
+      </c>
+      <c r="L35" s="7" t="n">
+        <v>0.0433</v>
+      </c>
+      <c r="M35" s="7" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="N35" s="3" t="n">
+        <v>332185.5208371161</v>
+      </c>
+      <c r="O35" s="3" t="n">
+        <v>430838.0223973978</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="B36" s="6" t="n">
+        <v>3938439863.321327</v>
+      </c>
+      <c r="C36" s="6" t="n">
+        <v>334970000</v>
+      </c>
+      <c r="D36" s="6" t="n">
+        <v>110840456.802935</v>
+      </c>
+      <c r="E36" s="6" t="n">
+        <v>90106496.23897925</v>
+      </c>
+      <c r="F36" s="6" t="n">
+        <v>73041937.31867403</v>
+      </c>
+      <c r="G36" s="6" t="n">
+        <v>289518568.352541</v>
+      </c>
+      <c r="H36" s="6" t="n">
+        <v>3039962404.608198</v>
+      </c>
+      <c r="I36" s="7" t="n">
+        <v>0.0375</v>
+      </c>
+      <c r="J36" s="7" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="K36" t="n">
+        <v>4</v>
+      </c>
+      <c r="L36" s="7" t="n">
+        <v>0.0433</v>
+      </c>
+      <c r="M36" s="7" t="n">
+        <v>0.0406125</v>
+      </c>
+      <c r="N36" s="3" t="n">
+        <v>331577.8870973847</v>
+      </c>
+      <c r="O36" s="3" t="n">
+        <v>429577.5389723965</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="8" t="inlineStr">
+        <is>
+          <t>Σ daily charges</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr"/>
+      <c r="C38" t="inlineStr"/>
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="inlineStr"/>
+      <c r="F38" t="inlineStr"/>
+      <c r="G38" t="inlineStr"/>
+      <c r="H38" t="inlineStr"/>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr"/>
+      <c r="N38" s="10" t="n">
+        <v>10742059.80203898</v>
+      </c>
+      <c r="O38" s="10" t="n">
+        <v>13377121.85957116</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/settlements/spark/2026-05/spark_settlement_may_2026.xlsx
+++ b/settlements/spark/2026-05/spark_settlement_may_2026.xlsx
@@ -662,7 +662,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-06-08T14:52:11+00:00</t>
+          <t>2026-06-08T16:54:34+00:00</t>
         </is>
       </c>
     </row>
@@ -689,7 +689,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S58"/>
+  <dimension ref="A1:S61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -4225,47 +4225,39 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>S56</t>
+          <t>PSM_CURVE_DEDUCT</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Spark Savings V2 — spUSDC vault</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>ethereum</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>S2</t>
-        </is>
-      </c>
+          <t>PSM3 USDS + PSM3 USDC (SDE) + Curve idle USDS — BR deduction (unattributed)</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr"/>
+      <c r="D54" t="inlineStr"/>
       <c r="E54" s="6" t="n">
-        <v>573332157.534611</v>
+        <v>0</v>
       </c>
       <c r="F54" s="6" t="n">
-        <v>303545287.192935</v>
+        <v>0</v>
       </c>
       <c r="G54" s="6" t="n">
-        <v>-269786870.341676</v>
+        <v>0</v>
       </c>
       <c r="H54" s="6" t="n">
-        <v>-2077933.247665395</v>
+        <v>0</v>
       </c>
       <c r="I54" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J54" s="6" t="n">
-        <v>-2077933.247665395</v>
+        <v>0</v>
       </c>
       <c r="K54" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L54" s="6" t="n">
-        <v>573332157.534611</v>
+        <v>0</v>
       </c>
       <c r="M54" s="7" t="n">
         <v>0</v>
@@ -4277,7 +4269,7 @@
         <v>0</v>
       </c>
       <c r="P54" s="6" t="n">
-        <v>-2077933.247665395</v>
+        <v>0</v>
       </c>
       <c r="Q54" s="6" t="n">
         <v>0</v>
@@ -4287,276 +4279,159 @@
       </c>
       <c r="S54" t="inlineStr">
         <is>
-          <t>CoF excluded (Savings V2 depositor capital; not in cum_alm_usds)</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>S57</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>Spark Savings V2 — spUSDT vault</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>ethereum</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>S2</t>
-        </is>
-      </c>
-      <c r="E55" s="6" t="n">
-        <v>1134703231.016836</v>
-      </c>
-      <c r="F55" s="6" t="n">
-        <v>1270360913.25412</v>
-      </c>
-      <c r="G55" s="6" t="n">
-        <v>135657682.237284</v>
-      </c>
-      <c r="H55" s="6" t="n">
-        <v>-2595205.75030597</v>
-      </c>
-      <c r="I55" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J55" s="6" t="n">
-        <v>-2595205.75030597</v>
-      </c>
-      <c r="K55" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L55" s="6" t="n">
-        <v>1134703231.016836</v>
-      </c>
-      <c r="M55" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N55" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O55" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P55" s="6" t="n">
-        <v>-2595205.75030597</v>
-      </c>
-      <c r="Q55" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R55" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S55" t="inlineStr">
-        <is>
-          <t>CoF excluded (Savings V2 depositor capital; not in cum_alm_usds)</t>
+          <t>BR deduction from PSM3 USDS leg + PSM3 USDC leg (SDE, ≈$0 yield) + Curve idle USDS — not tracked per-venue; residual = sky_rev_br_reduction − Σ(known venue deduction_avg × effective_br_rate × n_days)</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>S59</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>Spark Savings V2 — spPYUSD vault</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>ethereum</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>S2</t>
-        </is>
-      </c>
-      <c r="E56" s="6" t="n">
-        <v>1066559.875133</v>
-      </c>
-      <c r="F56" s="6" t="n">
-        <v>773533.783718</v>
-      </c>
-      <c r="G56" s="6" t="n">
-        <v>-293026.091415</v>
-      </c>
-      <c r="H56" s="6" t="n">
-        <v>-2640.43740244277</v>
-      </c>
-      <c r="I56" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J56" s="6" t="n">
-        <v>-2640.43740244277</v>
-      </c>
-      <c r="K56" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L56" s="6" t="n">
-        <v>1066559.875133</v>
-      </c>
-      <c r="M56" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N56" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O56" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P56" s="6" t="n">
-        <v>-2640.43740244277</v>
-      </c>
-      <c r="Q56" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R56" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S56" t="inlineStr">
-        <is>
-          <t>CoF excluded (Savings V2 depositor capital; not in cum_alm_usds)</t>
+      <c r="A56" s="8" t="inlineStr">
+        <is>
+          <t>Position-only venues (PnL aggregated at prime level)</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>S60</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>Spark Savings V2 — spUSDC vault (Avalanche-C, CREATE2 same address)</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>avalanche_c</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>S2</t>
-        </is>
-      </c>
-      <c r="E57" s="6" t="n">
-        <v>37138817.432463</v>
-      </c>
-      <c r="F57" s="6" t="n">
-        <v>25647247.422478</v>
-      </c>
-      <c r="G57" s="6" t="n">
-        <v>-11491570.009985</v>
-      </c>
-      <c r="H57" s="6" t="n">
-        <v>-94676.37115954701</v>
-      </c>
-      <c r="I57" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J57" s="6" t="n">
-        <v>-94676.37115954701</v>
-      </c>
-      <c r="K57" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L57" s="6" t="n">
-        <v>37138817.432463</v>
-      </c>
-      <c r="M57" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N57" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O57" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P57" s="6" t="n">
-        <v>-94676.37115954701</v>
-      </c>
-      <c r="Q57" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R57" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S57" t="inlineStr">
-        <is>
-          <t>CoF excluded (Savings V2 depositor capital; not in cum_alm_usds)</t>
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>Venue</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>Label</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>Chain</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>Pricing cat.</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>Position SoM</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>Position EoM</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>PSM_CURVE_DEDUCT</t>
+          <t>S56</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>PSM3 USDS + PSM3 USDC (SDE) + Curve idle USDS — BR deduction (unattributed)</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr"/>
-      <c r="D58" t="inlineStr"/>
+          <t>Spark Savings V2 — spUSDC vault</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>ethereum</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>S2</t>
+        </is>
+      </c>
       <c r="E58" s="6" t="n">
-        <v>0</v>
+        <v>573332157.534611</v>
       </c>
       <c r="F58" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G58" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H58" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I58" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J58" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K58" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L58" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M58" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N58" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O58" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P58" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q58" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R58" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S58" t="inlineStr">
-        <is>
-          <t>BR deduction from PSM3 USDS leg + PSM3 USDC leg (SDE, ≈$0 yield) + Curve idle USDS — not tracked per-venue; residual = sky_rev_br_reduction − Σ(known venue deduction_avg × effective_br_rate × n_days)</t>
-        </is>
+        <v>303545287.192935</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>S57</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Spark Savings V2 — spUSDT vault</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>ethereum</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>S2</t>
+        </is>
+      </c>
+      <c r="E59" s="6" t="n">
+        <v>1134703231.016836</v>
+      </c>
+      <c r="F59" s="6" t="n">
+        <v>1270360913.25412</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>S59</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Spark Savings V2 — spPYUSD vault</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>ethereum</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>S2</t>
+        </is>
+      </c>
+      <c r="E60" s="6" t="n">
+        <v>1066559.875133</v>
+      </c>
+      <c r="F60" s="6" t="n">
+        <v>773533.783718</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>S60</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Spark Savings V2 — spUSDC vault (Avalanche-C, CREATE2 same address)</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>avalanche_c</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>S2</t>
+        </is>
+      </c>
+      <c r="E61" s="6" t="n">
+        <v>37138817.432463</v>
+      </c>
+      <c r="F61" s="6" t="n">
+        <v>25647247.422478</v>
       </c>
     </row>
   </sheetData>

--- a/settlements/spark/2026-05/spark_settlement_may_2026.xlsx
+++ b/settlements/spark/2026-05/spark_settlement_may_2026.xlsx
@@ -75,7 +75,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -85,6 +85,7 @@
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -662,7 +663,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-06-08T16:54:34+00:00</t>
+          <t>2026-06-08T17:11:43+00:00</t>
         </is>
       </c>
     </row>
@@ -689,7 +690,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S61"/>
+  <dimension ref="A1:S62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -4434,6 +4435,20 @@
         <v>25647247.422478</v>
       </c>
     </row>
+    <row r="62">
+      <c r="A62" t="inlineStr"/>
+      <c r="B62" s="5" t="inlineStr">
+        <is>
+          <t>Aggregated actual_revenue (included in prime_agent_revenue, not in Venues body above)</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr"/>
+      <c r="D62" t="inlineStr"/>
+      <c r="E62" t="inlineStr"/>
+      <c r="F62" s="9" t="n">
+        <v>-4770455.806533354</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4539,14 +4554,14 @@
       </c>
     </row>
     <row r="13" ht="60" customHeight="1">
-      <c r="A13" s="9" t="inlineStr">
+      <c r="A13" s="10" t="inlineStr">
         <is>
           <t>Note: sky_revenue can EXCEED sky_revenue_gross for primes with active SDE positions — sky_revenue also adds sde_revenue on top of BR-on-utilized. The subsidised BR (ref_rate ramp) is already applied here; this is NOT the raw Maker base rate.</t>
         </is>
       </c>
     </row>
     <row r="15" ht="60" customHeight="1">
-      <c r="A15" s="9" t="inlineStr">
+      <c r="A15" s="10" t="inlineStr">
         <is>
           <t>sUSDS spread (Curve LP + PSM3) — 30 bps × value × n_days credited to prime_agent_revenue. Sky still charges full BR on the underlying utilized; this row is the prime's offsetting pickup on the share-price-appreciation accounting (SSR + BR + 30 bps nets to zero economically).</t>
         </is>
@@ -4866,7 +4881,7 @@
       </c>
     </row>
     <row r="3" ht="45" customHeight="1">
-      <c r="A3" s="9" t="inlineStr">
+      <c r="A3" s="10" t="inlineStr">
         <is>
           <t>cum_debt = Σ on-chain Vat dart from frob (0x76088703) + grab (0x7bab3f40). utilized = cum_debt − Σ deductions. base_apy = (1+SSR)(1+0.003)−1 (multiplicative). sub_apy applies on the first cap_usd of utilized when the subsidy is active; excess pays base_apy.</t>
         </is>
@@ -6485,10 +6500,10 @@
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr"/>
       <c r="M38" t="inlineStr"/>
-      <c r="N38" s="10" t="n">
+      <c r="N38" s="11" t="n">
         <v>10742059.80203898</v>
       </c>
-      <c r="O38" s="10" t="n">
+      <c r="O38" s="11" t="n">
         <v>13377121.85957116</v>
       </c>
     </row>

--- a/settlements/spark/2026-05/spark_settlement_may_2026.xlsx
+++ b/settlements/spark/2026-05/spark_settlement_may_2026.xlsx
@@ -75,7 +75,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -85,6 +85,7 @@
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -662,7 +663,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-06-08T14:52:11+00:00</t>
+          <t>2026-06-08T17:11:43+00:00</t>
         </is>
       </c>
     </row>
@@ -689,7 +690,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S58"/>
+  <dimension ref="A1:S62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -4225,47 +4226,39 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>S56</t>
+          <t>PSM_CURVE_DEDUCT</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Spark Savings V2 — spUSDC vault</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>ethereum</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>S2</t>
-        </is>
-      </c>
+          <t>PSM3 USDS + PSM3 USDC (SDE) + Curve idle USDS — BR deduction (unattributed)</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr"/>
+      <c r="D54" t="inlineStr"/>
       <c r="E54" s="6" t="n">
-        <v>573332157.534611</v>
+        <v>0</v>
       </c>
       <c r="F54" s="6" t="n">
-        <v>303545287.192935</v>
+        <v>0</v>
       </c>
       <c r="G54" s="6" t="n">
-        <v>-269786870.341676</v>
+        <v>0</v>
       </c>
       <c r="H54" s="6" t="n">
-        <v>-2077933.247665395</v>
+        <v>0</v>
       </c>
       <c r="I54" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J54" s="6" t="n">
-        <v>-2077933.247665395</v>
+        <v>0</v>
       </c>
       <c r="K54" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L54" s="6" t="n">
-        <v>573332157.534611</v>
+        <v>0</v>
       </c>
       <c r="M54" s="7" t="n">
         <v>0</v>
@@ -4277,7 +4270,7 @@
         <v>0</v>
       </c>
       <c r="P54" s="6" t="n">
-        <v>-2077933.247665395</v>
+        <v>0</v>
       </c>
       <c r="Q54" s="6" t="n">
         <v>0</v>
@@ -4287,276 +4280,173 @@
       </c>
       <c r="S54" t="inlineStr">
         <is>
-          <t>CoF excluded (Savings V2 depositor capital; not in cum_alm_usds)</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>S57</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>Spark Savings V2 — spUSDT vault</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>ethereum</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>S2</t>
-        </is>
-      </c>
-      <c r="E55" s="6" t="n">
-        <v>1134703231.016836</v>
-      </c>
-      <c r="F55" s="6" t="n">
-        <v>1270360913.25412</v>
-      </c>
-      <c r="G55" s="6" t="n">
-        <v>135657682.237284</v>
-      </c>
-      <c r="H55" s="6" t="n">
-        <v>-2595205.75030597</v>
-      </c>
-      <c r="I55" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J55" s="6" t="n">
-        <v>-2595205.75030597</v>
-      </c>
-      <c r="K55" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L55" s="6" t="n">
-        <v>1134703231.016836</v>
-      </c>
-      <c r="M55" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N55" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O55" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P55" s="6" t="n">
-        <v>-2595205.75030597</v>
-      </c>
-      <c r="Q55" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R55" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S55" t="inlineStr">
-        <is>
-          <t>CoF excluded (Savings V2 depositor capital; not in cum_alm_usds)</t>
+          <t>BR deduction from PSM3 USDS leg + PSM3 USDC leg (SDE, ≈$0 yield) + Curve idle USDS — not tracked per-venue; residual = sky_rev_br_reduction − Σ(known venue deduction_avg × effective_br_rate × n_days)</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>S59</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>Spark Savings V2 — spPYUSD vault</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>ethereum</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>S2</t>
-        </is>
-      </c>
-      <c r="E56" s="6" t="n">
-        <v>1066559.875133</v>
-      </c>
-      <c r="F56" s="6" t="n">
-        <v>773533.783718</v>
-      </c>
-      <c r="G56" s="6" t="n">
-        <v>-293026.091415</v>
-      </c>
-      <c r="H56" s="6" t="n">
-        <v>-2640.43740244277</v>
-      </c>
-      <c r="I56" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J56" s="6" t="n">
-        <v>-2640.43740244277</v>
-      </c>
-      <c r="K56" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L56" s="6" t="n">
-        <v>1066559.875133</v>
-      </c>
-      <c r="M56" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N56" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O56" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P56" s="6" t="n">
-        <v>-2640.43740244277</v>
-      </c>
-      <c r="Q56" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R56" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S56" t="inlineStr">
-        <is>
-          <t>CoF excluded (Savings V2 depositor capital; not in cum_alm_usds)</t>
+      <c r="A56" s="8" t="inlineStr">
+        <is>
+          <t>Position-only venues (PnL aggregated at prime level)</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>S60</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>Spark Savings V2 — spUSDC vault (Avalanche-C, CREATE2 same address)</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>avalanche_c</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>S2</t>
-        </is>
-      </c>
-      <c r="E57" s="6" t="n">
-        <v>37138817.432463</v>
-      </c>
-      <c r="F57" s="6" t="n">
-        <v>25647247.422478</v>
-      </c>
-      <c r="G57" s="6" t="n">
-        <v>-11491570.009985</v>
-      </c>
-      <c r="H57" s="6" t="n">
-        <v>-94676.37115954701</v>
-      </c>
-      <c r="I57" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J57" s="6" t="n">
-        <v>-94676.37115954701</v>
-      </c>
-      <c r="K57" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L57" s="6" t="n">
-        <v>37138817.432463</v>
-      </c>
-      <c r="M57" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N57" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O57" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P57" s="6" t="n">
-        <v>-94676.37115954701</v>
-      </c>
-      <c r="Q57" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R57" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S57" t="inlineStr">
-        <is>
-          <t>CoF excluded (Savings V2 depositor capital; not in cum_alm_usds)</t>
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>Venue</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>Label</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>Chain</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>Pricing cat.</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>Position SoM</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>Position EoM</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>PSM_CURVE_DEDUCT</t>
+          <t>S56</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>PSM3 USDS + PSM3 USDC (SDE) + Curve idle USDS — BR deduction (unattributed)</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr"/>
-      <c r="D58" t="inlineStr"/>
+          <t>Spark Savings V2 — spUSDC vault</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>ethereum</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>S2</t>
+        </is>
+      </c>
       <c r="E58" s="6" t="n">
-        <v>0</v>
+        <v>573332157.534611</v>
       </c>
       <c r="F58" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G58" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H58" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I58" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J58" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K58" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L58" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M58" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N58" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O58" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P58" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q58" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R58" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S58" t="inlineStr">
-        <is>
-          <t>BR deduction from PSM3 USDS leg + PSM3 USDC leg (SDE, ≈$0 yield) + Curve idle USDS — not tracked per-venue; residual = sky_rev_br_reduction − Σ(known venue deduction_avg × effective_br_rate × n_days)</t>
-        </is>
+        <v>303545287.192935</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>S57</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Spark Savings V2 — spUSDT vault</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>ethereum</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>S2</t>
+        </is>
+      </c>
+      <c r="E59" s="6" t="n">
+        <v>1134703231.016836</v>
+      </c>
+      <c r="F59" s="6" t="n">
+        <v>1270360913.25412</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>S59</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Spark Savings V2 — spPYUSD vault</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>ethereum</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>S2</t>
+        </is>
+      </c>
+      <c r="E60" s="6" t="n">
+        <v>1066559.875133</v>
+      </c>
+      <c r="F60" s="6" t="n">
+        <v>773533.783718</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>S60</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Spark Savings V2 — spUSDC vault (Avalanche-C, CREATE2 same address)</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>avalanche_c</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>S2</t>
+        </is>
+      </c>
+      <c r="E61" s="6" t="n">
+        <v>37138817.432463</v>
+      </c>
+      <c r="F61" s="6" t="n">
+        <v>25647247.422478</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr"/>
+      <c r="B62" s="5" t="inlineStr">
+        <is>
+          <t>Aggregated actual_revenue (included in prime_agent_revenue, not in Venues body above)</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr"/>
+      <c r="D62" t="inlineStr"/>
+      <c r="E62" t="inlineStr"/>
+      <c r="F62" s="9" t="n">
+        <v>-4770455.806533354</v>
       </c>
     </row>
   </sheetData>
@@ -4664,14 +4554,14 @@
       </c>
     </row>
     <row r="13" ht="60" customHeight="1">
-      <c r="A13" s="9" t="inlineStr">
+      <c r="A13" s="10" t="inlineStr">
         <is>
           <t>Note: sky_revenue can EXCEED sky_revenue_gross for primes with active SDE positions — sky_revenue also adds sde_revenue on top of BR-on-utilized. The subsidised BR (ref_rate ramp) is already applied here; this is NOT the raw Maker base rate.</t>
         </is>
       </c>
     </row>
     <row r="15" ht="60" customHeight="1">
-      <c r="A15" s="9" t="inlineStr">
+      <c r="A15" s="10" t="inlineStr">
         <is>
           <t>sUSDS spread (Curve LP + PSM3) — 30 bps × value × n_days credited to prime_agent_revenue. Sky still charges full BR on the underlying utilized; this row is the prime's offsetting pickup on the share-price-appreciation accounting (SSR + BR + 30 bps nets to zero economically).</t>
         </is>
@@ -4991,7 +4881,7 @@
       </c>
     </row>
     <row r="3" ht="45" customHeight="1">
-      <c r="A3" s="9" t="inlineStr">
+      <c r="A3" s="10" t="inlineStr">
         <is>
           <t>cum_debt = Σ on-chain Vat dart from frob (0x76088703) + grab (0x7bab3f40). utilized = cum_debt − Σ deductions. base_apy = (1+SSR)(1+0.003)−1 (multiplicative). sub_apy applies on the first cap_usd of utilized when the subsidy is active; excess pays base_apy.</t>
         </is>
@@ -6610,10 +6500,10 @@
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr"/>
       <c r="M38" t="inlineStr"/>
-      <c r="N38" s="10" t="n">
+      <c r="N38" s="11" t="n">
         <v>10742059.80203898</v>
       </c>
-      <c r="O38" s="10" t="n">
+      <c r="O38" s="11" t="n">
         <v>13377121.85957116</v>
       </c>
     </row>

--- a/settlements/spark/2026-05/spark_settlement_may_2026.xlsx
+++ b/settlements/spark/2026-05/spark_settlement_may_2026.xlsx
@@ -488,7 +488,7 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>8471023.892760478</v>
+        <v>7865873.684241995</v>
       </c>
     </row>
     <row r="5">
@@ -498,13 +498,13 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>0</v>
+        <v>121639.2149998229</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
       <c r="B6" s="4" t="n">
-        <v>8471023.892760478</v>
+        <v>7987512.899241818</v>
       </c>
     </row>
     <row r="8">
@@ -526,7 +526,7 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>10234615.9342856</v>
+        <v>10840739.61571033</v>
       </c>
     </row>
     <row r="10">
@@ -542,7 +542,7 @@
     <row r="11">
       <c r="A11" t="inlineStr"/>
       <c r="B11" s="4" t="n">
-        <v>10308771.99513011</v>
+        <v>10914895.67655484</v>
       </c>
     </row>
     <row r="13">
@@ -564,7 +564,7 @@
         </is>
       </c>
       <c r="B14" s="3" t="n">
-        <v>10234615.9342856</v>
+        <v>10840739.61571033</v>
       </c>
     </row>
     <row r="15">
@@ -580,13 +580,13 @@
     <row r="16">
       <c r="A16" t="inlineStr"/>
       <c r="B16" s="4" t="n">
-        <v>13377121.85957116</v>
+        <v>13983245.54099589</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>sUSDS spread (Curve LP + PSM3) — credited to prime_agent_revenue</t>
+          <t>sUSDS spread (Curve LP + PSM3) — deducted from sky_revenue</t>
         </is>
       </c>
       <c r="B18" s="3" t="n">
@@ -612,7 +612,7 @@
         </is>
       </c>
       <c r="B21" s="3" t="n">
-        <v>8471023.892760478</v>
+        <v>7865873.684241995</v>
       </c>
     </row>
     <row r="22">
@@ -622,13 +622,13 @@
         </is>
       </c>
       <c r="B22" s="3" t="n">
-        <v>-10234615.9342856</v>
+        <v>-10840739.61571033</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr"/>
       <c r="B23" s="4" t="n">
-        <v>-1948502.4602201</v>
+        <v>-3159776.350163311</v>
       </c>
     </row>
     <row r="25">
@@ -663,7 +663,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-06-08T17:11:43+00:00</t>
+          <t>2026-06-09T14:50:47+00:00</t>
         </is>
       </c>
     </row>
@@ -860,13 +860,13 @@
         <v>1</v>
       </c>
       <c r="N2" s="6" t="n">
-        <v>4167822.764039975</v>
+        <v>4410254.829322996</v>
       </c>
       <c r="O2" s="6" t="n">
-        <v>4167822.764039975</v>
+        <v>4410254.829322996</v>
       </c>
       <c r="P2" s="6" t="n">
-        <v>-4167822.764039975</v>
+        <v>-4410254.829322996</v>
       </c>
       <c r="Q2" s="6" t="n">
         <v>0</v>
@@ -925,13 +925,13 @@
         <v>1</v>
       </c>
       <c r="N3" s="6" t="n">
-        <v>1473003.887406189</v>
+        <v>1558684.923959588</v>
       </c>
       <c r="O3" s="6" t="n">
-        <v>1473003.887406189</v>
+        <v>1558684.923959588</v>
       </c>
       <c r="P3" s="6" t="n">
-        <v>395108.2808298113</v>
+        <v>309427.2442764115</v>
       </c>
       <c r="Q3" s="6" t="n">
         <v>0</v>
@@ -990,13 +990,13 @@
         <v>1</v>
       </c>
       <c r="N4" s="6" t="n">
-        <v>1349597.02588841</v>
+        <v>1428099.786876452</v>
       </c>
       <c r="O4" s="6" t="n">
-        <v>1349597.02588841</v>
+        <v>1428099.786876452</v>
       </c>
       <c r="P4" s="6" t="n">
-        <v>1741982.97411159</v>
+        <v>1663480.213123548</v>
       </c>
       <c r="Q4" s="6" t="n">
         <v>0</v>
@@ -1055,13 +1055,13 @@
         <v>1</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>1183578.826270314</v>
+        <v>1252424.714284955</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>1183578.826270314</v>
+        <v>1252424.714284955</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>-1378023.270714268</v>
+        <v>-1446869.158728908</v>
       </c>
       <c r="Q5" s="6" t="n">
         <v>0</v>
@@ -1120,13 +1120,13 @@
         <v>1</v>
       </c>
       <c r="N6" s="6" t="n">
-        <v>393717.3565437027</v>
+        <v>416618.9330474357</v>
       </c>
       <c r="O6" s="6" t="n">
-        <v>393717.3565437027</v>
+        <v>416618.9330474357</v>
       </c>
       <c r="P6" s="6" t="n">
-        <v>165735.5826975166</v>
+        <v>142834.0061937836</v>
       </c>
       <c r="Q6" s="6" t="n">
         <v>86642406.62655522</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="N7" s="6" t="n">
-        <v>314291.9993735298</v>
+        <v>332573.59694228</v>
       </c>
       <c r="O7" s="6" t="n">
-        <v>277827.1855317322</v>
+        <v>296108.7831004824</v>
       </c>
       <c r="P7" s="6" t="n">
-        <v>-314291.9993735298</v>
+        <v>-332573.59694228</v>
       </c>
       <c r="Q7" s="6" t="n">
         <v>0</v>
@@ -1254,13 +1254,13 @@
         <v>1</v>
       </c>
       <c r="N8" s="6" t="n">
-        <v>230418.5138801736</v>
+        <v>243821.3957592647</v>
       </c>
       <c r="O8" s="6" t="n">
-        <v>230418.5138801736</v>
+        <v>243821.3957592647</v>
       </c>
       <c r="P8" s="6" t="n">
-        <v>193112.0947030281</v>
+        <v>179709.2128239369</v>
       </c>
       <c r="Q8" s="6" t="n">
         <v>0</v>
@@ -1319,13 +1319,13 @@
         <v>1</v>
       </c>
       <c r="N9" s="6" t="n">
-        <v>219281.0959016976</v>
+        <v>232036.1413934696</v>
       </c>
       <c r="O9" s="6" t="n">
-        <v>219281.0959016976</v>
+        <v>232036.1413934696</v>
       </c>
       <c r="P9" s="6" t="n">
-        <v>-190277.1252016976</v>
+        <v>-203032.1706934696</v>
       </c>
       <c r="Q9" s="6" t="n">
         <v>0</v>
@@ -1384,13 +1384,13 @@
         <v>1</v>
       </c>
       <c r="N10" s="6" t="n">
-        <v>219277.4654279028</v>
+        <v>232032.2997438859</v>
       </c>
       <c r="O10" s="6" t="n">
-        <v>219277.4654279028</v>
+        <v>232032.2997438859</v>
       </c>
       <c r="P10" s="6" t="n">
-        <v>-212891.5815562624</v>
+        <v>-225646.4158722456</v>
       </c>
       <c r="Q10" s="6" t="n">
         <v>0</v>
@@ -1449,13 +1449,13 @@
         <v>1</v>
       </c>
       <c r="N11" s="6" t="n">
-        <v>223756.2828300607</v>
+        <v>236771.6390094491</v>
       </c>
       <c r="O11" s="6" t="n">
-        <v>197795.6118120444</v>
+        <v>210810.9679914328</v>
       </c>
       <c r="P11" s="6" t="n">
-        <v>-223756.2828300607</v>
+        <v>-236771.6390094491</v>
       </c>
       <c r="Q11" s="6" t="n">
         <v>0</v>
@@ -1514,13 +1514,13 @@
         <v>1</v>
       </c>
       <c r="N12" s="6" t="n">
-        <v>196519.3159684765</v>
+        <v>207950.3643444547</v>
       </c>
       <c r="O12" s="6" t="n">
-        <v>196519.3159684765</v>
+        <v>207950.3643444547</v>
       </c>
       <c r="P12" s="6" t="n">
-        <v>20750.08047808185</v>
+        <v>9319.032102103598</v>
       </c>
       <c r="Q12" s="6" t="n">
         <v>0</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="N13" s="6" t="n">
-        <v>166155.4201387819</v>
+        <v>175820.2748945458</v>
       </c>
       <c r="O13" s="6" t="n">
-        <v>146877.7214501635</v>
+        <v>156542.5762059274</v>
       </c>
       <c r="P13" s="6" t="n">
-        <v>-166155.4201387819</v>
+        <v>-175820.2748945458</v>
       </c>
       <c r="Q13" s="6" t="n">
         <v>0</v>
@@ -1644,13 +1644,13 @@
         <v>1</v>
       </c>
       <c r="N14" s="6" t="n">
-        <v>126593.836691988</v>
+        <v>133957.490815224</v>
       </c>
       <c r="O14" s="6" t="n">
-        <v>126593.836691988</v>
+        <v>133957.490815224</v>
       </c>
       <c r="P14" s="6" t="n">
-        <v>167497.6801844561</v>
+        <v>160134.02606122</v>
       </c>
       <c r="Q14" s="6" t="n">
         <v>103099818.9104406</v>
@@ -1843,13 +1843,13 @@
         <v>1</v>
       </c>
       <c r="N17" s="6" t="n">
-        <v>65067.17882175036</v>
+        <v>68851.97760926072</v>
       </c>
       <c r="O17" s="6" t="n">
-        <v>65067.17882175036</v>
+        <v>68851.97760926072</v>
       </c>
       <c r="P17" s="6" t="n">
-        <v>54574.43910422226</v>
+        <v>50789.6403167119</v>
       </c>
       <c r="Q17" s="6" t="n">
         <v>0</v>
@@ -1908,13 +1908,13 @@
         <v>1</v>
       </c>
       <c r="N18" s="6" t="n">
-        <v>20866.96526236113</v>
+        <v>22080.74563910623</v>
       </c>
       <c r="O18" s="6" t="n">
-        <v>20866.96526236113</v>
+        <v>22080.74563910623</v>
       </c>
       <c r="P18" s="6" t="n">
-        <v>834.506240336483</v>
+        <v>-379.2741364086218</v>
       </c>
       <c r="Q18" s="6" t="n">
         <v>0</v>
@@ -1973,13 +1973,13 @@
         <v>1</v>
       </c>
       <c r="N19" s="6" t="n">
-        <v>20445.85693754033</v>
+        <v>21635.14247209228</v>
       </c>
       <c r="O19" s="6" t="n">
-        <v>20445.85693754033</v>
+        <v>21635.14247209228</v>
       </c>
       <c r="P19" s="6" t="n">
-        <v>12057.04641545967</v>
+        <v>10867.76088090771</v>
       </c>
       <c r="Q19" s="6" t="n">
         <v>0</v>
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="N20" s="6" t="n">
-        <v>10961.84976257375</v>
+        <v>11599.47377580961</v>
       </c>
       <c r="O20" s="6" t="n">
-        <v>10961.84976257375</v>
+        <v>11599.47377580961</v>
       </c>
       <c r="P20" s="6" t="n">
-        <v>-10961.84976257152</v>
+        <v>-11599.47377580738</v>
       </c>
       <c r="Q20" s="6" t="n">
         <v>0</v>
@@ -2103,13 +2103,13 @@
         <v>1</v>
       </c>
       <c r="N21" s="6" t="n">
-        <v>10961.12595799393</v>
+        <v>11598.70786928614</v>
       </c>
       <c r="O21" s="6" t="n">
-        <v>10961.12595799393</v>
+        <v>11598.70786928614</v>
       </c>
       <c r="P21" s="6" t="n">
-        <v>-10961.12595799374</v>
+        <v>-11598.70786928596</v>
       </c>
       <c r="Q21" s="6" t="n">
         <v>0</v>
@@ -2168,13 +2168,13 @@
         <v>1</v>
       </c>
       <c r="N22" s="6" t="n">
-        <v>10959.09351594223</v>
+        <v>11596.55720504697</v>
       </c>
       <c r="O22" s="6" t="n">
-        <v>10959.09351594223</v>
+        <v>11596.55720504697</v>
       </c>
       <c r="P22" s="6" t="n">
-        <v>-10959.09351594223</v>
+        <v>-11596.55720504697</v>
       </c>
       <c r="Q22" s="6" t="n">
         <v>0</v>
@@ -2233,13 +2233,13 @@
         <v>1</v>
       </c>
       <c r="N23" s="6" t="n">
-        <v>10864.34675478342</v>
+        <v>11496.29925632405</v>
       </c>
       <c r="O23" s="6" t="n">
-        <v>10864.34675478342</v>
+        <v>11496.29925632405</v>
       </c>
       <c r="P23" s="6" t="n">
-        <v>-10864.34675478295</v>
+        <v>-11496.29925632357</v>
       </c>
       <c r="Q23" s="6" t="n">
         <v>0</v>
@@ -2280,31 +2280,31 @@
         <v>2796996.33696637</v>
       </c>
       <c r="H24" s="6" t="n">
-        <v>609955.0966986277</v>
+        <v>4804.888180144989</v>
       </c>
       <c r="I24" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J24" s="6" t="n">
-        <v>609955.0966986277</v>
+        <v>4804.888180144989</v>
       </c>
       <c r="K24" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L24" s="6" t="n">
-        <v>1472511.375313347</v>
+        <v>1492032.349781685</v>
       </c>
       <c r="M24" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N24" s="6" t="n">
-        <v>3228.934391728406</v>
+        <v>3462.049264890436</v>
       </c>
       <c r="O24" s="6" t="n">
-        <v>3228.934391728406</v>
+        <v>3462.049264890436</v>
       </c>
       <c r="P24" s="6" t="n">
-        <v>606726.1623068993</v>
+        <v>1342.838915254552</v>
       </c>
       <c r="Q24" s="6" t="n">
         <v>0</v>
@@ -2363,13 +2363,13 @@
         <v>1</v>
       </c>
       <c r="N25" s="6" t="n">
-        <v>2154.232305888279</v>
+        <v>2279.53873482809</v>
       </c>
       <c r="O25" s="6" t="n">
-        <v>1904.293776868191</v>
+        <v>2029.600205808002</v>
       </c>
       <c r="P25" s="6" t="n">
-        <v>-2154.232305888279</v>
+        <v>-2279.53873482809</v>
       </c>
       <c r="Q25" s="6" t="n">
         <v>0</v>
@@ -2428,13 +2428,13 @@
         <v>1</v>
       </c>
       <c r="N26" s="6" t="n">
-        <v>1.013431751019421</v>
+        <v>1.072380599454827</v>
       </c>
       <c r="O26" s="6" t="n">
-        <v>1.013431751019421</v>
+        <v>1.072380599454827</v>
       </c>
       <c r="P26" s="6" t="n">
-        <v>75.31703376818632</v>
+        <v>75.25808491975091</v>
       </c>
       <c r="Q26" s="6" t="n">
         <v>0</v>
@@ -2493,13 +2493,13 @@
         <v>1</v>
       </c>
       <c r="N27" s="6" t="n">
-        <v>0.807045574158881</v>
+        <v>0.8539894430318479</v>
       </c>
       <c r="O27" s="6" t="n">
-        <v>0.807045574158881</v>
+        <v>0.8539894430318479</v>
       </c>
       <c r="P27" s="6" t="n">
-        <v>0.3542997011788971</v>
+        <v>0.3073558323059302</v>
       </c>
       <c r="Q27" s="6" t="n">
         <v>0</v>
@@ -2558,13 +2558,13 @@
         <v>1</v>
       </c>
       <c r="N28" s="6" t="n">
-        <v>0.6225320944278722</v>
+        <v>0.6587432650801534</v>
       </c>
       <c r="O28" s="6" t="n">
-        <v>0.6225320944278722</v>
+        <v>0.6587432650801534</v>
       </c>
       <c r="P28" s="6" t="n">
-        <v>-0.6225320944278722</v>
+        <v>-0.6587432650801534</v>
       </c>
       <c r="Q28" s="6" t="n">
         <v>0</v>
@@ -2623,13 +2623,13 @@
         <v>1</v>
       </c>
       <c r="N29" s="6" t="n">
-        <v>0.2528534828828865</v>
+        <v>0.267561352084571</v>
       </c>
       <c r="O29" s="6" t="n">
-        <v>0.2528534828828865</v>
+        <v>0.267561352084571</v>
       </c>
       <c r="P29" s="6" t="n">
-        <v>-0.2528534832133453</v>
+        <v>-0.2675613524150298</v>
       </c>
       <c r="Q29" s="6" t="n">
         <v>0</v>
@@ -2688,13 +2688,13 @@
         <v>1</v>
       </c>
       <c r="N30" s="6" t="n">
-        <v>0.2181872112413053</v>
+        <v>0.2308786281355063</v>
       </c>
       <c r="O30" s="6" t="n">
-        <v>0.2181872112413053</v>
+        <v>0.2308786281355063</v>
       </c>
       <c r="P30" s="6" t="n">
-        <v>0.09357633719282084</v>
+        <v>0.08088492029861985</v>
       </c>
       <c r="Q30" s="6" t="n">
         <v>0</v>
@@ -2753,13 +2753,13 @@
         <v>1</v>
       </c>
       <c r="N31" s="6" t="n">
-        <v>0.04803697741683239</v>
+        <v>0.050831171005292</v>
       </c>
       <c r="O31" s="6" t="n">
-        <v>0.04803697741683239</v>
+        <v>0.050831171005292</v>
       </c>
       <c r="P31" s="6" t="n">
-        <v>-0.04803092370966239</v>
+        <v>-0.05082511729812201</v>
       </c>
       <c r="Q31" s="6" t="n">
         <v>0</v>
@@ -2818,13 +2818,13 @@
         <v>1</v>
       </c>
       <c r="N32" s="6" t="n">
-        <v>0.01293289080298069</v>
+        <v>0.01368516545690748</v>
       </c>
       <c r="O32" s="6" t="n">
-        <v>0.01293289080298069</v>
+        <v>0.01368516545690748</v>
       </c>
       <c r="P32" s="6" t="n">
-        <v>0.002457109197019311</v>
+        <v>0.001704834543092515</v>
       </c>
       <c r="Q32" s="6" t="n">
         <v>0</v>
@@ -2883,13 +2883,13 @@
         <v>1</v>
       </c>
       <c r="N33" s="6" t="n">
-        <v>0.003389223431433898</v>
+        <v>0.003586366276201048</v>
       </c>
       <c r="O33" s="6" t="n">
-        <v>0.003389223431433898</v>
+        <v>0.003586366276201048</v>
       </c>
       <c r="P33" s="6" t="n">
-        <v>8.466999776568565</v>
+        <v>8.466802633723798</v>
       </c>
       <c r="Q33" s="6" t="n">
         <v>0</v>
@@ -2948,13 +2948,13 @@
         <v>1</v>
       </c>
       <c r="N34" s="6" t="n">
-        <v>0.0003386374974134909</v>
+        <v>0.0003583352131101747</v>
       </c>
       <c r="O34" s="6" t="n">
-        <v>0.0003386374974134909</v>
+        <v>0.0003583352131101747</v>
       </c>
       <c r="P34" s="6" t="n">
-        <v>0.0003953625025865091</v>
+        <v>0.0003756647868898253</v>
       </c>
       <c r="Q34" s="6" t="n">
         <v>0</v>
@@ -3013,13 +3013,13 @@
         <v>1</v>
       </c>
       <c r="N35" s="6" t="n">
-        <v>0.0001267070116300726</v>
+        <v>0.0001340772488628917</v>
       </c>
       <c r="O35" s="6" t="n">
-        <v>0.0001267070116300726</v>
+        <v>0.0001340772488628917</v>
       </c>
       <c r="P35" s="6" t="n">
-        <v>5.929298836992738e-05</v>
+        <v>5.192275113710832e-05</v>
       </c>
       <c r="Q35" s="6" t="n">
         <v>0</v>
@@ -3078,13 +3078,13 @@
         <v>1</v>
       </c>
       <c r="N36" s="6" t="n">
-        <v>1.391555813655298e-05</v>
+        <v>1.472499214793124e-05</v>
       </c>
       <c r="O36" s="6" t="n">
-        <v>1.391555813655298e-05</v>
+        <v>1.472499214793124e-05</v>
       </c>
       <c r="P36" s="6" t="n">
-        <v>3.08444186344702e-06</v>
+        <v>2.275007852068764e-06</v>
       </c>
       <c r="Q36" s="6" t="n">
         <v>0</v>
@@ -3143,13 +3143,13 @@
         <v>1</v>
       </c>
       <c r="N37" s="6" t="n">
-        <v>1.259610861851073e-05</v>
+        <v>1.332879347576094e-05</v>
       </c>
       <c r="O37" s="6" t="n">
-        <v>1.259610861851073e-05</v>
+        <v>1.332879347576094e-05</v>
       </c>
       <c r="P37" s="6" t="n">
-        <v>-1.045228411314073e-05</v>
+        <v>-1.118496897039094e-05</v>
       </c>
       <c r="Q37" s="6" t="n">
         <v>0</v>
@@ -3208,13 +3208,13 @@
         <v>1</v>
       </c>
       <c r="N38" s="6" t="n">
-        <v>3.727773216536412e-06</v>
+        <v>3.944608674989458e-06</v>
       </c>
       <c r="O38" s="6" t="n">
-        <v>3.727773216536412e-06</v>
+        <v>3.944608674989458e-06</v>
       </c>
       <c r="P38" s="6" t="n">
-        <v>1.272226783463589e-06</v>
+        <v>1.055391325010542e-06</v>
       </c>
       <c r="Q38" s="6" t="n">
         <v>0</v>
@@ -3273,13 +3273,13 @@
         <v>1</v>
       </c>
       <c r="N39" s="6" t="n">
-        <v>2.719398874916082e-06</v>
+        <v>2.877579662079685e-06</v>
       </c>
       <c r="O39" s="6" t="n">
-        <v>2.719398874916082e-06</v>
+        <v>2.877579662079685e-06</v>
       </c>
       <c r="P39" s="6" t="n">
-        <v>-2.719398874916082e-06</v>
+        <v>-2.877579662079685e-06</v>
       </c>
       <c r="Q39" s="6" t="n">
         <v>0</v>
@@ -3338,13 +3338,13 @@
         <v>1</v>
       </c>
       <c r="N40" s="6" t="n">
-        <v>1.142379532868556e-06</v>
+        <v>1.208828958664657e-06</v>
       </c>
       <c r="O40" s="6" t="n">
-        <v>1.142379532868556e-06</v>
+        <v>1.208828958664657e-06</v>
       </c>
       <c r="P40" s="6" t="n">
-        <v>-4.356727260595558e-07</v>
+        <v>-5.021221518556572e-07</v>
       </c>
       <c r="Q40" s="6" t="n">
         <v>0</v>
@@ -3403,13 +3403,13 @@
         <v>1</v>
       </c>
       <c r="N41" s="6" t="n">
-        <v>1.642331360647951e-07</v>
+        <v>1.737861762534574e-07</v>
       </c>
       <c r="O41" s="6" t="n">
-        <v>1.642331360647951e-07</v>
+        <v>1.737861762534574e-07</v>
       </c>
       <c r="P41" s="6" t="n">
-        <v>-1.642331360647951e-07</v>
+        <v>-1.737861762534574e-07</v>
       </c>
       <c r="Q41" s="6" t="n">
         <v>0</v>
@@ -4493,7 +4493,7 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>10234615.9342856</v>
+        <v>10840739.61571033</v>
       </c>
     </row>
     <row r="5">
@@ -4513,7 +4513,7 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>10308771.99513011</v>
+        <v>10914895.67655484</v>
       </c>
     </row>
     <row r="8">
@@ -4530,7 +4530,7 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>13377121.85957116</v>
+        <v>13983245.54099589</v>
       </c>
     </row>
     <row r="11">
@@ -4540,7 +4540,7 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>10234615.9342856</v>
+        <v>10840739.61571033</v>
       </c>
     </row>
     <row r="12">
@@ -4563,7 +4563,7 @@
     <row r="15" ht="60" customHeight="1">
       <c r="A15" s="10" t="inlineStr">
         <is>
-          <t>sUSDS spread (Curve LP + PSM3) — 30 bps × value × n_days credited to prime_agent_revenue. Sky still charges full BR on the underlying utilized; this row is the prime's offsetting pickup on the share-price-appreciation accounting (SSR + BR + 30 bps nets to zero economically).</t>
+          <t>sUSDS spread (Curve LP + PSM3) — 30 bps × value × n_days deducted from sky_revenue. Sky charges full BR on the underlying utilized; this row is the offsetting refund to the prime so SSR + BR + 30 bps nets to zero economically.</t>
         </is>
       </c>
       <c r="B15" s="3" t="n">
@@ -4883,7 +4883,7 @@
     <row r="3" ht="45" customHeight="1">
       <c r="A3" s="10" t="inlineStr">
         <is>
-          <t>cum_debt = Σ on-chain Vat dart from frob (0x76088703) + grab (0x7bab3f40). utilized = cum_debt − Σ deductions. base_apy = (1+SSR)(1+0.003)−1 (multiplicative). sub_apy applies on the first cap_usd of utilized when the subsidy is active; excess pays base_apy.</t>
+          <t>cum_debt = Σ on-chain Vat dart from frob (0x76088703) + grab (0x7bab3f40), then scaled by Vat.ilks[ilk].rate_d / 1e27 read at each day's EoD block — actual outstanding USDS per day, not raw normalised Art. utilized = cum_debt − Σ deductions. base_apy = (1+SSR)(1+0.003)−1 (multiplicative). sub_apy applies on the first cap_usd of utilized when the subsidy is active; excess pays base_apy.</t>
         </is>
       </c>
     </row>
@@ -4970,7 +4970,7 @@
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>3786873547.945224</v>
+        <v>3958458569.003264</v>
       </c>
       <c r="C6" s="6" t="n">
         <v>334970000</v>
@@ -4988,7 +4988,7 @@
         <v>127906874.3387326</v>
       </c>
       <c r="H6" s="6" t="n">
-        <v>3064694189.09428</v>
+        <v>3236279210.15232</v>
       </c>
       <c r="I6" s="7" t="n">
         <v>0.0375</v>
@@ -5006,10 +5006,10 @@
         <v>0.0406125</v>
       </c>
       <c r="N6" s="3" t="n">
-        <v>334275.4575777341</v>
+        <v>352990.7544030308</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>413045.742878023</v>
+        <v>431761.0397033197</v>
       </c>
     </row>
     <row r="7">
@@ -5019,7 +5019,7 @@
         </is>
       </c>
       <c r="B7" s="6" t="n">
-        <v>4113602587.50019</v>
+        <v>4299991854.969555</v>
       </c>
       <c r="C7" s="6" t="n">
         <v>334970000</v>
@@ -5037,7 +5037,7 @@
         <v>131684974.1461452</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>3396951901.175869</v>
+        <v>3583341168.645234</v>
       </c>
       <c r="I7" s="7" t="n">
         <v>0.0375</v>
@@ -5055,10 +5055,10 @@
         <v>0.0406125</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>370515.8104113157</v>
+        <v>390845.8511353183</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>448683.0666899128</v>
+        <v>469013.1074139154</v>
       </c>
     </row>
     <row r="8">
@@ -5068,7 +5068,7 @@
         </is>
       </c>
       <c r="B8" s="6" t="n">
-        <v>4112495173.033005</v>
+        <v>4298834263.032152</v>
       </c>
       <c r="C8" s="6" t="n">
         <v>334970000</v>
@@ -5086,7 +5086,7 @@
         <v>129926697.4882286</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>3390890511.133594</v>
+        <v>3577229601.132741</v>
       </c>
       <c r="I8" s="7" t="n">
         <v>0.0375</v>
@@ -5104,10 +5104,10 @@
         <v>0.0406125</v>
       </c>
       <c r="N8" s="3" t="n">
-        <v>369854.6762801686</v>
+        <v>390179.243995844</v>
       </c>
       <c r="O8" s="3" t="n">
-        <v>448562.277647057</v>
+        <v>468886.8453627324</v>
       </c>
     </row>
     <row r="9">
@@ -5117,7 +5117,7 @@
         </is>
       </c>
       <c r="B9" s="6" t="n">
-        <v>4014386628.19746</v>
+        <v>4196280373.899142</v>
       </c>
       <c r="C9" s="6" t="n">
         <v>334970000</v>
@@ -5135,7 +5135,7 @@
         <v>129945312.0277757</v>
       </c>
       <c r="H9" s="6" t="n">
-        <v>3300217558.653535</v>
+        <v>3482111304.355217</v>
       </c>
       <c r="I9" s="7" t="n">
         <v>0.0375</v>
@@ -5153,10 +5153,10 @@
         <v>0.0406125</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>359964.7033138436</v>
+        <v>379804.4038919058</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>437861.2821500545</v>
+        <v>457700.9827281167</v>
       </c>
     </row>
     <row r="10">
@@ -5166,7 +5166,7 @@
         </is>
       </c>
       <c r="B10" s="6" t="n">
-        <v>3967538459.305897</v>
+        <v>4147309492.446936</v>
       </c>
       <c r="C10" s="6" t="n">
         <v>334970000</v>
@@ -5184,7 +5184,7 @@
         <v>129991339.9884334</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>3258291889.719903</v>
+        <v>3438062922.860942</v>
       </c>
       <c r="I10" s="7" t="n">
         <v>0.0375</v>
@@ -5202,10 +5202,10 @@
         <v>0.0406125</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>355391.7438920149</v>
+        <v>374999.9137956497</v>
       </c>
       <c r="O10" s="3" t="n">
-        <v>432751.4107806262</v>
+        <v>452359.580684261</v>
       </c>
     </row>
     <row r="11">
@@ -5215,7 +5215,7 @@
         </is>
       </c>
       <c r="B11" s="6" t="n">
-        <v>3773637803.723945</v>
+        <v>3944623106.987827</v>
       </c>
       <c r="C11" s="6" t="n">
         <v>334970000</v>
@@ -5233,7 +5233,7 @@
         <v>132866251.0455103</v>
       </c>
       <c r="H11" s="6" t="n">
-        <v>3061037681.897975</v>
+        <v>3232022985.161858</v>
       </c>
       <c r="I11" s="7" t="n">
         <v>0.0375</v>
@@ -5251,10 +5251,10 @@
         <v>0.0406125</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>333876.6312868336</v>
+        <v>352526.5150798046</v>
       </c>
       <c r="O11" s="3" t="n">
-        <v>411602.080253643</v>
+        <v>430251.9640466141</v>
       </c>
     </row>
     <row r="12">
@@ -5264,7 +5264,7 @@
         </is>
       </c>
       <c r="B12" s="6" t="n">
-        <v>3829641619.123199</v>
+        <v>4003164481.596004</v>
       </c>
       <c r="C12" s="6" t="n">
         <v>334970000</v>
@@ -5282,7 +5282,7 @@
         <v>133190285.3282568</v>
       </c>
       <c r="H12" s="6" t="n">
-        <v>3123331493.311244</v>
+        <v>3296854355.784049</v>
       </c>
       <c r="I12" s="7" t="n">
         <v>0.0375</v>
@@ -5300,10 +5300,10 @@
         <v>0.0406125</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>340671.2055672075</v>
+        <v>359597.8686123178</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>417710.5856586202</v>
+        <v>436637.2487037305</v>
       </c>
     </row>
     <row r="13">
@@ -5313,7 +5313,7 @@
         </is>
       </c>
       <c r="B13" s="6" t="n">
-        <v>3112489658.938523</v>
+        <v>3253518028.888103</v>
       </c>
       <c r="C13" s="6" t="n">
         <v>334970000</v>
@@ -5331,7 +5331,7 @@
         <v>136081135.6656561</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>2423139600.328023</v>
+        <v>2564167970.277603</v>
       </c>
       <c r="I13" s="7" t="n">
         <v>0.0375</v>
@@ -5349,10 +5349,10 @@
         <v>0.0406125</v>
       </c>
       <c r="N13" s="3" t="n">
-        <v>264299.1596214559</v>
+        <v>279681.550159505</v>
       </c>
       <c r="O13" s="3" t="n">
-        <v>339488.6539250828</v>
+        <v>354871.0444631319</v>
       </c>
     </row>
     <row r="14">
@@ -5362,7 +5362,7 @@
         </is>
       </c>
       <c r="B14" s="6" t="n">
-        <v>3862142308.882361</v>
+        <v>4037137792.890086</v>
       </c>
       <c r="C14" s="6" t="n">
         <v>334970000</v>
@@ -5380,7 +5380,7 @@
         <v>136418480.8456975</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>3158250277.049653</v>
+        <v>3333245761.057378</v>
       </c>
       <c r="I14" s="7" t="n">
         <v>0.0375</v>
@@ -5398,10 +5398,10 @@
         <v>0.0406125</v>
       </c>
       <c r="N14" s="3" t="n">
-        <v>344479.902844003</v>
+        <v>363567.1891706061</v>
       </c>
       <c r="O14" s="3" t="n">
-        <v>421255.5341169349</v>
+        <v>440342.8204435381</v>
       </c>
     </row>
     <row r="15">
@@ -5411,7 +5411,7 @@
         </is>
       </c>
       <c r="B15" s="6" t="n">
-        <v>4007860775.201573</v>
+        <v>4189458831.435534</v>
       </c>
       <c r="C15" s="6" t="n">
         <v>334970000</v>
@@ -5429,7 +5429,7 @@
         <v>136520708.1372503</v>
       </c>
       <c r="H15" s="6" t="n">
-        <v>3295738005.568375</v>
+        <v>3477336061.802335</v>
       </c>
       <c r="I15" s="7" t="n">
         <v>0.0375</v>
@@ -5447,10 +5447,10 @@
         <v>0.0406125</v>
       </c>
       <c r="N15" s="3" t="n">
-        <v>359476.1049203679</v>
+        <v>379283.5537545285</v>
       </c>
       <c r="O15" s="3" t="n">
-        <v>437149.4876408184</v>
+        <v>456956.936474979</v>
       </c>
     </row>
     <row r="16">
@@ -5460,7 +5460,7 @@
         </is>
       </c>
       <c r="B16" s="6" t="n">
-        <v>3944031608.133983</v>
+        <v>4122737534.795423</v>
       </c>
       <c r="C16" s="6" t="n">
         <v>334970000</v>
@@ -5478,7 +5478,7 @@
         <v>146800932.9007985</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>3200056943.599629</v>
+        <v>3378762870.261068</v>
       </c>
       <c r="I16" s="7" t="n">
         <v>0.0375</v>
@@ -5496,10 +5496,10 @@
         <v>0.0406125</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>349039.8823161875</v>
+        <v>368531.8778370391</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>430187.4474789483</v>
+        <v>449679.4429997999</v>
       </c>
     </row>
     <row r="17">
@@ -5509,7 +5509,7 @@
         </is>
       </c>
       <c r="B17" s="6" t="n">
-        <v>3869106066.859931</v>
+        <v>4044417082.016002</v>
       </c>
       <c r="C17" s="6" t="n">
         <v>334970000</v>
@@ -5527,7 +5527,7 @@
         <v>146820705.7658038</v>
       </c>
       <c r="H17" s="6" t="n">
-        <v>3141318441.973659</v>
+        <v>3316629457.12973</v>
       </c>
       <c r="I17" s="7" t="n">
         <v>0.0375</v>
@@ -5545,10 +5545,10 @@
         <v>0.0406125</v>
       </c>
       <c r="N17" s="3" t="n">
-        <v>342633.0964194667</v>
+        <v>361754.7986820444</v>
       </c>
       <c r="O17" s="3" t="n">
-        <v>422015.092245996</v>
+        <v>441136.7945085737</v>
       </c>
     </row>
     <row r="18">
@@ -5558,7 +5558,7 @@
         </is>
       </c>
       <c r="B18" s="6" t="n">
-        <v>3869966485.495641</v>
+        <v>4045316486.624668</v>
       </c>
       <c r="C18" s="6" t="n">
         <v>334970000</v>
@@ -5576,7 +5576,7 @@
         <v>146084521.7500651</v>
       </c>
       <c r="H18" s="6" t="n">
-        <v>3132456009.424751</v>
+        <v>3307806010.553778</v>
       </c>
       <c r="I18" s="7" t="n">
         <v>0.0375</v>
@@ -5594,10 +5594,10 @@
         <v>0.0406125</v>
       </c>
       <c r="N18" s="3" t="n">
-        <v>341666.4441165779</v>
+        <v>360792.3986970524</v>
       </c>
       <c r="O18" s="3" t="n">
-        <v>422108.9407070216</v>
+        <v>441234.8952874962</v>
       </c>
     </row>
     <row r="19">
@@ -5607,7 +5607,7 @@
         </is>
       </c>
       <c r="B19" s="6" t="n">
-        <v>3906757002.936191</v>
+        <v>4083773999.709474</v>
       </c>
       <c r="C19" s="6" t="n">
         <v>334970000</v>
@@ -5625,7 +5625,7 @@
         <v>174559965.1979237</v>
       </c>
       <c r="H19" s="6" t="n">
-        <v>3165704851.017045</v>
+        <v>3342721847.790328</v>
       </c>
       <c r="I19" s="7" t="n">
         <v>0.0375</v>
@@ -5643,10 +5643,10 @@
         <v>0.0406125</v>
       </c>
       <c r="N19" s="3" t="n">
-        <v>345292.9957564588</v>
+        <v>364600.7745899851</v>
       </c>
       <c r="O19" s="3" t="n">
-        <v>426121.7936356186</v>
+        <v>445429.5724691449</v>
       </c>
     </row>
     <row r="20">
@@ -5656,7 +5656,7 @@
         </is>
       </c>
       <c r="B20" s="6" t="n">
-        <v>3941296256.964431</v>
+        <v>4119878243.578207</v>
       </c>
       <c r="C20" s="6" t="n">
         <v>334970000</v>
@@ -5674,7 +5674,7 @@
         <v>169618722.6830847</v>
       </c>
       <c r="H20" s="6" t="n">
-        <v>3196152749.65845</v>
+        <v>3374734736.272226</v>
       </c>
       <c r="I20" s="7" t="n">
         <v>0.0375</v>
@@ -5692,10 +5692,10 @@
         <v>0.0406125</v>
       </c>
       <c r="N20" s="3" t="n">
-        <v>348614.0400834441</v>
+        <v>368092.5170887151</v>
       </c>
       <c r="O20" s="3" t="n">
-        <v>429889.0944598799</v>
+        <v>449367.5714651509</v>
       </c>
     </row>
     <row r="21">
@@ -5705,7 +5705,7 @@
         </is>
       </c>
       <c r="B21" s="6" t="n">
-        <v>3949955056.90474</v>
+        <v>4128929377.815208</v>
       </c>
       <c r="C21" s="6" t="n">
         <v>334970000</v>
@@ -5723,7 +5723,7 @@
         <v>172338153.0245515</v>
       </c>
       <c r="H21" s="6" t="n">
-        <v>3193714712.03263</v>
+        <v>3372689032.943098</v>
       </c>
       <c r="I21" s="7" t="n">
         <v>0.0375</v>
@@ -5741,10 +5741,10 @@
         <v>0.0406125</v>
       </c>
       <c r="N21" s="3" t="n">
-        <v>348348.1159511562</v>
+        <v>367869.3860439127</v>
       </c>
       <c r="O21" s="3" t="n">
-        <v>430833.5359387135</v>
+        <v>450354.80603147</v>
       </c>
     </row>
     <row r="22">
@@ -5754,7 +5754,7 @@
         </is>
       </c>
       <c r="B22" s="6" t="n">
-        <v>3930000358.477587</v>
+        <v>4108070522.619555</v>
       </c>
       <c r="C22" s="6" t="n">
         <v>334970000</v>
@@ -5772,7 +5772,7 @@
         <v>162877756.5589872</v>
       </c>
       <c r="H22" s="6" t="n">
-        <v>3173869467.112352</v>
+        <v>3351939631.25432</v>
       </c>
       <c r="I22" s="7" t="n">
         <v>0.0375</v>
@@ -5790,10 +5790,10 @@
         <v>0.0406125</v>
       </c>
       <c r="N22" s="3" t="n">
-        <v>346183.5351097547</v>
+        <v>365606.1860911532</v>
       </c>
       <c r="O22" s="3" t="n">
-        <v>428657.0166725176</v>
+        <v>448079.6676539161</v>
       </c>
     </row>
     <row r="23">
@@ -5803,7 +5803,7 @@
         </is>
       </c>
       <c r="B23" s="6" t="n">
-        <v>4128625750.909277</v>
+        <v>4315695724.97665</v>
       </c>
       <c r="C23" s="6" t="n">
         <v>334970000</v>
@@ -5821,7 +5821,7 @@
         <v>231737478.377994</v>
       </c>
       <c r="H23" s="6" t="n">
-        <v>3319950868.733045</v>
+        <v>3507020842.800418</v>
       </c>
       <c r="I23" s="7" t="n">
         <v>0.0375</v>
@@ -5839,10 +5839,10 @@
         <v>0.0406125</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>362117.0750838638</v>
+        <v>382521.3625337991</v>
       </c>
       <c r="O23" s="3" t="n">
-        <v>450321.6885271936</v>
+        <v>470725.9759771289</v>
       </c>
     </row>
     <row r="24">
@@ -5852,7 +5852,7 @@
         </is>
       </c>
       <c r="B24" s="6" t="n">
-        <v>4099347532.103574</v>
+        <v>4285090896.310144</v>
       </c>
       <c r="C24" s="6" t="n">
         <v>334970000</v>
@@ -5870,7 +5870,7 @@
         <v>229182741.6867744</v>
       </c>
       <c r="H24" s="6" t="n">
-        <v>3278042581.79532</v>
+        <v>3463785946.00189</v>
       </c>
       <c r="I24" s="7" t="n">
         <v>0.0375</v>
@@ -5888,10 +5888,10 @@
         <v>0.0406125</v>
       </c>
       <c r="N24" s="3" t="n">
-        <v>357546.011568862</v>
+        <v>377805.601671889</v>
       </c>
       <c r="O24" s="3" t="n">
-        <v>447128.2247149919</v>
+        <v>467387.814818019</v>
       </c>
     </row>
     <row r="25">
@@ -5901,7 +5901,7 @@
         </is>
       </c>
       <c r="B25" s="6" t="n">
-        <v>3849261001.889072</v>
+        <v>4023672827.820097</v>
       </c>
       <c r="C25" s="6" t="n">
         <v>334970000</v>
@@ -5919,7 +5919,7 @@
         <v>230888253.3173563</v>
       </c>
       <c r="H25" s="6" t="n">
-        <v>3031529776.667622</v>
+        <v>3205941602.598647</v>
       </c>
       <c r="I25" s="7" t="n">
         <v>0.0375</v>
@@ -5937,10 +5937,10 @@
         <v>0.0406125</v>
       </c>
       <c r="N25" s="3" t="n">
-        <v>330658.1148821178</v>
+        <v>349681.7398583154</v>
       </c>
       <c r="O25" s="3" t="n">
-        <v>419850.5310322215</v>
+        <v>438874.1560084191</v>
       </c>
     </row>
     <row r="26">
@@ -5950,7 +5950,7 @@
         </is>
       </c>
       <c r="B26" s="6" t="n">
-        <v>3796096805.831977</v>
+        <v>3968099737.041672</v>
       </c>
       <c r="C26" s="6" t="n">
         <v>334970000</v>
@@ -5968,7 +5968,7 @@
         <v>254742493.5135711</v>
       </c>
       <c r="H26" s="6" t="n">
-        <v>2952167920.756298</v>
+        <v>3124170851.965993</v>
       </c>
       <c r="I26" s="7" t="n">
         <v>0.0375</v>
@@ -5986,10 +5986,10 @@
         <v>0.0406125</v>
       </c>
       <c r="N26" s="3" t="n">
-        <v>322001.8774038798</v>
+        <v>340762.7569524604</v>
       </c>
       <c r="O26" s="3" t="n">
-        <v>414051.7514910269</v>
+        <v>432812.6310396074</v>
       </c>
     </row>
     <row r="27">
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="B27" s="6" t="n">
-        <v>4276518811.263577</v>
+        <v>4470289889.435416</v>
       </c>
       <c r="C27" s="6" t="n">
         <v>334970000</v>
@@ -6017,7 +6017,7 @@
         <v>239797730.4064276</v>
       </c>
       <c r="H27" s="6" t="n">
-        <v>3439871011.979409</v>
+        <v>3633642090.151248</v>
       </c>
       <c r="I27" s="7" t="n">
         <v>0.0375</v>
@@ -6035,10 +6035,10 @@
         <v>0.0406125</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>375197.1275403578</v>
+        <v>396332.3246676004</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>466452.8315947228</v>
+        <v>487588.0287219654</v>
       </c>
     </row>
     <row r="28">
@@ -6048,7 +6048,7 @@
         </is>
       </c>
       <c r="B28" s="6" t="n">
-        <v>4260541447.925423</v>
+        <v>4453588584.251801</v>
       </c>
       <c r="C28" s="6" t="n">
         <v>334970000</v>
@@ -6066,7 +6066,7 @@
         <v>240130221.5557107</v>
       </c>
       <c r="H28" s="6" t="n">
-        <v>3420062638.696182</v>
+        <v>3613109775.02256</v>
       </c>
       <c r="I28" s="7" t="n">
         <v>0.0375</v>
@@ -6084,10 +6084,10 @@
         <v>0.0406125</v>
       </c>
       <c r="N28" s="3" t="n">
-        <v>373036.568399846</v>
+        <v>394092.8030020469</v>
       </c>
       <c r="O28" s="3" t="n">
-        <v>464710.1322873164</v>
+        <v>485766.3668895173</v>
       </c>
     </row>
     <row r="29">
@@ -6097,7 +6097,7 @@
         </is>
       </c>
       <c r="B29" s="6" t="n">
-        <v>4278271428.210862</v>
+        <v>4472121918.280669</v>
       </c>
       <c r="C29" s="6" t="n">
         <v>334970000</v>
@@ -6115,7 +6115,7 @@
         <v>243572783.8200219</v>
       </c>
       <c r="H29" s="6" t="n">
-        <v>3434366864.528295</v>
+        <v>3628217354.598102</v>
       </c>
       <c r="I29" s="7" t="n">
         <v>0.0375</v>
@@ -6133,10 +6133,10 @@
         <v>0.0406125</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>374596.7735427734</v>
+        <v>395740.6323657326</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>466643.9948220676</v>
+        <v>487787.8536450268</v>
       </c>
     </row>
     <row r="30">
@@ -6146,7 +6146,7 @@
         </is>
       </c>
       <c r="B30" s="6" t="n">
-        <v>4275937035.604297</v>
+        <v>4469681753.247461</v>
       </c>
       <c r="C30" s="6" t="n">
         <v>334970000</v>
@@ -6164,7 +6164,7 @@
         <v>245605231.7022537</v>
       </c>
       <c r="H30" s="6" t="n">
-        <v>3428834151.644414</v>
+        <v>3622578869.287579</v>
       </c>
       <c r="I30" s="7" t="n">
         <v>0.0375</v>
@@ -6182,10 +6182,10 @@
         <v>0.0406125</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>373993.3038271044</v>
+        <v>395125.6257318154</v>
       </c>
       <c r="O30" s="3" t="n">
-        <v>466389.3755652744</v>
+        <v>487521.6974699855</v>
       </c>
     </row>
     <row r="31">
@@ -6195,7 +6195,7 @@
         </is>
       </c>
       <c r="B31" s="6" t="n">
-        <v>4019063778.948612</v>
+        <v>4201169448.550041</v>
       </c>
       <c r="C31" s="6" t="n">
         <v>334970000</v>
@@ -6213,7 +6213,7 @@
         <v>179571549.4489093</v>
       </c>
       <c r="H31" s="6" t="n">
-        <v>3231323652.541693</v>
+        <v>3413429322.143122</v>
       </c>
       <c r="I31" s="7" t="n">
         <v>0.0375</v>
@@ -6231,10 +6231,10 @@
         <v>0.0406125</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>352450.2367573421</v>
+        <v>372313.0525156438</v>
       </c>
       <c r="O31" s="3" t="n">
-        <v>438371.433118156</v>
+        <v>458234.2488764576</v>
       </c>
     </row>
     <row r="32">
@@ -6244,7 +6244,7 @@
         </is>
       </c>
       <c r="B32" s="6" t="n">
-        <v>3894612666.177943</v>
+        <v>4071079397.342402</v>
       </c>
       <c r="C32" s="6" t="n">
         <v>334970000</v>
@@ -6262,7 +6262,7 @@
         <v>206116586.0471416</v>
       </c>
       <c r="H32" s="6" t="n">
-        <v>3076501218.730989</v>
+        <v>3252967949.895449</v>
       </c>
       <c r="I32" s="7" t="n">
         <v>0.0375</v>
@@ -6280,10 +6280,10 @@
         <v>0.0406125</v>
       </c>
       <c r="N32" s="3" t="n">
-        <v>335563.2859843952</v>
+        <v>354811.0456849087</v>
       </c>
       <c r="O32" s="3" t="n">
-        <v>424797.1741217737</v>
+        <v>444044.9338222871</v>
       </c>
     </row>
     <row r="33">
@@ -6293,7 +6293,7 @@
         </is>
       </c>
       <c r="B33" s="6" t="n">
-        <v>3904793970.371299</v>
+        <v>4081722021.216043</v>
       </c>
       <c r="C33" s="6" t="n">
         <v>334970000</v>
@@ -6311,7 +6311,7 @@
         <v>248420857.3449725</v>
       </c>
       <c r="H33" s="6" t="n">
-        <v>3044549507.900335</v>
+        <v>3221477558.745079</v>
       </c>
       <c r="I33" s="7" t="n">
         <v>0.0375</v>
@@ -6329,10 +6329,10 @@
         <v>0.0406125</v>
       </c>
       <c r="N33" s="3" t="n">
-        <v>332078.2163169826</v>
+        <v>351376.2935492632</v>
       </c>
       <c r="O33" s="3" t="n">
-        <v>425907.6797409258</v>
+        <v>445205.7569732065</v>
       </c>
     </row>
     <row r="34">
@@ -6342,7 +6342,7 @@
         </is>
       </c>
       <c r="B34" s="6" t="n">
-        <v>3980438326.717189</v>
+        <v>4160793858.916194</v>
       </c>
       <c r="C34" s="6" t="n">
         <v>334970000</v>
@@ -6360,7 +6360,7 @@
         <v>303291142.7334828</v>
       </c>
       <c r="H34" s="6" t="n">
-        <v>3066517185.716836</v>
+        <v>3246872717.915842</v>
       </c>
       <c r="I34" s="7" t="n">
         <v>0.0375</v>
@@ -6378,10 +6378,10 @@
         <v>0.0406125</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>334474.2973289681</v>
+        <v>354146.2203113768</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>434158.4383062261</v>
+        <v>453830.3612886349</v>
       </c>
     </row>
     <row r="35">
@@ -6391,7 +6391,7 @@
         </is>
       </c>
       <c r="B35" s="6" t="n">
-        <v>3949996189.520216</v>
+        <v>4128972374.168832</v>
       </c>
       <c r="C35" s="6" t="n">
         <v>334970000</v>
@@ -6409,7 +6409,7 @@
         <v>295800536.4468129</v>
       </c>
       <c r="H35" s="6" t="n">
-        <v>3045533293.972157</v>
+        <v>3224509478.620773</v>
       </c>
       <c r="I35" s="7" t="n">
         <v>0.0375</v>
@@ -6427,10 +6427,10 @@
         <v>0.0406125</v>
       </c>
       <c r="N35" s="3" t="n">
-        <v>332185.5208371161</v>
+        <v>351706.9942134252</v>
       </c>
       <c r="O35" s="3" t="n">
-        <v>430838.0223973978</v>
+        <v>450359.4957737069</v>
       </c>
     </row>
     <row r="36">
@@ -6440,7 +6440,7 @@
         </is>
       </c>
       <c r="B36" s="6" t="n">
-        <v>3938439863.321327</v>
+        <v>4116892425.396048</v>
       </c>
       <c r="C36" s="6" t="n">
         <v>334970000</v>
@@ -6458,7 +6458,7 @@
         <v>289518568.352541</v>
       </c>
       <c r="H36" s="6" t="n">
-        <v>3039962404.608198</v>
+        <v>3218414966.682919</v>
       </c>
       <c r="I36" s="7" t="n">
         <v>0.0375</v>
@@ -6476,10 +6476,10 @@
         <v>0.0406125</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>331577.8870973847</v>
+        <v>351042.2473770235</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>429577.5389723965</v>
+        <v>449041.8992520352</v>
       </c>
     </row>
     <row r="38">
@@ -6501,10 +6501,10 @@
       <c r="L38" t="inlineStr"/>
       <c r="M38" t="inlineStr"/>
       <c r="N38" s="11" t="n">
-        <v>10742059.80203898</v>
+        <v>11348183.48346371</v>
       </c>
       <c r="O38" s="11" t="n">
-        <v>13377121.85957116</v>
+        <v>13983245.54099589</v>
       </c>
     </row>
   </sheetData>

--- a/settlements/spark/2026-05/spark_settlement_may_2026.xlsx
+++ b/settlements/spark/2026-05/spark_settlement_may_2026.xlsx
@@ -663,7 +663,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-06-09T14:50:47+00:00</t>
+          <t>2026-06-09T15:30:58+00:00</t>
         </is>
       </c>
     </row>

--- a/settlements/spark/2026-05/spark_settlement_may_2026.xlsx
+++ b/settlements/spark/2026-05/spark_settlement_may_2026.xlsx
@@ -663,7 +663,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-06-09T15:30:58+00:00</t>
+          <t>2026-06-09T15:42:51+00:00</t>
         </is>
       </c>
     </row>

--- a/settlements/spark/2026-05/spark_settlement_may_2026.xlsx
+++ b/settlements/spark/2026-05/spark_settlement_may_2026.xlsx
@@ -663,7 +663,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-06-09T15:42:51+00:00</t>
+          <t>2026-06-09T15:58:27+00:00</t>
         </is>
       </c>
     </row>

--- a/settlements/spark/2026-05/spark_settlement_may_2026.xlsx
+++ b/settlements/spark/2026-05/spark_settlement_may_2026.xlsx
@@ -498,13 +498,13 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>121639.2149998229</v>
+        <v>121900.7497091584</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
       <c r="B6" s="4" t="n">
-        <v>7987512.899241818</v>
+        <v>7987774.433951153</v>
       </c>
     </row>
     <row r="8">
@@ -663,7 +663,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-06-09T15:58:27+00:00</t>
+          <t>2026-06-09T16:20:36+00:00</t>
         </is>
       </c>
     </row>

--- a/settlements/spark/2026-05/spark_settlement_may_2026.xlsx
+++ b/settlements/spark/2026-05/spark_settlement_may_2026.xlsx
@@ -663,7 +663,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-06-09T16:20:36+00:00</t>
+          <t>2026-06-09T16:37:44+00:00</t>
         </is>
       </c>
     </row>

--- a/settlements/spark/2026-05/spark_settlement_may_2026.xlsx
+++ b/settlements/spark/2026-05/spark_settlement_may_2026.xlsx
@@ -663,7 +663,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-06-09T16:37:44+00:00</t>
+          <t>2026-06-09T17:00:59+00:00</t>
         </is>
       </c>
     </row>

--- a/settlements/spark/2026-05/spark_settlement_may_2026.xlsx
+++ b/settlements/spark/2026-05/spark_settlement_may_2026.xlsx
@@ -488,7 +488,7 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>8471023.892760478</v>
+        <v>7865873.684241995</v>
       </c>
     </row>
     <row r="5">
@@ -498,13 +498,13 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>0</v>
+        <v>121900.7497091584</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
       <c r="B6" s="4" t="n">
-        <v>8471023.892760478</v>
+        <v>7987774.433951153</v>
       </c>
     </row>
     <row r="8">
@@ -526,7 +526,7 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>10234615.9342856</v>
+        <v>10840739.61571033</v>
       </c>
     </row>
     <row r="10">
@@ -542,7 +542,7 @@
     <row r="11">
       <c r="A11" t="inlineStr"/>
       <c r="B11" s="4" t="n">
-        <v>10308771.99513011</v>
+        <v>10914895.67655484</v>
       </c>
     </row>
     <row r="13">
@@ -564,7 +564,7 @@
         </is>
       </c>
       <c r="B14" s="3" t="n">
-        <v>10234615.9342856</v>
+        <v>10840739.61571033</v>
       </c>
     </row>
     <row r="15">
@@ -580,13 +580,13 @@
     <row r="16">
       <c r="A16" t="inlineStr"/>
       <c r="B16" s="4" t="n">
-        <v>13377121.85957116</v>
+        <v>13983245.54099589</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>sUSDS spread (Curve LP + PSM3) — credited to prime_agent_revenue</t>
+          <t>sUSDS spread (Curve LP + PSM3) — deducted from sky_revenue</t>
         </is>
       </c>
       <c r="B18" s="3" t="n">
@@ -612,7 +612,7 @@
         </is>
       </c>
       <c r="B21" s="3" t="n">
-        <v>8471023.892760478</v>
+        <v>7865873.684241995</v>
       </c>
     </row>
     <row r="22">
@@ -622,13 +622,13 @@
         </is>
       </c>
       <c r="B22" s="3" t="n">
-        <v>-10234615.9342856</v>
+        <v>-10840739.61571033</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr"/>
       <c r="B23" s="4" t="n">
-        <v>-1948502.4602201</v>
+        <v>-3159776.350163311</v>
       </c>
     </row>
     <row r="25">
@@ -663,7 +663,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-06-08T17:11:43+00:00</t>
+          <t>2026-06-09T17:00:59+00:00</t>
         </is>
       </c>
     </row>
@@ -860,13 +860,13 @@
         <v>1</v>
       </c>
       <c r="N2" s="6" t="n">
-        <v>4167822.764039975</v>
+        <v>4410254.829322996</v>
       </c>
       <c r="O2" s="6" t="n">
-        <v>4167822.764039975</v>
+        <v>4410254.829322996</v>
       </c>
       <c r="P2" s="6" t="n">
-        <v>-4167822.764039975</v>
+        <v>-4410254.829322996</v>
       </c>
       <c r="Q2" s="6" t="n">
         <v>0</v>
@@ -925,13 +925,13 @@
         <v>1</v>
       </c>
       <c r="N3" s="6" t="n">
-        <v>1473003.887406189</v>
+        <v>1558684.923959588</v>
       </c>
       <c r="O3" s="6" t="n">
-        <v>1473003.887406189</v>
+        <v>1558684.923959588</v>
       </c>
       <c r="P3" s="6" t="n">
-        <v>395108.2808298113</v>
+        <v>309427.2442764115</v>
       </c>
       <c r="Q3" s="6" t="n">
         <v>0</v>
@@ -990,13 +990,13 @@
         <v>1</v>
       </c>
       <c r="N4" s="6" t="n">
-        <v>1349597.02588841</v>
+        <v>1428099.786876452</v>
       </c>
       <c r="O4" s="6" t="n">
-        <v>1349597.02588841</v>
+        <v>1428099.786876452</v>
       </c>
       <c r="P4" s="6" t="n">
-        <v>1741982.97411159</v>
+        <v>1663480.213123548</v>
       </c>
       <c r="Q4" s="6" t="n">
         <v>0</v>
@@ -1055,13 +1055,13 @@
         <v>1</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>1183578.826270314</v>
+        <v>1252424.714284955</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>1183578.826270314</v>
+        <v>1252424.714284955</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>-1378023.270714268</v>
+        <v>-1446869.158728908</v>
       </c>
       <c r="Q5" s="6" t="n">
         <v>0</v>
@@ -1120,13 +1120,13 @@
         <v>1</v>
       </c>
       <c r="N6" s="6" t="n">
-        <v>393717.3565437027</v>
+        <v>416618.9330474357</v>
       </c>
       <c r="O6" s="6" t="n">
-        <v>393717.3565437027</v>
+        <v>416618.9330474357</v>
       </c>
       <c r="P6" s="6" t="n">
-        <v>165735.5826975166</v>
+        <v>142834.0061937836</v>
       </c>
       <c r="Q6" s="6" t="n">
         <v>86642406.62655522</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="N7" s="6" t="n">
-        <v>314291.9993735298</v>
+        <v>332573.59694228</v>
       </c>
       <c r="O7" s="6" t="n">
-        <v>277827.1855317322</v>
+        <v>296108.7831004824</v>
       </c>
       <c r="P7" s="6" t="n">
-        <v>-314291.9993735298</v>
+        <v>-332573.59694228</v>
       </c>
       <c r="Q7" s="6" t="n">
         <v>0</v>
@@ -1254,13 +1254,13 @@
         <v>1</v>
       </c>
       <c r="N8" s="6" t="n">
-        <v>230418.5138801736</v>
+        <v>243821.3957592647</v>
       </c>
       <c r="O8" s="6" t="n">
-        <v>230418.5138801736</v>
+        <v>243821.3957592647</v>
       </c>
       <c r="P8" s="6" t="n">
-        <v>193112.0947030281</v>
+        <v>179709.2128239369</v>
       </c>
       <c r="Q8" s="6" t="n">
         <v>0</v>
@@ -1319,13 +1319,13 @@
         <v>1</v>
       </c>
       <c r="N9" s="6" t="n">
-        <v>219281.0959016976</v>
+        <v>232036.1413934696</v>
       </c>
       <c r="O9" s="6" t="n">
-        <v>219281.0959016976</v>
+        <v>232036.1413934696</v>
       </c>
       <c r="P9" s="6" t="n">
-        <v>-190277.1252016976</v>
+        <v>-203032.1706934696</v>
       </c>
       <c r="Q9" s="6" t="n">
         <v>0</v>
@@ -1384,13 +1384,13 @@
         <v>1</v>
       </c>
       <c r="N10" s="6" t="n">
-        <v>219277.4654279028</v>
+        <v>232032.2997438859</v>
       </c>
       <c r="O10" s="6" t="n">
-        <v>219277.4654279028</v>
+        <v>232032.2997438859</v>
       </c>
       <c r="P10" s="6" t="n">
-        <v>-212891.5815562624</v>
+        <v>-225646.4158722456</v>
       </c>
       <c r="Q10" s="6" t="n">
         <v>0</v>
@@ -1449,13 +1449,13 @@
         <v>1</v>
       </c>
       <c r="N11" s="6" t="n">
-        <v>223756.2828300607</v>
+        <v>236771.6390094491</v>
       </c>
       <c r="O11" s="6" t="n">
-        <v>197795.6118120444</v>
+        <v>210810.9679914328</v>
       </c>
       <c r="P11" s="6" t="n">
-        <v>-223756.2828300607</v>
+        <v>-236771.6390094491</v>
       </c>
       <c r="Q11" s="6" t="n">
         <v>0</v>
@@ -1514,13 +1514,13 @@
         <v>1</v>
       </c>
       <c r="N12" s="6" t="n">
-        <v>196519.3159684765</v>
+        <v>207950.3643444547</v>
       </c>
       <c r="O12" s="6" t="n">
-        <v>196519.3159684765</v>
+        <v>207950.3643444547</v>
       </c>
       <c r="P12" s="6" t="n">
-        <v>20750.08047808185</v>
+        <v>9319.032102103598</v>
       </c>
       <c r="Q12" s="6" t="n">
         <v>0</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="N13" s="6" t="n">
-        <v>166155.4201387819</v>
+        <v>175820.2748945458</v>
       </c>
       <c r="O13" s="6" t="n">
-        <v>146877.7214501635</v>
+        <v>156542.5762059274</v>
       </c>
       <c r="P13" s="6" t="n">
-        <v>-166155.4201387819</v>
+        <v>-175820.2748945458</v>
       </c>
       <c r="Q13" s="6" t="n">
         <v>0</v>
@@ -1644,13 +1644,13 @@
         <v>1</v>
       </c>
       <c r="N14" s="6" t="n">
-        <v>126593.836691988</v>
+        <v>133957.490815224</v>
       </c>
       <c r="O14" s="6" t="n">
-        <v>126593.836691988</v>
+        <v>133957.490815224</v>
       </c>
       <c r="P14" s="6" t="n">
-        <v>167497.6801844561</v>
+        <v>160134.02606122</v>
       </c>
       <c r="Q14" s="6" t="n">
         <v>103099818.9104406</v>
@@ -1843,13 +1843,13 @@
         <v>1</v>
       </c>
       <c r="N17" s="6" t="n">
-        <v>65067.17882175036</v>
+        <v>68851.97760926072</v>
       </c>
       <c r="O17" s="6" t="n">
-        <v>65067.17882175036</v>
+        <v>68851.97760926072</v>
       </c>
       <c r="P17" s="6" t="n">
-        <v>54574.43910422226</v>
+        <v>50789.6403167119</v>
       </c>
       <c r="Q17" s="6" t="n">
         <v>0</v>
@@ -1908,13 +1908,13 @@
         <v>1</v>
       </c>
       <c r="N18" s="6" t="n">
-        <v>20866.96526236113</v>
+        <v>22080.74563910623</v>
       </c>
       <c r="O18" s="6" t="n">
-        <v>20866.96526236113</v>
+        <v>22080.74563910623</v>
       </c>
       <c r="P18" s="6" t="n">
-        <v>834.506240336483</v>
+        <v>-379.2741364086218</v>
       </c>
       <c r="Q18" s="6" t="n">
         <v>0</v>
@@ -1973,13 +1973,13 @@
         <v>1</v>
       </c>
       <c r="N19" s="6" t="n">
-        <v>20445.85693754033</v>
+        <v>21635.14247209228</v>
       </c>
       <c r="O19" s="6" t="n">
-        <v>20445.85693754033</v>
+        <v>21635.14247209228</v>
       </c>
       <c r="P19" s="6" t="n">
-        <v>12057.04641545967</v>
+        <v>10867.76088090771</v>
       </c>
       <c r="Q19" s="6" t="n">
         <v>0</v>
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="N20" s="6" t="n">
-        <v>10961.84976257375</v>
+        <v>11599.47377580961</v>
       </c>
       <c r="O20" s="6" t="n">
-        <v>10961.84976257375</v>
+        <v>11599.47377580961</v>
       </c>
       <c r="P20" s="6" t="n">
-        <v>-10961.84976257152</v>
+        <v>-11599.47377580738</v>
       </c>
       <c r="Q20" s="6" t="n">
         <v>0</v>
@@ -2103,13 +2103,13 @@
         <v>1</v>
       </c>
       <c r="N21" s="6" t="n">
-        <v>10961.12595799393</v>
+        <v>11598.70786928614</v>
       </c>
       <c r="O21" s="6" t="n">
-        <v>10961.12595799393</v>
+        <v>11598.70786928614</v>
       </c>
       <c r="P21" s="6" t="n">
-        <v>-10961.12595799374</v>
+        <v>-11598.70786928596</v>
       </c>
       <c r="Q21" s="6" t="n">
         <v>0</v>
@@ -2168,13 +2168,13 @@
         <v>1</v>
       </c>
       <c r="N22" s="6" t="n">
-        <v>10959.09351594223</v>
+        <v>11596.55720504697</v>
       </c>
       <c r="O22" s="6" t="n">
-        <v>10959.09351594223</v>
+        <v>11596.55720504697</v>
       </c>
       <c r="P22" s="6" t="n">
-        <v>-10959.09351594223</v>
+        <v>-11596.55720504697</v>
       </c>
       <c r="Q22" s="6" t="n">
         <v>0</v>
@@ -2233,13 +2233,13 @@
         <v>1</v>
       </c>
       <c r="N23" s="6" t="n">
-        <v>10864.34675478342</v>
+        <v>11496.29925632405</v>
       </c>
       <c r="O23" s="6" t="n">
-        <v>10864.34675478342</v>
+        <v>11496.29925632405</v>
       </c>
       <c r="P23" s="6" t="n">
-        <v>-10864.34675478295</v>
+        <v>-11496.29925632357</v>
       </c>
       <c r="Q23" s="6" t="n">
         <v>0</v>
@@ -2280,31 +2280,31 @@
         <v>2796996.33696637</v>
       </c>
       <c r="H24" s="6" t="n">
-        <v>609955.0966986277</v>
+        <v>4804.888180144989</v>
       </c>
       <c r="I24" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J24" s="6" t="n">
-        <v>609955.0966986277</v>
+        <v>4804.888180144989</v>
       </c>
       <c r="K24" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L24" s="6" t="n">
-        <v>1472511.375313347</v>
+        <v>1492032.349781685</v>
       </c>
       <c r="M24" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N24" s="6" t="n">
-        <v>3228.934391728406</v>
+        <v>3462.049264890436</v>
       </c>
       <c r="O24" s="6" t="n">
-        <v>3228.934391728406</v>
+        <v>3462.049264890436</v>
       </c>
       <c r="P24" s="6" t="n">
-        <v>606726.1623068993</v>
+        <v>1342.838915254552</v>
       </c>
       <c r="Q24" s="6" t="n">
         <v>0</v>
@@ -2363,13 +2363,13 @@
         <v>1</v>
       </c>
       <c r="N25" s="6" t="n">
-        <v>2154.232305888279</v>
+        <v>2279.53873482809</v>
       </c>
       <c r="O25" s="6" t="n">
-        <v>1904.293776868191</v>
+        <v>2029.600205808002</v>
       </c>
       <c r="P25" s="6" t="n">
-        <v>-2154.232305888279</v>
+        <v>-2279.53873482809</v>
       </c>
       <c r="Q25" s="6" t="n">
         <v>0</v>
@@ -2428,13 +2428,13 @@
         <v>1</v>
       </c>
       <c r="N26" s="6" t="n">
-        <v>1.013431751019421</v>
+        <v>1.072380599454827</v>
       </c>
       <c r="O26" s="6" t="n">
-        <v>1.013431751019421</v>
+        <v>1.072380599454827</v>
       </c>
       <c r="P26" s="6" t="n">
-        <v>75.31703376818632</v>
+        <v>75.25808491975091</v>
       </c>
       <c r="Q26" s="6" t="n">
         <v>0</v>
@@ -2493,13 +2493,13 @@
         <v>1</v>
       </c>
       <c r="N27" s="6" t="n">
-        <v>0.807045574158881</v>
+        <v>0.8539894430318479</v>
       </c>
       <c r="O27" s="6" t="n">
-        <v>0.807045574158881</v>
+        <v>0.8539894430318479</v>
       </c>
       <c r="P27" s="6" t="n">
-        <v>0.3542997011788971</v>
+        <v>0.3073558323059302</v>
       </c>
       <c r="Q27" s="6" t="n">
         <v>0</v>
@@ -2558,13 +2558,13 @@
         <v>1</v>
       </c>
       <c r="N28" s="6" t="n">
-        <v>0.6225320944278722</v>
+        <v>0.6587432650801534</v>
       </c>
       <c r="O28" s="6" t="n">
-        <v>0.6225320944278722</v>
+        <v>0.6587432650801534</v>
       </c>
       <c r="P28" s="6" t="n">
-        <v>-0.6225320944278722</v>
+        <v>-0.6587432650801534</v>
       </c>
       <c r="Q28" s="6" t="n">
         <v>0</v>
@@ -2623,13 +2623,13 @@
         <v>1</v>
       </c>
       <c r="N29" s="6" t="n">
-        <v>0.2528534828828865</v>
+        <v>0.267561352084571</v>
       </c>
       <c r="O29" s="6" t="n">
-        <v>0.2528534828828865</v>
+        <v>0.267561352084571</v>
       </c>
       <c r="P29" s="6" t="n">
-        <v>-0.2528534832133453</v>
+        <v>-0.2675613524150298</v>
       </c>
       <c r="Q29" s="6" t="n">
         <v>0</v>
@@ -2688,13 +2688,13 @@
         <v>1</v>
       </c>
       <c r="N30" s="6" t="n">
-        <v>0.2181872112413053</v>
+        <v>0.2308786281355063</v>
       </c>
       <c r="O30" s="6" t="n">
-        <v>0.2181872112413053</v>
+        <v>0.2308786281355063</v>
       </c>
       <c r="P30" s="6" t="n">
-        <v>0.09357633719282084</v>
+        <v>0.08088492029861985</v>
       </c>
       <c r="Q30" s="6" t="n">
         <v>0</v>
@@ -2753,13 +2753,13 @@
         <v>1</v>
       </c>
       <c r="N31" s="6" t="n">
-        <v>0.04803697741683239</v>
+        <v>0.050831171005292</v>
       </c>
       <c r="O31" s="6" t="n">
-        <v>0.04803697741683239</v>
+        <v>0.050831171005292</v>
       </c>
       <c r="P31" s="6" t="n">
-        <v>-0.04803092370966239</v>
+        <v>-0.05082511729812201</v>
       </c>
       <c r="Q31" s="6" t="n">
         <v>0</v>
@@ -2818,13 +2818,13 @@
         <v>1</v>
       </c>
       <c r="N32" s="6" t="n">
-        <v>0.01293289080298069</v>
+        <v>0.01368516545690748</v>
       </c>
       <c r="O32" s="6" t="n">
-        <v>0.01293289080298069</v>
+        <v>0.01368516545690748</v>
       </c>
       <c r="P32" s="6" t="n">
-        <v>0.002457109197019311</v>
+        <v>0.001704834543092515</v>
       </c>
       <c r="Q32" s="6" t="n">
         <v>0</v>
@@ -2883,13 +2883,13 @@
         <v>1</v>
       </c>
       <c r="N33" s="6" t="n">
-        <v>0.003389223431433898</v>
+        <v>0.003586366276201048</v>
       </c>
       <c r="O33" s="6" t="n">
-        <v>0.003389223431433898</v>
+        <v>0.003586366276201048</v>
       </c>
       <c r="P33" s="6" t="n">
-        <v>8.466999776568565</v>
+        <v>8.466802633723798</v>
       </c>
       <c r="Q33" s="6" t="n">
         <v>0</v>
@@ -2948,13 +2948,13 @@
         <v>1</v>
       </c>
       <c r="N34" s="6" t="n">
-        <v>0.0003386374974134909</v>
+        <v>0.0003583352131101747</v>
       </c>
       <c r="O34" s="6" t="n">
-        <v>0.0003386374974134909</v>
+        <v>0.0003583352131101747</v>
       </c>
       <c r="P34" s="6" t="n">
-        <v>0.0003953625025865091</v>
+        <v>0.0003756647868898253</v>
       </c>
       <c r="Q34" s="6" t="n">
         <v>0</v>
@@ -3013,13 +3013,13 @@
         <v>1</v>
       </c>
       <c r="N35" s="6" t="n">
-        <v>0.0001267070116300726</v>
+        <v>0.0001340772488628917</v>
       </c>
       <c r="O35" s="6" t="n">
-        <v>0.0001267070116300726</v>
+        <v>0.0001340772488628917</v>
       </c>
       <c r="P35" s="6" t="n">
-        <v>5.929298836992738e-05</v>
+        <v>5.192275113710832e-05</v>
       </c>
       <c r="Q35" s="6" t="n">
         <v>0</v>
@@ -3078,13 +3078,13 @@
         <v>1</v>
       </c>
       <c r="N36" s="6" t="n">
-        <v>1.391555813655298e-05</v>
+        <v>1.472499214793124e-05</v>
       </c>
       <c r="O36" s="6" t="n">
-        <v>1.391555813655298e-05</v>
+        <v>1.472499214793124e-05</v>
       </c>
       <c r="P36" s="6" t="n">
-        <v>3.08444186344702e-06</v>
+        <v>2.275007852068764e-06</v>
       </c>
       <c r="Q36" s="6" t="n">
         <v>0</v>
@@ -3143,13 +3143,13 @@
         <v>1</v>
       </c>
       <c r="N37" s="6" t="n">
-        <v>1.259610861851073e-05</v>
+        <v>1.332879347576094e-05</v>
       </c>
       <c r="O37" s="6" t="n">
-        <v>1.259610861851073e-05</v>
+        <v>1.332879347576094e-05</v>
       </c>
       <c r="P37" s="6" t="n">
-        <v>-1.045228411314073e-05</v>
+        <v>-1.118496897039094e-05</v>
       </c>
       <c r="Q37" s="6" t="n">
         <v>0</v>
@@ -3208,13 +3208,13 @@
         <v>1</v>
       </c>
       <c r="N38" s="6" t="n">
-        <v>3.727773216536412e-06</v>
+        <v>3.944608674989458e-06</v>
       </c>
       <c r="O38" s="6" t="n">
-        <v>3.727773216536412e-06</v>
+        <v>3.944608674989458e-06</v>
       </c>
       <c r="P38" s="6" t="n">
-        <v>1.272226783463589e-06</v>
+        <v>1.055391325010542e-06</v>
       </c>
       <c r="Q38" s="6" t="n">
         <v>0</v>
@@ -3273,13 +3273,13 @@
         <v>1</v>
       </c>
       <c r="N39" s="6" t="n">
-        <v>2.719398874916082e-06</v>
+        <v>2.877579662079685e-06</v>
       </c>
       <c r="O39" s="6" t="n">
-        <v>2.719398874916082e-06</v>
+        <v>2.877579662079685e-06</v>
       </c>
       <c r="P39" s="6" t="n">
-        <v>-2.719398874916082e-06</v>
+        <v>-2.877579662079685e-06</v>
       </c>
       <c r="Q39" s="6" t="n">
         <v>0</v>
@@ -3338,13 +3338,13 @@
         <v>1</v>
       </c>
       <c r="N40" s="6" t="n">
-        <v>1.142379532868556e-06</v>
+        <v>1.208828958664657e-06</v>
       </c>
       <c r="O40" s="6" t="n">
-        <v>1.142379532868556e-06</v>
+        <v>1.208828958664657e-06</v>
       </c>
       <c r="P40" s="6" t="n">
-        <v>-4.356727260595558e-07</v>
+        <v>-5.021221518556572e-07</v>
       </c>
       <c r="Q40" s="6" t="n">
         <v>0</v>
@@ -3403,13 +3403,13 @@
         <v>1</v>
       </c>
       <c r="N41" s="6" t="n">
-        <v>1.642331360647951e-07</v>
+        <v>1.737861762534574e-07</v>
       </c>
       <c r="O41" s="6" t="n">
-        <v>1.642331360647951e-07</v>
+        <v>1.737861762534574e-07</v>
       </c>
       <c r="P41" s="6" t="n">
-        <v>-1.642331360647951e-07</v>
+        <v>-1.737861762534574e-07</v>
       </c>
       <c r="Q41" s="6" t="n">
         <v>0</v>
@@ -4493,7 +4493,7 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>10234615.9342856</v>
+        <v>10840739.61571033</v>
       </c>
     </row>
     <row r="5">
@@ -4513,7 +4513,7 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>10308771.99513011</v>
+        <v>10914895.67655484</v>
       </c>
     </row>
     <row r="8">
@@ -4530,7 +4530,7 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>13377121.85957116</v>
+        <v>13983245.54099589</v>
       </c>
     </row>
     <row r="11">
@@ -4540,7 +4540,7 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>10234615.9342856</v>
+        <v>10840739.61571033</v>
       </c>
     </row>
     <row r="12">
@@ -4563,7 +4563,7 @@
     <row r="15" ht="60" customHeight="1">
       <c r="A15" s="10" t="inlineStr">
         <is>
-          <t>sUSDS spread (Curve LP + PSM3) — 30 bps × value × n_days credited to prime_agent_revenue. Sky still charges full BR on the underlying utilized; this row is the prime's offsetting pickup on the share-price-appreciation accounting (SSR + BR + 30 bps nets to zero economically).</t>
+          <t>sUSDS spread (Curve LP + PSM3) — 30 bps × value × n_days deducted from sky_revenue. Sky charges full BR on the underlying utilized; this row is the offsetting refund to the prime so SSR + BR + 30 bps nets to zero economically.</t>
         </is>
       </c>
       <c r="B15" s="3" t="n">
@@ -4883,7 +4883,7 @@
     <row r="3" ht="45" customHeight="1">
       <c r="A3" s="10" t="inlineStr">
         <is>
-          <t>cum_debt = Σ on-chain Vat dart from frob (0x76088703) + grab (0x7bab3f40). utilized = cum_debt − Σ deductions. base_apy = (1+SSR)(1+0.003)−1 (multiplicative). sub_apy applies on the first cap_usd of utilized when the subsidy is active; excess pays base_apy.</t>
+          <t>cum_debt = Σ on-chain Vat dart from frob (0x76088703) + grab (0x7bab3f40), then scaled by Vat.ilks[ilk].rate_d / 1e27 read at each day's EoD block — actual outstanding USDS per day, not raw normalised Art. utilized = cum_debt − Σ deductions. base_apy = (1+SSR)(1+0.003)−1 (multiplicative). sub_apy applies on the first cap_usd of utilized when the subsidy is active; excess pays base_apy.</t>
         </is>
       </c>
     </row>
@@ -4970,7 +4970,7 @@
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>3786873547.945224</v>
+        <v>3958458569.003264</v>
       </c>
       <c r="C6" s="6" t="n">
         <v>334970000</v>
@@ -4988,7 +4988,7 @@
         <v>127906874.3387326</v>
       </c>
       <c r="H6" s="6" t="n">
-        <v>3064694189.09428</v>
+        <v>3236279210.15232</v>
       </c>
       <c r="I6" s="7" t="n">
         <v>0.0375</v>
@@ -5006,10 +5006,10 @@
         <v>0.0406125</v>
       </c>
       <c r="N6" s="3" t="n">
-        <v>334275.4575777341</v>
+        <v>352990.7544030308</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>413045.742878023</v>
+        <v>431761.0397033197</v>
       </c>
     </row>
     <row r="7">
@@ -5019,7 +5019,7 @@
         </is>
       </c>
       <c r="B7" s="6" t="n">
-        <v>4113602587.50019</v>
+        <v>4299991854.969555</v>
       </c>
       <c r="C7" s="6" t="n">
         <v>334970000</v>
@@ -5037,7 +5037,7 @@
         <v>131684974.1461452</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>3396951901.175869</v>
+        <v>3583341168.645234</v>
       </c>
       <c r="I7" s="7" t="n">
         <v>0.0375</v>
@@ -5055,10 +5055,10 @@
         <v>0.0406125</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>370515.8104113157</v>
+        <v>390845.8511353183</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>448683.0666899128</v>
+        <v>469013.1074139154</v>
       </c>
     </row>
     <row r="8">
@@ -5068,7 +5068,7 @@
         </is>
       </c>
       <c r="B8" s="6" t="n">
-        <v>4112495173.033005</v>
+        <v>4298834263.032152</v>
       </c>
       <c r="C8" s="6" t="n">
         <v>334970000</v>
@@ -5086,7 +5086,7 @@
         <v>129926697.4882286</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>3390890511.133594</v>
+        <v>3577229601.132741</v>
       </c>
       <c r="I8" s="7" t="n">
         <v>0.0375</v>
@@ -5104,10 +5104,10 @@
         <v>0.0406125</v>
       </c>
       <c r="N8" s="3" t="n">
-        <v>369854.6762801686</v>
+        <v>390179.243995844</v>
       </c>
       <c r="O8" s="3" t="n">
-        <v>448562.277647057</v>
+        <v>468886.8453627324</v>
       </c>
     </row>
     <row r="9">
@@ -5117,7 +5117,7 @@
         </is>
       </c>
       <c r="B9" s="6" t="n">
-        <v>4014386628.19746</v>
+        <v>4196280373.899142</v>
       </c>
       <c r="C9" s="6" t="n">
         <v>334970000</v>
@@ -5135,7 +5135,7 @@
         <v>129945312.0277757</v>
       </c>
       <c r="H9" s="6" t="n">
-        <v>3300217558.653535</v>
+        <v>3482111304.355217</v>
       </c>
       <c r="I9" s="7" t="n">
         <v>0.0375</v>
@@ -5153,10 +5153,10 @@
         <v>0.0406125</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>359964.7033138436</v>
+        <v>379804.4038919058</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>437861.2821500545</v>
+        <v>457700.9827281167</v>
       </c>
     </row>
     <row r="10">
@@ -5166,7 +5166,7 @@
         </is>
       </c>
       <c r="B10" s="6" t="n">
-        <v>3967538459.305897</v>
+        <v>4147309492.446936</v>
       </c>
       <c r="C10" s="6" t="n">
         <v>334970000</v>
@@ -5184,7 +5184,7 @@
         <v>129991339.9884334</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>3258291889.719903</v>
+        <v>3438062922.860942</v>
       </c>
       <c r="I10" s="7" t="n">
         <v>0.0375</v>
@@ -5202,10 +5202,10 @@
         <v>0.0406125</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>355391.7438920149</v>
+        <v>374999.9137956497</v>
       </c>
       <c r="O10" s="3" t="n">
-        <v>432751.4107806262</v>
+        <v>452359.580684261</v>
       </c>
     </row>
     <row r="11">
@@ -5215,7 +5215,7 @@
         </is>
       </c>
       <c r="B11" s="6" t="n">
-        <v>3773637803.723945</v>
+        <v>3944623106.987827</v>
       </c>
       <c r="C11" s="6" t="n">
         <v>334970000</v>
@@ -5233,7 +5233,7 @@
         <v>132866251.0455103</v>
       </c>
       <c r="H11" s="6" t="n">
-        <v>3061037681.897975</v>
+        <v>3232022985.161858</v>
       </c>
       <c r="I11" s="7" t="n">
         <v>0.0375</v>
@@ -5251,10 +5251,10 @@
         <v>0.0406125</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>333876.6312868336</v>
+        <v>352526.5150798046</v>
       </c>
       <c r="O11" s="3" t="n">
-        <v>411602.080253643</v>
+        <v>430251.9640466141</v>
       </c>
     </row>
     <row r="12">
@@ -5264,7 +5264,7 @@
         </is>
       </c>
       <c r="B12" s="6" t="n">
-        <v>3829641619.123199</v>
+        <v>4003164481.596004</v>
       </c>
       <c r="C12" s="6" t="n">
         <v>334970000</v>
@@ -5282,7 +5282,7 @@
         <v>133190285.3282568</v>
       </c>
       <c r="H12" s="6" t="n">
-        <v>3123331493.311244</v>
+        <v>3296854355.784049</v>
       </c>
       <c r="I12" s="7" t="n">
         <v>0.0375</v>
@@ -5300,10 +5300,10 @@
         <v>0.0406125</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>340671.2055672075</v>
+        <v>359597.8686123178</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>417710.5856586202</v>
+        <v>436637.2487037305</v>
       </c>
     </row>
     <row r="13">
@@ -5313,7 +5313,7 @@
         </is>
       </c>
       <c r="B13" s="6" t="n">
-        <v>3112489658.938523</v>
+        <v>3253518028.888103</v>
       </c>
       <c r="C13" s="6" t="n">
         <v>334970000</v>
@@ -5331,7 +5331,7 @@
         <v>136081135.6656561</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>2423139600.328023</v>
+        <v>2564167970.277603</v>
       </c>
       <c r="I13" s="7" t="n">
         <v>0.0375</v>
@@ -5349,10 +5349,10 @@
         <v>0.0406125</v>
       </c>
       <c r="N13" s="3" t="n">
-        <v>264299.1596214559</v>
+        <v>279681.550159505</v>
       </c>
       <c r="O13" s="3" t="n">
-        <v>339488.6539250828</v>
+        <v>354871.0444631319</v>
       </c>
     </row>
     <row r="14">
@@ -5362,7 +5362,7 @@
         </is>
       </c>
       <c r="B14" s="6" t="n">
-        <v>3862142308.882361</v>
+        <v>4037137792.890086</v>
       </c>
       <c r="C14" s="6" t="n">
         <v>334970000</v>
@@ -5380,7 +5380,7 @@
         <v>136418480.8456975</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>3158250277.049653</v>
+        <v>3333245761.057378</v>
       </c>
       <c r="I14" s="7" t="n">
         <v>0.0375</v>
@@ -5398,10 +5398,10 @@
         <v>0.0406125</v>
       </c>
       <c r="N14" s="3" t="n">
-        <v>344479.902844003</v>
+        <v>363567.1891706061</v>
       </c>
       <c r="O14" s="3" t="n">
-        <v>421255.5341169349</v>
+        <v>440342.8204435381</v>
       </c>
     </row>
     <row r="15">
@@ -5411,7 +5411,7 @@
         </is>
       </c>
       <c r="B15" s="6" t="n">
-        <v>4007860775.201573</v>
+        <v>4189458831.435534</v>
       </c>
       <c r="C15" s="6" t="n">
         <v>334970000</v>
@@ -5429,7 +5429,7 @@
         <v>136520708.1372503</v>
       </c>
       <c r="H15" s="6" t="n">
-        <v>3295738005.568375</v>
+        <v>3477336061.802335</v>
       </c>
       <c r="I15" s="7" t="n">
         <v>0.0375</v>
@@ -5447,10 +5447,10 @@
         <v>0.0406125</v>
       </c>
       <c r="N15" s="3" t="n">
-        <v>359476.1049203679</v>
+        <v>379283.5537545285</v>
       </c>
       <c r="O15" s="3" t="n">
-        <v>437149.4876408184</v>
+        <v>456956.936474979</v>
       </c>
     </row>
     <row r="16">
@@ -5460,7 +5460,7 @@
         </is>
       </c>
       <c r="B16" s="6" t="n">
-        <v>3944031608.133983</v>
+        <v>4122737534.795423</v>
       </c>
       <c r="C16" s="6" t="n">
         <v>334970000</v>
@@ -5478,7 +5478,7 @@
         <v>146800932.9007985</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>3200056943.599629</v>
+        <v>3378762870.261068</v>
       </c>
       <c r="I16" s="7" t="n">
         <v>0.0375</v>
@@ -5496,10 +5496,10 @@
         <v>0.0406125</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>349039.8823161875</v>
+        <v>368531.8778370391</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>430187.4474789483</v>
+        <v>449679.4429997999</v>
       </c>
     </row>
     <row r="17">
@@ -5509,7 +5509,7 @@
         </is>
       </c>
       <c r="B17" s="6" t="n">
-        <v>3869106066.859931</v>
+        <v>4044417082.016002</v>
       </c>
       <c r="C17" s="6" t="n">
         <v>334970000</v>
@@ -5527,7 +5527,7 @@
         <v>146820705.7658038</v>
       </c>
       <c r="H17" s="6" t="n">
-        <v>3141318441.973659</v>
+        <v>3316629457.12973</v>
       </c>
       <c r="I17" s="7" t="n">
         <v>0.0375</v>
@@ -5545,10 +5545,10 @@
         <v>0.0406125</v>
       </c>
       <c r="N17" s="3" t="n">
-        <v>342633.0964194667</v>
+        <v>361754.7986820444</v>
       </c>
       <c r="O17" s="3" t="n">
-        <v>422015.092245996</v>
+        <v>441136.7945085737</v>
       </c>
     </row>
     <row r="18">
@@ -5558,7 +5558,7 @@
         </is>
       </c>
       <c r="B18" s="6" t="n">
-        <v>3869966485.495641</v>
+        <v>4045316486.624668</v>
       </c>
       <c r="C18" s="6" t="n">
         <v>334970000</v>
@@ -5576,7 +5576,7 @@
         <v>146084521.7500651</v>
       </c>
       <c r="H18" s="6" t="n">
-        <v>3132456009.424751</v>
+        <v>3307806010.553778</v>
       </c>
       <c r="I18" s="7" t="n">
         <v>0.0375</v>
@@ -5594,10 +5594,10 @@
         <v>0.0406125</v>
       </c>
       <c r="N18" s="3" t="n">
-        <v>341666.4441165779</v>
+        <v>360792.3986970524</v>
       </c>
       <c r="O18" s="3" t="n">
-        <v>422108.9407070216</v>
+        <v>441234.8952874962</v>
       </c>
     </row>
     <row r="19">
@@ -5607,7 +5607,7 @@
         </is>
       </c>
       <c r="B19" s="6" t="n">
-        <v>3906757002.936191</v>
+        <v>4083773999.709474</v>
       </c>
       <c r="C19" s="6" t="n">
         <v>334970000</v>
@@ -5625,7 +5625,7 @@
         <v>174559965.1979237</v>
       </c>
       <c r="H19" s="6" t="n">
-        <v>3165704851.017045</v>
+        <v>3342721847.790328</v>
       </c>
       <c r="I19" s="7" t="n">
         <v>0.0375</v>
@@ -5643,10 +5643,10 @@
         <v>0.0406125</v>
       </c>
       <c r="N19" s="3" t="n">
-        <v>345292.9957564588</v>
+        <v>364600.7745899851</v>
       </c>
       <c r="O19" s="3" t="n">
-        <v>426121.7936356186</v>
+        <v>445429.5724691449</v>
       </c>
     </row>
     <row r="20">
@@ -5656,7 +5656,7 @@
         </is>
       </c>
       <c r="B20" s="6" t="n">
-        <v>3941296256.964431</v>
+        <v>4119878243.578207</v>
       </c>
       <c r="C20" s="6" t="n">
         <v>334970000</v>
@@ -5674,7 +5674,7 @@
         <v>169618722.6830847</v>
       </c>
       <c r="H20" s="6" t="n">
-        <v>3196152749.65845</v>
+        <v>3374734736.272226</v>
       </c>
       <c r="I20" s="7" t="n">
         <v>0.0375</v>
@@ -5692,10 +5692,10 @@
         <v>0.0406125</v>
       </c>
       <c r="N20" s="3" t="n">
-        <v>348614.0400834441</v>
+        <v>368092.5170887151</v>
       </c>
       <c r="O20" s="3" t="n">
-        <v>429889.0944598799</v>
+        <v>449367.5714651509</v>
       </c>
     </row>
     <row r="21">
@@ -5705,7 +5705,7 @@
         </is>
       </c>
       <c r="B21" s="6" t="n">
-        <v>3949955056.90474</v>
+        <v>4128929377.815208</v>
       </c>
       <c r="C21" s="6" t="n">
         <v>334970000</v>
@@ -5723,7 +5723,7 @@
         <v>172338153.0245515</v>
       </c>
       <c r="H21" s="6" t="n">
-        <v>3193714712.03263</v>
+        <v>3372689032.943098</v>
       </c>
       <c r="I21" s="7" t="n">
         <v>0.0375</v>
@@ -5741,10 +5741,10 @@
         <v>0.0406125</v>
       </c>
       <c r="N21" s="3" t="n">
-        <v>348348.1159511562</v>
+        <v>367869.3860439127</v>
       </c>
       <c r="O21" s="3" t="n">
-        <v>430833.5359387135</v>
+        <v>450354.80603147</v>
       </c>
     </row>
     <row r="22">
@@ -5754,7 +5754,7 @@
         </is>
       </c>
       <c r="B22" s="6" t="n">
-        <v>3930000358.477587</v>
+        <v>4108070522.619555</v>
       </c>
       <c r="C22" s="6" t="n">
         <v>334970000</v>
@@ -5772,7 +5772,7 @@
         <v>162877756.5589872</v>
       </c>
       <c r="H22" s="6" t="n">
-        <v>3173869467.112352</v>
+        <v>3351939631.25432</v>
       </c>
       <c r="I22" s="7" t="n">
         <v>0.0375</v>
@@ -5790,10 +5790,10 @@
         <v>0.0406125</v>
       </c>
       <c r="N22" s="3" t="n">
-        <v>346183.5351097547</v>
+        <v>365606.1860911532</v>
       </c>
       <c r="O22" s="3" t="n">
-        <v>428657.0166725176</v>
+        <v>448079.6676539161</v>
       </c>
     </row>
     <row r="23">
@@ -5803,7 +5803,7 @@
         </is>
       </c>
       <c r="B23" s="6" t="n">
-        <v>4128625750.909277</v>
+        <v>4315695724.97665</v>
       </c>
       <c r="C23" s="6" t="n">
         <v>334970000</v>
@@ -5821,7 +5821,7 @@
         <v>231737478.377994</v>
       </c>
       <c r="H23" s="6" t="n">
-        <v>3319950868.733045</v>
+        <v>3507020842.800418</v>
       </c>
       <c r="I23" s="7" t="n">
         <v>0.0375</v>
@@ -5839,10 +5839,10 @@
         <v>0.0406125</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>362117.0750838638</v>
+        <v>382521.3625337991</v>
       </c>
       <c r="O23" s="3" t="n">
-        <v>450321.6885271936</v>
+        <v>470725.9759771289</v>
       </c>
     </row>
     <row r="24">
@@ -5852,7 +5852,7 @@
         </is>
       </c>
       <c r="B24" s="6" t="n">
-        <v>4099347532.103574</v>
+        <v>4285090896.310144</v>
       </c>
       <c r="C24" s="6" t="n">
         <v>334970000</v>
@@ -5870,7 +5870,7 @@
         <v>229182741.6867744</v>
       </c>
       <c r="H24" s="6" t="n">
-        <v>3278042581.79532</v>
+        <v>3463785946.00189</v>
       </c>
       <c r="I24" s="7" t="n">
         <v>0.0375</v>
@@ -5888,10 +5888,10 @@
         <v>0.0406125</v>
       </c>
       <c r="N24" s="3" t="n">
-        <v>357546.011568862</v>
+        <v>377805.601671889</v>
       </c>
       <c r="O24" s="3" t="n">
-        <v>447128.2247149919</v>
+        <v>467387.814818019</v>
       </c>
     </row>
     <row r="25">
@@ -5901,7 +5901,7 @@
         </is>
       </c>
       <c r="B25" s="6" t="n">
-        <v>3849261001.889072</v>
+        <v>4023672827.820097</v>
       </c>
       <c r="C25" s="6" t="n">
         <v>334970000</v>
@@ -5919,7 +5919,7 @@
         <v>230888253.3173563</v>
       </c>
       <c r="H25" s="6" t="n">
-        <v>3031529776.667622</v>
+        <v>3205941602.598647</v>
       </c>
       <c r="I25" s="7" t="n">
         <v>0.0375</v>
@@ -5937,10 +5937,10 @@
         <v>0.0406125</v>
       </c>
       <c r="N25" s="3" t="n">
-        <v>330658.1148821178</v>
+        <v>349681.7398583154</v>
       </c>
       <c r="O25" s="3" t="n">
-        <v>419850.5310322215</v>
+        <v>438874.1560084191</v>
       </c>
     </row>
     <row r="26">
@@ -5950,7 +5950,7 @@
         </is>
       </c>
       <c r="B26" s="6" t="n">
-        <v>3796096805.831977</v>
+        <v>3968099737.041672</v>
       </c>
       <c r="C26" s="6" t="n">
         <v>334970000</v>
@@ -5968,7 +5968,7 @@
         <v>254742493.5135711</v>
       </c>
       <c r="H26" s="6" t="n">
-        <v>2952167920.756298</v>
+        <v>3124170851.965993</v>
       </c>
       <c r="I26" s="7" t="n">
         <v>0.0375</v>
@@ -5986,10 +5986,10 @@
         <v>0.0406125</v>
       </c>
       <c r="N26" s="3" t="n">
-        <v>322001.8774038798</v>
+        <v>340762.7569524604</v>
       </c>
       <c r="O26" s="3" t="n">
-        <v>414051.7514910269</v>
+        <v>432812.6310396074</v>
       </c>
     </row>
     <row r="27">
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="B27" s="6" t="n">
-        <v>4276518811.263577</v>
+        <v>4470289889.435416</v>
       </c>
       <c r="C27" s="6" t="n">
         <v>334970000</v>
@@ -6017,7 +6017,7 @@
         <v>239797730.4064276</v>
       </c>
       <c r="H27" s="6" t="n">
-        <v>3439871011.979409</v>
+        <v>3633642090.151248</v>
       </c>
       <c r="I27" s="7" t="n">
         <v>0.0375</v>
@@ -6035,10 +6035,10 @@
         <v>0.0406125</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>375197.1275403578</v>
+        <v>396332.3246676004</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>466452.8315947228</v>
+        <v>487588.0287219654</v>
       </c>
     </row>
     <row r="28">
@@ -6048,7 +6048,7 @@
         </is>
       </c>
       <c r="B28" s="6" t="n">
-        <v>4260541447.925423</v>
+        <v>4453588584.251801</v>
       </c>
       <c r="C28" s="6" t="n">
         <v>334970000</v>
@@ -6066,7 +6066,7 @@
         <v>240130221.5557107</v>
       </c>
       <c r="H28" s="6" t="n">
-        <v>3420062638.696182</v>
+        <v>3613109775.02256</v>
       </c>
       <c r="I28" s="7" t="n">
         <v>0.0375</v>
@@ -6084,10 +6084,10 @@
         <v>0.0406125</v>
       </c>
       <c r="N28" s="3" t="n">
-        <v>373036.568399846</v>
+        <v>394092.8030020469</v>
       </c>
       <c r="O28" s="3" t="n">
-        <v>464710.1322873164</v>
+        <v>485766.3668895173</v>
       </c>
     </row>
     <row r="29">
@@ -6097,7 +6097,7 @@
         </is>
       </c>
       <c r="B29" s="6" t="n">
-        <v>4278271428.210862</v>
+        <v>4472121918.280669</v>
       </c>
       <c r="C29" s="6" t="n">
         <v>334970000</v>
@@ -6115,7 +6115,7 @@
         <v>243572783.8200219</v>
       </c>
       <c r="H29" s="6" t="n">
-        <v>3434366864.528295</v>
+        <v>3628217354.598102</v>
       </c>
       <c r="I29" s="7" t="n">
         <v>0.0375</v>
@@ -6133,10 +6133,10 @@
         <v>0.0406125</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>374596.7735427734</v>
+        <v>395740.6323657326</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>466643.9948220676</v>
+        <v>487787.8536450268</v>
       </c>
     </row>
     <row r="30">
@@ -6146,7 +6146,7 @@
         </is>
       </c>
       <c r="B30" s="6" t="n">
-        <v>4275937035.604297</v>
+        <v>4469681753.247461</v>
       </c>
       <c r="C30" s="6" t="n">
         <v>334970000</v>
@@ -6164,7 +6164,7 @@
         <v>245605231.7022537</v>
       </c>
       <c r="H30" s="6" t="n">
-        <v>3428834151.644414</v>
+        <v>3622578869.287579</v>
       </c>
       <c r="I30" s="7" t="n">
         <v>0.0375</v>
@@ -6182,10 +6182,10 @@
         <v>0.0406125</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>373993.3038271044</v>
+        <v>395125.6257318154</v>
       </c>
       <c r="O30" s="3" t="n">
-        <v>466389.3755652744</v>
+        <v>487521.6974699855</v>
       </c>
     </row>
     <row r="31">
@@ -6195,7 +6195,7 @@
         </is>
       </c>
       <c r="B31" s="6" t="n">
-        <v>4019063778.948612</v>
+        <v>4201169448.550041</v>
       </c>
       <c r="C31" s="6" t="n">
         <v>334970000</v>
@@ -6213,7 +6213,7 @@
         <v>179571549.4489093</v>
       </c>
       <c r="H31" s="6" t="n">
-        <v>3231323652.541693</v>
+        <v>3413429322.143122</v>
       </c>
       <c r="I31" s="7" t="n">
         <v>0.0375</v>
@@ -6231,10 +6231,10 @@
         <v>0.0406125</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>352450.2367573421</v>
+        <v>372313.0525156438</v>
       </c>
       <c r="O31" s="3" t="n">
-        <v>438371.433118156</v>
+        <v>458234.2488764576</v>
       </c>
     </row>
     <row r="32">
@@ -6244,7 +6244,7 @@
         </is>
       </c>
       <c r="B32" s="6" t="n">
-        <v>3894612666.177943</v>
+        <v>4071079397.342402</v>
       </c>
       <c r="C32" s="6" t="n">
         <v>334970000</v>
@@ -6262,7 +6262,7 @@
         <v>206116586.0471416</v>
       </c>
       <c r="H32" s="6" t="n">
-        <v>3076501218.730989</v>
+        <v>3252967949.895449</v>
       </c>
       <c r="I32" s="7" t="n">
         <v>0.0375</v>
@@ -6280,10 +6280,10 @@
         <v>0.0406125</v>
       </c>
       <c r="N32" s="3" t="n">
-        <v>335563.2859843952</v>
+        <v>354811.0456849087</v>
       </c>
       <c r="O32" s="3" t="n">
-        <v>424797.1741217737</v>
+        <v>444044.9338222871</v>
       </c>
     </row>
     <row r="33">
@@ -6293,7 +6293,7 @@
         </is>
       </c>
       <c r="B33" s="6" t="n">
-        <v>3904793970.371299</v>
+        <v>4081722021.216043</v>
       </c>
       <c r="C33" s="6" t="n">
         <v>334970000</v>
@@ -6311,7 +6311,7 @@
         <v>248420857.3449725</v>
       </c>
       <c r="H33" s="6" t="n">
-        <v>3044549507.900335</v>
+        <v>3221477558.745079</v>
       </c>
       <c r="I33" s="7" t="n">
         <v>0.0375</v>
@@ -6329,10 +6329,10 @@
         <v>0.0406125</v>
       </c>
       <c r="N33" s="3" t="n">
-        <v>332078.2163169826</v>
+        <v>351376.2935492632</v>
       </c>
       <c r="O33" s="3" t="n">
-        <v>425907.6797409258</v>
+        <v>445205.7569732065</v>
       </c>
     </row>
     <row r="34">
@@ -6342,7 +6342,7 @@
         </is>
       </c>
       <c r="B34" s="6" t="n">
-        <v>3980438326.717189</v>
+        <v>4160793858.916194</v>
       </c>
       <c r="C34" s="6" t="n">
         <v>334970000</v>
@@ -6360,7 +6360,7 @@
         <v>303291142.7334828</v>
       </c>
       <c r="H34" s="6" t="n">
-        <v>3066517185.716836</v>
+        <v>3246872717.915842</v>
       </c>
       <c r="I34" s="7" t="n">
         <v>0.0375</v>
@@ -6378,10 +6378,10 @@
         <v>0.0406125</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>334474.2973289681</v>
+        <v>354146.2203113768</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>434158.4383062261</v>
+        <v>453830.3612886349</v>
       </c>
     </row>
     <row r="35">
@@ -6391,7 +6391,7 @@
         </is>
       </c>
       <c r="B35" s="6" t="n">
-        <v>3949996189.520216</v>
+        <v>4128972374.168832</v>
       </c>
       <c r="C35" s="6" t="n">
         <v>334970000</v>
@@ -6409,7 +6409,7 @@
         <v>295800536.4468129</v>
       </c>
       <c r="H35" s="6" t="n">
-        <v>3045533293.972157</v>
+        <v>3224509478.620773</v>
       </c>
       <c r="I35" s="7" t="n">
         <v>0.0375</v>
@@ -6427,10 +6427,10 @@
         <v>0.0406125</v>
       </c>
       <c r="N35" s="3" t="n">
-        <v>332185.5208371161</v>
+        <v>351706.9942134252</v>
       </c>
       <c r="O35" s="3" t="n">
-        <v>430838.0223973978</v>
+        <v>450359.4957737069</v>
       </c>
     </row>
     <row r="36">
@@ -6440,7 +6440,7 @@
         </is>
       </c>
       <c r="B36" s="6" t="n">
-        <v>3938439863.321327</v>
+        <v>4116892425.396048</v>
       </c>
       <c r="C36" s="6" t="n">
         <v>334970000</v>
@@ -6458,7 +6458,7 @@
         <v>289518568.352541</v>
       </c>
       <c r="H36" s="6" t="n">
-        <v>3039962404.608198</v>
+        <v>3218414966.682919</v>
       </c>
       <c r="I36" s="7" t="n">
         <v>0.0375</v>
@@ -6476,10 +6476,10 @@
         <v>0.0406125</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>331577.8870973847</v>
+        <v>351042.2473770235</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>429577.5389723965</v>
+        <v>449041.8992520352</v>
       </c>
     </row>
     <row r="38">
@@ -6501,10 +6501,10 @@
       <c r="L38" t="inlineStr"/>
       <c r="M38" t="inlineStr"/>
       <c r="N38" s="11" t="n">
-        <v>10742059.80203898</v>
+        <v>11348183.48346371</v>
       </c>
       <c r="O38" s="11" t="n">
-        <v>13377121.85957116</v>
+        <v>13983245.54099589</v>
       </c>
     </row>
   </sheetData>

--- a/settlements/spark/2026-05/spark_settlement_may_2026.xlsx
+++ b/settlements/spark/2026-05/spark_settlement_may_2026.xlsx
@@ -663,7 +663,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-06-09T17:00:59+00:00</t>
+          <t>2026-06-09T19:11:23+00:00</t>
         </is>
       </c>
     </row>

--- a/settlements/spark/2026-05/spark_settlement_may_2026.xlsx
+++ b/settlements/spark/2026-05/spark_settlement_may_2026.xlsx
@@ -663,7 +663,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-06-09T19:11:23+00:00</t>
+          <t>2026-06-09T19:55:37+00:00</t>
         </is>
       </c>
     </row>

--- a/settlements/spark/2026-05/spark_settlement_may_2026.xlsx
+++ b/settlements/spark/2026-05/spark_settlement_may_2026.xlsx
@@ -663,7 +663,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-06-09T19:55:37+00:00</t>
+          <t>2026-06-09T20:54:34+00:00</t>
         </is>
       </c>
     </row>

--- a/settlements/spark/2026-05/spark_settlement_may_2026.xlsx
+++ b/settlements/spark/2026-05/spark_settlement_may_2026.xlsx
@@ -663,7 +663,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-06-09T20:54:34+00:00</t>
+          <t>2026-06-09T22:04:38+00:00</t>
         </is>
       </c>
     </row>

--- a/settlements/spark/2026-05/spark_settlement_may_2026.xlsx
+++ b/settlements/spark/2026-05/spark_settlement_may_2026.xlsx
@@ -488,7 +488,7 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>7865873.684241995</v>
+        <v>8845861.937405553</v>
       </c>
     </row>
     <row r="5">
@@ -504,7 +504,7 @@
     <row r="6">
       <c r="A6" t="inlineStr"/>
       <c r="B6" s="4" t="n">
-        <v>7987774.433951153</v>
+        <v>8967762.68711471</v>
       </c>
     </row>
     <row r="8">
@@ -612,7 +612,7 @@
         </is>
       </c>
       <c r="B21" s="3" t="n">
-        <v>7865873.684241995</v>
+        <v>8845861.937405553</v>
       </c>
     </row>
     <row r="22">
@@ -628,7 +628,7 @@
     <row r="23">
       <c r="A23" t="inlineStr"/>
       <c r="B23" s="4" t="n">
-        <v>-3159776.350163311</v>
+        <v>-2179788.096999754</v>
       </c>
     </row>
     <row r="25">
@@ -663,7 +663,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-06-09T22:04:38+00:00</t>
+          <t>2026-06-09T22:11:38+00:00</t>
         </is>
       </c>
     </row>
@@ -1171,13 +1171,13 @@
         <v>436043.0489150246</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>0</v>
+        <v>436043.0489150246</v>
       </c>
       <c r="I7" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J7" s="6" t="n">
-        <v>0</v>
+        <v>436043.0489150246</v>
       </c>
       <c r="K7" s="6" t="n">
         <v>0</v>
@@ -1195,7 +1195,7 @@
         <v>296108.7831004824</v>
       </c>
       <c r="P7" s="6" t="n">
-        <v>-332573.59694228</v>
+        <v>103469.4519727446</v>
       </c>
       <c r="Q7" s="6" t="n">
         <v>0</v>
@@ -1431,13 +1431,13 @@
         <v>310435.429389201</v>
       </c>
       <c r="H11" s="6" t="n">
-        <v>0</v>
+        <v>310435.429389201</v>
       </c>
       <c r="I11" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J11" s="6" t="n">
-        <v>0</v>
+        <v>310435.429389201</v>
       </c>
       <c r="K11" s="6" t="n">
         <v>0</v>
@@ -1455,7 +1455,7 @@
         <v>210810.9679914328</v>
       </c>
       <c r="P11" s="6" t="n">
-        <v>-236771.6390094491</v>
+        <v>73663.79037975192</v>
       </c>
       <c r="Q11" s="6" t="n">
         <v>0</v>
@@ -1561,13 +1561,13 @@
         <v>230521.0318286367</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>0</v>
+        <v>230521.0318286367</v>
       </c>
       <c r="I13" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J13" s="6" t="n">
-        <v>0</v>
+        <v>230521.0318286367</v>
       </c>
       <c r="K13" s="6" t="n">
         <v>0</v>
@@ -1585,7 +1585,7 @@
         <v>156542.5762059274</v>
       </c>
       <c r="P13" s="6" t="n">
-        <v>-175820.2748945458</v>
+        <v>54700.75693409086</v>
       </c>
       <c r="Q13" s="6" t="n">
         <v>0</v>
@@ -2345,13 +2345,13 @@
         <v>2988.743030694792</v>
       </c>
       <c r="H25" s="6" t="n">
-        <v>0</v>
+        <v>2988.743030694792</v>
       </c>
       <c r="I25" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J25" s="6" t="n">
-        <v>0</v>
+        <v>2988.743030694792</v>
       </c>
       <c r="K25" s="6" t="n">
         <v>0</v>
@@ -2369,7 +2369,7 @@
         <v>2029.600205808002</v>
       </c>
       <c r="P25" s="6" t="n">
-        <v>-2279.53873482809</v>
+        <v>709.204295866702</v>
       </c>
       <c r="Q25" s="6" t="n">
         <v>0</v>

--- a/settlements/spark/2026-05/spark_settlement_may_2026.xlsx
+++ b/settlements/spark/2026-05/spark_settlement_may_2026.xlsx
@@ -488,7 +488,7 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>7865873.684241995</v>
+        <v>12636329.49077535</v>
       </c>
     </row>
     <row r="5">
@@ -504,7 +504,7 @@
     <row r="6">
       <c r="A6" t="inlineStr"/>
       <c r="B6" s="4" t="n">
-        <v>7987774.433951153</v>
+        <v>12758230.24048451</v>
       </c>
     </row>
     <row r="8">
@@ -612,7 +612,7 @@
         </is>
       </c>
       <c r="B21" s="3" t="n">
-        <v>7865873.684241995</v>
+        <v>12636329.49077535</v>
       </c>
     </row>
     <row r="22">
@@ -628,7 +628,7 @@
     <row r="23">
       <c r="A23" t="inlineStr"/>
       <c r="B23" s="4" t="n">
-        <v>-3159776.350163311</v>
+        <v>1610679.456370043</v>
       </c>
     </row>
     <row r="25">
@@ -663,7 +663,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-06-09T17:00:59+00:00</t>
+          <t>2026-06-09T22:32:54+00:00</t>
         </is>
       </c>
     </row>
@@ -4446,7 +4446,7 @@
       <c r="D62" t="inlineStr"/>
       <c r="E62" t="inlineStr"/>
       <c r="F62" s="9" t="n">
-        <v>-4770455.806533354</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/settlements/spark/2026-05/spark_settlement_may_2026.xlsx
+++ b/settlements/spark/2026-05/spark_settlement_may_2026.xlsx
@@ -663,7 +663,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-06-09T22:32:54+00:00</t>
+          <t>2026-06-09T23:18:46+00:00</t>
         </is>
       </c>
     </row>

--- a/settlements/spark/2026-05/spark_settlement_may_2026.xlsx
+++ b/settlements/spark/2026-05/spark_settlement_may_2026.xlsx
@@ -488,7 +488,7 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>12636329.49077535</v>
+        <v>13616317.74393891</v>
       </c>
     </row>
     <row r="5">
@@ -504,7 +504,7 @@
     <row r="6">
       <c r="A6" t="inlineStr"/>
       <c r="B6" s="4" t="n">
-        <v>12758230.24048451</v>
+        <v>13738218.49364807</v>
       </c>
     </row>
     <row r="8">
@@ -612,7 +612,7 @@
         </is>
       </c>
       <c r="B21" s="3" t="n">
-        <v>12636329.49077535</v>
+        <v>13616317.74393891</v>
       </c>
     </row>
     <row r="22">
@@ -628,7 +628,7 @@
     <row r="23">
       <c r="A23" t="inlineStr"/>
       <c r="B23" s="4" t="n">
-        <v>1610679.456370043</v>
+        <v>2590667.7095336</v>
       </c>
     </row>
     <row r="25">
@@ -663,7 +663,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-06-09T23:18:46+00:00</t>
+          <t>2026-06-09T23:35:55+00:00</t>
         </is>
       </c>
     </row>
@@ -1171,13 +1171,13 @@
         <v>436043.0489150246</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>0</v>
+        <v>436043.0489150246</v>
       </c>
       <c r="I7" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J7" s="6" t="n">
-        <v>0</v>
+        <v>436043.0489150246</v>
       </c>
       <c r="K7" s="6" t="n">
         <v>0</v>
@@ -1195,7 +1195,7 @@
         <v>296108.7831004824</v>
       </c>
       <c r="P7" s="6" t="n">
-        <v>-332573.59694228</v>
+        <v>103469.4519727446</v>
       </c>
       <c r="Q7" s="6" t="n">
         <v>0</v>
@@ -1431,13 +1431,13 @@
         <v>310435.429389201</v>
       </c>
       <c r="H11" s="6" t="n">
-        <v>0</v>
+        <v>310435.429389201</v>
       </c>
       <c r="I11" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J11" s="6" t="n">
-        <v>0</v>
+        <v>310435.429389201</v>
       </c>
       <c r="K11" s="6" t="n">
         <v>0</v>
@@ -1455,7 +1455,7 @@
         <v>210810.9679914328</v>
       </c>
       <c r="P11" s="6" t="n">
-        <v>-236771.6390094491</v>
+        <v>73663.79037975192</v>
       </c>
       <c r="Q11" s="6" t="n">
         <v>0</v>
@@ -1561,13 +1561,13 @@
         <v>230521.0318286367</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>0</v>
+        <v>230521.0318286367</v>
       </c>
       <c r="I13" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J13" s="6" t="n">
-        <v>0</v>
+        <v>230521.0318286367</v>
       </c>
       <c r="K13" s="6" t="n">
         <v>0</v>
@@ -1585,7 +1585,7 @@
         <v>156542.5762059274</v>
       </c>
       <c r="P13" s="6" t="n">
-        <v>-175820.2748945458</v>
+        <v>54700.75693409086</v>
       </c>
       <c r="Q13" s="6" t="n">
         <v>0</v>
@@ -2345,13 +2345,13 @@
         <v>2988.743030694792</v>
       </c>
       <c r="H25" s="6" t="n">
-        <v>0</v>
+        <v>2988.743030694792</v>
       </c>
       <c r="I25" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J25" s="6" t="n">
-        <v>0</v>
+        <v>2988.743030694792</v>
       </c>
       <c r="K25" s="6" t="n">
         <v>0</v>
@@ -2369,7 +2369,7 @@
         <v>2029.600205808002</v>
       </c>
       <c r="P25" s="6" t="n">
-        <v>-2279.53873482809</v>
+        <v>709.204295866702</v>
       </c>
       <c r="Q25" s="6" t="n">
         <v>0</v>

--- a/settlements/spark/2026-05/spark_settlement_may_2026.xlsx
+++ b/settlements/spark/2026-05/spark_settlement_may_2026.xlsx
@@ -488,7 +488,7 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>13616317.74393891</v>
+        <v>17362443.6152733</v>
       </c>
     </row>
     <row r="5">
@@ -504,7 +504,7 @@
     <row r="6">
       <c r="A6" t="inlineStr"/>
       <c r="B6" s="4" t="n">
-        <v>13738218.49364807</v>
+        <v>17484344.36498246</v>
       </c>
     </row>
     <row r="8">
@@ -612,7 +612,7 @@
         </is>
       </c>
       <c r="B21" s="3" t="n">
-        <v>13616317.74393891</v>
+        <v>17362443.6152733</v>
       </c>
     </row>
     <row r="22">
@@ -628,7 +628,7 @@
     <row r="23">
       <c r="A23" t="inlineStr"/>
       <c r="B23" s="4" t="n">
-        <v>2590667.7095336</v>
+        <v>6336793.580867989</v>
       </c>
     </row>
     <row r="25">
@@ -663,7 +663,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-06-09T23:35:55+00:00</t>
+          <t>2026-06-10T01:22:39+00:00</t>
         </is>
       </c>
     </row>
@@ -842,13 +842,13 @@
         <v>-145686527.279134</v>
       </c>
       <c r="H2" s="6" t="n">
-        <v>0</v>
+        <v>3746125.871334389</v>
       </c>
       <c r="I2" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J2" s="6" t="n">
-        <v>0</v>
+        <v>3746125.871334389</v>
       </c>
       <c r="K2" s="6" t="n">
         <v>0</v>
@@ -866,7 +866,7 @@
         <v>4410254.829322996</v>
       </c>
       <c r="P2" s="6" t="n">
-        <v>-4410254.829322996</v>
+        <v>-664128.9579886064</v>
       </c>
       <c r="Q2" s="6" t="n">
         <v>0</v>

--- a/settlements/spark/2026-05/spark_settlement_may_2026.xlsx
+++ b/settlements/spark/2026-05/spark_settlement_may_2026.xlsx
@@ -488,7 +488,7 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>17362443.6152733</v>
+        <v>18627818.80597491</v>
       </c>
     </row>
     <row r="5">
@@ -504,7 +504,7 @@
     <row r="6">
       <c r="A6" t="inlineStr"/>
       <c r="B6" s="4" t="n">
-        <v>17484344.36498246</v>
+        <v>18749719.55568407</v>
       </c>
     </row>
     <row r="8">
@@ -536,13 +536,13 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>74156.06084450937</v>
+        <v>39615.44347073233</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr"/>
       <c r="B11" s="4" t="n">
-        <v>10914895.67655484</v>
+        <v>10880355.05918106</v>
       </c>
     </row>
     <row r="13">
@@ -612,7 +612,7 @@
         </is>
       </c>
       <c r="B21" s="3" t="n">
-        <v>17362443.6152733</v>
+        <v>18627818.80597491</v>
       </c>
     </row>
     <row r="22">
@@ -628,7 +628,7 @@
     <row r="23">
       <c r="A23" t="inlineStr"/>
       <c r="B23" s="4" t="n">
-        <v>6336793.580867989</v>
+        <v>6371334.198241767</v>
       </c>
     </row>
     <row r="25">
@@ -663,7 +663,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-06-10T01:22:39+00:00</t>
+          <t>2026-06-10T01:54:54+00:00</t>
         </is>
       </c>
     </row>
@@ -1728,12 +1728,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>S24</t>
+          <t>S15</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Spark.fi USDT Reserve Curve (sUSDS/USDT)</t>
+          <t>Maple syrupUSDT (ERC-4626)</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1743,66 +1743,62 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E16" s="6" t="n">
-        <v>50002415.26289953</v>
+        <v>76904851.98939763</v>
       </c>
       <c r="F16" s="6" t="n">
-        <v>48750265.64989898</v>
+        <v>0</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>-1252149.613000547</v>
+        <v>-76904851.98939763</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>74156.06084450937</v>
+        <v>119641.6179259726</v>
       </c>
       <c r="I16" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J16" s="6" t="n">
-        <v>0</v>
+        <v>119641.6179259726</v>
       </c>
       <c r="K16" s="6" t="n">
-        <v>74156.06084450937</v>
+        <v>0</v>
       </c>
       <c r="L16" s="6" t="n">
-        <v>49959631.20890453</v>
+        <v>29672997.14110577</v>
       </c>
       <c r="M16" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N16" s="6" t="n">
-        <v>0</v>
+        <v>68851.97760926072</v>
       </c>
       <c r="O16" s="6" t="n">
-        <v>74156.06084450937</v>
+        <v>68851.97760926072</v>
       </c>
       <c r="P16" s="6" t="n">
-        <v>0</v>
+        <v>50789.6403167119</v>
       </c>
       <c r="Q16" s="6" t="n">
-        <v>49959631.20890453</v>
+        <v>0</v>
       </c>
       <c r="R16" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="S16" t="inlineStr">
-        <is>
-          <t>SDE (fixed)</t>
-        </is>
-      </c>
+      <c r="S16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>S15</t>
+          <t>S24</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Maple syrupUSDT (ERC-4626)</t>
+          <t>Spark.fi USDT Reserve Curve (sUSDS/USDT)</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1812,52 +1808,56 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>F</t>
         </is>
       </c>
       <c r="E17" s="6" t="n">
-        <v>76904851.98939763</v>
+        <v>50002415.26289953</v>
       </c>
       <c r="F17" s="6" t="n">
-        <v>0</v>
+        <v>48750265.64989898</v>
       </c>
       <c r="G17" s="6" t="n">
-        <v>-76904851.98939763</v>
+        <v>-1252149.613000547</v>
       </c>
       <c r="H17" s="6" t="n">
-        <v>119641.6179259726</v>
+        <v>39615.44347073233</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>0</v>
+        <v>34540.61737377704</v>
       </c>
       <c r="J17" s="6" t="n">
-        <v>119641.6179259726</v>
+        <v>34540.61737377704</v>
       </c>
       <c r="K17" s="6" t="n">
-        <v>0</v>
+        <v>39615.44347073233</v>
       </c>
       <c r="L17" s="6" t="n">
-        <v>29672997.14110577</v>
+        <v>49959631.20890453</v>
       </c>
       <c r="M17" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N17" s="6" t="n">
-        <v>68851.97760926072</v>
+        <v>0</v>
       </c>
       <c r="O17" s="6" t="n">
-        <v>68851.97760926072</v>
+        <v>39615.44347073233</v>
       </c>
       <c r="P17" s="6" t="n">
-        <v>50789.6403167119</v>
+        <v>34540.61737377704</v>
       </c>
       <c r="Q17" s="6" t="n">
-        <v>0</v>
+        <v>49959631.20890453</v>
       </c>
       <c r="R17" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="S17" t="inlineStr"/>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>SDE (fixed)</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -4503,7 +4503,7 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>74156.06084450937</v>
+        <v>39615.44347073233</v>
       </c>
     </row>
     <row r="6">
@@ -4513,7 +4513,7 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>10914895.67655484</v>
+        <v>10880355.05918106</v>
       </c>
     </row>
     <row r="8">
@@ -4836,10 +4836,10 @@
         </is>
       </c>
       <c r="I5" s="6" t="n">
-        <v>74156.06084450937</v>
+        <v>39615.44347073233</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>74156.06084450937</v>
+        <v>39615.44347073233</v>
       </c>
     </row>
   </sheetData>

--- a/settlements/spark/2026-05/spark_settlement_may_2026.xlsx
+++ b/settlements/spark/2026-05/spark_settlement_may_2026.xlsx
@@ -663,7 +663,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-06-10T01:54:54+00:00</t>
+          <t>2026-06-10T08:05:51+00:00</t>
         </is>
       </c>
     </row>

--- a/settlements/spark/2026-05/spark_settlement_may_2026.xlsx
+++ b/settlements/spark/2026-05/spark_settlement_may_2026.xlsx
@@ -488,7 +488,7 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>18627818.80597491</v>
+        <v>13356988.80597491</v>
       </c>
     </row>
     <row r="5">
@@ -504,7 +504,7 @@
     <row r="6">
       <c r="A6" t="inlineStr"/>
       <c r="B6" s="4" t="n">
-        <v>18749719.55568407</v>
+        <v>13478889.55568407</v>
       </c>
     </row>
     <row r="8">
@@ -612,7 +612,7 @@
         </is>
       </c>
       <c r="B21" s="3" t="n">
-        <v>18627818.80597491</v>
+        <v>13356988.80597491</v>
       </c>
     </row>
     <row r="22">
@@ -628,7 +628,7 @@
     <row r="23">
       <c r="A23" t="inlineStr"/>
       <c r="B23" s="4" t="n">
-        <v>6371334.198241767</v>
+        <v>1100504.198241766</v>
       </c>
     </row>
     <row r="25">
@@ -663,7 +663,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-06-10T08:05:51+00:00</t>
+          <t>2026-06-10T09:53:40+00:00</t>
         </is>
       </c>
     </row>
@@ -3714,13 +3714,13 @@
         <v>0</v>
       </c>
       <c r="H46" s="6" t="n">
-        <v>6162610.279999871</v>
+        <v>891780.2799998709</v>
       </c>
       <c r="I46" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J46" s="6" t="n">
-        <v>6162610.279999871</v>
+        <v>891780.2799998709</v>
       </c>
       <c r="K46" s="6" t="n">
         <v>0</v>
@@ -3738,7 +3738,7 @@
         <v>0</v>
       </c>
       <c r="P46" s="6" t="n">
-        <v>6162610.279999871</v>
+        <v>891780.2799998709</v>
       </c>
       <c r="Q46" s="6" t="n">
         <v>0</v>

--- a/settlements/spark/2026-05/spark_settlement_may_2026.xlsx
+++ b/settlements/spark/2026-05/spark_settlement_may_2026.xlsx
@@ -488,7 +488,7 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>13356988.80597491</v>
+        <v>13388258.15969513</v>
       </c>
     </row>
     <row r="5">
@@ -504,7 +504,7 @@
     <row r="6">
       <c r="A6" t="inlineStr"/>
       <c r="B6" s="4" t="n">
-        <v>13478889.55568407</v>
+        <v>13510158.90940429</v>
       </c>
     </row>
     <row r="8">
@@ -612,7 +612,7 @@
         </is>
       </c>
       <c r="B21" s="3" t="n">
-        <v>13356988.80597491</v>
+        <v>13388258.15969513</v>
       </c>
     </row>
     <row r="22">
@@ -628,7 +628,7 @@
     <row r="23">
       <c r="A23" t="inlineStr"/>
       <c r="B23" s="4" t="n">
-        <v>1100504.198241766</v>
+        <v>1131773.551961985</v>
       </c>
     </row>
     <row r="25">
@@ -663,7 +663,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-06-10T09:53:40+00:00</t>
+          <t>2026-06-10T11:03:01+00:00</t>
         </is>
       </c>
     </row>
@@ -842,13 +842,13 @@
         <v>-145686527.279134</v>
       </c>
       <c r="H2" s="6" t="n">
-        <v>3746125.871334389</v>
+        <v>3777395.225054608</v>
       </c>
       <c r="I2" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J2" s="6" t="n">
-        <v>3746125.871334389</v>
+        <v>3777395.225054608</v>
       </c>
       <c r="K2" s="6" t="n">
         <v>0</v>
@@ -866,7 +866,7 @@
         <v>4410254.829322996</v>
       </c>
       <c r="P2" s="6" t="n">
-        <v>-664128.9579886064</v>
+        <v>-632859.6042683872</v>
       </c>
       <c r="Q2" s="6" t="n">
         <v>0</v>

--- a/settlements/spark/2026-05/spark_settlement_may_2026.xlsx
+++ b/settlements/spark/2026-05/spark_settlement_may_2026.xlsx
@@ -488,7 +488,7 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>12636329.49077535</v>
+        <v>13388258.15969513</v>
       </c>
     </row>
     <row r="5">
@@ -504,7 +504,7 @@
     <row r="6">
       <c r="A6" t="inlineStr"/>
       <c r="B6" s="4" t="n">
-        <v>12758230.24048451</v>
+        <v>13510158.90940429</v>
       </c>
     </row>
     <row r="8">
@@ -536,13 +536,13 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>74156.06084450937</v>
+        <v>39615.44347073233</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr"/>
       <c r="B11" s="4" t="n">
-        <v>10914895.67655484</v>
+        <v>10880355.05918106</v>
       </c>
     </row>
     <row r="13">
@@ -612,7 +612,7 @@
         </is>
       </c>
       <c r="B21" s="3" t="n">
-        <v>12636329.49077535</v>
+        <v>13388258.15969513</v>
       </c>
     </row>
     <row r="22">
@@ -628,7 +628,7 @@
     <row r="23">
       <c r="A23" t="inlineStr"/>
       <c r="B23" s="4" t="n">
-        <v>1610679.456370043</v>
+        <v>1131773.551961985</v>
       </c>
     </row>
     <row r="25">
@@ -663,7 +663,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-06-09T23:18:46+00:00</t>
+          <t>2026-06-10T11:03:01+00:00</t>
         </is>
       </c>
     </row>
@@ -842,13 +842,13 @@
         <v>-145686527.279134</v>
       </c>
       <c r="H2" s="6" t="n">
-        <v>0</v>
+        <v>3777395.225054608</v>
       </c>
       <c r="I2" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J2" s="6" t="n">
-        <v>0</v>
+        <v>3777395.225054608</v>
       </c>
       <c r="K2" s="6" t="n">
         <v>0</v>
@@ -866,7 +866,7 @@
         <v>4410254.829322996</v>
       </c>
       <c r="P2" s="6" t="n">
-        <v>-4410254.829322996</v>
+        <v>-632859.6042683872</v>
       </c>
       <c r="Q2" s="6" t="n">
         <v>0</v>
@@ -1171,13 +1171,13 @@
         <v>436043.0489150246</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>0</v>
+        <v>436043.0489150246</v>
       </c>
       <c r="I7" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J7" s="6" t="n">
-        <v>0</v>
+        <v>436043.0489150246</v>
       </c>
       <c r="K7" s="6" t="n">
         <v>0</v>
@@ -1195,7 +1195,7 @@
         <v>296108.7831004824</v>
       </c>
       <c r="P7" s="6" t="n">
-        <v>-332573.59694228</v>
+        <v>103469.4519727446</v>
       </c>
       <c r="Q7" s="6" t="n">
         <v>0</v>
@@ -1431,13 +1431,13 @@
         <v>310435.429389201</v>
       </c>
       <c r="H11" s="6" t="n">
-        <v>0</v>
+        <v>310435.429389201</v>
       </c>
       <c r="I11" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J11" s="6" t="n">
-        <v>0</v>
+        <v>310435.429389201</v>
       </c>
       <c r="K11" s="6" t="n">
         <v>0</v>
@@ -1455,7 +1455,7 @@
         <v>210810.9679914328</v>
       </c>
       <c r="P11" s="6" t="n">
-        <v>-236771.6390094491</v>
+        <v>73663.79037975192</v>
       </c>
       <c r="Q11" s="6" t="n">
         <v>0</v>
@@ -1561,13 +1561,13 @@
         <v>230521.0318286367</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>0</v>
+        <v>230521.0318286367</v>
       </c>
       <c r="I13" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J13" s="6" t="n">
-        <v>0</v>
+        <v>230521.0318286367</v>
       </c>
       <c r="K13" s="6" t="n">
         <v>0</v>
@@ -1585,7 +1585,7 @@
         <v>156542.5762059274</v>
       </c>
       <c r="P13" s="6" t="n">
-        <v>-175820.2748945458</v>
+        <v>54700.75693409086</v>
       </c>
       <c r="Q13" s="6" t="n">
         <v>0</v>
@@ -1728,12 +1728,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>S24</t>
+          <t>S15</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Spark.fi USDT Reserve Curve (sUSDS/USDT)</t>
+          <t>Maple syrupUSDT (ERC-4626)</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1743,66 +1743,62 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E16" s="6" t="n">
-        <v>50002415.26289953</v>
+        <v>76904851.98939763</v>
       </c>
       <c r="F16" s="6" t="n">
-        <v>48750265.64989898</v>
+        <v>0</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>-1252149.613000547</v>
+        <v>-76904851.98939763</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>74156.06084450937</v>
+        <v>119641.6179259726</v>
       </c>
       <c r="I16" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J16" s="6" t="n">
-        <v>0</v>
+        <v>119641.6179259726</v>
       </c>
       <c r="K16" s="6" t="n">
-        <v>74156.06084450937</v>
+        <v>0</v>
       </c>
       <c r="L16" s="6" t="n">
-        <v>49959631.20890453</v>
+        <v>29672997.14110577</v>
       </c>
       <c r="M16" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N16" s="6" t="n">
-        <v>0</v>
+        <v>68851.97760926072</v>
       </c>
       <c r="O16" s="6" t="n">
-        <v>74156.06084450937</v>
+        <v>68851.97760926072</v>
       </c>
       <c r="P16" s="6" t="n">
-        <v>0</v>
+        <v>50789.6403167119</v>
       </c>
       <c r="Q16" s="6" t="n">
-        <v>49959631.20890453</v>
+        <v>0</v>
       </c>
       <c r="R16" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="S16" t="inlineStr">
-        <is>
-          <t>SDE (fixed)</t>
-        </is>
-      </c>
+      <c r="S16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>S15</t>
+          <t>S24</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Maple syrupUSDT (ERC-4626)</t>
+          <t>Spark.fi USDT Reserve Curve (sUSDS/USDT)</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1812,52 +1808,56 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>F</t>
         </is>
       </c>
       <c r="E17" s="6" t="n">
-        <v>76904851.98939763</v>
+        <v>50002415.26289953</v>
       </c>
       <c r="F17" s="6" t="n">
-        <v>0</v>
+        <v>48750265.64989898</v>
       </c>
       <c r="G17" s="6" t="n">
-        <v>-76904851.98939763</v>
+        <v>-1252149.613000547</v>
       </c>
       <c r="H17" s="6" t="n">
-        <v>119641.6179259726</v>
+        <v>39615.44347073233</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>0</v>
+        <v>34540.61737377704</v>
       </c>
       <c r="J17" s="6" t="n">
-        <v>119641.6179259726</v>
+        <v>34540.61737377704</v>
       </c>
       <c r="K17" s="6" t="n">
-        <v>0</v>
+        <v>39615.44347073233</v>
       </c>
       <c r="L17" s="6" t="n">
-        <v>29672997.14110577</v>
+        <v>49959631.20890453</v>
       </c>
       <c r="M17" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N17" s="6" t="n">
-        <v>68851.97760926072</v>
+        <v>0</v>
       </c>
       <c r="O17" s="6" t="n">
-        <v>68851.97760926072</v>
+        <v>39615.44347073233</v>
       </c>
       <c r="P17" s="6" t="n">
-        <v>50789.6403167119</v>
+        <v>34540.61737377704</v>
       </c>
       <c r="Q17" s="6" t="n">
-        <v>0</v>
+        <v>49959631.20890453</v>
       </c>
       <c r="R17" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="S17" t="inlineStr"/>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>SDE (fixed)</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2345,13 +2345,13 @@
         <v>2988.743030694792</v>
       </c>
       <c r="H25" s="6" t="n">
-        <v>0</v>
+        <v>2988.743030694792</v>
       </c>
       <c r="I25" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J25" s="6" t="n">
-        <v>0</v>
+        <v>2988.743030694792</v>
       </c>
       <c r="K25" s="6" t="n">
         <v>0</v>
@@ -2369,7 +2369,7 @@
         <v>2029.600205808002</v>
       </c>
       <c r="P25" s="6" t="n">
-        <v>-2279.53873482809</v>
+        <v>709.204295866702</v>
       </c>
       <c r="Q25" s="6" t="n">
         <v>0</v>
@@ -3714,13 +3714,13 @@
         <v>0</v>
       </c>
       <c r="H46" s="6" t="n">
-        <v>6162610.279999871</v>
+        <v>891780.2799998709</v>
       </c>
       <c r="I46" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J46" s="6" t="n">
-        <v>6162610.279999871</v>
+        <v>891780.2799998709</v>
       </c>
       <c r="K46" s="6" t="n">
         <v>0</v>
@@ -3738,7 +3738,7 @@
         <v>0</v>
       </c>
       <c r="P46" s="6" t="n">
-        <v>6162610.279999871</v>
+        <v>891780.2799998709</v>
       </c>
       <c r="Q46" s="6" t="n">
         <v>0</v>
@@ -4503,7 +4503,7 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>74156.06084450937</v>
+        <v>39615.44347073233</v>
       </c>
     </row>
     <row r="6">
@@ -4513,7 +4513,7 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>10914895.67655484</v>
+        <v>10880355.05918106</v>
       </c>
     </row>
     <row r="8">
@@ -4836,10 +4836,10 @@
         </is>
       </c>
       <c r="I5" s="6" t="n">
-        <v>74156.06084450937</v>
+        <v>39615.44347073233</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>74156.06084450937</v>
+        <v>39615.44347073233</v>
       </c>
     </row>
   </sheetData>

--- a/settlements/spark/2026-05/spark_settlement_may_2026.xlsx
+++ b/settlements/spark/2026-05/spark_settlement_may_2026.xlsx
@@ -20,10 +20,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00;&quot;−$&quot;#,##0.00;&quot;$&quot;0.00"/>
     <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0;&quot;−$&quot;#,##0;&quot;$&quot;0"/>
     <numFmt numFmtId="166" formatCode="0.000%"/>
+    <numFmt numFmtId="167" formatCode="0.0"/>
   </numFmts>
   <fonts count="4">
     <font>
@@ -75,7 +76,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -86,10 +87,12 @@
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -488,7 +491,7 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>13388258.15969513</v>
+        <v>13408944.7424591</v>
       </c>
     </row>
     <row r="5">
@@ -498,13 +501,13 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>121900.7497091584</v>
+        <v>118578.1793987423</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
       <c r="B6" s="4" t="n">
-        <v>13510158.90940429</v>
+        <v>13527522.92185785</v>
       </c>
     </row>
     <row r="8">
@@ -526,7 +529,7 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>10840739.61571033</v>
+        <v>10320044.68562127</v>
       </c>
     </row>
     <row r="10">
@@ -536,13 +539,13 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>39615.44347073233</v>
+        <v>40550.6842112442</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr"/>
       <c r="B11" s="4" t="n">
-        <v>10880355.05918106</v>
+        <v>10360595.36983252</v>
       </c>
     </row>
     <row r="13">
@@ -564,7 +567,7 @@
         </is>
       </c>
       <c r="B14" s="3" t="n">
-        <v>10840739.61571033</v>
+        <v>10320044.68562127</v>
       </c>
     </row>
     <row r="15">
@@ -574,13 +577,13 @@
         </is>
       </c>
       <c r="B15" s="3" t="n">
-        <v>-3142505.92528556</v>
+        <v>-3071820.300343978</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr"/>
       <c r="B16" s="4" t="n">
-        <v>13983245.54099589</v>
+        <v>13391864.98596525</v>
       </c>
     </row>
     <row r="18">
@@ -612,7 +615,7 @@
         </is>
       </c>
       <c r="B21" s="3" t="n">
-        <v>13388258.15969513</v>
+        <v>13408944.7424591</v>
       </c>
     </row>
     <row r="22">
@@ -622,13 +625,13 @@
         </is>
       </c>
       <c r="B22" s="3" t="n">
-        <v>-10840739.61571033</v>
+        <v>-10320044.68562127</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr"/>
       <c r="B23" s="4" t="n">
-        <v>1131773.551961985</v>
+        <v>1708588.925385048</v>
       </c>
     </row>
     <row r="25">
@@ -663,7 +666,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-06-10T11:03:01+00:00</t>
+          <t>2026-06-23T21:12:43+00:00</t>
         </is>
       </c>
     </row>
@@ -842,13 +845,13 @@
         <v>-145686527.279134</v>
       </c>
       <c r="H2" s="6" t="n">
-        <v>3777395.225054608</v>
+        <v>3834450.909129127</v>
       </c>
       <c r="I2" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J2" s="6" t="n">
-        <v>3777395.225054608</v>
+        <v>3834450.909129127</v>
       </c>
       <c r="K2" s="6" t="n">
         <v>0</v>
@@ -860,13 +863,13 @@
         <v>1</v>
       </c>
       <c r="N2" s="6" t="n">
-        <v>4410254.829322996</v>
+        <v>4201977.102126558</v>
       </c>
       <c r="O2" s="6" t="n">
-        <v>4410254.829322996</v>
+        <v>4201977.102126558</v>
       </c>
       <c r="P2" s="6" t="n">
-        <v>-632859.6042683872</v>
+        <v>-367526.192997431</v>
       </c>
       <c r="Q2" s="6" t="n">
         <v>0</v>
@@ -925,13 +928,13 @@
         <v>1</v>
       </c>
       <c r="N3" s="6" t="n">
-        <v>1558684.923959588</v>
+        <v>1485074.811632477</v>
       </c>
       <c r="O3" s="6" t="n">
-        <v>1558684.923959588</v>
+        <v>1485074.811632477</v>
       </c>
       <c r="P3" s="6" t="n">
-        <v>309427.2442764115</v>
+        <v>383037.3566035236</v>
       </c>
       <c r="Q3" s="6" t="n">
         <v>0</v>
@@ -990,13 +993,13 @@
         <v>1</v>
       </c>
       <c r="N4" s="6" t="n">
-        <v>1428099.786876452</v>
+        <v>1360656.659589858</v>
       </c>
       <c r="O4" s="6" t="n">
-        <v>1428099.786876452</v>
+        <v>1360656.659589858</v>
       </c>
       <c r="P4" s="6" t="n">
-        <v>1663480.213123548</v>
+        <v>1730923.340410141</v>
       </c>
       <c r="Q4" s="6" t="n">
         <v>0</v>
@@ -1055,13 +1058,13 @@
         <v>1</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>1252424.714284955</v>
+        <v>1193277.979442887</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>1252424.714284955</v>
+        <v>1193277.979442887</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>-1446869.158728908</v>
+        <v>-1387722.42388684</v>
       </c>
       <c r="Q5" s="6" t="n">
         <v>0</v>
@@ -1120,13 +1123,13 @@
         <v>1</v>
       </c>
       <c r="N6" s="6" t="n">
-        <v>416618.9330474357</v>
+        <v>396943.7786991677</v>
       </c>
       <c r="O6" s="6" t="n">
-        <v>416618.9330474357</v>
+        <v>396943.7786991677</v>
       </c>
       <c r="P6" s="6" t="n">
-        <v>142834.0061937836</v>
+        <v>162509.1605420516</v>
       </c>
       <c r="Q6" s="6" t="n">
         <v>86642406.62655522</v>
@@ -1189,13 +1192,13 @@
         <v>1</v>
       </c>
       <c r="N7" s="6" t="n">
-        <v>332573.59694228</v>
+        <v>316867.5492018788</v>
       </c>
       <c r="O7" s="6" t="n">
-        <v>296108.7831004824</v>
+        <v>280402.7353600811</v>
       </c>
       <c r="P7" s="6" t="n">
-        <v>103469.4519727446</v>
+        <v>119175.4997131458</v>
       </c>
       <c r="Q7" s="6" t="n">
         <v>0</v>
@@ -1254,13 +1257,13 @@
         <v>1</v>
       </c>
       <c r="N8" s="6" t="n">
-        <v>243821.3957592647</v>
+        <v>232306.7400044638</v>
       </c>
       <c r="O8" s="6" t="n">
-        <v>243821.3957592647</v>
+        <v>232306.7400044638</v>
       </c>
       <c r="P8" s="6" t="n">
-        <v>179709.2128239369</v>
+        <v>191223.8685787379</v>
       </c>
       <c r="Q8" s="6" t="n">
         <v>0</v>
@@ -1319,13 +1322,13 @@
         <v>1</v>
       </c>
       <c r="N9" s="6" t="n">
-        <v>232036.1413934696</v>
+        <v>221078.0534762956</v>
       </c>
       <c r="O9" s="6" t="n">
-        <v>232036.1413934696</v>
+        <v>221078.0534762956</v>
       </c>
       <c r="P9" s="6" t="n">
-        <v>-203032.1706934696</v>
+        <v>-192074.0827762955</v>
       </c>
       <c r="Q9" s="6" t="n">
         <v>0</v>
@@ -1384,13 +1387,13 @@
         <v>1</v>
       </c>
       <c r="N10" s="6" t="n">
-        <v>232032.2997438859</v>
+        <v>221074.3932516124</v>
       </c>
       <c r="O10" s="6" t="n">
-        <v>232032.2997438859</v>
+        <v>221074.3932516124</v>
       </c>
       <c r="P10" s="6" t="n">
-        <v>-225646.4158722456</v>
+        <v>-214688.5093799721</v>
       </c>
       <c r="Q10" s="6" t="n">
         <v>0</v>
@@ -1449,13 +1452,13 @@
         <v>1</v>
       </c>
       <c r="N11" s="6" t="n">
-        <v>236771.6390094491</v>
+        <v>225589.9135205768</v>
       </c>
       <c r="O11" s="6" t="n">
-        <v>210810.9679914328</v>
+        <v>199629.2425025605</v>
       </c>
       <c r="P11" s="6" t="n">
-        <v>73663.79037975192</v>
+        <v>84845.51586862426</v>
       </c>
       <c r="Q11" s="6" t="n">
         <v>0</v>
@@ -1514,13 +1517,13 @@
         <v>1</v>
       </c>
       <c r="N12" s="6" t="n">
-        <v>207950.3643444547</v>
+        <v>198129.7460510709</v>
       </c>
       <c r="O12" s="6" t="n">
-        <v>207950.3643444547</v>
+        <v>198129.7460510709</v>
       </c>
       <c r="P12" s="6" t="n">
-        <v>9319.032102103598</v>
+        <v>19139.65039548748</v>
       </c>
       <c r="Q12" s="6" t="n">
         <v>0</v>
@@ -1579,13 +1582,13 @@
         <v>1</v>
       </c>
       <c r="N13" s="6" t="n">
-        <v>175820.2748945458</v>
+        <v>167517.0251579064</v>
       </c>
       <c r="O13" s="6" t="n">
-        <v>156542.5762059274</v>
+        <v>148239.326469288</v>
       </c>
       <c r="P13" s="6" t="n">
-        <v>54700.75693409086</v>
+        <v>63004.00667073025</v>
       </c>
       <c r="Q13" s="6" t="n">
         <v>0</v>
@@ -1644,13 +1647,13 @@
         <v>1</v>
       </c>
       <c r="N14" s="6" t="n">
-        <v>133957.490815224</v>
+        <v>127631.243737067</v>
       </c>
       <c r="O14" s="6" t="n">
-        <v>133957.490815224</v>
+        <v>127631.243737067</v>
       </c>
       <c r="P14" s="6" t="n">
-        <v>160134.02606122</v>
+        <v>166460.273139377</v>
       </c>
       <c r="Q14" s="6" t="n">
         <v>103099818.9104406</v>
@@ -1774,13 +1777,13 @@
         <v>1</v>
       </c>
       <c r="N16" s="6" t="n">
-        <v>68851.97760926072</v>
+        <v>65600.38921711374</v>
       </c>
       <c r="O16" s="6" t="n">
-        <v>68851.97760926072</v>
+        <v>65600.38921711374</v>
       </c>
       <c r="P16" s="6" t="n">
-        <v>50789.6403167119</v>
+        <v>54041.22870885887</v>
       </c>
       <c r="Q16" s="6" t="n">
         <v>0</v>
@@ -1821,16 +1824,16 @@
         <v>-1252149.613000547</v>
       </c>
       <c r="H17" s="6" t="n">
-        <v>39615.44347073233</v>
+        <v>40550.6842112442</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>34540.61737377704</v>
+        <v>33605.37663326517</v>
       </c>
       <c r="J17" s="6" t="n">
-        <v>34540.61737377704</v>
+        <v>33605.37663326517</v>
       </c>
       <c r="K17" s="6" t="n">
-        <v>39615.44347073233</v>
+        <v>40550.6842112442</v>
       </c>
       <c r="L17" s="6" t="n">
         <v>49959631.20890453</v>
@@ -1842,10 +1845,10 @@
         <v>0</v>
       </c>
       <c r="O17" s="6" t="n">
-        <v>39615.44347073233</v>
+        <v>40550.6842112442</v>
       </c>
       <c r="P17" s="6" t="n">
-        <v>34540.61737377704</v>
+        <v>33605.37663326517</v>
       </c>
       <c r="Q17" s="6" t="n">
         <v>49959631.20890453</v>
@@ -1908,13 +1911,13 @@
         <v>1</v>
       </c>
       <c r="N18" s="6" t="n">
-        <v>22080.74563910623</v>
+        <v>21037.96518888412</v>
       </c>
       <c r="O18" s="6" t="n">
-        <v>22080.74563910623</v>
+        <v>21037.96518888412</v>
       </c>
       <c r="P18" s="6" t="n">
-        <v>-379.2741364086218</v>
+        <v>663.5063138134914</v>
       </c>
       <c r="Q18" s="6" t="n">
         <v>0</v>
@@ -1973,13 +1976,13 @@
         <v>1</v>
       </c>
       <c r="N19" s="6" t="n">
-        <v>21635.14247209228</v>
+        <v>20613.40597929416</v>
       </c>
       <c r="O19" s="6" t="n">
-        <v>21635.14247209228</v>
+        <v>20613.40597929416</v>
       </c>
       <c r="P19" s="6" t="n">
-        <v>10867.76088090771</v>
+        <v>11889.49737370584</v>
       </c>
       <c r="Q19" s="6" t="n">
         <v>0</v>
@@ -2038,13 +2041,13 @@
         <v>1</v>
       </c>
       <c r="N20" s="6" t="n">
-        <v>11599.47377580961</v>
+        <v>11051.67957157512</v>
       </c>
       <c r="O20" s="6" t="n">
-        <v>11599.47377580961</v>
+        <v>11051.67957157512</v>
       </c>
       <c r="P20" s="6" t="n">
-        <v>-11599.47377580738</v>
+        <v>-11051.67957157289</v>
       </c>
       <c r="Q20" s="6" t="n">
         <v>0</v>
@@ -2103,13 +2106,13 @@
         <v>1</v>
       </c>
       <c r="N21" s="6" t="n">
-        <v>11598.70786928614</v>
+        <v>11050.94983558513</v>
       </c>
       <c r="O21" s="6" t="n">
-        <v>11598.70786928614</v>
+        <v>11050.94983558513</v>
       </c>
       <c r="P21" s="6" t="n">
-        <v>-11598.70786928596</v>
+        <v>-11050.94983558495</v>
       </c>
       <c r="Q21" s="6" t="n">
         <v>0</v>
@@ -2168,13 +2171,13 @@
         <v>1</v>
       </c>
       <c r="N22" s="6" t="n">
-        <v>11596.55720504697</v>
+        <v>11048.90073814358</v>
       </c>
       <c r="O22" s="6" t="n">
-        <v>11596.55720504697</v>
+        <v>11048.90073814358</v>
       </c>
       <c r="P22" s="6" t="n">
-        <v>-11596.55720504697</v>
+        <v>-11048.90073814358</v>
       </c>
       <c r="Q22" s="6" t="n">
         <v>0</v>
@@ -2233,13 +2236,13 @@
         <v>1</v>
       </c>
       <c r="N23" s="6" t="n">
-        <v>11496.29925632405</v>
+        <v>10953.37754931583</v>
       </c>
       <c r="O23" s="6" t="n">
-        <v>11496.29925632405</v>
+        <v>10953.37754931583</v>
       </c>
       <c r="P23" s="6" t="n">
-        <v>-11496.29925632357</v>
+        <v>-10953.37754931536</v>
       </c>
       <c r="Q23" s="6" t="n">
         <v>0</v>
@@ -2298,13 +2301,13 @@
         <v>1</v>
       </c>
       <c r="N24" s="6" t="n">
-        <v>3462.049264890436</v>
+        <v>3298.551285694489</v>
       </c>
       <c r="O24" s="6" t="n">
-        <v>3462.049264890436</v>
+        <v>3298.551285694489</v>
       </c>
       <c r="P24" s="6" t="n">
-        <v>1342.838915254552</v>
+        <v>1506.336894450499</v>
       </c>
       <c r="Q24" s="6" t="n">
         <v>0</v>
@@ -2363,13 +2366,13 @@
         <v>1</v>
       </c>
       <c r="N25" s="6" t="n">
-        <v>2279.53873482809</v>
+        <v>2171.885738545533</v>
       </c>
       <c r="O25" s="6" t="n">
-        <v>2029.600205808002</v>
+        <v>1921.947209525445</v>
       </c>
       <c r="P25" s="6" t="n">
-        <v>709.204295866702</v>
+        <v>816.8572921492586</v>
       </c>
       <c r="Q25" s="6" t="n">
         <v>0</v>
@@ -2428,13 +2431,13 @@
         <v>1</v>
       </c>
       <c r="N26" s="6" t="n">
-        <v>1.072380599454827</v>
+        <v>1.021736588487712</v>
       </c>
       <c r="O26" s="6" t="n">
-        <v>1.072380599454827</v>
+        <v>1.021736588487712</v>
       </c>
       <c r="P26" s="6" t="n">
-        <v>75.25808491975091</v>
+        <v>75.30872893071803</v>
       </c>
       <c r="Q26" s="6" t="n">
         <v>0</v>
@@ -2493,13 +2496,13 @@
         <v>1</v>
       </c>
       <c r="N27" s="6" t="n">
-        <v>0.8539894430318479</v>
+        <v>0.8136591249146683</v>
       </c>
       <c r="O27" s="6" t="n">
-        <v>0.8539894430318479</v>
+        <v>0.8136591249146683</v>
       </c>
       <c r="P27" s="6" t="n">
-        <v>0.3073558323059302</v>
+        <v>0.3476861504231099</v>
       </c>
       <c r="Q27" s="6" t="n">
         <v>0</v>
@@ -2558,13 +2561,13 @@
         <v>1</v>
       </c>
       <c r="N28" s="6" t="n">
-        <v>0.6587432650801534</v>
+        <v>0.6276336001363896</v>
       </c>
       <c r="O28" s="6" t="n">
-        <v>0.6587432650801534</v>
+        <v>0.6276336001363896</v>
       </c>
       <c r="P28" s="6" t="n">
-        <v>-0.6587432650801534</v>
+        <v>-0.6276336001363896</v>
       </c>
       <c r="Q28" s="6" t="n">
         <v>0</v>
@@ -2623,13 +2626,13 @@
         <v>1</v>
       </c>
       <c r="N29" s="6" t="n">
-        <v>0.267561352084571</v>
+        <v>0.2549255583596232</v>
       </c>
       <c r="O29" s="6" t="n">
-        <v>0.267561352084571</v>
+        <v>0.2549255583596232</v>
       </c>
       <c r="P29" s="6" t="n">
-        <v>-0.2675613524150298</v>
+        <v>-0.254925558690082</v>
       </c>
       <c r="Q29" s="6" t="n">
         <v>0</v>
@@ -2688,13 +2691,13 @@
         <v>1</v>
       </c>
       <c r="N30" s="6" t="n">
-        <v>0.2308786281355063</v>
+        <v>0.2199752046855565</v>
       </c>
       <c r="O30" s="6" t="n">
-        <v>0.2308786281355063</v>
+        <v>0.2199752046855565</v>
       </c>
       <c r="P30" s="6" t="n">
-        <v>0.08088492029861985</v>
+        <v>0.09178834374856962</v>
       </c>
       <c r="Q30" s="6" t="n">
         <v>0</v>
@@ -2753,13 +2756,13 @@
         <v>1</v>
       </c>
       <c r="N31" s="6" t="n">
-        <v>0.050831171005292</v>
+        <v>0.04843062927302642</v>
       </c>
       <c r="O31" s="6" t="n">
-        <v>0.050831171005292</v>
+        <v>0.04843062927302642</v>
       </c>
       <c r="P31" s="6" t="n">
-        <v>-0.05082511729812201</v>
+        <v>-0.04842457556585644</v>
       </c>
       <c r="Q31" s="6" t="n">
         <v>0</v>
@@ -2818,13 +2821,13 @@
         <v>1</v>
       </c>
       <c r="N32" s="6" t="n">
-        <v>0.01368516545690748</v>
+        <v>0.01303887283483027</v>
       </c>
       <c r="O32" s="6" t="n">
-        <v>0.01368516545690748</v>
+        <v>0.01303887283483027</v>
       </c>
       <c r="P32" s="6" t="n">
-        <v>0.001704834543092515</v>
+        <v>0.002351127165169734</v>
       </c>
       <c r="Q32" s="6" t="n">
         <v>0</v>
@@ -2883,13 +2886,13 @@
         <v>1</v>
       </c>
       <c r="N33" s="6" t="n">
-        <v>0.003586366276201048</v>
+        <v>0.003416997329097425</v>
       </c>
       <c r="O33" s="6" t="n">
-        <v>0.003586366276201048</v>
+        <v>0.003416997329097425</v>
       </c>
       <c r="P33" s="6" t="n">
-        <v>8.466802633723798</v>
+        <v>8.466972002670902</v>
       </c>
       <c r="Q33" s="6" t="n">
         <v>0</v>
@@ -2948,13 +2951,13 @@
         <v>1</v>
       </c>
       <c r="N34" s="6" t="n">
-        <v>0.0003583352131101747</v>
+        <v>0.0003414125529353442</v>
       </c>
       <c r="O34" s="6" t="n">
-        <v>0.0003583352131101747</v>
+        <v>0.0003414125529353442</v>
       </c>
       <c r="P34" s="6" t="n">
-        <v>0.0003756647868898253</v>
+        <v>0.0003925874470646558</v>
       </c>
       <c r="Q34" s="6" t="n">
         <v>0</v>
@@ -3013,13 +3016,13 @@
         <v>1</v>
       </c>
       <c r="N35" s="6" t="n">
-        <v>0.0001340772488628917</v>
+        <v>0.000127745346117444</v>
       </c>
       <c r="O35" s="6" t="n">
-        <v>0.0001340772488628917</v>
+        <v>0.000127745346117444</v>
       </c>
       <c r="P35" s="6" t="n">
-        <v>5.192275113710832e-05</v>
+        <v>5.825465388255599e-05</v>
       </c>
       <c r="Q35" s="6" t="n">
         <v>0</v>
@@ -3078,13 +3081,13 @@
         <v>1</v>
       </c>
       <c r="N36" s="6" t="n">
-        <v>1.472499214793124e-05</v>
+        <v>1.402959289862589e-05</v>
       </c>
       <c r="O36" s="6" t="n">
-        <v>1.472499214793124e-05</v>
+        <v>1.402959289862589e-05</v>
       </c>
       <c r="P36" s="6" t="n">
-        <v>2.275007852068764e-06</v>
+        <v>2.970407101374112e-06</v>
       </c>
       <c r="Q36" s="6" t="n">
         <v>0</v>
@@ -3143,13 +3146,13 @@
         <v>1</v>
       </c>
       <c r="N37" s="6" t="n">
-        <v>1.332879347576094e-05</v>
+        <v>1.269933079869646e-05</v>
       </c>
       <c r="O37" s="6" t="n">
-        <v>1.332879347576094e-05</v>
+        <v>1.269933079869646e-05</v>
       </c>
       <c r="P37" s="6" t="n">
-        <v>-1.118496897039094e-05</v>
+        <v>-1.055550629332646e-05</v>
       </c>
       <c r="Q37" s="6" t="n">
         <v>0</v>
@@ -3208,13 +3211,13 @@
         <v>1</v>
       </c>
       <c r="N38" s="6" t="n">
-        <v>3.944608674989458e-06</v>
+        <v>3.758321450939806e-06</v>
       </c>
       <c r="O38" s="6" t="n">
-        <v>3.944608674989458e-06</v>
+        <v>3.758321450939806e-06</v>
       </c>
       <c r="P38" s="6" t="n">
-        <v>1.055391325010542e-06</v>
+        <v>1.241678549060194e-06</v>
       </c>
       <c r="Q38" s="6" t="n">
         <v>0</v>
@@ -3273,13 +3276,13 @@
         <v>1</v>
       </c>
       <c r="N39" s="6" t="n">
-        <v>2.877579662079685e-06</v>
+        <v>2.741683716144822e-06</v>
       </c>
       <c r="O39" s="6" t="n">
-        <v>2.877579662079685e-06</v>
+        <v>2.741683716144822e-06</v>
       </c>
       <c r="P39" s="6" t="n">
-        <v>-2.877579662079685e-06</v>
+        <v>-2.741683716144822e-06</v>
       </c>
       <c r="Q39" s="6" t="n">
         <v>0</v>
@@ -3338,13 +3341,13 @@
         <v>1</v>
       </c>
       <c r="N40" s="6" t="n">
-        <v>1.208828958664657e-06</v>
+        <v>1.151741067414945e-06</v>
       </c>
       <c r="O40" s="6" t="n">
-        <v>1.208828958664657e-06</v>
+        <v>1.151741067414945e-06</v>
       </c>
       <c r="P40" s="6" t="n">
-        <v>-5.021221518556572e-07</v>
+        <v>-4.450342606059448e-07</v>
       </c>
       <c r="Q40" s="6" t="n">
         <v>0</v>
@@ -3403,13 +3406,13 @@
         <v>1</v>
       </c>
       <c r="N41" s="6" t="n">
-        <v>1.737861762534574e-07</v>
+        <v>1.6557898841307e-07</v>
       </c>
       <c r="O41" s="6" t="n">
-        <v>1.737861762534574e-07</v>
+        <v>1.6557898841307e-07</v>
       </c>
       <c r="P41" s="6" t="n">
-        <v>-1.737861762534574e-07</v>
+        <v>-1.6557898841307e-07</v>
       </c>
       <c r="Q41" s="6" t="n">
         <v>0</v>
@@ -4460,7 +4463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B26"/>
+  <dimension ref="A1:D46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="80" customWidth="1" min="1" max="1"/>
@@ -4475,195 +4478,388 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>Component</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>USD</t>
+      <c r="A3" s="8" t="inlineStr">
+        <is>
+          <t>Rates &amp; subsidy — effective rate charged this period</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>CoF on utilized debt (= Σ_d max(utilized_d,0) × (1+BR_d)^(1/365)−1)</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="n">
-        <v>10840739.61571033</v>
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>+ Sky-Direct revenue (full venue yield on fixed/capped SDE)</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="n">
-        <v>39615.44347073233</v>
+          <t>Time-weighted utilized</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="n">
+        <v>3356195943.673027</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>equals sky_revenue (total Sky take this month)</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="n">
-        <v>10880355.05918106</v>
+          <t xml:space="preserve">  — first $1B (subsidised tranche)</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="n">
+        <v>1000000000</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  — excess (full base-rate tranche)</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="n">
+        <v>2356195943.673027</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="inlineStr">
-        <is>
-          <t>Utilized base = cum_debt − idle USDS − PSM USDS − Σ SDE asset value − Curve idle − lending idle</t>
-        </is>
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Base rate (BR = SSR + 30bps), period avg</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="n">
+        <v>0.03951513515348828</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Reference rate (effr), period avg</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="n">
+        <v>0.03628709677419355</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="8" t="inlineStr">
-        <is>
-          <t>Sky Revenue (max) — BR × full ilk debt (no deductions)</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="n">
-        <v>13983245.54099589</v>
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Subsidised rate (BR*), period avg</t>
+        </is>
+      </c>
+      <c r="B10" s="7" t="n">
+        <v>0.03682465368903005</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    ↳ actual CoF on Net_Subs (BR × utilized)</t>
-        </is>
-      </c>
-      <c r="B11" s="3" t="n">
-        <v>10840739.61571033</v>
+      <c r="A11" s="8" t="inlineStr">
+        <is>
+          <t>Effective blended rate charged</t>
+        </is>
+      </c>
+      <c r="B11" s="10" t="n">
+        <v>0.03871429258669792</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    ↳ reduction from idle/SDE deductions</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="n">
-        <v>-3142505.92528556</v>
-      </c>
-    </row>
-    <row r="13" ht="60" customHeight="1">
-      <c r="A13" s="10" t="inlineStr">
-        <is>
-          <t>Note: sky_revenue can EXCEED sky_revenue_gross for primes with active SDE positions — sky_revenue also adds sde_revenue on top of BR-on-utilized. The subsidised BR (ref_rate ramp) is already applied here; this is NOT the raw Maker base rate.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="60" customHeight="1">
-      <c r="A15" s="10" t="inlineStr">
-        <is>
-          <t>sUSDS spread (Curve LP + PSM3) — 30 bps × value × n_days deducted from sky_revenue. Sky charges full BR on the underlying utilized; this row is the offsetting refund to the prime so SSR + BR + 30 bps nets to zero economically.</t>
+      <c r="A12" s="8" t="inlineStr">
+        <is>
+          <t>Diff vs base rate (bps)</t>
+        </is>
+      </c>
+      <c r="B12" s="11" t="n">
+        <v>-8.008425667903683</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="8" t="inlineStr">
+        <is>
+          <t>Subsidy benefit to prime (USD)</t>
+        </is>
+      </c>
+      <c r="B13" s="12" t="n">
+        <v>219906.3997824828</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>CoF at full base rate (no subsidy)</t>
         </is>
       </c>
       <c r="B15" s="3" t="n">
-        <v>184910.418694979</v>
+        <v>11047394.95315714</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  − actual CoF (subsidy on first tranche)</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="n">
+        <v>10827488.55337466</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>Subsidy</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>Value</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>enabled</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
+      <c r="A17" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  = subsidy benefit</t>
+        </is>
+      </c>
+      <c r="B17" s="12" t="n">
+        <v>219906.3997824828</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>cap_usd</t>
-        </is>
-      </c>
-      <c r="B19" s="6" t="n">
-        <v>1000000000</v>
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>Tranche</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>Avg balance</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>Rate (APY)</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>CoF (USD)</t>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>program_start</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>2026-01-01</t>
-        </is>
+          <t>Subsidised (first $1B)</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="n">
+        <v>1000000000</v>
+      </c>
+      <c r="C20" s="7" t="n">
+        <v>0.03682465368903005</v>
+      </c>
+      <c r="D20" s="3" t="n">
+        <v>3071515.028318575</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
+          <t>Excess (&gt; cap)</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="n">
+        <v>2356195943.673027</v>
+      </c>
+      <c r="C21" s="7" t="n">
+        <v>0.03951513515348828</v>
+      </c>
+      <c r="D21" s="3" t="n">
+        <v>7755973.525058723</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>Component</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>CoF on utilized debt (= Σ_d max(utilized_d,0) × (1+BR_d)^(1/365)−1)</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="n">
+        <v>10320044.68562127</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>+ Sky-Direct revenue (full venue yield on fixed/capped SDE)</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="n">
+        <v>40550.6842112442</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>equals sky_revenue (total Sky take this month)</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="n">
+        <v>10360595.36983252</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>Utilized base = cum_debt − idle USDS − PSM USDS − Σ SDE asset value − Curve idle − lending idle</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="8" t="inlineStr">
+        <is>
+          <t>Sky Revenue (max) — BR × full ilk debt (no deductions)</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="n">
+        <v>13391864.98596525</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ↳ actual CoF on Net_Subs (BR × utilized)</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="n">
+        <v>10320044.68562127</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ↳ reduction from idle/SDE deductions</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="n">
+        <v>-3071820.300343978</v>
+      </c>
+    </row>
+    <row r="33" ht="60" customHeight="1">
+      <c r="A33" s="13" t="inlineStr">
+        <is>
+          <t>Note: sky_revenue can EXCEED sky_revenue_gross for primes with active SDE positions — sky_revenue also adds sde_revenue on top of BR-on-utilized. The subsidised BR (ref_rate ramp) is already applied here; this is NOT the raw Maker base rate.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="60" customHeight="1">
+      <c r="A35" s="13" t="inlineStr">
+        <is>
+          <t>sUSDS spread (Curve LP + PSM3) — 30 bps × value × n_days deducted from sky_revenue. Sky charges full BR on the underlying utilized; this row is the offsetting refund to the prime so SSR + BR + 30 bps nets to zero economically.</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="n">
+        <v>184910.418694979</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>Subsidy</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>enabled</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>cap_usd</t>
+        </is>
+      </c>
+      <c r="B39" s="6" t="n">
+        <v>1000000000</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>program_start</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
           <t>ramp_months</t>
         </is>
       </c>
-      <c r="B21" t="n">
+      <c r="B41" t="n">
         <v>24</v>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
+    <row r="42">
+      <c r="A42" t="inlineStr">
         <is>
           <t>ref_rate_kind</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B42" t="inlineStr">
         <is>
           <t>effr</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
+    <row r="43">
+      <c r="A43" t="inlineStr">
         <is>
           <t>T this period</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B43" t="inlineStr">
         <is>
           <t>4 (SoM) → 4 (EoM)</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="5" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="5" t="inlineStr">
         <is>
           <t>Formula</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B44" t="inlineStr">
         <is>
           <t>subsidised_apy = ref_rate + (base_apy − ref_rate) × min(T, 24) / 24, applied to first cap_usd of utilized; excess at full base_apy</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="5" t="inlineStr">
+    <row r="46">
+      <c r="A46" s="5" t="inlineStr">
         <is>
           <t>Base rate composition: base_apy = (1 + SSR)(1 + 30bps) − 1 (multiplicative)</t>
         </is>
@@ -4836,10 +5032,10 @@
         </is>
       </c>
       <c r="I5" s="6" t="n">
-        <v>39615.44347073233</v>
+        <v>40550.6842112442</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>39615.44347073233</v>
+        <v>40550.6842112442</v>
       </c>
     </row>
   </sheetData>
@@ -4881,7 +5077,7 @@
       </c>
     </row>
     <row r="3" ht="45" customHeight="1">
-      <c r="A3" s="10" t="inlineStr">
+      <c r="A3" s="13" t="inlineStr">
         <is>
           <t>cum_debt = Σ on-chain Vat dart from frob (0x76088703) + grab (0x7bab3f40), then scaled by Vat.ilks[ilk].rate_d / 1e27 read at each day's EoD block — actual outstanding USDS per day, not raw normalised Art. utilized = cum_debt − Σ deductions. base_apy = (1+SSR)(1+0.003)−1 (multiplicative). sub_apy applies on the first cap_usd of utilized when the subsidy is active; excess pays base_apy.</t>
         </is>
@@ -4991,25 +5187,25 @@
         <v>3236279210.15232</v>
       </c>
       <c r="I6" s="7" t="n">
-        <v>0.0375</v>
+        <v>0.03650000241537366</v>
       </c>
       <c r="J6" s="7" t="n">
-        <v>0.0406125</v>
+        <v>0.03960950242261978</v>
       </c>
       <c r="K6" t="n">
         <v>4</v>
       </c>
       <c r="L6" s="7" t="n">
-        <v>0.0433</v>
+        <v>0.0364</v>
       </c>
       <c r="M6" s="7" t="n">
-        <v>0.0406125</v>
+        <v>0.03693491707043663</v>
       </c>
       <c r="N6" s="3" t="n">
-        <v>352990.7544030308</v>
+        <v>337381.4365374905</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>431761.0397033197</v>
+        <v>414243.5423272011</v>
       </c>
     </row>
     <row r="7">
@@ -5040,25 +5236,25 @@
         <v>3583341168.645234</v>
       </c>
       <c r="I7" s="7" t="n">
-        <v>0.0375</v>
+        <v>0.03650000241537366</v>
       </c>
       <c r="J7" s="7" t="n">
-        <v>0.0406125</v>
+        <v>0.03960950242261978</v>
       </c>
       <c r="K7" t="n">
         <v>4</v>
       </c>
       <c r="L7" s="7" t="n">
-        <v>0.0433</v>
+        <v>0.0364</v>
       </c>
       <c r="M7" s="7" t="n">
-        <v>0.0406125</v>
+        <v>0.03693491707043663</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>390845.8511353183</v>
+        <v>374319.5082814827</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>469013.1074139154</v>
+        <v>450593.1931929035</v>
       </c>
     </row>
     <row r="8">
@@ -5089,25 +5285,25 @@
         <v>3577229601.132741</v>
       </c>
       <c r="I8" s="7" t="n">
-        <v>0.0375</v>
+        <v>0.03650000241537366</v>
       </c>
       <c r="J8" s="7" t="n">
-        <v>0.0406125</v>
+        <v>0.03960950242261978</v>
       </c>
       <c r="K8" t="n">
         <v>4</v>
       </c>
       <c r="L8" s="7" t="n">
-        <v>0.0433</v>
+        <v>0.0364</v>
       </c>
       <c r="M8" s="7" t="n">
-        <v>0.0406125</v>
+        <v>0.03693491707043663</v>
       </c>
       <c r="N8" s="3" t="n">
-        <v>390179.243995844</v>
+        <v>373669.0494405744</v>
       </c>
       <c r="O8" s="3" t="n">
-        <v>468886.8453627324</v>
+        <v>450469.9897907797</v>
       </c>
     </row>
     <row r="9">
@@ -5138,25 +5334,25 @@
         <v>3482111304.355217</v>
       </c>
       <c r="I9" s="7" t="n">
-        <v>0.0375</v>
+        <v>0.03650000241537366</v>
       </c>
       <c r="J9" s="7" t="n">
-        <v>0.0406125</v>
+        <v>0.03960950242261978</v>
       </c>
       <c r="K9" t="n">
         <v>4</v>
       </c>
       <c r="L9" s="7" t="n">
-        <v>0.0433</v>
+        <v>0.0364</v>
       </c>
       <c r="M9" s="7" t="n">
-        <v>0.0406125</v>
+        <v>0.03693491707043663</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>379804.4038919058</v>
+        <v>363545.5358011322</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>457700.9827281167</v>
+        <v>439555.1003258834</v>
       </c>
     </row>
     <row r="10">
@@ -5187,25 +5383,25 @@
         <v>3438062922.860942</v>
       </c>
       <c r="I10" s="7" t="n">
-        <v>0.0375</v>
+        <v>0.03650000241537366</v>
       </c>
       <c r="J10" s="7" t="n">
-        <v>0.0406125</v>
+        <v>0.03960950242261978</v>
       </c>
       <c r="K10" t="n">
         <v>4</v>
       </c>
       <c r="L10" s="7" t="n">
-        <v>0.0433</v>
+        <v>0.0364</v>
       </c>
       <c r="M10" s="7" t="n">
-        <v>0.0406125</v>
+        <v>0.03693491707043663</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>374999.9137956497</v>
+        <v>358857.4326079512</v>
       </c>
       <c r="O10" s="3" t="n">
-        <v>452359.580684261</v>
+        <v>434343.0916681122</v>
       </c>
     </row>
     <row r="11">
@@ -5236,25 +5432,25 @@
         <v>3232022985.161858</v>
       </c>
       <c r="I11" s="7" t="n">
-        <v>0.0375</v>
+        <v>0.03650000241537366</v>
       </c>
       <c r="J11" s="7" t="n">
-        <v>0.0406125</v>
+        <v>0.03960950242261978</v>
       </c>
       <c r="K11" t="n">
         <v>4</v>
       </c>
       <c r="L11" s="7" t="n">
-        <v>0.0433</v>
+        <v>0.0364</v>
       </c>
       <c r="M11" s="7" t="n">
-        <v>0.0406125</v>
+        <v>0.03693491707043663</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>352526.5150798046</v>
+        <v>336928.4432312262</v>
       </c>
       <c r="O11" s="3" t="n">
-        <v>430251.9640466141</v>
+        <v>412771.0234410728</v>
       </c>
     </row>
     <row r="12">
@@ -5285,25 +5481,25 @@
         <v>3296854355.784049</v>
       </c>
       <c r="I12" s="7" t="n">
-        <v>0.0375</v>
+        <v>0.03650000241537366</v>
       </c>
       <c r="J12" s="7" t="n">
-        <v>0.0406125</v>
+        <v>0.03960950242261978</v>
       </c>
       <c r="K12" t="n">
         <v>4</v>
       </c>
       <c r="L12" s="7" t="n">
-        <v>0.0433</v>
+        <v>0.0364</v>
       </c>
       <c r="M12" s="7" t="n">
-        <v>0.0406125</v>
+        <v>0.03693491707043663</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>359597.8686123178</v>
+        <v>343828.4959759949</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>436637.2487037305</v>
+        <v>419001.6270619906</v>
       </c>
     </row>
     <row r="13">
@@ -5334,25 +5530,25 @@
         <v>2564167970.277603</v>
       </c>
       <c r="I13" s="7" t="n">
-        <v>0.0375</v>
+        <v>0.03650000241537366</v>
       </c>
       <c r="J13" s="7" t="n">
-        <v>0.0406125</v>
+        <v>0.03960950242261978</v>
       </c>
       <c r="K13" t="n">
         <v>4</v>
       </c>
       <c r="L13" s="7" t="n">
-        <v>0.0433</v>
+        <v>0.0364</v>
       </c>
       <c r="M13" s="7" t="n">
-        <v>0.0406125</v>
+        <v>0.03693491707043663</v>
       </c>
       <c r="N13" s="3" t="n">
-        <v>279681.550159505</v>
+        <v>265848.1192409398</v>
       </c>
       <c r="O13" s="3" t="n">
-        <v>354871.0444631319</v>
+        <v>339216.1773025376</v>
       </c>
     </row>
     <row r="14">
@@ -5383,25 +5579,25 @@
         <v>3333245761.057378</v>
       </c>
       <c r="I14" s="7" t="n">
-        <v>0.0375</v>
+        <v>0.03650000241537366</v>
       </c>
       <c r="J14" s="7" t="n">
-        <v>0.0406125</v>
+        <v>0.03960950242261978</v>
       </c>
       <c r="K14" t="n">
         <v>4</v>
       </c>
       <c r="L14" s="7" t="n">
-        <v>0.0433</v>
+        <v>0.0364</v>
       </c>
       <c r="M14" s="7" t="n">
-        <v>0.0406125</v>
+        <v>0.03693491707043663</v>
       </c>
       <c r="N14" s="3" t="n">
-        <v>363567.1891706061</v>
+        <v>347701.6612882871</v>
       </c>
       <c r="O14" s="3" t="n">
-        <v>440342.8204435381</v>
+        <v>422617.4327683006</v>
       </c>
     </row>
     <row r="15">
@@ -5432,25 +5628,25 @@
         <v>3477336061.802335</v>
       </c>
       <c r="I15" s="7" t="n">
-        <v>0.0375</v>
+        <v>0.03650000241537366</v>
       </c>
       <c r="J15" s="7" t="n">
-        <v>0.0406125</v>
+        <v>0.03960950242261978</v>
       </c>
       <c r="K15" t="n">
         <v>4</v>
       </c>
       <c r="L15" s="7" t="n">
-        <v>0.0433</v>
+        <v>0.0364</v>
       </c>
       <c r="M15" s="7" t="n">
-        <v>0.0406125</v>
+        <v>0.03693491707043663</v>
       </c>
       <c r="N15" s="3" t="n">
-        <v>379283.5537545285</v>
+        <v>363037.3030556614</v>
       </c>
       <c r="O15" s="3" t="n">
-        <v>456956.936474979</v>
+        <v>438829.0783037072</v>
       </c>
     </row>
     <row r="16">
@@ -5481,25 +5677,25 @@
         <v>3378762870.261068</v>
       </c>
       <c r="I16" s="7" t="n">
-        <v>0.0375</v>
+        <v>0.03650000241537366</v>
       </c>
       <c r="J16" s="7" t="n">
-        <v>0.0406125</v>
+        <v>0.03960950242261978</v>
       </c>
       <c r="K16" t="n">
         <v>4</v>
       </c>
       <c r="L16" s="7" t="n">
-        <v>0.0433</v>
+        <v>0.0363</v>
       </c>
       <c r="M16" s="7" t="n">
-        <v>0.0406125</v>
+        <v>0.0368515837371033</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>368531.8778370391</v>
+        <v>352325.8733623142</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>449679.4429997999</v>
+        <v>431507.6703348673</v>
       </c>
     </row>
     <row r="17">
@@ -5530,25 +5726,25 @@
         <v>3316629457.12973</v>
       </c>
       <c r="I17" s="7" t="n">
-        <v>0.0375</v>
+        <v>0.03650000241537366</v>
       </c>
       <c r="J17" s="7" t="n">
-        <v>0.0406125</v>
+        <v>0.03960950242261978</v>
       </c>
       <c r="K17" t="n">
         <v>4</v>
       </c>
       <c r="L17" s="7" t="n">
-        <v>0.0433</v>
+        <v>0.0363</v>
       </c>
       <c r="M17" s="7" t="n">
-        <v>0.0406125</v>
+        <v>0.0368515837371033</v>
       </c>
       <c r="N17" s="3" t="n">
-        <v>361754.7986820444</v>
+        <v>345712.9663127756</v>
       </c>
       <c r="O17" s="3" t="n">
-        <v>441136.7945085737</v>
+        <v>423171.9641792552</v>
       </c>
     </row>
     <row r="18">
@@ -5579,25 +5775,25 @@
         <v>3307806010.553778</v>
       </c>
       <c r="I18" s="7" t="n">
-        <v>0.0375</v>
+        <v>0.03650000241537366</v>
       </c>
       <c r="J18" s="7" t="n">
-        <v>0.0406125</v>
+        <v>0.03960950242261978</v>
       </c>
       <c r="K18" t="n">
         <v>4</v>
       </c>
       <c r="L18" s="7" t="n">
-        <v>0.0433</v>
+        <v>0.0363</v>
       </c>
       <c r="M18" s="7" t="n">
-        <v>0.0406125</v>
+        <v>0.0368515837371033</v>
       </c>
       <c r="N18" s="3" t="n">
-        <v>360792.3986970524</v>
+        <v>344773.8800929344</v>
       </c>
       <c r="O18" s="3" t="n">
-        <v>441234.8952874962</v>
+        <v>423267.6885049809</v>
       </c>
     </row>
     <row r="19">
@@ -5628,25 +5824,25 @@
         <v>3342721847.790328</v>
       </c>
       <c r="I19" s="7" t="n">
-        <v>0.0375</v>
+        <v>0.03650000241537366</v>
       </c>
       <c r="J19" s="7" t="n">
-        <v>0.0406125</v>
+        <v>0.03960950242261978</v>
       </c>
       <c r="K19" t="n">
         <v>4</v>
       </c>
       <c r="L19" s="7" t="n">
-        <v>0.0433</v>
+        <v>0.0363</v>
       </c>
       <c r="M19" s="7" t="n">
-        <v>0.0406125</v>
+        <v>0.0368515837371033</v>
       </c>
       <c r="N19" s="3" t="n">
-        <v>364600.7745899851</v>
+        <v>348489.9995617628</v>
       </c>
       <c r="O19" s="3" t="n">
-        <v>445429.5724691449</v>
+        <v>427360.7512641225</v>
       </c>
     </row>
     <row r="20">
@@ -5677,25 +5873,25 @@
         <v>3374734736.272226</v>
       </c>
       <c r="I20" s="7" t="n">
-        <v>0.0375</v>
+        <v>0.03650000241537366</v>
       </c>
       <c r="J20" s="7" t="n">
-        <v>0.0406125</v>
+        <v>0.03960950242261978</v>
       </c>
       <c r="K20" t="n">
         <v>4</v>
       </c>
       <c r="L20" s="7" t="n">
-        <v>0.0433</v>
+        <v>0.0363</v>
       </c>
       <c r="M20" s="7" t="n">
-        <v>0.0406125</v>
+        <v>0.0368515837371033</v>
       </c>
       <c r="N20" s="3" t="n">
-        <v>368092.5170887151</v>
+        <v>351897.1559571559</v>
       </c>
       <c r="O20" s="3" t="n">
-        <v>449367.5714651509</v>
+        <v>431203.3537667908</v>
       </c>
     </row>
     <row r="21">
@@ -5726,25 +5922,25 @@
         <v>3372689032.943098</v>
       </c>
       <c r="I21" s="7" t="n">
-        <v>0.0375</v>
+        <v>0.03650000241537366</v>
       </c>
       <c r="J21" s="7" t="n">
-        <v>0.0406125</v>
+        <v>0.03960950242261978</v>
       </c>
       <c r="K21" t="n">
         <v>4</v>
       </c>
       <c r="L21" s="7" t="n">
-        <v>0.0433</v>
+        <v>0.0363</v>
       </c>
       <c r="M21" s="7" t="n">
-        <v>0.0406125</v>
+        <v>0.0368515837371033</v>
       </c>
       <c r="N21" s="3" t="n">
-        <v>367869.3860439127</v>
+        <v>351679.4301750899</v>
       </c>
       <c r="O21" s="3" t="n">
-        <v>450354.80603147</v>
+        <v>432166.6729598901</v>
       </c>
     </row>
     <row r="22">
@@ -5775,25 +5971,25 @@
         <v>3351939631.25432</v>
       </c>
       <c r="I22" s="7" t="n">
-        <v>0.0375</v>
+        <v>0.03650000241537366</v>
       </c>
       <c r="J22" s="7" t="n">
-        <v>0.0406125</v>
+        <v>0.03960950242261978</v>
       </c>
       <c r="K22" t="n">
         <v>4</v>
       </c>
       <c r="L22" s="7" t="n">
-        <v>0.0433</v>
+        <v>0.0363</v>
       </c>
       <c r="M22" s="7" t="n">
-        <v>0.0406125</v>
+        <v>0.0368515837371033</v>
       </c>
       <c r="N22" s="3" t="n">
-        <v>365606.1860911532</v>
+        <v>349471.0553605374</v>
       </c>
       <c r="O22" s="3" t="n">
-        <v>448079.6676539161</v>
+        <v>429946.6489242385</v>
       </c>
     </row>
     <row r="23">
@@ -5824,25 +6020,25 @@
         <v>3507020842.800418</v>
       </c>
       <c r="I23" s="7" t="n">
-        <v>0.0375</v>
+        <v>0.03650000241537366</v>
       </c>
       <c r="J23" s="7" t="n">
-        <v>0.0406125</v>
+        <v>0.03960950242261978</v>
       </c>
       <c r="K23" t="n">
         <v>4</v>
       </c>
       <c r="L23" s="7" t="n">
-        <v>0.0433</v>
+        <v>0.0362</v>
       </c>
       <c r="M23" s="7" t="n">
-        <v>0.0406125</v>
+        <v>0.03676825040376996</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>382521.3625337991</v>
+        <v>365756.2416435395</v>
       </c>
       <c r="O23" s="3" t="n">
-        <v>470725.9759771289</v>
+        <v>451824.132648079</v>
       </c>
     </row>
     <row r="24">
@@ -5873,25 +6069,25 @@
         <v>3463785946.00189</v>
       </c>
       <c r="I24" s="7" t="n">
-        <v>0.0375</v>
+        <v>0.03650000241537366</v>
       </c>
       <c r="J24" s="7" t="n">
-        <v>0.0406125</v>
+        <v>0.03960950242261978</v>
       </c>
       <c r="K24" t="n">
         <v>4</v>
       </c>
       <c r="L24" s="7" t="n">
-        <v>0.0433</v>
+        <v>0.0362</v>
       </c>
       <c r="M24" s="7" t="n">
-        <v>0.0406125</v>
+        <v>0.03676825040376996</v>
       </c>
       <c r="N24" s="3" t="n">
-        <v>377805.601671889</v>
+        <v>361154.7182535286</v>
       </c>
       <c r="O24" s="3" t="n">
-        <v>467387.814818019</v>
+        <v>448566.8371441148</v>
       </c>
     </row>
     <row r="25">
@@ -5922,25 +6118,25 @@
         <v>3205941602.598647</v>
       </c>
       <c r="I25" s="7" t="n">
-        <v>0.0375</v>
+        <v>0.03650000241537366</v>
       </c>
       <c r="J25" s="7" t="n">
-        <v>0.0406125</v>
+        <v>0.03960950242261978</v>
       </c>
       <c r="K25" t="n">
         <v>4</v>
       </c>
       <c r="L25" s="7" t="n">
-        <v>0.0433</v>
+        <v>0.0362</v>
       </c>
       <c r="M25" s="7" t="n">
-        <v>0.0406125</v>
+        <v>0.03676825040376996</v>
       </c>
       <c r="N25" s="3" t="n">
-        <v>349681.7398583154</v>
+        <v>333712.1460489289</v>
       </c>
       <c r="O25" s="3" t="n">
-        <v>438874.1560084191</v>
+        <v>420743.9106240411</v>
       </c>
     </row>
     <row r="26">
@@ -5971,25 +6167,25 @@
         <v>3124170851.965993</v>
       </c>
       <c r="I26" s="7" t="n">
-        <v>0.0375</v>
+        <v>0.03650000241537366</v>
       </c>
       <c r="J26" s="7" t="n">
-        <v>0.0406125</v>
+        <v>0.03960950242261978</v>
       </c>
       <c r="K26" t="n">
         <v>4</v>
       </c>
       <c r="L26" s="7" t="n">
-        <v>0.0433</v>
+        <v>0.0362</v>
       </c>
       <c r="M26" s="7" t="n">
-        <v>0.0406125</v>
+        <v>0.03676825040376996</v>
       </c>
       <c r="N26" s="3" t="n">
-        <v>340762.7569524604</v>
+        <v>325009.2220334444</v>
       </c>
       <c r="O26" s="3" t="n">
-        <v>432812.6310396074</v>
+        <v>414829.2237389592</v>
       </c>
     </row>
     <row r="27">
@@ -6020,25 +6216,25 @@
         <v>3633642090.151248</v>
       </c>
       <c r="I27" s="7" t="n">
-        <v>0.0375</v>
+        <v>0.03650000241537366</v>
       </c>
       <c r="J27" s="7" t="n">
-        <v>0.0406125</v>
+        <v>0.03960950242261978</v>
       </c>
       <c r="K27" t="n">
         <v>4</v>
       </c>
       <c r="L27" s="7" t="n">
-        <v>0.0433</v>
+        <v>0.0362</v>
       </c>
       <c r="M27" s="7" t="n">
-        <v>0.0406125</v>
+        <v>0.03676825040376996</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>396332.3246676004</v>
+        <v>379232.6385937233</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>487588.0287219654</v>
+        <v>468277.7087264755</v>
       </c>
     </row>
     <row r="28">
@@ -6069,25 +6265,25 @@
         <v>3613109775.02256</v>
       </c>
       <c r="I28" s="7" t="n">
-        <v>0.0375</v>
+        <v>0.03650000241537366</v>
       </c>
       <c r="J28" s="7" t="n">
-        <v>0.0406125</v>
+        <v>0.03960950242261978</v>
       </c>
       <c r="K28" t="n">
         <v>4</v>
       </c>
       <c r="L28" s="7" t="n">
-        <v>0.0433</v>
+        <v>0.0362</v>
       </c>
       <c r="M28" s="7" t="n">
-        <v>0.0406125</v>
+        <v>0.03676825040376996</v>
       </c>
       <c r="N28" s="3" t="n">
-        <v>394092.8030020469</v>
+        <v>377047.368469083</v>
       </c>
       <c r="O28" s="3" t="n">
-        <v>485766.3668895173</v>
+        <v>466500.1759430798</v>
       </c>
     </row>
     <row r="29">
@@ -6118,25 +6314,25 @@
         <v>3628217354.598102</v>
       </c>
       <c r="I29" s="7" t="n">
-        <v>0.0375</v>
+        <v>0.03650000241537366</v>
       </c>
       <c r="J29" s="7" t="n">
-        <v>0.0406125</v>
+        <v>0.03960950242261978</v>
       </c>
       <c r="K29" t="n">
         <v>4</v>
       </c>
       <c r="L29" s="7" t="n">
-        <v>0.0433</v>
+        <v>0.0362</v>
       </c>
       <c r="M29" s="7" t="n">
-        <v>0.0406125</v>
+        <v>0.03676825040376996</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>395740.6323657326</v>
+        <v>378655.279807631</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>487787.8536450268</v>
+        <v>468472.6929685309</v>
       </c>
     </row>
     <row r="30">
@@ -6167,25 +6363,25 @@
         <v>3622578869.287579</v>
       </c>
       <c r="I30" s="7" t="n">
-        <v>0.0375</v>
+        <v>0.03650000241537366</v>
       </c>
       <c r="J30" s="7" t="n">
-        <v>0.0406125</v>
+        <v>0.03960950242261978</v>
       </c>
       <c r="K30" t="n">
         <v>4</v>
       </c>
       <c r="L30" s="7" t="n">
-        <v>0.0433</v>
+        <v>0.0362</v>
       </c>
       <c r="M30" s="7" t="n">
-        <v>0.0406125</v>
+        <v>0.03676825040376996</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>395125.6257318154</v>
+        <v>378055.1714701112</v>
       </c>
       <c r="O30" s="3" t="n">
-        <v>487521.6974699855</v>
+        <v>468212.9843232642</v>
       </c>
     </row>
     <row r="31">
@@ -6216,25 +6412,25 @@
         <v>3413429322.143122</v>
       </c>
       <c r="I31" s="7" t="n">
-        <v>0.0375</v>
+        <v>0.03600000425292382</v>
       </c>
       <c r="J31" s="7" t="n">
-        <v>0.0406125</v>
+        <v>0.03910800426568259</v>
       </c>
       <c r="K31" t="n">
         <v>4</v>
       </c>
       <c r="L31" s="7" t="n">
-        <v>0.0433</v>
+        <v>0.0362</v>
       </c>
       <c r="M31" s="7" t="n">
-        <v>0.0406125</v>
+        <v>0.03668466737761376</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>372313.0525156438</v>
+        <v>352383.5789754955</v>
       </c>
       <c r="O31" s="3" t="n">
-        <v>458234.2488764576</v>
+        <v>435181.9142288258</v>
       </c>
     </row>
     <row r="32">
@@ -6265,25 +6461,25 @@
         <v>3252967949.895449</v>
       </c>
       <c r="I32" s="7" t="n">
-        <v>0.0375</v>
+        <v>0.03600000425292382</v>
       </c>
       <c r="J32" s="7" t="n">
-        <v>0.0406125</v>
+        <v>0.03910800426568259</v>
       </c>
       <c r="K32" t="n">
         <v>4</v>
       </c>
       <c r="L32" s="7" t="n">
-        <v>0.0433</v>
+        <v>0.0362</v>
       </c>
       <c r="M32" s="7" t="n">
-        <v>0.0406125</v>
+        <v>0.03668466737761376</v>
       </c>
       <c r="N32" s="3" t="n">
-        <v>354811.0456849087</v>
+        <v>335517.6938324182</v>
       </c>
       <c r="O32" s="3" t="n">
-        <v>444044.9338222871</v>
+        <v>421508.318950465</v>
       </c>
     </row>
     <row r="33">
@@ -6314,25 +6510,25 @@
         <v>3221477558.745079</v>
       </c>
       <c r="I33" s="7" t="n">
-        <v>0.0375</v>
+        <v>0.03600000425292382</v>
       </c>
       <c r="J33" s="7" t="n">
-        <v>0.0406125</v>
+        <v>0.03910800426568259</v>
       </c>
       <c r="K33" t="n">
         <v>4</v>
       </c>
       <c r="L33" s="7" t="n">
-        <v>0.0433</v>
+        <v>0.0362</v>
       </c>
       <c r="M33" s="7" t="n">
-        <v>0.0406125</v>
+        <v>0.03668466737761376</v>
       </c>
       <c r="N33" s="3" t="n">
-        <v>351376.2935492632</v>
+        <v>332207.7799708258</v>
       </c>
       <c r="O33" s="3" t="n">
-        <v>445205.7569732065</v>
+        <v>422626.9512378465</v>
       </c>
     </row>
     <row r="34">
@@ -6363,25 +6559,25 @@
         <v>3246872717.915842</v>
       </c>
       <c r="I34" s="7" t="n">
-        <v>0.0375</v>
+        <v>0.03600000425292382</v>
       </c>
       <c r="J34" s="7" t="n">
-        <v>0.0406125</v>
+        <v>0.03910800426568259</v>
       </c>
       <c r="K34" t="n">
         <v>4</v>
       </c>
       <c r="L34" s="7" t="n">
-        <v>0.0433</v>
+        <v>0.0362</v>
       </c>
       <c r="M34" s="7" t="n">
-        <v>0.0406125</v>
+        <v>0.03668466737761376</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>354146.2203113768</v>
+        <v>334877.0319644032</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>453830.3612886349</v>
+        <v>430938.0887659761</v>
       </c>
     </row>
     <row r="35">
@@ -6412,25 +6608,25 @@
         <v>3224509478.620773</v>
       </c>
       <c r="I35" s="7" t="n">
-        <v>0.0375</v>
+        <v>0.03600000425292382</v>
       </c>
       <c r="J35" s="7" t="n">
-        <v>0.0406125</v>
+        <v>0.03910800426568259</v>
       </c>
       <c r="K35" t="n">
         <v>4</v>
       </c>
       <c r="L35" s="7" t="n">
-        <v>0.0433</v>
+        <v>0.0362</v>
       </c>
       <c r="M35" s="7" t="n">
-        <v>0.0406125</v>
+        <v>0.03668466737761376</v>
       </c>
       <c r="N35" s="3" t="n">
-        <v>351706.9942134252</v>
+        <v>332526.4611067913</v>
       </c>
       <c r="O35" s="3" t="n">
-        <v>450359.4957737069</v>
+        <v>427593.374089083</v>
       </c>
     </row>
     <row r="36">
@@ -6461,25 +6657,25 @@
         <v>3218414966.682919</v>
       </c>
       <c r="I36" s="7" t="n">
-        <v>0.0375</v>
+        <v>0.03600000425292382</v>
       </c>
       <c r="J36" s="7" t="n">
-        <v>0.0406125</v>
+        <v>0.03910800426568259</v>
       </c>
       <c r="K36" t="n">
         <v>4</v>
       </c>
       <c r="L36" s="7" t="n">
-        <v>0.0433</v>
+        <v>0.0362</v>
       </c>
       <c r="M36" s="7" t="n">
-        <v>0.0406125</v>
+        <v>0.03668466737761376</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>351042.2473770235</v>
+        <v>331885.8749214238</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>449041.8992520352</v>
+        <v>426323.6664598752</v>
       </c>
     </row>
     <row r="38">
@@ -6500,11 +6696,11 @@
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr"/>
       <c r="M38" t="inlineStr"/>
-      <c r="N38" s="11" t="n">
-        <v>11348183.48346371</v>
-      </c>
-      <c r="O38" s="11" t="n">
-        <v>13983245.54099589</v>
+      <c r="N38" s="12" t="n">
+        <v>10827488.55337466</v>
+      </c>
+      <c r="O38" s="12" t="n">
+        <v>13391864.98596525</v>
       </c>
     </row>
   </sheetData>

--- a/settlements/spark/2026-05/spark_settlement_may_2026.xlsx
+++ b/settlements/spark/2026-05/spark_settlement_may_2026.xlsx
@@ -666,7 +666,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-06-23T21:12:43+00:00</t>
+          <t>2026-06-23T21:47:21+00:00</t>
         </is>
       </c>
     </row>
@@ -4463,7 +4463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D46"/>
+  <dimension ref="A1:C46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="80" customWidth="1" min="1" max="1"/>
@@ -4583,7 +4583,7 @@
         </is>
       </c>
       <c r="B13" s="12" t="n">
-        <v>219906.3997824828</v>
+        <v>219906.399780756</v>
       </c>
     </row>
     <row r="15">
@@ -4593,7 +4593,7 @@
         </is>
       </c>
       <c r="B15" s="3" t="n">
-        <v>11047394.95315714</v>
+        <v>11047394.95315541</v>
       </c>
     </row>
     <row r="16">
@@ -4613,7 +4613,7 @@
         </is>
       </c>
       <c r="B17" s="12" t="n">
-        <v>219906.3997824828</v>
+        <v>219906.399780756</v>
       </c>
     </row>
     <row r="19">
@@ -4629,11 +4629,6 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Rate (APY)</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
           <t>CoF (USD)</t>
         </is>
       </c>
@@ -4647,11 +4642,8 @@
       <c r="B20" s="6" t="n">
         <v>1000000000</v>
       </c>
-      <c r="C20" s="7" t="n">
-        <v>0.03682465368903005</v>
-      </c>
-      <c r="D20" s="3" t="n">
-        <v>3071515.028318575</v>
+      <c r="C20" s="3" t="n">
+        <v>3071515.028317151</v>
       </c>
     </row>
     <row r="21">
@@ -4663,11 +4655,8 @@
       <c r="B21" s="6" t="n">
         <v>2356195943.673027</v>
       </c>
-      <c r="C21" s="7" t="n">
-        <v>0.03951513515348828</v>
-      </c>
-      <c r="D21" s="3" t="n">
-        <v>7755973.525058723</v>
+      <c r="C21" s="3" t="n">
+        <v>7755973.525057507</v>
       </c>
     </row>
     <row r="23">

--- a/settlements/spark/2026-05/spark_settlement_may_2026.xlsx
+++ b/settlements/spark/2026-05/spark_settlement_may_2026.xlsx
@@ -20,10 +20,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00;&quot;−$&quot;#,##0.00;&quot;$&quot;0.00"/>
     <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0;&quot;−$&quot;#,##0;&quot;$&quot;0"/>
     <numFmt numFmtId="166" formatCode="0.000%"/>
+    <numFmt numFmtId="167" formatCode="0.0"/>
   </numFmts>
   <fonts count="4">
     <font>
@@ -75,7 +76,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -86,10 +87,12 @@
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -488,7 +491,7 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>13388258.15969513</v>
+        <v>13408944.7424591</v>
       </c>
     </row>
     <row r="5">
@@ -498,13 +501,13 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>121900.7497091584</v>
+        <v>118578.1793987423</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
       <c r="B6" s="4" t="n">
-        <v>13510158.90940429</v>
+        <v>13527522.92185785</v>
       </c>
     </row>
     <row r="8">
@@ -526,7 +529,7 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>10840739.61571033</v>
+        <v>10320044.68562127</v>
       </c>
     </row>
     <row r="10">
@@ -536,13 +539,13 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>39615.44347073233</v>
+        <v>40550.6842112442</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr"/>
       <c r="B11" s="4" t="n">
-        <v>10880355.05918106</v>
+        <v>10360595.36983252</v>
       </c>
     </row>
     <row r="13">
@@ -564,7 +567,7 @@
         </is>
       </c>
       <c r="B14" s="3" t="n">
-        <v>10840739.61571033</v>
+        <v>10320044.68562127</v>
       </c>
     </row>
     <row r="15">
@@ -574,13 +577,13 @@
         </is>
       </c>
       <c r="B15" s="3" t="n">
-        <v>-3142505.92528556</v>
+        <v>-3071820.300343978</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr"/>
       <c r="B16" s="4" t="n">
-        <v>13983245.54099589</v>
+        <v>13391864.98596525</v>
       </c>
     </row>
     <row r="18">
@@ -612,7 +615,7 @@
         </is>
       </c>
       <c r="B21" s="3" t="n">
-        <v>13388258.15969513</v>
+        <v>13408944.7424591</v>
       </c>
     </row>
     <row r="22">
@@ -622,13 +625,13 @@
         </is>
       </c>
       <c r="B22" s="3" t="n">
-        <v>-10840739.61571033</v>
+        <v>-10320044.68562127</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr"/>
       <c r="B23" s="4" t="n">
-        <v>1131773.551961985</v>
+        <v>1708588.925385048</v>
       </c>
     </row>
     <row r="25">
@@ -663,7 +666,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-06-10T11:03:01+00:00</t>
+          <t>2026-06-23T21:47:21+00:00</t>
         </is>
       </c>
     </row>
@@ -842,13 +845,13 @@
         <v>-145686527.279134</v>
       </c>
       <c r="H2" s="6" t="n">
-        <v>3777395.225054608</v>
+        <v>3834450.909129127</v>
       </c>
       <c r="I2" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J2" s="6" t="n">
-        <v>3777395.225054608</v>
+        <v>3834450.909129127</v>
       </c>
       <c r="K2" s="6" t="n">
         <v>0</v>
@@ -860,13 +863,13 @@
         <v>1</v>
       </c>
       <c r="N2" s="6" t="n">
-        <v>4410254.829322996</v>
+        <v>4201977.102126558</v>
       </c>
       <c r="O2" s="6" t="n">
-        <v>4410254.829322996</v>
+        <v>4201977.102126558</v>
       </c>
       <c r="P2" s="6" t="n">
-        <v>-632859.6042683872</v>
+        <v>-367526.192997431</v>
       </c>
       <c r="Q2" s="6" t="n">
         <v>0</v>
@@ -925,13 +928,13 @@
         <v>1</v>
       </c>
       <c r="N3" s="6" t="n">
-        <v>1558684.923959588</v>
+        <v>1485074.811632477</v>
       </c>
       <c r="O3" s="6" t="n">
-        <v>1558684.923959588</v>
+        <v>1485074.811632477</v>
       </c>
       <c r="P3" s="6" t="n">
-        <v>309427.2442764115</v>
+        <v>383037.3566035236</v>
       </c>
       <c r="Q3" s="6" t="n">
         <v>0</v>
@@ -990,13 +993,13 @@
         <v>1</v>
       </c>
       <c r="N4" s="6" t="n">
-        <v>1428099.786876452</v>
+        <v>1360656.659589858</v>
       </c>
       <c r="O4" s="6" t="n">
-        <v>1428099.786876452</v>
+        <v>1360656.659589858</v>
       </c>
       <c r="P4" s="6" t="n">
-        <v>1663480.213123548</v>
+        <v>1730923.340410141</v>
       </c>
       <c r="Q4" s="6" t="n">
         <v>0</v>
@@ -1055,13 +1058,13 @@
         <v>1</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>1252424.714284955</v>
+        <v>1193277.979442887</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>1252424.714284955</v>
+        <v>1193277.979442887</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>-1446869.158728908</v>
+        <v>-1387722.42388684</v>
       </c>
       <c r="Q5" s="6" t="n">
         <v>0</v>
@@ -1120,13 +1123,13 @@
         <v>1</v>
       </c>
       <c r="N6" s="6" t="n">
-        <v>416618.9330474357</v>
+        <v>396943.7786991677</v>
       </c>
       <c r="O6" s="6" t="n">
-        <v>416618.9330474357</v>
+        <v>396943.7786991677</v>
       </c>
       <c r="P6" s="6" t="n">
-        <v>142834.0061937836</v>
+        <v>162509.1605420516</v>
       </c>
       <c r="Q6" s="6" t="n">
         <v>86642406.62655522</v>
@@ -1189,13 +1192,13 @@
         <v>1</v>
       </c>
       <c r="N7" s="6" t="n">
-        <v>332573.59694228</v>
+        <v>316867.5492018788</v>
       </c>
       <c r="O7" s="6" t="n">
-        <v>296108.7831004824</v>
+        <v>280402.7353600811</v>
       </c>
       <c r="P7" s="6" t="n">
-        <v>103469.4519727446</v>
+        <v>119175.4997131458</v>
       </c>
       <c r="Q7" s="6" t="n">
         <v>0</v>
@@ -1254,13 +1257,13 @@
         <v>1</v>
       </c>
       <c r="N8" s="6" t="n">
-        <v>243821.3957592647</v>
+        <v>232306.7400044638</v>
       </c>
       <c r="O8" s="6" t="n">
-        <v>243821.3957592647</v>
+        <v>232306.7400044638</v>
       </c>
       <c r="P8" s="6" t="n">
-        <v>179709.2128239369</v>
+        <v>191223.8685787379</v>
       </c>
       <c r="Q8" s="6" t="n">
         <v>0</v>
@@ -1319,13 +1322,13 @@
         <v>1</v>
       </c>
       <c r="N9" s="6" t="n">
-        <v>232036.1413934696</v>
+        <v>221078.0534762956</v>
       </c>
       <c r="O9" s="6" t="n">
-        <v>232036.1413934696</v>
+        <v>221078.0534762956</v>
       </c>
       <c r="P9" s="6" t="n">
-        <v>-203032.1706934696</v>
+        <v>-192074.0827762955</v>
       </c>
       <c r="Q9" s="6" t="n">
         <v>0</v>
@@ -1384,13 +1387,13 @@
         <v>1</v>
       </c>
       <c r="N10" s="6" t="n">
-        <v>232032.2997438859</v>
+        <v>221074.3932516124</v>
       </c>
       <c r="O10" s="6" t="n">
-        <v>232032.2997438859</v>
+        <v>221074.3932516124</v>
       </c>
       <c r="P10" s="6" t="n">
-        <v>-225646.4158722456</v>
+        <v>-214688.5093799721</v>
       </c>
       <c r="Q10" s="6" t="n">
         <v>0</v>
@@ -1449,13 +1452,13 @@
         <v>1</v>
       </c>
       <c r="N11" s="6" t="n">
-        <v>236771.6390094491</v>
+        <v>225589.9135205768</v>
       </c>
       <c r="O11" s="6" t="n">
-        <v>210810.9679914328</v>
+        <v>199629.2425025605</v>
       </c>
       <c r="P11" s="6" t="n">
-        <v>73663.79037975192</v>
+        <v>84845.51586862426</v>
       </c>
       <c r="Q11" s="6" t="n">
         <v>0</v>
@@ -1514,13 +1517,13 @@
         <v>1</v>
       </c>
       <c r="N12" s="6" t="n">
-        <v>207950.3643444547</v>
+        <v>198129.7460510709</v>
       </c>
       <c r="O12" s="6" t="n">
-        <v>207950.3643444547</v>
+        <v>198129.7460510709</v>
       </c>
       <c r="P12" s="6" t="n">
-        <v>9319.032102103598</v>
+        <v>19139.65039548748</v>
       </c>
       <c r="Q12" s="6" t="n">
         <v>0</v>
@@ -1579,13 +1582,13 @@
         <v>1</v>
       </c>
       <c r="N13" s="6" t="n">
-        <v>175820.2748945458</v>
+        <v>167517.0251579064</v>
       </c>
       <c r="O13" s="6" t="n">
-        <v>156542.5762059274</v>
+        <v>148239.326469288</v>
       </c>
       <c r="P13" s="6" t="n">
-        <v>54700.75693409086</v>
+        <v>63004.00667073025</v>
       </c>
       <c r="Q13" s="6" t="n">
         <v>0</v>
@@ -1644,13 +1647,13 @@
         <v>1</v>
       </c>
       <c r="N14" s="6" t="n">
-        <v>133957.490815224</v>
+        <v>127631.243737067</v>
       </c>
       <c r="O14" s="6" t="n">
-        <v>133957.490815224</v>
+        <v>127631.243737067</v>
       </c>
       <c r="P14" s="6" t="n">
-        <v>160134.02606122</v>
+        <v>166460.273139377</v>
       </c>
       <c r="Q14" s="6" t="n">
         <v>103099818.9104406</v>
@@ -1774,13 +1777,13 @@
         <v>1</v>
       </c>
       <c r="N16" s="6" t="n">
-        <v>68851.97760926072</v>
+        <v>65600.38921711374</v>
       </c>
       <c r="O16" s="6" t="n">
-        <v>68851.97760926072</v>
+        <v>65600.38921711374</v>
       </c>
       <c r="P16" s="6" t="n">
-        <v>50789.6403167119</v>
+        <v>54041.22870885887</v>
       </c>
       <c r="Q16" s="6" t="n">
         <v>0</v>
@@ -1821,16 +1824,16 @@
         <v>-1252149.613000547</v>
       </c>
       <c r="H17" s="6" t="n">
-        <v>39615.44347073233</v>
+        <v>40550.6842112442</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>34540.61737377704</v>
+        <v>33605.37663326517</v>
       </c>
       <c r="J17" s="6" t="n">
-        <v>34540.61737377704</v>
+        <v>33605.37663326517</v>
       </c>
       <c r="K17" s="6" t="n">
-        <v>39615.44347073233</v>
+        <v>40550.6842112442</v>
       </c>
       <c r="L17" s="6" t="n">
         <v>49959631.20890453</v>
@@ -1842,10 +1845,10 @@
         <v>0</v>
       </c>
       <c r="O17" s="6" t="n">
-        <v>39615.44347073233</v>
+        <v>40550.6842112442</v>
       </c>
       <c r="P17" s="6" t="n">
-        <v>34540.61737377704</v>
+        <v>33605.37663326517</v>
       </c>
       <c r="Q17" s="6" t="n">
         <v>49959631.20890453</v>
@@ -1908,13 +1911,13 @@
         <v>1</v>
       </c>
       <c r="N18" s="6" t="n">
-        <v>22080.74563910623</v>
+        <v>21037.96518888412</v>
       </c>
       <c r="O18" s="6" t="n">
-        <v>22080.74563910623</v>
+        <v>21037.96518888412</v>
       </c>
       <c r="P18" s="6" t="n">
-        <v>-379.2741364086218</v>
+        <v>663.5063138134914</v>
       </c>
       <c r="Q18" s="6" t="n">
         <v>0</v>
@@ -1973,13 +1976,13 @@
         <v>1</v>
       </c>
       <c r="N19" s="6" t="n">
-        <v>21635.14247209228</v>
+        <v>20613.40597929416</v>
       </c>
       <c r="O19" s="6" t="n">
-        <v>21635.14247209228</v>
+        <v>20613.40597929416</v>
       </c>
       <c r="P19" s="6" t="n">
-        <v>10867.76088090771</v>
+        <v>11889.49737370584</v>
       </c>
       <c r="Q19" s="6" t="n">
         <v>0</v>
@@ -2038,13 +2041,13 @@
         <v>1</v>
       </c>
       <c r="N20" s="6" t="n">
-        <v>11599.47377580961</v>
+        <v>11051.67957157512</v>
       </c>
       <c r="O20" s="6" t="n">
-        <v>11599.47377580961</v>
+        <v>11051.67957157512</v>
       </c>
       <c r="P20" s="6" t="n">
-        <v>-11599.47377580738</v>
+        <v>-11051.67957157289</v>
       </c>
       <c r="Q20" s="6" t="n">
         <v>0</v>
@@ -2103,13 +2106,13 @@
         <v>1</v>
       </c>
       <c r="N21" s="6" t="n">
-        <v>11598.70786928614</v>
+        <v>11050.94983558513</v>
       </c>
       <c r="O21" s="6" t="n">
-        <v>11598.70786928614</v>
+        <v>11050.94983558513</v>
       </c>
       <c r="P21" s="6" t="n">
-        <v>-11598.70786928596</v>
+        <v>-11050.94983558495</v>
       </c>
       <c r="Q21" s="6" t="n">
         <v>0</v>
@@ -2168,13 +2171,13 @@
         <v>1</v>
       </c>
       <c r="N22" s="6" t="n">
-        <v>11596.55720504697</v>
+        <v>11048.90073814358</v>
       </c>
       <c r="O22" s="6" t="n">
-        <v>11596.55720504697</v>
+        <v>11048.90073814358</v>
       </c>
       <c r="P22" s="6" t="n">
-        <v>-11596.55720504697</v>
+        <v>-11048.90073814358</v>
       </c>
       <c r="Q22" s="6" t="n">
         <v>0</v>
@@ -2233,13 +2236,13 @@
         <v>1</v>
       </c>
       <c r="N23" s="6" t="n">
-        <v>11496.29925632405</v>
+        <v>10953.37754931583</v>
       </c>
       <c r="O23" s="6" t="n">
-        <v>11496.29925632405</v>
+        <v>10953.37754931583</v>
       </c>
       <c r="P23" s="6" t="n">
-        <v>-11496.29925632357</v>
+        <v>-10953.37754931536</v>
       </c>
       <c r="Q23" s="6" t="n">
         <v>0</v>
@@ -2298,13 +2301,13 @@
         <v>1</v>
       </c>
       <c r="N24" s="6" t="n">
-        <v>3462.049264890436</v>
+        <v>3298.551285694489</v>
       </c>
       <c r="O24" s="6" t="n">
-        <v>3462.049264890436</v>
+        <v>3298.551285694489</v>
       </c>
       <c r="P24" s="6" t="n">
-        <v>1342.838915254552</v>
+        <v>1506.336894450499</v>
       </c>
       <c r="Q24" s="6" t="n">
         <v>0</v>
@@ -2363,13 +2366,13 @@
         <v>1</v>
       </c>
       <c r="N25" s="6" t="n">
-        <v>2279.53873482809</v>
+        <v>2171.885738545533</v>
       </c>
       <c r="O25" s="6" t="n">
-        <v>2029.600205808002</v>
+        <v>1921.947209525445</v>
       </c>
       <c r="P25" s="6" t="n">
-        <v>709.204295866702</v>
+        <v>816.8572921492586</v>
       </c>
       <c r="Q25" s="6" t="n">
         <v>0</v>
@@ -2428,13 +2431,13 @@
         <v>1</v>
       </c>
       <c r="N26" s="6" t="n">
-        <v>1.072380599454827</v>
+        <v>1.021736588487712</v>
       </c>
       <c r="O26" s="6" t="n">
-        <v>1.072380599454827</v>
+        <v>1.021736588487712</v>
       </c>
       <c r="P26" s="6" t="n">
-        <v>75.25808491975091</v>
+        <v>75.30872893071803</v>
       </c>
       <c r="Q26" s="6" t="n">
         <v>0</v>
@@ -2493,13 +2496,13 @@
         <v>1</v>
       </c>
       <c r="N27" s="6" t="n">
-        <v>0.8539894430318479</v>
+        <v>0.8136591249146683</v>
       </c>
       <c r="O27" s="6" t="n">
-        <v>0.8539894430318479</v>
+        <v>0.8136591249146683</v>
       </c>
       <c r="P27" s="6" t="n">
-        <v>0.3073558323059302</v>
+        <v>0.3476861504231099</v>
       </c>
       <c r="Q27" s="6" t="n">
         <v>0</v>
@@ -2558,13 +2561,13 @@
         <v>1</v>
       </c>
       <c r="N28" s="6" t="n">
-        <v>0.6587432650801534</v>
+        <v>0.6276336001363896</v>
       </c>
       <c r="O28" s="6" t="n">
-        <v>0.6587432650801534</v>
+        <v>0.6276336001363896</v>
       </c>
       <c r="P28" s="6" t="n">
-        <v>-0.6587432650801534</v>
+        <v>-0.6276336001363896</v>
       </c>
       <c r="Q28" s="6" t="n">
         <v>0</v>
@@ -2623,13 +2626,13 @@
         <v>1</v>
       </c>
       <c r="N29" s="6" t="n">
-        <v>0.267561352084571</v>
+        <v>0.2549255583596232</v>
       </c>
       <c r="O29" s="6" t="n">
-        <v>0.267561352084571</v>
+        <v>0.2549255583596232</v>
       </c>
       <c r="P29" s="6" t="n">
-        <v>-0.2675613524150298</v>
+        <v>-0.254925558690082</v>
       </c>
       <c r="Q29" s="6" t="n">
         <v>0</v>
@@ -2688,13 +2691,13 @@
         <v>1</v>
       </c>
       <c r="N30" s="6" t="n">
-        <v>0.2308786281355063</v>
+        <v>0.2199752046855565</v>
       </c>
       <c r="O30" s="6" t="n">
-        <v>0.2308786281355063</v>
+        <v>0.2199752046855565</v>
       </c>
       <c r="P30" s="6" t="n">
-        <v>0.08088492029861985</v>
+        <v>0.09178834374856962</v>
       </c>
       <c r="Q30" s="6" t="n">
         <v>0</v>
@@ -2753,13 +2756,13 @@
         <v>1</v>
       </c>
       <c r="N31" s="6" t="n">
-        <v>0.050831171005292</v>
+        <v>0.04843062927302642</v>
       </c>
       <c r="O31" s="6" t="n">
-        <v>0.050831171005292</v>
+        <v>0.04843062927302642</v>
       </c>
       <c r="P31" s="6" t="n">
-        <v>-0.05082511729812201</v>
+        <v>-0.04842457556585644</v>
       </c>
       <c r="Q31" s="6" t="n">
         <v>0</v>
@@ -2818,13 +2821,13 @@
         <v>1</v>
       </c>
       <c r="N32" s="6" t="n">
-        <v>0.01368516545690748</v>
+        <v>0.01303887283483027</v>
       </c>
       <c r="O32" s="6" t="n">
-        <v>0.01368516545690748</v>
+        <v>0.01303887283483027</v>
       </c>
       <c r="P32" s="6" t="n">
-        <v>0.001704834543092515</v>
+        <v>0.002351127165169734</v>
       </c>
       <c r="Q32" s="6" t="n">
         <v>0</v>
@@ -2883,13 +2886,13 @@
         <v>1</v>
       </c>
       <c r="N33" s="6" t="n">
-        <v>0.003586366276201048</v>
+        <v>0.003416997329097425</v>
       </c>
       <c r="O33" s="6" t="n">
-        <v>0.003586366276201048</v>
+        <v>0.003416997329097425</v>
       </c>
       <c r="P33" s="6" t="n">
-        <v>8.466802633723798</v>
+        <v>8.466972002670902</v>
       </c>
       <c r="Q33" s="6" t="n">
         <v>0</v>
@@ -2948,13 +2951,13 @@
         <v>1</v>
       </c>
       <c r="N34" s="6" t="n">
-        <v>0.0003583352131101747</v>
+        <v>0.0003414125529353442</v>
       </c>
       <c r="O34" s="6" t="n">
-        <v>0.0003583352131101747</v>
+        <v>0.0003414125529353442</v>
       </c>
       <c r="P34" s="6" t="n">
-        <v>0.0003756647868898253</v>
+        <v>0.0003925874470646558</v>
       </c>
       <c r="Q34" s="6" t="n">
         <v>0</v>
@@ -3013,13 +3016,13 @@
         <v>1</v>
       </c>
       <c r="N35" s="6" t="n">
-        <v>0.0001340772488628917</v>
+        <v>0.000127745346117444</v>
       </c>
       <c r="O35" s="6" t="n">
-        <v>0.0001340772488628917</v>
+        <v>0.000127745346117444</v>
       </c>
       <c r="P35" s="6" t="n">
-        <v>5.192275113710832e-05</v>
+        <v>5.825465388255599e-05</v>
       </c>
       <c r="Q35" s="6" t="n">
         <v>0</v>
@@ -3078,13 +3081,13 @@
         <v>1</v>
       </c>
       <c r="N36" s="6" t="n">
-        <v>1.472499214793124e-05</v>
+        <v>1.402959289862589e-05</v>
       </c>
       <c r="O36" s="6" t="n">
-        <v>1.472499214793124e-05</v>
+        <v>1.402959289862589e-05</v>
       </c>
       <c r="P36" s="6" t="n">
-        <v>2.275007852068764e-06</v>
+        <v>2.970407101374112e-06</v>
       </c>
       <c r="Q36" s="6" t="n">
         <v>0</v>
@@ -3143,13 +3146,13 @@
         <v>1</v>
       </c>
       <c r="N37" s="6" t="n">
-        <v>1.332879347576094e-05</v>
+        <v>1.269933079869646e-05</v>
       </c>
       <c r="O37" s="6" t="n">
-        <v>1.332879347576094e-05</v>
+        <v>1.269933079869646e-05</v>
       </c>
       <c r="P37" s="6" t="n">
-        <v>-1.118496897039094e-05</v>
+        <v>-1.055550629332646e-05</v>
       </c>
       <c r="Q37" s="6" t="n">
         <v>0</v>
@@ -3208,13 +3211,13 @@
         <v>1</v>
       </c>
       <c r="N38" s="6" t="n">
-        <v>3.944608674989458e-06</v>
+        <v>3.758321450939806e-06</v>
       </c>
       <c r="O38" s="6" t="n">
-        <v>3.944608674989458e-06</v>
+        <v>3.758321450939806e-06</v>
       </c>
       <c r="P38" s="6" t="n">
-        <v>1.055391325010542e-06</v>
+        <v>1.241678549060194e-06</v>
       </c>
       <c r="Q38" s="6" t="n">
         <v>0</v>
@@ -3273,13 +3276,13 @@
         <v>1</v>
       </c>
       <c r="N39" s="6" t="n">
-        <v>2.877579662079685e-06</v>
+        <v>2.741683716144822e-06</v>
       </c>
       <c r="O39" s="6" t="n">
-        <v>2.877579662079685e-06</v>
+        <v>2.741683716144822e-06</v>
       </c>
       <c r="P39" s="6" t="n">
-        <v>-2.877579662079685e-06</v>
+        <v>-2.741683716144822e-06</v>
       </c>
       <c r="Q39" s="6" t="n">
         <v>0</v>
@@ -3338,13 +3341,13 @@
         <v>1</v>
       </c>
       <c r="N40" s="6" t="n">
-        <v>1.208828958664657e-06</v>
+        <v>1.151741067414945e-06</v>
       </c>
       <c r="O40" s="6" t="n">
-        <v>1.208828958664657e-06</v>
+        <v>1.151741067414945e-06</v>
       </c>
       <c r="P40" s="6" t="n">
-        <v>-5.021221518556572e-07</v>
+        <v>-4.450342606059448e-07</v>
       </c>
       <c r="Q40" s="6" t="n">
         <v>0</v>
@@ -3403,13 +3406,13 @@
         <v>1</v>
       </c>
       <c r="N41" s="6" t="n">
-        <v>1.737861762534574e-07</v>
+        <v>1.6557898841307e-07</v>
       </c>
       <c r="O41" s="6" t="n">
-        <v>1.737861762534574e-07</v>
+        <v>1.6557898841307e-07</v>
       </c>
       <c r="P41" s="6" t="n">
-        <v>-1.737861762534574e-07</v>
+        <v>-1.6557898841307e-07</v>
       </c>
       <c r="Q41" s="6" t="n">
         <v>0</v>
@@ -4460,7 +4463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B26"/>
+  <dimension ref="A1:C46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="80" customWidth="1" min="1" max="1"/>
@@ -4475,195 +4478,377 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>Component</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>USD</t>
+      <c r="A3" s="8" t="inlineStr">
+        <is>
+          <t>Rates &amp; subsidy — effective rate charged this period</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>CoF on utilized debt (= Σ_d max(utilized_d,0) × (1+BR_d)^(1/365)−1)</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="n">
-        <v>10840739.61571033</v>
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>+ Sky-Direct revenue (full venue yield on fixed/capped SDE)</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="n">
-        <v>39615.44347073233</v>
+          <t>Time-weighted utilized</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="n">
+        <v>3356195943.673027</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>equals sky_revenue (total Sky take this month)</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="n">
-        <v>10880355.05918106</v>
+          <t xml:space="preserve">  — first $1B (subsidised tranche)</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="n">
+        <v>1000000000</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  — excess (full base-rate tranche)</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="n">
+        <v>2356195943.673027</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="inlineStr">
-        <is>
-          <t>Utilized base = cum_debt − idle USDS − PSM USDS − Σ SDE asset value − Curve idle − lending idle</t>
-        </is>
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Base rate (BR = SSR + 30bps), period avg</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="n">
+        <v>0.03951513515348828</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Reference rate (effr), period avg</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="n">
+        <v>0.03628709677419355</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="8" t="inlineStr">
-        <is>
-          <t>Sky Revenue (max) — BR × full ilk debt (no deductions)</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="n">
-        <v>13983245.54099589</v>
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Subsidised rate (BR*), period avg</t>
+        </is>
+      </c>
+      <c r="B10" s="7" t="n">
+        <v>0.03682465368903005</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    ↳ actual CoF on Net_Subs (BR × utilized)</t>
-        </is>
-      </c>
-      <c r="B11" s="3" t="n">
-        <v>10840739.61571033</v>
+      <c r="A11" s="8" t="inlineStr">
+        <is>
+          <t>Effective blended rate charged</t>
+        </is>
+      </c>
+      <c r="B11" s="10" t="n">
+        <v>0.03871429258669792</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    ↳ reduction from idle/SDE deductions</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="n">
-        <v>-3142505.92528556</v>
-      </c>
-    </row>
-    <row r="13" ht="60" customHeight="1">
-      <c r="A13" s="10" t="inlineStr">
-        <is>
-          <t>Note: sky_revenue can EXCEED sky_revenue_gross for primes with active SDE positions — sky_revenue also adds sde_revenue on top of BR-on-utilized. The subsidised BR (ref_rate ramp) is already applied here; this is NOT the raw Maker base rate.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="60" customHeight="1">
-      <c r="A15" s="10" t="inlineStr">
-        <is>
-          <t>sUSDS spread (Curve LP + PSM3) — 30 bps × value × n_days deducted from sky_revenue. Sky charges full BR on the underlying utilized; this row is the offsetting refund to the prime so SSR + BR + 30 bps nets to zero economically.</t>
+      <c r="A12" s="8" t="inlineStr">
+        <is>
+          <t>Diff vs base rate (bps)</t>
+        </is>
+      </c>
+      <c r="B12" s="11" t="n">
+        <v>-8.008425667903683</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="8" t="inlineStr">
+        <is>
+          <t>Subsidy benefit to prime (USD)</t>
+        </is>
+      </c>
+      <c r="B13" s="12" t="n">
+        <v>219906.399780756</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>CoF at full base rate (no subsidy)</t>
         </is>
       </c>
       <c r="B15" s="3" t="n">
-        <v>184910.418694979</v>
+        <v>11047394.95315541</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  − actual CoF (subsidy on first tranche)</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="n">
+        <v>10827488.55337466</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>Subsidy</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>Value</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>enabled</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
+      <c r="A17" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  = subsidy benefit</t>
+        </is>
+      </c>
+      <c r="B17" s="12" t="n">
+        <v>219906.399780756</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>cap_usd</t>
-        </is>
-      </c>
-      <c r="B19" s="6" t="n">
-        <v>1000000000</v>
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>Tranche</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>Avg balance</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>CoF (USD)</t>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>program_start</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>2026-01-01</t>
-        </is>
+          <t>Subsidised (first $1B)</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="n">
+        <v>1000000000</v>
+      </c>
+      <c r="C20" s="3" t="n">
+        <v>3071515.028317151</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
+          <t>Excess (&gt; cap)</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="n">
+        <v>2356195943.673027</v>
+      </c>
+      <c r="C21" s="3" t="n">
+        <v>7755973.525057507</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>Component</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>CoF on utilized debt (= Σ_d max(utilized_d,0) × (1+BR_d)^(1/365)−1)</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="n">
+        <v>10320044.68562127</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>+ Sky-Direct revenue (full venue yield on fixed/capped SDE)</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="n">
+        <v>40550.6842112442</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>equals sky_revenue (total Sky take this month)</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="n">
+        <v>10360595.36983252</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>Utilized base = cum_debt − idle USDS − PSM USDS − Σ SDE asset value − Curve idle − lending idle</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="8" t="inlineStr">
+        <is>
+          <t>Sky Revenue (max) — BR × full ilk debt (no deductions)</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="n">
+        <v>13391864.98596525</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ↳ actual CoF on Net_Subs (BR × utilized)</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="n">
+        <v>10320044.68562127</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ↳ reduction from idle/SDE deductions</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="n">
+        <v>-3071820.300343978</v>
+      </c>
+    </row>
+    <row r="33" ht="60" customHeight="1">
+      <c r="A33" s="13" t="inlineStr">
+        <is>
+          <t>Note: sky_revenue can EXCEED sky_revenue_gross for primes with active SDE positions — sky_revenue also adds sde_revenue on top of BR-on-utilized. The subsidised BR (ref_rate ramp) is already applied here; this is NOT the raw Maker base rate.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="60" customHeight="1">
+      <c r="A35" s="13" t="inlineStr">
+        <is>
+          <t>sUSDS spread (Curve LP + PSM3) — 30 bps × value × n_days deducted from sky_revenue. Sky charges full BR on the underlying utilized; this row is the offsetting refund to the prime so SSR + BR + 30 bps nets to zero economically.</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="n">
+        <v>184910.418694979</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>Subsidy</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>enabled</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>cap_usd</t>
+        </is>
+      </c>
+      <c r="B39" s="6" t="n">
+        <v>1000000000</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>program_start</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
           <t>ramp_months</t>
         </is>
       </c>
-      <c r="B21" t="n">
+      <c r="B41" t="n">
         <v>24</v>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
+    <row r="42">
+      <c r="A42" t="inlineStr">
         <is>
           <t>ref_rate_kind</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B42" t="inlineStr">
         <is>
           <t>effr</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
+    <row r="43">
+      <c r="A43" t="inlineStr">
         <is>
           <t>T this period</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B43" t="inlineStr">
         <is>
           <t>4 (SoM) → 4 (EoM)</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="5" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="5" t="inlineStr">
         <is>
           <t>Formula</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B44" t="inlineStr">
         <is>
           <t>subsidised_apy = ref_rate + (base_apy − ref_rate) × min(T, 24) / 24, applied to first cap_usd of utilized; excess at full base_apy</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="5" t="inlineStr">
+    <row r="46">
+      <c r="A46" s="5" t="inlineStr">
         <is>
           <t>Base rate composition: base_apy = (1 + SSR)(1 + 30bps) − 1 (multiplicative)</t>
         </is>
@@ -4836,10 +5021,10 @@
         </is>
       </c>
       <c r="I5" s="6" t="n">
-        <v>39615.44347073233</v>
+        <v>40550.6842112442</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>39615.44347073233</v>
+        <v>40550.6842112442</v>
       </c>
     </row>
   </sheetData>
@@ -4881,7 +5066,7 @@
       </c>
     </row>
     <row r="3" ht="45" customHeight="1">
-      <c r="A3" s="10" t="inlineStr">
+      <c r="A3" s="13" t="inlineStr">
         <is>
           <t>cum_debt = Σ on-chain Vat dart from frob (0x76088703) + grab (0x7bab3f40), then scaled by Vat.ilks[ilk].rate_d / 1e27 read at each day's EoD block — actual outstanding USDS per day, not raw normalised Art. utilized = cum_debt − Σ deductions. base_apy = (1+SSR)(1+0.003)−1 (multiplicative). sub_apy applies on the first cap_usd of utilized when the subsidy is active; excess pays base_apy.</t>
         </is>
@@ -4991,25 +5176,25 @@
         <v>3236279210.15232</v>
       </c>
       <c r="I6" s="7" t="n">
-        <v>0.0375</v>
+        <v>0.03650000241537366</v>
       </c>
       <c r="J6" s="7" t="n">
-        <v>0.0406125</v>
+        <v>0.03960950242261978</v>
       </c>
       <c r="K6" t="n">
         <v>4</v>
       </c>
       <c r="L6" s="7" t="n">
-        <v>0.0433</v>
+        <v>0.0364</v>
       </c>
       <c r="M6" s="7" t="n">
-        <v>0.0406125</v>
+        <v>0.03693491707043663</v>
       </c>
       <c r="N6" s="3" t="n">
-        <v>352990.7544030308</v>
+        <v>337381.4365374905</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>431761.0397033197</v>
+        <v>414243.5423272011</v>
       </c>
     </row>
     <row r="7">
@@ -5040,25 +5225,25 @@
         <v>3583341168.645234</v>
       </c>
       <c r="I7" s="7" t="n">
-        <v>0.0375</v>
+        <v>0.03650000241537366</v>
       </c>
       <c r="J7" s="7" t="n">
-        <v>0.0406125</v>
+        <v>0.03960950242261978</v>
       </c>
       <c r="K7" t="n">
         <v>4</v>
       </c>
       <c r="L7" s="7" t="n">
-        <v>0.0433</v>
+        <v>0.0364</v>
       </c>
       <c r="M7" s="7" t="n">
-        <v>0.0406125</v>
+        <v>0.03693491707043663</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>390845.8511353183</v>
+        <v>374319.5082814827</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>469013.1074139154</v>
+        <v>450593.1931929035</v>
       </c>
     </row>
     <row r="8">
@@ -5089,25 +5274,25 @@
         <v>3577229601.132741</v>
       </c>
       <c r="I8" s="7" t="n">
-        <v>0.0375</v>
+        <v>0.03650000241537366</v>
       </c>
       <c r="J8" s="7" t="n">
-        <v>0.0406125</v>
+        <v>0.03960950242261978</v>
       </c>
       <c r="K8" t="n">
         <v>4</v>
       </c>
       <c r="L8" s="7" t="n">
-        <v>0.0433</v>
+        <v>0.0364</v>
       </c>
       <c r="M8" s="7" t="n">
-        <v>0.0406125</v>
+        <v>0.03693491707043663</v>
       </c>
       <c r="N8" s="3" t="n">
-        <v>390179.243995844</v>
+        <v>373669.0494405744</v>
       </c>
       <c r="O8" s="3" t="n">
-        <v>468886.8453627324</v>
+        <v>450469.9897907797</v>
       </c>
     </row>
     <row r="9">
@@ -5138,25 +5323,25 @@
         <v>3482111304.355217</v>
       </c>
       <c r="I9" s="7" t="n">
-        <v>0.0375</v>
+        <v>0.03650000241537366</v>
       </c>
       <c r="J9" s="7" t="n">
-        <v>0.0406125</v>
+        <v>0.03960950242261978</v>
       </c>
       <c r="K9" t="n">
         <v>4</v>
       </c>
       <c r="L9" s="7" t="n">
-        <v>0.0433</v>
+        <v>0.0364</v>
       </c>
       <c r="M9" s="7" t="n">
-        <v>0.0406125</v>
+        <v>0.03693491707043663</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>379804.4038919058</v>
+        <v>363545.5358011322</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>457700.9827281167</v>
+        <v>439555.1003258834</v>
       </c>
     </row>
     <row r="10">
@@ -5187,25 +5372,25 @@
         <v>3438062922.860942</v>
       </c>
       <c r="I10" s="7" t="n">
-        <v>0.0375</v>
+        <v>0.03650000241537366</v>
       </c>
       <c r="J10" s="7" t="n">
-        <v>0.0406125</v>
+        <v>0.03960950242261978</v>
       </c>
       <c r="K10" t="n">
         <v>4</v>
       </c>
       <c r="L10" s="7" t="n">
-        <v>0.0433</v>
+        <v>0.0364</v>
       </c>
       <c r="M10" s="7" t="n">
-        <v>0.0406125</v>
+        <v>0.03693491707043663</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>374999.9137956497</v>
+        <v>358857.4326079512</v>
       </c>
       <c r="O10" s="3" t="n">
-        <v>452359.580684261</v>
+        <v>434343.0916681122</v>
       </c>
     </row>
     <row r="11">
@@ -5236,25 +5421,25 @@
         <v>3232022985.161858</v>
       </c>
       <c r="I11" s="7" t="n">
-        <v>0.0375</v>
+        <v>0.03650000241537366</v>
       </c>
       <c r="J11" s="7" t="n">
-        <v>0.0406125</v>
+        <v>0.03960950242261978</v>
       </c>
       <c r="K11" t="n">
         <v>4</v>
       </c>
       <c r="L11" s="7" t="n">
-        <v>0.0433</v>
+        <v>0.0364</v>
       </c>
       <c r="M11" s="7" t="n">
-        <v>0.0406125</v>
+        <v>0.03693491707043663</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>352526.5150798046</v>
+        <v>336928.4432312262</v>
       </c>
       <c r="O11" s="3" t="n">
-        <v>430251.9640466141</v>
+        <v>412771.0234410728</v>
       </c>
     </row>
     <row r="12">
@@ -5285,25 +5470,25 @@
         <v>3296854355.784049</v>
       </c>
       <c r="I12" s="7" t="n">
-        <v>0.0375</v>
+        <v>0.03650000241537366</v>
       </c>
       <c r="J12" s="7" t="n">
-        <v>0.0406125</v>
+        <v>0.03960950242261978</v>
       </c>
       <c r="K12" t="n">
         <v>4</v>
       </c>
       <c r="L12" s="7" t="n">
-        <v>0.0433</v>
+        <v>0.0364</v>
       </c>
       <c r="M12" s="7" t="n">
-        <v>0.0406125</v>
+        <v>0.03693491707043663</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>359597.8686123178</v>
+        <v>343828.4959759949</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>436637.2487037305</v>
+        <v>419001.6270619906</v>
       </c>
     </row>
     <row r="13">
@@ -5334,25 +5519,25 @@
         <v>2564167970.277603</v>
       </c>
       <c r="I13" s="7" t="n">
-        <v>0.0375</v>
+        <v>0.03650000241537366</v>
       </c>
       <c r="J13" s="7" t="n">
-        <v>0.0406125</v>
+        <v>0.03960950242261978</v>
       </c>
       <c r="K13" t="n">
         <v>4</v>
       </c>
       <c r="L13" s="7" t="n">
-        <v>0.0433</v>
+        <v>0.0364</v>
       </c>
       <c r="M13" s="7" t="n">
-        <v>0.0406125</v>
+        <v>0.03693491707043663</v>
       </c>
       <c r="N13" s="3" t="n">
-        <v>279681.550159505</v>
+        <v>265848.1192409398</v>
       </c>
       <c r="O13" s="3" t="n">
-        <v>354871.0444631319</v>
+        <v>339216.1773025376</v>
       </c>
     </row>
     <row r="14">
@@ -5383,25 +5568,25 @@
         <v>3333245761.057378</v>
       </c>
       <c r="I14" s="7" t="n">
-        <v>0.0375</v>
+        <v>0.03650000241537366</v>
       </c>
       <c r="J14" s="7" t="n">
-        <v>0.0406125</v>
+        <v>0.03960950242261978</v>
       </c>
       <c r="K14" t="n">
         <v>4</v>
       </c>
       <c r="L14" s="7" t="n">
-        <v>0.0433</v>
+        <v>0.0364</v>
       </c>
       <c r="M14" s="7" t="n">
-        <v>0.0406125</v>
+        <v>0.03693491707043663</v>
       </c>
       <c r="N14" s="3" t="n">
-        <v>363567.1891706061</v>
+        <v>347701.6612882871</v>
       </c>
       <c r="O14" s="3" t="n">
-        <v>440342.8204435381</v>
+        <v>422617.4327683006</v>
       </c>
     </row>
     <row r="15">
@@ -5432,25 +5617,25 @@
         <v>3477336061.802335</v>
       </c>
       <c r="I15" s="7" t="n">
-        <v>0.0375</v>
+        <v>0.03650000241537366</v>
       </c>
       <c r="J15" s="7" t="n">
-        <v>0.0406125</v>
+        <v>0.03960950242261978</v>
       </c>
       <c r="K15" t="n">
         <v>4</v>
       </c>
       <c r="L15" s="7" t="n">
-        <v>0.0433</v>
+        <v>0.0364</v>
       </c>
       <c r="M15" s="7" t="n">
-        <v>0.0406125</v>
+        <v>0.03693491707043663</v>
       </c>
       <c r="N15" s="3" t="n">
-        <v>379283.5537545285</v>
+        <v>363037.3030556614</v>
       </c>
       <c r="O15" s="3" t="n">
-        <v>456956.936474979</v>
+        <v>438829.0783037072</v>
       </c>
     </row>
     <row r="16">
@@ -5481,25 +5666,25 @@
         <v>3378762870.261068</v>
       </c>
       <c r="I16" s="7" t="n">
-        <v>0.0375</v>
+        <v>0.03650000241537366</v>
       </c>
       <c r="J16" s="7" t="n">
-        <v>0.0406125</v>
+        <v>0.03960950242261978</v>
       </c>
       <c r="K16" t="n">
         <v>4</v>
       </c>
       <c r="L16" s="7" t="n">
-        <v>0.0433</v>
+        <v>0.0363</v>
       </c>
       <c r="M16" s="7" t="n">
-        <v>0.0406125</v>
+        <v>0.0368515837371033</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>368531.8778370391</v>
+        <v>352325.8733623142</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>449679.4429997999</v>
+        <v>431507.6703348673</v>
       </c>
     </row>
     <row r="17">
@@ -5530,25 +5715,25 @@
         <v>3316629457.12973</v>
       </c>
       <c r="I17" s="7" t="n">
-        <v>0.0375</v>
+        <v>0.03650000241537366</v>
       </c>
       <c r="J17" s="7" t="n">
-        <v>0.0406125</v>
+        <v>0.03960950242261978</v>
       </c>
       <c r="K17" t="n">
         <v>4</v>
       </c>
       <c r="L17" s="7" t="n">
-        <v>0.0433</v>
+        <v>0.0363</v>
       </c>
       <c r="M17" s="7" t="n">
-        <v>0.0406125</v>
+        <v>0.0368515837371033</v>
       </c>
       <c r="N17" s="3" t="n">
-        <v>361754.7986820444</v>
+        <v>345712.9663127756</v>
       </c>
       <c r="O17" s="3" t="n">
-        <v>441136.7945085737</v>
+        <v>423171.9641792552</v>
       </c>
     </row>
     <row r="18">
@@ -5579,25 +5764,25 @@
         <v>3307806010.553778</v>
       </c>
       <c r="I18" s="7" t="n">
-        <v>0.0375</v>
+        <v>0.03650000241537366</v>
       </c>
       <c r="J18" s="7" t="n">
-        <v>0.0406125</v>
+        <v>0.03960950242261978</v>
       </c>
       <c r="K18" t="n">
         <v>4</v>
       </c>
       <c r="L18" s="7" t="n">
-        <v>0.0433</v>
+        <v>0.0363</v>
       </c>
       <c r="M18" s="7" t="n">
-        <v>0.0406125</v>
+        <v>0.0368515837371033</v>
       </c>
       <c r="N18" s="3" t="n">
-        <v>360792.3986970524</v>
+        <v>344773.8800929344</v>
       </c>
       <c r="O18" s="3" t="n">
-        <v>441234.8952874962</v>
+        <v>423267.6885049809</v>
       </c>
     </row>
     <row r="19">
@@ -5628,25 +5813,25 @@
         <v>3342721847.790328</v>
       </c>
       <c r="I19" s="7" t="n">
-        <v>0.0375</v>
+        <v>0.03650000241537366</v>
       </c>
       <c r="J19" s="7" t="n">
-        <v>0.0406125</v>
+        <v>0.03960950242261978</v>
       </c>
       <c r="K19" t="n">
         <v>4</v>
       </c>
       <c r="L19" s="7" t="n">
-        <v>0.0433</v>
+        <v>0.0363</v>
       </c>
       <c r="M19" s="7" t="n">
-        <v>0.0406125</v>
+        <v>0.0368515837371033</v>
       </c>
       <c r="N19" s="3" t="n">
-        <v>364600.7745899851</v>
+        <v>348489.9995617628</v>
       </c>
       <c r="O19" s="3" t="n">
-        <v>445429.5724691449</v>
+        <v>427360.7512641225</v>
       </c>
     </row>
     <row r="20">
@@ -5677,25 +5862,25 @@
         <v>3374734736.272226</v>
       </c>
       <c r="I20" s="7" t="n">
-        <v>0.0375</v>
+        <v>0.03650000241537366</v>
       </c>
       <c r="J20" s="7" t="n">
-        <v>0.0406125</v>
+        <v>0.03960950242261978</v>
       </c>
       <c r="K20" t="n">
         <v>4</v>
       </c>
       <c r="L20" s="7" t="n">
-        <v>0.0433</v>
+        <v>0.0363</v>
       </c>
       <c r="M20" s="7" t="n">
-        <v>0.0406125</v>
+        <v>0.0368515837371033</v>
       </c>
       <c r="N20" s="3" t="n">
-        <v>368092.5170887151</v>
+        <v>351897.1559571559</v>
       </c>
       <c r="O20" s="3" t="n">
-        <v>449367.5714651509</v>
+        <v>431203.3537667908</v>
       </c>
     </row>
     <row r="21">
@@ -5726,25 +5911,25 @@
         <v>3372689032.943098</v>
       </c>
       <c r="I21" s="7" t="n">
-        <v>0.0375</v>
+        <v>0.03650000241537366</v>
       </c>
       <c r="J21" s="7" t="n">
-        <v>0.0406125</v>
+        <v>0.03960950242261978</v>
       </c>
       <c r="K21" t="n">
         <v>4</v>
       </c>
       <c r="L21" s="7" t="n">
-        <v>0.0433</v>
+        <v>0.0363</v>
       </c>
       <c r="M21" s="7" t="n">
-        <v>0.0406125</v>
+        <v>0.0368515837371033</v>
       </c>
       <c r="N21" s="3" t="n">
-        <v>367869.3860439127</v>
+        <v>351679.4301750899</v>
       </c>
       <c r="O21" s="3" t="n">
-        <v>450354.80603147</v>
+        <v>432166.6729598901</v>
       </c>
     </row>
     <row r="22">
@@ -5775,25 +5960,25 @@
         <v>3351939631.25432</v>
       </c>
       <c r="I22" s="7" t="n">
-        <v>0.0375</v>
+        <v>0.03650000241537366</v>
       </c>
       <c r="J22" s="7" t="n">
-        <v>0.0406125</v>
+        <v>0.03960950242261978</v>
       </c>
       <c r="K22" t="n">
         <v>4</v>
       </c>
       <c r="L22" s="7" t="n">
-        <v>0.0433</v>
+        <v>0.0363</v>
       </c>
       <c r="M22" s="7" t="n">
-        <v>0.0406125</v>
+        <v>0.0368515837371033</v>
       </c>
       <c r="N22" s="3" t="n">
-        <v>365606.1860911532</v>
+        <v>349471.0553605374</v>
       </c>
       <c r="O22" s="3" t="n">
-        <v>448079.6676539161</v>
+        <v>429946.6489242385</v>
       </c>
     </row>
     <row r="23">
@@ -5824,25 +6009,25 @@
         <v>3507020842.800418</v>
       </c>
       <c r="I23" s="7" t="n">
-        <v>0.0375</v>
+        <v>0.03650000241537366</v>
       </c>
       <c r="J23" s="7" t="n">
-        <v>0.0406125</v>
+        <v>0.03960950242261978</v>
       </c>
       <c r="K23" t="n">
         <v>4</v>
       </c>
       <c r="L23" s="7" t="n">
-        <v>0.0433</v>
+        <v>0.0362</v>
       </c>
       <c r="M23" s="7" t="n">
-        <v>0.0406125</v>
+        <v>0.03676825040376996</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>382521.3625337991</v>
+        <v>365756.2416435395</v>
       </c>
       <c r="O23" s="3" t="n">
-        <v>470725.9759771289</v>
+        <v>451824.132648079</v>
       </c>
     </row>
     <row r="24">
@@ -5873,25 +6058,25 @@
         <v>3463785946.00189</v>
       </c>
       <c r="I24" s="7" t="n">
-        <v>0.0375</v>
+        <v>0.03650000241537366</v>
       </c>
       <c r="J24" s="7" t="n">
-        <v>0.0406125</v>
+        <v>0.03960950242261978</v>
       </c>
       <c r="K24" t="n">
         <v>4</v>
       </c>
       <c r="L24" s="7" t="n">
-        <v>0.0433</v>
+        <v>0.0362</v>
       </c>
       <c r="M24" s="7" t="n">
-        <v>0.0406125</v>
+        <v>0.03676825040376996</v>
       </c>
       <c r="N24" s="3" t="n">
-        <v>377805.601671889</v>
+        <v>361154.7182535286</v>
       </c>
       <c r="O24" s="3" t="n">
-        <v>467387.814818019</v>
+        <v>448566.8371441148</v>
       </c>
     </row>
     <row r="25">
@@ -5922,25 +6107,25 @@
         <v>3205941602.598647</v>
       </c>
       <c r="I25" s="7" t="n">
-        <v>0.0375</v>
+        <v>0.03650000241537366</v>
       </c>
       <c r="J25" s="7" t="n">
-        <v>0.0406125</v>
+        <v>0.03960950242261978</v>
       </c>
       <c r="K25" t="n">
         <v>4</v>
       </c>
       <c r="L25" s="7" t="n">
-        <v>0.0433</v>
+        <v>0.0362</v>
       </c>
       <c r="M25" s="7" t="n">
-        <v>0.0406125</v>
+        <v>0.03676825040376996</v>
       </c>
       <c r="N25" s="3" t="n">
-        <v>349681.7398583154</v>
+        <v>333712.1460489289</v>
       </c>
       <c r="O25" s="3" t="n">
-        <v>438874.1560084191</v>
+        <v>420743.9106240411</v>
       </c>
     </row>
     <row r="26">
@@ -5971,25 +6156,25 @@
         <v>3124170851.965993</v>
       </c>
       <c r="I26" s="7" t="n">
-        <v>0.0375</v>
+        <v>0.03650000241537366</v>
       </c>
       <c r="J26" s="7" t="n">
-        <v>0.0406125</v>
+        <v>0.03960950242261978</v>
       </c>
       <c r="K26" t="n">
         <v>4</v>
       </c>
       <c r="L26" s="7" t="n">
-        <v>0.0433</v>
+        <v>0.0362</v>
       </c>
       <c r="M26" s="7" t="n">
-        <v>0.0406125</v>
+        <v>0.03676825040376996</v>
       </c>
       <c r="N26" s="3" t="n">
-        <v>340762.7569524604</v>
+        <v>325009.2220334444</v>
       </c>
       <c r="O26" s="3" t="n">
-        <v>432812.6310396074</v>
+        <v>414829.2237389592</v>
       </c>
     </row>
     <row r="27">
@@ -6020,25 +6205,25 @@
         <v>3633642090.151248</v>
       </c>
       <c r="I27" s="7" t="n">
-        <v>0.0375</v>
+        <v>0.03650000241537366</v>
       </c>
       <c r="J27" s="7" t="n">
-        <v>0.0406125</v>
+        <v>0.03960950242261978</v>
       </c>
       <c r="K27" t="n">
         <v>4</v>
       </c>
       <c r="L27" s="7" t="n">
-        <v>0.0433</v>
+        <v>0.0362</v>
       </c>
       <c r="M27" s="7" t="n">
-        <v>0.0406125</v>
+        <v>0.03676825040376996</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>396332.3246676004</v>
+        <v>379232.6385937233</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>487588.0287219654</v>
+        <v>468277.7087264755</v>
       </c>
     </row>
     <row r="28">
@@ -6069,25 +6254,25 @@
         <v>3613109775.02256</v>
       </c>
       <c r="I28" s="7" t="n">
-        <v>0.0375</v>
+        <v>0.03650000241537366</v>
       </c>
       <c r="J28" s="7" t="n">
-        <v>0.0406125</v>
+        <v>0.03960950242261978</v>
       </c>
       <c r="K28" t="n">
         <v>4</v>
       </c>
       <c r="L28" s="7" t="n">
-        <v>0.0433</v>
+        <v>0.0362</v>
       </c>
       <c r="M28" s="7" t="n">
-        <v>0.0406125</v>
+        <v>0.03676825040376996</v>
       </c>
       <c r="N28" s="3" t="n">
-        <v>394092.8030020469</v>
+        <v>377047.368469083</v>
       </c>
       <c r="O28" s="3" t="n">
-        <v>485766.3668895173</v>
+        <v>466500.1759430798</v>
       </c>
     </row>
     <row r="29">
@@ -6118,25 +6303,25 @@
         <v>3628217354.598102</v>
       </c>
       <c r="I29" s="7" t="n">
-        <v>0.0375</v>
+        <v>0.03650000241537366</v>
       </c>
       <c r="J29" s="7" t="n">
-        <v>0.0406125</v>
+        <v>0.03960950242261978</v>
       </c>
       <c r="K29" t="n">
         <v>4</v>
       </c>
       <c r="L29" s="7" t="n">
-        <v>0.0433</v>
+        <v>0.0362</v>
       </c>
       <c r="M29" s="7" t="n">
-        <v>0.0406125</v>
+        <v>0.03676825040376996</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>395740.6323657326</v>
+        <v>378655.279807631</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>487787.8536450268</v>
+        <v>468472.6929685309</v>
       </c>
     </row>
     <row r="30">
@@ -6167,25 +6352,25 @@
         <v>3622578869.287579</v>
       </c>
       <c r="I30" s="7" t="n">
-        <v>0.0375</v>
+        <v>0.03650000241537366</v>
       </c>
       <c r="J30" s="7" t="n">
-        <v>0.0406125</v>
+        <v>0.03960950242261978</v>
       </c>
       <c r="K30" t="n">
         <v>4</v>
       </c>
       <c r="L30" s="7" t="n">
-        <v>0.0433</v>
+        <v>0.0362</v>
       </c>
       <c r="M30" s="7" t="n">
-        <v>0.0406125</v>
+        <v>0.03676825040376996</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>395125.6257318154</v>
+        <v>378055.1714701112</v>
       </c>
       <c r="O30" s="3" t="n">
-        <v>487521.6974699855</v>
+        <v>468212.9843232642</v>
       </c>
     </row>
     <row r="31">
@@ -6216,25 +6401,25 @@
         <v>3413429322.143122</v>
       </c>
       <c r="I31" s="7" t="n">
-        <v>0.0375</v>
+        <v>0.03600000425292382</v>
       </c>
       <c r="J31" s="7" t="n">
-        <v>0.0406125</v>
+        <v>0.03910800426568259</v>
       </c>
       <c r="K31" t="n">
         <v>4</v>
       </c>
       <c r="L31" s="7" t="n">
-        <v>0.0433</v>
+        <v>0.0362</v>
       </c>
       <c r="M31" s="7" t="n">
-        <v>0.0406125</v>
+        <v>0.03668466737761376</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>372313.0525156438</v>
+        <v>352383.5789754955</v>
       </c>
       <c r="O31" s="3" t="n">
-        <v>458234.2488764576</v>
+        <v>435181.9142288258</v>
       </c>
     </row>
     <row r="32">
@@ -6265,25 +6450,25 @@
         <v>3252967949.895449</v>
       </c>
       <c r="I32" s="7" t="n">
-        <v>0.0375</v>
+        <v>0.03600000425292382</v>
       </c>
       <c r="J32" s="7" t="n">
-        <v>0.0406125</v>
+        <v>0.03910800426568259</v>
       </c>
       <c r="K32" t="n">
         <v>4</v>
       </c>
       <c r="L32" s="7" t="n">
-        <v>0.0433</v>
+        <v>0.0362</v>
       </c>
       <c r="M32" s="7" t="n">
-        <v>0.0406125</v>
+        <v>0.03668466737761376</v>
       </c>
       <c r="N32" s="3" t="n">
-        <v>354811.0456849087</v>
+        <v>335517.6938324182</v>
       </c>
       <c r="O32" s="3" t="n">
-        <v>444044.9338222871</v>
+        <v>421508.318950465</v>
       </c>
     </row>
     <row r="33">
@@ -6314,25 +6499,25 @@
         <v>3221477558.745079</v>
       </c>
       <c r="I33" s="7" t="n">
-        <v>0.0375</v>
+        <v>0.03600000425292382</v>
       </c>
       <c r="J33" s="7" t="n">
-        <v>0.0406125</v>
+        <v>0.03910800426568259</v>
       </c>
       <c r="K33" t="n">
         <v>4</v>
       </c>
       <c r="L33" s="7" t="n">
-        <v>0.0433</v>
+        <v>0.0362</v>
       </c>
       <c r="M33" s="7" t="n">
-        <v>0.0406125</v>
+        <v>0.03668466737761376</v>
       </c>
       <c r="N33" s="3" t="n">
-        <v>351376.2935492632</v>
+        <v>332207.7799708258</v>
       </c>
       <c r="O33" s="3" t="n">
-        <v>445205.7569732065</v>
+        <v>422626.9512378465</v>
       </c>
     </row>
     <row r="34">
@@ -6363,25 +6548,25 @@
         <v>3246872717.915842</v>
       </c>
       <c r="I34" s="7" t="n">
-        <v>0.0375</v>
+        <v>0.03600000425292382</v>
       </c>
       <c r="J34" s="7" t="n">
-        <v>0.0406125</v>
+        <v>0.03910800426568259</v>
       </c>
       <c r="K34" t="n">
         <v>4</v>
       </c>
       <c r="L34" s="7" t="n">
-        <v>0.0433</v>
+        <v>0.0362</v>
       </c>
       <c r="M34" s="7" t="n">
-        <v>0.0406125</v>
+        <v>0.03668466737761376</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>354146.2203113768</v>
+        <v>334877.0319644032</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>453830.3612886349</v>
+        <v>430938.0887659761</v>
       </c>
     </row>
     <row r="35">
@@ -6412,25 +6597,25 @@
         <v>3224509478.620773</v>
       </c>
       <c r="I35" s="7" t="n">
-        <v>0.0375</v>
+        <v>0.03600000425292382</v>
       </c>
       <c r="J35" s="7" t="n">
-        <v>0.0406125</v>
+        <v>0.03910800426568259</v>
       </c>
       <c r="K35" t="n">
         <v>4</v>
       </c>
       <c r="L35" s="7" t="n">
-        <v>0.0433</v>
+        <v>0.0362</v>
       </c>
       <c r="M35" s="7" t="n">
-        <v>0.0406125</v>
+        <v>0.03668466737761376</v>
       </c>
       <c r="N35" s="3" t="n">
-        <v>351706.9942134252</v>
+        <v>332526.4611067913</v>
       </c>
       <c r="O35" s="3" t="n">
-        <v>450359.4957737069</v>
+        <v>427593.374089083</v>
       </c>
     </row>
     <row r="36">
@@ -6461,25 +6646,25 @@
         <v>3218414966.682919</v>
       </c>
       <c r="I36" s="7" t="n">
-        <v>0.0375</v>
+        <v>0.03600000425292382</v>
       </c>
       <c r="J36" s="7" t="n">
-        <v>0.0406125</v>
+        <v>0.03910800426568259</v>
       </c>
       <c r="K36" t="n">
         <v>4</v>
       </c>
       <c r="L36" s="7" t="n">
-        <v>0.0433</v>
+        <v>0.0362</v>
       </c>
       <c r="M36" s="7" t="n">
-        <v>0.0406125</v>
+        <v>0.03668466737761376</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>351042.2473770235</v>
+        <v>331885.8749214238</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>449041.8992520352</v>
+        <v>426323.6664598752</v>
       </c>
     </row>
     <row r="38">
@@ -6500,11 +6685,11 @@
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr"/>
       <c r="M38" t="inlineStr"/>
-      <c r="N38" s="11" t="n">
-        <v>11348183.48346371</v>
-      </c>
-      <c r="O38" s="11" t="n">
-        <v>13983245.54099589</v>
+      <c r="N38" s="12" t="n">
+        <v>10827488.55337466</v>
+      </c>
+      <c r="O38" s="12" t="n">
+        <v>13391864.98596525</v>
       </c>
     </row>
   </sheetData>

--- a/settlements/spark/2026-05/spark_settlement_may_2026.xlsx
+++ b/settlements/spark/2026-05/spark_settlement_may_2026.xlsx
@@ -529,7 +529,7 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>10320044.68562127</v>
+        <v>10642578.13467968</v>
       </c>
     </row>
     <row r="10">
@@ -545,7 +545,7 @@
     <row r="11">
       <c r="A11" t="inlineStr"/>
       <c r="B11" s="4" t="n">
-        <v>10360595.36983252</v>
+        <v>10683128.81889092</v>
       </c>
     </row>
     <row r="13">
@@ -567,7 +567,7 @@
         </is>
       </c>
       <c r="B14" s="3" t="n">
-        <v>10320044.68562127</v>
+        <v>10642578.13467968</v>
       </c>
     </row>
     <row r="15">
@@ -577,7 +577,7 @@
         </is>
       </c>
       <c r="B15" s="3" t="n">
-        <v>-3071820.300343978</v>
+        <v>-2749286.851285571</v>
       </c>
     </row>
     <row r="16">
@@ -625,13 +625,13 @@
         </is>
       </c>
       <c r="B22" s="3" t="n">
-        <v>-10320044.68562127</v>
+        <v>-10642578.13467968</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr"/>
       <c r="B23" s="4" t="n">
-        <v>1708588.925385048</v>
+        <v>1386055.476326641</v>
       </c>
     </row>
     <row r="25">
@@ -666,7 +666,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-06-23T21:47:21+00:00</t>
+          <t>2026-06-25T11:45:43+00:00</t>
         </is>
       </c>
     </row>
@@ -822,7 +822,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>sUSDS raw / POL (ALM — Cat B 4626, demand-side spread + agent rate)</t>
+          <t>sUSDS raw / POL (ALM — Cat B 4626, demand-side spread)</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -863,13 +863,13 @@
         <v>1</v>
       </c>
       <c r="N2" s="6" t="n">
-        <v>4201977.102126558</v>
+        <v>4330990.330089472</v>
       </c>
       <c r="O2" s="6" t="n">
-        <v>4201977.102126558</v>
+        <v>4330990.330089472</v>
       </c>
       <c r="P2" s="6" t="n">
-        <v>-367526.192997431</v>
+        <v>-496539.4209603447</v>
       </c>
       <c r="Q2" s="6" t="n">
         <v>0</v>
@@ -928,13 +928,13 @@
         <v>1</v>
       </c>
       <c r="N3" s="6" t="n">
-        <v>1485074.811632477</v>
+        <v>1530671.037066013</v>
       </c>
       <c r="O3" s="6" t="n">
-        <v>1485074.811632477</v>
+        <v>1530671.037066013</v>
       </c>
       <c r="P3" s="6" t="n">
-        <v>383037.3566035236</v>
+        <v>337441.1311699869</v>
       </c>
       <c r="Q3" s="6" t="n">
         <v>0</v>
@@ -993,13 +993,13 @@
         <v>1</v>
       </c>
       <c r="N4" s="6" t="n">
-        <v>1360656.659589858</v>
+        <v>1402432.876722047</v>
       </c>
       <c r="O4" s="6" t="n">
-        <v>1360656.659589858</v>
+        <v>1402432.876722047</v>
       </c>
       <c r="P4" s="6" t="n">
-        <v>1730923.340410141</v>
+        <v>1689147.123277953</v>
       </c>
       <c r="Q4" s="6" t="n">
         <v>0</v>
@@ -1058,13 +1058,13 @@
         <v>1</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>1193277.979442887</v>
+        <v>1229915.171946168</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>1193277.979442887</v>
+        <v>1229915.171946168</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>-1387722.42388684</v>
+        <v>-1424359.616390121</v>
       </c>
       <c r="Q5" s="6" t="n">
         <v>0</v>
@@ -1123,13 +1123,13 @@
         <v>1</v>
       </c>
       <c r="N6" s="6" t="n">
-        <v>396943.7786991677</v>
+        <v>409131.1364512742</v>
       </c>
       <c r="O6" s="6" t="n">
-        <v>396943.7786991677</v>
+        <v>409131.1364512742</v>
       </c>
       <c r="P6" s="6" t="n">
-        <v>162509.1605420516</v>
+        <v>150321.8027899452</v>
       </c>
       <c r="Q6" s="6" t="n">
         <v>86642406.62655522</v>
@@ -1192,13 +1192,13 @@
         <v>1</v>
       </c>
       <c r="N7" s="6" t="n">
-        <v>316867.5492018788</v>
+        <v>326596.3279090599</v>
       </c>
       <c r="O7" s="6" t="n">
-        <v>280402.7353600811</v>
+        <v>290131.5140672624</v>
       </c>
       <c r="P7" s="6" t="n">
-        <v>119175.4997131458</v>
+        <v>109446.7210059646</v>
       </c>
       <c r="Q7" s="6" t="n">
         <v>0</v>
@@ -1257,13 +1257,13 @@
         <v>1</v>
       </c>
       <c r="N8" s="6" t="n">
-        <v>232306.7400044638</v>
+        <v>239439.2496962347</v>
       </c>
       <c r="O8" s="6" t="n">
-        <v>232306.7400044638</v>
+        <v>239439.2496962347</v>
       </c>
       <c r="P8" s="6" t="n">
-        <v>191223.8685787379</v>
+        <v>184091.3588869669</v>
       </c>
       <c r="Q8" s="6" t="n">
         <v>0</v>
@@ -1322,13 +1322,13 @@
         <v>1</v>
       </c>
       <c r="N9" s="6" t="n">
-        <v>221078.0534762956</v>
+        <v>227865.8090060199</v>
       </c>
       <c r="O9" s="6" t="n">
-        <v>221078.0534762956</v>
+        <v>227865.8090060199</v>
       </c>
       <c r="P9" s="6" t="n">
-        <v>-192074.0827762955</v>
+        <v>-198861.8383060199</v>
       </c>
       <c r="Q9" s="6" t="n">
         <v>0</v>
@@ -1387,13 +1387,13 @@
         <v>1</v>
       </c>
       <c r="N10" s="6" t="n">
-        <v>221074.3932516124</v>
+        <v>227862.0364015236</v>
       </c>
       <c r="O10" s="6" t="n">
-        <v>221074.3932516124</v>
+        <v>227862.0364015236</v>
       </c>
       <c r="P10" s="6" t="n">
-        <v>-214688.5093799721</v>
+        <v>-221476.1525298833</v>
       </c>
       <c r="Q10" s="6" t="n">
         <v>0</v>
@@ -1452,13 +1452,13 @@
         <v>1</v>
       </c>
       <c r="N11" s="6" t="n">
-        <v>225589.9135205768</v>
+        <v>232516.1966087057</v>
       </c>
       <c r="O11" s="6" t="n">
-        <v>199629.2425025605</v>
+        <v>206555.5255906894</v>
       </c>
       <c r="P11" s="6" t="n">
-        <v>84845.51586862426</v>
+        <v>77919.23278049534</v>
       </c>
       <c r="Q11" s="6" t="n">
         <v>0</v>
@@ -1517,13 +1517,13 @@
         <v>1</v>
       </c>
       <c r="N12" s="6" t="n">
-        <v>198129.7460510709</v>
+        <v>204212.920107537</v>
       </c>
       <c r="O12" s="6" t="n">
-        <v>198129.7460510709</v>
+        <v>204212.920107537</v>
       </c>
       <c r="P12" s="6" t="n">
-        <v>19139.65039548748</v>
+        <v>13056.47633902135</v>
       </c>
       <c r="Q12" s="6" t="n">
         <v>0</v>
@@ -1582,13 +1582,13 @@
         <v>1</v>
       </c>
       <c r="N13" s="6" t="n">
-        <v>167517.0251579064</v>
+        <v>172660.297391215</v>
       </c>
       <c r="O13" s="6" t="n">
-        <v>148239.326469288</v>
+        <v>153382.5987025966</v>
       </c>
       <c r="P13" s="6" t="n">
-        <v>63004.00667073025</v>
+        <v>57860.73443742163</v>
       </c>
       <c r="Q13" s="6" t="n">
         <v>0</v>
@@ -1647,13 +1647,13 @@
         <v>1</v>
       </c>
       <c r="N14" s="6" t="n">
-        <v>127631.243737067</v>
+        <v>131549.9035353575</v>
       </c>
       <c r="O14" s="6" t="n">
-        <v>127631.243737067</v>
+        <v>131549.9035353575</v>
       </c>
       <c r="P14" s="6" t="n">
-        <v>166460.273139377</v>
+        <v>162541.6133410866</v>
       </c>
       <c r="Q14" s="6" t="n">
         <v>103099818.9104406</v>
@@ -1777,13 +1777,13 @@
         <v>1</v>
       </c>
       <c r="N16" s="6" t="n">
-        <v>65600.38921711374</v>
+        <v>67614.51679630503</v>
       </c>
       <c r="O16" s="6" t="n">
-        <v>65600.38921711374</v>
+        <v>67614.51679630503</v>
       </c>
       <c r="P16" s="6" t="n">
-        <v>54041.22870885887</v>
+        <v>52027.10112966759</v>
       </c>
       <c r="Q16" s="6" t="n">
         <v>0</v>
@@ -1911,13 +1911,13 @@
         <v>1</v>
       </c>
       <c r="N18" s="6" t="n">
-        <v>21037.96518888412</v>
+        <v>21683.89345855882</v>
       </c>
       <c r="O18" s="6" t="n">
-        <v>21037.96518888412</v>
+        <v>21683.89345855882</v>
       </c>
       <c r="P18" s="6" t="n">
-        <v>663.5063138134914</v>
+        <v>17.57804413878375</v>
       </c>
       <c r="Q18" s="6" t="n">
         <v>0</v>
@@ -1976,13 +1976,13 @@
         <v>1</v>
       </c>
       <c r="N19" s="6" t="n">
-        <v>20613.40597929416</v>
+        <v>21246.29901513504</v>
       </c>
       <c r="O19" s="6" t="n">
-        <v>20613.40597929416</v>
+        <v>21246.29901513504</v>
       </c>
       <c r="P19" s="6" t="n">
-        <v>11889.49737370584</v>
+        <v>11256.60433786496</v>
       </c>
       <c r="Q19" s="6" t="n">
         <v>0</v>
@@ -2041,13 +2041,13 @@
         <v>1</v>
       </c>
       <c r="N20" s="6" t="n">
-        <v>11051.67957157512</v>
+        <v>11390.99909219295</v>
       </c>
       <c r="O20" s="6" t="n">
-        <v>11051.67957157512</v>
+        <v>11390.99909219295</v>
       </c>
       <c r="P20" s="6" t="n">
-        <v>-11051.67957157289</v>
+        <v>-11390.99909219072</v>
       </c>
       <c r="Q20" s="6" t="n">
         <v>0</v>
@@ -2106,13 +2106,13 @@
         <v>1</v>
       </c>
       <c r="N21" s="6" t="n">
-        <v>11050.94983558513</v>
+        <v>11390.24695113189</v>
       </c>
       <c r="O21" s="6" t="n">
-        <v>11050.94983558513</v>
+        <v>11390.24695113189</v>
       </c>
       <c r="P21" s="6" t="n">
-        <v>-11050.94983558495</v>
+        <v>-11390.2469511317</v>
       </c>
       <c r="Q21" s="6" t="n">
         <v>0</v>
@@ -2171,13 +2171,13 @@
         <v>1</v>
       </c>
       <c r="N22" s="6" t="n">
-        <v>11048.90073814358</v>
+        <v>11388.13494028817</v>
       </c>
       <c r="O22" s="6" t="n">
-        <v>11048.90073814358</v>
+        <v>11388.13494028817</v>
       </c>
       <c r="P22" s="6" t="n">
-        <v>-11048.90073814358</v>
+        <v>-11388.13494028817</v>
       </c>
       <c r="Q22" s="6" t="n">
         <v>0</v>
@@ -2236,13 +2236,13 @@
         <v>1</v>
       </c>
       <c r="N23" s="6" t="n">
-        <v>10953.37754931583</v>
+        <v>11289.67890469889</v>
       </c>
       <c r="O23" s="6" t="n">
-        <v>10953.37754931583</v>
+        <v>11289.67890469889</v>
       </c>
       <c r="P23" s="6" t="n">
-        <v>-10953.37754931536</v>
+        <v>-11289.67890469842</v>
       </c>
       <c r="Q23" s="6" t="n">
         <v>0</v>
@@ -2301,13 +2301,13 @@
         <v>1</v>
       </c>
       <c r="N24" s="6" t="n">
-        <v>3298.551285694489</v>
+        <v>3399.826646941293</v>
       </c>
       <c r="O24" s="6" t="n">
-        <v>3298.551285694489</v>
+        <v>3399.826646941293</v>
       </c>
       <c r="P24" s="6" t="n">
-        <v>1506.336894450499</v>
+        <v>1405.061533203695</v>
       </c>
       <c r="Q24" s="6" t="n">
         <v>0</v>
@@ -2366,13 +2366,13 @@
         <v>1</v>
       </c>
       <c r="N25" s="6" t="n">
-        <v>2171.885738545533</v>
+        <v>2238.56910760877</v>
       </c>
       <c r="O25" s="6" t="n">
-        <v>1921.947209525445</v>
+        <v>1988.630578588682</v>
       </c>
       <c r="P25" s="6" t="n">
-        <v>816.8572921492586</v>
+        <v>750.1739230860217</v>
       </c>
       <c r="Q25" s="6" t="n">
         <v>0</v>
@@ -2431,13 +2431,13 @@
         <v>1</v>
       </c>
       <c r="N26" s="6" t="n">
-        <v>1.021736588487712</v>
+        <v>1.053106948726445</v>
       </c>
       <c r="O26" s="6" t="n">
-        <v>1.021736588487712</v>
+        <v>1.053106948726445</v>
       </c>
       <c r="P26" s="6" t="n">
-        <v>75.30872893071803</v>
+        <v>75.27735857047929</v>
       </c>
       <c r="Q26" s="6" t="n">
         <v>0</v>
@@ -2496,13 +2496,13 @@
         <v>1</v>
       </c>
       <c r="N27" s="6" t="n">
-        <v>0.8136591249146683</v>
+        <v>0.8386408865034203</v>
       </c>
       <c r="O27" s="6" t="n">
-        <v>0.8136591249146683</v>
+        <v>0.8386408865034203</v>
       </c>
       <c r="P27" s="6" t="n">
-        <v>0.3476861504231099</v>
+        <v>0.3227043888343578</v>
       </c>
       <c r="Q27" s="6" t="n">
         <v>0</v>
@@ -2561,13 +2561,13 @@
         <v>1</v>
       </c>
       <c r="N28" s="6" t="n">
-        <v>0.6276336001363896</v>
+        <v>0.6469038233583584</v>
       </c>
       <c r="O28" s="6" t="n">
-        <v>0.6276336001363896</v>
+        <v>0.6469038233583584</v>
       </c>
       <c r="P28" s="6" t="n">
-        <v>-0.6276336001363896</v>
+        <v>-0.6469038233583584</v>
       </c>
       <c r="Q28" s="6" t="n">
         <v>0</v>
@@ -2626,13 +2626,13 @@
         <v>1</v>
       </c>
       <c r="N29" s="6" t="n">
-        <v>0.2549255583596232</v>
+        <v>0.2627525332276154</v>
       </c>
       <c r="O29" s="6" t="n">
-        <v>0.2549255583596232</v>
+        <v>0.2627525332276154</v>
       </c>
       <c r="P29" s="6" t="n">
-        <v>-0.254925558690082</v>
+        <v>-0.2627525335580742</v>
       </c>
       <c r="Q29" s="6" t="n">
         <v>0</v>
@@ -2691,13 +2691,13 @@
         <v>1</v>
       </c>
       <c r="N30" s="6" t="n">
-        <v>0.2199752046855565</v>
+        <v>0.2267290994685442</v>
       </c>
       <c r="O30" s="6" t="n">
-        <v>0.2199752046855565</v>
+        <v>0.2267290994685442</v>
       </c>
       <c r="P30" s="6" t="n">
-        <v>0.09178834374856962</v>
+        <v>0.08503444896558193</v>
       </c>
       <c r="Q30" s="6" t="n">
         <v>0</v>
@@ -2756,13 +2756,13 @@
         <v>1</v>
       </c>
       <c r="N31" s="6" t="n">
-        <v>0.04843062927302642</v>
+        <v>0.04991759401912802</v>
       </c>
       <c r="O31" s="6" t="n">
-        <v>0.04843062927302642</v>
+        <v>0.04991759401912802</v>
       </c>
       <c r="P31" s="6" t="n">
-        <v>-0.04842457556585644</v>
+        <v>-0.04991154031195803</v>
       </c>
       <c r="Q31" s="6" t="n">
         <v>0</v>
@@ -2821,13 +2821,13 @@
         <v>1</v>
       </c>
       <c r="N32" s="6" t="n">
-        <v>0.01303887283483027</v>
+        <v>0.01343920511473919</v>
       </c>
       <c r="O32" s="6" t="n">
-        <v>0.01303887283483027</v>
+        <v>0.01343920511473919</v>
       </c>
       <c r="P32" s="6" t="n">
-        <v>0.002351127165169734</v>
+        <v>0.001950794885260815</v>
       </c>
       <c r="Q32" s="6" t="n">
         <v>0</v>
@@ -2886,13 +2886,13 @@
         <v>1</v>
       </c>
       <c r="N33" s="6" t="n">
-        <v>0.003416997329097425</v>
+        <v>0.003521909337100613</v>
       </c>
       <c r="O33" s="6" t="n">
-        <v>0.003416997329097425</v>
+        <v>0.003521909337100613</v>
       </c>
       <c r="P33" s="6" t="n">
-        <v>8.466972002670902</v>
+        <v>8.4668670906629</v>
       </c>
       <c r="Q33" s="6" t="n">
         <v>0</v>
@@ -2951,13 +2951,13 @@
         <v>1</v>
       </c>
       <c r="N34" s="6" t="n">
-        <v>0.0003414125529353442</v>
+        <v>0.0003518949364540351</v>
       </c>
       <c r="O34" s="6" t="n">
-        <v>0.0003414125529353442</v>
+        <v>0.0003518949364540351</v>
       </c>
       <c r="P34" s="6" t="n">
-        <v>0.0003925874470646558</v>
+        <v>0.0003821050635459649</v>
       </c>
       <c r="Q34" s="6" t="n">
         <v>0</v>
@@ -3016,13 +3016,13 @@
         <v>1</v>
       </c>
       <c r="N35" s="6" t="n">
-        <v>0.000127745346117444</v>
+        <v>0.0001316675091990825</v>
       </c>
       <c r="O35" s="6" t="n">
-        <v>0.000127745346117444</v>
+        <v>0.0001316675091990825</v>
       </c>
       <c r="P35" s="6" t="n">
-        <v>5.825465388255599e-05</v>
+        <v>5.433249080091749e-05</v>
       </c>
       <c r="Q35" s="6" t="n">
         <v>0</v>
@@ -3081,13 +3081,13 @@
         <v>1</v>
       </c>
       <c r="N36" s="6" t="n">
-        <v>1.402959289862589e-05</v>
+        <v>1.446034323896955e-05</v>
       </c>
       <c r="O36" s="6" t="n">
-        <v>1.402959289862589e-05</v>
+        <v>1.446034323896955e-05</v>
       </c>
       <c r="P36" s="6" t="n">
-        <v>2.970407101374112e-06</v>
+        <v>2.539656761030448e-06</v>
       </c>
       <c r="Q36" s="6" t="n">
         <v>0</v>
@@ -3146,13 +3146,13 @@
         <v>1</v>
       </c>
       <c r="N37" s="6" t="n">
-        <v>1.269933079869646e-05</v>
+        <v>1.308923812553066e-05</v>
       </c>
       <c r="O37" s="6" t="n">
-        <v>1.269933079869646e-05</v>
+        <v>1.308923812553066e-05</v>
       </c>
       <c r="P37" s="6" t="n">
-        <v>-1.055550629332646e-05</v>
+        <v>-1.094541362016066e-05</v>
       </c>
       <c r="Q37" s="6" t="n">
         <v>0</v>
@@ -3211,13 +3211,13 @@
         <v>1</v>
       </c>
       <c r="N38" s="6" t="n">
-        <v>3.758321450939806e-06</v>
+        <v>3.873713127363416e-06</v>
       </c>
       <c r="O38" s="6" t="n">
-        <v>3.758321450939806e-06</v>
+        <v>3.873713127363416e-06</v>
       </c>
       <c r="P38" s="6" t="n">
-        <v>1.241678549060194e-06</v>
+        <v>1.126286872636584e-06</v>
       </c>
       <c r="Q38" s="6" t="n">
         <v>0</v>
@@ -3276,13 +3276,13 @@
         <v>1</v>
       </c>
       <c r="N39" s="6" t="n">
-        <v>2.741683716144822e-06</v>
+        <v>2.825861582343615e-06</v>
       </c>
       <c r="O39" s="6" t="n">
-        <v>2.741683716144822e-06</v>
+        <v>2.825861582343615e-06</v>
       </c>
       <c r="P39" s="6" t="n">
-        <v>-2.741683716144822e-06</v>
+        <v>-2.825861582343615e-06</v>
       </c>
       <c r="Q39" s="6" t="n">
         <v>0</v>
@@ -3341,13 +3341,13 @@
         <v>1</v>
       </c>
       <c r="N40" s="6" t="n">
-        <v>1.151741067414945e-06</v>
+        <v>1.18710295284965e-06</v>
       </c>
       <c r="O40" s="6" t="n">
-        <v>1.151741067414945e-06</v>
+        <v>1.18710295284965e-06</v>
       </c>
       <c r="P40" s="6" t="n">
-        <v>-4.450342606059448e-07</v>
+        <v>-4.8039614604065e-07</v>
       </c>
       <c r="Q40" s="6" t="n">
         <v>0</v>
@@ -3406,13 +3406,13 @@
         <v>1</v>
       </c>
       <c r="N41" s="6" t="n">
-        <v>1.6557898841307e-07</v>
+        <v>1.706627571387951e-07</v>
       </c>
       <c r="O41" s="6" t="n">
-        <v>1.6557898841307e-07</v>
+        <v>1.706627571387951e-07</v>
       </c>
       <c r="P41" s="6" t="n">
-        <v>-1.6557898841307e-07</v>
+        <v>-1.706627571387951e-07</v>
       </c>
       <c r="Q41" s="6" t="n">
         <v>0</v>
@@ -4678,7 +4678,7 @@
         </is>
       </c>
       <c r="B24" s="3" t="n">
-        <v>10320044.68562127</v>
+        <v>10642578.13467968</v>
       </c>
     </row>
     <row r="25">
@@ -4698,7 +4698,7 @@
         </is>
       </c>
       <c r="B26" s="3" t="n">
-        <v>10360595.36983252</v>
+        <v>10683128.81889092</v>
       </c>
     </row>
     <row r="28">
@@ -4725,7 +4725,7 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>10320044.68562127</v>
+        <v>10642578.13467968</v>
       </c>
     </row>
     <row r="32">
@@ -4735,7 +4735,7 @@
         </is>
       </c>
       <c r="B32" s="3" t="n">
-        <v>-3071820.300343978</v>
+        <v>-2749286.851285571</v>
       </c>
     </row>
     <row r="33" ht="60" customHeight="1">

--- a/settlements/spark/2026-05/spark_settlement_may_2026.xlsx
+++ b/settlements/spark/2026-05/spark_settlement_may_2026.xlsx
@@ -666,7 +666,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-06-25T11:45:43+00:00</t>
+          <t>2026-06-25T22:38:11+00:00</t>
         </is>
       </c>
     </row>

--- a/settlements/spark/2026-05/spark_settlement_may_2026.xlsx
+++ b/settlements/spark/2026-05/spark_settlement_may_2026.xlsx
@@ -458,7 +458,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B28"/>
+  <dimension ref="A1:B29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -505,178 +505,188 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr"/>
-      <c r="B6" s="4" t="n">
-        <v>13527522.92185785</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>+ distribution_rewards (settle-dr-dune)</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="n">
+        <v>1622762.97</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr"/>
+      <c r="B7" s="4" t="n">
+        <v>15150285.89185784</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>Sky side</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>CoF on utilized (BR × Net_Subs)</t>
-        </is>
-      </c>
-      <c r="B9" s="3" t="n">
-        <v>10642578.13467968</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>CoF on utilized (BR × Net_Subs)</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="n">
+        <v>10642578.13467968</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>+ SDE revenue (Sky-Direct, full to Sky)</t>
         </is>
       </c>
-      <c r="B10" s="3" t="n">
+      <c r="B11" s="3" t="n">
         <v>40550.6842112442</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr"/>
-      <c r="B11" s="4" t="n">
+    <row r="12">
+      <c r="A12" t="inlineStr"/>
+      <c r="B12" s="4" t="n">
         <v>10683128.81889092</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>Sky Revenue (max) — BR × full ilk debt, no deductions</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>CoF on Net_Subs (actual BR × utilized)</t>
-        </is>
-      </c>
-      <c r="B14" s="3" t="n">
-        <v>10642578.13467968</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>CoF on Net_Subs (actual BR × utilized)</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="n">
+        <v>10642578.13467968</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
           <t>reduction from idle/SDE deductions</t>
         </is>
       </c>
-      <c r="B15" s="3" t="n">
+      <c r="B16" s="3" t="n">
         <v>-2749286.851285571</v>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" t="inlineStr"/>
-      <c r="B16" s="4" t="n">
+    <row r="17">
+      <c r="A17" t="inlineStr"/>
+      <c r="B17" s="4" t="n">
         <v>13391864.98596525</v>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="5" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
         <is>
           <t>sUSDS spread (Curve LP + PSM3) — deducted from sky_revenue</t>
         </is>
       </c>
-      <c r="B18" s="3" t="n">
+      <c r="B19" s="3" t="n">
         <v>184910.418694979</v>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
         <is>
           <t>Comparison (Grove-style "Profit to Grove")</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
+      <c r="B21" s="2" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>prime_agent_revenue</t>
-        </is>
-      </c>
-      <c r="B21" s="3" t="n">
-        <v>13408944.7424591</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
+          <t>prime_agent_revenue</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="n">
+        <v>13408944.7424591</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
           <t>− CoF (deducted per-venue in display)</t>
         </is>
       </c>
-      <c r="B22" s="3" t="n">
+      <c r="B23" s="3" t="n">
         <v>-10642578.13467968</v>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" t="inlineStr"/>
-      <c r="B23" s="4" t="n">
+    <row r="24">
+      <c r="A24" t="inlineStr"/>
+      <c r="B24" s="4" t="n">
         <v>1386055.476326641</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Period</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>2026-05-01 → 2026-05-31 (31 days)</t>
-        </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Pin blocks</t>
+          <t>Period</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>arbitrum=468748167, avalanche_c=86865826, base=46741326, ethereum=25218797, optimism=152336611, unichain=49523640</t>
+          <t>2026-05-01 → 2026-05-31 (31 days)</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Generated</t>
+          <t>Pin blocks</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-06-25T22:38:11+00:00</t>
+          <t>arbitrum=468748167, avalanche_c=86865826, base=46741326, ethereum=25218797, optimism=152336611, unichain=49523640</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
+          <t>Generated</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2026-06-25T22:38:11+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
           <t>Pipeline</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B29" t="inlineStr">
         <is>
           <t>0.1.0</t>
         </is>

--- a/settlements/spark/2026-05/spark_settlement_may_2026.xlsx
+++ b/settlements/spark/2026-05/spark_settlement_may_2026.xlsx
@@ -458,7 +458,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B28"/>
+  <dimension ref="A1:B29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -505,178 +505,188 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr"/>
-      <c r="B6" s="4" t="n">
-        <v>13527522.92185785</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>+ distribution_rewards (settle-dr-dune)</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="n">
+        <v>1622762.97</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr"/>
+      <c r="B7" s="4" t="n">
+        <v>15150285.89185784</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>Sky side</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>CoF on utilized (BR × Net_Subs)</t>
-        </is>
-      </c>
-      <c r="B9" s="3" t="n">
-        <v>10642578.13467968</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>CoF on utilized (BR × Net_Subs)</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="n">
+        <v>10642578.13467968</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>+ SDE revenue (Sky-Direct, full to Sky)</t>
         </is>
       </c>
-      <c r="B10" s="3" t="n">
+      <c r="B11" s="3" t="n">
         <v>40550.6842112442</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr"/>
-      <c r="B11" s="4" t="n">
+    <row r="12">
+      <c r="A12" t="inlineStr"/>
+      <c r="B12" s="4" t="n">
         <v>10683128.81889092</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>Sky Revenue (max) — BR × full ilk debt, no deductions</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>CoF on Net_Subs (actual BR × utilized)</t>
-        </is>
-      </c>
-      <c r="B14" s="3" t="n">
-        <v>10642578.13467968</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>CoF on Net_Subs (actual BR × utilized)</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="n">
+        <v>10642578.13467968</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
           <t>reduction from idle/SDE deductions</t>
         </is>
       </c>
-      <c r="B15" s="3" t="n">
+      <c r="B16" s="3" t="n">
         <v>-2749286.851285571</v>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" t="inlineStr"/>
-      <c r="B16" s="4" t="n">
+    <row r="17">
+      <c r="A17" t="inlineStr"/>
+      <c r="B17" s="4" t="n">
         <v>13391864.98596525</v>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="5" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
         <is>
           <t>sUSDS spread (Curve LP + PSM3) — deducted from sky_revenue</t>
         </is>
       </c>
-      <c r="B18" s="3" t="n">
+      <c r="B19" s="3" t="n">
         <v>184910.418694979</v>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
         <is>
           <t>Comparison (Grove-style "Profit to Grove")</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
+      <c r="B21" s="2" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>prime_agent_revenue</t>
-        </is>
-      </c>
-      <c r="B21" s="3" t="n">
-        <v>13408944.7424591</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
+          <t>prime_agent_revenue</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="n">
+        <v>13408944.7424591</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
           <t>− CoF (deducted per-venue in display)</t>
         </is>
       </c>
-      <c r="B22" s="3" t="n">
+      <c r="B23" s="3" t="n">
         <v>-10642578.13467968</v>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" t="inlineStr"/>
-      <c r="B23" s="4" t="n">
+    <row r="24">
+      <c r="A24" t="inlineStr"/>
+      <c r="B24" s="4" t="n">
         <v>1386055.476326641</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Period</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>2026-05-01 → 2026-05-31 (31 days)</t>
-        </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Pin blocks</t>
+          <t>Period</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>arbitrum=468748167, avalanche_c=86865826, base=46741326, ethereum=25218797, optimism=152336611, unichain=49523640</t>
+          <t>2026-05-01 → 2026-05-31 (31 days)</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Generated</t>
+          <t>Pin blocks</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-06-25T11:45:43+00:00</t>
+          <t>arbitrum=468748167, avalanche_c=86865826, base=46741326, ethereum=25218797, optimism=152336611, unichain=49523640</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
+          <t>Generated</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2026-06-25T22:38:11+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
           <t>Pipeline</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B29" t="inlineStr">
         <is>
           <t>0.1.0</t>
         </is>

--- a/settlements/spark/2026-05/spark_settlement_may_2026.xlsx
+++ b/settlements/spark/2026-05/spark_settlement_may_2026.xlsx
@@ -511,13 +511,13 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>1622762.97</v>
+        <v>1632540.8</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr"/>
       <c r="B7" s="4" t="n">
-        <v>15150285.89185784</v>
+        <v>15160063.72185784</v>
       </c>
     </row>
     <row r="9">

--- a/settlements/spark/2026-05/spark_settlement_may_2026.xlsx
+++ b/settlements/spark/2026-05/spark_settlement_may_2026.xlsx
@@ -491,7 +491,7 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>13408944.7424591</v>
+        <v>13408944.74245897</v>
       </c>
     </row>
     <row r="5">
@@ -517,7 +517,7 @@
     <row r="7">
       <c r="A7" t="inlineStr"/>
       <c r="B7" s="4" t="n">
-        <v>15160063.72185784</v>
+        <v>15160063.72185771</v>
       </c>
     </row>
     <row r="9">
@@ -625,7 +625,7 @@
         </is>
       </c>
       <c r="B22" s="3" t="n">
-        <v>13408944.7424591</v>
+        <v>13408944.74245897</v>
       </c>
     </row>
     <row r="23">
@@ -641,7 +641,7 @@
     <row r="24">
       <c r="A24" t="inlineStr"/>
       <c r="B24" s="4" t="n">
-        <v>1386055.476326641</v>
+        <v>1386055.476326505</v>
       </c>
     </row>
     <row r="26">
@@ -676,7 +676,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-06-25T22:38:11+00:00</t>
+          <t>2026-07-03T07:25:43+00:00</t>
         </is>
       </c>
     </row>
@@ -855,13 +855,13 @@
         <v>-145686527.279134</v>
       </c>
       <c r="H2" s="6" t="n">
-        <v>3834450.909129127</v>
+        <v>3834450.909129192</v>
       </c>
       <c r="I2" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J2" s="6" t="n">
-        <v>3834450.909129127</v>
+        <v>3834450.909129192</v>
       </c>
       <c r="K2" s="6" t="n">
         <v>0</v>
@@ -879,7 +879,7 @@
         <v>4330990.330089472</v>
       </c>
       <c r="P2" s="6" t="n">
-        <v>-496539.4209603447</v>
+        <v>-496539.4209602798</v>
       </c>
       <c r="Q2" s="6" t="n">
         <v>0</v>
@@ -985,13 +985,13 @@
         <v>-414722895.155028</v>
       </c>
       <c r="H4" s="6" t="n">
-        <v>3091580</v>
+        <v>3091579.99999999</v>
       </c>
       <c r="I4" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J4" s="6" t="n">
-        <v>3091580</v>
+        <v>3091579.99999999</v>
       </c>
       <c r="K4" s="6" t="n">
         <v>0</v>
@@ -1009,7 +1009,7 @@
         <v>1402432.876722047</v>
       </c>
       <c r="P4" s="6" t="n">
-        <v>1689147.123277953</v>
+        <v>1689147.123277943</v>
       </c>
       <c r="Q4" s="6" t="n">
         <v>0</v>
@@ -1050,13 +1050,13 @@
         <v>125242118.592976</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>-194444.4444439532</v>
+        <v>-194444.4444439746</v>
       </c>
       <c r="I5" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>-194444.4444439532</v>
+        <v>-194444.4444439746</v>
       </c>
       <c r="K5" s="6" t="n">
         <v>0</v>
@@ -1074,7 +1074,7 @@
         <v>1229915.171946168</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>-1424359.616390121</v>
+        <v>-1424359.616390143</v>
       </c>
       <c r="Q5" s="6" t="n">
         <v>0</v>
@@ -1139,7 +1139,7 @@
         <v>409131.1364512742</v>
       </c>
       <c r="P6" s="6" t="n">
-        <v>150321.8027899452</v>
+        <v>150321.8027899451</v>
       </c>
       <c r="Q6" s="6" t="n">
         <v>86642406.62655522</v>
@@ -1509,19 +1509,19 @@
         <v>20232922.14688502</v>
       </c>
       <c r="H12" s="6" t="n">
-        <v>217269.3964465584</v>
+        <v>217269.396446639</v>
       </c>
       <c r="I12" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J12" s="6" t="n">
-        <v>217269.3964465584</v>
+        <v>217269.396446639</v>
       </c>
       <c r="K12" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L12" s="6" t="n">
-        <v>89619946.74579927</v>
+        <v>89619946.74579926</v>
       </c>
       <c r="M12" s="7" t="n">
         <v>1</v>
@@ -1533,7 +1533,7 @@
         <v>204212.920107537</v>
       </c>
       <c r="P12" s="6" t="n">
-        <v>13056.47633902135</v>
+        <v>13056.47633910202</v>
       </c>
       <c r="Q12" s="6" t="n">
         <v>0</v>
@@ -1663,7 +1663,7 @@
         <v>131549.9035353575</v>
       </c>
       <c r="P14" s="6" t="n">
-        <v>162541.6133410866</v>
+        <v>162541.6133410865</v>
       </c>
       <c r="Q14" s="6" t="n">
         <v>103099818.9104406</v>
@@ -1921,13 +1921,13 @@
         <v>1</v>
       </c>
       <c r="N18" s="6" t="n">
-        <v>21683.89345855882</v>
+        <v>21683.89345855883</v>
       </c>
       <c r="O18" s="6" t="n">
-        <v>21683.89345855882</v>
+        <v>21683.89345855883</v>
       </c>
       <c r="P18" s="6" t="n">
-        <v>17.57804413878375</v>
+        <v>17.57804413878301</v>
       </c>
       <c r="Q18" s="6" t="n">
         <v>0</v>
@@ -1986,10 +1986,10 @@
         <v>1</v>
       </c>
       <c r="N19" s="6" t="n">
-        <v>21246.29901513504</v>
+        <v>21246.29901513505</v>
       </c>
       <c r="O19" s="6" t="n">
-        <v>21246.29901513504</v>
+        <v>21246.29901513505</v>
       </c>
       <c r="P19" s="6" t="n">
         <v>11256.60433786496</v>
@@ -2033,31 +2033,31 @@
         <v>-2423.291386</v>
       </c>
       <c r="H20" s="6" t="n">
-        <v>2.228968e-09</v>
+        <v>-9.21792e-10</v>
       </c>
       <c r="I20" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J20" s="6" t="n">
-        <v>2.228968e-09</v>
+        <v>-9.21792e-10</v>
       </c>
       <c r="K20" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L20" s="6" t="n">
-        <v>4999001.686505451</v>
+        <v>4999001.686505452</v>
       </c>
       <c r="M20" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N20" s="6" t="n">
-        <v>11390.99909219295</v>
+        <v>11390.99909219296</v>
       </c>
       <c r="O20" s="6" t="n">
-        <v>11390.99909219295</v>
+        <v>11390.99909219296</v>
       </c>
       <c r="P20" s="6" t="n">
-        <v>-11390.99909219072</v>
+        <v>-11390.99909219388</v>
       </c>
       <c r="Q20" s="6" t="n">
         <v>0</v>
@@ -2122,7 +2122,7 @@
         <v>11390.24695113189</v>
       </c>
       <c r="P21" s="6" t="n">
-        <v>-11390.2469511317</v>
+        <v>-11390.24695113171</v>
       </c>
       <c r="Q21" s="6" t="n">
         <v>0</v>
@@ -2228,13 +2228,13 @@
         <v>-34185.096267</v>
       </c>
       <c r="H23" s="6" t="n">
-        <v>4.7e-10</v>
+        <v>5.4e-10</v>
       </c>
       <c r="I23" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J23" s="6" t="n">
-        <v>4.7e-10</v>
+        <v>5.4e-10</v>
       </c>
       <c r="K23" s="6" t="n">
         <v>0</v>
@@ -2252,7 +2252,7 @@
         <v>11289.67890469889</v>
       </c>
       <c r="P23" s="6" t="n">
-        <v>-11289.67890469842</v>
+        <v>-11289.67890469835</v>
       </c>
       <c r="Q23" s="6" t="n">
         <v>0</v>
@@ -2293,31 +2293,31 @@
         <v>2796996.33696637</v>
       </c>
       <c r="H24" s="6" t="n">
-        <v>4804.888180144989</v>
+        <v>4804.88818014498</v>
       </c>
       <c r="I24" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J24" s="6" t="n">
-        <v>4804.888180144989</v>
+        <v>4804.88818014498</v>
       </c>
       <c r="K24" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L24" s="6" t="n">
-        <v>1492032.349781685</v>
+        <v>1492032.349781683</v>
       </c>
       <c r="M24" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N24" s="6" t="n">
-        <v>3399.826646941293</v>
+        <v>3399.826646941288</v>
       </c>
       <c r="O24" s="6" t="n">
-        <v>3399.826646941293</v>
+        <v>3399.826646941288</v>
       </c>
       <c r="P24" s="6" t="n">
-        <v>1405.061533203695</v>
+        <v>1405.061533203692</v>
       </c>
       <c r="Q24" s="6" t="n">
         <v>0</v>
@@ -2488,31 +2488,31 @@
         <v>200.1934724172377</v>
       </c>
       <c r="H27" s="6" t="n">
-        <v>1.161345275337778</v>
+        <v>1.161345275089762</v>
       </c>
       <c r="I27" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J27" s="6" t="n">
-        <v>1.161345275337778</v>
+        <v>1.161345275089762</v>
       </c>
       <c r="K27" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L27" s="6" t="n">
-        <v>368.0420981576889</v>
+        <v>368.042098157809</v>
       </c>
       <c r="M27" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N27" s="6" t="n">
-        <v>0.8386408865034203</v>
+        <v>0.8386408865036938</v>
       </c>
       <c r="O27" s="6" t="n">
-        <v>0.8386408865034203</v>
+        <v>0.8386408865036938</v>
       </c>
       <c r="P27" s="6" t="n">
-        <v>0.3227043888343578</v>
+        <v>0.3227043885860684</v>
       </c>
       <c r="Q27" s="6" t="n">
         <v>0</v>
@@ -2707,7 +2707,7 @@
         <v>0.2267290994685442</v>
       </c>
       <c r="P30" s="6" t="n">
-        <v>0.08503444896558193</v>
+        <v>0.08503444896558192</v>
       </c>
       <c r="Q30" s="6" t="n">
         <v>0</v>
@@ -2837,7 +2837,7 @@
         <v>0.01343920511473919</v>
       </c>
       <c r="P32" s="6" t="n">
-        <v>0.001950794885260815</v>
+        <v>0.001950794885260814</v>
       </c>
       <c r="Q32" s="6" t="n">
         <v>0</v>
@@ -3727,13 +3727,13 @@
         <v>0</v>
       </c>
       <c r="H46" s="6" t="n">
-        <v>891780.2799998709</v>
+        <v>891780.2799998628</v>
       </c>
       <c r="I46" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J46" s="6" t="n">
-        <v>891780.2799998709</v>
+        <v>891780.2799998628</v>
       </c>
       <c r="K46" s="6" t="n">
         <v>0</v>
@@ -3751,7 +3751,7 @@
         <v>0</v>
       </c>
       <c r="P46" s="6" t="n">
-        <v>891780.2799998709</v>
+        <v>891780.2799998628</v>
       </c>
       <c r="Q46" s="6" t="n">
         <v>0</v>
@@ -3792,13 +3792,13 @@
         <v>0</v>
       </c>
       <c r="H47" s="6" t="n">
-        <v>8.19007e-07</v>
+        <v>7.850176e-07</v>
       </c>
       <c r="I47" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J47" s="6" t="n">
-        <v>8.19007e-07</v>
+        <v>7.850176e-07</v>
       </c>
       <c r="K47" s="6" t="n">
         <v>0</v>
@@ -3816,7 +3816,7 @@
         <v>0</v>
       </c>
       <c r="P47" s="6" t="n">
-        <v>8.19007e-07</v>
+        <v>7.850176e-07</v>
       </c>
       <c r="Q47" s="6" t="n">
         <v>0</v>
@@ -3857,19 +3857,19 @@
         <v>0</v>
       </c>
       <c r="H48" s="6" t="n">
-        <v>-2.5155451e-06</v>
+        <v>-2.7208051e-06</v>
       </c>
       <c r="I48" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J48" s="6" t="n">
-        <v>-2.5155451e-06</v>
+        <v>-2.7208051e-06</v>
       </c>
       <c r="K48" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L48" s="6" t="n">
-        <v>17.83075712531922</v>
+        <v>17.83075728228825</v>
       </c>
       <c r="M48" s="7" t="n">
         <v>0</v>
@@ -3881,7 +3881,7 @@
         <v>0</v>
       </c>
       <c r="P48" s="6" t="n">
-        <v>-2.5155451e-06</v>
+        <v>-2.7208051e-06</v>
       </c>
       <c r="Q48" s="6" t="n">
         <v>0</v>

--- a/settlements/spark/2026-05/spark_settlement_may_2026.xlsx
+++ b/settlements/spark/2026-05/spark_settlement_may_2026.xlsx
@@ -539,7 +539,7 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>10642578.13467968</v>
+        <v>10640588.58756836</v>
       </c>
     </row>
     <row r="11">
@@ -549,13 +549,13 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>40550.6842112442</v>
+        <v>40533.95751528406</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr"/>
       <c r="B12" s="4" t="n">
-        <v>10683128.81889092</v>
+        <v>10681122.54508365</v>
       </c>
     </row>
     <row r="14">
@@ -577,7 +577,7 @@
         </is>
       </c>
       <c r="B15" s="3" t="n">
-        <v>10642578.13467968</v>
+        <v>10640588.58756836</v>
       </c>
     </row>
     <row r="16">
@@ -587,7 +587,7 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>-2749286.851285571</v>
+        <v>-2751276.398396889</v>
       </c>
     </row>
     <row r="17">
@@ -635,13 +635,13 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>-10642578.13467968</v>
+        <v>-10640588.58756836</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr"/>
       <c r="B24" s="4" t="n">
-        <v>1386055.476326505</v>
+        <v>1388045.023437823</v>
       </c>
     </row>
     <row r="26">
@@ -676,7 +676,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-07-03T07:25:43+00:00</t>
+          <t>2026-07-07T00:55:42+00:00</t>
         </is>
       </c>
     </row>
@@ -703,7 +703,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S62"/>
+  <dimension ref="A1:S64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -873,13 +873,13 @@
         <v>1</v>
       </c>
       <c r="N2" s="6" t="n">
-        <v>4330990.330089472</v>
+        <v>4330194.512180462</v>
       </c>
       <c r="O2" s="6" t="n">
-        <v>4330990.330089472</v>
+        <v>4330194.512180462</v>
       </c>
       <c r="P2" s="6" t="n">
-        <v>-496539.4209602798</v>
+        <v>-495743.6030512699</v>
       </c>
       <c r="Q2" s="6" t="n">
         <v>0</v>
@@ -938,13 +938,13 @@
         <v>1</v>
       </c>
       <c r="N3" s="6" t="n">
-        <v>1530671.037066013</v>
+        <v>1530389.776815756</v>
       </c>
       <c r="O3" s="6" t="n">
-        <v>1530671.037066013</v>
+        <v>1530389.776815756</v>
       </c>
       <c r="P3" s="6" t="n">
-        <v>337441.1311699869</v>
+        <v>337722.3914202435</v>
       </c>
       <c r="Q3" s="6" t="n">
         <v>0</v>
@@ -1003,13 +1003,13 @@
         <v>1</v>
       </c>
       <c r="N4" s="6" t="n">
-        <v>1402432.876722047</v>
+        <v>1402175.18018744</v>
       </c>
       <c r="O4" s="6" t="n">
-        <v>1402432.876722047</v>
+        <v>1402175.18018744</v>
       </c>
       <c r="P4" s="6" t="n">
-        <v>1689147.123277943</v>
+        <v>1689404.81981255</v>
       </c>
       <c r="Q4" s="6" t="n">
         <v>0</v>
@@ -1068,13 +1068,13 @@
         <v>1</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>1229915.171946168</v>
+        <v>1229689.175477509</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>1229915.171946168</v>
+        <v>1229689.175477509</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>-1424359.616390143</v>
+        <v>-1424133.619921484</v>
       </c>
       <c r="Q5" s="6" t="n">
         <v>0</v>
@@ -1133,13 +1133,13 @@
         <v>1</v>
       </c>
       <c r="N6" s="6" t="n">
-        <v>409131.1364512742</v>
+        <v>409055.9587527096</v>
       </c>
       <c r="O6" s="6" t="n">
-        <v>409131.1364512742</v>
+        <v>409055.9587527096</v>
       </c>
       <c r="P6" s="6" t="n">
-        <v>150321.8027899451</v>
+        <v>150396.9804885097</v>
       </c>
       <c r="Q6" s="6" t="n">
         <v>86642406.62655522</v>
@@ -1202,13 +1202,13 @@
         <v>1</v>
       </c>
       <c r="N7" s="6" t="n">
-        <v>326596.3279090599</v>
+        <v>326536.3159517574</v>
       </c>
       <c r="O7" s="6" t="n">
-        <v>290131.5140672624</v>
+        <v>290071.5021099598</v>
       </c>
       <c r="P7" s="6" t="n">
-        <v>109446.7210059646</v>
+        <v>109506.7329632671</v>
       </c>
       <c r="Q7" s="6" t="n">
         <v>0</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="N8" s="6" t="n">
-        <v>239439.2496962347</v>
+        <v>239395.2528205769</v>
       </c>
       <c r="O8" s="6" t="n">
-        <v>239439.2496962347</v>
+        <v>239395.2528205769</v>
       </c>
       <c r="P8" s="6" t="n">
-        <v>184091.3588869669</v>
+        <v>184135.3557626247</v>
       </c>
       <c r="Q8" s="6" t="n">
         <v>0</v>
@@ -1332,13 +1332,13 @@
         <v>1</v>
       </c>
       <c r="N9" s="6" t="n">
-        <v>227865.8090060199</v>
+        <v>227823.9387459091</v>
       </c>
       <c r="O9" s="6" t="n">
-        <v>227865.8090060199</v>
+        <v>227823.9387459091</v>
       </c>
       <c r="P9" s="6" t="n">
-        <v>-198861.8383060199</v>
+        <v>-198819.9680459091</v>
       </c>
       <c r="Q9" s="6" t="n">
         <v>0</v>
@@ -1397,13 +1397,13 @@
         <v>1</v>
       </c>
       <c r="N10" s="6" t="n">
-        <v>227862.0364015236</v>
+        <v>227820.1668346276</v>
       </c>
       <c r="O10" s="6" t="n">
-        <v>227862.0364015236</v>
+        <v>227820.1668346276</v>
       </c>
       <c r="P10" s="6" t="n">
-        <v>-221476.1525298833</v>
+        <v>-221434.2829629873</v>
       </c>
       <c r="Q10" s="6" t="n">
         <v>0</v>
@@ -1462,13 +1462,13 @@
         <v>1</v>
       </c>
       <c r="N11" s="6" t="n">
-        <v>232516.1966087057</v>
+        <v>232473.4718415524</v>
       </c>
       <c r="O11" s="6" t="n">
-        <v>206555.5255906894</v>
+        <v>206512.8008235362</v>
       </c>
       <c r="P11" s="6" t="n">
-        <v>77919.23278049534</v>
+        <v>77961.95754764859</v>
       </c>
       <c r="Q11" s="6" t="n">
         <v>0</v>
@@ -1527,13 +1527,13 @@
         <v>1</v>
       </c>
       <c r="N12" s="6" t="n">
-        <v>204212.920107537</v>
+        <v>204175.396057219</v>
       </c>
       <c r="O12" s="6" t="n">
-        <v>204212.920107537</v>
+        <v>204175.396057219</v>
       </c>
       <c r="P12" s="6" t="n">
-        <v>13056.47633910202</v>
+        <v>13094.00038941996</v>
       </c>
       <c r="Q12" s="6" t="n">
         <v>0</v>
@@ -1592,13 +1592,13 @@
         <v>1</v>
       </c>
       <c r="N13" s="6" t="n">
-        <v>172660.297391215</v>
+        <v>172628.5711239259</v>
       </c>
       <c r="O13" s="6" t="n">
-        <v>153382.5987025966</v>
+        <v>153350.8724353075</v>
       </c>
       <c r="P13" s="6" t="n">
-        <v>57860.73443742163</v>
+        <v>57892.46070471073</v>
       </c>
       <c r="Q13" s="6" t="n">
         <v>0</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="N14" s="6" t="n">
-        <v>131549.9035353575</v>
+        <v>131525.7312880923</v>
       </c>
       <c r="O14" s="6" t="n">
-        <v>131549.9035353575</v>
+        <v>131525.7312880923</v>
       </c>
       <c r="P14" s="6" t="n">
-        <v>162541.6133410865</v>
+        <v>162565.7855883517</v>
       </c>
       <c r="Q14" s="6" t="n">
         <v>103099818.9104406</v>
@@ -1787,13 +1787,13 @@
         <v>1</v>
       </c>
       <c r="N16" s="6" t="n">
-        <v>67614.51679630503</v>
+        <v>67602.09265326281</v>
       </c>
       <c r="O16" s="6" t="n">
-        <v>67614.51679630503</v>
+        <v>67602.09265326281</v>
       </c>
       <c r="P16" s="6" t="n">
-        <v>52027.10112966759</v>
+        <v>52039.52527270982</v>
       </c>
       <c r="Q16" s="6" t="n">
         <v>0</v>
@@ -1921,13 +1921,13 @@
         <v>1</v>
       </c>
       <c r="N18" s="6" t="n">
-        <v>21683.89345855883</v>
+        <v>21679.90905096699</v>
       </c>
       <c r="O18" s="6" t="n">
-        <v>21683.89345855883</v>
+        <v>21679.90905096699</v>
       </c>
       <c r="P18" s="6" t="n">
-        <v>17.57804413878301</v>
+        <v>21.56245173062087</v>
       </c>
       <c r="Q18" s="6" t="n">
         <v>0</v>
@@ -1986,13 +1986,13 @@
         <v>1</v>
       </c>
       <c r="N19" s="6" t="n">
-        <v>21246.29901513505</v>
+        <v>21242.39501536415</v>
       </c>
       <c r="O19" s="6" t="n">
-        <v>21246.29901513505</v>
+        <v>21242.39501536415</v>
       </c>
       <c r="P19" s="6" t="n">
-        <v>11256.60433786496</v>
+        <v>11260.50833763585</v>
       </c>
       <c r="Q19" s="6" t="n">
         <v>0</v>
@@ -2051,13 +2051,13 @@
         <v>1</v>
       </c>
       <c r="N20" s="6" t="n">
-        <v>11390.99909219296</v>
+        <v>11388.90600022364</v>
       </c>
       <c r="O20" s="6" t="n">
-        <v>11390.99909219296</v>
+        <v>11388.90600022364</v>
       </c>
       <c r="P20" s="6" t="n">
-        <v>-11390.99909219388</v>
+        <v>-11388.90600022456</v>
       </c>
       <c r="Q20" s="6" t="n">
         <v>0</v>
@@ -2116,13 +2116,13 @@
         <v>1</v>
       </c>
       <c r="N21" s="6" t="n">
-        <v>11390.24695113189</v>
+        <v>11388.15399736822</v>
       </c>
       <c r="O21" s="6" t="n">
-        <v>11390.24695113189</v>
+        <v>11388.15399736822</v>
       </c>
       <c r="P21" s="6" t="n">
-        <v>-11390.24695113171</v>
+        <v>-11388.15399736804</v>
       </c>
       <c r="Q21" s="6" t="n">
         <v>0</v>
@@ -2181,13 +2181,13 @@
         <v>1</v>
       </c>
       <c r="N22" s="6" t="n">
-        <v>11388.13494028817</v>
+        <v>11386.04237460573</v>
       </c>
       <c r="O22" s="6" t="n">
-        <v>11388.13494028817</v>
+        <v>11386.04237460573</v>
       </c>
       <c r="P22" s="6" t="n">
-        <v>-11388.13494028817</v>
+        <v>-11386.04237460573</v>
       </c>
       <c r="Q22" s="6" t="n">
         <v>0</v>
@@ -2246,13 +2246,13 @@
         <v>1</v>
       </c>
       <c r="N23" s="6" t="n">
-        <v>11289.67890469889</v>
+        <v>11287.60443027744</v>
       </c>
       <c r="O23" s="6" t="n">
-        <v>11289.67890469889</v>
+        <v>11287.60443027744</v>
       </c>
       <c r="P23" s="6" t="n">
-        <v>-11289.67890469835</v>
+        <v>-11287.6044302769</v>
       </c>
       <c r="Q23" s="6" t="n">
         <v>0</v>
@@ -2311,13 +2311,13 @@
         <v>1</v>
       </c>
       <c r="N24" s="6" t="n">
-        <v>3399.826646941288</v>
+        <v>3399.201930022765</v>
       </c>
       <c r="O24" s="6" t="n">
-        <v>3399.826646941288</v>
+        <v>3399.201930022765</v>
       </c>
       <c r="P24" s="6" t="n">
-        <v>1405.061533203692</v>
+        <v>1405.686250122215</v>
       </c>
       <c r="Q24" s="6" t="n">
         <v>0</v>
@@ -2376,13 +2376,13 @@
         <v>1</v>
       </c>
       <c r="N25" s="6" t="n">
-        <v>2238.56910760877</v>
+        <v>2238.15777134371</v>
       </c>
       <c r="O25" s="6" t="n">
-        <v>1988.630578588682</v>
+        <v>1988.219242323622</v>
       </c>
       <c r="P25" s="6" t="n">
-        <v>750.1739230860217</v>
+        <v>750.585259351082</v>
       </c>
       <c r="Q25" s="6" t="n">
         <v>0</v>
@@ -2395,12 +2395,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>S12</t>
+          <t>S62</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Spark DAI Vault (Morpho)</t>
+          <t>Spark.fi USDT Reserve Uniswap V4 (USDT/USDS)</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2410,67 +2410,71 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>F</t>
         </is>
       </c>
       <c r="E26" s="6" t="n">
-        <v>458.5728307677575</v>
+        <v>219995.8104343477</v>
       </c>
       <c r="F26" s="6" t="n">
-        <v>539.8728953809741</v>
+        <v>1250066.267840007</v>
       </c>
       <c r="G26" s="6" t="n">
-        <v>81.30006461321658</v>
+        <v>1030070.45740566</v>
       </c>
       <c r="H26" s="6" t="n">
-        <v>76.33046551920575</v>
+        <v>-16.66956268247493</v>
       </c>
       <c r="I26" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J26" s="6" t="n">
-        <v>76.33046551920575</v>
+        <v>0</v>
       </c>
       <c r="K26" s="6" t="n">
-        <v>0</v>
+        <v>-16.66956268247493</v>
       </c>
       <c r="L26" s="6" t="n">
-        <v>462.161691889013</v>
+        <v>386130.3073909548</v>
       </c>
       <c r="M26" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N26" s="6" t="n">
-        <v>1.053106948726445</v>
+        <v>0</v>
       </c>
       <c r="O26" s="6" t="n">
-        <v>1.053106948726445</v>
+        <v>-16.66956268247493</v>
       </c>
       <c r="P26" s="6" t="n">
-        <v>75.27735857047929</v>
+        <v>0</v>
       </c>
       <c r="Q26" s="6" t="n">
-        <v>0</v>
+        <v>386130.3073909548</v>
       </c>
       <c r="R26" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="S26" t="inlineStr"/>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>SDE (fixed)</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>S34</t>
+          <t>S12</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Spark USDC Vault (Morpho, Base)</t>
+          <t>Spark DAI Vault (Morpho)</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>base</t>
+          <t>ethereum</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -2479,40 +2483,40 @@
         </is>
       </c>
       <c r="E27" s="6" t="n">
-        <v>224.7175624853434</v>
+        <v>458.5728307677575</v>
       </c>
       <c r="F27" s="6" t="n">
-        <v>424.9110349025811</v>
+        <v>539.8728953809741</v>
       </c>
       <c r="G27" s="6" t="n">
-        <v>200.1934724172377</v>
+        <v>81.30006461321658</v>
       </c>
       <c r="H27" s="6" t="n">
-        <v>1.161345275089762</v>
+        <v>76.33046551920575</v>
       </c>
       <c r="I27" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J27" s="6" t="n">
-        <v>1.161345275089762</v>
+        <v>76.33046551920575</v>
       </c>
       <c r="K27" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L27" s="6" t="n">
-        <v>368.042098157809</v>
+        <v>462.161691889013</v>
       </c>
       <c r="M27" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N27" s="6" t="n">
-        <v>0.8386408865036938</v>
+        <v>1.052913440704947</v>
       </c>
       <c r="O27" s="6" t="n">
-        <v>0.8386408865036938</v>
+        <v>1.052913440704947</v>
       </c>
       <c r="P27" s="6" t="n">
-        <v>0.3227043885860684</v>
+        <v>75.27755207850079</v>
       </c>
       <c r="Q27" s="6" t="n">
         <v>0</v>
@@ -2525,12 +2529,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>S36</t>
+          <t>S34</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Fluid Savings USDS (fsUSDS, Base)</t>
+          <t>Spark USDC Vault (Morpho, Base)</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2544,40 +2548,40 @@
         </is>
       </c>
       <c r="E28" s="6" t="n">
-        <v>283.8972488542868</v>
+        <v>224.7175624853434</v>
       </c>
       <c r="F28" s="6" t="n">
-        <v>283.8972488542868</v>
+        <v>424.9110349025811</v>
       </c>
       <c r="G28" s="6" t="n">
-        <v>0</v>
+        <v>200.1934724172377</v>
       </c>
       <c r="H28" s="6" t="n">
-        <v>0</v>
+        <v>1.161345275089762</v>
       </c>
       <c r="I28" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J28" s="6" t="n">
-        <v>0</v>
+        <v>1.161345275089762</v>
       </c>
       <c r="K28" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L28" s="6" t="n">
-        <v>283.8972488542868</v>
+        <v>368.042098157809</v>
       </c>
       <c r="M28" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N28" s="6" t="n">
-        <v>0.6469038233583584</v>
+        <v>0.8384867865436753</v>
       </c>
       <c r="O28" s="6" t="n">
-        <v>0.6469038233583584</v>
+        <v>0.8384867865436753</v>
       </c>
       <c r="P28" s="6" t="n">
-        <v>-0.6469038233583584</v>
+        <v>0.322858488546087</v>
       </c>
       <c r="Q28" s="6" t="n">
         <v>0</v>
@@ -2590,59 +2594,59 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>S55</t>
+          <t>S36</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>USDC raw (Avalanche-C — ALM idle)</t>
+          <t>Fluid Savings USDS (fsUSDS, Base)</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>avalanche_c</t>
+          <t>base</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E29" s="6" t="n">
-        <v>2500.221225</v>
+        <v>283.8972488542868</v>
       </c>
       <c r="F29" s="6" t="n">
-        <v>0</v>
+        <v>283.8972488542868</v>
       </c>
       <c r="G29" s="6" t="n">
-        <v>-2500.221225</v>
+        <v>0</v>
       </c>
       <c r="H29" s="6" t="n">
-        <v>-3.30458807350886e-10</v>
+        <v>0</v>
       </c>
       <c r="I29" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J29" s="6" t="n">
-        <v>-3.30458807350886e-10</v>
+        <v>0</v>
       </c>
       <c r="K29" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L29" s="6" t="n">
-        <v>115.3103732260555</v>
+        <v>283.8972488542868</v>
       </c>
       <c r="M29" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N29" s="6" t="n">
-        <v>0.2627525332276154</v>
+        <v>0.6467849550144467</v>
       </c>
       <c r="O29" s="6" t="n">
-        <v>0.2627525332276154</v>
+        <v>0.6467849550144467</v>
       </c>
       <c r="P29" s="6" t="n">
-        <v>-0.2627525335580742</v>
+        <v>-0.6467849550144467</v>
       </c>
       <c r="Q29" s="6" t="n">
         <v>0</v>
@@ -2655,59 +2659,59 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>S16</t>
+          <t>S55</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Ethena Staked USDe (sUSDe)</t>
+          <t>USDC raw (Avalanche-C — ALM idle)</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>ethereum</t>
+          <t>avalanche_c</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E30" s="6" t="n">
-        <v>99.50129408753318</v>
+        <v>2500.221225</v>
       </c>
       <c r="F30" s="6" t="n">
-        <v>99.81305763596731</v>
+        <v>0</v>
       </c>
       <c r="G30" s="6" t="n">
-        <v>0.3117635484341261</v>
+        <v>-2500.221225</v>
       </c>
       <c r="H30" s="6" t="n">
-        <v>0.3117635484341261</v>
+        <v>-3.30458807350886e-10</v>
       </c>
       <c r="I30" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J30" s="6" t="n">
-        <v>0.3117635484341261</v>
+        <v>-3.30458807350886e-10</v>
       </c>
       <c r="K30" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L30" s="6" t="n">
-        <v>99.50129408753318</v>
+        <v>115.3103732260555</v>
       </c>
       <c r="M30" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N30" s="6" t="n">
-        <v>0.2267290994685442</v>
+        <v>0.2627042525445283</v>
       </c>
       <c r="O30" s="6" t="n">
-        <v>0.2267290994685442</v>
+        <v>0.2627042525445283</v>
       </c>
       <c r="P30" s="6" t="n">
-        <v>0.08503444896558192</v>
+        <v>-0.2627042528749872</v>
       </c>
       <c r="Q30" s="6" t="n">
         <v>0</v>
@@ -2720,12 +2724,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>S13</t>
+          <t>S16</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Spark USDS Vault (Morpho)</t>
+          <t>Ethena Staked USDe (sUSDe)</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2739,40 +2743,40 @@
         </is>
       </c>
       <c r="E31" s="6" t="n">
-        <v>21.90660666972937</v>
+        <v>99.50129408753318</v>
       </c>
       <c r="F31" s="6" t="n">
-        <v>21.90661272343654</v>
+        <v>99.81305763596731</v>
       </c>
       <c r="G31" s="6" t="n">
-        <v>6.053707169991468e-06</v>
+        <v>0.3117635484341261</v>
       </c>
       <c r="H31" s="6" t="n">
-        <v>6.053707169991468e-06</v>
+        <v>0.3117635484341261</v>
       </c>
       <c r="I31" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J31" s="6" t="n">
-        <v>6.053707169991468e-06</v>
+        <v>0.3117635484341261</v>
       </c>
       <c r="K31" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L31" s="6" t="n">
-        <v>21.90660666972937</v>
+        <v>99.50129408753318</v>
       </c>
       <c r="M31" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N31" s="6" t="n">
-        <v>0.04991759401912802</v>
+        <v>0.2266874380784004</v>
       </c>
       <c r="O31" s="6" t="n">
-        <v>0.04991759401912802</v>
+        <v>0.2266874380784004</v>
       </c>
       <c r="P31" s="6" t="n">
-        <v>-0.04991154031195803</v>
+        <v>0.0850761103557257</v>
       </c>
       <c r="Q31" s="6" t="n">
         <v>0</v>
@@ -2785,12 +2789,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>S9</t>
+          <t>S61</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Aave Ethereum USDT (aToken)</t>
+          <t>Spark.fi PYUSD Reserve Uniswap V4 (PYUSD/USDS)</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2800,62 +2804,66 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>F</t>
         </is>
       </c>
       <c r="E32" s="6" t="n">
-        <v>5.897868</v>
+        <v>220002.7079018081</v>
       </c>
       <c r="F32" s="6" t="n">
-        <v>5.913258</v>
+        <v>220002.6507685304</v>
       </c>
       <c r="G32" s="6" t="n">
-        <v>0.01539</v>
+        <v>-0.0571332776681098</v>
       </c>
       <c r="H32" s="6" t="n">
-        <v>0.01539</v>
+        <v>-0.0571332776681098</v>
       </c>
       <c r="I32" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J32" s="6" t="n">
-        <v>0.01539</v>
+        <v>0</v>
       </c>
       <c r="K32" s="6" t="n">
-        <v>0</v>
+        <v>-0.0571332776681098</v>
       </c>
       <c r="L32" s="6" t="n">
-        <v>5.897868</v>
+        <v>220002.7079018081</v>
       </c>
       <c r="M32" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N32" s="6" t="n">
-        <v>0.01343920511473919</v>
+        <v>0</v>
       </c>
       <c r="O32" s="6" t="n">
-        <v>0.01343920511473919</v>
+        <v>-0.0571332776681098</v>
       </c>
       <c r="P32" s="6" t="n">
-        <v>0.001950794885260814</v>
+        <v>0</v>
       </c>
       <c r="Q32" s="6" t="n">
-        <v>0</v>
+        <v>220002.7079018081</v>
       </c>
       <c r="R32" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="S32" t="inlineStr"/>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>SDE (fixed)</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>S23</t>
+          <t>S13</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Anchorage tri-party loan escrow (USDC pass-through, ~$0 balance)</t>
+          <t>Spark USDS Vault (Morpho)</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2865,44 +2873,44 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E33" s="6" t="n">
-        <v>1.545609</v>
+        <v>21.90660666972937</v>
       </c>
       <c r="F33" s="6" t="n">
-        <v>10.015998</v>
+        <v>21.90661272343654</v>
       </c>
       <c r="G33" s="6" t="n">
-        <v>8.470389000000001</v>
+        <v>6.053707169991468e-06</v>
       </c>
       <c r="H33" s="6" t="n">
-        <v>8.470389000000001</v>
+        <v>6.053707169991468e-06</v>
       </c>
       <c r="I33" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J33" s="6" t="n">
-        <v>8.470389000000001</v>
+        <v>6.053707169991468e-06</v>
       </c>
       <c r="K33" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L33" s="6" t="n">
-        <v>1.545609</v>
+        <v>21.90660666972937</v>
       </c>
       <c r="M33" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N33" s="6" t="n">
-        <v>0.003521909337100613</v>
+        <v>0.04990842167925482</v>
       </c>
       <c r="O33" s="6" t="n">
-        <v>0.003521909337100613</v>
+        <v>0.04990842167925482</v>
       </c>
       <c r="P33" s="6" t="n">
-        <v>8.4668670906629</v>
+        <v>-0.04990236797208483</v>
       </c>
       <c r="Q33" s="6" t="n">
         <v>0</v>
@@ -2915,17 +2923,17 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>S54</t>
+          <t>S9</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Aave Avalanche USDC (aAvaUSDC)</t>
+          <t>Aave Ethereum USDT (aToken)</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>avalanche_c</t>
+          <t>ethereum</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -2934,40 +2942,40 @@
         </is>
       </c>
       <c r="E34" s="6" t="n">
-        <v>0.154431</v>
+        <v>5.897868</v>
       </c>
       <c r="F34" s="6" t="n">
-        <v>0.155165</v>
+        <v>5.913258</v>
       </c>
       <c r="G34" s="6" t="n">
-        <v>0.000734</v>
+        <v>0.01539</v>
       </c>
       <c r="H34" s="6" t="n">
-        <v>0.000734</v>
+        <v>0.01539</v>
       </c>
       <c r="I34" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J34" s="6" t="n">
-        <v>0.000734</v>
+        <v>0.01539</v>
       </c>
       <c r="K34" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L34" s="6" t="n">
-        <v>0.154431</v>
+        <v>5.897868</v>
       </c>
       <c r="M34" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N34" s="6" t="n">
-        <v>0.0003518949364540351</v>
+        <v>0.01343673566565294</v>
       </c>
       <c r="O34" s="6" t="n">
-        <v>0.0003518949364540351</v>
+        <v>0.01343673566565294</v>
       </c>
       <c r="P34" s="6" t="n">
-        <v>0.0003821050635459649</v>
+        <v>0.001953264334347057</v>
       </c>
       <c r="Q34" s="6" t="n">
         <v>0</v>
@@ -2980,12 +2988,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>S8</t>
+          <t>S23</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Aave Ethereum USDC (aToken)</t>
+          <t>Anchorage tri-party loan escrow (USDC pass-through, ~$0 balance)</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2995,44 +3003,44 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E35" s="6" t="n">
-        <v>0.057783</v>
+        <v>1.545609</v>
       </c>
       <c r="F35" s="6" t="n">
-        <v>0.057969</v>
+        <v>10.015998</v>
       </c>
       <c r="G35" s="6" t="n">
-        <v>0.000186</v>
+        <v>8.470389000000001</v>
       </c>
       <c r="H35" s="6" t="n">
-        <v>0.000186</v>
+        <v>8.470389000000001</v>
       </c>
       <c r="I35" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J35" s="6" t="n">
-        <v>0.000186</v>
+        <v>8.470389000000001</v>
       </c>
       <c r="K35" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L35" s="6" t="n">
-        <v>0.057783</v>
+        <v>1.545609</v>
       </c>
       <c r="M35" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N35" s="6" t="n">
-        <v>0.0001316675091990825</v>
+        <v>0.003521262187531864</v>
       </c>
       <c r="O35" s="6" t="n">
-        <v>0.0001316675091990825</v>
+        <v>0.003521262187531864</v>
       </c>
       <c r="P35" s="6" t="n">
-        <v>5.433249080091749e-05</v>
+        <v>8.466867737812468</v>
       </c>
       <c r="Q35" s="6" t="n">
         <v>0</v>
@@ -3045,17 +3053,17 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>S41</t>
+          <t>S54</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Aave Arbitrum USDCn (aArbUSDCn)</t>
+          <t>Aave Avalanche USDC (aAvaUSDC)</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>arbitrum</t>
+          <t>avalanche_c</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -3064,40 +3072,40 @@
         </is>
       </c>
       <c r="E36" s="6" t="n">
-        <v>0.006346</v>
+        <v>0.154431</v>
       </c>
       <c r="F36" s="6" t="n">
-        <v>0.006363</v>
+        <v>0.155165</v>
       </c>
       <c r="G36" s="6" t="n">
-        <v>1.7e-05</v>
+        <v>0.000734</v>
       </c>
       <c r="H36" s="6" t="n">
-        <v>1.7e-05</v>
+        <v>0.000734</v>
       </c>
       <c r="I36" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J36" s="6" t="n">
-        <v>1.7e-05</v>
+        <v>0.000734</v>
       </c>
       <c r="K36" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L36" s="6" t="n">
-        <v>0.006346</v>
+        <v>0.154431</v>
       </c>
       <c r="M36" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N36" s="6" t="n">
-        <v>1.446034323896955e-05</v>
+        <v>0.0003518302758865491</v>
       </c>
       <c r="O36" s="6" t="n">
-        <v>1.446034323896955e-05</v>
+        <v>0.0003518302758865491</v>
       </c>
       <c r="P36" s="6" t="n">
-        <v>2.539656761030448e-06</v>
+        <v>0.0003821697241134509</v>
       </c>
       <c r="Q36" s="6" t="n">
         <v>0</v>
@@ -3110,12 +3118,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>S7</t>
+          <t>S8</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Aave Ethereum USDS (aToken)</t>
+          <t>Aave Ethereum USDC (aToken)</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -3129,40 +3137,40 @@
         </is>
       </c>
       <c r="E37" s="6" t="n">
-        <v>0.005744283090097436</v>
+        <v>0.057783</v>
       </c>
       <c r="F37" s="6" t="n">
-        <v>0.005746426914602806</v>
+        <v>0.057969</v>
       </c>
       <c r="G37" s="6" t="n">
-        <v>2.14382450537e-06</v>
+        <v>0.000186</v>
       </c>
       <c r="H37" s="6" t="n">
-        <v>2.14382450537e-06</v>
+        <v>0.000186</v>
       </c>
       <c r="I37" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J37" s="6" t="n">
-        <v>2.14382450537e-06</v>
+        <v>0.000186</v>
       </c>
       <c r="K37" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L37" s="6" t="n">
-        <v>0.005744283090097436</v>
+        <v>0.057783</v>
       </c>
       <c r="M37" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N37" s="6" t="n">
-        <v>1.308923812553066e-05</v>
+        <v>0.0001316433153418191</v>
       </c>
       <c r="O37" s="6" t="n">
-        <v>1.308923812553066e-05</v>
+        <v>0.0001316433153418191</v>
       </c>
       <c r="P37" s="6" t="n">
-        <v>-1.094541362016066e-05</v>
+        <v>5.435668465818089e-05</v>
       </c>
       <c r="Q37" s="6" t="n">
         <v>0</v>
@@ -3175,17 +3183,17 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>S35</t>
+          <t>S41</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Aave Base USDC (aBasUSDC)</t>
+          <t>Aave Arbitrum USDCn (aArbUSDCn)</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>base</t>
+          <t>arbitrum</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -3194,40 +3202,40 @@
         </is>
       </c>
       <c r="E38" s="6" t="n">
-        <v>0.0017</v>
+        <v>0.006346</v>
       </c>
       <c r="F38" s="6" t="n">
-        <v>0.001705</v>
+        <v>0.006363</v>
       </c>
       <c r="G38" s="6" t="n">
-        <v>5e-06</v>
+        <v>1.7e-05</v>
       </c>
       <c r="H38" s="6" t="n">
-        <v>5e-06</v>
+        <v>1.7e-05</v>
       </c>
       <c r="I38" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J38" s="6" t="n">
-        <v>5e-06</v>
+        <v>1.7e-05</v>
       </c>
       <c r="K38" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L38" s="6" t="n">
-        <v>0.0017</v>
+        <v>0.006346</v>
       </c>
       <c r="M38" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N38" s="6" t="n">
-        <v>3.873713127363416e-06</v>
+        <v>1.445768615612177e-05</v>
       </c>
       <c r="O38" s="6" t="n">
-        <v>3.873713127363416e-06</v>
+        <v>1.445768615612177e-05</v>
       </c>
       <c r="P38" s="6" t="n">
-        <v>1.126286872636584e-06</v>
+        <v>2.542313843878233e-06</v>
       </c>
       <c r="Q38" s="6" t="n">
         <v>0</v>
@@ -3240,12 +3248,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>S17</t>
+          <t>S7</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Fluid Savings USDS (fsUSDS)</t>
+          <t>Aave Ethereum USDS (aToken)</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -3255,44 +3263,44 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E39" s="6" t="n">
-        <v>0.001240144670509943</v>
+        <v>0.005744283090097436</v>
       </c>
       <c r="F39" s="6" t="n">
-        <v>0.001240144670509943</v>
+        <v>0.005746426914602806</v>
       </c>
       <c r="G39" s="6" t="n">
-        <v>0</v>
+        <v>2.14382450537e-06</v>
       </c>
       <c r="H39" s="6" t="n">
-        <v>0</v>
+        <v>2.14382450537e-06</v>
       </c>
       <c r="I39" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J39" s="6" t="n">
-        <v>0</v>
+        <v>2.14382450537e-06</v>
       </c>
       <c r="K39" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L39" s="6" t="n">
-        <v>0.001240144670509943</v>
+        <v>0.005744283090097436</v>
       </c>
       <c r="M39" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N39" s="6" t="n">
-        <v>2.825861582343615e-06</v>
+        <v>1.30868329827523e-05</v>
       </c>
       <c r="O39" s="6" t="n">
-        <v>2.825861582343615e-06</v>
+        <v>1.30868329827523e-05</v>
       </c>
       <c r="P39" s="6" t="n">
-        <v>-2.825861582343615e-06</v>
+        <v>-1.09430084773823e-05</v>
       </c>
       <c r="Q39" s="6" t="n">
         <v>0</v>
@@ -3305,17 +3313,17 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>S6</t>
+          <t>S35</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Aave Ethereum Lido USDS (aToken)</t>
+          <t>Aave Base USDC (aBasUSDC)</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>ethereum</t>
+          <t>base</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -3324,40 +3332,40 @@
         </is>
       </c>
       <c r="E40" s="6" t="n">
-        <v>0.0005209665645060241</v>
+        <v>0.0017</v>
       </c>
       <c r="F40" s="6" t="n">
-        <v>0.000521673271312833</v>
+        <v>0.001705</v>
       </c>
       <c r="G40" s="6" t="n">
-        <v>7.06706806809e-07</v>
+        <v>5e-06</v>
       </c>
       <c r="H40" s="6" t="n">
-        <v>7.06706806809e-07</v>
+        <v>5e-06</v>
       </c>
       <c r="I40" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J40" s="6" t="n">
-        <v>7.06706806809e-07</v>
+        <v>5e-06</v>
       </c>
       <c r="K40" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L40" s="6" t="n">
-        <v>0.0005209665645060241</v>
+        <v>0.0017</v>
       </c>
       <c r="M40" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N40" s="6" t="n">
-        <v>1.18710295284965e-06</v>
+        <v>3.873001333975261e-06</v>
       </c>
       <c r="O40" s="6" t="n">
-        <v>1.18710295284965e-06</v>
+        <v>3.873001333975261e-06</v>
       </c>
       <c r="P40" s="6" t="n">
-        <v>-4.8039614604065e-07</v>
+        <v>1.126998666024739e-06</v>
       </c>
       <c r="Q40" s="6" t="n">
         <v>0</v>
@@ -3370,12 +3378,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>S30</t>
+          <t>S17</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>USDe raw (ALM idle)</t>
+          <t>Fluid Savings USDS (fsUSDS)</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -3385,14 +3393,14 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E41" s="6" t="n">
-        <v>7.4896275897803e-05</v>
+        <v>0.001240144670509943</v>
       </c>
       <c r="F41" s="6" t="n">
-        <v>7.4896275897803e-05</v>
+        <v>0.001240144670509943</v>
       </c>
       <c r="G41" s="6" t="n">
         <v>0</v>
@@ -3410,19 +3418,19 @@
         <v>0</v>
       </c>
       <c r="L41" s="6" t="n">
-        <v>7.4896275897803e-05</v>
+        <v>0.001240144670509943</v>
       </c>
       <c r="M41" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N41" s="6" t="n">
-        <v>1.706627571387951e-07</v>
+        <v>2.825342331298424e-06</v>
       </c>
       <c r="O41" s="6" t="n">
-        <v>1.706627571387951e-07</v>
+        <v>2.825342331298424e-06</v>
       </c>
       <c r="P41" s="6" t="n">
-        <v>-1.706627571387951e-07</v>
+        <v>-2.825342331298424e-06</v>
       </c>
       <c r="Q41" s="6" t="n">
         <v>0</v>
@@ -3435,12 +3443,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>S19</t>
+          <t>S6</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>BlackRock USD Institutional Digital Liquidity Fund (BUIDL-I)</t>
+          <t>Aave Ethereum Lido USDS (aToken)</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -3450,44 +3458,44 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E42" s="6" t="n">
-        <v>0</v>
+        <v>0.0005209665645060241</v>
       </c>
       <c r="F42" s="6" t="n">
-        <v>0</v>
+        <v>0.000521673271312833</v>
       </c>
       <c r="G42" s="6" t="n">
-        <v>0</v>
+        <v>7.06706806809e-07</v>
       </c>
       <c r="H42" s="6" t="n">
-        <v>0</v>
+        <v>7.06706806809e-07</v>
       </c>
       <c r="I42" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J42" s="6" t="n">
-        <v>0</v>
+        <v>7.06706806809e-07</v>
       </c>
       <c r="K42" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L42" s="6" t="n">
-        <v>0</v>
+        <v>0.0005209665645060241</v>
       </c>
       <c r="M42" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N42" s="6" t="n">
-        <v>0</v>
+        <v>1.186884823110788e-06</v>
       </c>
       <c r="O42" s="6" t="n">
-        <v>0</v>
+        <v>1.186884823110788e-06</v>
       </c>
       <c r="P42" s="6" t="n">
-        <v>0</v>
+        <v>-4.801780163017881e-07</v>
       </c>
       <c r="Q42" s="6" t="n">
         <v>0</v>
@@ -3500,12 +3508,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>S20</t>
+          <t>S30</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Janus Henderson Anemoy Treasury Fund (JTRSY)</t>
+          <t>USDe raw (ALM idle)</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3515,14 +3523,14 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E43" s="6" t="n">
-        <v>0</v>
+        <v>7.4896275897803e-05</v>
       </c>
       <c r="F43" s="6" t="n">
-        <v>0</v>
+        <v>7.4896275897803e-05</v>
       </c>
       <c r="G43" s="6" t="n">
         <v>0</v>
@@ -3540,19 +3548,19 @@
         <v>0</v>
       </c>
       <c r="L43" s="6" t="n">
-        <v>0</v>
+        <v>7.4896275897803e-05</v>
       </c>
       <c r="M43" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N43" s="6" t="n">
-        <v>0</v>
+        <v>1.70631397918806e-07</v>
       </c>
       <c r="O43" s="6" t="n">
-        <v>0</v>
+        <v>1.70631397918806e-07</v>
       </c>
       <c r="P43" s="6" t="n">
-        <v>0</v>
+        <v>-1.70631397918806e-07</v>
       </c>
       <c r="Q43" s="6" t="n">
         <v>0</v>
@@ -3565,12 +3573,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>S21</t>
+          <t>S19</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Superstate Short Duration US Government Securities Fund (USTB)</t>
+          <t>BlackRock USD Institutional Digital Liquidity Fund (BUIDL-I)</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3608,7 +3616,7 @@
         <v>0</v>
       </c>
       <c r="M44" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N44" s="6" t="n">
         <v>0</v>
@@ -3625,21 +3633,17 @@
       <c r="R44" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="S44" t="inlineStr">
-        <is>
-          <t>SDE (fixed)</t>
-        </is>
-      </c>
+      <c r="S44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>S22</t>
+          <t>S20</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Superstate Crypto Carry Fund (USCC)</t>
+          <t>Janus Henderson Anemoy Treasury Fund (JTRSY)</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3699,12 +3703,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>S26</t>
+          <t>S21</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>USDC raw (ALM idle)</t>
+          <t>Superstate Short Duration US Government Securities Fund (USTB)</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3714,7 +3718,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E46" s="6" t="n">
@@ -3727,13 +3731,13 @@
         <v>0</v>
       </c>
       <c r="H46" s="6" t="n">
-        <v>891780.2799998628</v>
+        <v>0</v>
       </c>
       <c r="I46" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J46" s="6" t="n">
-        <v>891780.2799998628</v>
+        <v>0</v>
       </c>
       <c r="K46" s="6" t="n">
         <v>0</v>
@@ -3742,7 +3746,7 @@
         <v>0</v>
       </c>
       <c r="M46" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N46" s="6" t="n">
         <v>0</v>
@@ -3751,7 +3755,7 @@
         <v>0</v>
       </c>
       <c r="P46" s="6" t="n">
-        <v>891780.2799998628</v>
+        <v>0</v>
       </c>
       <c r="Q46" s="6" t="n">
         <v>0</v>
@@ -3759,17 +3763,21 @@
       <c r="R46" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="S46" t="inlineStr"/>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>SDE (fixed)</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>S29</t>
+          <t>S22</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>DAI raw (ALM idle)</t>
+          <t>Superstate Crypto Carry Fund (USCC)</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3779,7 +3787,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E47" s="6" t="n">
@@ -3792,13 +3800,13 @@
         <v>0</v>
       </c>
       <c r="H47" s="6" t="n">
-        <v>7.850176e-07</v>
+        <v>0</v>
       </c>
       <c r="I47" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J47" s="6" t="n">
-        <v>7.850176e-07</v>
+        <v>0</v>
       </c>
       <c r="K47" s="6" t="n">
         <v>0</v>
@@ -3816,7 +3824,7 @@
         <v>0</v>
       </c>
       <c r="P47" s="6" t="n">
-        <v>7.850176e-07</v>
+        <v>0</v>
       </c>
       <c r="Q47" s="6" t="n">
         <v>0</v>
@@ -3829,12 +3837,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>S31</t>
+          <t>S26</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>USDS raw / POL (ALM idle — already netted out of utilized)</t>
+          <t>USDC raw (ALM idle)</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3857,22 +3865,22 @@
         <v>0</v>
       </c>
       <c r="H48" s="6" t="n">
-        <v>-2.7208051e-06</v>
+        <v>891780.2799998628</v>
       </c>
       <c r="I48" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J48" s="6" t="n">
-        <v>-2.7208051e-06</v>
+        <v>891780.2799998628</v>
       </c>
       <c r="K48" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L48" s="6" t="n">
-        <v>17.83075728228825</v>
+        <v>0</v>
       </c>
       <c r="M48" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N48" s="6" t="n">
         <v>0</v>
@@ -3881,7 +3889,7 @@
         <v>0</v>
       </c>
       <c r="P48" s="6" t="n">
-        <v>-2.7208051e-06</v>
+        <v>891780.2799998628</v>
       </c>
       <c r="Q48" s="6" t="n">
         <v>0</v>
@@ -3889,26 +3897,22 @@
       <c r="R48" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="S48" t="inlineStr">
-        <is>
-          <t>CoF excluded (Savings V2 depositor capital; not in cum_alm_usds)</t>
-        </is>
-      </c>
+      <c r="S48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>S38</t>
+          <t>S29</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>USDS raw (Base — POL)</t>
+          <t>DAI raw (ALM idle)</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>base</t>
+          <t>ethereum</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -3917,31 +3921,31 @@
         </is>
       </c>
       <c r="E49" s="6" t="n">
-        <v>65170000</v>
+        <v>0</v>
       </c>
       <c r="F49" s="6" t="n">
-        <v>65170000</v>
+        <v>0</v>
       </c>
       <c r="G49" s="6" t="n">
         <v>0</v>
       </c>
       <c r="H49" s="6" t="n">
-        <v>0</v>
+        <v>7.850176e-07</v>
       </c>
       <c r="I49" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J49" s="6" t="n">
-        <v>0</v>
+        <v>7.850176e-07</v>
       </c>
       <c r="K49" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L49" s="6" t="n">
-        <v>65170000</v>
+        <v>0</v>
       </c>
       <c r="M49" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N49" s="6" t="n">
         <v>0</v>
@@ -3950,39 +3954,35 @@
         <v>0</v>
       </c>
       <c r="P49" s="6" t="n">
-        <v>0</v>
+        <v>7.850176e-07</v>
       </c>
       <c r="Q49" s="6" t="n">
-        <v>65170000</v>
+        <v>0</v>
       </c>
       <c r="R49" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="S49" t="inlineStr">
-        <is>
-          <t>CoF excluded (already deducted from utilized)</t>
-        </is>
-      </c>
+      <c r="S49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>S42</t>
+          <t>S31</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Fluid Savings USDS (fsUSDS, Arbitrum)</t>
+          <t>USDS raw / POL (ALM idle — already netted out of utilized)</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>arbitrum</t>
+          <t>ethereum</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E50" s="6" t="n">
@@ -3995,22 +3995,22 @@
         <v>0</v>
       </c>
       <c r="H50" s="6" t="n">
-        <v>0</v>
+        <v>-2.7208051e-06</v>
       </c>
       <c r="I50" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J50" s="6" t="n">
-        <v>0</v>
+        <v>-2.7208051e-06</v>
       </c>
       <c r="K50" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L50" s="6" t="n">
-        <v>0</v>
+        <v>17.83075728228825</v>
       </c>
       <c r="M50" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N50" s="6" t="n">
         <v>0</v>
@@ -4019,7 +4019,7 @@
         <v>0</v>
       </c>
       <c r="P50" s="6" t="n">
-        <v>0</v>
+        <v>-2.7208051e-06</v>
       </c>
       <c r="Q50" s="6" t="n">
         <v>0</v>
@@ -4027,22 +4027,26 @@
       <c r="R50" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="S50" t="inlineStr"/>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>CoF excluded (Savings V2 depositor capital; not in cum_alm_usds)</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>S44</t>
+          <t>S38</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>USDS raw (Arbitrum — POL)</t>
+          <t>USDS raw (Base — POL)</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>arbitrum</t>
+          <t>base</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -4051,10 +4055,10 @@
         </is>
       </c>
       <c r="E51" s="6" t="n">
-        <v>90000000</v>
+        <v>65170000</v>
       </c>
       <c r="F51" s="6" t="n">
-        <v>90000000</v>
+        <v>65170000</v>
       </c>
       <c r="G51" s="6" t="n">
         <v>0</v>
@@ -4072,7 +4076,7 @@
         <v>0</v>
       </c>
       <c r="L51" s="6" t="n">
-        <v>90000000</v>
+        <v>65170000</v>
       </c>
       <c r="M51" s="7" t="n">
         <v>0</v>
@@ -4087,7 +4091,7 @@
         <v>0</v>
       </c>
       <c r="Q51" s="6" t="n">
-        <v>90000000</v>
+        <v>65170000</v>
       </c>
       <c r="R51" s="6" t="n">
         <v>0</v>
@@ -4101,29 +4105,29 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>S48</t>
+          <t>S42</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>USDS raw (Optimism — POL)</t>
+          <t>Fluid Savings USDS (fsUSDS, Arbitrum)</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>optimism</t>
+          <t>arbitrum</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E52" s="6" t="n">
-        <v>89900000</v>
+        <v>0</v>
       </c>
       <c r="F52" s="6" t="n">
-        <v>89900000</v>
+        <v>0</v>
       </c>
       <c r="G52" s="6" t="n">
         <v>0</v>
@@ -4141,10 +4145,10 @@
         <v>0</v>
       </c>
       <c r="L52" s="6" t="n">
-        <v>89900000</v>
+        <v>0</v>
       </c>
       <c r="M52" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N52" s="6" t="n">
         <v>0</v>
@@ -4156,31 +4160,27 @@
         <v>0</v>
       </c>
       <c r="Q52" s="6" t="n">
-        <v>89900000</v>
+        <v>0</v>
       </c>
       <c r="R52" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="S52" t="inlineStr">
-        <is>
-          <t>CoF excluded (already deducted from utilized)</t>
-        </is>
-      </c>
+      <c r="S52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>S52</t>
+          <t>S44</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>USDS raw (Unichain — POL)</t>
+          <t>USDS raw (Arbitrum — POL)</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>unichain</t>
+          <t>arbitrum</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -4189,10 +4189,10 @@
         </is>
       </c>
       <c r="E53" s="6" t="n">
-        <v>89900000</v>
+        <v>90000000</v>
       </c>
       <c r="F53" s="6" t="n">
-        <v>89900000</v>
+        <v>90000000</v>
       </c>
       <c r="G53" s="6" t="n">
         <v>0</v>
@@ -4210,7 +4210,7 @@
         <v>0</v>
       </c>
       <c r="L53" s="6" t="n">
-        <v>89900000</v>
+        <v>90000000</v>
       </c>
       <c r="M53" s="7" t="n">
         <v>0</v>
@@ -4225,7 +4225,7 @@
         <v>0</v>
       </c>
       <c r="Q53" s="6" t="n">
-        <v>89900000</v>
+        <v>90000000</v>
       </c>
       <c r="R53" s="6" t="n">
         <v>0</v>
@@ -4239,168 +4239,250 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
+          <t>S48</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>USDS raw (Optimism — POL)</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>optimism</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E54" s="6" t="n">
+        <v>89900000</v>
+      </c>
+      <c r="F54" s="6" t="n">
+        <v>89900000</v>
+      </c>
+      <c r="G54" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H54" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I54" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J54" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K54" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L54" s="6" t="n">
+        <v>89900000</v>
+      </c>
+      <c r="M54" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N54" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O54" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P54" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q54" s="6" t="n">
+        <v>89900000</v>
+      </c>
+      <c r="R54" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>CoF excluded (already deducted from utilized)</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>S52</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>USDS raw (Unichain — POL)</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>unichain</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E55" s="6" t="n">
+        <v>89900000</v>
+      </c>
+      <c r="F55" s="6" t="n">
+        <v>89900000</v>
+      </c>
+      <c r="G55" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H55" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I55" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J55" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K55" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L55" s="6" t="n">
+        <v>89900000</v>
+      </c>
+      <c r="M55" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N55" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O55" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P55" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q55" s="6" t="n">
+        <v>89900000</v>
+      </c>
+      <c r="R55" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>CoF excluded (already deducted from utilized)</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
           <t>PSM_CURVE_DEDUCT</t>
         </is>
       </c>
-      <c r="B54" t="inlineStr">
+      <c r="B56" t="inlineStr">
         <is>
           <t>PSM3 USDS + PSM3 USDC (SDE) + Curve idle USDS — BR deduction (unattributed)</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr"/>
-      <c r="D54" t="inlineStr"/>
-      <c r="E54" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F54" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G54" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H54" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I54" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J54" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K54" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L54" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M54" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N54" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O54" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P54" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q54" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R54" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S54" t="inlineStr">
+      <c r="C56" t="inlineStr"/>
+      <c r="D56" t="inlineStr"/>
+      <c r="E56" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F56" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G56" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H56" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I56" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J56" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K56" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L56" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M56" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N56" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O56" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P56" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q56" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R56" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S56" t="inlineStr">
         <is>
           <t>BR deduction from PSM3 USDS leg + PSM3 USDC leg (SDE, ≈$0 yield) + Curve idle USDS — not tracked per-venue; residual = sky_rev_br_reduction − Σ(known venue deduction_avg × effective_br_rate × n_days)</t>
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" s="8" t="inlineStr">
+    <row r="58">
+      <c r="A58" s="8" t="inlineStr">
         <is>
           <t>Position-only venues (PnL aggregated at prime level)</t>
         </is>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" s="2" t="inlineStr">
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
         <is>
           <t>Venue</t>
         </is>
       </c>
-      <c r="B57" s="2" t="inlineStr">
+      <c r="B59" s="2" t="inlineStr">
         <is>
           <t>Label</t>
         </is>
       </c>
-      <c r="C57" s="2" t="inlineStr">
+      <c r="C59" s="2" t="inlineStr">
         <is>
           <t>Chain</t>
         </is>
       </c>
-      <c r="D57" s="2" t="inlineStr">
+      <c r="D59" s="2" t="inlineStr">
         <is>
           <t>Pricing cat.</t>
         </is>
       </c>
-      <c r="E57" s="2" t="inlineStr">
+      <c r="E59" s="2" t="inlineStr">
         <is>
           <t>Position SoM</t>
         </is>
       </c>
-      <c r="F57" s="2" t="inlineStr">
+      <c r="F59" s="2" t="inlineStr">
         <is>
           <t>Position EoM</t>
         </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>S56</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>Spark Savings V2 — spUSDC vault</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>ethereum</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>S2</t>
-        </is>
-      </c>
-      <c r="E58" s="6" t="n">
-        <v>573332157.534611</v>
-      </c>
-      <c r="F58" s="6" t="n">
-        <v>303545287.192935</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>S57</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>Spark Savings V2 — spUSDT vault</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>ethereum</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>S2</t>
-        </is>
-      </c>
-      <c r="E59" s="6" t="n">
-        <v>1134703231.016836</v>
-      </c>
-      <c r="F59" s="6" t="n">
-        <v>1270360913.25412</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>S59</t>
+          <t>S56</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Spark Savings V2 — spPYUSD vault</t>
+          <t>Spark Savings V2 — spUSDC vault</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -4414,51 +4496,107 @@
         </is>
       </c>
       <c r="E60" s="6" t="n">
-        <v>1066559.875133</v>
+        <v>573332157.534611</v>
       </c>
       <c r="F60" s="6" t="n">
-        <v>773533.783718</v>
+        <v>303545287.192935</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
+          <t>S57</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Spark Savings V2 — spUSDT vault</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>ethereum</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>S2</t>
+        </is>
+      </c>
+      <c r="E61" s="6" t="n">
+        <v>1134703231.016836</v>
+      </c>
+      <c r="F61" s="6" t="n">
+        <v>1270360913.25412</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>S59</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Spark Savings V2 — spPYUSD vault</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>ethereum</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>S2</t>
+        </is>
+      </c>
+      <c r="E62" s="6" t="n">
+        <v>1066559.875133</v>
+      </c>
+      <c r="F62" s="6" t="n">
+        <v>773533.783718</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
           <t>S60</t>
         </is>
       </c>
-      <c r="B61" t="inlineStr">
+      <c r="B63" t="inlineStr">
         <is>
           <t>Spark Savings V2 — spUSDC vault (Avalanche-C, CREATE2 same address)</t>
         </is>
       </c>
-      <c r="C61" t="inlineStr">
+      <c r="C63" t="inlineStr">
         <is>
           <t>avalanche_c</t>
         </is>
       </c>
-      <c r="D61" t="inlineStr">
+      <c r="D63" t="inlineStr">
         <is>
           <t>S2</t>
         </is>
       </c>
-      <c r="E61" s="6" t="n">
+      <c r="E63" s="6" t="n">
         <v>37138817.432463</v>
       </c>
-      <c r="F61" s="6" t="n">
+      <c r="F63" s="6" t="n">
         <v>25647247.422478</v>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" t="inlineStr"/>
-      <c r="B62" s="5" t="inlineStr">
+    <row r="64">
+      <c r="A64" t="inlineStr"/>
+      <c r="B64" s="5" t="inlineStr">
         <is>
           <t>Aggregated actual_revenue (included in prime_agent_revenue, not in Venues body above)</t>
         </is>
       </c>
-      <c r="C62" t="inlineStr"/>
-      <c r="D62" t="inlineStr"/>
-      <c r="E62" t="inlineStr"/>
-      <c r="F62" s="9" t="n">
+      <c r="C64" t="inlineStr"/>
+      <c r="D64" t="inlineStr"/>
+      <c r="E64" t="inlineStr"/>
+      <c r="F64" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4513,7 +4651,7 @@
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>3356195943.673027</v>
+        <v>3355589811.023948</v>
       </c>
     </row>
     <row r="6">
@@ -4533,7 +4671,7 @@
         </is>
       </c>
       <c r="B7" s="6" t="n">
-        <v>2356195943.673027</v>
+        <v>2355589811.023948</v>
       </c>
     </row>
     <row r="8">
@@ -4543,7 +4681,7 @@
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>0.03951513515348828</v>
+        <v>0.03951515566338391</v>
       </c>
     </row>
     <row r="9">
@@ -4573,7 +4711,7 @@
         </is>
       </c>
       <c r="B11" s="10" t="n">
-        <v>0.03871429258669792</v>
+        <v>0.03871416843742665</v>
       </c>
     </row>
     <row r="12">
@@ -4583,7 +4721,7 @@
         </is>
       </c>
       <c r="B12" s="11" t="n">
-        <v>-8.008425667903683</v>
+        <v>-8.009872259572633</v>
       </c>
     </row>
     <row r="13">
@@ -4603,7 +4741,7 @@
         </is>
       </c>
       <c r="B15" s="3" t="n">
-        <v>11047394.95315541</v>
+        <v>11045405.4060441</v>
       </c>
     </row>
     <row r="16">
@@ -4613,7 +4751,7 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>10827488.55337466</v>
+        <v>10825499.00626334</v>
       </c>
     </row>
     <row r="17">
@@ -4663,10 +4801,10 @@
         </is>
       </c>
       <c r="B21" s="6" t="n">
-        <v>2356195943.673027</v>
+        <v>2355589811.023948</v>
       </c>
       <c r="C21" s="3" t="n">
-        <v>7755973.525057507</v>
+        <v>7753983.977946189</v>
       </c>
     </row>
     <row r="23">
@@ -4688,7 +4826,7 @@
         </is>
       </c>
       <c r="B24" s="3" t="n">
-        <v>10642578.13467968</v>
+        <v>10640588.58756836</v>
       </c>
     </row>
     <row r="25">
@@ -4698,7 +4836,7 @@
         </is>
       </c>
       <c r="B25" s="3" t="n">
-        <v>40550.6842112442</v>
+        <v>40533.95751528406</v>
       </c>
     </row>
     <row r="26">
@@ -4708,7 +4846,7 @@
         </is>
       </c>
       <c r="B26" s="3" t="n">
-        <v>10683128.81889092</v>
+        <v>10681122.54508365</v>
       </c>
     </row>
     <row r="28">
@@ -4735,7 +4873,7 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>10642578.13467968</v>
+        <v>10640588.58756836</v>
       </c>
     </row>
     <row r="32">
@@ -4745,7 +4883,7 @@
         </is>
       </c>
       <c r="B32" s="3" t="n">
-        <v>-2749286.851285571</v>
+        <v>-2751276.398396889</v>
       </c>
     </row>
     <row r="33" ht="60" customHeight="1">
@@ -4875,7 +5013,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J5"/>
+  <dimension ref="A1:J7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -5035,6 +5173,86 @@
       </c>
       <c r="J5" s="6" t="n">
         <v>40550.6842112442</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>S61</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>fixed</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>2026-02-01</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>PYUSD in PYUSD/USDS Uniswap V4</t>
+        </is>
+      </c>
+      <c r="I6" s="6" t="n">
+        <v>-0.0571332776681098</v>
+      </c>
+      <c r="J6" s="6" t="n">
+        <v>-0.0571332776681098</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>S62</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>fixed</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2026-02-01</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>USDT in USDT/USDS Uniswap V4</t>
+        </is>
+      </c>
+      <c r="I7" s="6" t="n">
+        <v>-16.66956268247493</v>
+      </c>
+      <c r="J7" s="6" t="n">
+        <v>-16.66956268247493</v>
       </c>
     </row>
   </sheetData>
@@ -5174,16 +5392,16 @@
         <v>109271584.0644501</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>81897516.64033359</v>
+        <v>82142361.16871259</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>68133383.80742754</v>
+        <v>68328535.28923744</v>
       </c>
       <c r="G6" s="6" t="n">
         <v>127906874.3387326</v>
       </c>
       <c r="H6" s="6" t="n">
-        <v>3236279210.15232</v>
+        <v>3235839214.142131</v>
       </c>
       <c r="I6" s="7" t="n">
         <v>0.03650000241537366</v>
@@ -5201,7 +5419,7 @@
         <v>0.03693491707043663</v>
       </c>
       <c r="N6" s="3" t="n">
-        <v>337381.4365374905</v>
+        <v>337334.6074229946</v>
       </c>
       <c r="O6" s="3" t="n">
         <v>414243.5423272011</v>
@@ -5223,16 +5441,16 @@
         <v>109236625.511487</v>
       </c>
       <c r="E7" s="6" t="n">
-        <v>74371158.35490692</v>
+        <v>74621119.61822292</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>66387928.31178243</v>
+        <v>66577961.80007715</v>
       </c>
       <c r="G7" s="6" t="n">
         <v>131684974.1461452</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>3583341168.645234</v>
+        <v>3582901173.893623</v>
       </c>
       <c r="I7" s="7" t="n">
         <v>0.03650000241537366</v>
@@ -5250,7 +5468,7 @@
         <v>0.03693491707043663</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>374319.5082814827</v>
+        <v>374272.6793009383</v>
       </c>
       <c r="O7" s="3" t="n">
         <v>450593.1931929035</v>
@@ -5272,16 +5490,16 @@
         <v>109212118.7652359</v>
       </c>
       <c r="E8" s="6" t="n">
-        <v>78198703.5201842</v>
+        <v>78444345.91632521</v>
       </c>
       <c r="F8" s="6" t="n">
-        <v>69297142.12576202</v>
+        <v>69491495.08307031</v>
       </c>
       <c r="G8" s="6" t="n">
         <v>129926697.4882286</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>3577229601.132741</v>
+        <v>3576789605.779292</v>
       </c>
       <c r="I8" s="7" t="n">
         <v>0.03650000241537366</v>
@@ -5299,7 +5517,7 @@
         <v>0.03693491707043663</v>
       </c>
       <c r="N8" s="3" t="n">
-        <v>373669.0494405744</v>
+        <v>373622.2203959758</v>
       </c>
       <c r="O8" s="3" t="n">
         <v>450469.9897907797</v>
@@ -5321,16 +5539,16 @@
         <v>109413093.6674421</v>
       </c>
       <c r="E9" s="6" t="n">
-        <v>75725030.78440267</v>
+        <v>75981184.90509167</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>64115633.06430446</v>
+        <v>64299473.27260611</v>
       </c>
       <c r="G9" s="6" t="n">
         <v>129945312.0277757</v>
       </c>
       <c r="H9" s="6" t="n">
-        <v>3482111304.355217</v>
+        <v>3481671310.026226</v>
       </c>
       <c r="I9" s="7" t="n">
         <v>0.03650000241537366</v>
@@ -5348,7 +5566,7 @@
         <v>0.03693491707043663</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>363545.5358011322</v>
+        <v>363498.7068655675</v>
       </c>
       <c r="O9" s="3" t="n">
         <v>439555.1003258834</v>
@@ -5370,16 +5588,16 @@
         <v>109666118.9886243</v>
       </c>
       <c r="E10" s="6" t="n">
-        <v>62633764.42527747</v>
+        <v>62871817.87979747</v>
       </c>
       <c r="F10" s="6" t="n">
-        <v>71985346.18365841</v>
+        <v>72187288.206479</v>
       </c>
       <c r="G10" s="6" t="n">
         <v>129991339.9884334</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>3438062922.860942</v>
+        <v>3437622927.383602</v>
       </c>
       <c r="I10" s="7" t="n">
         <v>0.03650000241537366</v>
@@ -5397,7 +5615,7 @@
         <v>0.03693491707043663</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>358857.4326079512</v>
+        <v>358810.6035501668</v>
       </c>
       <c r="O10" s="3" t="n">
         <v>434343.0916681122</v>
@@ -5419,16 +5637,16 @@
         <v>109667151.3287632</v>
       </c>
       <c r="E11" s="6" t="n">
-        <v>65914408.62152216</v>
+        <v>66159636.42202716</v>
       </c>
       <c r="F11" s="6" t="n">
-        <v>69182310.83017388</v>
+        <v>69377077.90643525</v>
       </c>
       <c r="G11" s="6" t="n">
         <v>132866251.0455103</v>
       </c>
       <c r="H11" s="6" t="n">
-        <v>3232022985.161858</v>
+        <v>3231582990.285091</v>
       </c>
       <c r="I11" s="7" t="n">
         <v>0.03650000241537366</v>
@@ -5446,7 +5664,7 @@
         <v>0.03693491707043663</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>336928.4432312262</v>
+        <v>336881.6142373614</v>
       </c>
       <c r="O11" s="3" t="n">
         <v>412771.0234410728</v>
@@ -5468,16 +5686,16 @@
         <v>109729057.8747254</v>
       </c>
       <c r="E12" s="6" t="n">
-        <v>68822191.85959996</v>
+        <v>69079227.17738196</v>
       </c>
       <c r="F12" s="6" t="n">
-        <v>59598590.74937253</v>
+        <v>59781549.70206153</v>
       </c>
       <c r="G12" s="6" t="n">
         <v>133190285.3282568</v>
       </c>
       <c r="H12" s="6" t="n">
-        <v>3296854355.784049</v>
+        <v>3296414361.513577</v>
       </c>
       <c r="I12" s="7" t="n">
         <v>0.03650000241537366</v>
@@ -5495,7 +5713,7 @@
         <v>0.03693491707043663</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>343828.4959759949</v>
+        <v>343781.6670466586</v>
       </c>
       <c r="O12" s="3" t="n">
         <v>419001.6270619906</v>
@@ -5517,16 +5735,16 @@
         <v>109756088.3909883</v>
       </c>
       <c r="E13" s="6" t="n">
-        <v>46416747.2661341</v>
+        <v>46671865.5163491</v>
       </c>
       <c r="F13" s="6" t="n">
-        <v>62126087.28772155</v>
+        <v>62310963.43055655</v>
       </c>
       <c r="G13" s="6" t="n">
         <v>136081135.6656561</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>2564167970.277603</v>
+        <v>2563727975.884553</v>
       </c>
       <c r="I13" s="7" t="n">
         <v>0.03650000241537366</v>
@@ -5544,7 +5762,7 @@
         <v>0.03693491707043663</v>
       </c>
       <c r="N13" s="3" t="n">
-        <v>265848.1192409398</v>
+        <v>265801.2902985573</v>
       </c>
       <c r="O13" s="3" t="n">
         <v>339216.1773025376</v>
@@ -5566,16 +5784,16 @@
         <v>109737227.1714184</v>
       </c>
       <c r="E14" s="6" t="n">
-        <v>59621771.27202594</v>
+        <v>59879909.05062393</v>
       </c>
       <c r="F14" s="6" t="n">
-        <v>63144552.54356655</v>
+        <v>63326409.10121229</v>
       </c>
       <c r="G14" s="6" t="n">
         <v>136418480.8456975</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>3333245761.057378</v>
+        <v>3332805766.721134</v>
       </c>
       <c r="I14" s="7" t="n">
         <v>0.03650000241537366</v>
@@ -5593,7 +5811,7 @@
         <v>0.03693491707043663</v>
       </c>
       <c r="N14" s="3" t="n">
-        <v>347701.6612882871</v>
+        <v>347654.8323519505</v>
       </c>
       <c r="O14" s="3" t="n">
         <v>422617.4327683006</v>
@@ -5615,16 +5833,16 @@
         <v>109820179.5695339</v>
       </c>
       <c r="E15" s="6" t="n">
-        <v>62881956.35592515</v>
+        <v>63129621.93620015</v>
       </c>
       <c r="F15" s="6" t="n">
-        <v>67929925.5704889</v>
+        <v>68122254.95171708</v>
       </c>
       <c r="G15" s="6" t="n">
         <v>136520708.1372503</v>
       </c>
       <c r="H15" s="6" t="n">
-        <v>3477336061.802335</v>
+        <v>3476896066.840832</v>
       </c>
       <c r="I15" s="7" t="n">
         <v>0.03650000241537366</v>
@@ -5642,7 +5860,7 @@
         <v>0.03693491707043663</v>
       </c>
       <c r="N15" s="3" t="n">
-        <v>363037.3030556614</v>
+        <v>362990.4740527779</v>
       </c>
       <c r="O15" s="3" t="n">
         <v>438829.0783037072</v>
@@ -5664,16 +5882,16 @@
         <v>109824143.9731289</v>
       </c>
       <c r="E16" s="6" t="n">
-        <v>84921355.55294961</v>
+        <v>85182147.1144466</v>
       </c>
       <c r="F16" s="6" t="n">
-        <v>67458232.10747725</v>
+        <v>67637436.39746803</v>
       </c>
       <c r="G16" s="6" t="n">
         <v>146800932.9007985</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>3378762870.261068</v>
+        <v>3378322874.40958</v>
       </c>
       <c r="I16" s="7" t="n">
         <v>0.03650000241537366</v>
@@ -5691,7 +5909,7 @@
         <v>0.0368515837371033</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>352325.8733623142</v>
+        <v>352279.0442647091</v>
       </c>
       <c r="O16" s="3" t="n">
         <v>431507.6703348673</v>
@@ -5713,16 +5931,16 @@
         <v>109837230.945328</v>
       </c>
       <c r="E17" s="6" t="n">
-        <v>78116321.12843026</v>
+        <v>78378013.05490325</v>
       </c>
       <c r="F17" s="6" t="n">
-        <v>58043367.04671003</v>
+        <v>58221669.33521393</v>
       </c>
       <c r="G17" s="6" t="n">
         <v>146820705.7658038</v>
       </c>
       <c r="H17" s="6" t="n">
-        <v>3316629457.12973</v>
+        <v>3316189462.914753</v>
       </c>
       <c r="I17" s="7" t="n">
         <v>0.03650000241537366</v>
@@ -5740,7 +5958,7 @@
         <v>0.0368515837371033</v>
       </c>
       <c r="N17" s="3" t="n">
-        <v>345712.9663127756</v>
+        <v>345666.1373893456</v>
       </c>
       <c r="O17" s="3" t="n">
         <v>423171.9641792552</v>
@@ -5762,16 +5980,16 @@
         <v>109812101.2069135</v>
       </c>
       <c r="E18" s="6" t="n">
-        <v>85902407.14010979</v>
+        <v>86180523.00512178</v>
       </c>
       <c r="F18" s="6" t="n">
-        <v>60741445.97380174</v>
+        <v>60903325.82203438</v>
       </c>
       <c r="G18" s="6" t="n">
         <v>146084521.7500651</v>
       </c>
       <c r="H18" s="6" t="n">
-        <v>3307806010.553778</v>
+        <v>3307366014.840533</v>
       </c>
       <c r="I18" s="7" t="n">
         <v>0.03650000241537366</v>
@@ -5789,7 +6007,7 @@
         <v>0.0368515837371033</v>
       </c>
       <c r="N18" s="3" t="n">
-        <v>344773.8800929344</v>
+        <v>344727.0510100425</v>
       </c>
       <c r="O18" s="3" t="n">
         <v>423267.6885049809</v>
@@ -5811,16 +6029,16 @@
         <v>109817281.9042201</v>
       </c>
       <c r="E19" s="6" t="n">
-        <v>63272317.16911007</v>
+        <v>63532399.84881508</v>
       </c>
       <c r="F19" s="6" t="n">
-        <v>58432587.64789255</v>
+        <v>58612499.0866286</v>
       </c>
       <c r="G19" s="6" t="n">
         <v>174559965.1979237</v>
       </c>
       <c r="H19" s="6" t="n">
-        <v>3342721847.790328</v>
+        <v>3342281853.671886</v>
       </c>
       <c r="I19" s="7" t="n">
         <v>0.03650000241537366</v>
@@ -5838,7 +6056,7 @@
         <v>0.0368515837371033</v>
       </c>
       <c r="N19" s="3" t="n">
-        <v>348489.9995617628</v>
+        <v>348443.1706486071</v>
       </c>
       <c r="O19" s="3" t="n">
         <v>427360.7512641225</v>
@@ -5860,16 +6078,16 @@
         <v>109861276.5733739</v>
       </c>
       <c r="E20" s="6" t="n">
-        <v>88511698.91894951</v>
+        <v>88822044.70791052</v>
       </c>
       <c r="F20" s="6" t="n">
-        <v>42181809.13057283</v>
+        <v>42311463.37438669</v>
       </c>
       <c r="G20" s="6" t="n">
         <v>169618722.6830847</v>
       </c>
       <c r="H20" s="6" t="n">
-        <v>3374734736.272226</v>
+        <v>3374294736.239451</v>
       </c>
       <c r="I20" s="7" t="n">
         <v>0.03650000241537366</v>
@@ -5887,7 +6105,7 @@
         <v>0.0368515837371033</v>
       </c>
       <c r="N20" s="3" t="n">
-        <v>351897.1559571559</v>
+        <v>351850.3264145331</v>
       </c>
       <c r="O20" s="3" t="n">
         <v>431203.3537667908</v>
@@ -5909,16 +6127,16 @@
         <v>109944218.3095993</v>
       </c>
       <c r="E21" s="6" t="n">
-        <v>87033668.77329952</v>
+        <v>87324941.35505652</v>
       </c>
       <c r="F21" s="6" t="n">
-        <v>51954304.76465927</v>
+        <v>52103028.76518045</v>
       </c>
       <c r="G21" s="6" t="n">
         <v>172338153.0245515</v>
       </c>
       <c r="H21" s="6" t="n">
-        <v>3372689032.943098</v>
+        <v>3372249036.36082</v>
       </c>
       <c r="I21" s="7" t="n">
         <v>0.03650000241537366</v>
@@ -5936,7 +6154,7 @@
         <v>0.0368515837371033</v>
       </c>
       <c r="N21" s="3" t="n">
-        <v>351679.4301750899</v>
+        <v>351632.6009997061</v>
       </c>
       <c r="O21" s="3" t="n">
         <v>432166.6729598901</v>
@@ -5958,16 +6176,16 @@
         <v>110151080.1866189</v>
       </c>
       <c r="E22" s="6" t="n">
-        <v>87868461.85445462</v>
+        <v>88161184.05425063</v>
       </c>
       <c r="F22" s="6" t="n">
-        <v>60263592.76517375</v>
+        <v>60410870.33975412</v>
       </c>
       <c r="G22" s="6" t="n">
         <v>162877756.5589872</v>
       </c>
       <c r="H22" s="6" t="n">
-        <v>3351939631.25432</v>
+        <v>3351499631.479944</v>
       </c>
       <c r="I22" s="7" t="n">
         <v>0.03650000241537366</v>
@@ -5985,7 +6203,7 @@
         <v>0.0368515837371033</v>
       </c>
       <c r="N22" s="3" t="n">
-        <v>349471.0553605374</v>
+        <v>349424.2258454161</v>
       </c>
       <c r="O22" s="3" t="n">
         <v>429946.6489242385</v>
@@ -6007,16 +6225,16 @@
         <v>110145162.8914285</v>
       </c>
       <c r="E23" s="6" t="n">
-        <v>89081856.06629945</v>
+        <v>89402812.06936745</v>
       </c>
       <c r="F23" s="6" t="n">
-        <v>42740384.84050981</v>
+        <v>42859433.25500631</v>
       </c>
       <c r="G23" s="6" t="n">
         <v>231737478.377994</v>
       </c>
       <c r="H23" s="6" t="n">
-        <v>3507020842.800418</v>
+        <v>3506580838.382854</v>
       </c>
       <c r="I23" s="7" t="n">
         <v>0.03650000241537366</v>
@@ -6034,7 +6252,7 @@
         <v>0.03676825040376996</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>365756.2416435395</v>
+        <v>365709.4116342401</v>
       </c>
       <c r="O23" s="3" t="n">
         <v>451824.132648079</v>
@@ -6056,16 +6274,16 @@
         <v>110135980.040481</v>
       </c>
       <c r="E24" s="6" t="n">
-        <v>90072399.6267707</v>
+        <v>90391669.8087067</v>
       </c>
       <c r="F24" s="6" t="n">
-        <v>56943828.95422778</v>
+        <v>57064571.04109526</v>
       </c>
       <c r="G24" s="6" t="n">
         <v>229182741.6867744</v>
       </c>
       <c r="H24" s="6" t="n">
-        <v>3463785946.00189</v>
+        <v>3463345933.733087</v>
       </c>
       <c r="I24" s="7" t="n">
         <v>0.03650000241537366</v>
@@ -6083,7 +6301,7 @@
         <v>0.03676825040376996</v>
       </c>
       <c r="N24" s="3" t="n">
-        <v>361154.7182535286</v>
+        <v>361107.8874086158</v>
       </c>
       <c r="O24" s="3" t="n">
         <v>448566.8371441148</v>
@@ -6105,16 +6323,16 @@
         <v>110063401.5573106</v>
       </c>
       <c r="E25" s="6" t="n">
-        <v>90207535.65130401</v>
+        <v>90542938.88715301</v>
       </c>
       <c r="F25" s="6" t="n">
-        <v>51602034.69547939</v>
+        <v>51706647.45903745</v>
       </c>
       <c r="G25" s="6" t="n">
         <v>230888253.3173563</v>
       </c>
       <c r="H25" s="6" t="n">
-        <v>3205941602.598647</v>
+        <v>3205501586.59924</v>
       </c>
       <c r="I25" s="7" t="n">
         <v>0.03650000241537366</v>
@@ -6132,7 +6350,7 @@
         <v>0.03676825040376996</v>
       </c>
       <c r="N25" s="3" t="n">
-        <v>333712.1460489289</v>
+        <v>333665.3148069651</v>
       </c>
       <c r="O25" s="3" t="n">
         <v>420743.9106240411</v>
@@ -6154,16 +6372,16 @@
         <v>110201806.0378861</v>
       </c>
       <c r="E26" s="6" t="n">
-        <v>90137880.50639333</v>
+        <v>90469977.96395934</v>
       </c>
       <c r="F26" s="6" t="n">
-        <v>53876705.01782864</v>
+        <v>53984623.44056258</v>
       </c>
       <c r="G26" s="6" t="n">
         <v>254742493.5135711</v>
       </c>
       <c r="H26" s="6" t="n">
-        <v>3124170851.965993</v>
+        <v>3123730836.085693</v>
       </c>
       <c r="I26" s="7" t="n">
         <v>0.03650000241537366</v>
@@ -6181,7 +6399,7 @@
         <v>0.03676825040376996</v>
       </c>
       <c r="N26" s="3" t="n">
-        <v>325009.2220334444</v>
+        <v>324962.3908041572</v>
       </c>
       <c r="O26" s="3" t="n">
         <v>414829.2237389592</v>
@@ -6203,16 +6421,16 @@
         <v>110246348.1665363</v>
       </c>
       <c r="E27" s="6" t="n">
-        <v>90683527.73142503</v>
+        <v>91027822.88844904</v>
       </c>
       <c r="F27" s="6" t="n">
-        <v>60950192.97977956</v>
+        <v>61045926.01292147</v>
       </c>
       <c r="G27" s="6" t="n">
         <v>239797730.4064276</v>
       </c>
       <c r="H27" s="6" t="n">
-        <v>3633642090.151248</v>
+        <v>3633202061.961082</v>
       </c>
       <c r="I27" s="7" t="n">
         <v>0.03650000241537366</v>
@@ -6230,7 +6448,7 @@
         <v>0.03676825040376996</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>379232.6385937233</v>
+        <v>379185.8060542876</v>
       </c>
       <c r="O27" s="3" t="n">
         <v>468277.7087264755</v>
@@ -6252,16 +6470,16 @@
         <v>110397429.3795781</v>
       </c>
       <c r="E28" s="6" t="n">
-        <v>90958523.65549019</v>
+        <v>91306691.58331019</v>
       </c>
       <c r="F28" s="6" t="n">
-        <v>64022634.63846193</v>
+        <v>64114506.36868194</v>
       </c>
       <c r="G28" s="6" t="n">
         <v>240130221.5557107</v>
       </c>
       <c r="H28" s="6" t="n">
-        <v>3613109775.02256</v>
+        <v>3612669735.36452</v>
       </c>
       <c r="I28" s="7" t="n">
         <v>0.03650000241537366</v>
@@ -6279,7 +6497,7 @@
         <v>0.03676825040376996</v>
       </c>
       <c r="N28" s="3" t="n">
-        <v>377047.368469083</v>
+        <v>377000.5347091127</v>
       </c>
       <c r="O28" s="3" t="n">
         <v>466500.1759430798</v>
@@ -6301,16 +6519,16 @@
         <v>110459412.1575361</v>
       </c>
       <c r="E29" s="6" t="n">
-        <v>91000613.80843022</v>
+        <v>91350355.52528024</v>
       </c>
       <c r="F29" s="6" t="n">
-        <v>63901753.89657893</v>
+        <v>63992052.9462667</v>
       </c>
       <c r="G29" s="6" t="n">
         <v>243572783.8200219</v>
       </c>
       <c r="H29" s="6" t="n">
-        <v>3628217354.598102</v>
+        <v>3627777313.831564</v>
       </c>
       <c r="I29" s="7" t="n">
         <v>0.03650000241537366</v>
@@ -6328,7 +6546,7 @@
         <v>0.03676825040376996</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>378655.279807631</v>
+        <v>378608.4459296824</v>
       </c>
       <c r="O29" s="3" t="n">
         <v>468472.6929685309</v>
@@ -6350,16 +6568,16 @@
         <v>110548351.2880701</v>
       </c>
       <c r="E30" s="6" t="n">
-        <v>90132356.81756249</v>
+        <v>90447819.29369049</v>
       </c>
       <c r="F30" s="6" t="n">
-        <v>65846944.15199657</v>
+        <v>65971496.3634856</v>
       </c>
       <c r="G30" s="6" t="n">
         <v>245605231.7022537</v>
       </c>
       <c r="H30" s="6" t="n">
-        <v>3622578869.287579</v>
+        <v>3622138854.599961</v>
       </c>
       <c r="I30" s="7" t="n">
         <v>0.03650000241537366</v>
@@ -6377,7 +6595,7 @@
         <v>0.03676825040376996</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>378055.1714701112</v>
+        <v>378008.3403677623</v>
       </c>
       <c r="O30" s="3" t="n">
         <v>468212.9843232642</v>
@@ -6399,16 +6617,16 @@
         <v>110567333.2809158</v>
       </c>
       <c r="E31" s="6" t="n">
-        <v>91214545.99128646</v>
+        <v>91552934.04846945</v>
       </c>
       <c r="F31" s="6" t="n">
-        <v>71416697.68580709</v>
+        <v>71518357.0439785</v>
       </c>
       <c r="G31" s="6" t="n">
         <v>179571549.4489093</v>
       </c>
       <c r="H31" s="6" t="n">
-        <v>3413429322.143122</v>
+        <v>3412989274.727767</v>
       </c>
       <c r="I31" s="7" t="n">
         <v>0.03600000425292382</v>
@@ -6426,7 +6644,7 @@
         <v>0.03668466737761376</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>352383.5789754955</v>
+        <v>352337.3261667297</v>
       </c>
       <c r="O31" s="3" t="n">
         <v>435181.9142288258</v>
@@ -6448,16 +6666,16 @@
         <v>110810390.8233007</v>
       </c>
       <c r="E32" s="6" t="n">
-        <v>91260440.13070874</v>
+        <v>92620030.42800373</v>
       </c>
       <c r="F32" s="6" t="n">
-        <v>74954030.44580247</v>
+        <v>75064444.32358976</v>
       </c>
       <c r="G32" s="6" t="n">
         <v>206116586.0471416</v>
       </c>
       <c r="H32" s="6" t="n">
-        <v>3252967949.895449</v>
+        <v>3251497945.720366</v>
       </c>
       <c r="I32" s="7" t="n">
         <v>0.03600000425292382</v>
@@ -6475,7 +6693,7 @@
         <v>0.03668466737761376</v>
       </c>
       <c r="N32" s="3" t="n">
-        <v>335517.6938324182</v>
+        <v>335363.1836146039</v>
       </c>
       <c r="O32" s="3" t="n">
         <v>421508.318950465</v>
@@ -6497,16 +6715,16 @@
         <v>110784766.9258687</v>
       </c>
       <c r="E33" s="6" t="n">
-        <v>90992031.3551863</v>
+        <v>92236283.99807629</v>
       </c>
       <c r="F33" s="6" t="n">
-        <v>75076806.84493634</v>
+        <v>75302434.82539035</v>
       </c>
       <c r="G33" s="6" t="n">
         <v>248420857.3449725</v>
       </c>
       <c r="H33" s="6" t="n">
-        <v>3221477558.745079</v>
+        <v>3220007678.121735</v>
       </c>
       <c r="I33" s="7" t="n">
         <v>0.03600000425292382</v>
@@ -6524,7 +6742,7 @@
         <v>0.03668466737761376</v>
       </c>
       <c r="N33" s="3" t="n">
-        <v>332207.7799708258</v>
+        <v>332053.2827393732</v>
       </c>
       <c r="O33" s="3" t="n">
         <v>422626.9512378465</v>
@@ -6546,16 +6764,16 @@
         <v>110800643.1083902</v>
       </c>
       <c r="E34" s="6" t="n">
-        <v>89742687.66481608</v>
+        <v>90968267.09769209</v>
       </c>
       <c r="F34" s="6" t="n">
-        <v>75116667.49366367</v>
+        <v>75361032.66147675</v>
       </c>
       <c r="G34" s="6" t="n">
         <v>303291142.7334828</v>
       </c>
       <c r="H34" s="6" t="n">
-        <v>3246872717.915842</v>
+        <v>3245402773.315153</v>
       </c>
       <c r="I34" s="7" t="n">
         <v>0.03600000425292382</v>
@@ -6573,7 +6791,7 @@
         <v>0.03668466737761376</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>334877.0319644032</v>
+        <v>334722.5280083754</v>
       </c>
       <c r="O34" s="3" t="n">
         <v>430938.0887659761</v>
@@ -6595,16 +6813,16 @@
         <v>110800910.0818387</v>
       </c>
       <c r="E35" s="6" t="n">
-        <v>89921451.17719229</v>
+        <v>91290713.85405229</v>
       </c>
       <c r="F35" s="6" t="n">
-        <v>72969997.84221481</v>
+        <v>73070804.63810319</v>
       </c>
       <c r="G35" s="6" t="n">
         <v>295800536.4468129</v>
       </c>
       <c r="H35" s="6" t="n">
-        <v>3224509478.620773</v>
+        <v>3223039409.148025</v>
       </c>
       <c r="I35" s="7" t="n">
         <v>0.03600000425292382</v>
@@ -6622,7 +6840,7 @@
         <v>0.03668466737761376</v>
       </c>
       <c r="N35" s="3" t="n">
-        <v>332526.4611067913</v>
+        <v>332371.9440256246</v>
       </c>
       <c r="O35" s="3" t="n">
         <v>427593.374089083</v>
@@ -6644,16 +6862,16 @@
         <v>110840456.802935</v>
       </c>
       <c r="E36" s="6" t="n">
-        <v>90106496.23897925</v>
+        <v>91478373.60984924</v>
       </c>
       <c r="F36" s="6" t="n">
-        <v>73041937.31867403</v>
+        <v>73140128.86641257</v>
       </c>
       <c r="G36" s="6" t="n">
         <v>289518568.352541</v>
       </c>
       <c r="H36" s="6" t="n">
-        <v>3218414966.682919</v>
+        <v>3216944897.76431</v>
       </c>
       <c r="I36" s="7" t="n">
         <v>0.03600000425292382</v>
@@ -6671,7 +6889,7 @@
         <v>0.03668466737761376</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>331885.8749214238</v>
+        <v>331731.357898502</v>
       </c>
       <c r="O36" s="3" t="n">
         <v>426323.6664598752</v>
@@ -6696,7 +6914,7 @@
       <c r="L38" t="inlineStr"/>
       <c r="M38" t="inlineStr"/>
       <c r="N38" s="12" t="n">
-        <v>10827488.55337466</v>
+        <v>10825499.00626334</v>
       </c>
       <c r="O38" s="12" t="n">
         <v>13391864.98596525</v>

--- a/settlements/spark/2026-05/spark_settlement_may_2026.xlsx
+++ b/settlements/spark/2026-05/spark_settlement_may_2026.xlsx
@@ -491,7 +491,7 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>13408944.7424591</v>
+        <v>13408944.74245897</v>
       </c>
     </row>
     <row r="5">
@@ -517,7 +517,7 @@
     <row r="7">
       <c r="A7" t="inlineStr"/>
       <c r="B7" s="4" t="n">
-        <v>15160063.72185784</v>
+        <v>15160063.72185771</v>
       </c>
     </row>
     <row r="9">
@@ -539,7 +539,7 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>10642578.13467968</v>
+        <v>10640588.58756836</v>
       </c>
     </row>
     <row r="11">
@@ -549,13 +549,13 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>40550.6842112442</v>
+        <v>40533.95751528406</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr"/>
       <c r="B12" s="4" t="n">
-        <v>10683128.81889092</v>
+        <v>10681122.54508365</v>
       </c>
     </row>
     <row r="14">
@@ -577,7 +577,7 @@
         </is>
       </c>
       <c r="B15" s="3" t="n">
-        <v>10642578.13467968</v>
+        <v>10640588.58756836</v>
       </c>
     </row>
     <row r="16">
@@ -587,7 +587,7 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>-2749286.851285571</v>
+        <v>-2751276.398396889</v>
       </c>
     </row>
     <row r="17">
@@ -625,7 +625,7 @@
         </is>
       </c>
       <c r="B22" s="3" t="n">
-        <v>13408944.7424591</v>
+        <v>13408944.74245897</v>
       </c>
     </row>
     <row r="23">
@@ -635,13 +635,13 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>-10642578.13467968</v>
+        <v>-10640588.58756836</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr"/>
       <c r="B24" s="4" t="n">
-        <v>1386055.476326641</v>
+        <v>1388045.023437823</v>
       </c>
     </row>
     <row r="26">
@@ -676,7 +676,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-06-25T22:38:11+00:00</t>
+          <t>2026-07-07T00:55:42+00:00</t>
         </is>
       </c>
     </row>
@@ -703,7 +703,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S62"/>
+  <dimension ref="A1:S64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -855,13 +855,13 @@
         <v>-145686527.279134</v>
       </c>
       <c r="H2" s="6" t="n">
-        <v>3834450.909129127</v>
+        <v>3834450.909129192</v>
       </c>
       <c r="I2" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J2" s="6" t="n">
-        <v>3834450.909129127</v>
+        <v>3834450.909129192</v>
       </c>
       <c r="K2" s="6" t="n">
         <v>0</v>
@@ -873,13 +873,13 @@
         <v>1</v>
       </c>
       <c r="N2" s="6" t="n">
-        <v>4330990.330089472</v>
+        <v>4330194.512180462</v>
       </c>
       <c r="O2" s="6" t="n">
-        <v>4330990.330089472</v>
+        <v>4330194.512180462</v>
       </c>
       <c r="P2" s="6" t="n">
-        <v>-496539.4209603447</v>
+        <v>-495743.6030512699</v>
       </c>
       <c r="Q2" s="6" t="n">
         <v>0</v>
@@ -938,13 +938,13 @@
         <v>1</v>
       </c>
       <c r="N3" s="6" t="n">
-        <v>1530671.037066013</v>
+        <v>1530389.776815756</v>
       </c>
       <c r="O3" s="6" t="n">
-        <v>1530671.037066013</v>
+        <v>1530389.776815756</v>
       </c>
       <c r="P3" s="6" t="n">
-        <v>337441.1311699869</v>
+        <v>337722.3914202435</v>
       </c>
       <c r="Q3" s="6" t="n">
         <v>0</v>
@@ -985,13 +985,13 @@
         <v>-414722895.155028</v>
       </c>
       <c r="H4" s="6" t="n">
-        <v>3091580</v>
+        <v>3091579.99999999</v>
       </c>
       <c r="I4" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J4" s="6" t="n">
-        <v>3091580</v>
+        <v>3091579.99999999</v>
       </c>
       <c r="K4" s="6" t="n">
         <v>0</v>
@@ -1003,13 +1003,13 @@
         <v>1</v>
       </c>
       <c r="N4" s="6" t="n">
-        <v>1402432.876722047</v>
+        <v>1402175.18018744</v>
       </c>
       <c r="O4" s="6" t="n">
-        <v>1402432.876722047</v>
+        <v>1402175.18018744</v>
       </c>
       <c r="P4" s="6" t="n">
-        <v>1689147.123277953</v>
+        <v>1689404.81981255</v>
       </c>
       <c r="Q4" s="6" t="n">
         <v>0</v>
@@ -1050,13 +1050,13 @@
         <v>125242118.592976</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>-194444.4444439532</v>
+        <v>-194444.4444439746</v>
       </c>
       <c r="I5" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>-194444.4444439532</v>
+        <v>-194444.4444439746</v>
       </c>
       <c r="K5" s="6" t="n">
         <v>0</v>
@@ -1068,13 +1068,13 @@
         <v>1</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>1229915.171946168</v>
+        <v>1229689.175477509</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>1229915.171946168</v>
+        <v>1229689.175477509</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>-1424359.616390121</v>
+        <v>-1424133.619921484</v>
       </c>
       <c r="Q5" s="6" t="n">
         <v>0</v>
@@ -1133,13 +1133,13 @@
         <v>1</v>
       </c>
       <c r="N6" s="6" t="n">
-        <v>409131.1364512742</v>
+        <v>409055.9587527096</v>
       </c>
       <c r="O6" s="6" t="n">
-        <v>409131.1364512742</v>
+        <v>409055.9587527096</v>
       </c>
       <c r="P6" s="6" t="n">
-        <v>150321.8027899452</v>
+        <v>150396.9804885097</v>
       </c>
       <c r="Q6" s="6" t="n">
         <v>86642406.62655522</v>
@@ -1202,13 +1202,13 @@
         <v>1</v>
       </c>
       <c r="N7" s="6" t="n">
-        <v>326596.3279090599</v>
+        <v>326536.3159517574</v>
       </c>
       <c r="O7" s="6" t="n">
-        <v>290131.5140672624</v>
+        <v>290071.5021099598</v>
       </c>
       <c r="P7" s="6" t="n">
-        <v>109446.7210059646</v>
+        <v>109506.7329632671</v>
       </c>
       <c r="Q7" s="6" t="n">
         <v>0</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="N8" s="6" t="n">
-        <v>239439.2496962347</v>
+        <v>239395.2528205769</v>
       </c>
       <c r="O8" s="6" t="n">
-        <v>239439.2496962347</v>
+        <v>239395.2528205769</v>
       </c>
       <c r="P8" s="6" t="n">
-        <v>184091.3588869669</v>
+        <v>184135.3557626247</v>
       </c>
       <c r="Q8" s="6" t="n">
         <v>0</v>
@@ -1332,13 +1332,13 @@
         <v>1</v>
       </c>
       <c r="N9" s="6" t="n">
-        <v>227865.8090060199</v>
+        <v>227823.9387459091</v>
       </c>
       <c r="O9" s="6" t="n">
-        <v>227865.8090060199</v>
+        <v>227823.9387459091</v>
       </c>
       <c r="P9" s="6" t="n">
-        <v>-198861.8383060199</v>
+        <v>-198819.9680459091</v>
       </c>
       <c r="Q9" s="6" t="n">
         <v>0</v>
@@ -1397,13 +1397,13 @@
         <v>1</v>
       </c>
       <c r="N10" s="6" t="n">
-        <v>227862.0364015236</v>
+        <v>227820.1668346276</v>
       </c>
       <c r="O10" s="6" t="n">
-        <v>227862.0364015236</v>
+        <v>227820.1668346276</v>
       </c>
       <c r="P10" s="6" t="n">
-        <v>-221476.1525298833</v>
+        <v>-221434.2829629873</v>
       </c>
       <c r="Q10" s="6" t="n">
         <v>0</v>
@@ -1462,13 +1462,13 @@
         <v>1</v>
       </c>
       <c r="N11" s="6" t="n">
-        <v>232516.1966087057</v>
+        <v>232473.4718415524</v>
       </c>
       <c r="O11" s="6" t="n">
-        <v>206555.5255906894</v>
+        <v>206512.8008235362</v>
       </c>
       <c r="P11" s="6" t="n">
-        <v>77919.23278049534</v>
+        <v>77961.95754764859</v>
       </c>
       <c r="Q11" s="6" t="n">
         <v>0</v>
@@ -1509,31 +1509,31 @@
         <v>20232922.14688502</v>
       </c>
       <c r="H12" s="6" t="n">
-        <v>217269.3964465584</v>
+        <v>217269.396446639</v>
       </c>
       <c r="I12" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J12" s="6" t="n">
-        <v>217269.3964465584</v>
+        <v>217269.396446639</v>
       </c>
       <c r="K12" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L12" s="6" t="n">
-        <v>89619946.74579927</v>
+        <v>89619946.74579926</v>
       </c>
       <c r="M12" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N12" s="6" t="n">
-        <v>204212.920107537</v>
+        <v>204175.396057219</v>
       </c>
       <c r="O12" s="6" t="n">
-        <v>204212.920107537</v>
+        <v>204175.396057219</v>
       </c>
       <c r="P12" s="6" t="n">
-        <v>13056.47633902135</v>
+        <v>13094.00038941996</v>
       </c>
       <c r="Q12" s="6" t="n">
         <v>0</v>
@@ -1592,13 +1592,13 @@
         <v>1</v>
       </c>
       <c r="N13" s="6" t="n">
-        <v>172660.297391215</v>
+        <v>172628.5711239259</v>
       </c>
       <c r="O13" s="6" t="n">
-        <v>153382.5987025966</v>
+        <v>153350.8724353075</v>
       </c>
       <c r="P13" s="6" t="n">
-        <v>57860.73443742163</v>
+        <v>57892.46070471073</v>
       </c>
       <c r="Q13" s="6" t="n">
         <v>0</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="N14" s="6" t="n">
-        <v>131549.9035353575</v>
+        <v>131525.7312880923</v>
       </c>
       <c r="O14" s="6" t="n">
-        <v>131549.9035353575</v>
+        <v>131525.7312880923</v>
       </c>
       <c r="P14" s="6" t="n">
-        <v>162541.6133410866</v>
+        <v>162565.7855883517</v>
       </c>
       <c r="Q14" s="6" t="n">
         <v>103099818.9104406</v>
@@ -1787,13 +1787,13 @@
         <v>1</v>
       </c>
       <c r="N16" s="6" t="n">
-        <v>67614.51679630503</v>
+        <v>67602.09265326281</v>
       </c>
       <c r="O16" s="6" t="n">
-        <v>67614.51679630503</v>
+        <v>67602.09265326281</v>
       </c>
       <c r="P16" s="6" t="n">
-        <v>52027.10112966759</v>
+        <v>52039.52527270982</v>
       </c>
       <c r="Q16" s="6" t="n">
         <v>0</v>
@@ -1921,13 +1921,13 @@
         <v>1</v>
       </c>
       <c r="N18" s="6" t="n">
-        <v>21683.89345855882</v>
+        <v>21679.90905096699</v>
       </c>
       <c r="O18" s="6" t="n">
-        <v>21683.89345855882</v>
+        <v>21679.90905096699</v>
       </c>
       <c r="P18" s="6" t="n">
-        <v>17.57804413878375</v>
+        <v>21.56245173062087</v>
       </c>
       <c r="Q18" s="6" t="n">
         <v>0</v>
@@ -1986,13 +1986,13 @@
         <v>1</v>
       </c>
       <c r="N19" s="6" t="n">
-        <v>21246.29901513504</v>
+        <v>21242.39501536415</v>
       </c>
       <c r="O19" s="6" t="n">
-        <v>21246.29901513504</v>
+        <v>21242.39501536415</v>
       </c>
       <c r="P19" s="6" t="n">
-        <v>11256.60433786496</v>
+        <v>11260.50833763585</v>
       </c>
       <c r="Q19" s="6" t="n">
         <v>0</v>
@@ -2033,31 +2033,31 @@
         <v>-2423.291386</v>
       </c>
       <c r="H20" s="6" t="n">
-        <v>2.228968e-09</v>
+        <v>-9.21792e-10</v>
       </c>
       <c r="I20" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J20" s="6" t="n">
-        <v>2.228968e-09</v>
+        <v>-9.21792e-10</v>
       </c>
       <c r="K20" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L20" s="6" t="n">
-        <v>4999001.686505451</v>
+        <v>4999001.686505452</v>
       </c>
       <c r="M20" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N20" s="6" t="n">
-        <v>11390.99909219295</v>
+        <v>11388.90600022364</v>
       </c>
       <c r="O20" s="6" t="n">
-        <v>11390.99909219295</v>
+        <v>11388.90600022364</v>
       </c>
       <c r="P20" s="6" t="n">
-        <v>-11390.99909219072</v>
+        <v>-11388.90600022456</v>
       </c>
       <c r="Q20" s="6" t="n">
         <v>0</v>
@@ -2116,13 +2116,13 @@
         <v>1</v>
       </c>
       <c r="N21" s="6" t="n">
-        <v>11390.24695113189</v>
+        <v>11388.15399736822</v>
       </c>
       <c r="O21" s="6" t="n">
-        <v>11390.24695113189</v>
+        <v>11388.15399736822</v>
       </c>
       <c r="P21" s="6" t="n">
-        <v>-11390.2469511317</v>
+        <v>-11388.15399736804</v>
       </c>
       <c r="Q21" s="6" t="n">
         <v>0</v>
@@ -2181,13 +2181,13 @@
         <v>1</v>
       </c>
       <c r="N22" s="6" t="n">
-        <v>11388.13494028817</v>
+        <v>11386.04237460573</v>
       </c>
       <c r="O22" s="6" t="n">
-        <v>11388.13494028817</v>
+        <v>11386.04237460573</v>
       </c>
       <c r="P22" s="6" t="n">
-        <v>-11388.13494028817</v>
+        <v>-11386.04237460573</v>
       </c>
       <c r="Q22" s="6" t="n">
         <v>0</v>
@@ -2228,13 +2228,13 @@
         <v>-34185.096267</v>
       </c>
       <c r="H23" s="6" t="n">
-        <v>4.7e-10</v>
+        <v>5.4e-10</v>
       </c>
       <c r="I23" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J23" s="6" t="n">
-        <v>4.7e-10</v>
+        <v>5.4e-10</v>
       </c>
       <c r="K23" s="6" t="n">
         <v>0</v>
@@ -2246,13 +2246,13 @@
         <v>1</v>
       </c>
       <c r="N23" s="6" t="n">
-        <v>11289.67890469889</v>
+        <v>11287.60443027744</v>
       </c>
       <c r="O23" s="6" t="n">
-        <v>11289.67890469889</v>
+        <v>11287.60443027744</v>
       </c>
       <c r="P23" s="6" t="n">
-        <v>-11289.67890469842</v>
+        <v>-11287.6044302769</v>
       </c>
       <c r="Q23" s="6" t="n">
         <v>0</v>
@@ -2293,31 +2293,31 @@
         <v>2796996.33696637</v>
       </c>
       <c r="H24" s="6" t="n">
-        <v>4804.888180144989</v>
+        <v>4804.88818014498</v>
       </c>
       <c r="I24" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J24" s="6" t="n">
-        <v>4804.888180144989</v>
+        <v>4804.88818014498</v>
       </c>
       <c r="K24" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L24" s="6" t="n">
-        <v>1492032.349781685</v>
+        <v>1492032.349781683</v>
       </c>
       <c r="M24" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N24" s="6" t="n">
-        <v>3399.826646941293</v>
+        <v>3399.201930022765</v>
       </c>
       <c r="O24" s="6" t="n">
-        <v>3399.826646941293</v>
+        <v>3399.201930022765</v>
       </c>
       <c r="P24" s="6" t="n">
-        <v>1405.061533203695</v>
+        <v>1405.686250122215</v>
       </c>
       <c r="Q24" s="6" t="n">
         <v>0</v>
@@ -2376,13 +2376,13 @@
         <v>1</v>
       </c>
       <c r="N25" s="6" t="n">
-        <v>2238.56910760877</v>
+        <v>2238.15777134371</v>
       </c>
       <c r="O25" s="6" t="n">
-        <v>1988.630578588682</v>
+        <v>1988.219242323622</v>
       </c>
       <c r="P25" s="6" t="n">
-        <v>750.1739230860217</v>
+        <v>750.585259351082</v>
       </c>
       <c r="Q25" s="6" t="n">
         <v>0</v>
@@ -2395,12 +2395,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>S12</t>
+          <t>S62</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Spark DAI Vault (Morpho)</t>
+          <t>Spark.fi USDT Reserve Uniswap V4 (USDT/USDS)</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2410,67 +2410,71 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>F</t>
         </is>
       </c>
       <c r="E26" s="6" t="n">
-        <v>458.5728307677575</v>
+        <v>219995.8104343477</v>
       </c>
       <c r="F26" s="6" t="n">
-        <v>539.8728953809741</v>
+        <v>1250066.267840007</v>
       </c>
       <c r="G26" s="6" t="n">
-        <v>81.30006461321658</v>
+        <v>1030070.45740566</v>
       </c>
       <c r="H26" s="6" t="n">
-        <v>76.33046551920575</v>
+        <v>-16.66956268247493</v>
       </c>
       <c r="I26" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J26" s="6" t="n">
-        <v>76.33046551920575</v>
+        <v>0</v>
       </c>
       <c r="K26" s="6" t="n">
-        <v>0</v>
+        <v>-16.66956268247493</v>
       </c>
       <c r="L26" s="6" t="n">
-        <v>462.161691889013</v>
+        <v>386130.3073909548</v>
       </c>
       <c r="M26" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N26" s="6" t="n">
-        <v>1.053106948726445</v>
+        <v>0</v>
       </c>
       <c r="O26" s="6" t="n">
-        <v>1.053106948726445</v>
+        <v>-16.66956268247493</v>
       </c>
       <c r="P26" s="6" t="n">
-        <v>75.27735857047929</v>
+        <v>0</v>
       </c>
       <c r="Q26" s="6" t="n">
-        <v>0</v>
+        <v>386130.3073909548</v>
       </c>
       <c r="R26" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="S26" t="inlineStr"/>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>SDE (fixed)</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>S34</t>
+          <t>S12</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Spark USDC Vault (Morpho, Base)</t>
+          <t>Spark DAI Vault (Morpho)</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>base</t>
+          <t>ethereum</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -2479,40 +2483,40 @@
         </is>
       </c>
       <c r="E27" s="6" t="n">
-        <v>224.7175624853434</v>
+        <v>458.5728307677575</v>
       </c>
       <c r="F27" s="6" t="n">
-        <v>424.9110349025811</v>
+        <v>539.8728953809741</v>
       </c>
       <c r="G27" s="6" t="n">
-        <v>200.1934724172377</v>
+        <v>81.30006461321658</v>
       </c>
       <c r="H27" s="6" t="n">
-        <v>1.161345275337778</v>
+        <v>76.33046551920575</v>
       </c>
       <c r="I27" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J27" s="6" t="n">
-        <v>1.161345275337778</v>
+        <v>76.33046551920575</v>
       </c>
       <c r="K27" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L27" s="6" t="n">
-        <v>368.0420981576889</v>
+        <v>462.161691889013</v>
       </c>
       <c r="M27" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N27" s="6" t="n">
-        <v>0.8386408865034203</v>
+        <v>1.052913440704947</v>
       </c>
       <c r="O27" s="6" t="n">
-        <v>0.8386408865034203</v>
+        <v>1.052913440704947</v>
       </c>
       <c r="P27" s="6" t="n">
-        <v>0.3227043888343578</v>
+        <v>75.27755207850079</v>
       </c>
       <c r="Q27" s="6" t="n">
         <v>0</v>
@@ -2525,12 +2529,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>S36</t>
+          <t>S34</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Fluid Savings USDS (fsUSDS, Base)</t>
+          <t>Spark USDC Vault (Morpho, Base)</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2544,40 +2548,40 @@
         </is>
       </c>
       <c r="E28" s="6" t="n">
-        <v>283.8972488542868</v>
+        <v>224.7175624853434</v>
       </c>
       <c r="F28" s="6" t="n">
-        <v>283.8972488542868</v>
+        <v>424.9110349025811</v>
       </c>
       <c r="G28" s="6" t="n">
-        <v>0</v>
+        <v>200.1934724172377</v>
       </c>
       <c r="H28" s="6" t="n">
-        <v>0</v>
+        <v>1.161345275089762</v>
       </c>
       <c r="I28" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J28" s="6" t="n">
-        <v>0</v>
+        <v>1.161345275089762</v>
       </c>
       <c r="K28" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L28" s="6" t="n">
-        <v>283.8972488542868</v>
+        <v>368.042098157809</v>
       </c>
       <c r="M28" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N28" s="6" t="n">
-        <v>0.6469038233583584</v>
+        <v>0.8384867865436753</v>
       </c>
       <c r="O28" s="6" t="n">
-        <v>0.6469038233583584</v>
+        <v>0.8384867865436753</v>
       </c>
       <c r="P28" s="6" t="n">
-        <v>-0.6469038233583584</v>
+        <v>0.322858488546087</v>
       </c>
       <c r="Q28" s="6" t="n">
         <v>0</v>
@@ -2590,59 +2594,59 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>S55</t>
+          <t>S36</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>USDC raw (Avalanche-C — ALM idle)</t>
+          <t>Fluid Savings USDS (fsUSDS, Base)</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>avalanche_c</t>
+          <t>base</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E29" s="6" t="n">
-        <v>2500.221225</v>
+        <v>283.8972488542868</v>
       </c>
       <c r="F29" s="6" t="n">
-        <v>0</v>
+        <v>283.8972488542868</v>
       </c>
       <c r="G29" s="6" t="n">
-        <v>-2500.221225</v>
+        <v>0</v>
       </c>
       <c r="H29" s="6" t="n">
-        <v>-3.30458807350886e-10</v>
+        <v>0</v>
       </c>
       <c r="I29" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J29" s="6" t="n">
-        <v>-3.30458807350886e-10</v>
+        <v>0</v>
       </c>
       <c r="K29" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L29" s="6" t="n">
-        <v>115.3103732260555</v>
+        <v>283.8972488542868</v>
       </c>
       <c r="M29" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N29" s="6" t="n">
-        <v>0.2627525332276154</v>
+        <v>0.6467849550144467</v>
       </c>
       <c r="O29" s="6" t="n">
-        <v>0.2627525332276154</v>
+        <v>0.6467849550144467</v>
       </c>
       <c r="P29" s="6" t="n">
-        <v>-0.2627525335580742</v>
+        <v>-0.6467849550144467</v>
       </c>
       <c r="Q29" s="6" t="n">
         <v>0</v>
@@ -2655,59 +2659,59 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>S16</t>
+          <t>S55</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Ethena Staked USDe (sUSDe)</t>
+          <t>USDC raw (Avalanche-C — ALM idle)</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>ethereum</t>
+          <t>avalanche_c</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E30" s="6" t="n">
-        <v>99.50129408753318</v>
+        <v>2500.221225</v>
       </c>
       <c r="F30" s="6" t="n">
-        <v>99.81305763596731</v>
+        <v>0</v>
       </c>
       <c r="G30" s="6" t="n">
-        <v>0.3117635484341261</v>
+        <v>-2500.221225</v>
       </c>
       <c r="H30" s="6" t="n">
-        <v>0.3117635484341261</v>
+        <v>-3.30458807350886e-10</v>
       </c>
       <c r="I30" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J30" s="6" t="n">
-        <v>0.3117635484341261</v>
+        <v>-3.30458807350886e-10</v>
       </c>
       <c r="K30" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L30" s="6" t="n">
-        <v>99.50129408753318</v>
+        <v>115.3103732260555</v>
       </c>
       <c r="M30" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N30" s="6" t="n">
-        <v>0.2267290994685442</v>
+        <v>0.2627042525445283</v>
       </c>
       <c r="O30" s="6" t="n">
-        <v>0.2267290994685442</v>
+        <v>0.2627042525445283</v>
       </c>
       <c r="P30" s="6" t="n">
-        <v>0.08503444896558193</v>
+        <v>-0.2627042528749872</v>
       </c>
       <c r="Q30" s="6" t="n">
         <v>0</v>
@@ -2720,12 +2724,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>S13</t>
+          <t>S16</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Spark USDS Vault (Morpho)</t>
+          <t>Ethena Staked USDe (sUSDe)</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2739,40 +2743,40 @@
         </is>
       </c>
       <c r="E31" s="6" t="n">
-        <v>21.90660666972937</v>
+        <v>99.50129408753318</v>
       </c>
       <c r="F31" s="6" t="n">
-        <v>21.90661272343654</v>
+        <v>99.81305763596731</v>
       </c>
       <c r="G31" s="6" t="n">
-        <v>6.053707169991468e-06</v>
+        <v>0.3117635484341261</v>
       </c>
       <c r="H31" s="6" t="n">
-        <v>6.053707169991468e-06</v>
+        <v>0.3117635484341261</v>
       </c>
       <c r="I31" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J31" s="6" t="n">
-        <v>6.053707169991468e-06</v>
+        <v>0.3117635484341261</v>
       </c>
       <c r="K31" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L31" s="6" t="n">
-        <v>21.90660666972937</v>
+        <v>99.50129408753318</v>
       </c>
       <c r="M31" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N31" s="6" t="n">
-        <v>0.04991759401912802</v>
+        <v>0.2266874380784004</v>
       </c>
       <c r="O31" s="6" t="n">
-        <v>0.04991759401912802</v>
+        <v>0.2266874380784004</v>
       </c>
       <c r="P31" s="6" t="n">
-        <v>-0.04991154031195803</v>
+        <v>0.0850761103557257</v>
       </c>
       <c r="Q31" s="6" t="n">
         <v>0</v>
@@ -2785,12 +2789,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>S9</t>
+          <t>S61</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Aave Ethereum USDT (aToken)</t>
+          <t>Spark.fi PYUSD Reserve Uniswap V4 (PYUSD/USDS)</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2800,62 +2804,66 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>F</t>
         </is>
       </c>
       <c r="E32" s="6" t="n">
-        <v>5.897868</v>
+        <v>220002.7079018081</v>
       </c>
       <c r="F32" s="6" t="n">
-        <v>5.913258</v>
+        <v>220002.6507685304</v>
       </c>
       <c r="G32" s="6" t="n">
-        <v>0.01539</v>
+        <v>-0.0571332776681098</v>
       </c>
       <c r="H32" s="6" t="n">
-        <v>0.01539</v>
+        <v>-0.0571332776681098</v>
       </c>
       <c r="I32" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J32" s="6" t="n">
-        <v>0.01539</v>
+        <v>0</v>
       </c>
       <c r="K32" s="6" t="n">
-        <v>0</v>
+        <v>-0.0571332776681098</v>
       </c>
       <c r="L32" s="6" t="n">
-        <v>5.897868</v>
+        <v>220002.7079018081</v>
       </c>
       <c r="M32" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N32" s="6" t="n">
-        <v>0.01343920511473919</v>
+        <v>0</v>
       </c>
       <c r="O32" s="6" t="n">
-        <v>0.01343920511473919</v>
+        <v>-0.0571332776681098</v>
       </c>
       <c r="P32" s="6" t="n">
-        <v>0.001950794885260815</v>
+        <v>0</v>
       </c>
       <c r="Q32" s="6" t="n">
-        <v>0</v>
+        <v>220002.7079018081</v>
       </c>
       <c r="R32" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="S32" t="inlineStr"/>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>SDE (fixed)</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>S23</t>
+          <t>S13</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Anchorage tri-party loan escrow (USDC pass-through, ~$0 balance)</t>
+          <t>Spark USDS Vault (Morpho)</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2865,44 +2873,44 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E33" s="6" t="n">
-        <v>1.545609</v>
+        <v>21.90660666972937</v>
       </c>
       <c r="F33" s="6" t="n">
-        <v>10.015998</v>
+        <v>21.90661272343654</v>
       </c>
       <c r="G33" s="6" t="n">
-        <v>8.470389000000001</v>
+        <v>6.053707169991468e-06</v>
       </c>
       <c r="H33" s="6" t="n">
-        <v>8.470389000000001</v>
+        <v>6.053707169991468e-06</v>
       </c>
       <c r="I33" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J33" s="6" t="n">
-        <v>8.470389000000001</v>
+        <v>6.053707169991468e-06</v>
       </c>
       <c r="K33" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L33" s="6" t="n">
-        <v>1.545609</v>
+        <v>21.90660666972937</v>
       </c>
       <c r="M33" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N33" s="6" t="n">
-        <v>0.003521909337100613</v>
+        <v>0.04990842167925482</v>
       </c>
       <c r="O33" s="6" t="n">
-        <v>0.003521909337100613</v>
+        <v>0.04990842167925482</v>
       </c>
       <c r="P33" s="6" t="n">
-        <v>8.4668670906629</v>
+        <v>-0.04990236797208483</v>
       </c>
       <c r="Q33" s="6" t="n">
         <v>0</v>
@@ -2915,17 +2923,17 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>S54</t>
+          <t>S9</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Aave Avalanche USDC (aAvaUSDC)</t>
+          <t>Aave Ethereum USDT (aToken)</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>avalanche_c</t>
+          <t>ethereum</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -2934,40 +2942,40 @@
         </is>
       </c>
       <c r="E34" s="6" t="n">
-        <v>0.154431</v>
+        <v>5.897868</v>
       </c>
       <c r="F34" s="6" t="n">
-        <v>0.155165</v>
+        <v>5.913258</v>
       </c>
       <c r="G34" s="6" t="n">
-        <v>0.000734</v>
+        <v>0.01539</v>
       </c>
       <c r="H34" s="6" t="n">
-        <v>0.000734</v>
+        <v>0.01539</v>
       </c>
       <c r="I34" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J34" s="6" t="n">
-        <v>0.000734</v>
+        <v>0.01539</v>
       </c>
       <c r="K34" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L34" s="6" t="n">
-        <v>0.154431</v>
+        <v>5.897868</v>
       </c>
       <c r="M34" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N34" s="6" t="n">
-        <v>0.0003518949364540351</v>
+        <v>0.01343673566565294</v>
       </c>
       <c r="O34" s="6" t="n">
-        <v>0.0003518949364540351</v>
+        <v>0.01343673566565294</v>
       </c>
       <c r="P34" s="6" t="n">
-        <v>0.0003821050635459649</v>
+        <v>0.001953264334347057</v>
       </c>
       <c r="Q34" s="6" t="n">
         <v>0</v>
@@ -2980,12 +2988,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>S8</t>
+          <t>S23</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Aave Ethereum USDC (aToken)</t>
+          <t>Anchorage tri-party loan escrow (USDC pass-through, ~$0 balance)</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2995,44 +3003,44 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E35" s="6" t="n">
-        <v>0.057783</v>
+        <v>1.545609</v>
       </c>
       <c r="F35" s="6" t="n">
-        <v>0.057969</v>
+        <v>10.015998</v>
       </c>
       <c r="G35" s="6" t="n">
-        <v>0.000186</v>
+        <v>8.470389000000001</v>
       </c>
       <c r="H35" s="6" t="n">
-        <v>0.000186</v>
+        <v>8.470389000000001</v>
       </c>
       <c r="I35" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J35" s="6" t="n">
-        <v>0.000186</v>
+        <v>8.470389000000001</v>
       </c>
       <c r="K35" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L35" s="6" t="n">
-        <v>0.057783</v>
+        <v>1.545609</v>
       </c>
       <c r="M35" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N35" s="6" t="n">
-        <v>0.0001316675091990825</v>
+        <v>0.003521262187531864</v>
       </c>
       <c r="O35" s="6" t="n">
-        <v>0.0001316675091990825</v>
+        <v>0.003521262187531864</v>
       </c>
       <c r="P35" s="6" t="n">
-        <v>5.433249080091749e-05</v>
+        <v>8.466867737812468</v>
       </c>
       <c r="Q35" s="6" t="n">
         <v>0</v>
@@ -3045,17 +3053,17 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>S41</t>
+          <t>S54</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Aave Arbitrum USDCn (aArbUSDCn)</t>
+          <t>Aave Avalanche USDC (aAvaUSDC)</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>arbitrum</t>
+          <t>avalanche_c</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -3064,40 +3072,40 @@
         </is>
       </c>
       <c r="E36" s="6" t="n">
-        <v>0.006346</v>
+        <v>0.154431</v>
       </c>
       <c r="F36" s="6" t="n">
-        <v>0.006363</v>
+        <v>0.155165</v>
       </c>
       <c r="G36" s="6" t="n">
-        <v>1.7e-05</v>
+        <v>0.000734</v>
       </c>
       <c r="H36" s="6" t="n">
-        <v>1.7e-05</v>
+        <v>0.000734</v>
       </c>
       <c r="I36" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J36" s="6" t="n">
-        <v>1.7e-05</v>
+        <v>0.000734</v>
       </c>
       <c r="K36" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L36" s="6" t="n">
-        <v>0.006346</v>
+        <v>0.154431</v>
       </c>
       <c r="M36" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N36" s="6" t="n">
-        <v>1.446034323896955e-05</v>
+        <v>0.0003518302758865491</v>
       </c>
       <c r="O36" s="6" t="n">
-        <v>1.446034323896955e-05</v>
+        <v>0.0003518302758865491</v>
       </c>
       <c r="P36" s="6" t="n">
-        <v>2.539656761030448e-06</v>
+        <v>0.0003821697241134509</v>
       </c>
       <c r="Q36" s="6" t="n">
         <v>0</v>
@@ -3110,12 +3118,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>S7</t>
+          <t>S8</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Aave Ethereum USDS (aToken)</t>
+          <t>Aave Ethereum USDC (aToken)</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -3129,40 +3137,40 @@
         </is>
       </c>
       <c r="E37" s="6" t="n">
-        <v>0.005744283090097436</v>
+        <v>0.057783</v>
       </c>
       <c r="F37" s="6" t="n">
-        <v>0.005746426914602806</v>
+        <v>0.057969</v>
       </c>
       <c r="G37" s="6" t="n">
-        <v>2.14382450537e-06</v>
+        <v>0.000186</v>
       </c>
       <c r="H37" s="6" t="n">
-        <v>2.14382450537e-06</v>
+        <v>0.000186</v>
       </c>
       <c r="I37" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J37" s="6" t="n">
-        <v>2.14382450537e-06</v>
+        <v>0.000186</v>
       </c>
       <c r="K37" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L37" s="6" t="n">
-        <v>0.005744283090097436</v>
+        <v>0.057783</v>
       </c>
       <c r="M37" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N37" s="6" t="n">
-        <v>1.308923812553066e-05</v>
+        <v>0.0001316433153418191</v>
       </c>
       <c r="O37" s="6" t="n">
-        <v>1.308923812553066e-05</v>
+        <v>0.0001316433153418191</v>
       </c>
       <c r="P37" s="6" t="n">
-        <v>-1.094541362016066e-05</v>
+        <v>5.435668465818089e-05</v>
       </c>
       <c r="Q37" s="6" t="n">
         <v>0</v>
@@ -3175,17 +3183,17 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>S35</t>
+          <t>S41</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Aave Base USDC (aBasUSDC)</t>
+          <t>Aave Arbitrum USDCn (aArbUSDCn)</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>base</t>
+          <t>arbitrum</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -3194,40 +3202,40 @@
         </is>
       </c>
       <c r="E38" s="6" t="n">
-        <v>0.0017</v>
+        <v>0.006346</v>
       </c>
       <c r="F38" s="6" t="n">
-        <v>0.001705</v>
+        <v>0.006363</v>
       </c>
       <c r="G38" s="6" t="n">
-        <v>5e-06</v>
+        <v>1.7e-05</v>
       </c>
       <c r="H38" s="6" t="n">
-        <v>5e-06</v>
+        <v>1.7e-05</v>
       </c>
       <c r="I38" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J38" s="6" t="n">
-        <v>5e-06</v>
+        <v>1.7e-05</v>
       </c>
       <c r="K38" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L38" s="6" t="n">
-        <v>0.0017</v>
+        <v>0.006346</v>
       </c>
       <c r="M38" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N38" s="6" t="n">
-        <v>3.873713127363416e-06</v>
+        <v>1.445768615612177e-05</v>
       </c>
       <c r="O38" s="6" t="n">
-        <v>3.873713127363416e-06</v>
+        <v>1.445768615612177e-05</v>
       </c>
       <c r="P38" s="6" t="n">
-        <v>1.126286872636584e-06</v>
+        <v>2.542313843878233e-06</v>
       </c>
       <c r="Q38" s="6" t="n">
         <v>0</v>
@@ -3240,12 +3248,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>S17</t>
+          <t>S7</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Fluid Savings USDS (fsUSDS)</t>
+          <t>Aave Ethereum USDS (aToken)</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -3255,44 +3263,44 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E39" s="6" t="n">
-        <v>0.001240144670509943</v>
+        <v>0.005744283090097436</v>
       </c>
       <c r="F39" s="6" t="n">
-        <v>0.001240144670509943</v>
+        <v>0.005746426914602806</v>
       </c>
       <c r="G39" s="6" t="n">
-        <v>0</v>
+        <v>2.14382450537e-06</v>
       </c>
       <c r="H39" s="6" t="n">
-        <v>0</v>
+        <v>2.14382450537e-06</v>
       </c>
       <c r="I39" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J39" s="6" t="n">
-        <v>0</v>
+        <v>2.14382450537e-06</v>
       </c>
       <c r="K39" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L39" s="6" t="n">
-        <v>0.001240144670509943</v>
+        <v>0.005744283090097436</v>
       </c>
       <c r="M39" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N39" s="6" t="n">
-        <v>2.825861582343615e-06</v>
+        <v>1.30868329827523e-05</v>
       </c>
       <c r="O39" s="6" t="n">
-        <v>2.825861582343615e-06</v>
+        <v>1.30868329827523e-05</v>
       </c>
       <c r="P39" s="6" t="n">
-        <v>-2.825861582343615e-06</v>
+        <v>-1.09430084773823e-05</v>
       </c>
       <c r="Q39" s="6" t="n">
         <v>0</v>
@@ -3305,17 +3313,17 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>S6</t>
+          <t>S35</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Aave Ethereum Lido USDS (aToken)</t>
+          <t>Aave Base USDC (aBasUSDC)</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>ethereum</t>
+          <t>base</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -3324,40 +3332,40 @@
         </is>
       </c>
       <c r="E40" s="6" t="n">
-        <v>0.0005209665645060241</v>
+        <v>0.0017</v>
       </c>
       <c r="F40" s="6" t="n">
-        <v>0.000521673271312833</v>
+        <v>0.001705</v>
       </c>
       <c r="G40" s="6" t="n">
-        <v>7.06706806809e-07</v>
+        <v>5e-06</v>
       </c>
       <c r="H40" s="6" t="n">
-        <v>7.06706806809e-07</v>
+        <v>5e-06</v>
       </c>
       <c r="I40" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J40" s="6" t="n">
-        <v>7.06706806809e-07</v>
+        <v>5e-06</v>
       </c>
       <c r="K40" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L40" s="6" t="n">
-        <v>0.0005209665645060241</v>
+        <v>0.0017</v>
       </c>
       <c r="M40" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N40" s="6" t="n">
-        <v>1.18710295284965e-06</v>
+        <v>3.873001333975261e-06</v>
       </c>
       <c r="O40" s="6" t="n">
-        <v>1.18710295284965e-06</v>
+        <v>3.873001333975261e-06</v>
       </c>
       <c r="P40" s="6" t="n">
-        <v>-4.8039614604065e-07</v>
+        <v>1.126998666024739e-06</v>
       </c>
       <c r="Q40" s="6" t="n">
         <v>0</v>
@@ -3370,12 +3378,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>S30</t>
+          <t>S17</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>USDe raw (ALM idle)</t>
+          <t>Fluid Savings USDS (fsUSDS)</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -3385,14 +3393,14 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E41" s="6" t="n">
-        <v>7.4896275897803e-05</v>
+        <v>0.001240144670509943</v>
       </c>
       <c r="F41" s="6" t="n">
-        <v>7.4896275897803e-05</v>
+        <v>0.001240144670509943</v>
       </c>
       <c r="G41" s="6" t="n">
         <v>0</v>
@@ -3410,19 +3418,19 @@
         <v>0</v>
       </c>
       <c r="L41" s="6" t="n">
-        <v>7.4896275897803e-05</v>
+        <v>0.001240144670509943</v>
       </c>
       <c r="M41" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N41" s="6" t="n">
-        <v>1.706627571387951e-07</v>
+        <v>2.825342331298424e-06</v>
       </c>
       <c r="O41" s="6" t="n">
-        <v>1.706627571387951e-07</v>
+        <v>2.825342331298424e-06</v>
       </c>
       <c r="P41" s="6" t="n">
-        <v>-1.706627571387951e-07</v>
+        <v>-2.825342331298424e-06</v>
       </c>
       <c r="Q41" s="6" t="n">
         <v>0</v>
@@ -3435,12 +3443,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>S19</t>
+          <t>S6</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>BlackRock USD Institutional Digital Liquidity Fund (BUIDL-I)</t>
+          <t>Aave Ethereum Lido USDS (aToken)</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -3450,44 +3458,44 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>C</t>
         </is>
       </c>
       <c r="E42" s="6" t="n">
-        <v>0</v>
+        <v>0.0005209665645060241</v>
       </c>
       <c r="F42" s="6" t="n">
-        <v>0</v>
+        <v>0.000521673271312833</v>
       </c>
       <c r="G42" s="6" t="n">
-        <v>0</v>
+        <v>7.06706806809e-07</v>
       </c>
       <c r="H42" s="6" t="n">
-        <v>0</v>
+        <v>7.06706806809e-07</v>
       </c>
       <c r="I42" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J42" s="6" t="n">
-        <v>0</v>
+        <v>7.06706806809e-07</v>
       </c>
       <c r="K42" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L42" s="6" t="n">
-        <v>0</v>
+        <v>0.0005209665645060241</v>
       </c>
       <c r="M42" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N42" s="6" t="n">
-        <v>0</v>
+        <v>1.186884823110788e-06</v>
       </c>
       <c r="O42" s="6" t="n">
-        <v>0</v>
+        <v>1.186884823110788e-06</v>
       </c>
       <c r="P42" s="6" t="n">
-        <v>0</v>
+        <v>-4.801780163017881e-07</v>
       </c>
       <c r="Q42" s="6" t="n">
         <v>0</v>
@@ -3500,12 +3508,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>S20</t>
+          <t>S30</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Janus Henderson Anemoy Treasury Fund (JTRSY)</t>
+          <t>USDe raw (ALM idle)</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3515,14 +3523,14 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E43" s="6" t="n">
-        <v>0</v>
+        <v>7.4896275897803e-05</v>
       </c>
       <c r="F43" s="6" t="n">
-        <v>0</v>
+        <v>7.4896275897803e-05</v>
       </c>
       <c r="G43" s="6" t="n">
         <v>0</v>
@@ -3540,19 +3548,19 @@
         <v>0</v>
       </c>
       <c r="L43" s="6" t="n">
-        <v>0</v>
+        <v>7.4896275897803e-05</v>
       </c>
       <c r="M43" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N43" s="6" t="n">
-        <v>0</v>
+        <v>1.70631397918806e-07</v>
       </c>
       <c r="O43" s="6" t="n">
-        <v>0</v>
+        <v>1.70631397918806e-07</v>
       </c>
       <c r="P43" s="6" t="n">
-        <v>0</v>
+        <v>-1.70631397918806e-07</v>
       </c>
       <c r="Q43" s="6" t="n">
         <v>0</v>
@@ -3565,12 +3573,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>S21</t>
+          <t>S19</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Superstate Short Duration US Government Securities Fund (USTB)</t>
+          <t>BlackRock USD Institutional Digital Liquidity Fund (BUIDL-I)</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3608,7 +3616,7 @@
         <v>0</v>
       </c>
       <c r="M44" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N44" s="6" t="n">
         <v>0</v>
@@ -3625,21 +3633,17 @@
       <c r="R44" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="S44" t="inlineStr">
-        <is>
-          <t>SDE (fixed)</t>
-        </is>
-      </c>
+      <c r="S44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>S22</t>
+          <t>S20</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Superstate Crypto Carry Fund (USCC)</t>
+          <t>Janus Henderson Anemoy Treasury Fund (JTRSY)</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3699,12 +3703,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>S26</t>
+          <t>S21</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>USDC raw (ALM idle)</t>
+          <t>Superstate Short Duration US Government Securities Fund (USTB)</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3714,7 +3718,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E46" s="6" t="n">
@@ -3727,13 +3731,13 @@
         <v>0</v>
       </c>
       <c r="H46" s="6" t="n">
-        <v>891780.2799998709</v>
+        <v>0</v>
       </c>
       <c r="I46" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J46" s="6" t="n">
-        <v>891780.2799998709</v>
+        <v>0</v>
       </c>
       <c r="K46" s="6" t="n">
         <v>0</v>
@@ -3742,7 +3746,7 @@
         <v>0</v>
       </c>
       <c r="M46" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N46" s="6" t="n">
         <v>0</v>
@@ -3751,7 +3755,7 @@
         <v>0</v>
       </c>
       <c r="P46" s="6" t="n">
-        <v>891780.2799998709</v>
+        <v>0</v>
       </c>
       <c r="Q46" s="6" t="n">
         <v>0</v>
@@ -3759,17 +3763,21 @@
       <c r="R46" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="S46" t="inlineStr"/>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>SDE (fixed)</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>S29</t>
+          <t>S22</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>DAI raw (ALM idle)</t>
+          <t>Superstate Crypto Carry Fund (USCC)</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3779,7 +3787,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>E</t>
         </is>
       </c>
       <c r="E47" s="6" t="n">
@@ -3792,13 +3800,13 @@
         <v>0</v>
       </c>
       <c r="H47" s="6" t="n">
-        <v>8.19007e-07</v>
+        <v>0</v>
       </c>
       <c r="I47" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J47" s="6" t="n">
-        <v>8.19007e-07</v>
+        <v>0</v>
       </c>
       <c r="K47" s="6" t="n">
         <v>0</v>
@@ -3816,7 +3824,7 @@
         <v>0</v>
       </c>
       <c r="P47" s="6" t="n">
-        <v>8.19007e-07</v>
+        <v>0</v>
       </c>
       <c r="Q47" s="6" t="n">
         <v>0</v>
@@ -3829,12 +3837,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>S31</t>
+          <t>S26</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>USDS raw / POL (ALM idle — already netted out of utilized)</t>
+          <t>USDC raw (ALM idle)</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3857,22 +3865,22 @@
         <v>0</v>
       </c>
       <c r="H48" s="6" t="n">
-        <v>-2.5155451e-06</v>
+        <v>891780.2799998628</v>
       </c>
       <c r="I48" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J48" s="6" t="n">
-        <v>-2.5155451e-06</v>
+        <v>891780.2799998628</v>
       </c>
       <c r="K48" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L48" s="6" t="n">
-        <v>17.83075712531922</v>
+        <v>0</v>
       </c>
       <c r="M48" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N48" s="6" t="n">
         <v>0</v>
@@ -3881,7 +3889,7 @@
         <v>0</v>
       </c>
       <c r="P48" s="6" t="n">
-        <v>-2.5155451e-06</v>
+        <v>891780.2799998628</v>
       </c>
       <c r="Q48" s="6" t="n">
         <v>0</v>
@@ -3889,26 +3897,22 @@
       <c r="R48" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="S48" t="inlineStr">
-        <is>
-          <t>CoF excluded (Savings V2 depositor capital; not in cum_alm_usds)</t>
-        </is>
-      </c>
+      <c r="S48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>S38</t>
+          <t>S29</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>USDS raw (Base — POL)</t>
+          <t>DAI raw (ALM idle)</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>base</t>
+          <t>ethereum</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -3917,31 +3921,31 @@
         </is>
       </c>
       <c r="E49" s="6" t="n">
-        <v>65170000</v>
+        <v>0</v>
       </c>
       <c r="F49" s="6" t="n">
-        <v>65170000</v>
+        <v>0</v>
       </c>
       <c r="G49" s="6" t="n">
         <v>0</v>
       </c>
       <c r="H49" s="6" t="n">
-        <v>0</v>
+        <v>7.850176e-07</v>
       </c>
       <c r="I49" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J49" s="6" t="n">
-        <v>0</v>
+        <v>7.850176e-07</v>
       </c>
       <c r="K49" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L49" s="6" t="n">
-        <v>65170000</v>
+        <v>0</v>
       </c>
       <c r="M49" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N49" s="6" t="n">
         <v>0</v>
@@ -3950,39 +3954,35 @@
         <v>0</v>
       </c>
       <c r="P49" s="6" t="n">
-        <v>0</v>
+        <v>7.850176e-07</v>
       </c>
       <c r="Q49" s="6" t="n">
-        <v>65170000</v>
+        <v>0</v>
       </c>
       <c r="R49" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="S49" t="inlineStr">
-        <is>
-          <t>CoF excluded (already deducted from utilized)</t>
-        </is>
-      </c>
+      <c r="S49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>S42</t>
+          <t>S31</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Fluid Savings USDS (fsUSDS, Arbitrum)</t>
+          <t>USDS raw / POL (ALM idle — already netted out of utilized)</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>arbitrum</t>
+          <t>ethereum</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E50" s="6" t="n">
@@ -3995,22 +3995,22 @@
         <v>0</v>
       </c>
       <c r="H50" s="6" t="n">
-        <v>0</v>
+        <v>-2.7208051e-06</v>
       </c>
       <c r="I50" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J50" s="6" t="n">
-        <v>0</v>
+        <v>-2.7208051e-06</v>
       </c>
       <c r="K50" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L50" s="6" t="n">
-        <v>0</v>
+        <v>17.83075728228825</v>
       </c>
       <c r="M50" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N50" s="6" t="n">
         <v>0</v>
@@ -4019,7 +4019,7 @@
         <v>0</v>
       </c>
       <c r="P50" s="6" t="n">
-        <v>0</v>
+        <v>-2.7208051e-06</v>
       </c>
       <c r="Q50" s="6" t="n">
         <v>0</v>
@@ -4027,22 +4027,26 @@
       <c r="R50" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="S50" t="inlineStr"/>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>CoF excluded (Savings V2 depositor capital; not in cum_alm_usds)</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>S44</t>
+          <t>S38</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>USDS raw (Arbitrum — POL)</t>
+          <t>USDS raw (Base — POL)</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>arbitrum</t>
+          <t>base</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -4051,10 +4055,10 @@
         </is>
       </c>
       <c r="E51" s="6" t="n">
-        <v>90000000</v>
+        <v>65170000</v>
       </c>
       <c r="F51" s="6" t="n">
-        <v>90000000</v>
+        <v>65170000</v>
       </c>
       <c r="G51" s="6" t="n">
         <v>0</v>
@@ -4072,7 +4076,7 @@
         <v>0</v>
       </c>
       <c r="L51" s="6" t="n">
-        <v>90000000</v>
+        <v>65170000</v>
       </c>
       <c r="M51" s="7" t="n">
         <v>0</v>
@@ -4087,7 +4091,7 @@
         <v>0</v>
       </c>
       <c r="Q51" s="6" t="n">
-        <v>90000000</v>
+        <v>65170000</v>
       </c>
       <c r="R51" s="6" t="n">
         <v>0</v>
@@ -4101,29 +4105,29 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>S48</t>
+          <t>S42</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>USDS raw (Optimism — POL)</t>
+          <t>Fluid Savings USDS (fsUSDS, Arbitrum)</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>optimism</t>
+          <t>arbitrum</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E52" s="6" t="n">
-        <v>89900000</v>
+        <v>0</v>
       </c>
       <c r="F52" s="6" t="n">
-        <v>89900000</v>
+        <v>0</v>
       </c>
       <c r="G52" s="6" t="n">
         <v>0</v>
@@ -4141,10 +4145,10 @@
         <v>0</v>
       </c>
       <c r="L52" s="6" t="n">
-        <v>89900000</v>
+        <v>0</v>
       </c>
       <c r="M52" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N52" s="6" t="n">
         <v>0</v>
@@ -4156,31 +4160,27 @@
         <v>0</v>
       </c>
       <c r="Q52" s="6" t="n">
-        <v>89900000</v>
+        <v>0</v>
       </c>
       <c r="R52" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="S52" t="inlineStr">
-        <is>
-          <t>CoF excluded (already deducted from utilized)</t>
-        </is>
-      </c>
+      <c r="S52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>S52</t>
+          <t>S44</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>USDS raw (Unichain — POL)</t>
+          <t>USDS raw (Arbitrum — POL)</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>unichain</t>
+          <t>arbitrum</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -4189,10 +4189,10 @@
         </is>
       </c>
       <c r="E53" s="6" t="n">
-        <v>89900000</v>
+        <v>90000000</v>
       </c>
       <c r="F53" s="6" t="n">
-        <v>89900000</v>
+        <v>90000000</v>
       </c>
       <c r="G53" s="6" t="n">
         <v>0</v>
@@ -4210,7 +4210,7 @@
         <v>0</v>
       </c>
       <c r="L53" s="6" t="n">
-        <v>89900000</v>
+        <v>90000000</v>
       </c>
       <c r="M53" s="7" t="n">
         <v>0</v>
@@ -4225,7 +4225,7 @@
         <v>0</v>
       </c>
       <c r="Q53" s="6" t="n">
-        <v>89900000</v>
+        <v>90000000</v>
       </c>
       <c r="R53" s="6" t="n">
         <v>0</v>
@@ -4239,168 +4239,250 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
+          <t>S48</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>USDS raw (Optimism — POL)</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>optimism</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E54" s="6" t="n">
+        <v>89900000</v>
+      </c>
+      <c r="F54" s="6" t="n">
+        <v>89900000</v>
+      </c>
+      <c r="G54" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H54" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I54" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J54" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K54" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L54" s="6" t="n">
+        <v>89900000</v>
+      </c>
+      <c r="M54" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N54" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O54" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P54" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q54" s="6" t="n">
+        <v>89900000</v>
+      </c>
+      <c r="R54" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>CoF excluded (already deducted from utilized)</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>S52</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>USDS raw (Unichain — POL)</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>unichain</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E55" s="6" t="n">
+        <v>89900000</v>
+      </c>
+      <c r="F55" s="6" t="n">
+        <v>89900000</v>
+      </c>
+      <c r="G55" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H55" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I55" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J55" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K55" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L55" s="6" t="n">
+        <v>89900000</v>
+      </c>
+      <c r="M55" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N55" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O55" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P55" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q55" s="6" t="n">
+        <v>89900000</v>
+      </c>
+      <c r="R55" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>CoF excluded (already deducted from utilized)</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
           <t>PSM_CURVE_DEDUCT</t>
         </is>
       </c>
-      <c r="B54" t="inlineStr">
+      <c r="B56" t="inlineStr">
         <is>
           <t>PSM3 USDS + PSM3 USDC (SDE) + Curve idle USDS — BR deduction (unattributed)</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr"/>
-      <c r="D54" t="inlineStr"/>
-      <c r="E54" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F54" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G54" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H54" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I54" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J54" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K54" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L54" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M54" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N54" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O54" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P54" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q54" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R54" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S54" t="inlineStr">
+      <c r="C56" t="inlineStr"/>
+      <c r="D56" t="inlineStr"/>
+      <c r="E56" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F56" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G56" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H56" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I56" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J56" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K56" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L56" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M56" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N56" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O56" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P56" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q56" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R56" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S56" t="inlineStr">
         <is>
           <t>BR deduction from PSM3 USDS leg + PSM3 USDC leg (SDE, ≈$0 yield) + Curve idle USDS — not tracked per-venue; residual = sky_rev_br_reduction − Σ(known venue deduction_avg × effective_br_rate × n_days)</t>
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" s="8" t="inlineStr">
+    <row r="58">
+      <c r="A58" s="8" t="inlineStr">
         <is>
           <t>Position-only venues (PnL aggregated at prime level)</t>
         </is>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" s="2" t="inlineStr">
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
         <is>
           <t>Venue</t>
         </is>
       </c>
-      <c r="B57" s="2" t="inlineStr">
+      <c r="B59" s="2" t="inlineStr">
         <is>
           <t>Label</t>
         </is>
       </c>
-      <c r="C57" s="2" t="inlineStr">
+      <c r="C59" s="2" t="inlineStr">
         <is>
           <t>Chain</t>
         </is>
       </c>
-      <c r="D57" s="2" t="inlineStr">
+      <c r="D59" s="2" t="inlineStr">
         <is>
           <t>Pricing cat.</t>
         </is>
       </c>
-      <c r="E57" s="2" t="inlineStr">
+      <c r="E59" s="2" t="inlineStr">
         <is>
           <t>Position SoM</t>
         </is>
       </c>
-      <c r="F57" s="2" t="inlineStr">
+      <c r="F59" s="2" t="inlineStr">
         <is>
           <t>Position EoM</t>
         </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>S56</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>Spark Savings V2 — spUSDC vault</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>ethereum</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>S2</t>
-        </is>
-      </c>
-      <c r="E58" s="6" t="n">
-        <v>573332157.534611</v>
-      </c>
-      <c r="F58" s="6" t="n">
-        <v>303545287.192935</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>S57</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>Spark Savings V2 — spUSDT vault</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>ethereum</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>S2</t>
-        </is>
-      </c>
-      <c r="E59" s="6" t="n">
-        <v>1134703231.016836</v>
-      </c>
-      <c r="F59" s="6" t="n">
-        <v>1270360913.25412</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>S59</t>
+          <t>S56</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Spark Savings V2 — spPYUSD vault</t>
+          <t>Spark Savings V2 — spUSDC vault</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -4414,51 +4496,107 @@
         </is>
       </c>
       <c r="E60" s="6" t="n">
-        <v>1066559.875133</v>
+        <v>573332157.534611</v>
       </c>
       <c r="F60" s="6" t="n">
-        <v>773533.783718</v>
+        <v>303545287.192935</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
+          <t>S57</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Spark Savings V2 — spUSDT vault</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>ethereum</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>S2</t>
+        </is>
+      </c>
+      <c r="E61" s="6" t="n">
+        <v>1134703231.016836</v>
+      </c>
+      <c r="F61" s="6" t="n">
+        <v>1270360913.25412</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>S59</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Spark Savings V2 — spPYUSD vault</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>ethereum</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>S2</t>
+        </is>
+      </c>
+      <c r="E62" s="6" t="n">
+        <v>1066559.875133</v>
+      </c>
+      <c r="F62" s="6" t="n">
+        <v>773533.783718</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
           <t>S60</t>
         </is>
       </c>
-      <c r="B61" t="inlineStr">
+      <c r="B63" t="inlineStr">
         <is>
           <t>Spark Savings V2 — spUSDC vault (Avalanche-C, CREATE2 same address)</t>
         </is>
       </c>
-      <c r="C61" t="inlineStr">
+      <c r="C63" t="inlineStr">
         <is>
           <t>avalanche_c</t>
         </is>
       </c>
-      <c r="D61" t="inlineStr">
+      <c r="D63" t="inlineStr">
         <is>
           <t>S2</t>
         </is>
       </c>
-      <c r="E61" s="6" t="n">
+      <c r="E63" s="6" t="n">
         <v>37138817.432463</v>
       </c>
-      <c r="F61" s="6" t="n">
+      <c r="F63" s="6" t="n">
         <v>25647247.422478</v>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" t="inlineStr"/>
-      <c r="B62" s="5" t="inlineStr">
+    <row r="64">
+      <c r="A64" t="inlineStr"/>
+      <c r="B64" s="5" t="inlineStr">
         <is>
           <t>Aggregated actual_revenue (included in prime_agent_revenue, not in Venues body above)</t>
         </is>
       </c>
-      <c r="C62" t="inlineStr"/>
-      <c r="D62" t="inlineStr"/>
-      <c r="E62" t="inlineStr"/>
-      <c r="F62" s="9" t="n">
+      <c r="C64" t="inlineStr"/>
+      <c r="D64" t="inlineStr"/>
+      <c r="E64" t="inlineStr"/>
+      <c r="F64" s="9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4513,7 +4651,7 @@
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>3356195943.673027</v>
+        <v>3355589811.023948</v>
       </c>
     </row>
     <row r="6">
@@ -4533,7 +4671,7 @@
         </is>
       </c>
       <c r="B7" s="6" t="n">
-        <v>2356195943.673027</v>
+        <v>2355589811.023948</v>
       </c>
     </row>
     <row r="8">
@@ -4543,7 +4681,7 @@
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>0.03951513515348828</v>
+        <v>0.03951515566338391</v>
       </c>
     </row>
     <row r="9">
@@ -4573,7 +4711,7 @@
         </is>
       </c>
       <c r="B11" s="10" t="n">
-        <v>0.03871429258669792</v>
+        <v>0.03871416843742665</v>
       </c>
     </row>
     <row r="12">
@@ -4583,7 +4721,7 @@
         </is>
       </c>
       <c r="B12" s="11" t="n">
-        <v>-8.008425667903683</v>
+        <v>-8.009872259572633</v>
       </c>
     </row>
     <row r="13">
@@ -4603,7 +4741,7 @@
         </is>
       </c>
       <c r="B15" s="3" t="n">
-        <v>11047394.95315541</v>
+        <v>11045405.4060441</v>
       </c>
     </row>
     <row r="16">
@@ -4613,7 +4751,7 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>10827488.55337466</v>
+        <v>10825499.00626334</v>
       </c>
     </row>
     <row r="17">
@@ -4663,10 +4801,10 @@
         </is>
       </c>
       <c r="B21" s="6" t="n">
-        <v>2356195943.673027</v>
+        <v>2355589811.023948</v>
       </c>
       <c r="C21" s="3" t="n">
-        <v>7755973.525057507</v>
+        <v>7753983.977946189</v>
       </c>
     </row>
     <row r="23">
@@ -4688,7 +4826,7 @@
         </is>
       </c>
       <c r="B24" s="3" t="n">
-        <v>10642578.13467968</v>
+        <v>10640588.58756836</v>
       </c>
     </row>
     <row r="25">
@@ -4698,7 +4836,7 @@
         </is>
       </c>
       <c r="B25" s="3" t="n">
-        <v>40550.6842112442</v>
+        <v>40533.95751528406</v>
       </c>
     </row>
     <row r="26">
@@ -4708,7 +4846,7 @@
         </is>
       </c>
       <c r="B26" s="3" t="n">
-        <v>10683128.81889092</v>
+        <v>10681122.54508365</v>
       </c>
     </row>
     <row r="28">
@@ -4735,7 +4873,7 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>10642578.13467968</v>
+        <v>10640588.58756836</v>
       </c>
     </row>
     <row r="32">
@@ -4745,7 +4883,7 @@
         </is>
       </c>
       <c r="B32" s="3" t="n">
-        <v>-2749286.851285571</v>
+        <v>-2751276.398396889</v>
       </c>
     </row>
     <row r="33" ht="60" customHeight="1">
@@ -4875,7 +5013,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J5"/>
+  <dimension ref="A1:J7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -5035,6 +5173,86 @@
       </c>
       <c r="J5" s="6" t="n">
         <v>40550.6842112442</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>S61</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>fixed</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>2026-02-01</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>PYUSD in PYUSD/USDS Uniswap V4</t>
+        </is>
+      </c>
+      <c r="I6" s="6" t="n">
+        <v>-0.0571332776681098</v>
+      </c>
+      <c r="J6" s="6" t="n">
+        <v>-0.0571332776681098</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>S62</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>fixed</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2026-02-01</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>USDT in USDT/USDS Uniswap V4</t>
+        </is>
+      </c>
+      <c r="I7" s="6" t="n">
+        <v>-16.66956268247493</v>
+      </c>
+      <c r="J7" s="6" t="n">
+        <v>-16.66956268247493</v>
       </c>
     </row>
   </sheetData>
@@ -5174,16 +5392,16 @@
         <v>109271584.0644501</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>81897516.64033359</v>
+        <v>82142361.16871259</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>68133383.80742754</v>
+        <v>68328535.28923744</v>
       </c>
       <c r="G6" s="6" t="n">
         <v>127906874.3387326</v>
       </c>
       <c r="H6" s="6" t="n">
-        <v>3236279210.15232</v>
+        <v>3235839214.142131</v>
       </c>
       <c r="I6" s="7" t="n">
         <v>0.03650000241537366</v>
@@ -5201,7 +5419,7 @@
         <v>0.03693491707043663</v>
       </c>
       <c r="N6" s="3" t="n">
-        <v>337381.4365374905</v>
+        <v>337334.6074229946</v>
       </c>
       <c r="O6" s="3" t="n">
         <v>414243.5423272011</v>
@@ -5223,16 +5441,16 @@
         <v>109236625.511487</v>
       </c>
       <c r="E7" s="6" t="n">
-        <v>74371158.35490692</v>
+        <v>74621119.61822292</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>66387928.31178243</v>
+        <v>66577961.80007715</v>
       </c>
       <c r="G7" s="6" t="n">
         <v>131684974.1461452</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>3583341168.645234</v>
+        <v>3582901173.893623</v>
       </c>
       <c r="I7" s="7" t="n">
         <v>0.03650000241537366</v>
@@ -5250,7 +5468,7 @@
         <v>0.03693491707043663</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>374319.5082814827</v>
+        <v>374272.6793009383</v>
       </c>
       <c r="O7" s="3" t="n">
         <v>450593.1931929035</v>
@@ -5272,16 +5490,16 @@
         <v>109212118.7652359</v>
       </c>
       <c r="E8" s="6" t="n">
-        <v>78198703.5201842</v>
+        <v>78444345.91632521</v>
       </c>
       <c r="F8" s="6" t="n">
-        <v>69297142.12576202</v>
+        <v>69491495.08307031</v>
       </c>
       <c r="G8" s="6" t="n">
         <v>129926697.4882286</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>3577229601.132741</v>
+        <v>3576789605.779292</v>
       </c>
       <c r="I8" s="7" t="n">
         <v>0.03650000241537366</v>
@@ -5299,7 +5517,7 @@
         <v>0.03693491707043663</v>
       </c>
       <c r="N8" s="3" t="n">
-        <v>373669.0494405744</v>
+        <v>373622.2203959758</v>
       </c>
       <c r="O8" s="3" t="n">
         <v>450469.9897907797</v>
@@ -5321,16 +5539,16 @@
         <v>109413093.6674421</v>
       </c>
       <c r="E9" s="6" t="n">
-        <v>75725030.78440267</v>
+        <v>75981184.90509167</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>64115633.06430446</v>
+        <v>64299473.27260611</v>
       </c>
       <c r="G9" s="6" t="n">
         <v>129945312.0277757</v>
       </c>
       <c r="H9" s="6" t="n">
-        <v>3482111304.355217</v>
+        <v>3481671310.026226</v>
       </c>
       <c r="I9" s="7" t="n">
         <v>0.03650000241537366</v>
@@ -5348,7 +5566,7 @@
         <v>0.03693491707043663</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>363545.5358011322</v>
+        <v>363498.7068655675</v>
       </c>
       <c r="O9" s="3" t="n">
         <v>439555.1003258834</v>
@@ -5370,16 +5588,16 @@
         <v>109666118.9886243</v>
       </c>
       <c r="E10" s="6" t="n">
-        <v>62633764.42527747</v>
+        <v>62871817.87979747</v>
       </c>
       <c r="F10" s="6" t="n">
-        <v>71985346.18365841</v>
+        <v>72187288.206479</v>
       </c>
       <c r="G10" s="6" t="n">
         <v>129991339.9884334</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>3438062922.860942</v>
+        <v>3437622927.383602</v>
       </c>
       <c r="I10" s="7" t="n">
         <v>0.03650000241537366</v>
@@ -5397,7 +5615,7 @@
         <v>0.03693491707043663</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>358857.4326079512</v>
+        <v>358810.6035501668</v>
       </c>
       <c r="O10" s="3" t="n">
         <v>434343.0916681122</v>
@@ -5419,16 +5637,16 @@
         <v>109667151.3287632</v>
       </c>
       <c r="E11" s="6" t="n">
-        <v>65914408.62152216</v>
+        <v>66159636.42202716</v>
       </c>
       <c r="F11" s="6" t="n">
-        <v>69182310.83017388</v>
+        <v>69377077.90643525</v>
       </c>
       <c r="G11" s="6" t="n">
         <v>132866251.0455103</v>
       </c>
       <c r="H11" s="6" t="n">
-        <v>3232022985.161858</v>
+        <v>3231582990.285091</v>
       </c>
       <c r="I11" s="7" t="n">
         <v>0.03650000241537366</v>
@@ -5446,7 +5664,7 @@
         <v>0.03693491707043663</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>336928.4432312262</v>
+        <v>336881.6142373614</v>
       </c>
       <c r="O11" s="3" t="n">
         <v>412771.0234410728</v>
@@ -5468,16 +5686,16 @@
         <v>109729057.8747254</v>
       </c>
       <c r="E12" s="6" t="n">
-        <v>68822191.85959996</v>
+        <v>69079227.17738196</v>
       </c>
       <c r="F12" s="6" t="n">
-        <v>59598590.74937253</v>
+        <v>59781549.70206153</v>
       </c>
       <c r="G12" s="6" t="n">
         <v>133190285.3282568</v>
       </c>
       <c r="H12" s="6" t="n">
-        <v>3296854355.784049</v>
+        <v>3296414361.513577</v>
       </c>
       <c r="I12" s="7" t="n">
         <v>0.03650000241537366</v>
@@ -5495,7 +5713,7 @@
         <v>0.03693491707043663</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>343828.4959759949</v>
+        <v>343781.6670466586</v>
       </c>
       <c r="O12" s="3" t="n">
         <v>419001.6270619906</v>
@@ -5517,16 +5735,16 @@
         <v>109756088.3909883</v>
       </c>
       <c r="E13" s="6" t="n">
-        <v>46416747.2661341</v>
+        <v>46671865.5163491</v>
       </c>
       <c r="F13" s="6" t="n">
-        <v>62126087.28772155</v>
+        <v>62310963.43055655</v>
       </c>
       <c r="G13" s="6" t="n">
         <v>136081135.6656561</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>2564167970.277603</v>
+        <v>2563727975.884553</v>
       </c>
       <c r="I13" s="7" t="n">
         <v>0.03650000241537366</v>
@@ -5544,7 +5762,7 @@
         <v>0.03693491707043663</v>
       </c>
       <c r="N13" s="3" t="n">
-        <v>265848.1192409398</v>
+        <v>265801.2902985573</v>
       </c>
       <c r="O13" s="3" t="n">
         <v>339216.1773025376</v>
@@ -5566,16 +5784,16 @@
         <v>109737227.1714184</v>
       </c>
       <c r="E14" s="6" t="n">
-        <v>59621771.27202594</v>
+        <v>59879909.05062393</v>
       </c>
       <c r="F14" s="6" t="n">
-        <v>63144552.54356655</v>
+        <v>63326409.10121229</v>
       </c>
       <c r="G14" s="6" t="n">
         <v>136418480.8456975</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>3333245761.057378</v>
+        <v>3332805766.721134</v>
       </c>
       <c r="I14" s="7" t="n">
         <v>0.03650000241537366</v>
@@ -5593,7 +5811,7 @@
         <v>0.03693491707043663</v>
       </c>
       <c r="N14" s="3" t="n">
-        <v>347701.6612882871</v>
+        <v>347654.8323519505</v>
       </c>
       <c r="O14" s="3" t="n">
         <v>422617.4327683006</v>
@@ -5615,16 +5833,16 @@
         <v>109820179.5695339</v>
       </c>
       <c r="E15" s="6" t="n">
-        <v>62881956.35592515</v>
+        <v>63129621.93620015</v>
       </c>
       <c r="F15" s="6" t="n">
-        <v>67929925.5704889</v>
+        <v>68122254.95171708</v>
       </c>
       <c r="G15" s="6" t="n">
         <v>136520708.1372503</v>
       </c>
       <c r="H15" s="6" t="n">
-        <v>3477336061.802335</v>
+        <v>3476896066.840832</v>
       </c>
       <c r="I15" s="7" t="n">
         <v>0.03650000241537366</v>
@@ -5642,7 +5860,7 @@
         <v>0.03693491707043663</v>
       </c>
       <c r="N15" s="3" t="n">
-        <v>363037.3030556614</v>
+        <v>362990.4740527779</v>
       </c>
       <c r="O15" s="3" t="n">
         <v>438829.0783037072</v>
@@ -5664,16 +5882,16 @@
         <v>109824143.9731289</v>
       </c>
       <c r="E16" s="6" t="n">
-        <v>84921355.55294961</v>
+        <v>85182147.1144466</v>
       </c>
       <c r="F16" s="6" t="n">
-        <v>67458232.10747725</v>
+        <v>67637436.39746803</v>
       </c>
       <c r="G16" s="6" t="n">
         <v>146800932.9007985</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>3378762870.261068</v>
+        <v>3378322874.40958</v>
       </c>
       <c r="I16" s="7" t="n">
         <v>0.03650000241537366</v>
@@ -5691,7 +5909,7 @@
         <v>0.0368515837371033</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>352325.8733623142</v>
+        <v>352279.0442647091</v>
       </c>
       <c r="O16" s="3" t="n">
         <v>431507.6703348673</v>
@@ -5713,16 +5931,16 @@
         <v>109837230.945328</v>
       </c>
       <c r="E17" s="6" t="n">
-        <v>78116321.12843026</v>
+        <v>78378013.05490325</v>
       </c>
       <c r="F17" s="6" t="n">
-        <v>58043367.04671003</v>
+        <v>58221669.33521393</v>
       </c>
       <c r="G17" s="6" t="n">
         <v>146820705.7658038</v>
       </c>
       <c r="H17" s="6" t="n">
-        <v>3316629457.12973</v>
+        <v>3316189462.914753</v>
       </c>
       <c r="I17" s="7" t="n">
         <v>0.03650000241537366</v>
@@ -5740,7 +5958,7 @@
         <v>0.0368515837371033</v>
       </c>
       <c r="N17" s="3" t="n">
-        <v>345712.9663127756</v>
+        <v>345666.1373893456</v>
       </c>
       <c r="O17" s="3" t="n">
         <v>423171.9641792552</v>
@@ -5762,16 +5980,16 @@
         <v>109812101.2069135</v>
       </c>
       <c r="E18" s="6" t="n">
-        <v>85902407.14010979</v>
+        <v>86180523.00512178</v>
       </c>
       <c r="F18" s="6" t="n">
-        <v>60741445.97380174</v>
+        <v>60903325.82203438</v>
       </c>
       <c r="G18" s="6" t="n">
         <v>146084521.7500651</v>
       </c>
       <c r="H18" s="6" t="n">
-        <v>3307806010.553778</v>
+        <v>3307366014.840533</v>
       </c>
       <c r="I18" s="7" t="n">
         <v>0.03650000241537366</v>
@@ -5789,7 +6007,7 @@
         <v>0.0368515837371033</v>
       </c>
       <c r="N18" s="3" t="n">
-        <v>344773.8800929344</v>
+        <v>344727.0510100425</v>
       </c>
       <c r="O18" s="3" t="n">
         <v>423267.6885049809</v>
@@ -5811,16 +6029,16 @@
         <v>109817281.9042201</v>
       </c>
       <c r="E19" s="6" t="n">
-        <v>63272317.16911007</v>
+        <v>63532399.84881508</v>
       </c>
       <c r="F19" s="6" t="n">
-        <v>58432587.64789255</v>
+        <v>58612499.0866286</v>
       </c>
       <c r="G19" s="6" t="n">
         <v>174559965.1979237</v>
       </c>
       <c r="H19" s="6" t="n">
-        <v>3342721847.790328</v>
+        <v>3342281853.671886</v>
       </c>
       <c r="I19" s="7" t="n">
         <v>0.03650000241537366</v>
@@ -5838,7 +6056,7 @@
         <v>0.0368515837371033</v>
       </c>
       <c r="N19" s="3" t="n">
-        <v>348489.9995617628</v>
+        <v>348443.1706486071</v>
       </c>
       <c r="O19" s="3" t="n">
         <v>427360.7512641225</v>
@@ -5860,16 +6078,16 @@
         <v>109861276.5733739</v>
       </c>
       <c r="E20" s="6" t="n">
-        <v>88511698.91894951</v>
+        <v>88822044.70791052</v>
       </c>
       <c r="F20" s="6" t="n">
-        <v>42181809.13057283</v>
+        <v>42311463.37438669</v>
       </c>
       <c r="G20" s="6" t="n">
         <v>169618722.6830847</v>
       </c>
       <c r="H20" s="6" t="n">
-        <v>3374734736.272226</v>
+        <v>3374294736.239451</v>
       </c>
       <c r="I20" s="7" t="n">
         <v>0.03650000241537366</v>
@@ -5887,7 +6105,7 @@
         <v>0.0368515837371033</v>
       </c>
       <c r="N20" s="3" t="n">
-        <v>351897.1559571559</v>
+        <v>351850.3264145331</v>
       </c>
       <c r="O20" s="3" t="n">
         <v>431203.3537667908</v>
@@ -5909,16 +6127,16 @@
         <v>109944218.3095993</v>
       </c>
       <c r="E21" s="6" t="n">
-        <v>87033668.77329952</v>
+        <v>87324941.35505652</v>
       </c>
       <c r="F21" s="6" t="n">
-        <v>51954304.76465927</v>
+        <v>52103028.76518045</v>
       </c>
       <c r="G21" s="6" t="n">
         <v>172338153.0245515</v>
       </c>
       <c r="H21" s="6" t="n">
-        <v>3372689032.943098</v>
+        <v>3372249036.36082</v>
       </c>
       <c r="I21" s="7" t="n">
         <v>0.03650000241537366</v>
@@ -5936,7 +6154,7 @@
         <v>0.0368515837371033</v>
       </c>
       <c r="N21" s="3" t="n">
-        <v>351679.4301750899</v>
+        <v>351632.6009997061</v>
       </c>
       <c r="O21" s="3" t="n">
         <v>432166.6729598901</v>
@@ -5958,16 +6176,16 @@
         <v>110151080.1866189</v>
       </c>
       <c r="E22" s="6" t="n">
-        <v>87868461.85445462</v>
+        <v>88161184.05425063</v>
       </c>
       <c r="F22" s="6" t="n">
-        <v>60263592.76517375</v>
+        <v>60410870.33975412</v>
       </c>
       <c r="G22" s="6" t="n">
         <v>162877756.5589872</v>
       </c>
       <c r="H22" s="6" t="n">
-        <v>3351939631.25432</v>
+        <v>3351499631.479944</v>
       </c>
       <c r="I22" s="7" t="n">
         <v>0.03650000241537366</v>
@@ -5985,7 +6203,7 @@
         <v>0.0368515837371033</v>
       </c>
       <c r="N22" s="3" t="n">
-        <v>349471.0553605374</v>
+        <v>349424.2258454161</v>
       </c>
       <c r="O22" s="3" t="n">
         <v>429946.6489242385</v>
@@ -6007,16 +6225,16 @@
         <v>110145162.8914285</v>
       </c>
       <c r="E23" s="6" t="n">
-        <v>89081856.06629945</v>
+        <v>89402812.06936745</v>
       </c>
       <c r="F23" s="6" t="n">
-        <v>42740384.84050981</v>
+        <v>42859433.25500631</v>
       </c>
       <c r="G23" s="6" t="n">
         <v>231737478.377994</v>
       </c>
       <c r="H23" s="6" t="n">
-        <v>3507020842.800418</v>
+        <v>3506580838.382854</v>
       </c>
       <c r="I23" s="7" t="n">
         <v>0.03650000241537366</v>
@@ -6034,7 +6252,7 @@
         <v>0.03676825040376996</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>365756.2416435395</v>
+        <v>365709.4116342401</v>
       </c>
       <c r="O23" s="3" t="n">
         <v>451824.132648079</v>
@@ -6056,16 +6274,16 @@
         <v>110135980.040481</v>
       </c>
       <c r="E24" s="6" t="n">
-        <v>90072399.6267707</v>
+        <v>90391669.8087067</v>
       </c>
       <c r="F24" s="6" t="n">
-        <v>56943828.95422778</v>
+        <v>57064571.04109526</v>
       </c>
       <c r="G24" s="6" t="n">
         <v>229182741.6867744</v>
       </c>
       <c r="H24" s="6" t="n">
-        <v>3463785946.00189</v>
+        <v>3463345933.733087</v>
       </c>
       <c r="I24" s="7" t="n">
         <v>0.03650000241537366</v>
@@ -6083,7 +6301,7 @@
         <v>0.03676825040376996</v>
       </c>
       <c r="N24" s="3" t="n">
-        <v>361154.7182535286</v>
+        <v>361107.8874086158</v>
       </c>
       <c r="O24" s="3" t="n">
         <v>448566.8371441148</v>
@@ -6105,16 +6323,16 @@
         <v>110063401.5573106</v>
       </c>
       <c r="E25" s="6" t="n">
-        <v>90207535.65130401</v>
+        <v>90542938.88715301</v>
       </c>
       <c r="F25" s="6" t="n">
-        <v>51602034.69547939</v>
+        <v>51706647.45903745</v>
       </c>
       <c r="G25" s="6" t="n">
         <v>230888253.3173563</v>
       </c>
       <c r="H25" s="6" t="n">
-        <v>3205941602.598647</v>
+        <v>3205501586.59924</v>
       </c>
       <c r="I25" s="7" t="n">
         <v>0.03650000241537366</v>
@@ -6132,7 +6350,7 @@
         <v>0.03676825040376996</v>
       </c>
       <c r="N25" s="3" t="n">
-        <v>333712.1460489289</v>
+        <v>333665.3148069651</v>
       </c>
       <c r="O25" s="3" t="n">
         <v>420743.9106240411</v>
@@ -6154,16 +6372,16 @@
         <v>110201806.0378861</v>
       </c>
       <c r="E26" s="6" t="n">
-        <v>90137880.50639333</v>
+        <v>90469977.96395934</v>
       </c>
       <c r="F26" s="6" t="n">
-        <v>53876705.01782864</v>
+        <v>53984623.44056258</v>
       </c>
       <c r="G26" s="6" t="n">
         <v>254742493.5135711</v>
       </c>
       <c r="H26" s="6" t="n">
-        <v>3124170851.965993</v>
+        <v>3123730836.085693</v>
       </c>
       <c r="I26" s="7" t="n">
         <v>0.03650000241537366</v>
@@ -6181,7 +6399,7 @@
         <v>0.03676825040376996</v>
       </c>
       <c r="N26" s="3" t="n">
-        <v>325009.2220334444</v>
+        <v>324962.3908041572</v>
       </c>
       <c r="O26" s="3" t="n">
         <v>414829.2237389592</v>
@@ -6203,16 +6421,16 @@
         <v>110246348.1665363</v>
       </c>
       <c r="E27" s="6" t="n">
-        <v>90683527.73142503</v>
+        <v>91027822.88844904</v>
       </c>
       <c r="F27" s="6" t="n">
-        <v>60950192.97977956</v>
+        <v>61045926.01292147</v>
       </c>
       <c r="G27" s="6" t="n">
         <v>239797730.4064276</v>
       </c>
       <c r="H27" s="6" t="n">
-        <v>3633642090.151248</v>
+        <v>3633202061.961082</v>
       </c>
       <c r="I27" s="7" t="n">
         <v>0.03650000241537366</v>
@@ -6230,7 +6448,7 @@
         <v>0.03676825040376996</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>379232.6385937233</v>
+        <v>379185.8060542876</v>
       </c>
       <c r="O27" s="3" t="n">
         <v>468277.7087264755</v>
@@ -6252,16 +6470,16 @@
         <v>110397429.3795781</v>
       </c>
       <c r="E28" s="6" t="n">
-        <v>90958523.65549019</v>
+        <v>91306691.58331019</v>
       </c>
       <c r="F28" s="6" t="n">
-        <v>64022634.63846193</v>
+        <v>64114506.36868194</v>
       </c>
       <c r="G28" s="6" t="n">
         <v>240130221.5557107</v>
       </c>
       <c r="H28" s="6" t="n">
-        <v>3613109775.02256</v>
+        <v>3612669735.36452</v>
       </c>
       <c r="I28" s="7" t="n">
         <v>0.03650000241537366</v>
@@ -6279,7 +6497,7 @@
         <v>0.03676825040376996</v>
       </c>
       <c r="N28" s="3" t="n">
-        <v>377047.368469083</v>
+        <v>377000.5347091127</v>
       </c>
       <c r="O28" s="3" t="n">
         <v>466500.1759430798</v>
@@ -6301,16 +6519,16 @@
         <v>110459412.1575361</v>
       </c>
       <c r="E29" s="6" t="n">
-        <v>91000613.80843022</v>
+        <v>91350355.52528024</v>
       </c>
       <c r="F29" s="6" t="n">
-        <v>63901753.89657893</v>
+        <v>63992052.9462667</v>
       </c>
       <c r="G29" s="6" t="n">
         <v>243572783.8200219</v>
       </c>
       <c r="H29" s="6" t="n">
-        <v>3628217354.598102</v>
+        <v>3627777313.831564</v>
       </c>
       <c r="I29" s="7" t="n">
         <v>0.03650000241537366</v>
@@ -6328,7 +6546,7 @@
         <v>0.03676825040376996</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>378655.279807631</v>
+        <v>378608.4459296824</v>
       </c>
       <c r="O29" s="3" t="n">
         <v>468472.6929685309</v>
@@ -6350,16 +6568,16 @@
         <v>110548351.2880701</v>
       </c>
       <c r="E30" s="6" t="n">
-        <v>90132356.81756249</v>
+        <v>90447819.29369049</v>
       </c>
       <c r="F30" s="6" t="n">
-        <v>65846944.15199657</v>
+        <v>65971496.3634856</v>
       </c>
       <c r="G30" s="6" t="n">
         <v>245605231.7022537</v>
       </c>
       <c r="H30" s="6" t="n">
-        <v>3622578869.287579</v>
+        <v>3622138854.599961</v>
       </c>
       <c r="I30" s="7" t="n">
         <v>0.03650000241537366</v>
@@ -6377,7 +6595,7 @@
         <v>0.03676825040376996</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>378055.1714701112</v>
+        <v>378008.3403677623</v>
       </c>
       <c r="O30" s="3" t="n">
         <v>468212.9843232642</v>
@@ -6399,16 +6617,16 @@
         <v>110567333.2809158</v>
       </c>
       <c r="E31" s="6" t="n">
-        <v>91214545.99128646</v>
+        <v>91552934.04846945</v>
       </c>
       <c r="F31" s="6" t="n">
-        <v>71416697.68580709</v>
+        <v>71518357.0439785</v>
       </c>
       <c r="G31" s="6" t="n">
         <v>179571549.4489093</v>
       </c>
       <c r="H31" s="6" t="n">
-        <v>3413429322.143122</v>
+        <v>3412989274.727767</v>
       </c>
       <c r="I31" s="7" t="n">
         <v>0.03600000425292382</v>
@@ -6426,7 +6644,7 @@
         <v>0.03668466737761376</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>352383.5789754955</v>
+        <v>352337.3261667297</v>
       </c>
       <c r="O31" s="3" t="n">
         <v>435181.9142288258</v>
@@ -6448,16 +6666,16 @@
         <v>110810390.8233007</v>
       </c>
       <c r="E32" s="6" t="n">
-        <v>91260440.13070874</v>
+        <v>92620030.42800373</v>
       </c>
       <c r="F32" s="6" t="n">
-        <v>74954030.44580247</v>
+        <v>75064444.32358976</v>
       </c>
       <c r="G32" s="6" t="n">
         <v>206116586.0471416</v>
       </c>
       <c r="H32" s="6" t="n">
-        <v>3252967949.895449</v>
+        <v>3251497945.720366</v>
       </c>
       <c r="I32" s="7" t="n">
         <v>0.03600000425292382</v>
@@ -6475,7 +6693,7 @@
         <v>0.03668466737761376</v>
       </c>
       <c r="N32" s="3" t="n">
-        <v>335517.6938324182</v>
+        <v>335363.1836146039</v>
       </c>
       <c r="O32" s="3" t="n">
         <v>421508.318950465</v>
@@ -6497,16 +6715,16 @@
         <v>110784766.9258687</v>
       </c>
       <c r="E33" s="6" t="n">
-        <v>90992031.3551863</v>
+        <v>92236283.99807629</v>
       </c>
       <c r="F33" s="6" t="n">
-        <v>75076806.84493634</v>
+        <v>75302434.82539035</v>
       </c>
       <c r="G33" s="6" t="n">
         <v>248420857.3449725</v>
       </c>
       <c r="H33" s="6" t="n">
-        <v>3221477558.745079</v>
+        <v>3220007678.121735</v>
       </c>
       <c r="I33" s="7" t="n">
         <v>0.03600000425292382</v>
@@ -6524,7 +6742,7 @@
         <v>0.03668466737761376</v>
       </c>
       <c r="N33" s="3" t="n">
-        <v>332207.7799708258</v>
+        <v>332053.2827393732</v>
       </c>
       <c r="O33" s="3" t="n">
         <v>422626.9512378465</v>
@@ -6546,16 +6764,16 @@
         <v>110800643.1083902</v>
       </c>
       <c r="E34" s="6" t="n">
-        <v>89742687.66481608</v>
+        <v>90968267.09769209</v>
       </c>
       <c r="F34" s="6" t="n">
-        <v>75116667.49366367</v>
+        <v>75361032.66147675</v>
       </c>
       <c r="G34" s="6" t="n">
         <v>303291142.7334828</v>
       </c>
       <c r="H34" s="6" t="n">
-        <v>3246872717.915842</v>
+        <v>3245402773.315153</v>
       </c>
       <c r="I34" s="7" t="n">
         <v>0.03600000425292382</v>
@@ -6573,7 +6791,7 @@
         <v>0.03668466737761376</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>334877.0319644032</v>
+        <v>334722.5280083754</v>
       </c>
       <c r="O34" s="3" t="n">
         <v>430938.0887659761</v>
@@ -6595,16 +6813,16 @@
         <v>110800910.0818387</v>
       </c>
       <c r="E35" s="6" t="n">
-        <v>89921451.17719229</v>
+        <v>91290713.85405229</v>
       </c>
       <c r="F35" s="6" t="n">
-        <v>72969997.84221481</v>
+        <v>73070804.63810319</v>
       </c>
       <c r="G35" s="6" t="n">
         <v>295800536.4468129</v>
       </c>
       <c r="H35" s="6" t="n">
-        <v>3224509478.620773</v>
+        <v>3223039409.148025</v>
       </c>
       <c r="I35" s="7" t="n">
         <v>0.03600000425292382</v>
@@ -6622,7 +6840,7 @@
         <v>0.03668466737761376</v>
       </c>
       <c r="N35" s="3" t="n">
-        <v>332526.4611067913</v>
+        <v>332371.9440256246</v>
       </c>
       <c r="O35" s="3" t="n">
         <v>427593.374089083</v>
@@ -6644,16 +6862,16 @@
         <v>110840456.802935</v>
       </c>
       <c r="E36" s="6" t="n">
-        <v>90106496.23897925</v>
+        <v>91478373.60984924</v>
       </c>
       <c r="F36" s="6" t="n">
-        <v>73041937.31867403</v>
+        <v>73140128.86641257</v>
       </c>
       <c r="G36" s="6" t="n">
         <v>289518568.352541</v>
       </c>
       <c r="H36" s="6" t="n">
-        <v>3218414966.682919</v>
+        <v>3216944897.76431</v>
       </c>
       <c r="I36" s="7" t="n">
         <v>0.03600000425292382</v>
@@ -6671,7 +6889,7 @@
         <v>0.03668466737761376</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>331885.8749214238</v>
+        <v>331731.357898502</v>
       </c>
       <c r="O36" s="3" t="n">
         <v>426323.6664598752</v>
@@ -6696,7 +6914,7 @@
       <c r="L38" t="inlineStr"/>
       <c r="M38" t="inlineStr"/>
       <c r="N38" s="12" t="n">
-        <v>10827488.55337466</v>
+        <v>10825499.00626334</v>
       </c>
       <c r="O38" s="12" t="n">
         <v>13391864.98596525</v>

--- a/settlements/spark/2026-05/spark_settlement_may_2026.xlsx
+++ b/settlements/spark/2026-05/spark_settlement_may_2026.xlsx
@@ -676,7 +676,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-07-07T00:55:42+00:00</t>
+          <t>2026-07-07T14:48:24+00:00</t>
         </is>
       </c>
     </row>

--- a/settlements/spark/2026-05/spark_settlement_may_2026.xlsx
+++ b/settlements/spark/2026-05/spark_settlement_may_2026.xlsx
@@ -491,7 +491,7 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>13408944.74245897</v>
+        <v>13603389.18690488</v>
       </c>
     </row>
     <row r="5">
@@ -517,7 +517,7 @@
     <row r="7">
       <c r="A7" t="inlineStr"/>
       <c r="B7" s="4" t="n">
-        <v>15160063.72185771</v>
+        <v>15354508.16630362</v>
       </c>
     </row>
     <row r="9">
@@ -625,7 +625,7 @@
         </is>
       </c>
       <c r="B22" s="3" t="n">
-        <v>13408944.74245897</v>
+        <v>13603389.18690488</v>
       </c>
     </row>
     <row r="23">
@@ -641,7 +641,7 @@
     <row r="24">
       <c r="A24" t="inlineStr"/>
       <c r="B24" s="4" t="n">
-        <v>1388045.023437823</v>
+        <v>1582489.467883734</v>
       </c>
     </row>
     <row r="26">
@@ -676,7 +676,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-07-07T14:48:24+00:00</t>
+          <t>2026-07-10T11:14:08+00:00</t>
         </is>
       </c>
     </row>
@@ -873,13 +873,13 @@
         <v>1</v>
       </c>
       <c r="N2" s="6" t="n">
-        <v>4330194.512180462</v>
+        <v>4378311.680114231</v>
       </c>
       <c r="O2" s="6" t="n">
-        <v>4330194.512180462</v>
+        <v>4378311.680114231</v>
       </c>
       <c r="P2" s="6" t="n">
-        <v>-495743.6030512699</v>
+        <v>-543860.7709850385</v>
       </c>
       <c r="Q2" s="6" t="n">
         <v>0</v>
@@ -938,13 +938,13 @@
         <v>1</v>
       </c>
       <c r="N3" s="6" t="n">
-        <v>1530389.776815756</v>
+        <v>1547395.484454993</v>
       </c>
       <c r="O3" s="6" t="n">
-        <v>1530389.776815756</v>
+        <v>1547395.484454993</v>
       </c>
       <c r="P3" s="6" t="n">
-        <v>337722.3914202435</v>
+        <v>320716.6837810071</v>
       </c>
       <c r="Q3" s="6" t="n">
         <v>0</v>
@@ -1003,13 +1003,13 @@
         <v>1</v>
       </c>
       <c r="N4" s="6" t="n">
-        <v>1402175.18018744</v>
+        <v>1417756.165851677</v>
       </c>
       <c r="O4" s="6" t="n">
-        <v>1402175.18018744</v>
+        <v>1417756.165851677</v>
       </c>
       <c r="P4" s="6" t="n">
-        <v>1689404.81981255</v>
+        <v>1673823.834148313</v>
       </c>
       <c r="Q4" s="6" t="n">
         <v>0</v>
@@ -1050,31 +1050,31 @@
         <v>125242118.592976</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>-194444.4444439746</v>
+        <v>0</v>
       </c>
       <c r="I5" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>-194444.4444439746</v>
+        <v>0</v>
       </c>
       <c r="K5" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L5" s="6" t="n">
-        <v>539754938.8825277</v>
+        <v>487476634.2639929</v>
       </c>
       <c r="M5" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>1229689.175477509</v>
+        <v>1122927.708827552</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>1229689.175477509</v>
+        <v>1122927.708827552</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>-1424133.619921484</v>
+        <v>-1122927.708827552</v>
       </c>
       <c r="Q5" s="6" t="n">
         <v>0</v>
@@ -1133,13 +1133,13 @@
         <v>1</v>
       </c>
       <c r="N6" s="6" t="n">
-        <v>409055.9587527096</v>
+        <v>413601.3929603987</v>
       </c>
       <c r="O6" s="6" t="n">
-        <v>409055.9587527096</v>
+        <v>413601.3929603987</v>
       </c>
       <c r="P6" s="6" t="n">
-        <v>150396.9804885097</v>
+        <v>145851.5462808206</v>
       </c>
       <c r="Q6" s="6" t="n">
         <v>86642406.62655522</v>
@@ -1202,13 +1202,13 @@
         <v>1</v>
       </c>
       <c r="N7" s="6" t="n">
-        <v>326536.3159517574</v>
+        <v>330164.7910022265</v>
       </c>
       <c r="O7" s="6" t="n">
-        <v>290071.5021099598</v>
+        <v>293699.9771604289</v>
       </c>
       <c r="P7" s="6" t="n">
-        <v>109506.7329632671</v>
+        <v>105878.2579127981</v>
       </c>
       <c r="Q7" s="6" t="n">
         <v>0</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="N8" s="6" t="n">
-        <v>239395.2528205769</v>
+        <v>242055.4154414737</v>
       </c>
       <c r="O8" s="6" t="n">
-        <v>239395.2528205769</v>
+        <v>242055.4154414737</v>
       </c>
       <c r="P8" s="6" t="n">
-        <v>184135.3557626247</v>
+        <v>181475.193141728</v>
       </c>
       <c r="Q8" s="6" t="n">
         <v>0</v>
@@ -1332,13 +1332,13 @@
         <v>1</v>
       </c>
       <c r="N9" s="6" t="n">
-        <v>227823.9387459091</v>
+        <v>230355.5208005105</v>
       </c>
       <c r="O9" s="6" t="n">
-        <v>227823.9387459091</v>
+        <v>230355.5208005105</v>
       </c>
       <c r="P9" s="6" t="n">
-        <v>-198819.9680459091</v>
+        <v>-201351.5501005105</v>
       </c>
       <c r="Q9" s="6" t="n">
         <v>0</v>
@@ -1397,13 +1397,13 @@
         <v>1</v>
       </c>
       <c r="N10" s="6" t="n">
-        <v>227820.1668346276</v>
+        <v>230351.7069757103</v>
       </c>
       <c r="O10" s="6" t="n">
-        <v>227820.1668346276</v>
+        <v>230351.7069757103</v>
       </c>
       <c r="P10" s="6" t="n">
-        <v>-221434.2829629873</v>
+        <v>-223965.82310407</v>
       </c>
       <c r="Q10" s="6" t="n">
         <v>0</v>
@@ -1462,13 +1462,13 @@
         <v>1</v>
       </c>
       <c r="N11" s="6" t="n">
-        <v>232473.4718415524</v>
+        <v>235056.7195578573</v>
       </c>
       <c r="O11" s="6" t="n">
-        <v>206512.8008235362</v>
+        <v>209096.0485398411</v>
       </c>
       <c r="P11" s="6" t="n">
-        <v>77961.95754764859</v>
+        <v>75378.70983134369</v>
       </c>
       <c r="Q11" s="6" t="n">
         <v>0</v>
@@ -1527,13 +1527,13 @@
         <v>1</v>
       </c>
       <c r="N12" s="6" t="n">
-        <v>204175.396057219</v>
+        <v>206444.195251434</v>
       </c>
       <c r="O12" s="6" t="n">
-        <v>204175.396057219</v>
+        <v>206444.195251434</v>
       </c>
       <c r="P12" s="6" t="n">
-        <v>13094.00038941996</v>
+        <v>10825.20119520503</v>
       </c>
       <c r="Q12" s="6" t="n">
         <v>0</v>
@@ -1592,13 +1592,13 @@
         <v>1</v>
       </c>
       <c r="N13" s="6" t="n">
-        <v>172628.5711239259</v>
+        <v>174546.82166061</v>
       </c>
       <c r="O13" s="6" t="n">
-        <v>153350.8724353075</v>
+        <v>155269.1229719916</v>
       </c>
       <c r="P13" s="6" t="n">
-        <v>57892.46070471073</v>
+        <v>55974.21016802668</v>
       </c>
       <c r="Q13" s="6" t="n">
         <v>0</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="N14" s="6" t="n">
-        <v>131525.7312880923</v>
+        <v>132987.2466269989</v>
       </c>
       <c r="O14" s="6" t="n">
-        <v>131525.7312880923</v>
+        <v>132987.2466269989</v>
       </c>
       <c r="P14" s="6" t="n">
-        <v>162565.7855883517</v>
+        <v>161104.2702494451</v>
       </c>
       <c r="Q14" s="6" t="n">
         <v>103099818.9104406</v>
@@ -1787,13 +1787,13 @@
         <v>1</v>
       </c>
       <c r="N16" s="6" t="n">
-        <v>67602.09265326281</v>
+        <v>68353.28783299927</v>
       </c>
       <c r="O16" s="6" t="n">
-        <v>67602.09265326281</v>
+        <v>68353.28783299927</v>
       </c>
       <c r="P16" s="6" t="n">
-        <v>52039.52527270982</v>
+        <v>51288.33009297336</v>
       </c>
       <c r="Q16" s="6" t="n">
         <v>0</v>
@@ -1921,13 +1921,13 @@
         <v>1</v>
       </c>
       <c r="N18" s="6" t="n">
-        <v>21679.90905096699</v>
+        <v>21920.81643322426</v>
       </c>
       <c r="O18" s="6" t="n">
-        <v>21679.90905096699</v>
+        <v>21920.81643322426</v>
       </c>
       <c r="P18" s="6" t="n">
-        <v>21.56245173062087</v>
+        <v>-219.3449305266534</v>
       </c>
       <c r="Q18" s="6" t="n">
         <v>0</v>
@@ -1986,13 +1986,13 @@
         <v>1</v>
       </c>
       <c r="N19" s="6" t="n">
-        <v>21242.39501536415</v>
+        <v>21478.44073695808</v>
       </c>
       <c r="O19" s="6" t="n">
-        <v>21242.39501536415</v>
+        <v>21478.44073695808</v>
       </c>
       <c r="P19" s="6" t="n">
-        <v>11260.50833763585</v>
+        <v>11024.46261604192</v>
       </c>
       <c r="Q19" s="6" t="n">
         <v>0</v>
@@ -2005,17 +2005,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>S39</t>
+          <t>S45</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>USDC raw (Base — ALM idle)</t>
+          <t>USDC raw (Arbitrum — ALM idle)</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>base</t>
+          <t>arbitrum</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2024,40 +2024,40 @@
         </is>
       </c>
       <c r="E20" s="6" t="n">
-        <v>5000000</v>
+        <v>5009602.263622</v>
       </c>
       <c r="F20" s="6" t="n">
-        <v>4997576.708614</v>
+        <v>4975417.167355</v>
       </c>
       <c r="G20" s="6" t="n">
-        <v>-2423.291386</v>
+        <v>-34185.096267</v>
       </c>
       <c r="H20" s="6" t="n">
-        <v>-9.21792e-10</v>
+        <v>0</v>
       </c>
       <c r="I20" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J20" s="6" t="n">
-        <v>-9.21792e-10</v>
+        <v>0</v>
       </c>
       <c r="K20" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L20" s="6" t="n">
-        <v>4999001.686505452</v>
+        <v>5008499.518581129</v>
       </c>
       <c r="M20" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N20" s="6" t="n">
-        <v>11388.90600022364</v>
+        <v>11537.33839480485</v>
       </c>
       <c r="O20" s="6" t="n">
-        <v>11388.90600022364</v>
+        <v>11537.33839480485</v>
       </c>
       <c r="P20" s="6" t="n">
-        <v>-11388.90600022456</v>
+        <v>-11537.33839480485</v>
       </c>
       <c r="Q20" s="6" t="n">
         <v>0</v>
@@ -2098,31 +2098,31 @@
         <v>19997.4</v>
       </c>
       <c r="H21" s="6" t="n">
-        <v>1.8405064066e-10</v>
+        <v>0</v>
       </c>
       <c r="I21" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J21" s="6" t="n">
-        <v>1.8405064066e-10</v>
+        <v>0</v>
       </c>
       <c r="K21" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L21" s="6" t="n">
-        <v>4998671.605324483</v>
+        <v>5000645.077419355</v>
       </c>
       <c r="M21" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N21" s="6" t="n">
-        <v>11388.15399736822</v>
+        <v>11519.24528223705</v>
       </c>
       <c r="O21" s="6" t="n">
-        <v>11388.15399736822</v>
+        <v>11519.24528223705</v>
       </c>
       <c r="P21" s="6" t="n">
-        <v>-11388.15399736804</v>
+        <v>-11519.24528223705</v>
       </c>
       <c r="Q21" s="6" t="n">
         <v>0</v>
@@ -2135,17 +2135,17 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>S53</t>
+          <t>S39</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>USDC raw (Unichain — ALM idle)</t>
+          <t>USDC raw (Base — ALM idle)</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>unichain</t>
+          <t>base</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -2154,13 +2154,13 @@
         </is>
       </c>
       <c r="E22" s="6" t="n">
-        <v>4996314.282982</v>
+        <v>5000000</v>
       </c>
       <c r="F22" s="6" t="n">
-        <v>4992819.462732</v>
+        <v>4997576.708614</v>
       </c>
       <c r="G22" s="6" t="n">
-        <v>-3494.82025</v>
+        <v>-2423.291386</v>
       </c>
       <c r="H22" s="6" t="n">
         <v>0</v>
@@ -2175,19 +2175,19 @@
         <v>0</v>
       </c>
       <c r="L22" s="6" t="n">
-        <v>4997744.737919419</v>
+        <v>4999921.829310129</v>
       </c>
       <c r="M22" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N22" s="6" t="n">
-        <v>11386.04237460573</v>
+        <v>11517.57924270793</v>
       </c>
       <c r="O22" s="6" t="n">
-        <v>11386.04237460573</v>
+        <v>11517.57924270793</v>
       </c>
       <c r="P22" s="6" t="n">
-        <v>-11386.04237460573</v>
+        <v>-11517.57924270793</v>
       </c>
       <c r="Q22" s="6" t="n">
         <v>0</v>
@@ -2200,17 +2200,17 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>S45</t>
+          <t>S53</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>USDC raw (Arbitrum — ALM idle)</t>
+          <t>USDC raw (Unichain — ALM idle)</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>arbitrum</t>
+          <t>unichain</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -2219,40 +2219,40 @@
         </is>
       </c>
       <c r="E23" s="6" t="n">
-        <v>5009602.263622</v>
+        <v>4996314.282982</v>
       </c>
       <c r="F23" s="6" t="n">
-        <v>4975417.167355</v>
+        <v>4992819.462732</v>
       </c>
       <c r="G23" s="6" t="n">
-        <v>-34185.096267</v>
+        <v>-3494.82025</v>
       </c>
       <c r="H23" s="6" t="n">
-        <v>5.4e-10</v>
+        <v>0</v>
       </c>
       <c r="I23" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J23" s="6" t="n">
-        <v>5.4e-10</v>
+        <v>0</v>
       </c>
       <c r="K23" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L23" s="6" t="n">
-        <v>4954536.773106677</v>
+        <v>4996201.546844903</v>
       </c>
       <c r="M23" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N23" s="6" t="n">
-        <v>11287.60443027744</v>
+        <v>11509.0093791058</v>
       </c>
       <c r="O23" s="6" t="n">
-        <v>11287.60443027744</v>
+        <v>11509.0093791058</v>
       </c>
       <c r="P23" s="6" t="n">
-        <v>-11287.6044302769</v>
+        <v>-11509.0093791058</v>
       </c>
       <c r="Q23" s="6" t="n">
         <v>0</v>
@@ -2311,13 +2311,13 @@
         <v>1</v>
       </c>
       <c r="N24" s="6" t="n">
-        <v>3399.201930022765</v>
+        <v>3436.973898382989</v>
       </c>
       <c r="O24" s="6" t="n">
-        <v>3399.201930022765</v>
+        <v>3436.973898382989</v>
       </c>
       <c r="P24" s="6" t="n">
-        <v>1405.686250122215</v>
+        <v>1367.914281761991</v>
       </c>
       <c r="Q24" s="6" t="n">
         <v>0</v>
@@ -2376,13 +2376,13 @@
         <v>1</v>
       </c>
       <c r="N25" s="6" t="n">
-        <v>2238.15777134371</v>
+        <v>2263.028204540898</v>
       </c>
       <c r="O25" s="6" t="n">
-        <v>1988.219242323622</v>
+        <v>2013.08967552081</v>
       </c>
       <c r="P25" s="6" t="n">
-        <v>750.585259351082</v>
+        <v>725.7148261538939</v>
       </c>
       <c r="Q25" s="6" t="n">
         <v>0</v>
@@ -2464,59 +2464,59 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>S12</t>
+          <t>S55</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Spark DAI Vault (Morpho)</t>
+          <t>USDC raw (Avalanche-C — ALM idle)</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>ethereum</t>
+          <t>avalanche_c</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E27" s="6" t="n">
-        <v>458.5728307677575</v>
+        <v>2500.221225</v>
       </c>
       <c r="F27" s="6" t="n">
-        <v>539.8728953809741</v>
+        <v>0</v>
       </c>
       <c r="G27" s="6" t="n">
-        <v>81.30006461321658</v>
+        <v>-2500.221225</v>
       </c>
       <c r="H27" s="6" t="n">
-        <v>76.33046551920575</v>
+        <v>0</v>
       </c>
       <c r="I27" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J27" s="6" t="n">
-        <v>76.33046551920575</v>
+        <v>0</v>
       </c>
       <c r="K27" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L27" s="6" t="n">
-        <v>462.161691889013</v>
+        <v>2419.568927419355</v>
       </c>
       <c r="M27" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N27" s="6" t="n">
-        <v>1.052913440704947</v>
+        <v>5.573602509419893</v>
       </c>
       <c r="O27" s="6" t="n">
-        <v>1.052913440704947</v>
+        <v>5.573602509419893</v>
       </c>
       <c r="P27" s="6" t="n">
-        <v>75.27755207850079</v>
+        <v>-5.573602509419893</v>
       </c>
       <c r="Q27" s="6" t="n">
         <v>0</v>
@@ -2529,17 +2529,17 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>S34</t>
+          <t>S12</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Spark USDC Vault (Morpho, Base)</t>
+          <t>Spark DAI Vault (Morpho)</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>base</t>
+          <t>ethereum</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -2548,40 +2548,40 @@
         </is>
       </c>
       <c r="E28" s="6" t="n">
-        <v>224.7175624853434</v>
+        <v>458.5728307677575</v>
       </c>
       <c r="F28" s="6" t="n">
-        <v>424.9110349025811</v>
+        <v>539.8728953809741</v>
       </c>
       <c r="G28" s="6" t="n">
-        <v>200.1934724172377</v>
+        <v>81.30006461321658</v>
       </c>
       <c r="H28" s="6" t="n">
-        <v>1.161345275089762</v>
+        <v>76.33046551920575</v>
       </c>
       <c r="I28" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J28" s="6" t="n">
-        <v>1.161345275089762</v>
+        <v>76.33046551920575</v>
       </c>
       <c r="K28" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L28" s="6" t="n">
-        <v>368.042098157809</v>
+        <v>462.161691889013</v>
       </c>
       <c r="M28" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N28" s="6" t="n">
-        <v>0.8384867865436753</v>
+        <v>1.064613426168328</v>
       </c>
       <c r="O28" s="6" t="n">
-        <v>0.8384867865436753</v>
+        <v>1.064613426168328</v>
       </c>
       <c r="P28" s="6" t="n">
-        <v>0.322858488546087</v>
+        <v>75.26585209303741</v>
       </c>
       <c r="Q28" s="6" t="n">
         <v>0</v>
@@ -2594,12 +2594,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>S36</t>
+          <t>S34</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Fluid Savings USDS (fsUSDS, Base)</t>
+          <t>Spark USDC Vault (Morpho, Base)</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2613,40 +2613,40 @@
         </is>
       </c>
       <c r="E29" s="6" t="n">
-        <v>283.8972488542868</v>
+        <v>224.7175624853434</v>
       </c>
       <c r="F29" s="6" t="n">
-        <v>283.8972488542868</v>
+        <v>424.9110349025811</v>
       </c>
       <c r="G29" s="6" t="n">
-        <v>0</v>
+        <v>200.1934724172377</v>
       </c>
       <c r="H29" s="6" t="n">
-        <v>0</v>
+        <v>1.161345275089762</v>
       </c>
       <c r="I29" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J29" s="6" t="n">
-        <v>0</v>
+        <v>1.161345275089762</v>
       </c>
       <c r="K29" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L29" s="6" t="n">
-        <v>283.8972488542868</v>
+        <v>368.042098157809</v>
       </c>
       <c r="M29" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N29" s="6" t="n">
-        <v>0.6467849550144467</v>
+        <v>0.847804060722671</v>
       </c>
       <c r="O29" s="6" t="n">
-        <v>0.6467849550144467</v>
+        <v>0.847804060722671</v>
       </c>
       <c r="P29" s="6" t="n">
-        <v>-0.6467849550144467</v>
+        <v>0.3135412143670913</v>
       </c>
       <c r="Q29" s="6" t="n">
         <v>0</v>
@@ -2659,59 +2659,59 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>S55</t>
+          <t>S36</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>USDC raw (Avalanche-C — ALM idle)</t>
+          <t>Fluid Savings USDS (fsUSDS, Base)</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>avalanche_c</t>
+          <t>base</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E30" s="6" t="n">
-        <v>2500.221225</v>
+        <v>283.8972488542868</v>
       </c>
       <c r="F30" s="6" t="n">
-        <v>0</v>
+        <v>283.8972488542868</v>
       </c>
       <c r="G30" s="6" t="n">
-        <v>-2500.221225</v>
+        <v>0</v>
       </c>
       <c r="H30" s="6" t="n">
-        <v>-3.30458807350886e-10</v>
+        <v>0</v>
       </c>
       <c r="I30" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J30" s="6" t="n">
-        <v>-3.30458807350886e-10</v>
+        <v>0</v>
       </c>
       <c r="K30" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L30" s="6" t="n">
-        <v>115.3103732260555</v>
+        <v>283.8972488542868</v>
       </c>
       <c r="M30" s="7" t="n">
         <v>1</v>
       </c>
       <c r="N30" s="6" t="n">
-        <v>0.2627042525445283</v>
+        <v>0.653972036382252</v>
       </c>
       <c r="O30" s="6" t="n">
-        <v>0.2627042525445283</v>
+        <v>0.653972036382252</v>
       </c>
       <c r="P30" s="6" t="n">
-        <v>-0.2627042528749872</v>
+        <v>-0.653972036382252</v>
       </c>
       <c r="Q30" s="6" t="n">
         <v>0</v>
@@ -2770,13 +2770,13 @@
         <v>1</v>
       </c>
       <c r="N31" s="6" t="n">
-        <v>0.2266874380784004</v>
+        <v>0.2292063913253763</v>
       </c>
       <c r="O31" s="6" t="n">
-        <v>0.2266874380784004</v>
+        <v>0.2292063913253763</v>
       </c>
       <c r="P31" s="6" t="n">
-        <v>0.0850761103557257</v>
+        <v>0.08255715710874979</v>
       </c>
       <c r="Q31" s="6" t="n">
         <v>0</v>
@@ -2904,13 +2904,13 @@
         <v>1</v>
       </c>
       <c r="N33" s="6" t="n">
-        <v>0.04990842167925482</v>
+        <v>0.05046300459706486</v>
       </c>
       <c r="O33" s="6" t="n">
-        <v>0.04990842167925482</v>
+        <v>0.05046300459706486</v>
       </c>
       <c r="P33" s="6" t="n">
-        <v>-0.04990236797208483</v>
+        <v>-0.05045695088989487</v>
       </c>
       <c r="Q33" s="6" t="n">
         <v>0</v>
@@ -2969,13 +2969,13 @@
         <v>1</v>
       </c>
       <c r="N34" s="6" t="n">
-        <v>0.01343673566565294</v>
+        <v>0.01358604481670545</v>
       </c>
       <c r="O34" s="6" t="n">
-        <v>0.01343673566565294</v>
+        <v>0.01358604481670545</v>
       </c>
       <c r="P34" s="6" t="n">
-        <v>0.001953264334347057</v>
+        <v>0.001803955183294552</v>
       </c>
       <c r="Q34" s="6" t="n">
         <v>0</v>
@@ -3034,13 +3034,13 @@
         <v>1</v>
       </c>
       <c r="N35" s="6" t="n">
-        <v>0.003521262187531864</v>
+        <v>0.003560390490784686</v>
       </c>
       <c r="O35" s="6" t="n">
-        <v>0.003521262187531864</v>
+        <v>0.003560390490784686</v>
       </c>
       <c r="P35" s="6" t="n">
-        <v>8.466867737812468</v>
+        <v>8.466828609509216</v>
       </c>
       <c r="Q35" s="6" t="n">
         <v>0</v>
@@ -3099,13 +3099,13 @@
         <v>1</v>
       </c>
       <c r="N36" s="6" t="n">
-        <v>0.0003518302758865491</v>
+        <v>0.0003557398176915182</v>
       </c>
       <c r="O36" s="6" t="n">
-        <v>0.0003518302758865491</v>
+        <v>0.0003557398176915182</v>
       </c>
       <c r="P36" s="6" t="n">
-        <v>0.0003821697241134509</v>
+        <v>0.0003782601823084818</v>
       </c>
       <c r="Q36" s="6" t="n">
         <v>0</v>
@@ -3164,13 +3164,13 @@
         <v>1</v>
       </c>
       <c r="N37" s="6" t="n">
-        <v>0.0001316433153418191</v>
+        <v>0.0001331061372759938</v>
       </c>
       <c r="O37" s="6" t="n">
-        <v>0.0001316433153418191</v>
+        <v>0.0001331061372759938</v>
       </c>
       <c r="P37" s="6" t="n">
-        <v>5.435668465818089e-05</v>
+        <v>5.289386272400622e-05</v>
       </c>
       <c r="Q37" s="6" t="n">
         <v>0</v>
@@ -3229,13 +3229,13 @@
         <v>1</v>
       </c>
       <c r="N38" s="6" t="n">
-        <v>1.445768615612177e-05</v>
+        <v>1.461834011999129e-05</v>
       </c>
       <c r="O38" s="6" t="n">
-        <v>1.445768615612177e-05</v>
+        <v>1.461834011999129e-05</v>
       </c>
       <c r="P38" s="6" t="n">
-        <v>2.542313843878233e-06</v>
+        <v>2.381659880008713e-06</v>
       </c>
       <c r="Q38" s="6" t="n">
         <v>0</v>
@@ -3294,13 +3294,13 @@
         <v>1</v>
       </c>
       <c r="N39" s="6" t="n">
-        <v>1.30868329827523e-05</v>
+        <v>1.32322540114338e-05</v>
       </c>
       <c r="O39" s="6" t="n">
-        <v>1.30868329827523e-05</v>
+        <v>1.32322540114338e-05</v>
       </c>
       <c r="P39" s="6" t="n">
-        <v>-1.09430084773823e-05</v>
+        <v>-1.10884295060638e-05</v>
       </c>
       <c r="Q39" s="6" t="n">
         <v>0</v>
@@ -3359,13 +3359,13 @@
         <v>1</v>
       </c>
       <c r="N40" s="6" t="n">
-        <v>3.873001333975261e-06</v>
+        <v>3.9160381664017e-06</v>
       </c>
       <c r="O40" s="6" t="n">
-        <v>3.873001333975261e-06</v>
+        <v>3.9160381664017e-06</v>
       </c>
       <c r="P40" s="6" t="n">
-        <v>1.126998666024739e-06</v>
+        <v>1.0839618335983e-06</v>
       </c>
       <c r="Q40" s="6" t="n">
         <v>0</v>
@@ -3424,13 +3424,13 @@
         <v>1</v>
       </c>
       <c r="N41" s="6" t="n">
-        <v>2.825342331298424e-06</v>
+        <v>2.856737565633293e-06</v>
       </c>
       <c r="O41" s="6" t="n">
-        <v>2.825342331298424e-06</v>
+        <v>2.856737565633293e-06</v>
       </c>
       <c r="P41" s="6" t="n">
-        <v>-2.825342331298424e-06</v>
+        <v>-2.856737565633293e-06</v>
       </c>
       <c r="Q41" s="6" t="n">
         <v>0</v>
@@ -3489,13 +3489,13 @@
         <v>1</v>
       </c>
       <c r="N42" s="6" t="n">
-        <v>1.186884823110788e-06</v>
+        <v>1.200073500014567e-06</v>
       </c>
       <c r="O42" s="6" t="n">
-        <v>1.186884823110788e-06</v>
+        <v>1.200073500014567e-06</v>
       </c>
       <c r="P42" s="6" t="n">
-        <v>-4.801780163017881e-07</v>
+        <v>-4.933666932055665e-07</v>
       </c>
       <c r="Q42" s="6" t="n">
         <v>0</v>
@@ -3554,13 +3554,13 @@
         <v>1</v>
       </c>
       <c r="N43" s="6" t="n">
-        <v>1.70631397918806e-07</v>
+        <v>1.725274558453813e-07</v>
       </c>
       <c r="O43" s="6" t="n">
-        <v>1.70631397918806e-07</v>
+        <v>1.725274558453813e-07</v>
       </c>
       <c r="P43" s="6" t="n">
-        <v>-1.70631397918806e-07</v>
+        <v>-1.725274558453813e-07</v>
       </c>
       <c r="Q43" s="6" t="n">
         <v>0</v>
@@ -3930,13 +3930,13 @@
         <v>0</v>
       </c>
       <c r="H49" s="6" t="n">
-        <v>7.850176e-07</v>
+        <v>0</v>
       </c>
       <c r="I49" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J49" s="6" t="n">
-        <v>7.850176e-07</v>
+        <v>0</v>
       </c>
       <c r="K49" s="6" t="n">
         <v>0</v>
@@ -3954,7 +3954,7 @@
         <v>0</v>
       </c>
       <c r="P49" s="6" t="n">
-        <v>7.850176e-07</v>
+        <v>0</v>
       </c>
       <c r="Q49" s="6" t="n">
         <v>0</v>
@@ -3995,19 +3995,19 @@
         <v>0</v>
       </c>
       <c r="H50" s="6" t="n">
-        <v>-2.7208051e-06</v>
+        <v>0</v>
       </c>
       <c r="I50" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J50" s="6" t="n">
-        <v>-2.7208051e-06</v>
+        <v>0</v>
       </c>
       <c r="K50" s="6" t="n">
         <v>0</v>
       </c>
       <c r="L50" s="6" t="n">
-        <v>17.83075728228825</v>
+        <v>0</v>
       </c>
       <c r="M50" s="7" t="n">
         <v>0</v>
@@ -4019,7 +4019,7 @@
         <v>0</v>
       </c>
       <c r="P50" s="6" t="n">
-        <v>-2.7208051e-06</v>
+        <v>0</v>
       </c>
       <c r="Q50" s="6" t="n">
         <v>0</v>
@@ -4029,7 +4029,7 @@
       </c>
       <c r="S50" t="inlineStr">
         <is>
-          <t>CoF excluded (Savings V2 depositor capital; not in cum_alm_usds)</t>
+          <t>CoF excluded (already deducted from utilized)</t>
         </is>
       </c>
     </row>

--- a/settlements/spark/2026-05/spark_settlement_may_2026.xlsx
+++ b/settlements/spark/2026-05/spark_settlement_may_2026.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Venues" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sky Revenue" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sky Direct" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Debt" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Venues" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Sky Revenue" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Sky Direct" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Debt" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -539,7 +539,7 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>10640588.58756836</v>
+        <v>10681760.35714488</v>
       </c>
     </row>
     <row r="11">
@@ -555,7 +555,7 @@
     <row r="12">
       <c r="A12" t="inlineStr"/>
       <c r="B12" s="4" t="n">
-        <v>10681122.54508365</v>
+        <v>10722294.31466017</v>
       </c>
     </row>
     <row r="14">
@@ -577,7 +577,7 @@
         </is>
       </c>
       <c r="B15" s="3" t="n">
-        <v>10640588.58756836</v>
+        <v>10681760.35714488</v>
       </c>
     </row>
     <row r="16">
@@ -593,7 +593,7 @@
     <row r="17">
       <c r="A17" t="inlineStr"/>
       <c r="B17" s="4" t="n">
-        <v>13391864.98596525</v>
+        <v>13433036.75554177</v>
       </c>
     </row>
     <row r="19">
@@ -635,13 +635,13 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>-10640588.58756836</v>
+        <v>-10681760.35714488</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr"/>
       <c r="B24" s="4" t="n">
-        <v>1582489.467883734</v>
+        <v>1541317.698307214</v>
       </c>
     </row>
     <row r="26">
@@ -676,7 +676,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-07-10T11:14:08+00:00</t>
+          <t>2026-07-30T23:20:11+00:00</t>
         </is>
       </c>
     </row>
@@ -873,13 +873,13 @@
         <v>1</v>
       </c>
       <c r="N2" s="6" t="n">
-        <v>4378311.680114231</v>
+        <v>4394963.3688284</v>
       </c>
       <c r="O2" s="6" t="n">
-        <v>4378311.680114231</v>
+        <v>4394963.3688284</v>
       </c>
       <c r="P2" s="6" t="n">
-        <v>-543860.7709850385</v>
+        <v>-560512.4596992081</v>
       </c>
       <c r="Q2" s="6" t="n">
         <v>0</v>
@@ -938,13 +938,13 @@
         <v>1</v>
       </c>
       <c r="N3" s="6" t="n">
-        <v>1547395.484454993</v>
+        <v>1553280.572088632</v>
       </c>
       <c r="O3" s="6" t="n">
-        <v>1547395.484454993</v>
+        <v>1553280.572088632</v>
       </c>
       <c r="P3" s="6" t="n">
-        <v>320716.6837810071</v>
+        <v>314831.5961473684</v>
       </c>
       <c r="Q3" s="6" t="n">
         <v>0</v>
@@ -1003,13 +1003,13 @@
         <v>1</v>
       </c>
       <c r="N4" s="6" t="n">
-        <v>1417756.165851677</v>
+        <v>1423148.206453442</v>
       </c>
       <c r="O4" s="6" t="n">
-        <v>1417756.165851677</v>
+        <v>1423148.206453442</v>
       </c>
       <c r="P4" s="6" t="n">
-        <v>1673823.834148313</v>
+        <v>1668431.793546548</v>
       </c>
       <c r="Q4" s="6" t="n">
         <v>0</v>
@@ -1068,13 +1068,13 @@
         <v>1</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>1122927.708827552</v>
+        <v>1127198.451529777</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>1122927.708827552</v>
+        <v>1127198.451529777</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>-1122927.708827552</v>
+        <v>-1127198.451529777</v>
       </c>
       <c r="Q5" s="6" t="n">
         <v>0</v>
@@ -1133,13 +1133,13 @@
         <v>1</v>
       </c>
       <c r="N6" s="6" t="n">
-        <v>413601.3929603987</v>
+        <v>415174.4106326225</v>
       </c>
       <c r="O6" s="6" t="n">
-        <v>413601.3929603987</v>
+        <v>415174.4106326225</v>
       </c>
       <c r="P6" s="6" t="n">
-        <v>145851.5462808206</v>
+        <v>144278.5286085968</v>
       </c>
       <c r="Q6" s="6" t="n">
         <v>86642406.62655522</v>
@@ -1202,13 +1202,13 @@
         <v>1</v>
       </c>
       <c r="N7" s="6" t="n">
-        <v>330164.7910022265</v>
+        <v>331420.4808036443</v>
       </c>
       <c r="O7" s="6" t="n">
-        <v>293699.9771604289</v>
+        <v>294955.6669618467</v>
       </c>
       <c r="P7" s="6" t="n">
-        <v>105878.2579127981</v>
+        <v>104622.5681113802</v>
       </c>
       <c r="Q7" s="6" t="n">
         <v>0</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="N8" s="6" t="n">
-        <v>242055.4154414737</v>
+        <v>242976.0057794839</v>
       </c>
       <c r="O8" s="6" t="n">
-        <v>242055.4154414737</v>
+        <v>242976.0057794839</v>
       </c>
       <c r="P8" s="6" t="n">
-        <v>181475.193141728</v>
+        <v>180554.6028037178</v>
       </c>
       <c r="Q8" s="6" t="n">
         <v>0</v>
@@ -1332,13 +1332,13 @@
         <v>1</v>
       </c>
       <c r="N9" s="6" t="n">
-        <v>230355.5208005105</v>
+        <v>231231.613848747</v>
       </c>
       <c r="O9" s="6" t="n">
-        <v>230355.5208005105</v>
+        <v>231231.613848747</v>
       </c>
       <c r="P9" s="6" t="n">
-        <v>-201351.5501005105</v>
+        <v>-202227.643148747</v>
       </c>
       <c r="Q9" s="6" t="n">
         <v>0</v>
@@ -1397,13 +1397,13 @@
         <v>1</v>
       </c>
       <c r="N10" s="6" t="n">
-        <v>230351.7069757103</v>
+        <v>231227.7855191266</v>
       </c>
       <c r="O10" s="6" t="n">
-        <v>230351.7069757103</v>
+        <v>231227.7855191266</v>
       </c>
       <c r="P10" s="6" t="n">
-        <v>-223965.82310407</v>
+        <v>-224841.9016474863</v>
       </c>
       <c r="Q10" s="6" t="n">
         <v>0</v>
@@ -1462,13 +1462,13 @@
         <v>1</v>
       </c>
       <c r="N11" s="6" t="n">
-        <v>235056.7195578573</v>
+        <v>235950.6923058526</v>
       </c>
       <c r="O11" s="6" t="n">
-        <v>209096.0485398411</v>
+        <v>209990.0212878363</v>
       </c>
       <c r="P11" s="6" t="n">
-        <v>75378.70983134369</v>
+        <v>74484.73708334846</v>
       </c>
       <c r="Q11" s="6" t="n">
         <v>0</v>
@@ -1527,13 +1527,13 @@
         <v>1</v>
       </c>
       <c r="N12" s="6" t="n">
-        <v>206444.195251434</v>
+        <v>207229.3482344405</v>
       </c>
       <c r="O12" s="6" t="n">
-        <v>206444.195251434</v>
+        <v>207229.3482344405</v>
       </c>
       <c r="P12" s="6" t="n">
-        <v>10825.20119520503</v>
+        <v>10040.04821219848</v>
       </c>
       <c r="Q12" s="6" t="n">
         <v>0</v>
@@ -1592,13 +1592,13 @@
         <v>1</v>
       </c>
       <c r="N13" s="6" t="n">
-        <v>174546.82166061</v>
+        <v>175210.6618695063</v>
       </c>
       <c r="O13" s="6" t="n">
-        <v>155269.1229719916</v>
+        <v>155932.9631808879</v>
       </c>
       <c r="P13" s="6" t="n">
-        <v>55974.21016802668</v>
+        <v>55310.36995913038</v>
       </c>
       <c r="Q13" s="6" t="n">
         <v>0</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="N14" s="6" t="n">
-        <v>132987.2466269989</v>
+        <v>133493.0265704061</v>
       </c>
       <c r="O14" s="6" t="n">
-        <v>132987.2466269989</v>
+        <v>133493.0265704061</v>
       </c>
       <c r="P14" s="6" t="n">
-        <v>161104.2702494451</v>
+        <v>160598.4903060379</v>
       </c>
       <c r="Q14" s="6" t="n">
         <v>103099818.9104406</v>
@@ -1787,13 +1787,13 @@
         <v>1</v>
       </c>
       <c r="N16" s="6" t="n">
-        <v>68353.28783299927</v>
+        <v>68613.25052061575</v>
       </c>
       <c r="O16" s="6" t="n">
-        <v>68353.28783299927</v>
+        <v>68613.25052061575</v>
       </c>
       <c r="P16" s="6" t="n">
-        <v>51288.33009297336</v>
+        <v>51028.36740535688</v>
       </c>
       <c r="Q16" s="6" t="n">
         <v>0</v>
@@ -1921,13 +1921,13 @@
         <v>1</v>
       </c>
       <c r="N18" s="6" t="n">
-        <v>21920.81643322426</v>
+        <v>22004.18615157126</v>
       </c>
       <c r="O18" s="6" t="n">
-        <v>21920.81643322426</v>
+        <v>22004.18615157126</v>
       </c>
       <c r="P18" s="6" t="n">
-        <v>-219.3449305266534</v>
+        <v>-302.7146488736535</v>
       </c>
       <c r="Q18" s="6" t="n">
         <v>0</v>
@@ -1986,13 +1986,13 @@
         <v>1</v>
       </c>
       <c r="N19" s="6" t="n">
-        <v>21478.44073695808</v>
+        <v>21560.12800258652</v>
       </c>
       <c r="O19" s="6" t="n">
-        <v>21478.44073695808</v>
+        <v>21560.12800258652</v>
       </c>
       <c r="P19" s="6" t="n">
-        <v>11024.46261604192</v>
+        <v>10942.77535041349</v>
       </c>
       <c r="Q19" s="6" t="n">
         <v>0</v>
@@ -2051,13 +2051,13 @@
         <v>1</v>
       </c>
       <c r="N20" s="6" t="n">
-        <v>11537.33839480485</v>
+        <v>11581.21744718316</v>
       </c>
       <c r="O20" s="6" t="n">
-        <v>11537.33839480485</v>
+        <v>11581.21744718316</v>
       </c>
       <c r="P20" s="6" t="n">
-        <v>-11537.33839480485</v>
+        <v>-11581.21744718316</v>
       </c>
       <c r="Q20" s="6" t="n">
         <v>0</v>
@@ -2116,13 +2116,13 @@
         <v>1</v>
       </c>
       <c r="N21" s="6" t="n">
-        <v>11519.24528223705</v>
+        <v>11563.0555225023</v>
       </c>
       <c r="O21" s="6" t="n">
-        <v>11519.24528223705</v>
+        <v>11563.0555225023</v>
       </c>
       <c r="P21" s="6" t="n">
-        <v>-11519.24528223705</v>
+        <v>-11563.0555225023</v>
       </c>
       <c r="Q21" s="6" t="n">
         <v>0</v>
@@ -2181,13 +2181,13 @@
         <v>1</v>
       </c>
       <c r="N22" s="6" t="n">
-        <v>11517.57924270793</v>
+        <v>11561.38314665597</v>
       </c>
       <c r="O22" s="6" t="n">
-        <v>11517.57924270793</v>
+        <v>11561.38314665597</v>
       </c>
       <c r="P22" s="6" t="n">
-        <v>-11517.57924270793</v>
+        <v>-11561.38314665597</v>
       </c>
       <c r="Q22" s="6" t="n">
         <v>0</v>
@@ -2246,13 +2246,13 @@
         <v>1</v>
       </c>
       <c r="N23" s="6" t="n">
-        <v>11509.0093791058</v>
+        <v>11552.78068996513</v>
       </c>
       <c r="O23" s="6" t="n">
-        <v>11509.0093791058</v>
+        <v>11552.78068996513</v>
       </c>
       <c r="P23" s="6" t="n">
-        <v>-11509.0093791058</v>
+        <v>-11552.78068996513</v>
       </c>
       <c r="Q23" s="6" t="n">
         <v>0</v>
@@ -2311,13 +2311,13 @@
         <v>1</v>
       </c>
       <c r="N24" s="6" t="n">
-        <v>3436.973898382989</v>
+        <v>3450.045471093204</v>
       </c>
       <c r="O24" s="6" t="n">
-        <v>3436.973898382989</v>
+        <v>3450.045471093204</v>
       </c>
       <c r="P24" s="6" t="n">
-        <v>1367.914281761991</v>
+        <v>1354.842709051775</v>
       </c>
       <c r="Q24" s="6" t="n">
         <v>0</v>
@@ -2376,13 +2376,13 @@
         <v>1</v>
       </c>
       <c r="N25" s="6" t="n">
-        <v>2263.028204540898</v>
+        <v>2271.635001856072</v>
       </c>
       <c r="O25" s="6" t="n">
-        <v>2013.08967552081</v>
+        <v>2021.696472835984</v>
       </c>
       <c r="P25" s="6" t="n">
-        <v>725.7148261538939</v>
+        <v>717.1080288387201</v>
       </c>
       <c r="Q25" s="6" t="n">
         <v>0</v>
@@ -2510,13 +2510,13 @@
         <v>1</v>
       </c>
       <c r="N27" s="6" t="n">
-        <v>5.573602509419893</v>
+        <v>5.594800153805263</v>
       </c>
       <c r="O27" s="6" t="n">
-        <v>5.573602509419893</v>
+        <v>5.594800153805263</v>
       </c>
       <c r="P27" s="6" t="n">
-        <v>-5.573602509419893</v>
+        <v>-5.594800153805263</v>
       </c>
       <c r="Q27" s="6" t="n">
         <v>0</v>
@@ -2575,13 +2575,13 @@
         <v>1</v>
       </c>
       <c r="N28" s="6" t="n">
-        <v>1.064613426168328</v>
+        <v>1.068662386742331</v>
       </c>
       <c r="O28" s="6" t="n">
-        <v>1.064613426168328</v>
+        <v>1.068662386742331</v>
       </c>
       <c r="P28" s="6" t="n">
-        <v>75.26585209303741</v>
+        <v>75.26180313246341</v>
       </c>
       <c r="Q28" s="6" t="n">
         <v>0</v>
@@ -2640,13 +2640,13 @@
         <v>1</v>
       </c>
       <c r="N29" s="6" t="n">
-        <v>0.847804060722671</v>
+        <v>0.8510284472764841</v>
       </c>
       <c r="O29" s="6" t="n">
-        <v>0.847804060722671</v>
+        <v>0.8510284472764841</v>
       </c>
       <c r="P29" s="6" t="n">
-        <v>0.3135412143670913</v>
+        <v>0.3103168278132782</v>
       </c>
       <c r="Q29" s="6" t="n">
         <v>0</v>
@@ -2705,13 +2705,13 @@
         <v>1</v>
       </c>
       <c r="N30" s="6" t="n">
-        <v>0.653972036382252</v>
+        <v>0.6564592368314728</v>
       </c>
       <c r="O30" s="6" t="n">
-        <v>0.653972036382252</v>
+        <v>0.6564592368314728</v>
       </c>
       <c r="P30" s="6" t="n">
-        <v>-0.653972036382252</v>
+        <v>-0.6564592368314728</v>
       </c>
       <c r="Q30" s="6" t="n">
         <v>0</v>
@@ -2770,13 +2770,13 @@
         <v>1</v>
       </c>
       <c r="N31" s="6" t="n">
-        <v>0.2292063913253763</v>
+        <v>0.230078113979792</v>
       </c>
       <c r="O31" s="6" t="n">
-        <v>0.2292063913253763</v>
+        <v>0.230078113979792</v>
       </c>
       <c r="P31" s="6" t="n">
-        <v>0.08255715710874979</v>
+        <v>0.08168543445433413</v>
       </c>
       <c r="Q31" s="6" t="n">
         <v>0</v>
@@ -2904,13 +2904,13 @@
         <v>1</v>
       </c>
       <c r="N33" s="6" t="n">
-        <v>0.05046300459706486</v>
+        <v>0.05065492657647728</v>
       </c>
       <c r="O33" s="6" t="n">
-        <v>0.05046300459706486</v>
+        <v>0.05065492657647728</v>
       </c>
       <c r="P33" s="6" t="n">
-        <v>-0.05045695088989487</v>
+        <v>-0.05064887286930728</v>
       </c>
       <c r="Q33" s="6" t="n">
         <v>0</v>
@@ -2969,13 +2969,13 @@
         <v>1</v>
       </c>
       <c r="N34" s="6" t="n">
-        <v>0.01358604481670545</v>
+        <v>0.01363771555320693</v>
       </c>
       <c r="O34" s="6" t="n">
-        <v>0.01358604481670545</v>
+        <v>0.01363771555320693</v>
       </c>
       <c r="P34" s="6" t="n">
-        <v>0.001803955183294552</v>
+        <v>0.001752284446793072</v>
       </c>
       <c r="Q34" s="6" t="n">
         <v>0</v>
@@ -3034,13 +3034,13 @@
         <v>1</v>
       </c>
       <c r="N35" s="6" t="n">
-        <v>0.003560390490784686</v>
+        <v>0.003573931444121267</v>
       </c>
       <c r="O35" s="6" t="n">
-        <v>0.003560390490784686</v>
+        <v>0.003573931444121267</v>
       </c>
       <c r="P35" s="6" t="n">
-        <v>8.466828609509216</v>
+        <v>8.46681506855588</v>
       </c>
       <c r="Q35" s="6" t="n">
         <v>0</v>
@@ -3099,13 +3099,13 @@
         <v>1</v>
       </c>
       <c r="N36" s="6" t="n">
-        <v>0.0003557398176915182</v>
+        <v>0.0003570927749819595</v>
       </c>
       <c r="O36" s="6" t="n">
-        <v>0.0003557398176915182</v>
+        <v>0.0003570927749819595</v>
       </c>
       <c r="P36" s="6" t="n">
-        <v>0.0003782601823084818</v>
+        <v>0.0003769072250180406</v>
       </c>
       <c r="Q36" s="6" t="n">
         <v>0</v>
@@ -3164,13 +3164,13 @@
         <v>1</v>
       </c>
       <c r="N37" s="6" t="n">
-        <v>0.0001331061372759938</v>
+        <v>0.0001336123693868625</v>
       </c>
       <c r="O37" s="6" t="n">
-        <v>0.0001331061372759938</v>
+        <v>0.0001336123693868625</v>
       </c>
       <c r="P37" s="6" t="n">
-        <v>5.289386272400622e-05</v>
+        <v>5.238763061313751e-05</v>
       </c>
       <c r="Q37" s="6" t="n">
         <v>0</v>
@@ -3229,13 +3229,13 @@
         <v>1</v>
       </c>
       <c r="N38" s="6" t="n">
-        <v>1.461834011999129e-05</v>
+        <v>1.467393690408995e-05</v>
       </c>
       <c r="O38" s="6" t="n">
-        <v>1.461834011999129e-05</v>
+        <v>1.467393690408995e-05</v>
       </c>
       <c r="P38" s="6" t="n">
-        <v>2.381659880008713e-06</v>
+        <v>2.326063095910053e-06</v>
       </c>
       <c r="Q38" s="6" t="n">
         <v>0</v>
@@ -3294,13 +3294,13 @@
         <v>1</v>
       </c>
       <c r="N39" s="6" t="n">
-        <v>1.32322540114338e-05</v>
+        <v>1.32825792031706e-05</v>
       </c>
       <c r="O39" s="6" t="n">
-        <v>1.32322540114338e-05</v>
+        <v>1.32825792031706e-05</v>
       </c>
       <c r="P39" s="6" t="n">
-        <v>-1.10884295060638e-05</v>
+        <v>-1.11387546978006e-05</v>
       </c>
       <c r="Q39" s="6" t="n">
         <v>0</v>
@@ -3359,13 +3359,13 @@
         <v>1</v>
       </c>
       <c r="N40" s="6" t="n">
-        <v>3.9160381664017e-06</v>
+        <v>3.930931726592013e-06</v>
       </c>
       <c r="O40" s="6" t="n">
-        <v>3.9160381664017e-06</v>
+        <v>3.930931726592013e-06</v>
       </c>
       <c r="P40" s="6" t="n">
-        <v>1.0839618335983e-06</v>
+        <v>1.069068273407988e-06</v>
       </c>
       <c r="Q40" s="6" t="n">
         <v>0</v>
@@ -3424,13 +3424,13 @@
         <v>1</v>
       </c>
       <c r="N41" s="6" t="n">
-        <v>2.856737565633293e-06</v>
+        <v>2.867602371100902e-06</v>
       </c>
       <c r="O41" s="6" t="n">
-        <v>2.856737565633293e-06</v>
+        <v>2.867602371100902e-06</v>
       </c>
       <c r="P41" s="6" t="n">
-        <v>-2.856737565633293e-06</v>
+        <v>-2.867602371100902e-06</v>
       </c>
       <c r="Q41" s="6" t="n">
         <v>0</v>
@@ -3489,13 +3489,13 @@
         <v>1</v>
       </c>
       <c r="N42" s="6" t="n">
-        <v>1.200073500014567e-06</v>
+        <v>1.204637645241396e-06</v>
       </c>
       <c r="O42" s="6" t="n">
-        <v>1.200073500014567e-06</v>
+        <v>1.204637645241396e-06</v>
       </c>
       <c r="P42" s="6" t="n">
-        <v>-4.933666932055665e-07</v>
+        <v>-4.979308384323964e-07</v>
       </c>
       <c r="Q42" s="6" t="n">
         <v>0</v>
@@ -3554,13 +3554,13 @@
         <v>1</v>
       </c>
       <c r="N43" s="6" t="n">
-        <v>1.725274558453813e-07</v>
+        <v>1.731836159589779e-07</v>
       </c>
       <c r="O43" s="6" t="n">
-        <v>1.725274558453813e-07</v>
+        <v>1.731836159589779e-07</v>
       </c>
       <c r="P43" s="6" t="n">
-        <v>-1.725274558453813e-07</v>
+        <v>-1.731836159589779e-07</v>
       </c>
       <c r="Q43" s="6" t="n">
         <v>0</v>
@@ -4687,11 +4687,11 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Reference rate (effr), period avg</t>
+          <t>Reference rate (tbill_3m), period avg</t>
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>0.03628709677419355</v>
+        <v>0.03689032258064516</v>
       </c>
     </row>
     <row r="10">
@@ -4701,7 +4701,7 @@
         </is>
       </c>
       <c r="B10" s="7" t="n">
-        <v>0.03682465368903005</v>
+        <v>0.03732734186107307</v>
       </c>
     </row>
     <row r="11">
@@ -4711,7 +4711,7 @@
         </is>
       </c>
       <c r="B11" s="10" t="n">
-        <v>0.03871416843742665</v>
+        <v>0.03886397464150784</v>
       </c>
     </row>
     <row r="12">
@@ -4721,7 +4721,7 @@
         </is>
       </c>
       <c r="B12" s="11" t="n">
-        <v>-8.009872259572633</v>
+        <v>-6.511810218760741</v>
       </c>
     </row>
     <row r="13">
@@ -4731,7 +4731,7 @@
         </is>
       </c>
       <c r="B13" s="12" t="n">
-        <v>219906.399780756</v>
+        <v>178734.630204236</v>
       </c>
     </row>
     <row r="15">
@@ -4751,7 +4751,7 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>10825499.00626334</v>
+        <v>10866670.77583986</v>
       </c>
     </row>
     <row r="17">
@@ -4761,7 +4761,7 @@
         </is>
       </c>
       <c r="B17" s="12" t="n">
-        <v>219906.399780756</v>
+        <v>178734.630204236</v>
       </c>
     </row>
     <row r="19">
@@ -4791,7 +4791,7 @@
         <v>1000000000</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>3071515.028317151</v>
+        <v>3112686.797893671</v>
       </c>
     </row>
     <row r="21">
@@ -4826,7 +4826,7 @@
         </is>
       </c>
       <c r="B24" s="3" t="n">
-        <v>10640588.58756836</v>
+        <v>10681760.35714488</v>
       </c>
     </row>
     <row r="25">
@@ -4846,7 +4846,7 @@
         </is>
       </c>
       <c r="B26" s="3" t="n">
-        <v>10681122.54508365</v>
+        <v>10722294.31466017</v>
       </c>
     </row>
     <row r="28">
@@ -4863,7 +4863,7 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>13391864.98596525</v>
+        <v>13433036.75554177</v>
       </c>
     </row>
     <row r="31">
@@ -4873,7 +4873,7 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>10640588.58756836</v>
+        <v>10681760.35714488</v>
       </c>
     </row>
     <row r="32">
@@ -4967,7 +4967,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>effr</t>
+          <t>tbill_3m</t>
         </is>
       </c>
     </row>
@@ -5413,16 +5413,16 @@
         <v>4</v>
       </c>
       <c r="L6" s="7" t="n">
-        <v>0.0364</v>
+        <v>0.0368</v>
       </c>
       <c r="M6" s="7" t="n">
-        <v>0.03693491707043663</v>
+        <v>0.03726825040376996</v>
       </c>
       <c r="N6" s="3" t="n">
-        <v>337334.6074229946</v>
+        <v>338215.2667380225</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>414243.5423272011</v>
+        <v>415124.201642229</v>
       </c>
     </row>
     <row r="7">
@@ -5462,16 +5462,16 @@
         <v>4</v>
       </c>
       <c r="L7" s="7" t="n">
-        <v>0.0364</v>
+        <v>0.0368</v>
       </c>
       <c r="M7" s="7" t="n">
-        <v>0.03693491707043663</v>
+        <v>0.03726825040376996</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>374272.6793009383</v>
+        <v>375153.3386159662</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>450593.1931929035</v>
+        <v>451473.8525079314</v>
       </c>
     </row>
     <row r="8">
@@ -5511,16 +5511,16 @@
         <v>4</v>
       </c>
       <c r="L8" s="7" t="n">
-        <v>0.0364</v>
+        <v>0.0368</v>
       </c>
       <c r="M8" s="7" t="n">
-        <v>0.03693491707043663</v>
+        <v>0.03726825040376996</v>
       </c>
       <c r="N8" s="3" t="n">
-        <v>373622.2203959758</v>
+        <v>374502.8797110037</v>
       </c>
       <c r="O8" s="3" t="n">
-        <v>450469.9897907797</v>
+        <v>451350.6491058076</v>
       </c>
     </row>
     <row r="9">
@@ -5560,16 +5560,16 @@
         <v>4</v>
       </c>
       <c r="L9" s="7" t="n">
-        <v>0.0364</v>
+        <v>0.037</v>
       </c>
       <c r="M9" s="7" t="n">
-        <v>0.03693491707043663</v>
+        <v>0.03743491707043663</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>363498.7068655675</v>
+        <v>364819.5900073207</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>439555.1003258834</v>
+        <v>440875.9834676367</v>
       </c>
     </row>
     <row r="10">
@@ -5609,16 +5609,16 @@
         <v>4</v>
       </c>
       <c r="L10" s="7" t="n">
-        <v>0.0364</v>
+        <v>0.037</v>
       </c>
       <c r="M10" s="7" t="n">
-        <v>0.03693491707043663</v>
+        <v>0.03743491707043663</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>358810.6035501668</v>
+        <v>360131.4866919201</v>
       </c>
       <c r="O10" s="3" t="n">
-        <v>434343.0916681122</v>
+        <v>435663.9748098655</v>
       </c>
     </row>
     <row r="11">
@@ -5658,16 +5658,16 @@
         <v>4</v>
       </c>
       <c r="L11" s="7" t="n">
-        <v>0.0364</v>
+        <v>0.037</v>
       </c>
       <c r="M11" s="7" t="n">
-        <v>0.03693491707043663</v>
+        <v>0.03743491707043663</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>336881.6142373614</v>
+        <v>338202.4973791146</v>
       </c>
       <c r="O11" s="3" t="n">
-        <v>412771.0234410728</v>
+        <v>414091.9065828261</v>
       </c>
     </row>
     <row r="12">
@@ -5707,16 +5707,16 @@
         <v>4</v>
       </c>
       <c r="L12" s="7" t="n">
-        <v>0.0364</v>
+        <v>0.037</v>
       </c>
       <c r="M12" s="7" t="n">
-        <v>0.03693491707043663</v>
+        <v>0.03743491707043663</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>343781.6670466586</v>
+        <v>345102.5501884118</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>419001.6270619906</v>
+        <v>420322.5102037438</v>
       </c>
     </row>
     <row r="13">
@@ -5756,16 +5756,16 @@
         <v>4</v>
       </c>
       <c r="L13" s="7" t="n">
-        <v>0.0364</v>
+        <v>0.037</v>
       </c>
       <c r="M13" s="7" t="n">
-        <v>0.03693491707043663</v>
+        <v>0.03743491707043663</v>
       </c>
       <c r="N13" s="3" t="n">
-        <v>265801.2902985573</v>
+        <v>267122.1734403106</v>
       </c>
       <c r="O13" s="3" t="n">
-        <v>339216.1773025376</v>
+        <v>340537.0604442909</v>
       </c>
     </row>
     <row r="14">
@@ -5805,16 +5805,16 @@
         <v>4</v>
       </c>
       <c r="L14" s="7" t="n">
-        <v>0.0364</v>
+        <v>0.037</v>
       </c>
       <c r="M14" s="7" t="n">
-        <v>0.03693491707043663</v>
+        <v>0.03743491707043663</v>
       </c>
       <c r="N14" s="3" t="n">
-        <v>347654.8323519505</v>
+        <v>348975.7154937037</v>
       </c>
       <c r="O14" s="3" t="n">
-        <v>422617.4327683006</v>
+        <v>423938.3159100538</v>
       </c>
     </row>
     <row r="15">
@@ -5854,16 +5854,16 @@
         <v>4</v>
       </c>
       <c r="L15" s="7" t="n">
-        <v>0.0364</v>
+        <v>0.037</v>
       </c>
       <c r="M15" s="7" t="n">
-        <v>0.03693491707043663</v>
+        <v>0.03743491707043663</v>
       </c>
       <c r="N15" s="3" t="n">
-        <v>362990.4740527779</v>
+        <v>364311.3571945312</v>
       </c>
       <c r="O15" s="3" t="n">
-        <v>438829.0783037072</v>
+        <v>440149.9614454605</v>
       </c>
     </row>
     <row r="16">
@@ -5903,16 +5903,16 @@
         <v>4</v>
       </c>
       <c r="L16" s="7" t="n">
-        <v>0.0363</v>
+        <v>0.037</v>
       </c>
       <c r="M16" s="7" t="n">
-        <v>0.0368515837371033</v>
+        <v>0.03743491707043663</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>352279.0442647091</v>
+        <v>353820.1363477663</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>431507.6703348673</v>
+        <v>433048.7624179245</v>
       </c>
     </row>
     <row r="17">
@@ -5952,16 +5952,16 @@
         <v>4</v>
       </c>
       <c r="L17" s="7" t="n">
-        <v>0.0363</v>
+        <v>0.037</v>
       </c>
       <c r="M17" s="7" t="n">
-        <v>0.0368515837371033</v>
+        <v>0.03743491707043663</v>
       </c>
       <c r="N17" s="3" t="n">
-        <v>345666.1373893456</v>
+        <v>347207.2294724027</v>
       </c>
       <c r="O17" s="3" t="n">
-        <v>423171.9641792552</v>
+        <v>424713.0562623124</v>
       </c>
     </row>
     <row r="18">
@@ -6001,16 +6001,16 @@
         <v>4</v>
       </c>
       <c r="L18" s="7" t="n">
-        <v>0.0363</v>
+        <v>0.037</v>
       </c>
       <c r="M18" s="7" t="n">
-        <v>0.0368515837371033</v>
+        <v>0.03743491707043663</v>
       </c>
       <c r="N18" s="3" t="n">
-        <v>344727.0510100425</v>
+        <v>346268.1430930997</v>
       </c>
       <c r="O18" s="3" t="n">
-        <v>423267.6885049809</v>
+        <v>424808.7805880381</v>
       </c>
     </row>
     <row r="19">
@@ -6050,16 +6050,16 @@
         <v>4</v>
       </c>
       <c r="L19" s="7" t="n">
-        <v>0.0363</v>
+        <v>0.037</v>
       </c>
       <c r="M19" s="7" t="n">
-        <v>0.0368515837371033</v>
+        <v>0.03743491707043663</v>
       </c>
       <c r="N19" s="3" t="n">
-        <v>348443.1706486071</v>
+        <v>349984.2627316643</v>
       </c>
       <c r="O19" s="3" t="n">
-        <v>427360.7512641225</v>
+        <v>428901.8433471797</v>
       </c>
     </row>
     <row r="20">
@@ -6099,16 +6099,16 @@
         <v>4</v>
       </c>
       <c r="L20" s="7" t="n">
-        <v>0.0363</v>
+        <v>0.037</v>
       </c>
       <c r="M20" s="7" t="n">
-        <v>0.0368515837371033</v>
+        <v>0.03743491707043663</v>
       </c>
       <c r="N20" s="3" t="n">
-        <v>351850.3264145331</v>
+        <v>353391.4184975902</v>
       </c>
       <c r="O20" s="3" t="n">
-        <v>431203.3537667908</v>
+        <v>432744.445849848</v>
       </c>
     </row>
     <row r="21">
@@ -6148,16 +6148,16 @@
         <v>4</v>
       </c>
       <c r="L21" s="7" t="n">
-        <v>0.0363</v>
+        <v>0.037</v>
       </c>
       <c r="M21" s="7" t="n">
-        <v>0.0368515837371033</v>
+        <v>0.03743491707043663</v>
       </c>
       <c r="N21" s="3" t="n">
-        <v>351632.6009997061</v>
+        <v>353173.6930827632</v>
       </c>
       <c r="O21" s="3" t="n">
-        <v>432166.6729598901</v>
+        <v>433707.7650429473</v>
       </c>
     </row>
     <row r="22">
@@ -6197,16 +6197,16 @@
         <v>4</v>
       </c>
       <c r="L22" s="7" t="n">
-        <v>0.0363</v>
+        <v>0.037</v>
       </c>
       <c r="M22" s="7" t="n">
-        <v>0.0368515837371033</v>
+        <v>0.03743491707043663</v>
       </c>
       <c r="N22" s="3" t="n">
-        <v>349424.2258454161</v>
+        <v>350965.3179284733</v>
       </c>
       <c r="O22" s="3" t="n">
-        <v>429946.6489242385</v>
+        <v>431487.7410072957</v>
       </c>
     </row>
     <row r="23">
@@ -6246,16 +6246,16 @@
         <v>4</v>
       </c>
       <c r="L23" s="7" t="n">
-        <v>0.0362</v>
+        <v>0.0368</v>
       </c>
       <c r="M23" s="7" t="n">
-        <v>0.03676825040376996</v>
+        <v>0.03726825040376996</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>365709.4116342401</v>
+        <v>367030.5064828676</v>
       </c>
       <c r="O23" s="3" t="n">
-        <v>451824.132648079</v>
+        <v>453145.2274967065</v>
       </c>
     </row>
     <row r="24">
@@ -6295,16 +6295,16 @@
         <v>4</v>
       </c>
       <c r="L24" s="7" t="n">
-        <v>0.0362</v>
+        <v>0.0368</v>
       </c>
       <c r="M24" s="7" t="n">
-        <v>0.03676825040376996</v>
+        <v>0.03726825040376996</v>
       </c>
       <c r="N24" s="3" t="n">
-        <v>361107.8874086158</v>
+        <v>362428.9822572433</v>
       </c>
       <c r="O24" s="3" t="n">
-        <v>448566.8371441148</v>
+        <v>449887.9319927423</v>
       </c>
     </row>
     <row r="25">
@@ -6344,16 +6344,16 @@
         <v>4</v>
       </c>
       <c r="L25" s="7" t="n">
-        <v>0.0362</v>
+        <v>0.0368</v>
       </c>
       <c r="M25" s="7" t="n">
-        <v>0.03676825040376996</v>
+        <v>0.03726825040376996</v>
       </c>
       <c r="N25" s="3" t="n">
-        <v>333665.3148069651</v>
+        <v>334986.4096555927</v>
       </c>
       <c r="O25" s="3" t="n">
-        <v>420743.9106240411</v>
+        <v>422065.0054726686</v>
       </c>
     </row>
     <row r="26">
@@ -6393,16 +6393,16 @@
         <v>4</v>
       </c>
       <c r="L26" s="7" t="n">
-        <v>0.0362</v>
+        <v>0.0368</v>
       </c>
       <c r="M26" s="7" t="n">
-        <v>0.03676825040376996</v>
+        <v>0.03726825040376996</v>
       </c>
       <c r="N26" s="3" t="n">
-        <v>324962.3908041572</v>
+        <v>326283.4856527848</v>
       </c>
       <c r="O26" s="3" t="n">
-        <v>414829.2237389592</v>
+        <v>416150.3185875867</v>
       </c>
     </row>
     <row r="27">
@@ -6442,16 +6442,16 @@
         <v>4</v>
       </c>
       <c r="L27" s="7" t="n">
-        <v>0.0362</v>
+        <v>0.0368</v>
       </c>
       <c r="M27" s="7" t="n">
-        <v>0.03676825040376996</v>
+        <v>0.03726825040376996</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>379185.8060542876</v>
+        <v>380506.9009029152</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>468277.7087264755</v>
+        <v>469598.8035751031</v>
       </c>
     </row>
     <row r="28">
@@ -6491,16 +6491,16 @@
         <v>4</v>
       </c>
       <c r="L28" s="7" t="n">
-        <v>0.0362</v>
+        <v>0.0368</v>
       </c>
       <c r="M28" s="7" t="n">
-        <v>0.03676825040376996</v>
+        <v>0.03726825040376996</v>
       </c>
       <c r="N28" s="3" t="n">
-        <v>377000.5347091127</v>
+        <v>378321.6295577402</v>
       </c>
       <c r="O28" s="3" t="n">
-        <v>466500.1759430798</v>
+        <v>467821.2707917073</v>
       </c>
     </row>
     <row r="29">
@@ -6540,16 +6540,16 @@
         <v>4</v>
       </c>
       <c r="L29" s="7" t="n">
-        <v>0.0362</v>
+        <v>0.0368</v>
       </c>
       <c r="M29" s="7" t="n">
-        <v>0.03676825040376996</v>
+        <v>0.03726825040376996</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>378608.4459296824</v>
+        <v>379929.5407783099</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>468472.6929685309</v>
+        <v>469793.7878171585</v>
       </c>
     </row>
     <row r="30">
@@ -6589,16 +6589,16 @@
         <v>4</v>
       </c>
       <c r="L30" s="7" t="n">
-        <v>0.0362</v>
+        <v>0.0368</v>
       </c>
       <c r="M30" s="7" t="n">
-        <v>0.03676825040376996</v>
+        <v>0.03726825040376996</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>378008.3403677623</v>
+        <v>379329.4352163898</v>
       </c>
       <c r="O30" s="3" t="n">
-        <v>468212.9843232642</v>
+        <v>469534.0791718918</v>
       </c>
     </row>
     <row r="31">
@@ -6638,16 +6638,16 @@
         <v>4</v>
       </c>
       <c r="L31" s="7" t="n">
-        <v>0.0362</v>
+        <v>0.0368</v>
       </c>
       <c r="M31" s="7" t="n">
-        <v>0.03668466737761376</v>
+        <v>0.03718466737761376</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>352337.3261667297</v>
+        <v>353658.5272115202</v>
       </c>
       <c r="O31" s="3" t="n">
-        <v>435181.9142288258</v>
+        <v>436503.1152736163</v>
       </c>
     </row>
     <row r="32">
@@ -6687,16 +6687,16 @@
         <v>4</v>
       </c>
       <c r="L32" s="7" t="n">
-        <v>0.0362</v>
+        <v>0.0368</v>
       </c>
       <c r="M32" s="7" t="n">
-        <v>0.03668466737761376</v>
+        <v>0.03718466737761376</v>
       </c>
       <c r="N32" s="3" t="n">
-        <v>335363.1836146039</v>
+        <v>336684.3846593943</v>
       </c>
       <c r="O32" s="3" t="n">
-        <v>421508.318950465</v>
+        <v>422829.5199952555</v>
       </c>
     </row>
     <row r="33">
@@ -6736,16 +6736,16 @@
         <v>4</v>
       </c>
       <c r="L33" s="7" t="n">
-        <v>0.0362</v>
+        <v>0.0368</v>
       </c>
       <c r="M33" s="7" t="n">
-        <v>0.03668466737761376</v>
+        <v>0.03718466737761376</v>
       </c>
       <c r="N33" s="3" t="n">
-        <v>332053.2827393732</v>
+        <v>333374.4837841637</v>
       </c>
       <c r="O33" s="3" t="n">
-        <v>422626.9512378465</v>
+        <v>423948.152282637</v>
       </c>
     </row>
     <row r="34">
@@ -6785,16 +6785,16 @@
         <v>4</v>
       </c>
       <c r="L34" s="7" t="n">
-        <v>0.0362</v>
+        <v>0.0368</v>
       </c>
       <c r="M34" s="7" t="n">
-        <v>0.03668466737761376</v>
+        <v>0.03718466737761376</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>334722.5280083754</v>
+        <v>336043.7290531659</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>430938.0887659761</v>
+        <v>432259.2898107666</v>
       </c>
     </row>
     <row r="35">
@@ -6834,16 +6834,16 @@
         <v>4</v>
       </c>
       <c r="L35" s="7" t="n">
-        <v>0.0362</v>
+        <v>0.0368</v>
       </c>
       <c r="M35" s="7" t="n">
-        <v>0.03668466737761376</v>
+        <v>0.03718466737761376</v>
       </c>
       <c r="N35" s="3" t="n">
-        <v>332371.9440256246</v>
+        <v>333693.1450704151</v>
       </c>
       <c r="O35" s="3" t="n">
-        <v>427593.374089083</v>
+        <v>428914.5751338735</v>
       </c>
     </row>
     <row r="36">
@@ -6883,16 +6883,16 @@
         <v>4</v>
       </c>
       <c r="L36" s="7" t="n">
-        <v>0.0362</v>
+        <v>0.0368</v>
       </c>
       <c r="M36" s="7" t="n">
-        <v>0.03668466737761376</v>
+        <v>0.03718466737761376</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>331731.357898502</v>
+        <v>333052.5589432925</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>426323.6664598752</v>
+        <v>427644.8675046656</v>
       </c>
     </row>
     <row r="38">
@@ -6914,10 +6914,10 @@
       <c r="L38" t="inlineStr"/>
       <c r="M38" t="inlineStr"/>
       <c r="N38" s="12" t="n">
-        <v>10825499.00626334</v>
+        <v>10866670.77583986</v>
       </c>
       <c r="O38" s="12" t="n">
-        <v>13391864.98596525</v>
+        <v>13433036.75554177</v>
       </c>
     </row>
   </sheetData>

--- a/settlements/spark/2026-05/spark_settlement_may_2026.xlsx
+++ b/settlements/spark/2026-05/spark_settlement_may_2026.xlsx
@@ -539,7 +539,7 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>10681760.35714488</v>
+        <v>10679339.17037492</v>
       </c>
     </row>
     <row r="11">
@@ -555,7 +555,7 @@
     <row r="12">
       <c r="A12" t="inlineStr"/>
       <c r="B12" s="4" t="n">
-        <v>10722294.31466017</v>
+        <v>10719873.1278902</v>
       </c>
     </row>
     <row r="14">
@@ -577,7 +577,7 @@
         </is>
       </c>
       <c r="B15" s="3" t="n">
-        <v>10681760.35714488</v>
+        <v>10679339.17037492</v>
       </c>
     </row>
     <row r="16">
@@ -593,7 +593,7 @@
     <row r="17">
       <c r="A17" t="inlineStr"/>
       <c r="B17" s="4" t="n">
-        <v>13433036.75554177</v>
+        <v>13430615.56877181</v>
       </c>
     </row>
     <row r="19">
@@ -635,13 +635,13 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>-10681760.35714488</v>
+        <v>-10679339.17037492</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr"/>
       <c r="B24" s="4" t="n">
-        <v>1541317.698307214</v>
+        <v>1543738.885077177</v>
       </c>
     </row>
     <row r="26">
@@ -676,7 +676,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-07-30T23:20:11+00:00</t>
+          <t>2026-07-31T00:21:48+00:00</t>
         </is>
       </c>
     </row>
@@ -873,13 +873,13 @@
         <v>1</v>
       </c>
       <c r="N2" s="6" t="n">
-        <v>4394963.3688284</v>
+        <v>4393984.133570189</v>
       </c>
       <c r="O2" s="6" t="n">
-        <v>4394963.3688284</v>
+        <v>4393984.133570189</v>
       </c>
       <c r="P2" s="6" t="n">
-        <v>-560512.4596992081</v>
+        <v>-559533.2244409967</v>
       </c>
       <c r="Q2" s="6" t="n">
         <v>0</v>
@@ -938,13 +938,13 @@
         <v>1</v>
       </c>
       <c r="N3" s="6" t="n">
-        <v>1553280.572088632</v>
+        <v>1552934.487952215</v>
       </c>
       <c r="O3" s="6" t="n">
-        <v>1553280.572088632</v>
+        <v>1552934.487952215</v>
       </c>
       <c r="P3" s="6" t="n">
-        <v>314831.5961473684</v>
+        <v>315177.6802837852</v>
       </c>
       <c r="Q3" s="6" t="n">
         <v>0</v>
@@ -1003,13 +1003,13 @@
         <v>1</v>
       </c>
       <c r="N4" s="6" t="n">
-        <v>1423148.206453442</v>
+        <v>1422831.116916063</v>
       </c>
       <c r="O4" s="6" t="n">
-        <v>1423148.206453442</v>
+        <v>1422831.116916063</v>
       </c>
       <c r="P4" s="6" t="n">
-        <v>1668431.793546548</v>
+        <v>1668748.883083927</v>
       </c>
       <c r="Q4" s="6" t="n">
         <v>0</v>
@@ -1068,13 +1068,13 @@
         <v>1</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>1127198.451529777</v>
+        <v>1126947.302117573</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>1127198.451529777</v>
+        <v>1126947.302117573</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>-1127198.451529777</v>
+        <v>-1126947.302117573</v>
       </c>
       <c r="Q5" s="6" t="n">
         <v>0</v>
@@ -1133,13 +1133,13 @@
         <v>1</v>
       </c>
       <c r="N6" s="6" t="n">
-        <v>415174.4106326225</v>
+        <v>415081.9062390519</v>
       </c>
       <c r="O6" s="6" t="n">
-        <v>415174.4106326225</v>
+        <v>415081.9062390519</v>
       </c>
       <c r="P6" s="6" t="n">
-        <v>144278.5286085968</v>
+        <v>144371.0330021674</v>
       </c>
       <c r="Q6" s="6" t="n">
         <v>86642406.62655522</v>
@@ -1202,13 +1202,13 @@
         <v>1</v>
       </c>
       <c r="N7" s="6" t="n">
-        <v>331420.4808036443</v>
+        <v>331346.637498738</v>
       </c>
       <c r="O7" s="6" t="n">
-        <v>294955.6669618467</v>
+        <v>294881.8236569404</v>
       </c>
       <c r="P7" s="6" t="n">
-        <v>104622.5681113802</v>
+        <v>104696.4114162865</v>
       </c>
       <c r="Q7" s="6" t="n">
         <v>0</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="N8" s="6" t="n">
-        <v>242976.0057794839</v>
+        <v>242921.8686566477</v>
       </c>
       <c r="O8" s="6" t="n">
-        <v>242976.0057794839</v>
+        <v>242921.8686566477</v>
       </c>
       <c r="P8" s="6" t="n">
-        <v>180554.6028037178</v>
+        <v>180608.7399265539</v>
       </c>
       <c r="Q8" s="6" t="n">
         <v>0</v>
@@ -1332,13 +1332,13 @@
         <v>1</v>
       </c>
       <c r="N9" s="6" t="n">
-        <v>231231.613848747</v>
+        <v>231180.0934764272</v>
       </c>
       <c r="O9" s="6" t="n">
-        <v>231231.613848747</v>
+        <v>231180.0934764272</v>
       </c>
       <c r="P9" s="6" t="n">
-        <v>-202227.643148747</v>
+        <v>-202176.1227764272</v>
       </c>
       <c r="Q9" s="6" t="n">
         <v>0</v>
@@ -1397,13 +1397,13 @@
         <v>1</v>
       </c>
       <c r="N10" s="6" t="n">
-        <v>231227.7855191266</v>
+        <v>231176.2659997913</v>
       </c>
       <c r="O10" s="6" t="n">
-        <v>231227.7855191266</v>
+        <v>231176.2659997913</v>
       </c>
       <c r="P10" s="6" t="n">
-        <v>-224841.9016474863</v>
+        <v>-224790.382128151</v>
       </c>
       <c r="Q10" s="6" t="n">
         <v>0</v>
@@ -1462,13 +1462,13 @@
         <v>1</v>
       </c>
       <c r="N11" s="6" t="n">
-        <v>235950.6923058526</v>
+        <v>235898.1204826733</v>
       </c>
       <c r="O11" s="6" t="n">
-        <v>209990.0212878363</v>
+        <v>209937.4494646571</v>
       </c>
       <c r="P11" s="6" t="n">
-        <v>74484.73708334846</v>
+        <v>74537.30890652772</v>
       </c>
       <c r="Q11" s="6" t="n">
         <v>0</v>
@@ -1527,13 +1527,13 @@
         <v>1</v>
       </c>
       <c r="N12" s="6" t="n">
-        <v>207229.3482344405</v>
+        <v>207183.1757712599</v>
       </c>
       <c r="O12" s="6" t="n">
-        <v>207229.3482344405</v>
+        <v>207183.1757712599</v>
       </c>
       <c r="P12" s="6" t="n">
-        <v>10040.04821219848</v>
+        <v>10086.22067537909</v>
       </c>
       <c r="Q12" s="6" t="n">
         <v>0</v>
@@ -1592,13 +1592,13 @@
         <v>1</v>
       </c>
       <c r="N13" s="6" t="n">
-        <v>175210.6618695063</v>
+        <v>175171.6234422616</v>
       </c>
       <c r="O13" s="6" t="n">
-        <v>155932.9631808879</v>
+        <v>155893.9247536432</v>
       </c>
       <c r="P13" s="6" t="n">
-        <v>55310.36995913038</v>
+        <v>55349.40838637509</v>
       </c>
       <c r="Q13" s="6" t="n">
         <v>0</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="N14" s="6" t="n">
-        <v>133493.0265704061</v>
+        <v>133463.2831874987</v>
       </c>
       <c r="O14" s="6" t="n">
-        <v>133493.0265704061</v>
+        <v>133463.2831874987</v>
       </c>
       <c r="P14" s="6" t="n">
-        <v>160598.4903060379</v>
+        <v>160628.2336889453</v>
       </c>
       <c r="Q14" s="6" t="n">
         <v>103099818.9104406</v>
@@ -1787,13 +1787,13 @@
         <v>1</v>
       </c>
       <c r="N16" s="6" t="n">
-        <v>68613.25052061575</v>
+        <v>68597.9629042122</v>
       </c>
       <c r="O16" s="6" t="n">
-        <v>68613.25052061575</v>
+        <v>68597.9629042122</v>
       </c>
       <c r="P16" s="6" t="n">
-        <v>51028.36740535688</v>
+        <v>51043.65502176042</v>
       </c>
       <c r="Q16" s="6" t="n">
         <v>0</v>
@@ -1921,13 +1921,13 @@
         <v>1</v>
       </c>
       <c r="N18" s="6" t="n">
-        <v>22004.18615157126</v>
+        <v>21999.28343154845</v>
       </c>
       <c r="O18" s="6" t="n">
-        <v>22004.18615157126</v>
+        <v>21999.28343154845</v>
       </c>
       <c r="P18" s="6" t="n">
-        <v>-302.7146488736535</v>
+        <v>-297.811928850844</v>
       </c>
       <c r="Q18" s="6" t="n">
         <v>0</v>
@@ -1986,13 +1986,13 @@
         <v>1</v>
       </c>
       <c r="N19" s="6" t="n">
-        <v>21560.12800258652</v>
+        <v>21555.3242225001</v>
       </c>
       <c r="O19" s="6" t="n">
-        <v>21560.12800258652</v>
+        <v>21555.3242225001</v>
       </c>
       <c r="P19" s="6" t="n">
-        <v>10942.77535041349</v>
+        <v>10947.5791304999</v>
       </c>
       <c r="Q19" s="6" t="n">
         <v>0</v>
@@ -2051,13 +2051,13 @@
         <v>1</v>
       </c>
       <c r="N20" s="6" t="n">
-        <v>11581.21744718316</v>
+        <v>11578.63705333103</v>
       </c>
       <c r="O20" s="6" t="n">
-        <v>11581.21744718316</v>
+        <v>11578.63705333103</v>
       </c>
       <c r="P20" s="6" t="n">
-        <v>-11581.21744718316</v>
+        <v>-11578.63705333103</v>
       </c>
       <c r="Q20" s="6" t="n">
         <v>0</v>
@@ -2116,13 +2116,13 @@
         <v>1</v>
       </c>
       <c r="N21" s="6" t="n">
-        <v>11563.0555225023</v>
+        <v>11560.47917528162</v>
       </c>
       <c r="O21" s="6" t="n">
-        <v>11563.0555225023</v>
+        <v>11560.47917528162</v>
       </c>
       <c r="P21" s="6" t="n">
-        <v>-11563.0555225023</v>
+        <v>-11560.47917528162</v>
       </c>
       <c r="Q21" s="6" t="n">
         <v>0</v>
@@ -2181,13 +2181,13 @@
         <v>1</v>
       </c>
       <c r="N22" s="6" t="n">
-        <v>11561.38314665597</v>
+        <v>11558.80717205487</v>
       </c>
       <c r="O22" s="6" t="n">
-        <v>11561.38314665597</v>
+        <v>11558.80717205487</v>
       </c>
       <c r="P22" s="6" t="n">
-        <v>-11561.38314665597</v>
+        <v>-11558.80717205487</v>
       </c>
       <c r="Q22" s="6" t="n">
         <v>0</v>
@@ -2246,13 +2246,13 @@
         <v>1</v>
       </c>
       <c r="N23" s="6" t="n">
-        <v>11552.78068996513</v>
+        <v>11550.20663206462</v>
       </c>
       <c r="O23" s="6" t="n">
-        <v>11552.78068996513</v>
+        <v>11550.20663206462</v>
       </c>
       <c r="P23" s="6" t="n">
-        <v>-11552.78068996513</v>
+        <v>-11550.20663206462</v>
       </c>
       <c r="Q23" s="6" t="n">
         <v>0</v>
@@ -2311,13 +2311,13 @@
         <v>1</v>
       </c>
       <c r="N24" s="6" t="n">
-        <v>3450.045471093204</v>
+        <v>3449.276771587837</v>
       </c>
       <c r="O24" s="6" t="n">
-        <v>3450.045471093204</v>
+        <v>3449.276771587837</v>
       </c>
       <c r="P24" s="6" t="n">
-        <v>1354.842709051775</v>
+        <v>1355.611408557143</v>
       </c>
       <c r="Q24" s="6" t="n">
         <v>0</v>
@@ -2376,13 +2376,13 @@
         <v>1</v>
       </c>
       <c r="N25" s="6" t="n">
-        <v>2271.635001856072</v>
+        <v>2271.128862236483</v>
       </c>
       <c r="O25" s="6" t="n">
-        <v>2021.696472835984</v>
+        <v>2021.190333216395</v>
       </c>
       <c r="P25" s="6" t="n">
-        <v>717.1080288387201</v>
+        <v>717.6141684583088</v>
       </c>
       <c r="Q25" s="6" t="n">
         <v>0</v>
@@ -2510,13 +2510,13 @@
         <v>1</v>
       </c>
       <c r="N27" s="6" t="n">
-        <v>5.594800153805263</v>
+        <v>5.593553584695698</v>
       </c>
       <c r="O27" s="6" t="n">
-        <v>5.594800153805263</v>
+        <v>5.593553584695698</v>
       </c>
       <c r="P27" s="6" t="n">
-        <v>-5.594800153805263</v>
+        <v>-5.593553584695698</v>
       </c>
       <c r="Q27" s="6" t="n">
         <v>0</v>
@@ -2575,13 +2575,13 @@
         <v>1</v>
       </c>
       <c r="N28" s="6" t="n">
-        <v>1.068662386742331</v>
+        <v>1.06842427966375</v>
       </c>
       <c r="O28" s="6" t="n">
-        <v>1.068662386742331</v>
+        <v>1.06842427966375</v>
       </c>
       <c r="P28" s="6" t="n">
-        <v>75.26180313246341</v>
+        <v>75.26204123954199</v>
       </c>
       <c r="Q28" s="6" t="n">
         <v>0</v>
@@ -2640,13 +2640,13 @@
         <v>1</v>
       </c>
       <c r="N29" s="6" t="n">
-        <v>0.8510284472764841</v>
+        <v>0.8508388308925968</v>
       </c>
       <c r="O29" s="6" t="n">
-        <v>0.8510284472764841</v>
+        <v>0.8508388308925968</v>
       </c>
       <c r="P29" s="6" t="n">
-        <v>0.3103168278132782</v>
+        <v>0.3105064441971654</v>
       </c>
       <c r="Q29" s="6" t="n">
         <v>0</v>
@@ -2705,13 +2705,13 @@
         <v>1</v>
       </c>
       <c r="N30" s="6" t="n">
-        <v>0.6564592368314728</v>
+        <v>0.6563129721242756</v>
       </c>
       <c r="O30" s="6" t="n">
-        <v>0.6564592368314728</v>
+        <v>0.6563129721242756</v>
       </c>
       <c r="P30" s="6" t="n">
-        <v>-0.6564592368314728</v>
+        <v>-0.6563129721242756</v>
       </c>
       <c r="Q30" s="6" t="n">
         <v>0</v>
@@ -2770,13 +2770,13 @@
         <v>1</v>
       </c>
       <c r="N31" s="6" t="n">
-        <v>0.230078113979792</v>
+        <v>0.2300268506170642</v>
       </c>
       <c r="O31" s="6" t="n">
-        <v>0.230078113979792</v>
+        <v>0.2300268506170642</v>
       </c>
       <c r="P31" s="6" t="n">
-        <v>0.08168543445433413</v>
+        <v>0.08173669781706197</v>
       </c>
       <c r="Q31" s="6" t="n">
         <v>0</v>
@@ -2904,13 +2904,13 @@
         <v>1</v>
       </c>
       <c r="N33" s="6" t="n">
-        <v>0.05065492657647728</v>
+        <v>0.05064364022754941</v>
       </c>
       <c r="O33" s="6" t="n">
-        <v>0.05065492657647728</v>
+        <v>0.05064364022754941</v>
       </c>
       <c r="P33" s="6" t="n">
-        <v>-0.05064887286930728</v>
+        <v>-0.05063758652037942</v>
       </c>
       <c r="Q33" s="6" t="n">
         <v>0</v>
@@ -2969,13 +2969,13 @@
         <v>1</v>
       </c>
       <c r="N34" s="6" t="n">
-        <v>0.01363771555320693</v>
+        <v>0.01363467695406731</v>
       </c>
       <c r="O34" s="6" t="n">
-        <v>0.01363771555320693</v>
+        <v>0.01363467695406731</v>
       </c>
       <c r="P34" s="6" t="n">
-        <v>0.001752284446793072</v>
+        <v>0.001755323045932687</v>
       </c>
       <c r="Q34" s="6" t="n">
         <v>0</v>
@@ -3034,13 +3034,13 @@
         <v>1</v>
       </c>
       <c r="N35" s="6" t="n">
-        <v>0.003573931444121267</v>
+        <v>0.003573135141766317</v>
       </c>
       <c r="O35" s="6" t="n">
-        <v>0.003573931444121267</v>
+        <v>0.003573135141766317</v>
       </c>
       <c r="P35" s="6" t="n">
-        <v>8.46681506855588</v>
+        <v>8.466815864858233</v>
       </c>
       <c r="Q35" s="6" t="n">
         <v>0</v>
@@ -3099,13 +3099,13 @@
         <v>1</v>
       </c>
       <c r="N36" s="6" t="n">
-        <v>0.0003570927749819595</v>
+        <v>0.000357013211671331</v>
       </c>
       <c r="O36" s="6" t="n">
-        <v>0.0003570927749819595</v>
+        <v>0.000357013211671331</v>
       </c>
       <c r="P36" s="6" t="n">
-        <v>0.0003769072250180406</v>
+        <v>0.0003769867883286691</v>
       </c>
       <c r="Q36" s="6" t="n">
         <v>0</v>
@@ -3164,13 +3164,13 @@
         <v>1</v>
       </c>
       <c r="N37" s="6" t="n">
-        <v>0.0001336123693868625</v>
+        <v>0.0001335825994133595</v>
       </c>
       <c r="O37" s="6" t="n">
-        <v>0.0001336123693868625</v>
+        <v>0.0001335825994133595</v>
       </c>
       <c r="P37" s="6" t="n">
-        <v>5.238763061313751e-05</v>
+        <v>5.241740058664053e-05</v>
       </c>
       <c r="Q37" s="6" t="n">
         <v>0</v>
@@ -3229,13 +3229,13 @@
         <v>1</v>
       </c>
       <c r="N38" s="6" t="n">
-        <v>1.467393690408995e-05</v>
+        <v>1.467066742601075e-05</v>
       </c>
       <c r="O38" s="6" t="n">
-        <v>1.467393690408995e-05</v>
+        <v>1.467066742601075e-05</v>
       </c>
       <c r="P38" s="6" t="n">
-        <v>2.326063095910053e-06</v>
+        <v>2.32933257398925e-06</v>
       </c>
       <c r="Q38" s="6" t="n">
         <v>0</v>
@@ -3294,13 +3294,13 @@
         <v>1</v>
       </c>
       <c r="N39" s="6" t="n">
-        <v>1.32825792031706e-05</v>
+        <v>1.327961973143347e-05</v>
       </c>
       <c r="O39" s="6" t="n">
-        <v>1.32825792031706e-05</v>
+        <v>1.327961973143347e-05</v>
       </c>
       <c r="P39" s="6" t="n">
-        <v>-1.11387546978006e-05</v>
+        <v>-1.113579522606348e-05</v>
       </c>
       <c r="Q39" s="6" t="n">
         <v>0</v>
@@ -3359,13 +3359,13 @@
         <v>1</v>
       </c>
       <c r="N40" s="6" t="n">
-        <v>3.930931726592013e-06</v>
+        <v>3.930055881534553e-06</v>
       </c>
       <c r="O40" s="6" t="n">
-        <v>3.930931726592013e-06</v>
+        <v>3.930055881534553e-06</v>
       </c>
       <c r="P40" s="6" t="n">
-        <v>1.069068273407988e-06</v>
+        <v>1.069944118465447e-06</v>
       </c>
       <c r="Q40" s="6" t="n">
         <v>0</v>
@@ -3424,13 +3424,13 @@
         <v>1</v>
       </c>
       <c r="N41" s="6" t="n">
-        <v>2.867602371100902e-06</v>
+        <v>2.866963444877255e-06</v>
       </c>
       <c r="O41" s="6" t="n">
-        <v>2.867602371100902e-06</v>
+        <v>2.866963444877255e-06</v>
       </c>
       <c r="P41" s="6" t="n">
-        <v>-2.867602371100902e-06</v>
+        <v>-2.866963444877255e-06</v>
       </c>
       <c r="Q41" s="6" t="n">
         <v>0</v>
@@ -3489,13 +3489,13 @@
         <v>1</v>
       </c>
       <c r="N42" s="6" t="n">
-        <v>1.204637645241396e-06</v>
+        <v>1.2043692417175e-06</v>
       </c>
       <c r="O42" s="6" t="n">
-        <v>1.204637645241396e-06</v>
+        <v>1.2043692417175e-06</v>
       </c>
       <c r="P42" s="6" t="n">
-        <v>-4.979308384323964e-07</v>
+        <v>-4.976624349084999e-07</v>
       </c>
       <c r="Q42" s="6" t="n">
         <v>0</v>
@@ -3554,13 +3554,13 @@
         <v>1</v>
       </c>
       <c r="N43" s="6" t="n">
-        <v>1.731836159589779e-07</v>
+        <v>1.731450291748208e-07</v>
       </c>
       <c r="O43" s="6" t="n">
-        <v>1.731836159589779e-07</v>
+        <v>1.731450291748208e-07</v>
       </c>
       <c r="P43" s="6" t="n">
-        <v>-1.731836159589779e-07</v>
+        <v>-1.731450291748208e-07</v>
       </c>
       <c r="Q43" s="6" t="n">
         <v>0</v>
@@ -4691,7 +4691,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>0.03689032258064516</v>
+        <v>0.03685483870967742</v>
       </c>
     </row>
     <row r="10">
@@ -4701,7 +4701,7 @@
         </is>
       </c>
       <c r="B10" s="7" t="n">
-        <v>0.03732734186107307</v>
+        <v>0.03729777196859994</v>
       </c>
     </row>
     <row r="11">
@@ -4711,7 +4711,7 @@
         </is>
       </c>
       <c r="B11" s="10" t="n">
-        <v>0.03886397464150784</v>
+        <v>0.038855162511856</v>
       </c>
     </row>
     <row r="12">
@@ -4721,7 +4721,7 @@
         </is>
       </c>
       <c r="B12" s="11" t="n">
-        <v>-6.511810218760741</v>
+        <v>-6.599931515279089</v>
       </c>
     </row>
     <row r="13">
@@ -4731,7 +4731,7 @@
         </is>
       </c>
       <c r="B13" s="12" t="n">
-        <v>178734.630204236</v>
+        <v>181155.816974199</v>
       </c>
     </row>
     <row r="15">
@@ -4751,7 +4751,7 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>10866670.77583986</v>
+        <v>10864249.5890699</v>
       </c>
     </row>
     <row r="17">
@@ -4761,7 +4761,7 @@
         </is>
       </c>
       <c r="B17" s="12" t="n">
-        <v>178734.630204236</v>
+        <v>181155.816974199</v>
       </c>
     </row>
     <row r="19">
@@ -4791,7 +4791,7 @@
         <v>1000000000</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>3112686.797893671</v>
+        <v>3110265.611123708</v>
       </c>
     </row>
     <row r="21">
@@ -4826,7 +4826,7 @@
         </is>
       </c>
       <c r="B24" s="3" t="n">
-        <v>10681760.35714488</v>
+        <v>10679339.17037492</v>
       </c>
     </row>
     <row r="25">
@@ -4846,7 +4846,7 @@
         </is>
       </c>
       <c r="B26" s="3" t="n">
-        <v>10722294.31466017</v>
+        <v>10719873.1278902</v>
       </c>
     </row>
     <row r="28">
@@ -4863,7 +4863,7 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>13433036.75554177</v>
+        <v>13430615.56877181</v>
       </c>
     </row>
     <row r="31">
@@ -4873,7 +4873,7 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>10681760.35714488</v>
+        <v>10679339.17037492</v>
       </c>
     </row>
     <row r="32">
@@ -5609,16 +5609,16 @@
         <v>4</v>
       </c>
       <c r="L10" s="7" t="n">
-        <v>0.037</v>
+        <v>0.0369</v>
       </c>
       <c r="M10" s="7" t="n">
-        <v>0.03743491707043663</v>
+        <v>0.0373515837371033</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>360131.4866919201</v>
+        <v>359911.3835955046</v>
       </c>
       <c r="O10" s="3" t="n">
-        <v>435663.9748098655</v>
+        <v>435443.8717134499</v>
       </c>
     </row>
     <row r="11">
@@ -5658,16 +5658,16 @@
         <v>4</v>
       </c>
       <c r="L11" s="7" t="n">
-        <v>0.037</v>
+        <v>0.0369</v>
       </c>
       <c r="M11" s="7" t="n">
-        <v>0.03743491707043663</v>
+        <v>0.0373515837371033</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>338202.4973791146</v>
+        <v>337982.3942826991</v>
       </c>
       <c r="O11" s="3" t="n">
-        <v>414091.9065828261</v>
+        <v>413871.8034864106</v>
       </c>
     </row>
     <row r="12">
@@ -5707,16 +5707,16 @@
         <v>4</v>
       </c>
       <c r="L12" s="7" t="n">
-        <v>0.037</v>
+        <v>0.0369</v>
       </c>
       <c r="M12" s="7" t="n">
-        <v>0.03743491707043663</v>
+        <v>0.0373515837371033</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>345102.5501884118</v>
+        <v>344882.4470919963</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>420322.5102037438</v>
+        <v>420102.4071073283</v>
       </c>
     </row>
     <row r="13">
@@ -5756,16 +5756,16 @@
         <v>4</v>
       </c>
       <c r="L13" s="7" t="n">
-        <v>0.037</v>
+        <v>0.0369</v>
       </c>
       <c r="M13" s="7" t="n">
-        <v>0.03743491707043663</v>
+        <v>0.0373515837371033</v>
       </c>
       <c r="N13" s="3" t="n">
-        <v>267122.1734403106</v>
+        <v>266902.0703438951</v>
       </c>
       <c r="O13" s="3" t="n">
-        <v>340537.0604442909</v>
+        <v>340316.9573478753</v>
       </c>
     </row>
     <row r="14">
@@ -5805,16 +5805,16 @@
         <v>4</v>
       </c>
       <c r="L14" s="7" t="n">
-        <v>0.037</v>
+        <v>0.0369</v>
       </c>
       <c r="M14" s="7" t="n">
-        <v>0.03743491707043663</v>
+        <v>0.0373515837371033</v>
       </c>
       <c r="N14" s="3" t="n">
-        <v>348975.7154937037</v>
+        <v>348755.6123972882</v>
       </c>
       <c r="O14" s="3" t="n">
-        <v>423938.3159100538</v>
+        <v>423718.2128136383</v>
       </c>
     </row>
     <row r="15">
@@ -5854,16 +5854,16 @@
         <v>4</v>
       </c>
       <c r="L15" s="7" t="n">
-        <v>0.037</v>
+        <v>0.0369</v>
       </c>
       <c r="M15" s="7" t="n">
-        <v>0.03743491707043663</v>
+        <v>0.0373515837371033</v>
       </c>
       <c r="N15" s="3" t="n">
-        <v>364311.3571945312</v>
+        <v>364091.2540981157</v>
       </c>
       <c r="O15" s="3" t="n">
-        <v>440149.9614454605</v>
+        <v>439929.858349045</v>
       </c>
     </row>
     <row r="16">
@@ -6001,16 +6001,16 @@
         <v>4</v>
       </c>
       <c r="L18" s="7" t="n">
-        <v>0.037</v>
+        <v>0.0369</v>
       </c>
       <c r="M18" s="7" t="n">
-        <v>0.03743491707043663</v>
+        <v>0.0373515837371033</v>
       </c>
       <c r="N18" s="3" t="n">
-        <v>346268.1430930997</v>
+        <v>346048.0399966842</v>
       </c>
       <c r="O18" s="3" t="n">
-        <v>424808.7805880381</v>
+        <v>424588.6774916226</v>
       </c>
     </row>
     <row r="19">
@@ -6050,16 +6050,16 @@
         <v>4</v>
       </c>
       <c r="L19" s="7" t="n">
-        <v>0.037</v>
+        <v>0.0369</v>
       </c>
       <c r="M19" s="7" t="n">
-        <v>0.03743491707043663</v>
+        <v>0.0373515837371033</v>
       </c>
       <c r="N19" s="3" t="n">
-        <v>349984.2627316643</v>
+        <v>349764.1596352488</v>
       </c>
       <c r="O19" s="3" t="n">
-        <v>428901.8433471797</v>
+        <v>428681.7402507642</v>
       </c>
     </row>
     <row r="20">
@@ -6099,16 +6099,16 @@
         <v>4</v>
       </c>
       <c r="L20" s="7" t="n">
-        <v>0.037</v>
+        <v>0.0369</v>
       </c>
       <c r="M20" s="7" t="n">
-        <v>0.03743491707043663</v>
+        <v>0.0373515837371033</v>
       </c>
       <c r="N20" s="3" t="n">
-        <v>353391.4184975902</v>
+        <v>353171.3154011748</v>
       </c>
       <c r="O20" s="3" t="n">
-        <v>432744.445849848</v>
+        <v>432524.3427534325</v>
       </c>
     </row>
     <row r="21">
@@ -6148,16 +6148,16 @@
         <v>4</v>
       </c>
       <c r="L21" s="7" t="n">
-        <v>0.037</v>
+        <v>0.0369</v>
       </c>
       <c r="M21" s="7" t="n">
-        <v>0.03743491707043663</v>
+        <v>0.0373515837371033</v>
       </c>
       <c r="N21" s="3" t="n">
-        <v>353173.6930827632</v>
+        <v>352953.5899863477</v>
       </c>
       <c r="O21" s="3" t="n">
-        <v>433707.7650429473</v>
+        <v>433487.6619465318</v>
       </c>
     </row>
     <row r="22">
@@ -6197,16 +6197,16 @@
         <v>4</v>
       </c>
       <c r="L22" s="7" t="n">
-        <v>0.037</v>
+        <v>0.0369</v>
       </c>
       <c r="M22" s="7" t="n">
-        <v>0.03743491707043663</v>
+        <v>0.0373515837371033</v>
       </c>
       <c r="N22" s="3" t="n">
-        <v>350965.3179284733</v>
+        <v>350745.2148320578</v>
       </c>
       <c r="O22" s="3" t="n">
-        <v>431487.7410072957</v>
+        <v>431267.6379108802</v>
       </c>
     </row>
     <row r="23">
@@ -6295,16 +6295,16 @@
         <v>4</v>
       </c>
       <c r="L24" s="7" t="n">
-        <v>0.0368</v>
+        <v>0.0367</v>
       </c>
       <c r="M24" s="7" t="n">
-        <v>0.03726825040376996</v>
+        <v>0.03718491707043663</v>
       </c>
       <c r="N24" s="3" t="n">
-        <v>362428.9822572433</v>
+        <v>362208.8438903746</v>
       </c>
       <c r="O24" s="3" t="n">
-        <v>449887.9319927423</v>
+        <v>449667.7936258736</v>
       </c>
     </row>
     <row r="25">
@@ -6344,16 +6344,16 @@
         <v>4</v>
       </c>
       <c r="L25" s="7" t="n">
-        <v>0.0368</v>
+        <v>0.0365</v>
       </c>
       <c r="M25" s="7" t="n">
-        <v>0.03726825040376996</v>
+        <v>0.03701825040376996</v>
       </c>
       <c r="N25" s="3" t="n">
-        <v>334986.4096555927</v>
+        <v>334325.9416342076</v>
       </c>
       <c r="O25" s="3" t="n">
-        <v>422065.0054726686</v>
+        <v>421404.5374512835</v>
       </c>
     </row>
     <row r="26">
@@ -6736,16 +6736,16 @@
         <v>4</v>
       </c>
       <c r="L33" s="7" t="n">
-        <v>0.0368</v>
+        <v>0.0369</v>
       </c>
       <c r="M33" s="7" t="n">
-        <v>0.03718466737761376</v>
+        <v>0.0372680007109471</v>
       </c>
       <c r="N33" s="3" t="n">
-        <v>333374.4837841637</v>
+        <v>333594.622203879</v>
       </c>
       <c r="O33" s="3" t="n">
-        <v>423948.152282637</v>
+        <v>424168.2907023524</v>
       </c>
     </row>
     <row r="34">
@@ -6785,16 +6785,16 @@
         <v>4</v>
       </c>
       <c r="L34" s="7" t="n">
-        <v>0.0368</v>
+        <v>0.0369</v>
       </c>
       <c r="M34" s="7" t="n">
-        <v>0.03718466737761376</v>
+        <v>0.0372680007109471</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>336043.7290531659</v>
+        <v>336263.8674728812</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>432259.2898107666</v>
+        <v>432479.428230482</v>
       </c>
     </row>
     <row r="35">
@@ -6834,16 +6834,16 @@
         <v>4</v>
       </c>
       <c r="L35" s="7" t="n">
-        <v>0.0368</v>
+        <v>0.0369</v>
       </c>
       <c r="M35" s="7" t="n">
-        <v>0.03718466737761376</v>
+        <v>0.0372680007109471</v>
       </c>
       <c r="N35" s="3" t="n">
-        <v>333693.1450704151</v>
+        <v>333913.2834901304</v>
       </c>
       <c r="O35" s="3" t="n">
-        <v>428914.5751338735</v>
+        <v>429134.7135535888</v>
       </c>
     </row>
     <row r="36">
@@ -6883,16 +6883,16 @@
         <v>4</v>
       </c>
       <c r="L36" s="7" t="n">
-        <v>0.0368</v>
+        <v>0.0369</v>
       </c>
       <c r="M36" s="7" t="n">
-        <v>0.03718466737761376</v>
+        <v>0.0372680007109471</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>333052.5589432925</v>
+        <v>333272.6973630079</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>427644.8675046656</v>
+        <v>427865.005924381</v>
       </c>
     </row>
     <row r="38">
@@ -6914,10 +6914,10 @@
       <c r="L38" t="inlineStr"/>
       <c r="M38" t="inlineStr"/>
       <c r="N38" s="12" t="n">
-        <v>10866670.77583986</v>
+        <v>10864249.5890699</v>
       </c>
       <c r="O38" s="12" t="n">
-        <v>13433036.75554177</v>
+        <v>13430615.56877181</v>
       </c>
     </row>
   </sheetData>

--- a/settlements/spark/2026-05/spark_settlement_may_2026.xlsx
+++ b/settlements/spark/2026-05/spark_settlement_may_2026.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Venues" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sky Revenue" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sky Direct" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Debt" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Venues" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Sky Revenue" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Sky Direct" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Debt" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -539,7 +539,7 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>10640588.58756836</v>
+        <v>10679339.17037492</v>
       </c>
     </row>
     <row r="11">
@@ -555,7 +555,7 @@
     <row r="12">
       <c r="A12" t="inlineStr"/>
       <c r="B12" s="4" t="n">
-        <v>10681122.54508365</v>
+        <v>10719873.1278902</v>
       </c>
     </row>
     <row r="14">
@@ -577,7 +577,7 @@
         </is>
       </c>
       <c r="B15" s="3" t="n">
-        <v>10640588.58756836</v>
+        <v>10679339.17037492</v>
       </c>
     </row>
     <row r="16">
@@ -593,7 +593,7 @@
     <row r="17">
       <c r="A17" t="inlineStr"/>
       <c r="B17" s="4" t="n">
-        <v>13391864.98596525</v>
+        <v>13430615.56877181</v>
       </c>
     </row>
     <row r="19">
@@ -635,13 +635,13 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>-10640588.58756836</v>
+        <v>-10679339.17037492</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr"/>
       <c r="B24" s="4" t="n">
-        <v>1582489.467883734</v>
+        <v>1543738.885077177</v>
       </c>
     </row>
     <row r="26">
@@ -676,7 +676,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-07-10T11:14:08+00:00</t>
+          <t>2026-07-31T00:21:48+00:00</t>
         </is>
       </c>
     </row>
@@ -873,13 +873,13 @@
         <v>1</v>
       </c>
       <c r="N2" s="6" t="n">
-        <v>4378311.680114231</v>
+        <v>4393984.133570189</v>
       </c>
       <c r="O2" s="6" t="n">
-        <v>4378311.680114231</v>
+        <v>4393984.133570189</v>
       </c>
       <c r="P2" s="6" t="n">
-        <v>-543860.7709850385</v>
+        <v>-559533.2244409967</v>
       </c>
       <c r="Q2" s="6" t="n">
         <v>0</v>
@@ -938,13 +938,13 @@
         <v>1</v>
       </c>
       <c r="N3" s="6" t="n">
-        <v>1547395.484454993</v>
+        <v>1552934.487952215</v>
       </c>
       <c r="O3" s="6" t="n">
-        <v>1547395.484454993</v>
+        <v>1552934.487952215</v>
       </c>
       <c r="P3" s="6" t="n">
-        <v>320716.6837810071</v>
+        <v>315177.6802837852</v>
       </c>
       <c r="Q3" s="6" t="n">
         <v>0</v>
@@ -1003,13 +1003,13 @@
         <v>1</v>
       </c>
       <c r="N4" s="6" t="n">
-        <v>1417756.165851677</v>
+        <v>1422831.116916063</v>
       </c>
       <c r="O4" s="6" t="n">
-        <v>1417756.165851677</v>
+        <v>1422831.116916063</v>
       </c>
       <c r="P4" s="6" t="n">
-        <v>1673823.834148313</v>
+        <v>1668748.883083927</v>
       </c>
       <c r="Q4" s="6" t="n">
         <v>0</v>
@@ -1068,13 +1068,13 @@
         <v>1</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>1122927.708827552</v>
+        <v>1126947.302117573</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>1122927.708827552</v>
+        <v>1126947.302117573</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>-1122927.708827552</v>
+        <v>-1126947.302117573</v>
       </c>
       <c r="Q5" s="6" t="n">
         <v>0</v>
@@ -1133,13 +1133,13 @@
         <v>1</v>
       </c>
       <c r="N6" s="6" t="n">
-        <v>413601.3929603987</v>
+        <v>415081.9062390519</v>
       </c>
       <c r="O6" s="6" t="n">
-        <v>413601.3929603987</v>
+        <v>415081.9062390519</v>
       </c>
       <c r="P6" s="6" t="n">
-        <v>145851.5462808206</v>
+        <v>144371.0330021674</v>
       </c>
       <c r="Q6" s="6" t="n">
         <v>86642406.62655522</v>
@@ -1202,13 +1202,13 @@
         <v>1</v>
       </c>
       <c r="N7" s="6" t="n">
-        <v>330164.7910022265</v>
+        <v>331346.637498738</v>
       </c>
       <c r="O7" s="6" t="n">
-        <v>293699.9771604289</v>
+        <v>294881.8236569404</v>
       </c>
       <c r="P7" s="6" t="n">
-        <v>105878.2579127981</v>
+        <v>104696.4114162865</v>
       </c>
       <c r="Q7" s="6" t="n">
         <v>0</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="N8" s="6" t="n">
-        <v>242055.4154414737</v>
+        <v>242921.8686566477</v>
       </c>
       <c r="O8" s="6" t="n">
-        <v>242055.4154414737</v>
+        <v>242921.8686566477</v>
       </c>
       <c r="P8" s="6" t="n">
-        <v>181475.193141728</v>
+        <v>180608.7399265539</v>
       </c>
       <c r="Q8" s="6" t="n">
         <v>0</v>
@@ -1332,13 +1332,13 @@
         <v>1</v>
       </c>
       <c r="N9" s="6" t="n">
-        <v>230355.5208005105</v>
+        <v>231180.0934764272</v>
       </c>
       <c r="O9" s="6" t="n">
-        <v>230355.5208005105</v>
+        <v>231180.0934764272</v>
       </c>
       <c r="P9" s="6" t="n">
-        <v>-201351.5501005105</v>
+        <v>-202176.1227764272</v>
       </c>
       <c r="Q9" s="6" t="n">
         <v>0</v>
@@ -1397,13 +1397,13 @@
         <v>1</v>
       </c>
       <c r="N10" s="6" t="n">
-        <v>230351.7069757103</v>
+        <v>231176.2659997913</v>
       </c>
       <c r="O10" s="6" t="n">
-        <v>230351.7069757103</v>
+        <v>231176.2659997913</v>
       </c>
       <c r="P10" s="6" t="n">
-        <v>-223965.82310407</v>
+        <v>-224790.382128151</v>
       </c>
       <c r="Q10" s="6" t="n">
         <v>0</v>
@@ -1462,13 +1462,13 @@
         <v>1</v>
       </c>
       <c r="N11" s="6" t="n">
-        <v>235056.7195578573</v>
+        <v>235898.1204826733</v>
       </c>
       <c r="O11" s="6" t="n">
-        <v>209096.0485398411</v>
+        <v>209937.4494646571</v>
       </c>
       <c r="P11" s="6" t="n">
-        <v>75378.70983134369</v>
+        <v>74537.30890652772</v>
       </c>
       <c r="Q11" s="6" t="n">
         <v>0</v>
@@ -1527,13 +1527,13 @@
         <v>1</v>
       </c>
       <c r="N12" s="6" t="n">
-        <v>206444.195251434</v>
+        <v>207183.1757712599</v>
       </c>
       <c r="O12" s="6" t="n">
-        <v>206444.195251434</v>
+        <v>207183.1757712599</v>
       </c>
       <c r="P12" s="6" t="n">
-        <v>10825.20119520503</v>
+        <v>10086.22067537909</v>
       </c>
       <c r="Q12" s="6" t="n">
         <v>0</v>
@@ -1592,13 +1592,13 @@
         <v>1</v>
       </c>
       <c r="N13" s="6" t="n">
-        <v>174546.82166061</v>
+        <v>175171.6234422616</v>
       </c>
       <c r="O13" s="6" t="n">
-        <v>155269.1229719916</v>
+        <v>155893.9247536432</v>
       </c>
       <c r="P13" s="6" t="n">
-        <v>55974.21016802668</v>
+        <v>55349.40838637509</v>
       </c>
       <c r="Q13" s="6" t="n">
         <v>0</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="N14" s="6" t="n">
-        <v>132987.2466269989</v>
+        <v>133463.2831874987</v>
       </c>
       <c r="O14" s="6" t="n">
-        <v>132987.2466269989</v>
+        <v>133463.2831874987</v>
       </c>
       <c r="P14" s="6" t="n">
-        <v>161104.2702494451</v>
+        <v>160628.2336889453</v>
       </c>
       <c r="Q14" s="6" t="n">
         <v>103099818.9104406</v>
@@ -1787,13 +1787,13 @@
         <v>1</v>
       </c>
       <c r="N16" s="6" t="n">
-        <v>68353.28783299927</v>
+        <v>68597.9629042122</v>
       </c>
       <c r="O16" s="6" t="n">
-        <v>68353.28783299927</v>
+        <v>68597.9629042122</v>
       </c>
       <c r="P16" s="6" t="n">
-        <v>51288.33009297336</v>
+        <v>51043.65502176042</v>
       </c>
       <c r="Q16" s="6" t="n">
         <v>0</v>
@@ -1921,13 +1921,13 @@
         <v>1</v>
       </c>
       <c r="N18" s="6" t="n">
-        <v>21920.81643322426</v>
+        <v>21999.28343154845</v>
       </c>
       <c r="O18" s="6" t="n">
-        <v>21920.81643322426</v>
+        <v>21999.28343154845</v>
       </c>
       <c r="P18" s="6" t="n">
-        <v>-219.3449305266534</v>
+        <v>-297.811928850844</v>
       </c>
       <c r="Q18" s="6" t="n">
         <v>0</v>
@@ -1986,13 +1986,13 @@
         <v>1</v>
       </c>
       <c r="N19" s="6" t="n">
-        <v>21478.44073695808</v>
+        <v>21555.3242225001</v>
       </c>
       <c r="O19" s="6" t="n">
-        <v>21478.44073695808</v>
+        <v>21555.3242225001</v>
       </c>
       <c r="P19" s="6" t="n">
-        <v>11024.46261604192</v>
+        <v>10947.5791304999</v>
       </c>
       <c r="Q19" s="6" t="n">
         <v>0</v>
@@ -2051,13 +2051,13 @@
         <v>1</v>
       </c>
       <c r="N20" s="6" t="n">
-        <v>11537.33839480485</v>
+        <v>11578.63705333103</v>
       </c>
       <c r="O20" s="6" t="n">
-        <v>11537.33839480485</v>
+        <v>11578.63705333103</v>
       </c>
       <c r="P20" s="6" t="n">
-        <v>-11537.33839480485</v>
+        <v>-11578.63705333103</v>
       </c>
       <c r="Q20" s="6" t="n">
         <v>0</v>
@@ -2116,13 +2116,13 @@
         <v>1</v>
       </c>
       <c r="N21" s="6" t="n">
-        <v>11519.24528223705</v>
+        <v>11560.47917528162</v>
       </c>
       <c r="O21" s="6" t="n">
-        <v>11519.24528223705</v>
+        <v>11560.47917528162</v>
       </c>
       <c r="P21" s="6" t="n">
-        <v>-11519.24528223705</v>
+        <v>-11560.47917528162</v>
       </c>
       <c r="Q21" s="6" t="n">
         <v>0</v>
@@ -2181,13 +2181,13 @@
         <v>1</v>
       </c>
       <c r="N22" s="6" t="n">
-        <v>11517.57924270793</v>
+        <v>11558.80717205487</v>
       </c>
       <c r="O22" s="6" t="n">
-        <v>11517.57924270793</v>
+        <v>11558.80717205487</v>
       </c>
       <c r="P22" s="6" t="n">
-        <v>-11517.57924270793</v>
+        <v>-11558.80717205487</v>
       </c>
       <c r="Q22" s="6" t="n">
         <v>0</v>
@@ -2246,13 +2246,13 @@
         <v>1</v>
       </c>
       <c r="N23" s="6" t="n">
-        <v>11509.0093791058</v>
+        <v>11550.20663206462</v>
       </c>
       <c r="O23" s="6" t="n">
-        <v>11509.0093791058</v>
+        <v>11550.20663206462</v>
       </c>
       <c r="P23" s="6" t="n">
-        <v>-11509.0093791058</v>
+        <v>-11550.20663206462</v>
       </c>
       <c r="Q23" s="6" t="n">
         <v>0</v>
@@ -2311,13 +2311,13 @@
         <v>1</v>
       </c>
       <c r="N24" s="6" t="n">
-        <v>3436.973898382989</v>
+        <v>3449.276771587837</v>
       </c>
       <c r="O24" s="6" t="n">
-        <v>3436.973898382989</v>
+        <v>3449.276771587837</v>
       </c>
       <c r="P24" s="6" t="n">
-        <v>1367.914281761991</v>
+        <v>1355.611408557143</v>
       </c>
       <c r="Q24" s="6" t="n">
         <v>0</v>
@@ -2376,13 +2376,13 @@
         <v>1</v>
       </c>
       <c r="N25" s="6" t="n">
-        <v>2263.028204540898</v>
+        <v>2271.128862236483</v>
       </c>
       <c r="O25" s="6" t="n">
-        <v>2013.08967552081</v>
+        <v>2021.190333216395</v>
       </c>
       <c r="P25" s="6" t="n">
-        <v>725.7148261538939</v>
+        <v>717.6141684583088</v>
       </c>
       <c r="Q25" s="6" t="n">
         <v>0</v>
@@ -2510,13 +2510,13 @@
         <v>1</v>
       </c>
       <c r="N27" s="6" t="n">
-        <v>5.573602509419893</v>
+        <v>5.593553584695698</v>
       </c>
       <c r="O27" s="6" t="n">
-        <v>5.573602509419893</v>
+        <v>5.593553584695698</v>
       </c>
       <c r="P27" s="6" t="n">
-        <v>-5.573602509419893</v>
+        <v>-5.593553584695698</v>
       </c>
       <c r="Q27" s="6" t="n">
         <v>0</v>
@@ -2575,13 +2575,13 @@
         <v>1</v>
       </c>
       <c r="N28" s="6" t="n">
-        <v>1.064613426168328</v>
+        <v>1.06842427966375</v>
       </c>
       <c r="O28" s="6" t="n">
-        <v>1.064613426168328</v>
+        <v>1.06842427966375</v>
       </c>
       <c r="P28" s="6" t="n">
-        <v>75.26585209303741</v>
+        <v>75.26204123954199</v>
       </c>
       <c r="Q28" s="6" t="n">
         <v>0</v>
@@ -2640,13 +2640,13 @@
         <v>1</v>
       </c>
       <c r="N29" s="6" t="n">
-        <v>0.847804060722671</v>
+        <v>0.8508388308925968</v>
       </c>
       <c r="O29" s="6" t="n">
-        <v>0.847804060722671</v>
+        <v>0.8508388308925968</v>
       </c>
       <c r="P29" s="6" t="n">
-        <v>0.3135412143670913</v>
+        <v>0.3105064441971654</v>
       </c>
       <c r="Q29" s="6" t="n">
         <v>0</v>
@@ -2705,13 +2705,13 @@
         <v>1</v>
       </c>
       <c r="N30" s="6" t="n">
-        <v>0.653972036382252</v>
+        <v>0.6563129721242756</v>
       </c>
       <c r="O30" s="6" t="n">
-        <v>0.653972036382252</v>
+        <v>0.6563129721242756</v>
       </c>
       <c r="P30" s="6" t="n">
-        <v>-0.653972036382252</v>
+        <v>-0.6563129721242756</v>
       </c>
       <c r="Q30" s="6" t="n">
         <v>0</v>
@@ -2770,13 +2770,13 @@
         <v>1</v>
       </c>
       <c r="N31" s="6" t="n">
-        <v>0.2292063913253763</v>
+        <v>0.2300268506170642</v>
       </c>
       <c r="O31" s="6" t="n">
-        <v>0.2292063913253763</v>
+        <v>0.2300268506170642</v>
       </c>
       <c r="P31" s="6" t="n">
-        <v>0.08255715710874979</v>
+        <v>0.08173669781706197</v>
       </c>
       <c r="Q31" s="6" t="n">
         <v>0</v>
@@ -2904,13 +2904,13 @@
         <v>1</v>
       </c>
       <c r="N33" s="6" t="n">
-        <v>0.05046300459706486</v>
+        <v>0.05064364022754941</v>
       </c>
       <c r="O33" s="6" t="n">
-        <v>0.05046300459706486</v>
+        <v>0.05064364022754941</v>
       </c>
       <c r="P33" s="6" t="n">
-        <v>-0.05045695088989487</v>
+        <v>-0.05063758652037942</v>
       </c>
       <c r="Q33" s="6" t="n">
         <v>0</v>
@@ -2969,13 +2969,13 @@
         <v>1</v>
       </c>
       <c r="N34" s="6" t="n">
-        <v>0.01358604481670545</v>
+        <v>0.01363467695406731</v>
       </c>
       <c r="O34" s="6" t="n">
-        <v>0.01358604481670545</v>
+        <v>0.01363467695406731</v>
       </c>
       <c r="P34" s="6" t="n">
-        <v>0.001803955183294552</v>
+        <v>0.001755323045932687</v>
       </c>
       <c r="Q34" s="6" t="n">
         <v>0</v>
@@ -3034,13 +3034,13 @@
         <v>1</v>
       </c>
       <c r="N35" s="6" t="n">
-        <v>0.003560390490784686</v>
+        <v>0.003573135141766317</v>
       </c>
       <c r="O35" s="6" t="n">
-        <v>0.003560390490784686</v>
+        <v>0.003573135141766317</v>
       </c>
       <c r="P35" s="6" t="n">
-        <v>8.466828609509216</v>
+        <v>8.466815864858233</v>
       </c>
       <c r="Q35" s="6" t="n">
         <v>0</v>
@@ -3099,13 +3099,13 @@
         <v>1</v>
       </c>
       <c r="N36" s="6" t="n">
-        <v>0.0003557398176915182</v>
+        <v>0.000357013211671331</v>
       </c>
       <c r="O36" s="6" t="n">
-        <v>0.0003557398176915182</v>
+        <v>0.000357013211671331</v>
       </c>
       <c r="P36" s="6" t="n">
-        <v>0.0003782601823084818</v>
+        <v>0.0003769867883286691</v>
       </c>
       <c r="Q36" s="6" t="n">
         <v>0</v>
@@ -3164,13 +3164,13 @@
         <v>1</v>
       </c>
       <c r="N37" s="6" t="n">
-        <v>0.0001331061372759938</v>
+        <v>0.0001335825994133595</v>
       </c>
       <c r="O37" s="6" t="n">
-        <v>0.0001331061372759938</v>
+        <v>0.0001335825994133595</v>
       </c>
       <c r="P37" s="6" t="n">
-        <v>5.289386272400622e-05</v>
+        <v>5.241740058664053e-05</v>
       </c>
       <c r="Q37" s="6" t="n">
         <v>0</v>
@@ -3229,13 +3229,13 @@
         <v>1</v>
       </c>
       <c r="N38" s="6" t="n">
-        <v>1.461834011999129e-05</v>
+        <v>1.467066742601075e-05</v>
       </c>
       <c r="O38" s="6" t="n">
-        <v>1.461834011999129e-05</v>
+        <v>1.467066742601075e-05</v>
       </c>
       <c r="P38" s="6" t="n">
-        <v>2.381659880008713e-06</v>
+        <v>2.32933257398925e-06</v>
       </c>
       <c r="Q38" s="6" t="n">
         <v>0</v>
@@ -3294,13 +3294,13 @@
         <v>1</v>
       </c>
       <c r="N39" s="6" t="n">
-        <v>1.32322540114338e-05</v>
+        <v>1.327961973143347e-05</v>
       </c>
       <c r="O39" s="6" t="n">
-        <v>1.32322540114338e-05</v>
+        <v>1.327961973143347e-05</v>
       </c>
       <c r="P39" s="6" t="n">
-        <v>-1.10884295060638e-05</v>
+        <v>-1.113579522606348e-05</v>
       </c>
       <c r="Q39" s="6" t="n">
         <v>0</v>
@@ -3359,13 +3359,13 @@
         <v>1</v>
       </c>
       <c r="N40" s="6" t="n">
-        <v>3.9160381664017e-06</v>
+        <v>3.930055881534553e-06</v>
       </c>
       <c r="O40" s="6" t="n">
-        <v>3.9160381664017e-06</v>
+        <v>3.930055881534553e-06</v>
       </c>
       <c r="P40" s="6" t="n">
-        <v>1.0839618335983e-06</v>
+        <v>1.069944118465447e-06</v>
       </c>
       <c r="Q40" s="6" t="n">
         <v>0</v>
@@ -3424,13 +3424,13 @@
         <v>1</v>
       </c>
       <c r="N41" s="6" t="n">
-        <v>2.856737565633293e-06</v>
+        <v>2.866963444877255e-06</v>
       </c>
       <c r="O41" s="6" t="n">
-        <v>2.856737565633293e-06</v>
+        <v>2.866963444877255e-06</v>
       </c>
       <c r="P41" s="6" t="n">
-        <v>-2.856737565633293e-06</v>
+        <v>-2.866963444877255e-06</v>
       </c>
       <c r="Q41" s="6" t="n">
         <v>0</v>
@@ -3489,13 +3489,13 @@
         <v>1</v>
       </c>
       <c r="N42" s="6" t="n">
-        <v>1.200073500014567e-06</v>
+        <v>1.2043692417175e-06</v>
       </c>
       <c r="O42" s="6" t="n">
-        <v>1.200073500014567e-06</v>
+        <v>1.2043692417175e-06</v>
       </c>
       <c r="P42" s="6" t="n">
-        <v>-4.933666932055665e-07</v>
+        <v>-4.976624349084999e-07</v>
       </c>
       <c r="Q42" s="6" t="n">
         <v>0</v>
@@ -3554,13 +3554,13 @@
         <v>1</v>
       </c>
       <c r="N43" s="6" t="n">
-        <v>1.725274558453813e-07</v>
+        <v>1.731450291748208e-07</v>
       </c>
       <c r="O43" s="6" t="n">
-        <v>1.725274558453813e-07</v>
+        <v>1.731450291748208e-07</v>
       </c>
       <c r="P43" s="6" t="n">
-        <v>-1.725274558453813e-07</v>
+        <v>-1.731450291748208e-07</v>
       </c>
       <c r="Q43" s="6" t="n">
         <v>0</v>
@@ -4687,11 +4687,11 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Reference rate (effr), period avg</t>
+          <t>Reference rate (tbill_3m), period avg</t>
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>0.03628709677419355</v>
+        <v>0.03685483870967742</v>
       </c>
     </row>
     <row r="10">
@@ -4701,7 +4701,7 @@
         </is>
       </c>
       <c r="B10" s="7" t="n">
-        <v>0.03682465368903005</v>
+        <v>0.03729777196859994</v>
       </c>
     </row>
     <row r="11">
@@ -4711,7 +4711,7 @@
         </is>
       </c>
       <c r="B11" s="10" t="n">
-        <v>0.03871416843742665</v>
+        <v>0.038855162511856</v>
       </c>
     </row>
     <row r="12">
@@ -4721,7 +4721,7 @@
         </is>
       </c>
       <c r="B12" s="11" t="n">
-        <v>-8.009872259572633</v>
+        <v>-6.599931515279089</v>
       </c>
     </row>
     <row r="13">
@@ -4731,7 +4731,7 @@
         </is>
       </c>
       <c r="B13" s="12" t="n">
-        <v>219906.399780756</v>
+        <v>181155.816974199</v>
       </c>
     </row>
     <row r="15">
@@ -4751,7 +4751,7 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>10825499.00626334</v>
+        <v>10864249.5890699</v>
       </c>
     </row>
     <row r="17">
@@ -4761,7 +4761,7 @@
         </is>
       </c>
       <c r="B17" s="12" t="n">
-        <v>219906.399780756</v>
+        <v>181155.816974199</v>
       </c>
     </row>
     <row r="19">
@@ -4791,7 +4791,7 @@
         <v>1000000000</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>3071515.028317151</v>
+        <v>3110265.611123708</v>
       </c>
     </row>
     <row r="21">
@@ -4826,7 +4826,7 @@
         </is>
       </c>
       <c r="B24" s="3" t="n">
-        <v>10640588.58756836</v>
+        <v>10679339.17037492</v>
       </c>
     </row>
     <row r="25">
@@ -4846,7 +4846,7 @@
         </is>
       </c>
       <c r="B26" s="3" t="n">
-        <v>10681122.54508365</v>
+        <v>10719873.1278902</v>
       </c>
     </row>
     <row r="28">
@@ -4863,7 +4863,7 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>13391864.98596525</v>
+        <v>13430615.56877181</v>
       </c>
     </row>
     <row r="31">
@@ -4873,7 +4873,7 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>10640588.58756836</v>
+        <v>10679339.17037492</v>
       </c>
     </row>
     <row r="32">
@@ -4967,7 +4967,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>effr</t>
+          <t>tbill_3m</t>
         </is>
       </c>
     </row>
@@ -5413,16 +5413,16 @@
         <v>4</v>
       </c>
       <c r="L6" s="7" t="n">
-        <v>0.0364</v>
+        <v>0.0368</v>
       </c>
       <c r="M6" s="7" t="n">
-        <v>0.03693491707043663</v>
+        <v>0.03726825040376996</v>
       </c>
       <c r="N6" s="3" t="n">
-        <v>337334.6074229946</v>
+        <v>338215.2667380225</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>414243.5423272011</v>
+        <v>415124.201642229</v>
       </c>
     </row>
     <row r="7">
@@ -5462,16 +5462,16 @@
         <v>4</v>
       </c>
       <c r="L7" s="7" t="n">
-        <v>0.0364</v>
+        <v>0.0368</v>
       </c>
       <c r="M7" s="7" t="n">
-        <v>0.03693491707043663</v>
+        <v>0.03726825040376996</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>374272.6793009383</v>
+        <v>375153.3386159662</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>450593.1931929035</v>
+        <v>451473.8525079314</v>
       </c>
     </row>
     <row r="8">
@@ -5511,16 +5511,16 @@
         <v>4</v>
       </c>
       <c r="L8" s="7" t="n">
-        <v>0.0364</v>
+        <v>0.0368</v>
       </c>
       <c r="M8" s="7" t="n">
-        <v>0.03693491707043663</v>
+        <v>0.03726825040376996</v>
       </c>
       <c r="N8" s="3" t="n">
-        <v>373622.2203959758</v>
+        <v>374502.8797110037</v>
       </c>
       <c r="O8" s="3" t="n">
-        <v>450469.9897907797</v>
+        <v>451350.6491058076</v>
       </c>
     </row>
     <row r="9">
@@ -5560,16 +5560,16 @@
         <v>4</v>
       </c>
       <c r="L9" s="7" t="n">
-        <v>0.0364</v>
+        <v>0.037</v>
       </c>
       <c r="M9" s="7" t="n">
-        <v>0.03693491707043663</v>
+        <v>0.03743491707043663</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>363498.7068655675</v>
+        <v>364819.5900073207</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>439555.1003258834</v>
+        <v>440875.9834676367</v>
       </c>
     </row>
     <row r="10">
@@ -5609,16 +5609,16 @@
         <v>4</v>
       </c>
       <c r="L10" s="7" t="n">
-        <v>0.0364</v>
+        <v>0.0369</v>
       </c>
       <c r="M10" s="7" t="n">
-        <v>0.03693491707043663</v>
+        <v>0.0373515837371033</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>358810.6035501668</v>
+        <v>359911.3835955046</v>
       </c>
       <c r="O10" s="3" t="n">
-        <v>434343.0916681122</v>
+        <v>435443.8717134499</v>
       </c>
     </row>
     <row r="11">
@@ -5658,16 +5658,16 @@
         <v>4</v>
       </c>
       <c r="L11" s="7" t="n">
-        <v>0.0364</v>
+        <v>0.0369</v>
       </c>
       <c r="M11" s="7" t="n">
-        <v>0.03693491707043663</v>
+        <v>0.0373515837371033</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>336881.6142373614</v>
+        <v>337982.3942826991</v>
       </c>
       <c r="O11" s="3" t="n">
-        <v>412771.0234410728</v>
+        <v>413871.8034864106</v>
       </c>
     </row>
     <row r="12">
@@ -5707,16 +5707,16 @@
         <v>4</v>
       </c>
       <c r="L12" s="7" t="n">
-        <v>0.0364</v>
+        <v>0.0369</v>
       </c>
       <c r="M12" s="7" t="n">
-        <v>0.03693491707043663</v>
+        <v>0.0373515837371033</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>343781.6670466586</v>
+        <v>344882.4470919963</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>419001.6270619906</v>
+        <v>420102.4071073283</v>
       </c>
     </row>
     <row r="13">
@@ -5756,16 +5756,16 @@
         <v>4</v>
       </c>
       <c r="L13" s="7" t="n">
-        <v>0.0364</v>
+        <v>0.0369</v>
       </c>
       <c r="M13" s="7" t="n">
-        <v>0.03693491707043663</v>
+        <v>0.0373515837371033</v>
       </c>
       <c r="N13" s="3" t="n">
-        <v>265801.2902985573</v>
+        <v>266902.0703438951</v>
       </c>
       <c r="O13" s="3" t="n">
-        <v>339216.1773025376</v>
+        <v>340316.9573478753</v>
       </c>
     </row>
     <row r="14">
@@ -5805,16 +5805,16 @@
         <v>4</v>
       </c>
       <c r="L14" s="7" t="n">
-        <v>0.0364</v>
+        <v>0.0369</v>
       </c>
       <c r="M14" s="7" t="n">
-        <v>0.03693491707043663</v>
+        <v>0.0373515837371033</v>
       </c>
       <c r="N14" s="3" t="n">
-        <v>347654.8323519505</v>
+        <v>348755.6123972882</v>
       </c>
       <c r="O14" s="3" t="n">
-        <v>422617.4327683006</v>
+        <v>423718.2128136383</v>
       </c>
     </row>
     <row r="15">
@@ -5854,16 +5854,16 @@
         <v>4</v>
       </c>
       <c r="L15" s="7" t="n">
-        <v>0.0364</v>
+        <v>0.0369</v>
       </c>
       <c r="M15" s="7" t="n">
-        <v>0.03693491707043663</v>
+        <v>0.0373515837371033</v>
       </c>
       <c r="N15" s="3" t="n">
-        <v>362990.4740527779</v>
+        <v>364091.2540981157</v>
       </c>
       <c r="O15" s="3" t="n">
-        <v>438829.0783037072</v>
+        <v>439929.858349045</v>
       </c>
     </row>
     <row r="16">
@@ -5903,16 +5903,16 @@
         <v>4</v>
       </c>
       <c r="L16" s="7" t="n">
-        <v>0.0363</v>
+        <v>0.037</v>
       </c>
       <c r="M16" s="7" t="n">
-        <v>0.0368515837371033</v>
+        <v>0.03743491707043663</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>352279.0442647091</v>
+        <v>353820.1363477663</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>431507.6703348673</v>
+        <v>433048.7624179245</v>
       </c>
     </row>
     <row r="17">
@@ -5952,16 +5952,16 @@
         <v>4</v>
       </c>
       <c r="L17" s="7" t="n">
-        <v>0.0363</v>
+        <v>0.037</v>
       </c>
       <c r="M17" s="7" t="n">
-        <v>0.0368515837371033</v>
+        <v>0.03743491707043663</v>
       </c>
       <c r="N17" s="3" t="n">
-        <v>345666.1373893456</v>
+        <v>347207.2294724027</v>
       </c>
       <c r="O17" s="3" t="n">
-        <v>423171.9641792552</v>
+        <v>424713.0562623124</v>
       </c>
     </row>
     <row r="18">
@@ -6001,16 +6001,16 @@
         <v>4</v>
       </c>
       <c r="L18" s="7" t="n">
-        <v>0.0363</v>
+        <v>0.0369</v>
       </c>
       <c r="M18" s="7" t="n">
-        <v>0.0368515837371033</v>
+        <v>0.0373515837371033</v>
       </c>
       <c r="N18" s="3" t="n">
-        <v>344727.0510100425</v>
+        <v>346048.0399966842</v>
       </c>
       <c r="O18" s="3" t="n">
-        <v>423267.6885049809</v>
+        <v>424588.6774916226</v>
       </c>
     </row>
     <row r="19">
@@ -6050,16 +6050,16 @@
         <v>4</v>
       </c>
       <c r="L19" s="7" t="n">
-        <v>0.0363</v>
+        <v>0.0369</v>
       </c>
       <c r="M19" s="7" t="n">
-        <v>0.0368515837371033</v>
+        <v>0.0373515837371033</v>
       </c>
       <c r="N19" s="3" t="n">
-        <v>348443.1706486071</v>
+        <v>349764.1596352488</v>
       </c>
       <c r="O19" s="3" t="n">
-        <v>427360.7512641225</v>
+        <v>428681.7402507642</v>
       </c>
     </row>
     <row r="20">
@@ -6099,16 +6099,16 @@
         <v>4</v>
       </c>
       <c r="L20" s="7" t="n">
-        <v>0.0363</v>
+        <v>0.0369</v>
       </c>
       <c r="M20" s="7" t="n">
-        <v>0.0368515837371033</v>
+        <v>0.0373515837371033</v>
       </c>
       <c r="N20" s="3" t="n">
-        <v>351850.3264145331</v>
+        <v>353171.3154011748</v>
       </c>
       <c r="O20" s="3" t="n">
-        <v>431203.3537667908</v>
+        <v>432524.3427534325</v>
       </c>
     </row>
     <row r="21">
@@ -6148,16 +6148,16 @@
         <v>4</v>
       </c>
       <c r="L21" s="7" t="n">
-        <v>0.0363</v>
+        <v>0.0369</v>
       </c>
       <c r="M21" s="7" t="n">
-        <v>0.0368515837371033</v>
+        <v>0.0373515837371033</v>
       </c>
       <c r="N21" s="3" t="n">
-        <v>351632.6009997061</v>
+        <v>352953.5899863477</v>
       </c>
       <c r="O21" s="3" t="n">
-        <v>432166.6729598901</v>
+        <v>433487.6619465318</v>
       </c>
     </row>
     <row r="22">
@@ -6197,16 +6197,16 @@
         <v>4</v>
       </c>
       <c r="L22" s="7" t="n">
-        <v>0.0363</v>
+        <v>0.0369</v>
       </c>
       <c r="M22" s="7" t="n">
-        <v>0.0368515837371033</v>
+        <v>0.0373515837371033</v>
       </c>
       <c r="N22" s="3" t="n">
-        <v>349424.2258454161</v>
+        <v>350745.2148320578</v>
       </c>
       <c r="O22" s="3" t="n">
-        <v>429946.6489242385</v>
+        <v>431267.6379108802</v>
       </c>
     </row>
     <row r="23">
@@ -6246,16 +6246,16 @@
         <v>4</v>
       </c>
       <c r="L23" s="7" t="n">
-        <v>0.0362</v>
+        <v>0.0368</v>
       </c>
       <c r="M23" s="7" t="n">
-        <v>0.03676825040376996</v>
+        <v>0.03726825040376996</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>365709.4116342401</v>
+        <v>367030.5064828676</v>
       </c>
       <c r="O23" s="3" t="n">
-        <v>451824.132648079</v>
+        <v>453145.2274967065</v>
       </c>
     </row>
     <row r="24">
@@ -6295,16 +6295,16 @@
         <v>4</v>
       </c>
       <c r="L24" s="7" t="n">
-        <v>0.0362</v>
+        <v>0.0367</v>
       </c>
       <c r="M24" s="7" t="n">
-        <v>0.03676825040376996</v>
+        <v>0.03718491707043663</v>
       </c>
       <c r="N24" s="3" t="n">
-        <v>361107.8874086158</v>
+        <v>362208.8438903746</v>
       </c>
       <c r="O24" s="3" t="n">
-        <v>448566.8371441148</v>
+        <v>449667.7936258736</v>
       </c>
     </row>
     <row r="25">
@@ -6344,16 +6344,16 @@
         <v>4</v>
       </c>
       <c r="L25" s="7" t="n">
-        <v>0.0362</v>
+        <v>0.0365</v>
       </c>
       <c r="M25" s="7" t="n">
-        <v>0.03676825040376996</v>
+        <v>0.03701825040376996</v>
       </c>
       <c r="N25" s="3" t="n">
-        <v>333665.3148069651</v>
+        <v>334325.9416342076</v>
       </c>
       <c r="O25" s="3" t="n">
-        <v>420743.9106240411</v>
+        <v>421404.5374512835</v>
       </c>
     </row>
     <row r="26">
@@ -6393,16 +6393,16 @@
         <v>4</v>
       </c>
       <c r="L26" s="7" t="n">
-        <v>0.0362</v>
+        <v>0.0368</v>
       </c>
       <c r="M26" s="7" t="n">
-        <v>0.03676825040376996</v>
+        <v>0.03726825040376996</v>
       </c>
       <c r="N26" s="3" t="n">
-        <v>324962.3908041572</v>
+        <v>326283.4856527848</v>
       </c>
       <c r="O26" s="3" t="n">
-        <v>414829.2237389592</v>
+        <v>416150.3185875867</v>
       </c>
     </row>
     <row r="27">
@@ -6442,16 +6442,16 @@
         <v>4</v>
       </c>
       <c r="L27" s="7" t="n">
-        <v>0.0362</v>
+        <v>0.0368</v>
       </c>
       <c r="M27" s="7" t="n">
-        <v>0.03676825040376996</v>
+        <v>0.03726825040376996</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>379185.8060542876</v>
+        <v>380506.9009029152</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>468277.7087264755</v>
+        <v>469598.8035751031</v>
       </c>
     </row>
     <row r="28">
@@ -6491,16 +6491,16 @@
         <v>4</v>
       </c>
       <c r="L28" s="7" t="n">
-        <v>0.0362</v>
+        <v>0.0368</v>
       </c>
       <c r="M28" s="7" t="n">
-        <v>0.03676825040376996</v>
+        <v>0.03726825040376996</v>
       </c>
       <c r="N28" s="3" t="n">
-        <v>377000.5347091127</v>
+        <v>378321.6295577402</v>
       </c>
       <c r="O28" s="3" t="n">
-        <v>466500.1759430798</v>
+        <v>467821.2707917073</v>
       </c>
     </row>
     <row r="29">
@@ -6540,16 +6540,16 @@
         <v>4</v>
       </c>
       <c r="L29" s="7" t="n">
-        <v>0.0362</v>
+        <v>0.0368</v>
       </c>
       <c r="M29" s="7" t="n">
-        <v>0.03676825040376996</v>
+        <v>0.03726825040376996</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>378608.4459296824</v>
+        <v>379929.5407783099</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>468472.6929685309</v>
+        <v>469793.7878171585</v>
       </c>
     </row>
     <row r="30">
@@ -6589,16 +6589,16 @@
         <v>4</v>
       </c>
       <c r="L30" s="7" t="n">
-        <v>0.0362</v>
+        <v>0.0368</v>
       </c>
       <c r="M30" s="7" t="n">
-        <v>0.03676825040376996</v>
+        <v>0.03726825040376996</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>378008.3403677623</v>
+        <v>379329.4352163898</v>
       </c>
       <c r="O30" s="3" t="n">
-        <v>468212.9843232642</v>
+        <v>469534.0791718918</v>
       </c>
     </row>
     <row r="31">
@@ -6638,16 +6638,16 @@
         <v>4</v>
       </c>
       <c r="L31" s="7" t="n">
-        <v>0.0362</v>
+        <v>0.0368</v>
       </c>
       <c r="M31" s="7" t="n">
-        <v>0.03668466737761376</v>
+        <v>0.03718466737761376</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>352337.3261667297</v>
+        <v>353658.5272115202</v>
       </c>
       <c r="O31" s="3" t="n">
-        <v>435181.9142288258</v>
+        <v>436503.1152736163</v>
       </c>
     </row>
     <row r="32">
@@ -6687,16 +6687,16 @@
         <v>4</v>
       </c>
       <c r="L32" s="7" t="n">
-        <v>0.0362</v>
+        <v>0.0368</v>
       </c>
       <c r="M32" s="7" t="n">
-        <v>0.03668466737761376</v>
+        <v>0.03718466737761376</v>
       </c>
       <c r="N32" s="3" t="n">
-        <v>335363.1836146039</v>
+        <v>336684.3846593943</v>
       </c>
       <c r="O32" s="3" t="n">
-        <v>421508.318950465</v>
+        <v>422829.5199952555</v>
       </c>
     </row>
     <row r="33">
@@ -6736,16 +6736,16 @@
         <v>4</v>
       </c>
       <c r="L33" s="7" t="n">
-        <v>0.0362</v>
+        <v>0.0369</v>
       </c>
       <c r="M33" s="7" t="n">
-        <v>0.03668466737761376</v>
+        <v>0.0372680007109471</v>
       </c>
       <c r="N33" s="3" t="n">
-        <v>332053.2827393732</v>
+        <v>333594.622203879</v>
       </c>
       <c r="O33" s="3" t="n">
-        <v>422626.9512378465</v>
+        <v>424168.2907023524</v>
       </c>
     </row>
     <row r="34">
@@ -6785,16 +6785,16 @@
         <v>4</v>
       </c>
       <c r="L34" s="7" t="n">
-        <v>0.0362</v>
+        <v>0.0369</v>
       </c>
       <c r="M34" s="7" t="n">
-        <v>0.03668466737761376</v>
+        <v>0.0372680007109471</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>334722.5280083754</v>
+        <v>336263.8674728812</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>430938.0887659761</v>
+        <v>432479.428230482</v>
       </c>
     </row>
     <row r="35">
@@ -6834,16 +6834,16 @@
         <v>4</v>
       </c>
       <c r="L35" s="7" t="n">
-        <v>0.0362</v>
+        <v>0.0369</v>
       </c>
       <c r="M35" s="7" t="n">
-        <v>0.03668466737761376</v>
+        <v>0.0372680007109471</v>
       </c>
       <c r="N35" s="3" t="n">
-        <v>332371.9440256246</v>
+        <v>333913.2834901304</v>
       </c>
       <c r="O35" s="3" t="n">
-        <v>427593.374089083</v>
+        <v>429134.7135535888</v>
       </c>
     </row>
     <row r="36">
@@ -6883,16 +6883,16 @@
         <v>4</v>
       </c>
       <c r="L36" s="7" t="n">
-        <v>0.0362</v>
+        <v>0.0369</v>
       </c>
       <c r="M36" s="7" t="n">
-        <v>0.03668466737761376</v>
+        <v>0.0372680007109471</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>331731.357898502</v>
+        <v>333272.6973630079</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>426323.6664598752</v>
+        <v>427865.005924381</v>
       </c>
     </row>
     <row r="38">
@@ -6914,10 +6914,10 @@
       <c r="L38" t="inlineStr"/>
       <c r="M38" t="inlineStr"/>
       <c r="N38" s="12" t="n">
-        <v>10825499.00626334</v>
+        <v>10864249.5890699</v>
       </c>
       <c r="O38" s="12" t="n">
-        <v>13391864.98596525</v>
+        <v>13430615.56877181</v>
       </c>
     </row>
   </sheetData>

--- a/settlements/spark/2026-05/spark_settlement_may_2026.xlsx
+++ b/settlements/spark/2026-05/spark_settlement_may_2026.xlsx
@@ -511,13 +511,13 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>1632540.8</v>
+        <v>1629543.84</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr"/>
       <c r="B7" s="4" t="n">
-        <v>15354508.16630362</v>
+        <v>15351511.20630362</v>
       </c>
     </row>
     <row r="9">

--- a/settlements/spark/2026-05/spark_settlement_may_2026.xlsx
+++ b/settlements/spark/2026-05/spark_settlement_may_2026.xlsx
@@ -4677,7 +4677,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Base rate (BR = SSR + 30bps), period avg</t>
+          <t>Base rate (BR = SSR (+) spread; 30bps, 20bps from 2026-07-23), period avg</t>
         </is>
       </c>
       <c r="B8" s="7" t="n">
@@ -4896,7 +4896,7 @@
     <row r="35" ht="60" customHeight="1">
       <c r="A35" s="13" t="inlineStr">
         <is>
-          <t>sUSDS spread (Curve LP + PSM3) — 30 bps × value × n_days deducted from sky_revenue. Sky charges full BR on the underlying utilized; this row is the offsetting refund to the prime so SSR + BR + 30 bps nets to zero economically.</t>
+          <t>sUSDS spread (Curve LP + PSM3) — the BR−SSR spread (30 bps; 20 bps from 2026-07-23) × value, integrated daily, deducted from sky_revenue. Sky charges full BR on the underlying utilized; this row is the offsetting refund to the prime so SSR + BR + spread nets to zero economically.</t>
         </is>
       </c>
       <c r="B35" s="3" t="n">
@@ -4967,7 +4967,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>tbill_3m</t>
+          <t>tbill_3m→sofr@2026-07-23</t>
         </is>
       </c>
     </row>
@@ -4998,7 +4998,7 @@
     <row r="46">
       <c r="A46" s="5" t="inlineStr">
         <is>
-          <t>Base rate composition: base_apy = (1 + SSR)(1 + 30bps) − 1 (multiplicative)</t>
+          <t>Base rate composition: base_apy = (1 + SSR)(1 + spread) − 1 (multiplicative; spread 30bps, 20bps from 2026-07-23)</t>
         </is>
       </c>
     </row>
@@ -5296,7 +5296,7 @@
     <row r="3" ht="45" customHeight="1">
       <c r="A3" s="13" t="inlineStr">
         <is>
-          <t>cum_debt = Σ on-chain Vat dart from frob (0x76088703) + grab (0x7bab3f40), then scaled by Vat.ilks[ilk].rate_d / 1e27 read at each day's EoD block — actual outstanding USDS per day, not raw normalised Art. utilized = cum_debt − Σ deductions. base_apy = (1+SSR)(1+0.003)−1 (multiplicative). sub_apy applies on the first cap_usd of utilized when the subsidy is active; excess pays base_apy.</t>
+          <t>cum_debt = Σ on-chain Vat dart from frob (0x76088703) + grab (0x7bab3f40), then scaled by Vat.ilks[ilk].rate_d / 1e27 read at each day's EoD block — actual outstanding USDS per day, not raw normalised Art. utilized = cum_debt − Σ deductions. base_apy = (1+SSR)(1+spread)−1 (multiplicative; spread 30bps, 20bps from 2026-07-23). sub_apy applies on the first cap_usd of utilized when the subsidy is active; excess pays base_apy.</t>
         </is>
       </c>
     </row>
